--- a/MedinaCares_Test_Plan.xlsx
+++ b/MedinaCares_Test_Plan.xlsx
@@ -1014,30 +1014,30 @@
         </is>
       </c>
       <c r="B6" s="13" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C6" s="14">
-        <f>COUNTIF('iOS'!$E$3:$E$101,"Pass")</f>
+        <f>COUNTIF('iOS'!$E$3:$E$105,"Pass")</f>
         <v/>
       </c>
       <c r="D6" s="14">
-        <f>COUNTIF('iOS'!$E$3:$E$101,"Fail")</f>
+        <f>COUNTIF('iOS'!$E$3:$E$105,"Fail")</f>
         <v/>
       </c>
       <c r="E6" s="14">
-        <f>COUNTIF('iOS'!$E$3:$E$101,"Blocked")</f>
+        <f>COUNTIF('iOS'!$E$3:$E$105,"Blocked")</f>
         <v/>
       </c>
       <c r="F6" s="14">
-        <f>COUNTIF('iOS'!$E$3:$E$101,"Not tested")</f>
+        <f>COUNTIF('iOS'!$E$3:$E$105,"Not tested")</f>
         <v/>
       </c>
       <c r="G6" s="14">
-        <f>$B6-COUNTA('iOS'!$E$3:$E$101)</f>
+        <f>$B6-COUNTA('iOS'!$E$3:$E$105)</f>
         <v/>
       </c>
       <c r="H6" s="15">
-        <f>IF($B6=0,0,(COUNTIF('iOS'!$E$3:$E$101,"Pass")+COUNTIF('iOS'!$E$3:$E$101,"Fail")+COUNTIF('iOS'!$E$3:$E$101,"Blocked")+COUNTIF('iOS'!$E$3:$E$101,"Not tested"))/$B6)</f>
+        <f>IF($B6=0,0,(COUNTIF('iOS'!$E$3:$E$105,"Pass")+COUNTIF('iOS'!$E$3:$E$105,"Fail")+COUNTIF('iOS'!$E$3:$E$105,"Blocked")+COUNTIF('iOS'!$E$3:$E$105,"Not tested"))/$B6)</f>
         <v/>
       </c>
     </row>
@@ -1048,30 +1048,30 @@
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C7" s="14">
-        <f>COUNTIF('Android'!$E$3:$E$101,"Pass")</f>
+        <f>COUNTIF('Android'!$E$3:$E$105,"Pass")</f>
         <v/>
       </c>
       <c r="D7" s="14">
-        <f>COUNTIF('Android'!$E$3:$E$101,"Fail")</f>
+        <f>COUNTIF('Android'!$E$3:$E$105,"Fail")</f>
         <v/>
       </c>
       <c r="E7" s="14">
-        <f>COUNTIF('Android'!$E$3:$E$101,"Blocked")</f>
+        <f>COUNTIF('Android'!$E$3:$E$105,"Blocked")</f>
         <v/>
       </c>
       <c r="F7" s="14">
-        <f>COUNTIF('Android'!$E$3:$E$101,"Not tested")</f>
+        <f>COUNTIF('Android'!$E$3:$E$105,"Not tested")</f>
         <v/>
       </c>
       <c r="G7" s="14">
-        <f>$B7-COUNTA('Android'!$E$3:$E$101)</f>
+        <f>$B7-COUNTA('Android'!$E$3:$E$105)</f>
         <v/>
       </c>
       <c r="H7" s="15">
-        <f>IF($B7=0,0,(COUNTIF('Android'!$E$3:$E$101,"Pass")+COUNTIF('Android'!$E$3:$E$101,"Fail")+COUNTIF('Android'!$E$3:$E$101,"Blocked")+COUNTIF('Android'!$E$3:$E$101,"Not tested"))/$B7)</f>
+        <f>IF($B7=0,0,(COUNTIF('Android'!$E$3:$E$105,"Pass")+COUNTIF('Android'!$E$3:$E$105,"Fail")+COUNTIF('Android'!$E$3:$E$105,"Blocked")+COUNTIF('Android'!$E$3:$E$105,"Not tested"))/$B7)</f>
         <v/>
       </c>
     </row>
@@ -1082,30 +1082,30 @@
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C8" s="14">
-        <f>COUNTIF('Desktop Chrome'!$E$3:$E$101,"Pass")</f>
+        <f>COUNTIF('Desktop Chrome'!$E$3:$E$105,"Pass")</f>
         <v/>
       </c>
       <c r="D8" s="14">
-        <f>COUNTIF('Desktop Chrome'!$E$3:$E$101,"Fail")</f>
+        <f>COUNTIF('Desktop Chrome'!$E$3:$E$105,"Fail")</f>
         <v/>
       </c>
       <c r="E8" s="14">
-        <f>COUNTIF('Desktop Chrome'!$E$3:$E$101,"Blocked")</f>
+        <f>COUNTIF('Desktop Chrome'!$E$3:$E$105,"Blocked")</f>
         <v/>
       </c>
       <c r="F8" s="14">
-        <f>COUNTIF('Desktop Chrome'!$E$3:$E$101,"Not tested")</f>
+        <f>COUNTIF('Desktop Chrome'!$E$3:$E$105,"Not tested")</f>
         <v/>
       </c>
       <c r="G8" s="14">
-        <f>$B8-COUNTA('Desktop Chrome'!$E$3:$E$101)</f>
+        <f>$B8-COUNTA('Desktop Chrome'!$E$3:$E$105)</f>
         <v/>
       </c>
       <c r="H8" s="15">
-        <f>IF($B8=0,0,(COUNTIF('Desktop Chrome'!$E$3:$E$101,"Pass")+COUNTIF('Desktop Chrome'!$E$3:$E$101,"Fail")+COUNTIF('Desktop Chrome'!$E$3:$E$101,"Blocked")+COUNTIF('Desktop Chrome'!$E$3:$E$101,"Not tested"))/$B8)</f>
+        <f>IF($B8=0,0,(COUNTIF('Desktop Chrome'!$E$3:$E$105,"Pass")+COUNTIF('Desktop Chrome'!$E$3:$E$105,"Fail")+COUNTIF('Desktop Chrome'!$E$3:$E$105,"Blocked")+COUNTIF('Desktop Chrome'!$E$3:$E$105,"Not tested"))/$B8)</f>
         <v/>
       </c>
     </row>
@@ -1116,30 +1116,30 @@
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C9" s="14">
-        <f>COUNTIF('Desktop Firefox'!$E$3:$E$101,"Pass")</f>
+        <f>COUNTIF('Desktop Firefox'!$E$3:$E$105,"Pass")</f>
         <v/>
       </c>
       <c r="D9" s="14">
-        <f>COUNTIF('Desktop Firefox'!$E$3:$E$101,"Fail")</f>
+        <f>COUNTIF('Desktop Firefox'!$E$3:$E$105,"Fail")</f>
         <v/>
       </c>
       <c r="E9" s="14">
-        <f>COUNTIF('Desktop Firefox'!$E$3:$E$101,"Blocked")</f>
+        <f>COUNTIF('Desktop Firefox'!$E$3:$E$105,"Blocked")</f>
         <v/>
       </c>
       <c r="F9" s="14">
-        <f>COUNTIF('Desktop Firefox'!$E$3:$E$101,"Not tested")</f>
+        <f>COUNTIF('Desktop Firefox'!$E$3:$E$105,"Not tested")</f>
         <v/>
       </c>
       <c r="G9" s="14">
-        <f>$B9-COUNTA('Desktop Firefox'!$E$3:$E$101)</f>
+        <f>$B9-COUNTA('Desktop Firefox'!$E$3:$E$105)</f>
         <v/>
       </c>
       <c r="H9" s="15">
-        <f>IF($B9=0,0,(COUNTIF('Desktop Firefox'!$E$3:$E$101,"Pass")+COUNTIF('Desktop Firefox'!$E$3:$E$101,"Fail")+COUNTIF('Desktop Firefox'!$E$3:$E$101,"Blocked")+COUNTIF('Desktop Firefox'!$E$3:$E$101,"Not tested"))/$B9)</f>
+        <f>IF($B9=0,0,(COUNTIF('Desktop Firefox'!$E$3:$E$105,"Pass")+COUNTIF('Desktop Firefox'!$E$3:$E$105,"Fail")+COUNTIF('Desktop Firefox'!$E$3:$E$105,"Blocked")+COUNTIF('Desktop Firefox'!$E$3:$E$105,"Not tested"))/$B9)</f>
         <v/>
       </c>
     </row>
@@ -1150,30 +1150,30 @@
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C10" s="14">
-        <f>COUNTIF('Desktop Other'!$E$3:$E$101,"Pass")</f>
+        <f>COUNTIF('Desktop Other'!$E$3:$E$105,"Pass")</f>
         <v/>
       </c>
       <c r="D10" s="14">
-        <f>COUNTIF('Desktop Other'!$E$3:$E$101,"Fail")</f>
+        <f>COUNTIF('Desktop Other'!$E$3:$E$105,"Fail")</f>
         <v/>
       </c>
       <c r="E10" s="14">
-        <f>COUNTIF('Desktop Other'!$E$3:$E$101,"Blocked")</f>
+        <f>COUNTIF('Desktop Other'!$E$3:$E$105,"Blocked")</f>
         <v/>
       </c>
       <c r="F10" s="14">
-        <f>COUNTIF('Desktop Other'!$E$3:$E$101,"Not tested")</f>
+        <f>COUNTIF('Desktop Other'!$E$3:$E$105,"Not tested")</f>
         <v/>
       </c>
       <c r="G10" s="14">
-        <f>$B10-COUNTA('Desktop Other'!$E$3:$E$101)</f>
+        <f>$B10-COUNTA('Desktop Other'!$E$3:$E$105)</f>
         <v/>
       </c>
       <c r="H10" s="15">
-        <f>IF($B10=0,0,(COUNTIF('Desktop Other'!$E$3:$E$101,"Pass")+COUNTIF('Desktop Other'!$E$3:$E$101,"Fail")+COUNTIF('Desktop Other'!$E$3:$E$101,"Blocked")+COUNTIF('Desktop Other'!$E$3:$E$101,"Not tested"))/$B10)</f>
+        <f>IF($B10=0,0,(COUNTIF('Desktop Other'!$E$3:$E$105,"Pass")+COUNTIF('Desktop Other'!$E$3:$E$105,"Fail")+COUNTIF('Desktop Other'!$E$3:$E$105,"Blocked")+COUNTIF('Desktop Other'!$E$3:$E$105,"Not tested"))/$B10)</f>
         <v/>
       </c>
     </row>
@@ -1288,27 +1288,27 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIF('iOS'!$E$36:$E$44,"Pass")</f>
+        <f>COUNTIF('iOS'!$E$36:$E$48,"Pass")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIF('Android'!$E$36:$E$44,"Pass")</f>
+        <f>COUNTIF('Android'!$E$36:$E$48,"Pass")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIF('Desktop Chrome'!$E$36:$E$44,"Pass")</f>
+        <f>COUNTIF('Desktop Chrome'!$E$36:$E$48,"Pass")</f>
         <v/>
       </c>
       <c r="E16" s="13">
-        <f>COUNTIF('Desktop Firefox'!$E$36:$E$44,"Pass")</f>
+        <f>COUNTIF('Desktop Firefox'!$E$36:$E$48,"Pass")</f>
         <v/>
       </c>
       <c r="F16" s="13">
-        <f>COUNTIF('Desktop Other'!$E$36:$E$44,"Pass")</f>
+        <f>COUNTIF('Desktop Other'!$E$36:$E$48,"Pass")</f>
         <v/>
       </c>
       <c r="G16" s="13" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17">
@@ -1318,23 +1318,23 @@
         </is>
       </c>
       <c r="B17" s="13">
-        <f>COUNTIF('iOS'!$E$46:$E$50,"Pass")</f>
+        <f>COUNTIF('iOS'!$E$50:$E$54,"Pass")</f>
         <v/>
       </c>
       <c r="C17" s="13">
-        <f>COUNTIF('Android'!$E$46:$E$50,"Pass")</f>
+        <f>COUNTIF('Android'!$E$50:$E$54,"Pass")</f>
         <v/>
       </c>
       <c r="D17" s="13">
-        <f>COUNTIF('Desktop Chrome'!$E$46:$E$50,"Pass")</f>
+        <f>COUNTIF('Desktop Chrome'!$E$50:$E$54,"Pass")</f>
         <v/>
       </c>
       <c r="E17" s="13">
-        <f>COUNTIF('Desktop Firefox'!$E$46:$E$50,"Pass")</f>
+        <f>COUNTIF('Desktop Firefox'!$E$50:$E$54,"Pass")</f>
         <v/>
       </c>
       <c r="F17" s="13">
-        <f>COUNTIF('Desktop Other'!$E$46:$E$50,"Pass")</f>
+        <f>COUNTIF('Desktop Other'!$E$50:$E$54,"Pass")</f>
         <v/>
       </c>
       <c r="G17" s="13" t="n">
@@ -1348,23 +1348,23 @@
         </is>
       </c>
       <c r="B18" s="13">
-        <f>COUNTIF('iOS'!$E$52:$E$70,"Pass")</f>
+        <f>COUNTIF('iOS'!$E$56:$E$74,"Pass")</f>
         <v/>
       </c>
       <c r="C18" s="13">
-        <f>COUNTIF('Android'!$E$52:$E$70,"Pass")</f>
+        <f>COUNTIF('Android'!$E$56:$E$74,"Pass")</f>
         <v/>
       </c>
       <c r="D18" s="13">
-        <f>COUNTIF('Desktop Chrome'!$E$52:$E$70,"Pass")</f>
+        <f>COUNTIF('Desktop Chrome'!$E$56:$E$74,"Pass")</f>
         <v/>
       </c>
       <c r="E18" s="13">
-        <f>COUNTIF('Desktop Firefox'!$E$52:$E$70,"Pass")</f>
+        <f>COUNTIF('Desktop Firefox'!$E$56:$E$74,"Pass")</f>
         <v/>
       </c>
       <c r="F18" s="13">
-        <f>COUNTIF('Desktop Other'!$E$52:$E$70,"Pass")</f>
+        <f>COUNTIF('Desktop Other'!$E$56:$E$74,"Pass")</f>
         <v/>
       </c>
       <c r="G18" s="13" t="n">
@@ -1378,23 +1378,23 @@
         </is>
       </c>
       <c r="B19" s="13">
-        <f>COUNTIF('iOS'!$E$72:$E$85,"Pass")</f>
+        <f>COUNTIF('iOS'!$E$76:$E$89,"Pass")</f>
         <v/>
       </c>
       <c r="C19" s="13">
-        <f>COUNTIF('Android'!$E$72:$E$85,"Pass")</f>
+        <f>COUNTIF('Android'!$E$76:$E$89,"Pass")</f>
         <v/>
       </c>
       <c r="D19" s="13">
-        <f>COUNTIF('Desktop Chrome'!$E$72:$E$85,"Pass")</f>
+        <f>COUNTIF('Desktop Chrome'!$E$76:$E$89,"Pass")</f>
         <v/>
       </c>
       <c r="E19" s="13">
-        <f>COUNTIF('Desktop Firefox'!$E$72:$E$85,"Pass")</f>
+        <f>COUNTIF('Desktop Firefox'!$E$76:$E$89,"Pass")</f>
         <v/>
       </c>
       <c r="F19" s="13">
-        <f>COUNTIF('Desktop Other'!$E$72:$E$85,"Pass")</f>
+        <f>COUNTIF('Desktop Other'!$E$76:$E$89,"Pass")</f>
         <v/>
       </c>
       <c r="G19" s="13" t="n">
@@ -1408,23 +1408,23 @@
         </is>
       </c>
       <c r="B20" s="13">
-        <f>COUNTIF('iOS'!$E$87:$E$98,"Pass")</f>
+        <f>COUNTIF('iOS'!$E$91:$E$102,"Pass")</f>
         <v/>
       </c>
       <c r="C20" s="13">
-        <f>COUNTIF('Android'!$E$87:$E$98,"Pass")</f>
+        <f>COUNTIF('Android'!$E$91:$E$102,"Pass")</f>
         <v/>
       </c>
       <c r="D20" s="13">
-        <f>COUNTIF('Desktop Chrome'!$E$87:$E$98,"Pass")</f>
+        <f>COUNTIF('Desktop Chrome'!$E$91:$E$102,"Pass")</f>
         <v/>
       </c>
       <c r="E20" s="13">
-        <f>COUNTIF('Desktop Firefox'!$E$87:$E$98,"Pass")</f>
+        <f>COUNTIF('Desktop Firefox'!$E$91:$E$102,"Pass")</f>
         <v/>
       </c>
       <c r="F20" s="13">
-        <f>COUNTIF('Desktop Other'!$E$87:$E$98,"Pass")</f>
+        <f>COUNTIF('Desktop Other'!$E$91:$E$102,"Pass")</f>
         <v/>
       </c>
       <c r="G20" s="13" t="n">
@@ -1438,23 +1438,23 @@
         </is>
       </c>
       <c r="B21" s="13">
-        <f>COUNTIF('iOS'!$E$100:$E$101,"Pass")</f>
+        <f>COUNTIF('iOS'!$E$104:$E$105,"Pass")</f>
         <v/>
       </c>
       <c r="C21" s="13">
-        <f>COUNTIF('Android'!$E$100:$E$101,"Pass")</f>
+        <f>COUNTIF('Android'!$E$104:$E$105,"Pass")</f>
         <v/>
       </c>
       <c r="D21" s="13">
-        <f>COUNTIF('Desktop Chrome'!$E$100:$E$101,"Pass")</f>
+        <f>COUNTIF('Desktop Chrome'!$E$104:$E$105,"Pass")</f>
         <v/>
       </c>
       <c r="E21" s="13">
-        <f>COUNTIF('Desktop Firefox'!$E$100:$E$101,"Pass")</f>
+        <f>COUNTIF('Desktop Firefox'!$E$104:$E$105,"Pass")</f>
         <v/>
       </c>
       <c r="F21" s="13">
-        <f>COUNTIF('Desktop Other'!$E$100:$E$101,"Pass")</f>
+        <f>COUNTIF('Desktop Other'!$E$104:$E$105,"Pass")</f>
         <v/>
       </c>
       <c r="G21" s="13" t="n">
@@ -1475,7 +1475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:G105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2551,38 +2551,50 @@
       <c r="F44" s="22" t="n"/>
       <c r="G44" s="23" t="n"/>
     </row>
-    <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="19" t="inlineStr">
-        <is>
-          <t>Parent — viewer (grades 6–12 student)</t>
-        </is>
-      </c>
-      <c r="B45" s="20" t="n"/>
-      <c r="C45" s="20" t="n"/>
-      <c r="D45" s="20" t="n"/>
-      <c r="E45" s="20" t="n"/>
-      <c r="F45" s="20" t="n"/>
-      <c r="G45" s="20" t="n"/>
+    <row r="45" ht="42" customHeight="1">
+      <c r="A45" s="21" t="inlineStr">
+        <is>
+          <t>PE10</t>
+        </is>
+      </c>
+      <c r="B45" s="22" t="inlineStr">
+        <is>
+          <t>As a parent, I want to submit my child's hours after an event (child has no login).</t>
+        </is>
+      </c>
+      <c r="C45" s="22" t="inlineStr">
+        <is>
+          <t>Dashboard → the child's 'Submit hours (past events)' → enter hours → Submit.</t>
+        </is>
+      </c>
+      <c r="D45" s="22" t="inlineStr">
+        <is>
+          <t>Hours go to the supervisor for approval; status shows 'Waiting for review'.</t>
+        </is>
+      </c>
+      <c r="E45" s="23" t="n"/>
+      <c r="F45" s="22" t="n"/>
+      <c r="G45" s="23" t="n"/>
     </row>
     <row r="46" ht="42" customHeight="1">
       <c r="A46" s="21" t="inlineStr">
         <is>
-          <t>PV1</t>
+          <t>PE11</t>
         </is>
       </c>
       <c r="B46" s="22" t="inlineStr">
         <is>
-          <t>As a parent of a 6–12 student, I want to register for view-only access.</t>
+          <t>As a parent, I want to resubmit my child's rejected hours.</t>
         </is>
       </c>
       <c r="C46" s="22" t="inlineStr">
         <is>
-          <t>Create account → parent of a 6–12 student.</t>
+          <t>On a rejected past event, enter corrected hours → Resubmit.</t>
         </is>
       </c>
       <c r="D46" s="22" t="inlineStr">
         <is>
-          <t>Account created; no invite required to register.</t>
+          <t>Returns to 'Waiting for review'.</t>
         </is>
       </c>
       <c r="E46" s="23" t="n"/>
@@ -2592,22 +2604,22 @@
     <row r="47" ht="42" customHeight="1">
       <c r="A47" s="21" t="inlineStr">
         <is>
-          <t>PV2</t>
+          <t>PE12</t>
         </is>
       </c>
       <c r="B47" s="22" t="inlineStr">
         <is>
-          <t>As a viewer parent, my student links automatically by email.</t>
+          <t>As a parent, I want to see each past event's hours status for my child.</t>
         </is>
       </c>
       <c r="C47" s="22" t="inlineStr">
         <is>
-          <t>Have a student enter this exact email as their parent email (before or after you register).</t>
+          <t>Look at the child's past events list.</t>
         </is>
       </c>
       <c r="D47" s="22" t="inlineStr">
         <is>
-          <t>The student appears on your dashboard automatically; empty until then.</t>
+          <t>Each shows Approved / Waiting / Rejected as appropriate.</t>
         </is>
       </c>
       <c r="E47" s="23" t="n"/>
@@ -2617,110 +2629,110 @@
     <row r="48" ht="42" customHeight="1">
       <c r="A48" s="21" t="inlineStr">
         <is>
-          <t>PV3</t>
+          <t>PE13</t>
         </is>
       </c>
       <c r="B48" s="22" t="inlineStr">
         <is>
-          <t>As a viewer parent, I want to see my student's schedule/progress.</t>
+          <t>As a parent, all core participant actions are available to me for my child.</t>
         </is>
       </c>
       <c r="C48" s="22" t="inlineStr">
         <is>
-          <t>Open the dashboard.</t>
+          <t>Confirm: browse, sign up, withdraw, add-to-calendar, submit hours, view progress toward medals.</t>
         </is>
       </c>
       <c r="D48" s="22" t="inlineStr">
         <is>
-          <t>View-only schedule and progress.</t>
+          <t>All participant-style actions work on the child's behalf (the child never logs in).</t>
         </is>
       </c>
       <c r="E48" s="23" t="n"/>
       <c r="F48" s="22" t="n"/>
       <c r="G48" s="23" t="n"/>
     </row>
-    <row r="49" ht="42" customHeight="1">
-      <c r="A49" s="21" t="inlineStr">
-        <is>
-          <t>PV4</t>
-        </is>
-      </c>
-      <c r="B49" s="22" t="inlineStr">
-        <is>
-          <t>As a viewer parent, I do NOT sign the student up.</t>
-        </is>
-      </c>
-      <c r="C49" s="22" t="inlineStr">
-        <is>
-          <t>Look for a sign-up action.</t>
-        </is>
-      </c>
-      <c r="D49" s="22" t="inlineStr">
-        <is>
-          <t>No sign-up on the student's behalf — the student self-serves.</t>
-        </is>
-      </c>
-      <c r="E49" s="23" t="n"/>
-      <c r="F49" s="22" t="n"/>
-      <c r="G49" s="23" t="n"/>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="19" t="inlineStr">
+        <is>
+          <t>Parent — viewer (grades 6–12 student)</t>
+        </is>
+      </c>
+      <c r="B49" s="20" t="n"/>
+      <c r="C49" s="20" t="n"/>
+      <c r="D49" s="20" t="n"/>
+      <c r="E49" s="20" t="n"/>
+      <c r="F49" s="20" t="n"/>
+      <c r="G49" s="20" t="n"/>
     </row>
     <row r="50" ht="42" customHeight="1">
       <c r="A50" s="21" t="inlineStr">
         <is>
-          <t>PV5</t>
+          <t>PV1</t>
         </is>
       </c>
       <c r="B50" s="22" t="inlineStr">
         <is>
-          <t>As a viewer parent, I want to invite a co-guardian.</t>
+          <t>As a parent of a 6–12 student, I want to register for view-only access.</t>
         </is>
       </c>
       <c r="C50" s="22" t="inlineStr">
         <is>
-          <t>Invite a co-guardian by email.</t>
+          <t>Create account → parent of a 6–12 student.</t>
         </is>
       </c>
       <c r="D50" s="22" t="inlineStr">
         <is>
-          <t>Invite email sent; shared access on registration.</t>
+          <t>Account created; no invite required to register.</t>
         </is>
       </c>
       <c r="E50" s="23" t="n"/>
       <c r="F50" s="22" t="n"/>
       <c r="G50" s="23" t="n"/>
     </row>
-    <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="19" t="inlineStr">
-        <is>
-          <t>Supervisor (created by an Admin)</t>
-        </is>
-      </c>
-      <c r="B51" s="20" t="n"/>
-      <c r="C51" s="20" t="n"/>
-      <c r="D51" s="20" t="n"/>
-      <c r="E51" s="20" t="n"/>
-      <c r="F51" s="20" t="n"/>
-      <c r="G51" s="20" t="n"/>
+    <row r="51" ht="42" customHeight="1">
+      <c r="A51" s="21" t="inlineStr">
+        <is>
+          <t>PV2</t>
+        </is>
+      </c>
+      <c r="B51" s="22" t="inlineStr">
+        <is>
+          <t>As a viewer parent, my student links automatically by email.</t>
+        </is>
+      </c>
+      <c r="C51" s="22" t="inlineStr">
+        <is>
+          <t>Have a student enter this exact email as their parent email (before or after you register).</t>
+        </is>
+      </c>
+      <c r="D51" s="22" t="inlineStr">
+        <is>
+          <t>The student appears on your dashboard automatically; empty until then.</t>
+        </is>
+      </c>
+      <c r="E51" s="23" t="n"/>
+      <c r="F51" s="22" t="n"/>
+      <c r="G51" s="23" t="n"/>
     </row>
     <row r="52" ht="42" customHeight="1">
       <c r="A52" s="21" t="inlineStr">
         <is>
-          <t>SV1</t>
+          <t>PV3</t>
         </is>
       </c>
       <c r="B52" s="22" t="inlineStr">
         <is>
-          <t>As the program, a supervisor cannot self-register.</t>
+          <t>As a viewer parent, I want to see my student's schedule/progress.</t>
         </is>
       </c>
       <c r="C52" s="22" t="inlineStr">
         <is>
-          <t>Review the sign-up options.</t>
+          <t>Open the dashboard.</t>
         </is>
       </c>
       <c r="D52" s="22" t="inlineStr">
         <is>
-          <t>No supervisor option exists on registration.</t>
+          <t>View-only schedule and progress.</t>
         </is>
       </c>
       <c r="E52" s="23" t="n"/>
@@ -2730,22 +2742,22 @@
     <row r="53" ht="42" customHeight="1">
       <c r="A53" s="21" t="inlineStr">
         <is>
-          <t>SV2</t>
+          <t>PV4</t>
         </is>
       </c>
       <c r="B53" s="22" t="inlineStr">
         <is>
-          <t>As a new supervisor, I get an invite to set my password.</t>
+          <t>As a viewer parent, I do NOT sign the student up.</t>
         </is>
       </c>
       <c r="C53" s="22" t="inlineStr">
         <is>
-          <t>Have an Admin create your account; open the invite email; set password; sign in.</t>
+          <t>Look for a sign-up action.</t>
         </is>
       </c>
       <c r="D53" s="22" t="inlineStr">
         <is>
-          <t>Invite email arrives with a working set-password link; you can sign in.</t>
+          <t>No sign-up on the student's behalf — the student self-serves.</t>
         </is>
       </c>
       <c r="E53" s="23" t="n"/>
@@ -2755,72 +2767,60 @@
     <row r="54" ht="42" customHeight="1">
       <c r="A54" s="21" t="inlineStr">
         <is>
-          <t>SV3</t>
+          <t>PV5</t>
         </is>
       </c>
       <c r="B54" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want the correct 7 left-menu tabs.</t>
+          <t>As a viewer parent, I want to invite a co-guardian.</t>
         </is>
       </c>
       <c r="C54" s="22" t="inlineStr">
         <is>
-          <t>Look at the left menu.</t>
+          <t>Invite a co-guardian by email.</t>
         </is>
       </c>
       <c r="D54" s="22" t="inlineStr">
         <is>
-          <t>Dashboard, Pending Reviews, Reviewed History, My Events, All Opportunities, My Hours, Help.</t>
+          <t>Invite email sent; shared access on registration.</t>
         </is>
       </c>
       <c r="E54" s="23" t="n"/>
       <c r="F54" s="22" t="n"/>
       <c r="G54" s="23" t="n"/>
     </row>
-    <row r="55" ht="42" customHeight="1">
-      <c r="A55" s="21" t="inlineStr">
-        <is>
-          <t>SV4</t>
-        </is>
-      </c>
-      <c r="B55" s="22" t="inlineStr">
-        <is>
-          <t>As a supervisor, I want a dashboard.</t>
-        </is>
-      </c>
-      <c r="C55" s="22" t="inlineStr">
-        <is>
-          <t>Open the dashboard.</t>
-        </is>
-      </c>
-      <c r="D55" s="22" t="inlineStr">
-        <is>
-          <t>Review queue, approved/rejected counts, registrations, hours, upcoming events + Roster links.</t>
-        </is>
-      </c>
-      <c r="E55" s="23" t="n"/>
-      <c r="F55" s="22" t="n"/>
-      <c r="G55" s="23" t="n"/>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="19" t="inlineStr">
+        <is>
+          <t>Supervisor (created by an Admin)</t>
+        </is>
+      </c>
+      <c r="B55" s="20" t="n"/>
+      <c r="C55" s="20" t="n"/>
+      <c r="D55" s="20" t="n"/>
+      <c r="E55" s="20" t="n"/>
+      <c r="F55" s="20" t="n"/>
+      <c r="G55" s="20" t="n"/>
     </row>
     <row r="56" ht="42" customHeight="1">
       <c r="A56" s="21" t="inlineStr">
         <is>
-          <t>SV5</t>
+          <t>SV1</t>
         </is>
       </c>
       <c r="B56" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to approve hours.</t>
+          <t>As the program, a supervisor cannot self-register.</t>
         </is>
       </c>
       <c r="C56" s="22" t="inlineStr">
         <is>
-          <t>Pending Reviews → open → Approve.</t>
+          <t>Review the sign-up options.</t>
         </is>
       </c>
       <c r="D56" s="22" t="inlineStr">
         <is>
-          <t>Approved; moves to Reviewed History; participant total updates; email sent.</t>
+          <t>No supervisor option exists on registration.</t>
         </is>
       </c>
       <c r="E56" s="23" t="n"/>
@@ -2830,22 +2830,22 @@
     <row r="57" ht="42" customHeight="1">
       <c r="A57" s="21" t="inlineStr">
         <is>
-          <t>SV6</t>
+          <t>SV2</t>
         </is>
       </c>
       <c r="B57" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to reject hours with a reason.</t>
+          <t>As a new supervisor, I get an invite to set my password.</t>
         </is>
       </c>
       <c r="C57" s="22" t="inlineStr">
         <is>
-          <t>Reject without a reason, then with one.</t>
+          <t>Have an Admin create your account; open the invite email; set password; sign in.</t>
         </is>
       </c>
       <c r="D57" s="22" t="inlineStr">
         <is>
-          <t>Blocked until a reason is given; then rejected and the participant notified.</t>
+          <t>Invite email arrives with a working set-password link; you can sign in.</t>
         </is>
       </c>
       <c r="E57" s="23" t="n"/>
@@ -2855,22 +2855,22 @@
     <row r="58" ht="42" customHeight="1">
       <c r="A58" s="21" t="inlineStr">
         <is>
-          <t>SV7</t>
+          <t>SV3</t>
         </is>
       </c>
       <c r="B58" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to review external submissions.</t>
+          <t>As a supervisor, I want the correct 7 left-menu tabs.</t>
         </is>
       </c>
       <c r="C58" s="22" t="inlineStr">
         <is>
-          <t>Pending Reviews → external tab → approve/reject.</t>
+          <t>Look at the left menu.</t>
         </is>
       </c>
       <c r="D58" s="22" t="inlineStr">
         <is>
-          <t>External items reviewable, including any proof.</t>
+          <t>Dashboard, Pending Reviews, Reviewed History, My Events, All Opportunities, My Hours, Help.</t>
         </is>
       </c>
       <c r="E58" s="23" t="n"/>
@@ -2880,22 +2880,22 @@
     <row r="59" ht="42" customHeight="1">
       <c r="A59" s="21" t="inlineStr">
         <is>
-          <t>SV8</t>
+          <t>SV4</t>
         </is>
       </c>
       <c r="B59" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to create an event.</t>
+          <t>As a supervisor, I want a dashboard.</t>
         </is>
       </c>
       <c r="C59" s="22" t="inlineStr">
         <is>
-          <t>New Event → title, description, slot, address, date, times, capacity, grade limits → save.</t>
+          <t>Open the dashboard.</t>
         </is>
       </c>
       <c r="D59" s="22" t="inlineStr">
         <is>
-          <t>Credit auto-calculated from times; event created in My Events.</t>
+          <t>Review queue, approved/rejected counts, registrations, hours, upcoming events + Roster links.</t>
         </is>
       </c>
       <c r="E59" s="23" t="n"/>
@@ -2905,22 +2905,22 @@
     <row r="60" ht="42" customHeight="1">
       <c r="A60" s="21" t="inlineStr">
         <is>
-          <t>SV9</t>
+          <t>SV5</t>
         </is>
       </c>
       <c r="B60" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to edit an event.</t>
+          <t>As a supervisor, I want to approve hours.</t>
         </is>
       </c>
       <c r="C60" s="22" t="inlineStr">
         <is>
-          <t>My Events → edit → save.</t>
+          <t>Pending Reviews → open → Approve.</t>
         </is>
       </c>
       <c r="D60" s="22" t="inlineStr">
         <is>
-          <t>Changes persist and show to participants.</t>
+          <t>Approved; moves to Reviewed History; participant total updates; email sent.</t>
         </is>
       </c>
       <c r="E60" s="23" t="n"/>
@@ -2930,22 +2930,22 @@
     <row r="61" ht="42" customHeight="1">
       <c r="A61" s="21" t="inlineStr">
         <is>
-          <t>SV10</t>
+          <t>SV6</t>
         </is>
       </c>
       <c r="B61" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to delete an event with no approved hours.</t>
+          <t>As a supervisor, I want to reject hours with a reason.</t>
         </is>
       </c>
       <c r="C61" s="22" t="inlineStr">
         <is>
-          <t>Delete such an event → confirm.</t>
+          <t>Reject without a reason, then with one.</t>
         </is>
       </c>
       <c r="D61" s="22" t="inlineStr">
         <is>
-          <t>Event deleted.</t>
+          <t>Blocked until a reason is given; then rejected and the participant notified.</t>
         </is>
       </c>
       <c r="E61" s="23" t="n"/>
@@ -2955,22 +2955,22 @@
     <row r="62" ht="42" customHeight="1">
       <c r="A62" s="21" t="inlineStr">
         <is>
-          <t>SV11</t>
+          <t>SV7</t>
         </is>
       </c>
       <c r="B62" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, deleting an event with approved hours is blocked.</t>
+          <t>As a supervisor, I want to review external submissions.</t>
         </is>
       </c>
       <c r="C62" s="22" t="inlineStr">
         <is>
-          <t>Try to delete an event that has approved hours.</t>
+          <t>Pending Reviews → external tab → approve/reject.</t>
         </is>
       </c>
       <c r="D62" s="22" t="inlineStr">
         <is>
-          <t>Blocked with a message that approved hours must be preserved.</t>
+          <t>External items reviewable, including any proof.</t>
         </is>
       </c>
       <c r="E62" s="23" t="n"/>
@@ -2980,22 +2980,22 @@
     <row r="63" ht="42" customHeight="1">
       <c r="A63" s="21" t="inlineStr">
         <is>
-          <t>SV12</t>
+          <t>SV8</t>
         </is>
       </c>
       <c r="B63" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to see who signed up.</t>
+          <t>As a supervisor, I want to create an event.</t>
         </is>
       </c>
       <c r="C63" s="22" t="inlineStr">
         <is>
-          <t>Open the event Roster.</t>
+          <t>New Event → title, description, slot, address, date, times, capacity, grade limits → save.</t>
         </is>
       </c>
       <c r="D63" s="22" t="inlineStr">
         <is>
-          <t>Registrants listed with grade and status.</t>
+          <t>Credit auto-calculated from times; event created in My Events.</t>
         </is>
       </c>
       <c r="E63" s="23" t="n"/>
@@ -3005,22 +3005,22 @@
     <row r="64" ht="42" customHeight="1">
       <c r="A64" s="21" t="inlineStr">
         <is>
-          <t>SV13</t>
+          <t>SV9</t>
         </is>
       </c>
       <c r="B64" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to check people in / mark no-show.</t>
+          <t>As a supervisor, I want to edit an event.</t>
         </is>
       </c>
       <c r="C64" s="22" t="inlineStr">
         <is>
-          <t>On the roster, Check in and Mark no-show.</t>
+          <t>My Events → edit → save.</t>
         </is>
       </c>
       <c r="D64" s="22" t="inlineStr">
         <is>
-          <t>Status updates and persists.</t>
+          <t>Changes persist and show to participants.</t>
         </is>
       </c>
       <c r="E64" s="23" t="n"/>
@@ -3030,22 +3030,22 @@
     <row r="65" ht="42" customHeight="1">
       <c r="A65" s="21" t="inlineStr">
         <is>
-          <t>SV14</t>
+          <t>SV10</t>
         </is>
       </c>
       <c r="B65" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to message everyone signed up.</t>
+          <t>As a supervisor, I want to delete an event with no approved hours.</t>
         </is>
       </c>
       <c r="C65" s="22" t="inlineStr">
         <is>
-          <t>Roster → Message attendees → subject+message → send (include guardians on).</t>
+          <t>Delete such an event → confirm.</t>
         </is>
       </c>
       <c r="D65" s="22" t="inlineStr">
         <is>
-          <t>Each registrant (and guardians) emailed individually; recipient count shown.</t>
+          <t>Event deleted.</t>
         </is>
       </c>
       <c r="E65" s="23" t="n"/>
@@ -3055,22 +3055,22 @@
     <row r="66" ht="42" customHeight="1">
       <c r="A66" s="21" t="inlineStr">
         <is>
-          <t>SV15</t>
+          <t>SV11</t>
         </is>
       </c>
       <c r="B66" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want a history of what I reviewed.</t>
+          <t>As a supervisor, deleting an event with approved hours is blocked.</t>
         </is>
       </c>
       <c r="C66" s="22" t="inlineStr">
         <is>
-          <t>Open Reviewed History.</t>
+          <t>Try to delete an event that has approved hours.</t>
         </is>
       </c>
       <c r="D66" s="22" t="inlineStr">
         <is>
-          <t>Every approved/rejected item with dates and volunteers.</t>
+          <t>Blocked with a message that approved hours must be preserved.</t>
         </is>
       </c>
       <c r="E66" s="23" t="n"/>
@@ -3080,22 +3080,22 @@
     <row r="67" ht="42" customHeight="1">
       <c r="A67" s="21" t="inlineStr">
         <is>
-          <t>SV16</t>
+          <t>SV12</t>
         </is>
       </c>
       <c r="B67" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to browse all opportunities view-only.</t>
+          <t>As a supervisor, I want to see who signed up.</t>
         </is>
       </c>
       <c r="C67" s="22" t="inlineStr">
         <is>
-          <t>All Opportunities → search / upcoming-past.</t>
+          <t>Open the event Roster.</t>
         </is>
       </c>
       <c r="D67" s="22" t="inlineStr">
         <is>
-          <t>Every event listed read-only; can't edit others' events.</t>
+          <t>Registrants listed with grade and status.</t>
         </is>
       </c>
       <c r="E67" s="23" t="n"/>
@@ -3105,22 +3105,22 @@
     <row r="68" ht="42" customHeight="1">
       <c r="A68" s="21" t="inlineStr">
         <is>
-          <t>SV17</t>
+          <t>SV13</t>
         </is>
       </c>
       <c r="B68" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to log my own adult hours.</t>
+          <t>As a supervisor, I want to check people in / mark no-show.</t>
         </is>
       </c>
       <c r="C68" s="22" t="inlineStr">
         <is>
-          <t>My Hours → log an activity, date, hours → save.</t>
+          <t>On the roster, Check in and Mark no-show.</t>
         </is>
       </c>
       <c r="D68" s="22" t="inlineStr">
         <is>
-          <t>Recorded instantly with a running total; clearly NOT part of the student competition.</t>
+          <t>Status updates and persists.</t>
         </is>
       </c>
       <c r="E68" s="23" t="n"/>
@@ -3130,22 +3130,22 @@
     <row r="69" ht="42" customHeight="1">
       <c r="A69" s="21" t="inlineStr">
         <is>
-          <t>SV18</t>
+          <t>SV14</t>
         </is>
       </c>
       <c r="B69" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to delete an adult-hours entry.</t>
+          <t>As a supervisor, I want to message everyone signed up.</t>
         </is>
       </c>
       <c r="C69" s="22" t="inlineStr">
         <is>
-          <t>My Hours → delete an entry → confirm.</t>
+          <t>Roster → Message attendees → subject+message → send (include guardians on).</t>
         </is>
       </c>
       <c r="D69" s="22" t="inlineStr">
         <is>
-          <t>Removed; total updates.</t>
+          <t>Each registrant (and guardians) emailed individually; recipient count shown.</t>
         </is>
       </c>
       <c r="E69" s="23" t="n"/>
@@ -3155,60 +3155,72 @@
     <row r="70" ht="42" customHeight="1">
       <c r="A70" s="21" t="inlineStr">
         <is>
-          <t>SV19</t>
+          <t>SV15</t>
         </is>
       </c>
       <c r="B70" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I must NOT access user or org management.</t>
+          <t>As a supervisor, I want a history of what I reviewed.</t>
         </is>
       </c>
       <c r="C70" s="22" t="inlineStr">
         <is>
-          <t>Look for Users / Organizations in the menu.</t>
+          <t>Open Reviewed History.</t>
         </is>
       </c>
       <c r="D70" s="22" t="inlineStr">
         <is>
-          <t>Those tabs are absent; direct URLs are blocked.</t>
+          <t>Every approved/rejected item with dates and volunteers.</t>
         </is>
       </c>
       <c r="E70" s="23" t="n"/>
       <c r="F70" s="22" t="n"/>
       <c r="G70" s="23" t="n"/>
     </row>
-    <row r="71" ht="20" customHeight="1">
-      <c r="A71" s="19" t="inlineStr">
-        <is>
-          <t>Admin (org-scoped)</t>
-        </is>
-      </c>
-      <c r="B71" s="20" t="n"/>
-      <c r="C71" s="20" t="n"/>
-      <c r="D71" s="20" t="n"/>
-      <c r="E71" s="20" t="n"/>
-      <c r="F71" s="20" t="n"/>
-      <c r="G71" s="20" t="n"/>
+    <row r="71" ht="42" customHeight="1">
+      <c r="A71" s="21" t="inlineStr">
+        <is>
+          <t>SV16</t>
+        </is>
+      </c>
+      <c r="B71" s="22" t="inlineStr">
+        <is>
+          <t>As a supervisor, I want to browse all opportunities view-only.</t>
+        </is>
+      </c>
+      <c r="C71" s="22" t="inlineStr">
+        <is>
+          <t>All Opportunities → search / upcoming-past.</t>
+        </is>
+      </c>
+      <c r="D71" s="22" t="inlineStr">
+        <is>
+          <t>Every event listed read-only; can't edit others' events.</t>
+        </is>
+      </c>
+      <c r="E71" s="23" t="n"/>
+      <c r="F71" s="22" t="n"/>
+      <c r="G71" s="23" t="n"/>
     </row>
     <row r="72" ht="42" customHeight="1">
       <c r="A72" s="21" t="inlineStr">
         <is>
-          <t>AD1</t>
+          <t>SV17</t>
         </is>
       </c>
       <c r="B72" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I want the correct menu tabs.</t>
+          <t>As a supervisor, I want to log my own adult hours.</t>
         </is>
       </c>
       <c r="C72" s="22" t="inlineStr">
         <is>
-          <t>Look at the left menu.</t>
+          <t>My Hours → log an activity, date, hours → save.</t>
         </is>
       </c>
       <c r="D72" s="22" t="inlineStr">
         <is>
-          <t>Dashboard, Pending Reviews, Reviewed History, My Events, All Opportunities, Users, Organizations, My Hours, Help.</t>
+          <t>Recorded instantly with a running total; clearly NOT part of the student competition.</t>
         </is>
       </c>
       <c r="E72" s="23" t="n"/>
@@ -3218,22 +3230,22 @@
     <row r="73" ht="42" customHeight="1">
       <c r="A73" s="21" t="inlineStr">
         <is>
-          <t>AD2</t>
+          <t>SV18</t>
         </is>
       </c>
       <c r="B73" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I can do everything a supervisor can.</t>
+          <t>As a supervisor, I want to delete an adult-hours entry.</t>
         </is>
       </c>
       <c r="C73" s="22" t="inlineStr">
         <is>
-          <t>Spot-check: approve an item and create an event.</t>
+          <t>My Hours → delete an entry → confirm.</t>
         </is>
       </c>
       <c r="D73" s="22" t="inlineStr">
         <is>
-          <t>Both work.</t>
+          <t>Removed; total updates.</t>
         </is>
       </c>
       <c r="E73" s="23" t="n"/>
@@ -3243,72 +3255,60 @@
     <row r="74" ht="42" customHeight="1">
       <c r="A74" s="21" t="inlineStr">
         <is>
-          <t>AD3</t>
+          <t>SV19</t>
         </is>
       </c>
       <c r="B74" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I only see my org's non-admin users.</t>
+          <t>As a supervisor, I must NOT access user or org management.</t>
         </is>
       </c>
       <c r="C74" s="22" t="inlineStr">
         <is>
-          <t>Open Users.</t>
+          <t>Look for Users / Organizations in the menu.</t>
         </is>
       </c>
       <c r="D74" s="22" t="inlineStr">
         <is>
-          <t>Only participants/parents/supervisors in your org; no admins/super admins; no other orgs.</t>
+          <t>Those tabs are absent; direct URLs are blocked.</t>
         </is>
       </c>
       <c r="E74" s="23" t="n"/>
       <c r="F74" s="22" t="n"/>
       <c r="G74" s="23" t="n"/>
     </row>
-    <row r="75" ht="42" customHeight="1">
-      <c r="A75" s="21" t="inlineStr">
-        <is>
-          <t>AD4</t>
-        </is>
-      </c>
-      <c r="B75" s="22" t="inlineStr">
-        <is>
-          <t>As an Admin, I want to add a supervisor.</t>
-        </is>
-      </c>
-      <c r="C75" s="22" t="inlineStr">
-        <is>
-          <t>Users → Add user → Supervisor → save.</t>
-        </is>
-      </c>
-      <c r="D75" s="22" t="inlineStr">
-        <is>
-          <t>Supervisor created, stamped to your org; invite email sent.</t>
-        </is>
-      </c>
-      <c r="E75" s="23" t="n"/>
-      <c r="F75" s="22" t="n"/>
-      <c r="G75" s="23" t="n"/>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="19" t="inlineStr">
+        <is>
+          <t>Admin (org-scoped)</t>
+        </is>
+      </c>
+      <c r="B75" s="20" t="n"/>
+      <c r="C75" s="20" t="n"/>
+      <c r="D75" s="20" t="n"/>
+      <c r="E75" s="20" t="n"/>
+      <c r="F75" s="20" t="n"/>
+      <c r="G75" s="20" t="n"/>
     </row>
     <row r="76" ht="42" customHeight="1">
       <c r="A76" s="21" t="inlineStr">
         <is>
-          <t>AD5</t>
+          <t>AD1</t>
         </is>
       </c>
       <c r="B76" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I want to create a participant as a fallback.</t>
+          <t>As an Admin, I want the correct menu tabs.</t>
         </is>
       </c>
       <c r="C76" s="22" t="inlineStr">
         <is>
-          <t>Users → Add user → Participant → save.</t>
+          <t>Look at the left menu.</t>
         </is>
       </c>
       <c r="D76" s="22" t="inlineStr">
         <is>
-          <t>Participant created with a set-password invite (no silent password).</t>
+          <t>Dashboard, Pending Reviews, Reviewed History, My Events, All Opportunities, Users, Organizations, My Hours, Help.</t>
         </is>
       </c>
       <c r="E76" s="23" t="n"/>
@@ -3318,22 +3318,22 @@
     <row r="77" ht="42" customHeight="1">
       <c r="A77" s="21" t="inlineStr">
         <is>
-          <t>AD6</t>
+          <t>AD2</t>
         </is>
       </c>
       <c r="B77" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I want to grant participant hours.</t>
+          <t>As an Admin, I can do everything a supervisor can.</t>
         </is>
       </c>
       <c r="C77" s="22" t="inlineStr">
         <is>
-          <t>Open a participant in your org → Add hours.</t>
+          <t>Spot-check: approve an item and create an event.</t>
         </is>
       </c>
       <c r="D77" s="22" t="inlineStr">
         <is>
-          <t>Hours auto-approved; count toward their total/medals.</t>
+          <t>Both work.</t>
         </is>
       </c>
       <c r="E77" s="23" t="n"/>
@@ -3343,22 +3343,22 @@
     <row r="78" ht="42" customHeight="1">
       <c r="A78" s="21" t="inlineStr">
         <is>
-          <t>AD7</t>
+          <t>AD3</t>
         </is>
       </c>
       <c r="B78" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I want a participant's service record.</t>
+          <t>As an Admin, I only see my org's non-admin users.</t>
         </is>
       </c>
       <c r="C78" s="22" t="inlineStr">
         <is>
-          <t>Users → Service record for a participant in your org.</t>
+          <t>Open Users.</t>
         </is>
       </c>
       <c r="D78" s="22" t="inlineStr">
         <is>
-          <t>Record opens.</t>
+          <t>Only participants/parents/supervisors in your org; no admins/super admins; no other orgs.</t>
         </is>
       </c>
       <c r="E78" s="23" t="n"/>
@@ -3368,22 +3368,22 @@
     <row r="79" ht="42" customHeight="1">
       <c r="A79" s="21" t="inlineStr">
         <is>
-          <t>AD8</t>
+          <t>AD4</t>
         </is>
       </c>
       <c r="B79" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I want to edit/delete my org's users.</t>
+          <t>As an Admin, I want to add a supervisor.</t>
         </is>
       </c>
       <c r="C79" s="22" t="inlineStr">
         <is>
-          <t>Edit a name/phone; delete a test user.</t>
+          <t>Users → Add user → Supervisor → save.</t>
         </is>
       </c>
       <c r="D79" s="22" t="inlineStr">
         <is>
-          <t>Changes apply within your org.</t>
+          <t>Supervisor created, stamped to your org; invite email sent.</t>
         </is>
       </c>
       <c r="E79" s="23" t="n"/>
@@ -3393,22 +3393,22 @@
     <row r="80" ht="42" customHeight="1">
       <c r="A80" s="21" t="inlineStr">
         <is>
-          <t>AD9</t>
+          <t>AD5</t>
         </is>
       </c>
       <c r="B80" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I must NOT act on users outside my org.</t>
+          <t>As an Admin, I want to create a participant as a fallback.</t>
         </is>
       </c>
       <c r="C80" s="22" t="inlineStr">
         <is>
-          <t>Attempt to reach another org's user (e.g. direct URL).</t>
+          <t>Users → Add user → Participant → save.</t>
         </is>
       </c>
       <c r="D80" s="22" t="inlineStr">
         <is>
-          <t>Blocked / not visible.</t>
+          <t>Participant created with a set-password invite (no silent password).</t>
         </is>
       </c>
       <c r="E80" s="23" t="n"/>
@@ -3418,22 +3418,22 @@
     <row r="81" ht="42" customHeight="1">
       <c r="A81" s="21" t="inlineStr">
         <is>
-          <t>AD10</t>
+          <t>AD6</t>
         </is>
       </c>
       <c r="B81" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I cannot grant Admin access or manage admins.</t>
+          <t>As an Admin, I want to grant participant hours.</t>
         </is>
       </c>
       <c r="C81" s="22" t="inlineStr">
         <is>
-          <t>Look for the 'grant Admin access' action.</t>
+          <t>Open a participant in your org → Add hours.</t>
         </is>
       </c>
       <c r="D81" s="22" t="inlineStr">
         <is>
-          <t>No such button; attempts are blocked server-side.</t>
+          <t>Hours auto-approved; count toward their total/medals.</t>
         </is>
       </c>
       <c r="E81" s="23" t="n"/>
@@ -3443,22 +3443,22 @@
     <row r="82" ht="42" customHeight="1">
       <c r="A82" s="21" t="inlineStr">
         <is>
-          <t>AD11</t>
+          <t>AD7</t>
         </is>
       </c>
       <c r="B82" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I see and edit only my own organization.</t>
+          <t>As an Admin, I want a participant's service record.</t>
         </is>
       </c>
       <c r="C82" s="22" t="inlineStr">
         <is>
-          <t>Open Organizations.</t>
+          <t>Users → Service record for a participant in your org.</t>
         </is>
       </c>
       <c r="D82" s="22" t="inlineStr">
         <is>
-          <t>Only your org shows; you can edit its settings.</t>
+          <t>Record opens.</t>
         </is>
       </c>
       <c r="E82" s="23" t="n"/>
@@ -3468,22 +3468,22 @@
     <row r="83" ht="42" customHeight="1">
       <c r="A83" s="21" t="inlineStr">
         <is>
-          <t>AD12</t>
+          <t>AD8</t>
         </is>
       </c>
       <c r="B83" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I want to generate/rotate my org's join code.</t>
+          <t>As an Admin, I want to edit/delete my org's users.</t>
         </is>
       </c>
       <c r="C83" s="22" t="inlineStr">
         <is>
-          <t>Organizations → set/generate a join code → save.</t>
+          <t>Edit a name/phone; delete a test user.</t>
         </is>
       </c>
       <c r="D83" s="22" t="inlineStr">
         <is>
-          <t>Join code saved; usable at sign-up.</t>
+          <t>Changes apply within your org.</t>
         </is>
       </c>
       <c r="E83" s="23" t="n"/>
@@ -3493,22 +3493,22 @@
     <row r="84" ht="42" customHeight="1">
       <c r="A84" s="21" t="inlineStr">
         <is>
-          <t>AD13</t>
+          <t>AD9</t>
         </is>
       </c>
       <c r="B84" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I cannot create organizations.</t>
+          <t>As an Admin, I must NOT act on users outside my org.</t>
         </is>
       </c>
       <c r="C84" s="22" t="inlineStr">
         <is>
-          <t>Look for 'Add organization'.</t>
+          <t>Attempt to reach another org's user (e.g. direct URL).</t>
         </is>
       </c>
       <c r="D84" s="22" t="inlineStr">
         <is>
-          <t>No Add button; creation blocked.</t>
+          <t>Blocked / not visible.</t>
         </is>
       </c>
       <c r="E84" s="23" t="n"/>
@@ -3518,60 +3518,72 @@
     <row r="85" ht="42" customHeight="1">
       <c r="A85" s="21" t="inlineStr">
         <is>
-          <t>AD14</t>
+          <t>AD10</t>
         </is>
       </c>
       <c r="B85" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I cannot change the recycling cans total.</t>
+          <t>As an Admin, I cannot grant Admin access or manage admins.</t>
         </is>
       </c>
       <c r="C85" s="22" t="inlineStr">
         <is>
-          <t>Look for the cans/bin admin control.</t>
+          <t>Look for the 'grant Admin access' action.</t>
         </is>
       </c>
       <c r="D85" s="22" t="inlineStr">
         <is>
-          <t>Not available (Super Admin only).</t>
+          <t>No such button; attempts are blocked server-side.</t>
         </is>
       </c>
       <c r="E85" s="23" t="n"/>
       <c r="F85" s="22" t="n"/>
       <c r="G85" s="23" t="n"/>
     </row>
-    <row r="86" ht="20" customHeight="1">
-      <c r="A86" s="19" t="inlineStr">
-        <is>
-          <t>Super Admin (global)</t>
-        </is>
-      </c>
-      <c r="B86" s="20" t="n"/>
-      <c r="C86" s="20" t="n"/>
-      <c r="D86" s="20" t="n"/>
-      <c r="E86" s="20" t="n"/>
-      <c r="F86" s="20" t="n"/>
-      <c r="G86" s="20" t="n"/>
+    <row r="86" ht="42" customHeight="1">
+      <c r="A86" s="21" t="inlineStr">
+        <is>
+          <t>AD11</t>
+        </is>
+      </c>
+      <c r="B86" s="22" t="inlineStr">
+        <is>
+          <t>As an Admin, I see and edit only my own organization.</t>
+        </is>
+      </c>
+      <c r="C86" s="22" t="inlineStr">
+        <is>
+          <t>Open Organizations.</t>
+        </is>
+      </c>
+      <c r="D86" s="22" t="inlineStr">
+        <is>
+          <t>Only your org shows; you can edit its settings.</t>
+        </is>
+      </c>
+      <c r="E86" s="23" t="n"/>
+      <c r="F86" s="22" t="n"/>
+      <c r="G86" s="23" t="n"/>
     </row>
     <row r="87" ht="42" customHeight="1">
       <c r="A87" s="21" t="inlineStr">
         <is>
-          <t>SA1</t>
+          <t>AD12</t>
         </is>
       </c>
       <c r="B87" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want the correct menu tabs.</t>
+          <t>As an Admin, I want to generate/rotate my org's join code.</t>
         </is>
       </c>
       <c r="C87" s="22" t="inlineStr">
         <is>
-          <t>Look at the left menu.</t>
+          <t>Organizations → set/generate a join code → save.</t>
         </is>
       </c>
       <c r="D87" s="22" t="inlineStr">
         <is>
-          <t>Dashboard, Reports, Users, Events, Organizations (Help in footer).</t>
+          <t>Join code saved; usable at sign-up.</t>
         </is>
       </c>
       <c r="E87" s="23" t="n"/>
@@ -3581,22 +3593,22 @@
     <row r="88" ht="42" customHeight="1">
       <c r="A88" s="21" t="inlineStr">
         <is>
-          <t>SA2</t>
+          <t>AD13</t>
         </is>
       </c>
       <c r="B88" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I can do everything an Admin can, across all orgs.</t>
+          <t>As an Admin, I cannot create organizations.</t>
         </is>
       </c>
       <c r="C88" s="22" t="inlineStr">
         <is>
-          <t>Spot-check user + org actions on more than one org.</t>
+          <t>Look for 'Add organization'.</t>
         </is>
       </c>
       <c r="D88" s="22" t="inlineStr">
         <is>
-          <t>All allowed regardless of org.</t>
+          <t>No Add button; creation blocked.</t>
         </is>
       </c>
       <c r="E88" s="23" t="n"/>
@@ -3606,72 +3618,60 @@
     <row r="89" ht="42" customHeight="1">
       <c r="A89" s="21" t="inlineStr">
         <is>
-          <t>SA3</t>
+          <t>AD14</t>
         </is>
       </c>
       <c r="B89" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to create users incl. Supervisor and Super Admin.</t>
+          <t>As an Admin, I cannot change the recycling cans total.</t>
         </is>
       </c>
       <c r="C89" s="22" t="inlineStr">
         <is>
-          <t>Users → Add user → each role.</t>
+          <t>Look for the cans/bin admin control.</t>
         </is>
       </c>
       <c r="D89" s="22" t="inlineStr">
         <is>
-          <t>Participant/Supervisor/Super Admin options available; account created + invite email.</t>
+          <t>Not available (Super Admin only).</t>
         </is>
       </c>
       <c r="E89" s="23" t="n"/>
       <c r="F89" s="22" t="n"/>
       <c r="G89" s="23" t="n"/>
     </row>
-    <row r="90" ht="42" customHeight="1">
-      <c r="A90" s="21" t="inlineStr">
-        <is>
-          <t>SA4</t>
-        </is>
-      </c>
-      <c r="B90" s="22" t="inlineStr">
-        <is>
-          <t>As a Super Admin, I want to grant/revoke Admin access.</t>
-        </is>
-      </c>
-      <c r="C90" s="22" t="inlineStr">
-        <is>
-          <t>Open a user → grant Admin access → check org(s) → save; then uncheck all → save.</t>
-        </is>
-      </c>
-      <c r="D90" s="22" t="inlineStr">
-        <is>
-          <t>Checking orgs makes an Admin; unchecking all reverts to participant.</t>
-        </is>
-      </c>
-      <c r="E90" s="23" t="n"/>
-      <c r="F90" s="22" t="n"/>
-      <c r="G90" s="23" t="n"/>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="19" t="inlineStr">
+        <is>
+          <t>Super Admin (global)</t>
+        </is>
+      </c>
+      <c r="B90" s="20" t="n"/>
+      <c r="C90" s="20" t="n"/>
+      <c r="D90" s="20" t="n"/>
+      <c r="E90" s="20" t="n"/>
+      <c r="F90" s="20" t="n"/>
+      <c r="G90" s="20" t="n"/>
     </row>
     <row r="91" ht="42" customHeight="1">
       <c r="A91" s="21" t="inlineStr">
         <is>
-          <t>SA5</t>
+          <t>SA1</t>
         </is>
       </c>
       <c r="B91" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to create organizations + join codes.</t>
+          <t>As a Super Admin, I want the correct menu tabs.</t>
         </is>
       </c>
       <c r="C91" s="22" t="inlineStr">
         <is>
-          <t>Organizations → Add organization → set details + join code.</t>
+          <t>Look at the left menu.</t>
         </is>
       </c>
       <c r="D91" s="22" t="inlineStr">
         <is>
-          <t>Org created with its join code.</t>
+          <t>Dashboard, Reports, Users, Events, Organizations (Help in footer).</t>
         </is>
       </c>
       <c r="E91" s="23" t="n"/>
@@ -3681,22 +3681,22 @@
     <row r="92" ht="42" customHeight="1">
       <c r="A92" s="21" t="inlineStr">
         <is>
-          <t>SA6</t>
+          <t>SA2</t>
         </is>
       </c>
       <c r="B92" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to find users by type.</t>
+          <t>As a Super Admin, I can do everything an Admin can, across all orgs.</t>
         </is>
       </c>
       <c r="C92" s="22" t="inlineStr">
         <is>
-          <t>Users → role filter pills + search.</t>
+          <t>Spot-check user + org actions on more than one org.</t>
         </is>
       </c>
       <c r="D92" s="22" t="inlineStr">
         <is>
-          <t>Filter by role with counts; search by name/email across all orgs.</t>
+          <t>All allowed regardless of org.</t>
         </is>
       </c>
       <c r="E92" s="23" t="n"/>
@@ -3706,22 +3706,22 @@
     <row r="93" ht="42" customHeight="1">
       <c r="A93" s="21" t="inlineStr">
         <is>
-          <t>SA7</t>
+          <t>SA3</t>
         </is>
       </c>
       <c r="B93" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to search events.</t>
+          <t>As a Super Admin, I want to create users incl. Supervisor and Super Admin.</t>
         </is>
       </c>
       <c r="C93" s="22" t="inlineStr">
         <is>
-          <t>Events → search + date range; check supervisor/org per card.</t>
+          <t>Users → Add user → each role.</t>
         </is>
       </c>
       <c r="D93" s="22" t="inlineStr">
         <is>
-          <t>Filters work; each event shows supervisor and organization.</t>
+          <t>Participant/Supervisor/Super Admin options available; account created + invite email.</t>
         </is>
       </c>
       <c r="E93" s="23" t="n"/>
@@ -3731,22 +3731,22 @@
     <row r="94" ht="42" customHeight="1">
       <c r="A94" s="21" t="inlineStr">
         <is>
-          <t>SA8</t>
+          <t>SA4</t>
         </is>
       </c>
       <c r="B94" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want clear event-visibility labels.</t>
+          <t>As a Super Admin, I want to grant/revoke Admin access.</t>
         </is>
       </c>
       <c r="C94" s="22" t="inlineStr">
         <is>
-          <t>New Event → 'Who can see this'.</t>
+          <t>Open a user → grant Admin access → check org(s) → save; then uncheck all → save.</t>
         </is>
       </c>
       <c r="D94" s="22" t="inlineStr">
         <is>
-          <t>'Open to all (community)' and 'Only &lt;org&gt; students' with helper text.</t>
+          <t>Checking orgs makes an Admin; unchecking all reverts to participant.</t>
         </is>
       </c>
       <c r="E94" s="23" t="n"/>
@@ -3756,22 +3756,22 @@
     <row r="95" ht="42" customHeight="1">
       <c r="A95" s="21" t="inlineStr">
         <is>
-          <t>SA9</t>
+          <t>SA5</t>
         </is>
       </c>
       <c r="B95" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want program-wide reports.</t>
+          <t>As a Super Admin, I want to create organizations + join codes.</t>
         </is>
       </c>
       <c r="C95" s="22" t="inlineStr">
         <is>
-          <t>Open Reports / Dashboard.</t>
+          <t>Organizations → Add organization → set details + join code.</t>
         </is>
       </c>
       <c r="D95" s="22" t="inlineStr">
         <is>
-          <t>Totals and charts across the whole program.</t>
+          <t>Org created with its join code.</t>
         </is>
       </c>
       <c r="E95" s="23" t="n"/>
@@ -3781,22 +3781,22 @@
     <row r="96" ht="42" customHeight="1">
       <c r="A96" s="21" t="inlineStr">
         <is>
-          <t>SA10</t>
+          <t>SA6</t>
         </is>
       </c>
       <c r="B96" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to verify email works.</t>
+          <t>As a Super Admin, I want to find users by type.</t>
         </is>
       </c>
       <c r="C96" s="22" t="inlineStr">
         <is>
-          <t>Dashboard → Send test email.</t>
+          <t>Users → role filter pills + search.</t>
         </is>
       </c>
       <c r="D96" s="22" t="inlineStr">
         <is>
-          <t>Result shown (success or the exact failure reason).</t>
+          <t>Filter by role with counts; search by name/email across all orgs.</t>
         </is>
       </c>
       <c r="E96" s="23" t="n"/>
@@ -3806,22 +3806,22 @@
     <row r="97" ht="42" customHeight="1">
       <c r="A97" s="21" t="inlineStr">
         <is>
-          <t>SA11</t>
+          <t>SA7</t>
         </is>
       </c>
       <c r="B97" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to update the recycling cans total.</t>
+          <t>As a Super Admin, I want to search events.</t>
         </is>
       </c>
       <c r="C97" s="22" t="inlineStr">
         <is>
-          <t>Use the cans/bin admin control.</t>
+          <t>Events → search + date range; check supervisor/org per card.</t>
         </is>
       </c>
       <c r="D97" s="22" t="inlineStr">
         <is>
-          <t>Total updates; the ribbon reflects it.</t>
+          <t>Filters work; each event shows supervisor and organization.</t>
         </is>
       </c>
       <c r="E97" s="23" t="n"/>
@@ -3831,60 +3831,72 @@
     <row r="98" ht="42" customHeight="1">
       <c r="A98" s="21" t="inlineStr">
         <is>
-          <t>SA12</t>
+          <t>SA8</t>
         </is>
       </c>
       <c r="B98" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want hours + records for any user.</t>
+          <t>As a Super Admin, I want clear event-visibility labels.</t>
         </is>
       </c>
       <c r="C98" s="22" t="inlineStr">
         <is>
-          <t>Add manual hours / open service record for any participant.</t>
+          <t>New Event → 'Who can see this'.</t>
         </is>
       </c>
       <c r="D98" s="22" t="inlineStr">
         <is>
-          <t>Works for any org.</t>
+          <t>'Open to all (community)' and 'Only &lt;org&gt; students' with helper text.</t>
         </is>
       </c>
       <c r="E98" s="23" t="n"/>
       <c r="F98" s="22" t="n"/>
       <c r="G98" s="23" t="n"/>
     </row>
-    <row r="99" ht="20" customHeight="1">
-      <c r="A99" s="19" t="inlineStr">
-        <is>
-          <t>Cross-cutting</t>
-        </is>
-      </c>
-      <c r="B99" s="20" t="n"/>
-      <c r="C99" s="20" t="n"/>
-      <c r="D99" s="20" t="n"/>
-      <c r="E99" s="20" t="n"/>
-      <c r="F99" s="20" t="n"/>
-      <c r="G99" s="20" t="n"/>
+    <row r="99" ht="42" customHeight="1">
+      <c r="A99" s="21" t="inlineStr">
+        <is>
+          <t>SA9</t>
+        </is>
+      </c>
+      <c r="B99" s="22" t="inlineStr">
+        <is>
+          <t>As a Super Admin, I want program-wide reports.</t>
+        </is>
+      </c>
+      <c r="C99" s="22" t="inlineStr">
+        <is>
+          <t>Open Reports / Dashboard.</t>
+        </is>
+      </c>
+      <c r="D99" s="22" t="inlineStr">
+        <is>
+          <t>Totals and charts across the whole program.</t>
+        </is>
+      </c>
+      <c r="E99" s="23" t="n"/>
+      <c r="F99" s="22" t="n"/>
+      <c r="G99" s="23" t="n"/>
     </row>
     <row r="100" ht="42" customHeight="1">
       <c r="A100" s="21" t="inlineStr">
         <is>
-          <t>X1</t>
+          <t>SA10</t>
         </is>
       </c>
       <c r="B100" s="22" t="inlineStr">
         <is>
-          <t>As a phone user, I want a usable mobile layout.</t>
+          <t>As a Super Admin, I want to verify email works.</t>
         </is>
       </c>
       <c r="C100" s="22" t="inlineStr">
         <is>
-          <t>Open at phone width; use the menu drawer.</t>
+          <t>Dashboard → Send test email.</t>
         </is>
       </c>
       <c r="D100" s="22" t="inlineStr">
         <is>
-          <t>Layout adapts; drawer opens/closes; no horizontal scroll.</t>
+          <t>Result shown (success or the exact failure reason).</t>
         </is>
       </c>
       <c r="E100" s="23" t="n"/>
@@ -3894,39 +3906,127 @@
     <row r="101" ht="42" customHeight="1">
       <c r="A101" s="21" t="inlineStr">
         <is>
-          <t>X2</t>
+          <t>SA11</t>
         </is>
       </c>
       <c r="B101" s="22" t="inlineStr">
         <is>
-          <t>As a visitor, I want the recycling ribbon on the login page.</t>
+          <t>As a Super Admin, I want to update the recycling cans total.</t>
         </is>
       </c>
       <c r="C101" s="22" t="inlineStr">
         <is>
-          <t>Open login signed out.</t>
+          <t>Use the cans/bin admin control.</t>
         </is>
       </c>
       <c r="D101" s="22" t="inlineStr">
         <is>
-          <t>Green ribbon shows on login.</t>
+          <t>Total updates; the ribbon reflects it.</t>
         </is>
       </c>
       <c r="E101" s="23" t="n"/>
       <c r="F101" s="22" t="n"/>
       <c r="G101" s="23" t="n"/>
     </row>
+    <row r="102" ht="42" customHeight="1">
+      <c r="A102" s="21" t="inlineStr">
+        <is>
+          <t>SA12</t>
+        </is>
+      </c>
+      <c r="B102" s="22" t="inlineStr">
+        <is>
+          <t>As a Super Admin, I want hours + records for any user.</t>
+        </is>
+      </c>
+      <c r="C102" s="22" t="inlineStr">
+        <is>
+          <t>Add manual hours / open service record for any participant.</t>
+        </is>
+      </c>
+      <c r="D102" s="22" t="inlineStr">
+        <is>
+          <t>Works for any org.</t>
+        </is>
+      </c>
+      <c r="E102" s="23" t="n"/>
+      <c r="F102" s="22" t="n"/>
+      <c r="G102" s="23" t="n"/>
+    </row>
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="19" t="inlineStr">
+        <is>
+          <t>Cross-cutting</t>
+        </is>
+      </c>
+      <c r="B103" s="20" t="n"/>
+      <c r="C103" s="20" t="n"/>
+      <c r="D103" s="20" t="n"/>
+      <c r="E103" s="20" t="n"/>
+      <c r="F103" s="20" t="n"/>
+      <c r="G103" s="20" t="n"/>
+    </row>
+    <row r="104" ht="42" customHeight="1">
+      <c r="A104" s="21" t="inlineStr">
+        <is>
+          <t>X1</t>
+        </is>
+      </c>
+      <c r="B104" s="22" t="inlineStr">
+        <is>
+          <t>As a phone user, I want a usable mobile layout.</t>
+        </is>
+      </c>
+      <c r="C104" s="22" t="inlineStr">
+        <is>
+          <t>Open at phone width; use the menu drawer.</t>
+        </is>
+      </c>
+      <c r="D104" s="22" t="inlineStr">
+        <is>
+          <t>Layout adapts; drawer opens/closes; no horizontal scroll.</t>
+        </is>
+      </c>
+      <c r="E104" s="23" t="n"/>
+      <c r="F104" s="22" t="n"/>
+      <c r="G104" s="23" t="n"/>
+    </row>
+    <row r="105" ht="42" customHeight="1">
+      <c r="A105" s="21" t="inlineStr">
+        <is>
+          <t>X2</t>
+        </is>
+      </c>
+      <c r="B105" s="22" t="inlineStr">
+        <is>
+          <t>As a visitor, I want the recycling ribbon on the login page.</t>
+        </is>
+      </c>
+      <c r="C105" s="22" t="inlineStr">
+        <is>
+          <t>Open login signed out.</t>
+        </is>
+      </c>
+      <c r="D105" s="22" t="inlineStr">
+        <is>
+          <t>Green ribbon shows on login.</t>
+        </is>
+      </c>
+      <c r="E105" s="23" t="n"/>
+      <c r="F105" s="22" t="n"/>
+      <c r="G105" s="23" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A99:G99"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A55:G55"/>
     <mergeCell ref="A35:G35"/>
-    <mergeCell ref="A86:G86"/>
-    <mergeCell ref="A71:G71"/>
-    <mergeCell ref="A51:G51"/>
+    <mergeCell ref="A90:G90"/>
+    <mergeCell ref="A49:G49"/>
     <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="A103:G103"/>
+    <mergeCell ref="A75:G75"/>
   </mergeCells>
   <conditionalFormatting sqref="E4:E9">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
@@ -3950,7 +4050,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E36:E44">
+  <conditionalFormatting sqref="E36:E48">
     <cfRule type="cellIs" priority="7" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -3961,7 +4061,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E46:E50">
+  <conditionalFormatting sqref="E50:E54">
     <cfRule type="cellIs" priority="10" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -3972,7 +4072,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E52:E70">
+  <conditionalFormatting sqref="E56:E74">
     <cfRule type="cellIs" priority="13" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -3983,7 +4083,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E72:E85">
+  <conditionalFormatting sqref="E76:E89">
     <cfRule type="cellIs" priority="16" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -3994,7 +4094,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E87:E98">
+  <conditionalFormatting sqref="E91:E102">
     <cfRule type="cellIs" priority="19" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -4005,7 +4105,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E100:E101">
+  <conditionalFormatting sqref="E104:E105">
     <cfRule type="cellIs" priority="22" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -4017,7 +4117,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E4:E9 E11:E34 E36:E44 E46:E50 E52:E70 E72:E85 E87:E98 E100:E101" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E4:E9 E11:E34 E36:E48 E50:E54 E56:E74 E76:E89 E91:E102 E104:E105" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pass,Fail,Blocked,Not tested,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4031,7 +4131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:G105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5107,38 +5207,50 @@
       <c r="F44" s="22" t="n"/>
       <c r="G44" s="23" t="n"/>
     </row>
-    <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="19" t="inlineStr">
-        <is>
-          <t>Parent — viewer (grades 6–12 student)</t>
-        </is>
-      </c>
-      <c r="B45" s="20" t="n"/>
-      <c r="C45" s="20" t="n"/>
-      <c r="D45" s="20" t="n"/>
-      <c r="E45" s="20" t="n"/>
-      <c r="F45" s="20" t="n"/>
-      <c r="G45" s="20" t="n"/>
+    <row r="45" ht="42" customHeight="1">
+      <c r="A45" s="21" t="inlineStr">
+        <is>
+          <t>PE10</t>
+        </is>
+      </c>
+      <c r="B45" s="22" t="inlineStr">
+        <is>
+          <t>As a parent, I want to submit my child's hours after an event (child has no login).</t>
+        </is>
+      </c>
+      <c r="C45" s="22" t="inlineStr">
+        <is>
+          <t>Dashboard → the child's 'Submit hours (past events)' → enter hours → Submit.</t>
+        </is>
+      </c>
+      <c r="D45" s="22" t="inlineStr">
+        <is>
+          <t>Hours go to the supervisor for approval; status shows 'Waiting for review'.</t>
+        </is>
+      </c>
+      <c r="E45" s="23" t="n"/>
+      <c r="F45" s="22" t="n"/>
+      <c r="G45" s="23" t="n"/>
     </row>
     <row r="46" ht="42" customHeight="1">
       <c r="A46" s="21" t="inlineStr">
         <is>
-          <t>PV1</t>
+          <t>PE11</t>
         </is>
       </c>
       <c r="B46" s="22" t="inlineStr">
         <is>
-          <t>As a parent of a 6–12 student, I want to register for view-only access.</t>
+          <t>As a parent, I want to resubmit my child's rejected hours.</t>
         </is>
       </c>
       <c r="C46" s="22" t="inlineStr">
         <is>
-          <t>Create account → parent of a 6–12 student.</t>
+          <t>On a rejected past event, enter corrected hours → Resubmit.</t>
         </is>
       </c>
       <c r="D46" s="22" t="inlineStr">
         <is>
-          <t>Account created; no invite required to register.</t>
+          <t>Returns to 'Waiting for review'.</t>
         </is>
       </c>
       <c r="E46" s="23" t="n"/>
@@ -5148,22 +5260,22 @@
     <row r="47" ht="42" customHeight="1">
       <c r="A47" s="21" t="inlineStr">
         <is>
-          <t>PV2</t>
+          <t>PE12</t>
         </is>
       </c>
       <c r="B47" s="22" t="inlineStr">
         <is>
-          <t>As a viewer parent, my student links automatically by email.</t>
+          <t>As a parent, I want to see each past event's hours status for my child.</t>
         </is>
       </c>
       <c r="C47" s="22" t="inlineStr">
         <is>
-          <t>Have a student enter this exact email as their parent email (before or after you register).</t>
+          <t>Look at the child's past events list.</t>
         </is>
       </c>
       <c r="D47" s="22" t="inlineStr">
         <is>
-          <t>The student appears on your dashboard automatically; empty until then.</t>
+          <t>Each shows Approved / Waiting / Rejected as appropriate.</t>
         </is>
       </c>
       <c r="E47" s="23" t="n"/>
@@ -5173,110 +5285,110 @@
     <row r="48" ht="42" customHeight="1">
       <c r="A48" s="21" t="inlineStr">
         <is>
-          <t>PV3</t>
+          <t>PE13</t>
         </is>
       </c>
       <c r="B48" s="22" t="inlineStr">
         <is>
-          <t>As a viewer parent, I want to see my student's schedule/progress.</t>
+          <t>As a parent, all core participant actions are available to me for my child.</t>
         </is>
       </c>
       <c r="C48" s="22" t="inlineStr">
         <is>
-          <t>Open the dashboard.</t>
+          <t>Confirm: browse, sign up, withdraw, add-to-calendar, submit hours, view progress toward medals.</t>
         </is>
       </c>
       <c r="D48" s="22" t="inlineStr">
         <is>
-          <t>View-only schedule and progress.</t>
+          <t>All participant-style actions work on the child's behalf (the child never logs in).</t>
         </is>
       </c>
       <c r="E48" s="23" t="n"/>
       <c r="F48" s="22" t="n"/>
       <c r="G48" s="23" t="n"/>
     </row>
-    <row r="49" ht="42" customHeight="1">
-      <c r="A49" s="21" t="inlineStr">
-        <is>
-          <t>PV4</t>
-        </is>
-      </c>
-      <c r="B49" s="22" t="inlineStr">
-        <is>
-          <t>As a viewer parent, I do NOT sign the student up.</t>
-        </is>
-      </c>
-      <c r="C49" s="22" t="inlineStr">
-        <is>
-          <t>Look for a sign-up action.</t>
-        </is>
-      </c>
-      <c r="D49" s="22" t="inlineStr">
-        <is>
-          <t>No sign-up on the student's behalf — the student self-serves.</t>
-        </is>
-      </c>
-      <c r="E49" s="23" t="n"/>
-      <c r="F49" s="22" t="n"/>
-      <c r="G49" s="23" t="n"/>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="19" t="inlineStr">
+        <is>
+          <t>Parent — viewer (grades 6–12 student)</t>
+        </is>
+      </c>
+      <c r="B49" s="20" t="n"/>
+      <c r="C49" s="20" t="n"/>
+      <c r="D49" s="20" t="n"/>
+      <c r="E49" s="20" t="n"/>
+      <c r="F49" s="20" t="n"/>
+      <c r="G49" s="20" t="n"/>
     </row>
     <row r="50" ht="42" customHeight="1">
       <c r="A50" s="21" t="inlineStr">
         <is>
-          <t>PV5</t>
+          <t>PV1</t>
         </is>
       </c>
       <c r="B50" s="22" t="inlineStr">
         <is>
-          <t>As a viewer parent, I want to invite a co-guardian.</t>
+          <t>As a parent of a 6–12 student, I want to register for view-only access.</t>
         </is>
       </c>
       <c r="C50" s="22" t="inlineStr">
         <is>
-          <t>Invite a co-guardian by email.</t>
+          <t>Create account → parent of a 6–12 student.</t>
         </is>
       </c>
       <c r="D50" s="22" t="inlineStr">
         <is>
-          <t>Invite email sent; shared access on registration.</t>
+          <t>Account created; no invite required to register.</t>
         </is>
       </c>
       <c r="E50" s="23" t="n"/>
       <c r="F50" s="22" t="n"/>
       <c r="G50" s="23" t="n"/>
     </row>
-    <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="19" t="inlineStr">
-        <is>
-          <t>Supervisor (created by an Admin)</t>
-        </is>
-      </c>
-      <c r="B51" s="20" t="n"/>
-      <c r="C51" s="20" t="n"/>
-      <c r="D51" s="20" t="n"/>
-      <c r="E51" s="20" t="n"/>
-      <c r="F51" s="20" t="n"/>
-      <c r="G51" s="20" t="n"/>
+    <row r="51" ht="42" customHeight="1">
+      <c r="A51" s="21" t="inlineStr">
+        <is>
+          <t>PV2</t>
+        </is>
+      </c>
+      <c r="B51" s="22" t="inlineStr">
+        <is>
+          <t>As a viewer parent, my student links automatically by email.</t>
+        </is>
+      </c>
+      <c r="C51" s="22" t="inlineStr">
+        <is>
+          <t>Have a student enter this exact email as their parent email (before or after you register).</t>
+        </is>
+      </c>
+      <c r="D51" s="22" t="inlineStr">
+        <is>
+          <t>The student appears on your dashboard automatically; empty until then.</t>
+        </is>
+      </c>
+      <c r="E51" s="23" t="n"/>
+      <c r="F51" s="22" t="n"/>
+      <c r="G51" s="23" t="n"/>
     </row>
     <row r="52" ht="42" customHeight="1">
       <c r="A52" s="21" t="inlineStr">
         <is>
-          <t>SV1</t>
+          <t>PV3</t>
         </is>
       </c>
       <c r="B52" s="22" t="inlineStr">
         <is>
-          <t>As the program, a supervisor cannot self-register.</t>
+          <t>As a viewer parent, I want to see my student's schedule/progress.</t>
         </is>
       </c>
       <c r="C52" s="22" t="inlineStr">
         <is>
-          <t>Review the sign-up options.</t>
+          <t>Open the dashboard.</t>
         </is>
       </c>
       <c r="D52" s="22" t="inlineStr">
         <is>
-          <t>No supervisor option exists on registration.</t>
+          <t>View-only schedule and progress.</t>
         </is>
       </c>
       <c r="E52" s="23" t="n"/>
@@ -5286,22 +5398,22 @@
     <row r="53" ht="42" customHeight="1">
       <c r="A53" s="21" t="inlineStr">
         <is>
-          <t>SV2</t>
+          <t>PV4</t>
         </is>
       </c>
       <c r="B53" s="22" t="inlineStr">
         <is>
-          <t>As a new supervisor, I get an invite to set my password.</t>
+          <t>As a viewer parent, I do NOT sign the student up.</t>
         </is>
       </c>
       <c r="C53" s="22" t="inlineStr">
         <is>
-          <t>Have an Admin create your account; open the invite email; set password; sign in.</t>
+          <t>Look for a sign-up action.</t>
         </is>
       </c>
       <c r="D53" s="22" t="inlineStr">
         <is>
-          <t>Invite email arrives with a working set-password link; you can sign in.</t>
+          <t>No sign-up on the student's behalf — the student self-serves.</t>
         </is>
       </c>
       <c r="E53" s="23" t="n"/>
@@ -5311,72 +5423,60 @@
     <row r="54" ht="42" customHeight="1">
       <c r="A54" s="21" t="inlineStr">
         <is>
-          <t>SV3</t>
+          <t>PV5</t>
         </is>
       </c>
       <c r="B54" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want the correct 7 left-menu tabs.</t>
+          <t>As a viewer parent, I want to invite a co-guardian.</t>
         </is>
       </c>
       <c r="C54" s="22" t="inlineStr">
         <is>
-          <t>Look at the left menu.</t>
+          <t>Invite a co-guardian by email.</t>
         </is>
       </c>
       <c r="D54" s="22" t="inlineStr">
         <is>
-          <t>Dashboard, Pending Reviews, Reviewed History, My Events, All Opportunities, My Hours, Help.</t>
+          <t>Invite email sent; shared access on registration.</t>
         </is>
       </c>
       <c r="E54" s="23" t="n"/>
       <c r="F54" s="22" t="n"/>
       <c r="G54" s="23" t="n"/>
     </row>
-    <row r="55" ht="42" customHeight="1">
-      <c r="A55" s="21" t="inlineStr">
-        <is>
-          <t>SV4</t>
-        </is>
-      </c>
-      <c r="B55" s="22" t="inlineStr">
-        <is>
-          <t>As a supervisor, I want a dashboard.</t>
-        </is>
-      </c>
-      <c r="C55" s="22" t="inlineStr">
-        <is>
-          <t>Open the dashboard.</t>
-        </is>
-      </c>
-      <c r="D55" s="22" t="inlineStr">
-        <is>
-          <t>Review queue, approved/rejected counts, registrations, hours, upcoming events + Roster links.</t>
-        </is>
-      </c>
-      <c r="E55" s="23" t="n"/>
-      <c r="F55" s="22" t="n"/>
-      <c r="G55" s="23" t="n"/>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="19" t="inlineStr">
+        <is>
+          <t>Supervisor (created by an Admin)</t>
+        </is>
+      </c>
+      <c r="B55" s="20" t="n"/>
+      <c r="C55" s="20" t="n"/>
+      <c r="D55" s="20" t="n"/>
+      <c r="E55" s="20" t="n"/>
+      <c r="F55" s="20" t="n"/>
+      <c r="G55" s="20" t="n"/>
     </row>
     <row r="56" ht="42" customHeight="1">
       <c r="A56" s="21" t="inlineStr">
         <is>
-          <t>SV5</t>
+          <t>SV1</t>
         </is>
       </c>
       <c r="B56" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to approve hours.</t>
+          <t>As the program, a supervisor cannot self-register.</t>
         </is>
       </c>
       <c r="C56" s="22" t="inlineStr">
         <is>
-          <t>Pending Reviews → open → Approve.</t>
+          <t>Review the sign-up options.</t>
         </is>
       </c>
       <c r="D56" s="22" t="inlineStr">
         <is>
-          <t>Approved; moves to Reviewed History; participant total updates; email sent.</t>
+          <t>No supervisor option exists on registration.</t>
         </is>
       </c>
       <c r="E56" s="23" t="n"/>
@@ -5386,22 +5486,22 @@
     <row r="57" ht="42" customHeight="1">
       <c r="A57" s="21" t="inlineStr">
         <is>
-          <t>SV6</t>
+          <t>SV2</t>
         </is>
       </c>
       <c r="B57" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to reject hours with a reason.</t>
+          <t>As a new supervisor, I get an invite to set my password.</t>
         </is>
       </c>
       <c r="C57" s="22" t="inlineStr">
         <is>
-          <t>Reject without a reason, then with one.</t>
+          <t>Have an Admin create your account; open the invite email; set password; sign in.</t>
         </is>
       </c>
       <c r="D57" s="22" t="inlineStr">
         <is>
-          <t>Blocked until a reason is given; then rejected and the participant notified.</t>
+          <t>Invite email arrives with a working set-password link; you can sign in.</t>
         </is>
       </c>
       <c r="E57" s="23" t="n"/>
@@ -5411,22 +5511,22 @@
     <row r="58" ht="42" customHeight="1">
       <c r="A58" s="21" t="inlineStr">
         <is>
-          <t>SV7</t>
+          <t>SV3</t>
         </is>
       </c>
       <c r="B58" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to review external submissions.</t>
+          <t>As a supervisor, I want the correct 7 left-menu tabs.</t>
         </is>
       </c>
       <c r="C58" s="22" t="inlineStr">
         <is>
-          <t>Pending Reviews → external tab → approve/reject.</t>
+          <t>Look at the left menu.</t>
         </is>
       </c>
       <c r="D58" s="22" t="inlineStr">
         <is>
-          <t>External items reviewable, including any proof.</t>
+          <t>Dashboard, Pending Reviews, Reviewed History, My Events, All Opportunities, My Hours, Help.</t>
         </is>
       </c>
       <c r="E58" s="23" t="n"/>
@@ -5436,22 +5536,22 @@
     <row r="59" ht="42" customHeight="1">
       <c r="A59" s="21" t="inlineStr">
         <is>
-          <t>SV8</t>
+          <t>SV4</t>
         </is>
       </c>
       <c r="B59" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to create an event.</t>
+          <t>As a supervisor, I want a dashboard.</t>
         </is>
       </c>
       <c r="C59" s="22" t="inlineStr">
         <is>
-          <t>New Event → title, description, slot, address, date, times, capacity, grade limits → save.</t>
+          <t>Open the dashboard.</t>
         </is>
       </c>
       <c r="D59" s="22" t="inlineStr">
         <is>
-          <t>Credit auto-calculated from times; event created in My Events.</t>
+          <t>Review queue, approved/rejected counts, registrations, hours, upcoming events + Roster links.</t>
         </is>
       </c>
       <c r="E59" s="23" t="n"/>
@@ -5461,22 +5561,22 @@
     <row r="60" ht="42" customHeight="1">
       <c r="A60" s="21" t="inlineStr">
         <is>
-          <t>SV9</t>
+          <t>SV5</t>
         </is>
       </c>
       <c r="B60" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to edit an event.</t>
+          <t>As a supervisor, I want to approve hours.</t>
         </is>
       </c>
       <c r="C60" s="22" t="inlineStr">
         <is>
-          <t>My Events → edit → save.</t>
+          <t>Pending Reviews → open → Approve.</t>
         </is>
       </c>
       <c r="D60" s="22" t="inlineStr">
         <is>
-          <t>Changes persist and show to participants.</t>
+          <t>Approved; moves to Reviewed History; participant total updates; email sent.</t>
         </is>
       </c>
       <c r="E60" s="23" t="n"/>
@@ -5486,22 +5586,22 @@
     <row r="61" ht="42" customHeight="1">
       <c r="A61" s="21" t="inlineStr">
         <is>
-          <t>SV10</t>
+          <t>SV6</t>
         </is>
       </c>
       <c r="B61" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to delete an event with no approved hours.</t>
+          <t>As a supervisor, I want to reject hours with a reason.</t>
         </is>
       </c>
       <c r="C61" s="22" t="inlineStr">
         <is>
-          <t>Delete such an event → confirm.</t>
+          <t>Reject without a reason, then with one.</t>
         </is>
       </c>
       <c r="D61" s="22" t="inlineStr">
         <is>
-          <t>Event deleted.</t>
+          <t>Blocked until a reason is given; then rejected and the participant notified.</t>
         </is>
       </c>
       <c r="E61" s="23" t="n"/>
@@ -5511,22 +5611,22 @@
     <row r="62" ht="42" customHeight="1">
       <c r="A62" s="21" t="inlineStr">
         <is>
-          <t>SV11</t>
+          <t>SV7</t>
         </is>
       </c>
       <c r="B62" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, deleting an event with approved hours is blocked.</t>
+          <t>As a supervisor, I want to review external submissions.</t>
         </is>
       </c>
       <c r="C62" s="22" t="inlineStr">
         <is>
-          <t>Try to delete an event that has approved hours.</t>
+          <t>Pending Reviews → external tab → approve/reject.</t>
         </is>
       </c>
       <c r="D62" s="22" t="inlineStr">
         <is>
-          <t>Blocked with a message that approved hours must be preserved.</t>
+          <t>External items reviewable, including any proof.</t>
         </is>
       </c>
       <c r="E62" s="23" t="n"/>
@@ -5536,22 +5636,22 @@
     <row r="63" ht="42" customHeight="1">
       <c r="A63" s="21" t="inlineStr">
         <is>
-          <t>SV12</t>
+          <t>SV8</t>
         </is>
       </c>
       <c r="B63" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to see who signed up.</t>
+          <t>As a supervisor, I want to create an event.</t>
         </is>
       </c>
       <c r="C63" s="22" t="inlineStr">
         <is>
-          <t>Open the event Roster.</t>
+          <t>New Event → title, description, slot, address, date, times, capacity, grade limits → save.</t>
         </is>
       </c>
       <c r="D63" s="22" t="inlineStr">
         <is>
-          <t>Registrants listed with grade and status.</t>
+          <t>Credit auto-calculated from times; event created in My Events.</t>
         </is>
       </c>
       <c r="E63" s="23" t="n"/>
@@ -5561,22 +5661,22 @@
     <row r="64" ht="42" customHeight="1">
       <c r="A64" s="21" t="inlineStr">
         <is>
-          <t>SV13</t>
+          <t>SV9</t>
         </is>
       </c>
       <c r="B64" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to check people in / mark no-show.</t>
+          <t>As a supervisor, I want to edit an event.</t>
         </is>
       </c>
       <c r="C64" s="22" t="inlineStr">
         <is>
-          <t>On the roster, Check in and Mark no-show.</t>
+          <t>My Events → edit → save.</t>
         </is>
       </c>
       <c r="D64" s="22" t="inlineStr">
         <is>
-          <t>Status updates and persists.</t>
+          <t>Changes persist and show to participants.</t>
         </is>
       </c>
       <c r="E64" s="23" t="n"/>
@@ -5586,22 +5686,22 @@
     <row r="65" ht="42" customHeight="1">
       <c r="A65" s="21" t="inlineStr">
         <is>
-          <t>SV14</t>
+          <t>SV10</t>
         </is>
       </c>
       <c r="B65" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to message everyone signed up.</t>
+          <t>As a supervisor, I want to delete an event with no approved hours.</t>
         </is>
       </c>
       <c r="C65" s="22" t="inlineStr">
         <is>
-          <t>Roster → Message attendees → subject+message → send (include guardians on).</t>
+          <t>Delete such an event → confirm.</t>
         </is>
       </c>
       <c r="D65" s="22" t="inlineStr">
         <is>
-          <t>Each registrant (and guardians) emailed individually; recipient count shown.</t>
+          <t>Event deleted.</t>
         </is>
       </c>
       <c r="E65" s="23" t="n"/>
@@ -5611,22 +5711,22 @@
     <row r="66" ht="42" customHeight="1">
       <c r="A66" s="21" t="inlineStr">
         <is>
-          <t>SV15</t>
+          <t>SV11</t>
         </is>
       </c>
       <c r="B66" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want a history of what I reviewed.</t>
+          <t>As a supervisor, deleting an event with approved hours is blocked.</t>
         </is>
       </c>
       <c r="C66" s="22" t="inlineStr">
         <is>
-          <t>Open Reviewed History.</t>
+          <t>Try to delete an event that has approved hours.</t>
         </is>
       </c>
       <c r="D66" s="22" t="inlineStr">
         <is>
-          <t>Every approved/rejected item with dates and volunteers.</t>
+          <t>Blocked with a message that approved hours must be preserved.</t>
         </is>
       </c>
       <c r="E66" s="23" t="n"/>
@@ -5636,22 +5736,22 @@
     <row r="67" ht="42" customHeight="1">
       <c r="A67" s="21" t="inlineStr">
         <is>
-          <t>SV16</t>
+          <t>SV12</t>
         </is>
       </c>
       <c r="B67" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to browse all opportunities view-only.</t>
+          <t>As a supervisor, I want to see who signed up.</t>
         </is>
       </c>
       <c r="C67" s="22" t="inlineStr">
         <is>
-          <t>All Opportunities → search / upcoming-past.</t>
+          <t>Open the event Roster.</t>
         </is>
       </c>
       <c r="D67" s="22" t="inlineStr">
         <is>
-          <t>Every event listed read-only; can't edit others' events.</t>
+          <t>Registrants listed with grade and status.</t>
         </is>
       </c>
       <c r="E67" s="23" t="n"/>
@@ -5661,22 +5761,22 @@
     <row r="68" ht="42" customHeight="1">
       <c r="A68" s="21" t="inlineStr">
         <is>
-          <t>SV17</t>
+          <t>SV13</t>
         </is>
       </c>
       <c r="B68" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to log my own adult hours.</t>
+          <t>As a supervisor, I want to check people in / mark no-show.</t>
         </is>
       </c>
       <c r="C68" s="22" t="inlineStr">
         <is>
-          <t>My Hours → log an activity, date, hours → save.</t>
+          <t>On the roster, Check in and Mark no-show.</t>
         </is>
       </c>
       <c r="D68" s="22" t="inlineStr">
         <is>
-          <t>Recorded instantly with a running total; clearly NOT part of the student competition.</t>
+          <t>Status updates and persists.</t>
         </is>
       </c>
       <c r="E68" s="23" t="n"/>
@@ -5686,22 +5786,22 @@
     <row r="69" ht="42" customHeight="1">
       <c r="A69" s="21" t="inlineStr">
         <is>
-          <t>SV18</t>
+          <t>SV14</t>
         </is>
       </c>
       <c r="B69" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to delete an adult-hours entry.</t>
+          <t>As a supervisor, I want to message everyone signed up.</t>
         </is>
       </c>
       <c r="C69" s="22" t="inlineStr">
         <is>
-          <t>My Hours → delete an entry → confirm.</t>
+          <t>Roster → Message attendees → subject+message → send (include guardians on).</t>
         </is>
       </c>
       <c r="D69" s="22" t="inlineStr">
         <is>
-          <t>Removed; total updates.</t>
+          <t>Each registrant (and guardians) emailed individually; recipient count shown.</t>
         </is>
       </c>
       <c r="E69" s="23" t="n"/>
@@ -5711,60 +5811,72 @@
     <row r="70" ht="42" customHeight="1">
       <c r="A70" s="21" t="inlineStr">
         <is>
-          <t>SV19</t>
+          <t>SV15</t>
         </is>
       </c>
       <c r="B70" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I must NOT access user or org management.</t>
+          <t>As a supervisor, I want a history of what I reviewed.</t>
         </is>
       </c>
       <c r="C70" s="22" t="inlineStr">
         <is>
-          <t>Look for Users / Organizations in the menu.</t>
+          <t>Open Reviewed History.</t>
         </is>
       </c>
       <c r="D70" s="22" t="inlineStr">
         <is>
-          <t>Those tabs are absent; direct URLs are blocked.</t>
+          <t>Every approved/rejected item with dates and volunteers.</t>
         </is>
       </c>
       <c r="E70" s="23" t="n"/>
       <c r="F70" s="22" t="n"/>
       <c r="G70" s="23" t="n"/>
     </row>
-    <row r="71" ht="20" customHeight="1">
-      <c r="A71" s="19" t="inlineStr">
-        <is>
-          <t>Admin (org-scoped)</t>
-        </is>
-      </c>
-      <c r="B71" s="20" t="n"/>
-      <c r="C71" s="20" t="n"/>
-      <c r="D71" s="20" t="n"/>
-      <c r="E71" s="20" t="n"/>
-      <c r="F71" s="20" t="n"/>
-      <c r="G71" s="20" t="n"/>
+    <row r="71" ht="42" customHeight="1">
+      <c r="A71" s="21" t="inlineStr">
+        <is>
+          <t>SV16</t>
+        </is>
+      </c>
+      <c r="B71" s="22" t="inlineStr">
+        <is>
+          <t>As a supervisor, I want to browse all opportunities view-only.</t>
+        </is>
+      </c>
+      <c r="C71" s="22" t="inlineStr">
+        <is>
+          <t>All Opportunities → search / upcoming-past.</t>
+        </is>
+      </c>
+      <c r="D71" s="22" t="inlineStr">
+        <is>
+          <t>Every event listed read-only; can't edit others' events.</t>
+        </is>
+      </c>
+      <c r="E71" s="23" t="n"/>
+      <c r="F71" s="22" t="n"/>
+      <c r="G71" s="23" t="n"/>
     </row>
     <row r="72" ht="42" customHeight="1">
       <c r="A72" s="21" t="inlineStr">
         <is>
-          <t>AD1</t>
+          <t>SV17</t>
         </is>
       </c>
       <c r="B72" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I want the correct menu tabs.</t>
+          <t>As a supervisor, I want to log my own adult hours.</t>
         </is>
       </c>
       <c r="C72" s="22" t="inlineStr">
         <is>
-          <t>Look at the left menu.</t>
+          <t>My Hours → log an activity, date, hours → save.</t>
         </is>
       </c>
       <c r="D72" s="22" t="inlineStr">
         <is>
-          <t>Dashboard, Pending Reviews, Reviewed History, My Events, All Opportunities, Users, Organizations, My Hours, Help.</t>
+          <t>Recorded instantly with a running total; clearly NOT part of the student competition.</t>
         </is>
       </c>
       <c r="E72" s="23" t="n"/>
@@ -5774,22 +5886,22 @@
     <row r="73" ht="42" customHeight="1">
       <c r="A73" s="21" t="inlineStr">
         <is>
-          <t>AD2</t>
+          <t>SV18</t>
         </is>
       </c>
       <c r="B73" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I can do everything a supervisor can.</t>
+          <t>As a supervisor, I want to delete an adult-hours entry.</t>
         </is>
       </c>
       <c r="C73" s="22" t="inlineStr">
         <is>
-          <t>Spot-check: approve an item and create an event.</t>
+          <t>My Hours → delete an entry → confirm.</t>
         </is>
       </c>
       <c r="D73" s="22" t="inlineStr">
         <is>
-          <t>Both work.</t>
+          <t>Removed; total updates.</t>
         </is>
       </c>
       <c r="E73" s="23" t="n"/>
@@ -5799,72 +5911,60 @@
     <row r="74" ht="42" customHeight="1">
       <c r="A74" s="21" t="inlineStr">
         <is>
-          <t>AD3</t>
+          <t>SV19</t>
         </is>
       </c>
       <c r="B74" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I only see my org's non-admin users.</t>
+          <t>As a supervisor, I must NOT access user or org management.</t>
         </is>
       </c>
       <c r="C74" s="22" t="inlineStr">
         <is>
-          <t>Open Users.</t>
+          <t>Look for Users / Organizations in the menu.</t>
         </is>
       </c>
       <c r="D74" s="22" t="inlineStr">
         <is>
-          <t>Only participants/parents/supervisors in your org; no admins/super admins; no other orgs.</t>
+          <t>Those tabs are absent; direct URLs are blocked.</t>
         </is>
       </c>
       <c r="E74" s="23" t="n"/>
       <c r="F74" s="22" t="n"/>
       <c r="G74" s="23" t="n"/>
     </row>
-    <row r="75" ht="42" customHeight="1">
-      <c r="A75" s="21" t="inlineStr">
-        <is>
-          <t>AD4</t>
-        </is>
-      </c>
-      <c r="B75" s="22" t="inlineStr">
-        <is>
-          <t>As an Admin, I want to add a supervisor.</t>
-        </is>
-      </c>
-      <c r="C75" s="22" t="inlineStr">
-        <is>
-          <t>Users → Add user → Supervisor → save.</t>
-        </is>
-      </c>
-      <c r="D75" s="22" t="inlineStr">
-        <is>
-          <t>Supervisor created, stamped to your org; invite email sent.</t>
-        </is>
-      </c>
-      <c r="E75" s="23" t="n"/>
-      <c r="F75" s="22" t="n"/>
-      <c r="G75" s="23" t="n"/>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="19" t="inlineStr">
+        <is>
+          <t>Admin (org-scoped)</t>
+        </is>
+      </c>
+      <c r="B75" s="20" t="n"/>
+      <c r="C75" s="20" t="n"/>
+      <c r="D75" s="20" t="n"/>
+      <c r="E75" s="20" t="n"/>
+      <c r="F75" s="20" t="n"/>
+      <c r="G75" s="20" t="n"/>
     </row>
     <row r="76" ht="42" customHeight="1">
       <c r="A76" s="21" t="inlineStr">
         <is>
-          <t>AD5</t>
+          <t>AD1</t>
         </is>
       </c>
       <c r="B76" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I want to create a participant as a fallback.</t>
+          <t>As an Admin, I want the correct menu tabs.</t>
         </is>
       </c>
       <c r="C76" s="22" t="inlineStr">
         <is>
-          <t>Users → Add user → Participant → save.</t>
+          <t>Look at the left menu.</t>
         </is>
       </c>
       <c r="D76" s="22" t="inlineStr">
         <is>
-          <t>Participant created with a set-password invite (no silent password).</t>
+          <t>Dashboard, Pending Reviews, Reviewed History, My Events, All Opportunities, Users, Organizations, My Hours, Help.</t>
         </is>
       </c>
       <c r="E76" s="23" t="n"/>
@@ -5874,22 +5974,22 @@
     <row r="77" ht="42" customHeight="1">
       <c r="A77" s="21" t="inlineStr">
         <is>
-          <t>AD6</t>
+          <t>AD2</t>
         </is>
       </c>
       <c r="B77" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I want to grant participant hours.</t>
+          <t>As an Admin, I can do everything a supervisor can.</t>
         </is>
       </c>
       <c r="C77" s="22" t="inlineStr">
         <is>
-          <t>Open a participant in your org → Add hours.</t>
+          <t>Spot-check: approve an item and create an event.</t>
         </is>
       </c>
       <c r="D77" s="22" t="inlineStr">
         <is>
-          <t>Hours auto-approved; count toward their total/medals.</t>
+          <t>Both work.</t>
         </is>
       </c>
       <c r="E77" s="23" t="n"/>
@@ -5899,22 +5999,22 @@
     <row r="78" ht="42" customHeight="1">
       <c r="A78" s="21" t="inlineStr">
         <is>
-          <t>AD7</t>
+          <t>AD3</t>
         </is>
       </c>
       <c r="B78" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I want a participant's service record.</t>
+          <t>As an Admin, I only see my org's non-admin users.</t>
         </is>
       </c>
       <c r="C78" s="22" t="inlineStr">
         <is>
-          <t>Users → Service record for a participant in your org.</t>
+          <t>Open Users.</t>
         </is>
       </c>
       <c r="D78" s="22" t="inlineStr">
         <is>
-          <t>Record opens.</t>
+          <t>Only participants/parents/supervisors in your org; no admins/super admins; no other orgs.</t>
         </is>
       </c>
       <c r="E78" s="23" t="n"/>
@@ -5924,22 +6024,22 @@
     <row r="79" ht="42" customHeight="1">
       <c r="A79" s="21" t="inlineStr">
         <is>
-          <t>AD8</t>
+          <t>AD4</t>
         </is>
       </c>
       <c r="B79" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I want to edit/delete my org's users.</t>
+          <t>As an Admin, I want to add a supervisor.</t>
         </is>
       </c>
       <c r="C79" s="22" t="inlineStr">
         <is>
-          <t>Edit a name/phone; delete a test user.</t>
+          <t>Users → Add user → Supervisor → save.</t>
         </is>
       </c>
       <c r="D79" s="22" t="inlineStr">
         <is>
-          <t>Changes apply within your org.</t>
+          <t>Supervisor created, stamped to your org; invite email sent.</t>
         </is>
       </c>
       <c r="E79" s="23" t="n"/>
@@ -5949,22 +6049,22 @@
     <row r="80" ht="42" customHeight="1">
       <c r="A80" s="21" t="inlineStr">
         <is>
-          <t>AD9</t>
+          <t>AD5</t>
         </is>
       </c>
       <c r="B80" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I must NOT act on users outside my org.</t>
+          <t>As an Admin, I want to create a participant as a fallback.</t>
         </is>
       </c>
       <c r="C80" s="22" t="inlineStr">
         <is>
-          <t>Attempt to reach another org's user (e.g. direct URL).</t>
+          <t>Users → Add user → Participant → save.</t>
         </is>
       </c>
       <c r="D80" s="22" t="inlineStr">
         <is>
-          <t>Blocked / not visible.</t>
+          <t>Participant created with a set-password invite (no silent password).</t>
         </is>
       </c>
       <c r="E80" s="23" t="n"/>
@@ -5974,22 +6074,22 @@
     <row r="81" ht="42" customHeight="1">
       <c r="A81" s="21" t="inlineStr">
         <is>
-          <t>AD10</t>
+          <t>AD6</t>
         </is>
       </c>
       <c r="B81" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I cannot grant Admin access or manage admins.</t>
+          <t>As an Admin, I want to grant participant hours.</t>
         </is>
       </c>
       <c r="C81" s="22" t="inlineStr">
         <is>
-          <t>Look for the 'grant Admin access' action.</t>
+          <t>Open a participant in your org → Add hours.</t>
         </is>
       </c>
       <c r="D81" s="22" t="inlineStr">
         <is>
-          <t>No such button; attempts are blocked server-side.</t>
+          <t>Hours auto-approved; count toward their total/medals.</t>
         </is>
       </c>
       <c r="E81" s="23" t="n"/>
@@ -5999,22 +6099,22 @@
     <row r="82" ht="42" customHeight="1">
       <c r="A82" s="21" t="inlineStr">
         <is>
-          <t>AD11</t>
+          <t>AD7</t>
         </is>
       </c>
       <c r="B82" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I see and edit only my own organization.</t>
+          <t>As an Admin, I want a participant's service record.</t>
         </is>
       </c>
       <c r="C82" s="22" t="inlineStr">
         <is>
-          <t>Open Organizations.</t>
+          <t>Users → Service record for a participant in your org.</t>
         </is>
       </c>
       <c r="D82" s="22" t="inlineStr">
         <is>
-          <t>Only your org shows; you can edit its settings.</t>
+          <t>Record opens.</t>
         </is>
       </c>
       <c r="E82" s="23" t="n"/>
@@ -6024,22 +6124,22 @@
     <row r="83" ht="42" customHeight="1">
       <c r="A83" s="21" t="inlineStr">
         <is>
-          <t>AD12</t>
+          <t>AD8</t>
         </is>
       </c>
       <c r="B83" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I want to generate/rotate my org's join code.</t>
+          <t>As an Admin, I want to edit/delete my org's users.</t>
         </is>
       </c>
       <c r="C83" s="22" t="inlineStr">
         <is>
-          <t>Organizations → set/generate a join code → save.</t>
+          <t>Edit a name/phone; delete a test user.</t>
         </is>
       </c>
       <c r="D83" s="22" t="inlineStr">
         <is>
-          <t>Join code saved; usable at sign-up.</t>
+          <t>Changes apply within your org.</t>
         </is>
       </c>
       <c r="E83" s="23" t="n"/>
@@ -6049,22 +6149,22 @@
     <row r="84" ht="42" customHeight="1">
       <c r="A84" s="21" t="inlineStr">
         <is>
-          <t>AD13</t>
+          <t>AD9</t>
         </is>
       </c>
       <c r="B84" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I cannot create organizations.</t>
+          <t>As an Admin, I must NOT act on users outside my org.</t>
         </is>
       </c>
       <c r="C84" s="22" t="inlineStr">
         <is>
-          <t>Look for 'Add organization'.</t>
+          <t>Attempt to reach another org's user (e.g. direct URL).</t>
         </is>
       </c>
       <c r="D84" s="22" t="inlineStr">
         <is>
-          <t>No Add button; creation blocked.</t>
+          <t>Blocked / not visible.</t>
         </is>
       </c>
       <c r="E84" s="23" t="n"/>
@@ -6074,60 +6174,72 @@
     <row r="85" ht="42" customHeight="1">
       <c r="A85" s="21" t="inlineStr">
         <is>
-          <t>AD14</t>
+          <t>AD10</t>
         </is>
       </c>
       <c r="B85" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I cannot change the recycling cans total.</t>
+          <t>As an Admin, I cannot grant Admin access or manage admins.</t>
         </is>
       </c>
       <c r="C85" s="22" t="inlineStr">
         <is>
-          <t>Look for the cans/bin admin control.</t>
+          <t>Look for the 'grant Admin access' action.</t>
         </is>
       </c>
       <c r="D85" s="22" t="inlineStr">
         <is>
-          <t>Not available (Super Admin only).</t>
+          <t>No such button; attempts are blocked server-side.</t>
         </is>
       </c>
       <c r="E85" s="23" t="n"/>
       <c r="F85" s="22" t="n"/>
       <c r="G85" s="23" t="n"/>
     </row>
-    <row r="86" ht="20" customHeight="1">
-      <c r="A86" s="19" t="inlineStr">
-        <is>
-          <t>Super Admin (global)</t>
-        </is>
-      </c>
-      <c r="B86" s="20" t="n"/>
-      <c r="C86" s="20" t="n"/>
-      <c r="D86" s="20" t="n"/>
-      <c r="E86" s="20" t="n"/>
-      <c r="F86" s="20" t="n"/>
-      <c r="G86" s="20" t="n"/>
+    <row r="86" ht="42" customHeight="1">
+      <c r="A86" s="21" t="inlineStr">
+        <is>
+          <t>AD11</t>
+        </is>
+      </c>
+      <c r="B86" s="22" t="inlineStr">
+        <is>
+          <t>As an Admin, I see and edit only my own organization.</t>
+        </is>
+      </c>
+      <c r="C86" s="22" t="inlineStr">
+        <is>
+          <t>Open Organizations.</t>
+        </is>
+      </c>
+      <c r="D86" s="22" t="inlineStr">
+        <is>
+          <t>Only your org shows; you can edit its settings.</t>
+        </is>
+      </c>
+      <c r="E86" s="23" t="n"/>
+      <c r="F86" s="22" t="n"/>
+      <c r="G86" s="23" t="n"/>
     </row>
     <row r="87" ht="42" customHeight="1">
       <c r="A87" s="21" t="inlineStr">
         <is>
-          <t>SA1</t>
+          <t>AD12</t>
         </is>
       </c>
       <c r="B87" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want the correct menu tabs.</t>
+          <t>As an Admin, I want to generate/rotate my org's join code.</t>
         </is>
       </c>
       <c r="C87" s="22" t="inlineStr">
         <is>
-          <t>Look at the left menu.</t>
+          <t>Organizations → set/generate a join code → save.</t>
         </is>
       </c>
       <c r="D87" s="22" t="inlineStr">
         <is>
-          <t>Dashboard, Reports, Users, Events, Organizations (Help in footer).</t>
+          <t>Join code saved; usable at sign-up.</t>
         </is>
       </c>
       <c r="E87" s="23" t="n"/>
@@ -6137,22 +6249,22 @@
     <row r="88" ht="42" customHeight="1">
       <c r="A88" s="21" t="inlineStr">
         <is>
-          <t>SA2</t>
+          <t>AD13</t>
         </is>
       </c>
       <c r="B88" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I can do everything an Admin can, across all orgs.</t>
+          <t>As an Admin, I cannot create organizations.</t>
         </is>
       </c>
       <c r="C88" s="22" t="inlineStr">
         <is>
-          <t>Spot-check user + org actions on more than one org.</t>
+          <t>Look for 'Add organization'.</t>
         </is>
       </c>
       <c r="D88" s="22" t="inlineStr">
         <is>
-          <t>All allowed regardless of org.</t>
+          <t>No Add button; creation blocked.</t>
         </is>
       </c>
       <c r="E88" s="23" t="n"/>
@@ -6162,72 +6274,60 @@
     <row r="89" ht="42" customHeight="1">
       <c r="A89" s="21" t="inlineStr">
         <is>
-          <t>SA3</t>
+          <t>AD14</t>
         </is>
       </c>
       <c r="B89" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to create users incl. Supervisor and Super Admin.</t>
+          <t>As an Admin, I cannot change the recycling cans total.</t>
         </is>
       </c>
       <c r="C89" s="22" t="inlineStr">
         <is>
-          <t>Users → Add user → each role.</t>
+          <t>Look for the cans/bin admin control.</t>
         </is>
       </c>
       <c r="D89" s="22" t="inlineStr">
         <is>
-          <t>Participant/Supervisor/Super Admin options available; account created + invite email.</t>
+          <t>Not available (Super Admin only).</t>
         </is>
       </c>
       <c r="E89" s="23" t="n"/>
       <c r="F89" s="22" t="n"/>
       <c r="G89" s="23" t="n"/>
     </row>
-    <row r="90" ht="42" customHeight="1">
-      <c r="A90" s="21" t="inlineStr">
-        <is>
-          <t>SA4</t>
-        </is>
-      </c>
-      <c r="B90" s="22" t="inlineStr">
-        <is>
-          <t>As a Super Admin, I want to grant/revoke Admin access.</t>
-        </is>
-      </c>
-      <c r="C90" s="22" t="inlineStr">
-        <is>
-          <t>Open a user → grant Admin access → check org(s) → save; then uncheck all → save.</t>
-        </is>
-      </c>
-      <c r="D90" s="22" t="inlineStr">
-        <is>
-          <t>Checking orgs makes an Admin; unchecking all reverts to participant.</t>
-        </is>
-      </c>
-      <c r="E90" s="23" t="n"/>
-      <c r="F90" s="22" t="n"/>
-      <c r="G90" s="23" t="n"/>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="19" t="inlineStr">
+        <is>
+          <t>Super Admin (global)</t>
+        </is>
+      </c>
+      <c r="B90" s="20" t="n"/>
+      <c r="C90" s="20" t="n"/>
+      <c r="D90" s="20" t="n"/>
+      <c r="E90" s="20" t="n"/>
+      <c r="F90" s="20" t="n"/>
+      <c r="G90" s="20" t="n"/>
     </row>
     <row r="91" ht="42" customHeight="1">
       <c r="A91" s="21" t="inlineStr">
         <is>
-          <t>SA5</t>
+          <t>SA1</t>
         </is>
       </c>
       <c r="B91" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to create organizations + join codes.</t>
+          <t>As a Super Admin, I want the correct menu tabs.</t>
         </is>
       </c>
       <c r="C91" s="22" t="inlineStr">
         <is>
-          <t>Organizations → Add organization → set details + join code.</t>
+          <t>Look at the left menu.</t>
         </is>
       </c>
       <c r="D91" s="22" t="inlineStr">
         <is>
-          <t>Org created with its join code.</t>
+          <t>Dashboard, Reports, Users, Events, Organizations (Help in footer).</t>
         </is>
       </c>
       <c r="E91" s="23" t="n"/>
@@ -6237,22 +6337,22 @@
     <row r="92" ht="42" customHeight="1">
       <c r="A92" s="21" t="inlineStr">
         <is>
-          <t>SA6</t>
+          <t>SA2</t>
         </is>
       </c>
       <c r="B92" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to find users by type.</t>
+          <t>As a Super Admin, I can do everything an Admin can, across all orgs.</t>
         </is>
       </c>
       <c r="C92" s="22" t="inlineStr">
         <is>
-          <t>Users → role filter pills + search.</t>
+          <t>Spot-check user + org actions on more than one org.</t>
         </is>
       </c>
       <c r="D92" s="22" t="inlineStr">
         <is>
-          <t>Filter by role with counts; search by name/email across all orgs.</t>
+          <t>All allowed regardless of org.</t>
         </is>
       </c>
       <c r="E92" s="23" t="n"/>
@@ -6262,22 +6362,22 @@
     <row r="93" ht="42" customHeight="1">
       <c r="A93" s="21" t="inlineStr">
         <is>
-          <t>SA7</t>
+          <t>SA3</t>
         </is>
       </c>
       <c r="B93" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to search events.</t>
+          <t>As a Super Admin, I want to create users incl. Supervisor and Super Admin.</t>
         </is>
       </c>
       <c r="C93" s="22" t="inlineStr">
         <is>
-          <t>Events → search + date range; check supervisor/org per card.</t>
+          <t>Users → Add user → each role.</t>
         </is>
       </c>
       <c r="D93" s="22" t="inlineStr">
         <is>
-          <t>Filters work; each event shows supervisor and organization.</t>
+          <t>Participant/Supervisor/Super Admin options available; account created + invite email.</t>
         </is>
       </c>
       <c r="E93" s="23" t="n"/>
@@ -6287,22 +6387,22 @@
     <row r="94" ht="42" customHeight="1">
       <c r="A94" s="21" t="inlineStr">
         <is>
-          <t>SA8</t>
+          <t>SA4</t>
         </is>
       </c>
       <c r="B94" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want clear event-visibility labels.</t>
+          <t>As a Super Admin, I want to grant/revoke Admin access.</t>
         </is>
       </c>
       <c r="C94" s="22" t="inlineStr">
         <is>
-          <t>New Event → 'Who can see this'.</t>
+          <t>Open a user → grant Admin access → check org(s) → save; then uncheck all → save.</t>
         </is>
       </c>
       <c r="D94" s="22" t="inlineStr">
         <is>
-          <t>'Open to all (community)' and 'Only &lt;org&gt; students' with helper text.</t>
+          <t>Checking orgs makes an Admin; unchecking all reverts to participant.</t>
         </is>
       </c>
       <c r="E94" s="23" t="n"/>
@@ -6312,22 +6412,22 @@
     <row r="95" ht="42" customHeight="1">
       <c r="A95" s="21" t="inlineStr">
         <is>
-          <t>SA9</t>
+          <t>SA5</t>
         </is>
       </c>
       <c r="B95" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want program-wide reports.</t>
+          <t>As a Super Admin, I want to create organizations + join codes.</t>
         </is>
       </c>
       <c r="C95" s="22" t="inlineStr">
         <is>
-          <t>Open Reports / Dashboard.</t>
+          <t>Organizations → Add organization → set details + join code.</t>
         </is>
       </c>
       <c r="D95" s="22" t="inlineStr">
         <is>
-          <t>Totals and charts across the whole program.</t>
+          <t>Org created with its join code.</t>
         </is>
       </c>
       <c r="E95" s="23" t="n"/>
@@ -6337,22 +6437,22 @@
     <row r="96" ht="42" customHeight="1">
       <c r="A96" s="21" t="inlineStr">
         <is>
-          <t>SA10</t>
+          <t>SA6</t>
         </is>
       </c>
       <c r="B96" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to verify email works.</t>
+          <t>As a Super Admin, I want to find users by type.</t>
         </is>
       </c>
       <c r="C96" s="22" t="inlineStr">
         <is>
-          <t>Dashboard → Send test email.</t>
+          <t>Users → role filter pills + search.</t>
         </is>
       </c>
       <c r="D96" s="22" t="inlineStr">
         <is>
-          <t>Result shown (success or the exact failure reason).</t>
+          <t>Filter by role with counts; search by name/email across all orgs.</t>
         </is>
       </c>
       <c r="E96" s="23" t="n"/>
@@ -6362,22 +6462,22 @@
     <row r="97" ht="42" customHeight="1">
       <c r="A97" s="21" t="inlineStr">
         <is>
-          <t>SA11</t>
+          <t>SA7</t>
         </is>
       </c>
       <c r="B97" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to update the recycling cans total.</t>
+          <t>As a Super Admin, I want to search events.</t>
         </is>
       </c>
       <c r="C97" s="22" t="inlineStr">
         <is>
-          <t>Use the cans/bin admin control.</t>
+          <t>Events → search + date range; check supervisor/org per card.</t>
         </is>
       </c>
       <c r="D97" s="22" t="inlineStr">
         <is>
-          <t>Total updates; the ribbon reflects it.</t>
+          <t>Filters work; each event shows supervisor and organization.</t>
         </is>
       </c>
       <c r="E97" s="23" t="n"/>
@@ -6387,60 +6487,72 @@
     <row r="98" ht="42" customHeight="1">
       <c r="A98" s="21" t="inlineStr">
         <is>
-          <t>SA12</t>
+          <t>SA8</t>
         </is>
       </c>
       <c r="B98" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want hours + records for any user.</t>
+          <t>As a Super Admin, I want clear event-visibility labels.</t>
         </is>
       </c>
       <c r="C98" s="22" t="inlineStr">
         <is>
-          <t>Add manual hours / open service record for any participant.</t>
+          <t>New Event → 'Who can see this'.</t>
         </is>
       </c>
       <c r="D98" s="22" t="inlineStr">
         <is>
-          <t>Works for any org.</t>
+          <t>'Open to all (community)' and 'Only &lt;org&gt; students' with helper text.</t>
         </is>
       </c>
       <c r="E98" s="23" t="n"/>
       <c r="F98" s="22" t="n"/>
       <c r="G98" s="23" t="n"/>
     </row>
-    <row r="99" ht="20" customHeight="1">
-      <c r="A99" s="19" t="inlineStr">
-        <is>
-          <t>Cross-cutting</t>
-        </is>
-      </c>
-      <c r="B99" s="20" t="n"/>
-      <c r="C99" s="20" t="n"/>
-      <c r="D99" s="20" t="n"/>
-      <c r="E99" s="20" t="n"/>
-      <c r="F99" s="20" t="n"/>
-      <c r="G99" s="20" t="n"/>
+    <row r="99" ht="42" customHeight="1">
+      <c r="A99" s="21" t="inlineStr">
+        <is>
+          <t>SA9</t>
+        </is>
+      </c>
+      <c r="B99" s="22" t="inlineStr">
+        <is>
+          <t>As a Super Admin, I want program-wide reports.</t>
+        </is>
+      </c>
+      <c r="C99" s="22" t="inlineStr">
+        <is>
+          <t>Open Reports / Dashboard.</t>
+        </is>
+      </c>
+      <c r="D99" s="22" t="inlineStr">
+        <is>
+          <t>Totals and charts across the whole program.</t>
+        </is>
+      </c>
+      <c r="E99" s="23" t="n"/>
+      <c r="F99" s="22" t="n"/>
+      <c r="G99" s="23" t="n"/>
     </row>
     <row r="100" ht="42" customHeight="1">
       <c r="A100" s="21" t="inlineStr">
         <is>
-          <t>X1</t>
+          <t>SA10</t>
         </is>
       </c>
       <c r="B100" s="22" t="inlineStr">
         <is>
-          <t>As a phone user, I want a usable mobile layout.</t>
+          <t>As a Super Admin, I want to verify email works.</t>
         </is>
       </c>
       <c r="C100" s="22" t="inlineStr">
         <is>
-          <t>Open at phone width; use the menu drawer.</t>
+          <t>Dashboard → Send test email.</t>
         </is>
       </c>
       <c r="D100" s="22" t="inlineStr">
         <is>
-          <t>Layout adapts; drawer opens/closes; no horizontal scroll.</t>
+          <t>Result shown (success or the exact failure reason).</t>
         </is>
       </c>
       <c r="E100" s="23" t="n"/>
@@ -6450,39 +6562,127 @@
     <row r="101" ht="42" customHeight="1">
       <c r="A101" s="21" t="inlineStr">
         <is>
-          <t>X2</t>
+          <t>SA11</t>
         </is>
       </c>
       <c r="B101" s="22" t="inlineStr">
         <is>
-          <t>As a visitor, I want the recycling ribbon on the login page.</t>
+          <t>As a Super Admin, I want to update the recycling cans total.</t>
         </is>
       </c>
       <c r="C101" s="22" t="inlineStr">
         <is>
-          <t>Open login signed out.</t>
+          <t>Use the cans/bin admin control.</t>
         </is>
       </c>
       <c r="D101" s="22" t="inlineStr">
         <is>
-          <t>Green ribbon shows on login.</t>
+          <t>Total updates; the ribbon reflects it.</t>
         </is>
       </c>
       <c r="E101" s="23" t="n"/>
       <c r="F101" s="22" t="n"/>
       <c r="G101" s="23" t="n"/>
     </row>
+    <row r="102" ht="42" customHeight="1">
+      <c r="A102" s="21" t="inlineStr">
+        <is>
+          <t>SA12</t>
+        </is>
+      </c>
+      <c r="B102" s="22" t="inlineStr">
+        <is>
+          <t>As a Super Admin, I want hours + records for any user.</t>
+        </is>
+      </c>
+      <c r="C102" s="22" t="inlineStr">
+        <is>
+          <t>Add manual hours / open service record for any participant.</t>
+        </is>
+      </c>
+      <c r="D102" s="22" t="inlineStr">
+        <is>
+          <t>Works for any org.</t>
+        </is>
+      </c>
+      <c r="E102" s="23" t="n"/>
+      <c r="F102" s="22" t="n"/>
+      <c r="G102" s="23" t="n"/>
+    </row>
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="19" t="inlineStr">
+        <is>
+          <t>Cross-cutting</t>
+        </is>
+      </c>
+      <c r="B103" s="20" t="n"/>
+      <c r="C103" s="20" t="n"/>
+      <c r="D103" s="20" t="n"/>
+      <c r="E103" s="20" t="n"/>
+      <c r="F103" s="20" t="n"/>
+      <c r="G103" s="20" t="n"/>
+    </row>
+    <row r="104" ht="42" customHeight="1">
+      <c r="A104" s="21" t="inlineStr">
+        <is>
+          <t>X1</t>
+        </is>
+      </c>
+      <c r="B104" s="22" t="inlineStr">
+        <is>
+          <t>As a phone user, I want a usable mobile layout.</t>
+        </is>
+      </c>
+      <c r="C104" s="22" t="inlineStr">
+        <is>
+          <t>Open at phone width; use the menu drawer.</t>
+        </is>
+      </c>
+      <c r="D104" s="22" t="inlineStr">
+        <is>
+          <t>Layout adapts; drawer opens/closes; no horizontal scroll.</t>
+        </is>
+      </c>
+      <c r="E104" s="23" t="n"/>
+      <c r="F104" s="22" t="n"/>
+      <c r="G104" s="23" t="n"/>
+    </row>
+    <row r="105" ht="42" customHeight="1">
+      <c r="A105" s="21" t="inlineStr">
+        <is>
+          <t>X2</t>
+        </is>
+      </c>
+      <c r="B105" s="22" t="inlineStr">
+        <is>
+          <t>As a visitor, I want the recycling ribbon on the login page.</t>
+        </is>
+      </c>
+      <c r="C105" s="22" t="inlineStr">
+        <is>
+          <t>Open login signed out.</t>
+        </is>
+      </c>
+      <c r="D105" s="22" t="inlineStr">
+        <is>
+          <t>Green ribbon shows on login.</t>
+        </is>
+      </c>
+      <c r="E105" s="23" t="n"/>
+      <c r="F105" s="22" t="n"/>
+      <c r="G105" s="23" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A99:G99"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A55:G55"/>
     <mergeCell ref="A35:G35"/>
-    <mergeCell ref="A86:G86"/>
-    <mergeCell ref="A71:G71"/>
-    <mergeCell ref="A51:G51"/>
+    <mergeCell ref="A90:G90"/>
+    <mergeCell ref="A49:G49"/>
     <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="A103:G103"/>
+    <mergeCell ref="A75:G75"/>
   </mergeCells>
   <conditionalFormatting sqref="E4:E9">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
@@ -6506,7 +6706,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E36:E44">
+  <conditionalFormatting sqref="E36:E48">
     <cfRule type="cellIs" priority="7" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -6517,7 +6717,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E46:E50">
+  <conditionalFormatting sqref="E50:E54">
     <cfRule type="cellIs" priority="10" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -6528,7 +6728,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E52:E70">
+  <conditionalFormatting sqref="E56:E74">
     <cfRule type="cellIs" priority="13" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -6539,7 +6739,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E72:E85">
+  <conditionalFormatting sqref="E76:E89">
     <cfRule type="cellIs" priority="16" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -6550,7 +6750,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E87:E98">
+  <conditionalFormatting sqref="E91:E102">
     <cfRule type="cellIs" priority="19" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -6561,7 +6761,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E100:E101">
+  <conditionalFormatting sqref="E104:E105">
     <cfRule type="cellIs" priority="22" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -6573,7 +6773,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E4:E9 E11:E34 E36:E44 E46:E50 E52:E70 E72:E85 E87:E98 E100:E101" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E4:E9 E11:E34 E36:E48 E50:E54 E56:E74 E76:E89 E91:E102 E104:E105" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pass,Fail,Blocked,Not tested,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6587,7 +6787,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:G105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7663,38 +7863,50 @@
       <c r="F44" s="22" t="n"/>
       <c r="G44" s="23" t="n"/>
     </row>
-    <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="19" t="inlineStr">
-        <is>
-          <t>Parent — viewer (grades 6–12 student)</t>
-        </is>
-      </c>
-      <c r="B45" s="20" t="n"/>
-      <c r="C45" s="20" t="n"/>
-      <c r="D45" s="20" t="n"/>
-      <c r="E45" s="20" t="n"/>
-      <c r="F45" s="20" t="n"/>
-      <c r="G45" s="20" t="n"/>
+    <row r="45" ht="42" customHeight="1">
+      <c r="A45" s="21" t="inlineStr">
+        <is>
+          <t>PE10</t>
+        </is>
+      </c>
+      <c r="B45" s="22" t="inlineStr">
+        <is>
+          <t>As a parent, I want to submit my child's hours after an event (child has no login).</t>
+        </is>
+      </c>
+      <c r="C45" s="22" t="inlineStr">
+        <is>
+          <t>Dashboard → the child's 'Submit hours (past events)' → enter hours → Submit.</t>
+        </is>
+      </c>
+      <c r="D45" s="22" t="inlineStr">
+        <is>
+          <t>Hours go to the supervisor for approval; status shows 'Waiting for review'.</t>
+        </is>
+      </c>
+      <c r="E45" s="23" t="n"/>
+      <c r="F45" s="22" t="n"/>
+      <c r="G45" s="23" t="n"/>
     </row>
     <row r="46" ht="42" customHeight="1">
       <c r="A46" s="21" t="inlineStr">
         <is>
-          <t>PV1</t>
+          <t>PE11</t>
         </is>
       </c>
       <c r="B46" s="22" t="inlineStr">
         <is>
-          <t>As a parent of a 6–12 student, I want to register for view-only access.</t>
+          <t>As a parent, I want to resubmit my child's rejected hours.</t>
         </is>
       </c>
       <c r="C46" s="22" t="inlineStr">
         <is>
-          <t>Create account → parent of a 6–12 student.</t>
+          <t>On a rejected past event, enter corrected hours → Resubmit.</t>
         </is>
       </c>
       <c r="D46" s="22" t="inlineStr">
         <is>
-          <t>Account created; no invite required to register.</t>
+          <t>Returns to 'Waiting for review'.</t>
         </is>
       </c>
       <c r="E46" s="23" t="n"/>
@@ -7704,22 +7916,22 @@
     <row r="47" ht="42" customHeight="1">
       <c r="A47" s="21" t="inlineStr">
         <is>
-          <t>PV2</t>
+          <t>PE12</t>
         </is>
       </c>
       <c r="B47" s="22" t="inlineStr">
         <is>
-          <t>As a viewer parent, my student links automatically by email.</t>
+          <t>As a parent, I want to see each past event's hours status for my child.</t>
         </is>
       </c>
       <c r="C47" s="22" t="inlineStr">
         <is>
-          <t>Have a student enter this exact email as their parent email (before or after you register).</t>
+          <t>Look at the child's past events list.</t>
         </is>
       </c>
       <c r="D47" s="22" t="inlineStr">
         <is>
-          <t>The student appears on your dashboard automatically; empty until then.</t>
+          <t>Each shows Approved / Waiting / Rejected as appropriate.</t>
         </is>
       </c>
       <c r="E47" s="23" t="n"/>
@@ -7729,110 +7941,110 @@
     <row r="48" ht="42" customHeight="1">
       <c r="A48" s="21" t="inlineStr">
         <is>
-          <t>PV3</t>
+          <t>PE13</t>
         </is>
       </c>
       <c r="B48" s="22" t="inlineStr">
         <is>
-          <t>As a viewer parent, I want to see my student's schedule/progress.</t>
+          <t>As a parent, all core participant actions are available to me for my child.</t>
         </is>
       </c>
       <c r="C48" s="22" t="inlineStr">
         <is>
-          <t>Open the dashboard.</t>
+          <t>Confirm: browse, sign up, withdraw, add-to-calendar, submit hours, view progress toward medals.</t>
         </is>
       </c>
       <c r="D48" s="22" t="inlineStr">
         <is>
-          <t>View-only schedule and progress.</t>
+          <t>All participant-style actions work on the child's behalf (the child never logs in).</t>
         </is>
       </c>
       <c r="E48" s="23" t="n"/>
       <c r="F48" s="22" t="n"/>
       <c r="G48" s="23" t="n"/>
     </row>
-    <row r="49" ht="42" customHeight="1">
-      <c r="A49" s="21" t="inlineStr">
-        <is>
-          <t>PV4</t>
-        </is>
-      </c>
-      <c r="B49" s="22" t="inlineStr">
-        <is>
-          <t>As a viewer parent, I do NOT sign the student up.</t>
-        </is>
-      </c>
-      <c r="C49" s="22" t="inlineStr">
-        <is>
-          <t>Look for a sign-up action.</t>
-        </is>
-      </c>
-      <c r="D49" s="22" t="inlineStr">
-        <is>
-          <t>No sign-up on the student's behalf — the student self-serves.</t>
-        </is>
-      </c>
-      <c r="E49" s="23" t="n"/>
-      <c r="F49" s="22" t="n"/>
-      <c r="G49" s="23" t="n"/>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="19" t="inlineStr">
+        <is>
+          <t>Parent — viewer (grades 6–12 student)</t>
+        </is>
+      </c>
+      <c r="B49" s="20" t="n"/>
+      <c r="C49" s="20" t="n"/>
+      <c r="D49" s="20" t="n"/>
+      <c r="E49" s="20" t="n"/>
+      <c r="F49" s="20" t="n"/>
+      <c r="G49" s="20" t="n"/>
     </row>
     <row r="50" ht="42" customHeight="1">
       <c r="A50" s="21" t="inlineStr">
         <is>
-          <t>PV5</t>
+          <t>PV1</t>
         </is>
       </c>
       <c r="B50" s="22" t="inlineStr">
         <is>
-          <t>As a viewer parent, I want to invite a co-guardian.</t>
+          <t>As a parent of a 6–12 student, I want to register for view-only access.</t>
         </is>
       </c>
       <c r="C50" s="22" t="inlineStr">
         <is>
-          <t>Invite a co-guardian by email.</t>
+          <t>Create account → parent of a 6–12 student.</t>
         </is>
       </c>
       <c r="D50" s="22" t="inlineStr">
         <is>
-          <t>Invite email sent; shared access on registration.</t>
+          <t>Account created; no invite required to register.</t>
         </is>
       </c>
       <c r="E50" s="23" t="n"/>
       <c r="F50" s="22" t="n"/>
       <c r="G50" s="23" t="n"/>
     </row>
-    <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="19" t="inlineStr">
-        <is>
-          <t>Supervisor (created by an Admin)</t>
-        </is>
-      </c>
-      <c r="B51" s="20" t="n"/>
-      <c r="C51" s="20" t="n"/>
-      <c r="D51" s="20" t="n"/>
-      <c r="E51" s="20" t="n"/>
-      <c r="F51" s="20" t="n"/>
-      <c r="G51" s="20" t="n"/>
+    <row r="51" ht="42" customHeight="1">
+      <c r="A51" s="21" t="inlineStr">
+        <is>
+          <t>PV2</t>
+        </is>
+      </c>
+      <c r="B51" s="22" t="inlineStr">
+        <is>
+          <t>As a viewer parent, my student links automatically by email.</t>
+        </is>
+      </c>
+      <c r="C51" s="22" t="inlineStr">
+        <is>
+          <t>Have a student enter this exact email as their parent email (before or after you register).</t>
+        </is>
+      </c>
+      <c r="D51" s="22" t="inlineStr">
+        <is>
+          <t>The student appears on your dashboard automatically; empty until then.</t>
+        </is>
+      </c>
+      <c r="E51" s="23" t="n"/>
+      <c r="F51" s="22" t="n"/>
+      <c r="G51" s="23" t="n"/>
     </row>
     <row r="52" ht="42" customHeight="1">
       <c r="A52" s="21" t="inlineStr">
         <is>
-          <t>SV1</t>
+          <t>PV3</t>
         </is>
       </c>
       <c r="B52" s="22" t="inlineStr">
         <is>
-          <t>As the program, a supervisor cannot self-register.</t>
+          <t>As a viewer parent, I want to see my student's schedule/progress.</t>
         </is>
       </c>
       <c r="C52" s="22" t="inlineStr">
         <is>
-          <t>Review the sign-up options.</t>
+          <t>Open the dashboard.</t>
         </is>
       </c>
       <c r="D52" s="22" t="inlineStr">
         <is>
-          <t>No supervisor option exists on registration.</t>
+          <t>View-only schedule and progress.</t>
         </is>
       </c>
       <c r="E52" s="23" t="n"/>
@@ -7842,22 +8054,22 @@
     <row r="53" ht="42" customHeight="1">
       <c r="A53" s="21" t="inlineStr">
         <is>
-          <t>SV2</t>
+          <t>PV4</t>
         </is>
       </c>
       <c r="B53" s="22" t="inlineStr">
         <is>
-          <t>As a new supervisor, I get an invite to set my password.</t>
+          <t>As a viewer parent, I do NOT sign the student up.</t>
         </is>
       </c>
       <c r="C53" s="22" t="inlineStr">
         <is>
-          <t>Have an Admin create your account; open the invite email; set password; sign in.</t>
+          <t>Look for a sign-up action.</t>
         </is>
       </c>
       <c r="D53" s="22" t="inlineStr">
         <is>
-          <t>Invite email arrives with a working set-password link; you can sign in.</t>
+          <t>No sign-up on the student's behalf — the student self-serves.</t>
         </is>
       </c>
       <c r="E53" s="23" t="n"/>
@@ -7867,72 +8079,60 @@
     <row r="54" ht="42" customHeight="1">
       <c r="A54" s="21" t="inlineStr">
         <is>
-          <t>SV3</t>
+          <t>PV5</t>
         </is>
       </c>
       <c r="B54" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want the correct 7 left-menu tabs.</t>
+          <t>As a viewer parent, I want to invite a co-guardian.</t>
         </is>
       </c>
       <c r="C54" s="22" t="inlineStr">
         <is>
-          <t>Look at the left menu.</t>
+          <t>Invite a co-guardian by email.</t>
         </is>
       </c>
       <c r="D54" s="22" t="inlineStr">
         <is>
-          <t>Dashboard, Pending Reviews, Reviewed History, My Events, All Opportunities, My Hours, Help.</t>
+          <t>Invite email sent; shared access on registration.</t>
         </is>
       </c>
       <c r="E54" s="23" t="n"/>
       <c r="F54" s="22" t="n"/>
       <c r="G54" s="23" t="n"/>
     </row>
-    <row r="55" ht="42" customHeight="1">
-      <c r="A55" s="21" t="inlineStr">
-        <is>
-          <t>SV4</t>
-        </is>
-      </c>
-      <c r="B55" s="22" t="inlineStr">
-        <is>
-          <t>As a supervisor, I want a dashboard.</t>
-        </is>
-      </c>
-      <c r="C55" s="22" t="inlineStr">
-        <is>
-          <t>Open the dashboard.</t>
-        </is>
-      </c>
-      <c r="D55" s="22" t="inlineStr">
-        <is>
-          <t>Review queue, approved/rejected counts, registrations, hours, upcoming events + Roster links.</t>
-        </is>
-      </c>
-      <c r="E55" s="23" t="n"/>
-      <c r="F55" s="22" t="n"/>
-      <c r="G55" s="23" t="n"/>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="19" t="inlineStr">
+        <is>
+          <t>Supervisor (created by an Admin)</t>
+        </is>
+      </c>
+      <c r="B55" s="20" t="n"/>
+      <c r="C55" s="20" t="n"/>
+      <c r="D55" s="20" t="n"/>
+      <c r="E55" s="20" t="n"/>
+      <c r="F55" s="20" t="n"/>
+      <c r="G55" s="20" t="n"/>
     </row>
     <row r="56" ht="42" customHeight="1">
       <c r="A56" s="21" t="inlineStr">
         <is>
-          <t>SV5</t>
+          <t>SV1</t>
         </is>
       </c>
       <c r="B56" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to approve hours.</t>
+          <t>As the program, a supervisor cannot self-register.</t>
         </is>
       </c>
       <c r="C56" s="22" t="inlineStr">
         <is>
-          <t>Pending Reviews → open → Approve.</t>
+          <t>Review the sign-up options.</t>
         </is>
       </c>
       <c r="D56" s="22" t="inlineStr">
         <is>
-          <t>Approved; moves to Reviewed History; participant total updates; email sent.</t>
+          <t>No supervisor option exists on registration.</t>
         </is>
       </c>
       <c r="E56" s="23" t="n"/>
@@ -7942,22 +8142,22 @@
     <row r="57" ht="42" customHeight="1">
       <c r="A57" s="21" t="inlineStr">
         <is>
-          <t>SV6</t>
+          <t>SV2</t>
         </is>
       </c>
       <c r="B57" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to reject hours with a reason.</t>
+          <t>As a new supervisor, I get an invite to set my password.</t>
         </is>
       </c>
       <c r="C57" s="22" t="inlineStr">
         <is>
-          <t>Reject without a reason, then with one.</t>
+          <t>Have an Admin create your account; open the invite email; set password; sign in.</t>
         </is>
       </c>
       <c r="D57" s="22" t="inlineStr">
         <is>
-          <t>Blocked until a reason is given; then rejected and the participant notified.</t>
+          <t>Invite email arrives with a working set-password link; you can sign in.</t>
         </is>
       </c>
       <c r="E57" s="23" t="n"/>
@@ -7967,22 +8167,22 @@
     <row r="58" ht="42" customHeight="1">
       <c r="A58" s="21" t="inlineStr">
         <is>
-          <t>SV7</t>
+          <t>SV3</t>
         </is>
       </c>
       <c r="B58" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to review external submissions.</t>
+          <t>As a supervisor, I want the correct 7 left-menu tabs.</t>
         </is>
       </c>
       <c r="C58" s="22" t="inlineStr">
         <is>
-          <t>Pending Reviews → external tab → approve/reject.</t>
+          <t>Look at the left menu.</t>
         </is>
       </c>
       <c r="D58" s="22" t="inlineStr">
         <is>
-          <t>External items reviewable, including any proof.</t>
+          <t>Dashboard, Pending Reviews, Reviewed History, My Events, All Opportunities, My Hours, Help.</t>
         </is>
       </c>
       <c r="E58" s="23" t="n"/>
@@ -7992,22 +8192,22 @@
     <row r="59" ht="42" customHeight="1">
       <c r="A59" s="21" t="inlineStr">
         <is>
-          <t>SV8</t>
+          <t>SV4</t>
         </is>
       </c>
       <c r="B59" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to create an event.</t>
+          <t>As a supervisor, I want a dashboard.</t>
         </is>
       </c>
       <c r="C59" s="22" t="inlineStr">
         <is>
-          <t>New Event → title, description, slot, address, date, times, capacity, grade limits → save.</t>
+          <t>Open the dashboard.</t>
         </is>
       </c>
       <c r="D59" s="22" t="inlineStr">
         <is>
-          <t>Credit auto-calculated from times; event created in My Events.</t>
+          <t>Review queue, approved/rejected counts, registrations, hours, upcoming events + Roster links.</t>
         </is>
       </c>
       <c r="E59" s="23" t="n"/>
@@ -8017,22 +8217,22 @@
     <row r="60" ht="42" customHeight="1">
       <c r="A60" s="21" t="inlineStr">
         <is>
-          <t>SV9</t>
+          <t>SV5</t>
         </is>
       </c>
       <c r="B60" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to edit an event.</t>
+          <t>As a supervisor, I want to approve hours.</t>
         </is>
       </c>
       <c r="C60" s="22" t="inlineStr">
         <is>
-          <t>My Events → edit → save.</t>
+          <t>Pending Reviews → open → Approve.</t>
         </is>
       </c>
       <c r="D60" s="22" t="inlineStr">
         <is>
-          <t>Changes persist and show to participants.</t>
+          <t>Approved; moves to Reviewed History; participant total updates; email sent.</t>
         </is>
       </c>
       <c r="E60" s="23" t="n"/>
@@ -8042,22 +8242,22 @@
     <row r="61" ht="42" customHeight="1">
       <c r="A61" s="21" t="inlineStr">
         <is>
-          <t>SV10</t>
+          <t>SV6</t>
         </is>
       </c>
       <c r="B61" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to delete an event with no approved hours.</t>
+          <t>As a supervisor, I want to reject hours with a reason.</t>
         </is>
       </c>
       <c r="C61" s="22" t="inlineStr">
         <is>
-          <t>Delete such an event → confirm.</t>
+          <t>Reject without a reason, then with one.</t>
         </is>
       </c>
       <c r="D61" s="22" t="inlineStr">
         <is>
-          <t>Event deleted.</t>
+          <t>Blocked until a reason is given; then rejected and the participant notified.</t>
         </is>
       </c>
       <c r="E61" s="23" t="n"/>
@@ -8067,22 +8267,22 @@
     <row r="62" ht="42" customHeight="1">
       <c r="A62" s="21" t="inlineStr">
         <is>
-          <t>SV11</t>
+          <t>SV7</t>
         </is>
       </c>
       <c r="B62" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, deleting an event with approved hours is blocked.</t>
+          <t>As a supervisor, I want to review external submissions.</t>
         </is>
       </c>
       <c r="C62" s="22" t="inlineStr">
         <is>
-          <t>Try to delete an event that has approved hours.</t>
+          <t>Pending Reviews → external tab → approve/reject.</t>
         </is>
       </c>
       <c r="D62" s="22" t="inlineStr">
         <is>
-          <t>Blocked with a message that approved hours must be preserved.</t>
+          <t>External items reviewable, including any proof.</t>
         </is>
       </c>
       <c r="E62" s="23" t="n"/>
@@ -8092,22 +8292,22 @@
     <row r="63" ht="42" customHeight="1">
       <c r="A63" s="21" t="inlineStr">
         <is>
-          <t>SV12</t>
+          <t>SV8</t>
         </is>
       </c>
       <c r="B63" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to see who signed up.</t>
+          <t>As a supervisor, I want to create an event.</t>
         </is>
       </c>
       <c r="C63" s="22" t="inlineStr">
         <is>
-          <t>Open the event Roster.</t>
+          <t>New Event → title, description, slot, address, date, times, capacity, grade limits → save.</t>
         </is>
       </c>
       <c r="D63" s="22" t="inlineStr">
         <is>
-          <t>Registrants listed with grade and status.</t>
+          <t>Credit auto-calculated from times; event created in My Events.</t>
         </is>
       </c>
       <c r="E63" s="23" t="n"/>
@@ -8117,22 +8317,22 @@
     <row r="64" ht="42" customHeight="1">
       <c r="A64" s="21" t="inlineStr">
         <is>
-          <t>SV13</t>
+          <t>SV9</t>
         </is>
       </c>
       <c r="B64" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to check people in / mark no-show.</t>
+          <t>As a supervisor, I want to edit an event.</t>
         </is>
       </c>
       <c r="C64" s="22" t="inlineStr">
         <is>
-          <t>On the roster, Check in and Mark no-show.</t>
+          <t>My Events → edit → save.</t>
         </is>
       </c>
       <c r="D64" s="22" t="inlineStr">
         <is>
-          <t>Status updates and persists.</t>
+          <t>Changes persist and show to participants.</t>
         </is>
       </c>
       <c r="E64" s="23" t="n"/>
@@ -8142,22 +8342,22 @@
     <row r="65" ht="42" customHeight="1">
       <c r="A65" s="21" t="inlineStr">
         <is>
-          <t>SV14</t>
+          <t>SV10</t>
         </is>
       </c>
       <c r="B65" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to message everyone signed up.</t>
+          <t>As a supervisor, I want to delete an event with no approved hours.</t>
         </is>
       </c>
       <c r="C65" s="22" t="inlineStr">
         <is>
-          <t>Roster → Message attendees → subject+message → send (include guardians on).</t>
+          <t>Delete such an event → confirm.</t>
         </is>
       </c>
       <c r="D65" s="22" t="inlineStr">
         <is>
-          <t>Each registrant (and guardians) emailed individually; recipient count shown.</t>
+          <t>Event deleted.</t>
         </is>
       </c>
       <c r="E65" s="23" t="n"/>
@@ -8167,22 +8367,22 @@
     <row r="66" ht="42" customHeight="1">
       <c r="A66" s="21" t="inlineStr">
         <is>
-          <t>SV15</t>
+          <t>SV11</t>
         </is>
       </c>
       <c r="B66" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want a history of what I reviewed.</t>
+          <t>As a supervisor, deleting an event with approved hours is blocked.</t>
         </is>
       </c>
       <c r="C66" s="22" t="inlineStr">
         <is>
-          <t>Open Reviewed History.</t>
+          <t>Try to delete an event that has approved hours.</t>
         </is>
       </c>
       <c r="D66" s="22" t="inlineStr">
         <is>
-          <t>Every approved/rejected item with dates and volunteers.</t>
+          <t>Blocked with a message that approved hours must be preserved.</t>
         </is>
       </c>
       <c r="E66" s="23" t="n"/>
@@ -8192,22 +8392,22 @@
     <row r="67" ht="42" customHeight="1">
       <c r="A67" s="21" t="inlineStr">
         <is>
-          <t>SV16</t>
+          <t>SV12</t>
         </is>
       </c>
       <c r="B67" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to browse all opportunities view-only.</t>
+          <t>As a supervisor, I want to see who signed up.</t>
         </is>
       </c>
       <c r="C67" s="22" t="inlineStr">
         <is>
-          <t>All Opportunities → search / upcoming-past.</t>
+          <t>Open the event Roster.</t>
         </is>
       </c>
       <c r="D67" s="22" t="inlineStr">
         <is>
-          <t>Every event listed read-only; can't edit others' events.</t>
+          <t>Registrants listed with grade and status.</t>
         </is>
       </c>
       <c r="E67" s="23" t="n"/>
@@ -8217,22 +8417,22 @@
     <row r="68" ht="42" customHeight="1">
       <c r="A68" s="21" t="inlineStr">
         <is>
-          <t>SV17</t>
+          <t>SV13</t>
         </is>
       </c>
       <c r="B68" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to log my own adult hours.</t>
+          <t>As a supervisor, I want to check people in / mark no-show.</t>
         </is>
       </c>
       <c r="C68" s="22" t="inlineStr">
         <is>
-          <t>My Hours → log an activity, date, hours → save.</t>
+          <t>On the roster, Check in and Mark no-show.</t>
         </is>
       </c>
       <c r="D68" s="22" t="inlineStr">
         <is>
-          <t>Recorded instantly with a running total; clearly NOT part of the student competition.</t>
+          <t>Status updates and persists.</t>
         </is>
       </c>
       <c r="E68" s="23" t="n"/>
@@ -8242,22 +8442,22 @@
     <row r="69" ht="42" customHeight="1">
       <c r="A69" s="21" t="inlineStr">
         <is>
-          <t>SV18</t>
+          <t>SV14</t>
         </is>
       </c>
       <c r="B69" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to delete an adult-hours entry.</t>
+          <t>As a supervisor, I want to message everyone signed up.</t>
         </is>
       </c>
       <c r="C69" s="22" t="inlineStr">
         <is>
-          <t>My Hours → delete an entry → confirm.</t>
+          <t>Roster → Message attendees → subject+message → send (include guardians on).</t>
         </is>
       </c>
       <c r="D69" s="22" t="inlineStr">
         <is>
-          <t>Removed; total updates.</t>
+          <t>Each registrant (and guardians) emailed individually; recipient count shown.</t>
         </is>
       </c>
       <c r="E69" s="23" t="n"/>
@@ -8267,60 +8467,72 @@
     <row r="70" ht="42" customHeight="1">
       <c r="A70" s="21" t="inlineStr">
         <is>
-          <t>SV19</t>
+          <t>SV15</t>
         </is>
       </c>
       <c r="B70" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I must NOT access user or org management.</t>
+          <t>As a supervisor, I want a history of what I reviewed.</t>
         </is>
       </c>
       <c r="C70" s="22" t="inlineStr">
         <is>
-          <t>Look for Users / Organizations in the menu.</t>
+          <t>Open Reviewed History.</t>
         </is>
       </c>
       <c r="D70" s="22" t="inlineStr">
         <is>
-          <t>Those tabs are absent; direct URLs are blocked.</t>
+          <t>Every approved/rejected item with dates and volunteers.</t>
         </is>
       </c>
       <c r="E70" s="23" t="n"/>
       <c r="F70" s="22" t="n"/>
       <c r="G70" s="23" t="n"/>
     </row>
-    <row r="71" ht="20" customHeight="1">
-      <c r="A71" s="19" t="inlineStr">
-        <is>
-          <t>Admin (org-scoped)</t>
-        </is>
-      </c>
-      <c r="B71" s="20" t="n"/>
-      <c r="C71" s="20" t="n"/>
-      <c r="D71" s="20" t="n"/>
-      <c r="E71" s="20" t="n"/>
-      <c r="F71" s="20" t="n"/>
-      <c r="G71" s="20" t="n"/>
+    <row r="71" ht="42" customHeight="1">
+      <c r="A71" s="21" t="inlineStr">
+        <is>
+          <t>SV16</t>
+        </is>
+      </c>
+      <c r="B71" s="22" t="inlineStr">
+        <is>
+          <t>As a supervisor, I want to browse all opportunities view-only.</t>
+        </is>
+      </c>
+      <c r="C71" s="22" t="inlineStr">
+        <is>
+          <t>All Opportunities → search / upcoming-past.</t>
+        </is>
+      </c>
+      <c r="D71" s="22" t="inlineStr">
+        <is>
+          <t>Every event listed read-only; can't edit others' events.</t>
+        </is>
+      </c>
+      <c r="E71" s="23" t="n"/>
+      <c r="F71" s="22" t="n"/>
+      <c r="G71" s="23" t="n"/>
     </row>
     <row r="72" ht="42" customHeight="1">
       <c r="A72" s="21" t="inlineStr">
         <is>
-          <t>AD1</t>
+          <t>SV17</t>
         </is>
       </c>
       <c r="B72" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I want the correct menu tabs.</t>
+          <t>As a supervisor, I want to log my own adult hours.</t>
         </is>
       </c>
       <c r="C72" s="22" t="inlineStr">
         <is>
-          <t>Look at the left menu.</t>
+          <t>My Hours → log an activity, date, hours → save.</t>
         </is>
       </c>
       <c r="D72" s="22" t="inlineStr">
         <is>
-          <t>Dashboard, Pending Reviews, Reviewed History, My Events, All Opportunities, Users, Organizations, My Hours, Help.</t>
+          <t>Recorded instantly with a running total; clearly NOT part of the student competition.</t>
         </is>
       </c>
       <c r="E72" s="23" t="n"/>
@@ -8330,22 +8542,22 @@
     <row r="73" ht="42" customHeight="1">
       <c r="A73" s="21" t="inlineStr">
         <is>
-          <t>AD2</t>
+          <t>SV18</t>
         </is>
       </c>
       <c r="B73" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I can do everything a supervisor can.</t>
+          <t>As a supervisor, I want to delete an adult-hours entry.</t>
         </is>
       </c>
       <c r="C73" s="22" t="inlineStr">
         <is>
-          <t>Spot-check: approve an item and create an event.</t>
+          <t>My Hours → delete an entry → confirm.</t>
         </is>
       </c>
       <c r="D73" s="22" t="inlineStr">
         <is>
-          <t>Both work.</t>
+          <t>Removed; total updates.</t>
         </is>
       </c>
       <c r="E73" s="23" t="n"/>
@@ -8355,72 +8567,60 @@
     <row r="74" ht="42" customHeight="1">
       <c r="A74" s="21" t="inlineStr">
         <is>
-          <t>AD3</t>
+          <t>SV19</t>
         </is>
       </c>
       <c r="B74" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I only see my org's non-admin users.</t>
+          <t>As a supervisor, I must NOT access user or org management.</t>
         </is>
       </c>
       <c r="C74" s="22" t="inlineStr">
         <is>
-          <t>Open Users.</t>
+          <t>Look for Users / Organizations in the menu.</t>
         </is>
       </c>
       <c r="D74" s="22" t="inlineStr">
         <is>
-          <t>Only participants/parents/supervisors in your org; no admins/super admins; no other orgs.</t>
+          <t>Those tabs are absent; direct URLs are blocked.</t>
         </is>
       </c>
       <c r="E74" s="23" t="n"/>
       <c r="F74" s="22" t="n"/>
       <c r="G74" s="23" t="n"/>
     </row>
-    <row r="75" ht="42" customHeight="1">
-      <c r="A75" s="21" t="inlineStr">
-        <is>
-          <t>AD4</t>
-        </is>
-      </c>
-      <c r="B75" s="22" t="inlineStr">
-        <is>
-          <t>As an Admin, I want to add a supervisor.</t>
-        </is>
-      </c>
-      <c r="C75" s="22" t="inlineStr">
-        <is>
-          <t>Users → Add user → Supervisor → save.</t>
-        </is>
-      </c>
-      <c r="D75" s="22" t="inlineStr">
-        <is>
-          <t>Supervisor created, stamped to your org; invite email sent.</t>
-        </is>
-      </c>
-      <c r="E75" s="23" t="n"/>
-      <c r="F75" s="22" t="n"/>
-      <c r="G75" s="23" t="n"/>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="19" t="inlineStr">
+        <is>
+          <t>Admin (org-scoped)</t>
+        </is>
+      </c>
+      <c r="B75" s="20" t="n"/>
+      <c r="C75" s="20" t="n"/>
+      <c r="D75" s="20" t="n"/>
+      <c r="E75" s="20" t="n"/>
+      <c r="F75" s="20" t="n"/>
+      <c r="G75" s="20" t="n"/>
     </row>
     <row r="76" ht="42" customHeight="1">
       <c r="A76" s="21" t="inlineStr">
         <is>
-          <t>AD5</t>
+          <t>AD1</t>
         </is>
       </c>
       <c r="B76" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I want to create a participant as a fallback.</t>
+          <t>As an Admin, I want the correct menu tabs.</t>
         </is>
       </c>
       <c r="C76" s="22" t="inlineStr">
         <is>
-          <t>Users → Add user → Participant → save.</t>
+          <t>Look at the left menu.</t>
         </is>
       </c>
       <c r="D76" s="22" t="inlineStr">
         <is>
-          <t>Participant created with a set-password invite (no silent password).</t>
+          <t>Dashboard, Pending Reviews, Reviewed History, My Events, All Opportunities, Users, Organizations, My Hours, Help.</t>
         </is>
       </c>
       <c r="E76" s="23" t="n"/>
@@ -8430,22 +8630,22 @@
     <row r="77" ht="42" customHeight="1">
       <c r="A77" s="21" t="inlineStr">
         <is>
-          <t>AD6</t>
+          <t>AD2</t>
         </is>
       </c>
       <c r="B77" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I want to grant participant hours.</t>
+          <t>As an Admin, I can do everything a supervisor can.</t>
         </is>
       </c>
       <c r="C77" s="22" t="inlineStr">
         <is>
-          <t>Open a participant in your org → Add hours.</t>
+          <t>Spot-check: approve an item and create an event.</t>
         </is>
       </c>
       <c r="D77" s="22" t="inlineStr">
         <is>
-          <t>Hours auto-approved; count toward their total/medals.</t>
+          <t>Both work.</t>
         </is>
       </c>
       <c r="E77" s="23" t="n"/>
@@ -8455,22 +8655,22 @@
     <row r="78" ht="42" customHeight="1">
       <c r="A78" s="21" t="inlineStr">
         <is>
-          <t>AD7</t>
+          <t>AD3</t>
         </is>
       </c>
       <c r="B78" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I want a participant's service record.</t>
+          <t>As an Admin, I only see my org's non-admin users.</t>
         </is>
       </c>
       <c r="C78" s="22" t="inlineStr">
         <is>
-          <t>Users → Service record for a participant in your org.</t>
+          <t>Open Users.</t>
         </is>
       </c>
       <c r="D78" s="22" t="inlineStr">
         <is>
-          <t>Record opens.</t>
+          <t>Only participants/parents/supervisors in your org; no admins/super admins; no other orgs.</t>
         </is>
       </c>
       <c r="E78" s="23" t="n"/>
@@ -8480,22 +8680,22 @@
     <row r="79" ht="42" customHeight="1">
       <c r="A79" s="21" t="inlineStr">
         <is>
-          <t>AD8</t>
+          <t>AD4</t>
         </is>
       </c>
       <c r="B79" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I want to edit/delete my org's users.</t>
+          <t>As an Admin, I want to add a supervisor.</t>
         </is>
       </c>
       <c r="C79" s="22" t="inlineStr">
         <is>
-          <t>Edit a name/phone; delete a test user.</t>
+          <t>Users → Add user → Supervisor → save.</t>
         </is>
       </c>
       <c r="D79" s="22" t="inlineStr">
         <is>
-          <t>Changes apply within your org.</t>
+          <t>Supervisor created, stamped to your org; invite email sent.</t>
         </is>
       </c>
       <c r="E79" s="23" t="n"/>
@@ -8505,22 +8705,22 @@
     <row r="80" ht="42" customHeight="1">
       <c r="A80" s="21" t="inlineStr">
         <is>
-          <t>AD9</t>
+          <t>AD5</t>
         </is>
       </c>
       <c r="B80" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I must NOT act on users outside my org.</t>
+          <t>As an Admin, I want to create a participant as a fallback.</t>
         </is>
       </c>
       <c r="C80" s="22" t="inlineStr">
         <is>
-          <t>Attempt to reach another org's user (e.g. direct URL).</t>
+          <t>Users → Add user → Participant → save.</t>
         </is>
       </c>
       <c r="D80" s="22" t="inlineStr">
         <is>
-          <t>Blocked / not visible.</t>
+          <t>Participant created with a set-password invite (no silent password).</t>
         </is>
       </c>
       <c r="E80" s="23" t="n"/>
@@ -8530,22 +8730,22 @@
     <row r="81" ht="42" customHeight="1">
       <c r="A81" s="21" t="inlineStr">
         <is>
-          <t>AD10</t>
+          <t>AD6</t>
         </is>
       </c>
       <c r="B81" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I cannot grant Admin access or manage admins.</t>
+          <t>As an Admin, I want to grant participant hours.</t>
         </is>
       </c>
       <c r="C81" s="22" t="inlineStr">
         <is>
-          <t>Look for the 'grant Admin access' action.</t>
+          <t>Open a participant in your org → Add hours.</t>
         </is>
       </c>
       <c r="D81" s="22" t="inlineStr">
         <is>
-          <t>No such button; attempts are blocked server-side.</t>
+          <t>Hours auto-approved; count toward their total/medals.</t>
         </is>
       </c>
       <c r="E81" s="23" t="n"/>
@@ -8555,22 +8755,22 @@
     <row r="82" ht="42" customHeight="1">
       <c r="A82" s="21" t="inlineStr">
         <is>
-          <t>AD11</t>
+          <t>AD7</t>
         </is>
       </c>
       <c r="B82" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I see and edit only my own organization.</t>
+          <t>As an Admin, I want a participant's service record.</t>
         </is>
       </c>
       <c r="C82" s="22" t="inlineStr">
         <is>
-          <t>Open Organizations.</t>
+          <t>Users → Service record for a participant in your org.</t>
         </is>
       </c>
       <c r="D82" s="22" t="inlineStr">
         <is>
-          <t>Only your org shows; you can edit its settings.</t>
+          <t>Record opens.</t>
         </is>
       </c>
       <c r="E82" s="23" t="n"/>
@@ -8580,22 +8780,22 @@
     <row r="83" ht="42" customHeight="1">
       <c r="A83" s="21" t="inlineStr">
         <is>
-          <t>AD12</t>
+          <t>AD8</t>
         </is>
       </c>
       <c r="B83" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I want to generate/rotate my org's join code.</t>
+          <t>As an Admin, I want to edit/delete my org's users.</t>
         </is>
       </c>
       <c r="C83" s="22" t="inlineStr">
         <is>
-          <t>Organizations → set/generate a join code → save.</t>
+          <t>Edit a name/phone; delete a test user.</t>
         </is>
       </c>
       <c r="D83" s="22" t="inlineStr">
         <is>
-          <t>Join code saved; usable at sign-up.</t>
+          <t>Changes apply within your org.</t>
         </is>
       </c>
       <c r="E83" s="23" t="n"/>
@@ -8605,22 +8805,22 @@
     <row r="84" ht="42" customHeight="1">
       <c r="A84" s="21" t="inlineStr">
         <is>
-          <t>AD13</t>
+          <t>AD9</t>
         </is>
       </c>
       <c r="B84" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I cannot create organizations.</t>
+          <t>As an Admin, I must NOT act on users outside my org.</t>
         </is>
       </c>
       <c r="C84" s="22" t="inlineStr">
         <is>
-          <t>Look for 'Add organization'.</t>
+          <t>Attempt to reach another org's user (e.g. direct URL).</t>
         </is>
       </c>
       <c r="D84" s="22" t="inlineStr">
         <is>
-          <t>No Add button; creation blocked.</t>
+          <t>Blocked / not visible.</t>
         </is>
       </c>
       <c r="E84" s="23" t="n"/>
@@ -8630,60 +8830,72 @@
     <row r="85" ht="42" customHeight="1">
       <c r="A85" s="21" t="inlineStr">
         <is>
-          <t>AD14</t>
+          <t>AD10</t>
         </is>
       </c>
       <c r="B85" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I cannot change the recycling cans total.</t>
+          <t>As an Admin, I cannot grant Admin access or manage admins.</t>
         </is>
       </c>
       <c r="C85" s="22" t="inlineStr">
         <is>
-          <t>Look for the cans/bin admin control.</t>
+          <t>Look for the 'grant Admin access' action.</t>
         </is>
       </c>
       <c r="D85" s="22" t="inlineStr">
         <is>
-          <t>Not available (Super Admin only).</t>
+          <t>No such button; attempts are blocked server-side.</t>
         </is>
       </c>
       <c r="E85" s="23" t="n"/>
       <c r="F85" s="22" t="n"/>
       <c r="G85" s="23" t="n"/>
     </row>
-    <row r="86" ht="20" customHeight="1">
-      <c r="A86" s="19" t="inlineStr">
-        <is>
-          <t>Super Admin (global)</t>
-        </is>
-      </c>
-      <c r="B86" s="20" t="n"/>
-      <c r="C86" s="20" t="n"/>
-      <c r="D86" s="20" t="n"/>
-      <c r="E86" s="20" t="n"/>
-      <c r="F86" s="20" t="n"/>
-      <c r="G86" s="20" t="n"/>
+    <row r="86" ht="42" customHeight="1">
+      <c r="A86" s="21" t="inlineStr">
+        <is>
+          <t>AD11</t>
+        </is>
+      </c>
+      <c r="B86" s="22" t="inlineStr">
+        <is>
+          <t>As an Admin, I see and edit only my own organization.</t>
+        </is>
+      </c>
+      <c r="C86" s="22" t="inlineStr">
+        <is>
+          <t>Open Organizations.</t>
+        </is>
+      </c>
+      <c r="D86" s="22" t="inlineStr">
+        <is>
+          <t>Only your org shows; you can edit its settings.</t>
+        </is>
+      </c>
+      <c r="E86" s="23" t="n"/>
+      <c r="F86" s="22" t="n"/>
+      <c r="G86" s="23" t="n"/>
     </row>
     <row r="87" ht="42" customHeight="1">
       <c r="A87" s="21" t="inlineStr">
         <is>
-          <t>SA1</t>
+          <t>AD12</t>
         </is>
       </c>
       <c r="B87" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want the correct menu tabs.</t>
+          <t>As an Admin, I want to generate/rotate my org's join code.</t>
         </is>
       </c>
       <c r="C87" s="22" t="inlineStr">
         <is>
-          <t>Look at the left menu.</t>
+          <t>Organizations → set/generate a join code → save.</t>
         </is>
       </c>
       <c r="D87" s="22" t="inlineStr">
         <is>
-          <t>Dashboard, Reports, Users, Events, Organizations (Help in footer).</t>
+          <t>Join code saved; usable at sign-up.</t>
         </is>
       </c>
       <c r="E87" s="23" t="n"/>
@@ -8693,22 +8905,22 @@
     <row r="88" ht="42" customHeight="1">
       <c r="A88" s="21" t="inlineStr">
         <is>
-          <t>SA2</t>
+          <t>AD13</t>
         </is>
       </c>
       <c r="B88" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I can do everything an Admin can, across all orgs.</t>
+          <t>As an Admin, I cannot create organizations.</t>
         </is>
       </c>
       <c r="C88" s="22" t="inlineStr">
         <is>
-          <t>Spot-check user + org actions on more than one org.</t>
+          <t>Look for 'Add organization'.</t>
         </is>
       </c>
       <c r="D88" s="22" t="inlineStr">
         <is>
-          <t>All allowed regardless of org.</t>
+          <t>No Add button; creation blocked.</t>
         </is>
       </c>
       <c r="E88" s="23" t="n"/>
@@ -8718,72 +8930,60 @@
     <row r="89" ht="42" customHeight="1">
       <c r="A89" s="21" t="inlineStr">
         <is>
-          <t>SA3</t>
+          <t>AD14</t>
         </is>
       </c>
       <c r="B89" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to create users incl. Supervisor and Super Admin.</t>
+          <t>As an Admin, I cannot change the recycling cans total.</t>
         </is>
       </c>
       <c r="C89" s="22" t="inlineStr">
         <is>
-          <t>Users → Add user → each role.</t>
+          <t>Look for the cans/bin admin control.</t>
         </is>
       </c>
       <c r="D89" s="22" t="inlineStr">
         <is>
-          <t>Participant/Supervisor/Super Admin options available; account created + invite email.</t>
+          <t>Not available (Super Admin only).</t>
         </is>
       </c>
       <c r="E89" s="23" t="n"/>
       <c r="F89" s="22" t="n"/>
       <c r="G89" s="23" t="n"/>
     </row>
-    <row r="90" ht="42" customHeight="1">
-      <c r="A90" s="21" t="inlineStr">
-        <is>
-          <t>SA4</t>
-        </is>
-      </c>
-      <c r="B90" s="22" t="inlineStr">
-        <is>
-          <t>As a Super Admin, I want to grant/revoke Admin access.</t>
-        </is>
-      </c>
-      <c r="C90" s="22" t="inlineStr">
-        <is>
-          <t>Open a user → grant Admin access → check org(s) → save; then uncheck all → save.</t>
-        </is>
-      </c>
-      <c r="D90" s="22" t="inlineStr">
-        <is>
-          <t>Checking orgs makes an Admin; unchecking all reverts to participant.</t>
-        </is>
-      </c>
-      <c r="E90" s="23" t="n"/>
-      <c r="F90" s="22" t="n"/>
-      <c r="G90" s="23" t="n"/>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="19" t="inlineStr">
+        <is>
+          <t>Super Admin (global)</t>
+        </is>
+      </c>
+      <c r="B90" s="20" t="n"/>
+      <c r="C90" s="20" t="n"/>
+      <c r="D90" s="20" t="n"/>
+      <c r="E90" s="20" t="n"/>
+      <c r="F90" s="20" t="n"/>
+      <c r="G90" s="20" t="n"/>
     </row>
     <row r="91" ht="42" customHeight="1">
       <c r="A91" s="21" t="inlineStr">
         <is>
-          <t>SA5</t>
+          <t>SA1</t>
         </is>
       </c>
       <c r="B91" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to create organizations + join codes.</t>
+          <t>As a Super Admin, I want the correct menu tabs.</t>
         </is>
       </c>
       <c r="C91" s="22" t="inlineStr">
         <is>
-          <t>Organizations → Add organization → set details + join code.</t>
+          <t>Look at the left menu.</t>
         </is>
       </c>
       <c r="D91" s="22" t="inlineStr">
         <is>
-          <t>Org created with its join code.</t>
+          <t>Dashboard, Reports, Users, Events, Organizations (Help in footer).</t>
         </is>
       </c>
       <c r="E91" s="23" t="n"/>
@@ -8793,22 +8993,22 @@
     <row r="92" ht="42" customHeight="1">
       <c r="A92" s="21" t="inlineStr">
         <is>
-          <t>SA6</t>
+          <t>SA2</t>
         </is>
       </c>
       <c r="B92" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to find users by type.</t>
+          <t>As a Super Admin, I can do everything an Admin can, across all orgs.</t>
         </is>
       </c>
       <c r="C92" s="22" t="inlineStr">
         <is>
-          <t>Users → role filter pills + search.</t>
+          <t>Spot-check user + org actions on more than one org.</t>
         </is>
       </c>
       <c r="D92" s="22" t="inlineStr">
         <is>
-          <t>Filter by role with counts; search by name/email across all orgs.</t>
+          <t>All allowed regardless of org.</t>
         </is>
       </c>
       <c r="E92" s="23" t="n"/>
@@ -8818,22 +9018,22 @@
     <row r="93" ht="42" customHeight="1">
       <c r="A93" s="21" t="inlineStr">
         <is>
-          <t>SA7</t>
+          <t>SA3</t>
         </is>
       </c>
       <c r="B93" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to search events.</t>
+          <t>As a Super Admin, I want to create users incl. Supervisor and Super Admin.</t>
         </is>
       </c>
       <c r="C93" s="22" t="inlineStr">
         <is>
-          <t>Events → search + date range; check supervisor/org per card.</t>
+          <t>Users → Add user → each role.</t>
         </is>
       </c>
       <c r="D93" s="22" t="inlineStr">
         <is>
-          <t>Filters work; each event shows supervisor and organization.</t>
+          <t>Participant/Supervisor/Super Admin options available; account created + invite email.</t>
         </is>
       </c>
       <c r="E93" s="23" t="n"/>
@@ -8843,22 +9043,22 @@
     <row r="94" ht="42" customHeight="1">
       <c r="A94" s="21" t="inlineStr">
         <is>
-          <t>SA8</t>
+          <t>SA4</t>
         </is>
       </c>
       <c r="B94" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want clear event-visibility labels.</t>
+          <t>As a Super Admin, I want to grant/revoke Admin access.</t>
         </is>
       </c>
       <c r="C94" s="22" t="inlineStr">
         <is>
-          <t>New Event → 'Who can see this'.</t>
+          <t>Open a user → grant Admin access → check org(s) → save; then uncheck all → save.</t>
         </is>
       </c>
       <c r="D94" s="22" t="inlineStr">
         <is>
-          <t>'Open to all (community)' and 'Only &lt;org&gt; students' with helper text.</t>
+          <t>Checking orgs makes an Admin; unchecking all reverts to participant.</t>
         </is>
       </c>
       <c r="E94" s="23" t="n"/>
@@ -8868,22 +9068,22 @@
     <row r="95" ht="42" customHeight="1">
       <c r="A95" s="21" t="inlineStr">
         <is>
-          <t>SA9</t>
+          <t>SA5</t>
         </is>
       </c>
       <c r="B95" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want program-wide reports.</t>
+          <t>As a Super Admin, I want to create organizations + join codes.</t>
         </is>
       </c>
       <c r="C95" s="22" t="inlineStr">
         <is>
-          <t>Open Reports / Dashboard.</t>
+          <t>Organizations → Add organization → set details + join code.</t>
         </is>
       </c>
       <c r="D95" s="22" t="inlineStr">
         <is>
-          <t>Totals and charts across the whole program.</t>
+          <t>Org created with its join code.</t>
         </is>
       </c>
       <c r="E95" s="23" t="n"/>
@@ -8893,22 +9093,22 @@
     <row r="96" ht="42" customHeight="1">
       <c r="A96" s="21" t="inlineStr">
         <is>
-          <t>SA10</t>
+          <t>SA6</t>
         </is>
       </c>
       <c r="B96" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to verify email works.</t>
+          <t>As a Super Admin, I want to find users by type.</t>
         </is>
       </c>
       <c r="C96" s="22" t="inlineStr">
         <is>
-          <t>Dashboard → Send test email.</t>
+          <t>Users → role filter pills + search.</t>
         </is>
       </c>
       <c r="D96" s="22" t="inlineStr">
         <is>
-          <t>Result shown (success or the exact failure reason).</t>
+          <t>Filter by role with counts; search by name/email across all orgs.</t>
         </is>
       </c>
       <c r="E96" s="23" t="n"/>
@@ -8918,22 +9118,22 @@
     <row r="97" ht="42" customHeight="1">
       <c r="A97" s="21" t="inlineStr">
         <is>
-          <t>SA11</t>
+          <t>SA7</t>
         </is>
       </c>
       <c r="B97" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to update the recycling cans total.</t>
+          <t>As a Super Admin, I want to search events.</t>
         </is>
       </c>
       <c r="C97" s="22" t="inlineStr">
         <is>
-          <t>Use the cans/bin admin control.</t>
+          <t>Events → search + date range; check supervisor/org per card.</t>
         </is>
       </c>
       <c r="D97" s="22" t="inlineStr">
         <is>
-          <t>Total updates; the ribbon reflects it.</t>
+          <t>Filters work; each event shows supervisor and organization.</t>
         </is>
       </c>
       <c r="E97" s="23" t="n"/>
@@ -8943,60 +9143,72 @@
     <row r="98" ht="42" customHeight="1">
       <c r="A98" s="21" t="inlineStr">
         <is>
-          <t>SA12</t>
+          <t>SA8</t>
         </is>
       </c>
       <c r="B98" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want hours + records for any user.</t>
+          <t>As a Super Admin, I want clear event-visibility labels.</t>
         </is>
       </c>
       <c r="C98" s="22" t="inlineStr">
         <is>
-          <t>Add manual hours / open service record for any participant.</t>
+          <t>New Event → 'Who can see this'.</t>
         </is>
       </c>
       <c r="D98" s="22" t="inlineStr">
         <is>
-          <t>Works for any org.</t>
+          <t>'Open to all (community)' and 'Only &lt;org&gt; students' with helper text.</t>
         </is>
       </c>
       <c r="E98" s="23" t="n"/>
       <c r="F98" s="22" t="n"/>
       <c r="G98" s="23" t="n"/>
     </row>
-    <row r="99" ht="20" customHeight="1">
-      <c r="A99" s="19" t="inlineStr">
-        <is>
-          <t>Cross-cutting</t>
-        </is>
-      </c>
-      <c r="B99" s="20" t="n"/>
-      <c r="C99" s="20" t="n"/>
-      <c r="D99" s="20" t="n"/>
-      <c r="E99" s="20" t="n"/>
-      <c r="F99" s="20" t="n"/>
-      <c r="G99" s="20" t="n"/>
+    <row r="99" ht="42" customHeight="1">
+      <c r="A99" s="21" t="inlineStr">
+        <is>
+          <t>SA9</t>
+        </is>
+      </c>
+      <c r="B99" s="22" t="inlineStr">
+        <is>
+          <t>As a Super Admin, I want program-wide reports.</t>
+        </is>
+      </c>
+      <c r="C99" s="22" t="inlineStr">
+        <is>
+          <t>Open Reports / Dashboard.</t>
+        </is>
+      </c>
+      <c r="D99" s="22" t="inlineStr">
+        <is>
+          <t>Totals and charts across the whole program.</t>
+        </is>
+      </c>
+      <c r="E99" s="23" t="n"/>
+      <c r="F99" s="22" t="n"/>
+      <c r="G99" s="23" t="n"/>
     </row>
     <row r="100" ht="42" customHeight="1">
       <c r="A100" s="21" t="inlineStr">
         <is>
-          <t>X1</t>
+          <t>SA10</t>
         </is>
       </c>
       <c r="B100" s="22" t="inlineStr">
         <is>
-          <t>As a phone user, I want a usable mobile layout.</t>
+          <t>As a Super Admin, I want to verify email works.</t>
         </is>
       </c>
       <c r="C100" s="22" t="inlineStr">
         <is>
-          <t>Open at phone width; use the menu drawer.</t>
+          <t>Dashboard → Send test email.</t>
         </is>
       </c>
       <c r="D100" s="22" t="inlineStr">
         <is>
-          <t>Layout adapts; drawer opens/closes; no horizontal scroll.</t>
+          <t>Result shown (success or the exact failure reason).</t>
         </is>
       </c>
       <c r="E100" s="23" t="n"/>
@@ -9006,39 +9218,127 @@
     <row r="101" ht="42" customHeight="1">
       <c r="A101" s="21" t="inlineStr">
         <is>
-          <t>X2</t>
+          <t>SA11</t>
         </is>
       </c>
       <c r="B101" s="22" t="inlineStr">
         <is>
-          <t>As a visitor, I want the recycling ribbon on the login page.</t>
+          <t>As a Super Admin, I want to update the recycling cans total.</t>
         </is>
       </c>
       <c r="C101" s="22" t="inlineStr">
         <is>
-          <t>Open login signed out.</t>
+          <t>Use the cans/bin admin control.</t>
         </is>
       </c>
       <c r="D101" s="22" t="inlineStr">
         <is>
-          <t>Green ribbon shows on login.</t>
+          <t>Total updates; the ribbon reflects it.</t>
         </is>
       </c>
       <c r="E101" s="23" t="n"/>
       <c r="F101" s="22" t="n"/>
       <c r="G101" s="23" t="n"/>
     </row>
+    <row r="102" ht="42" customHeight="1">
+      <c r="A102" s="21" t="inlineStr">
+        <is>
+          <t>SA12</t>
+        </is>
+      </c>
+      <c r="B102" s="22" t="inlineStr">
+        <is>
+          <t>As a Super Admin, I want hours + records for any user.</t>
+        </is>
+      </c>
+      <c r="C102" s="22" t="inlineStr">
+        <is>
+          <t>Add manual hours / open service record for any participant.</t>
+        </is>
+      </c>
+      <c r="D102" s="22" t="inlineStr">
+        <is>
+          <t>Works for any org.</t>
+        </is>
+      </c>
+      <c r="E102" s="23" t="n"/>
+      <c r="F102" s="22" t="n"/>
+      <c r="G102" s="23" t="n"/>
+    </row>
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="19" t="inlineStr">
+        <is>
+          <t>Cross-cutting</t>
+        </is>
+      </c>
+      <c r="B103" s="20" t="n"/>
+      <c r="C103" s="20" t="n"/>
+      <c r="D103" s="20" t="n"/>
+      <c r="E103" s="20" t="n"/>
+      <c r="F103" s="20" t="n"/>
+      <c r="G103" s="20" t="n"/>
+    </row>
+    <row r="104" ht="42" customHeight="1">
+      <c r="A104" s="21" t="inlineStr">
+        <is>
+          <t>X1</t>
+        </is>
+      </c>
+      <c r="B104" s="22" t="inlineStr">
+        <is>
+          <t>As a phone user, I want a usable mobile layout.</t>
+        </is>
+      </c>
+      <c r="C104" s="22" t="inlineStr">
+        <is>
+          <t>Open at phone width; use the menu drawer.</t>
+        </is>
+      </c>
+      <c r="D104" s="22" t="inlineStr">
+        <is>
+          <t>Layout adapts; drawer opens/closes; no horizontal scroll.</t>
+        </is>
+      </c>
+      <c r="E104" s="23" t="n"/>
+      <c r="F104" s="22" t="n"/>
+      <c r="G104" s="23" t="n"/>
+    </row>
+    <row r="105" ht="42" customHeight="1">
+      <c r="A105" s="21" t="inlineStr">
+        <is>
+          <t>X2</t>
+        </is>
+      </c>
+      <c r="B105" s="22" t="inlineStr">
+        <is>
+          <t>As a visitor, I want the recycling ribbon on the login page.</t>
+        </is>
+      </c>
+      <c r="C105" s="22" t="inlineStr">
+        <is>
+          <t>Open login signed out.</t>
+        </is>
+      </c>
+      <c r="D105" s="22" t="inlineStr">
+        <is>
+          <t>Green ribbon shows on login.</t>
+        </is>
+      </c>
+      <c r="E105" s="23" t="n"/>
+      <c r="F105" s="22" t="n"/>
+      <c r="G105" s="23" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A99:G99"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A55:G55"/>
     <mergeCell ref="A35:G35"/>
-    <mergeCell ref="A86:G86"/>
-    <mergeCell ref="A71:G71"/>
-    <mergeCell ref="A51:G51"/>
+    <mergeCell ref="A90:G90"/>
+    <mergeCell ref="A49:G49"/>
     <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="A103:G103"/>
+    <mergeCell ref="A75:G75"/>
   </mergeCells>
   <conditionalFormatting sqref="E4:E9">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
@@ -9062,7 +9362,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E36:E44">
+  <conditionalFormatting sqref="E36:E48">
     <cfRule type="cellIs" priority="7" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -9073,7 +9373,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E46:E50">
+  <conditionalFormatting sqref="E50:E54">
     <cfRule type="cellIs" priority="10" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -9084,7 +9384,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E52:E70">
+  <conditionalFormatting sqref="E56:E74">
     <cfRule type="cellIs" priority="13" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -9095,7 +9395,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E72:E85">
+  <conditionalFormatting sqref="E76:E89">
     <cfRule type="cellIs" priority="16" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -9106,7 +9406,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E87:E98">
+  <conditionalFormatting sqref="E91:E102">
     <cfRule type="cellIs" priority="19" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -9117,7 +9417,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E100:E101">
+  <conditionalFormatting sqref="E104:E105">
     <cfRule type="cellIs" priority="22" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -9129,7 +9429,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E4:E9 E11:E34 E36:E44 E46:E50 E52:E70 E72:E85 E87:E98 E100:E101" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E4:E9 E11:E34 E36:E48 E50:E54 E56:E74 E76:E89 E91:E102 E104:E105" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pass,Fail,Blocked,Not tested,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -9143,7 +9443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:G105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10219,38 +10519,50 @@
       <c r="F44" s="22" t="n"/>
       <c r="G44" s="23" t="n"/>
     </row>
-    <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="19" t="inlineStr">
-        <is>
-          <t>Parent — viewer (grades 6–12 student)</t>
-        </is>
-      </c>
-      <c r="B45" s="20" t="n"/>
-      <c r="C45" s="20" t="n"/>
-      <c r="D45" s="20" t="n"/>
-      <c r="E45" s="20" t="n"/>
-      <c r="F45" s="20" t="n"/>
-      <c r="G45" s="20" t="n"/>
+    <row r="45" ht="42" customHeight="1">
+      <c r="A45" s="21" t="inlineStr">
+        <is>
+          <t>PE10</t>
+        </is>
+      </c>
+      <c r="B45" s="22" t="inlineStr">
+        <is>
+          <t>As a parent, I want to submit my child's hours after an event (child has no login).</t>
+        </is>
+      </c>
+      <c r="C45" s="22" t="inlineStr">
+        <is>
+          <t>Dashboard → the child's 'Submit hours (past events)' → enter hours → Submit.</t>
+        </is>
+      </c>
+      <c r="D45" s="22" t="inlineStr">
+        <is>
+          <t>Hours go to the supervisor for approval; status shows 'Waiting for review'.</t>
+        </is>
+      </c>
+      <c r="E45" s="23" t="n"/>
+      <c r="F45" s="22" t="n"/>
+      <c r="G45" s="23" t="n"/>
     </row>
     <row r="46" ht="42" customHeight="1">
       <c r="A46" s="21" t="inlineStr">
         <is>
-          <t>PV1</t>
+          <t>PE11</t>
         </is>
       </c>
       <c r="B46" s="22" t="inlineStr">
         <is>
-          <t>As a parent of a 6–12 student, I want to register for view-only access.</t>
+          <t>As a parent, I want to resubmit my child's rejected hours.</t>
         </is>
       </c>
       <c r="C46" s="22" t="inlineStr">
         <is>
-          <t>Create account → parent of a 6–12 student.</t>
+          <t>On a rejected past event, enter corrected hours → Resubmit.</t>
         </is>
       </c>
       <c r="D46" s="22" t="inlineStr">
         <is>
-          <t>Account created; no invite required to register.</t>
+          <t>Returns to 'Waiting for review'.</t>
         </is>
       </c>
       <c r="E46" s="23" t="n"/>
@@ -10260,22 +10572,22 @@
     <row r="47" ht="42" customHeight="1">
       <c r="A47" s="21" t="inlineStr">
         <is>
-          <t>PV2</t>
+          <t>PE12</t>
         </is>
       </c>
       <c r="B47" s="22" t="inlineStr">
         <is>
-          <t>As a viewer parent, my student links automatically by email.</t>
+          <t>As a parent, I want to see each past event's hours status for my child.</t>
         </is>
       </c>
       <c r="C47" s="22" t="inlineStr">
         <is>
-          <t>Have a student enter this exact email as their parent email (before or after you register).</t>
+          <t>Look at the child's past events list.</t>
         </is>
       </c>
       <c r="D47" s="22" t="inlineStr">
         <is>
-          <t>The student appears on your dashboard automatically; empty until then.</t>
+          <t>Each shows Approved / Waiting / Rejected as appropriate.</t>
         </is>
       </c>
       <c r="E47" s="23" t="n"/>
@@ -10285,110 +10597,110 @@
     <row r="48" ht="42" customHeight="1">
       <c r="A48" s="21" t="inlineStr">
         <is>
-          <t>PV3</t>
+          <t>PE13</t>
         </is>
       </c>
       <c r="B48" s="22" t="inlineStr">
         <is>
-          <t>As a viewer parent, I want to see my student's schedule/progress.</t>
+          <t>As a parent, all core participant actions are available to me for my child.</t>
         </is>
       </c>
       <c r="C48" s="22" t="inlineStr">
         <is>
-          <t>Open the dashboard.</t>
+          <t>Confirm: browse, sign up, withdraw, add-to-calendar, submit hours, view progress toward medals.</t>
         </is>
       </c>
       <c r="D48" s="22" t="inlineStr">
         <is>
-          <t>View-only schedule and progress.</t>
+          <t>All participant-style actions work on the child's behalf (the child never logs in).</t>
         </is>
       </c>
       <c r="E48" s="23" t="n"/>
       <c r="F48" s="22" t="n"/>
       <c r="G48" s="23" t="n"/>
     </row>
-    <row r="49" ht="42" customHeight="1">
-      <c r="A49" s="21" t="inlineStr">
-        <is>
-          <t>PV4</t>
-        </is>
-      </c>
-      <c r="B49" s="22" t="inlineStr">
-        <is>
-          <t>As a viewer parent, I do NOT sign the student up.</t>
-        </is>
-      </c>
-      <c r="C49" s="22" t="inlineStr">
-        <is>
-          <t>Look for a sign-up action.</t>
-        </is>
-      </c>
-      <c r="D49" s="22" t="inlineStr">
-        <is>
-          <t>No sign-up on the student's behalf — the student self-serves.</t>
-        </is>
-      </c>
-      <c r="E49" s="23" t="n"/>
-      <c r="F49" s="22" t="n"/>
-      <c r="G49" s="23" t="n"/>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="19" t="inlineStr">
+        <is>
+          <t>Parent — viewer (grades 6–12 student)</t>
+        </is>
+      </c>
+      <c r="B49" s="20" t="n"/>
+      <c r="C49" s="20" t="n"/>
+      <c r="D49" s="20" t="n"/>
+      <c r="E49" s="20" t="n"/>
+      <c r="F49" s="20" t="n"/>
+      <c r="G49" s="20" t="n"/>
     </row>
     <row r="50" ht="42" customHeight="1">
       <c r="A50" s="21" t="inlineStr">
         <is>
-          <t>PV5</t>
+          <t>PV1</t>
         </is>
       </c>
       <c r="B50" s="22" t="inlineStr">
         <is>
-          <t>As a viewer parent, I want to invite a co-guardian.</t>
+          <t>As a parent of a 6–12 student, I want to register for view-only access.</t>
         </is>
       </c>
       <c r="C50" s="22" t="inlineStr">
         <is>
-          <t>Invite a co-guardian by email.</t>
+          <t>Create account → parent of a 6–12 student.</t>
         </is>
       </c>
       <c r="D50" s="22" t="inlineStr">
         <is>
-          <t>Invite email sent; shared access on registration.</t>
+          <t>Account created; no invite required to register.</t>
         </is>
       </c>
       <c r="E50" s="23" t="n"/>
       <c r="F50" s="22" t="n"/>
       <c r="G50" s="23" t="n"/>
     </row>
-    <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="19" t="inlineStr">
-        <is>
-          <t>Supervisor (created by an Admin)</t>
-        </is>
-      </c>
-      <c r="B51" s="20" t="n"/>
-      <c r="C51" s="20" t="n"/>
-      <c r="D51" s="20" t="n"/>
-      <c r="E51" s="20" t="n"/>
-      <c r="F51" s="20" t="n"/>
-      <c r="G51" s="20" t="n"/>
+    <row r="51" ht="42" customHeight="1">
+      <c r="A51" s="21" t="inlineStr">
+        <is>
+          <t>PV2</t>
+        </is>
+      </c>
+      <c r="B51" s="22" t="inlineStr">
+        <is>
+          <t>As a viewer parent, my student links automatically by email.</t>
+        </is>
+      </c>
+      <c r="C51" s="22" t="inlineStr">
+        <is>
+          <t>Have a student enter this exact email as their parent email (before or after you register).</t>
+        </is>
+      </c>
+      <c r="D51" s="22" t="inlineStr">
+        <is>
+          <t>The student appears on your dashboard automatically; empty until then.</t>
+        </is>
+      </c>
+      <c r="E51" s="23" t="n"/>
+      <c r="F51" s="22" t="n"/>
+      <c r="G51" s="23" t="n"/>
     </row>
     <row r="52" ht="42" customHeight="1">
       <c r="A52" s="21" t="inlineStr">
         <is>
-          <t>SV1</t>
+          <t>PV3</t>
         </is>
       </c>
       <c r="B52" s="22" t="inlineStr">
         <is>
-          <t>As the program, a supervisor cannot self-register.</t>
+          <t>As a viewer parent, I want to see my student's schedule/progress.</t>
         </is>
       </c>
       <c r="C52" s="22" t="inlineStr">
         <is>
-          <t>Review the sign-up options.</t>
+          <t>Open the dashboard.</t>
         </is>
       </c>
       <c r="D52" s="22" t="inlineStr">
         <is>
-          <t>No supervisor option exists on registration.</t>
+          <t>View-only schedule and progress.</t>
         </is>
       </c>
       <c r="E52" s="23" t="n"/>
@@ -10398,22 +10710,22 @@
     <row r="53" ht="42" customHeight="1">
       <c r="A53" s="21" t="inlineStr">
         <is>
-          <t>SV2</t>
+          <t>PV4</t>
         </is>
       </c>
       <c r="B53" s="22" t="inlineStr">
         <is>
-          <t>As a new supervisor, I get an invite to set my password.</t>
+          <t>As a viewer parent, I do NOT sign the student up.</t>
         </is>
       </c>
       <c r="C53" s="22" t="inlineStr">
         <is>
-          <t>Have an Admin create your account; open the invite email; set password; sign in.</t>
+          <t>Look for a sign-up action.</t>
         </is>
       </c>
       <c r="D53" s="22" t="inlineStr">
         <is>
-          <t>Invite email arrives with a working set-password link; you can sign in.</t>
+          <t>No sign-up on the student's behalf — the student self-serves.</t>
         </is>
       </c>
       <c r="E53" s="23" t="n"/>
@@ -10423,72 +10735,60 @@
     <row r="54" ht="42" customHeight="1">
       <c r="A54" s="21" t="inlineStr">
         <is>
-          <t>SV3</t>
+          <t>PV5</t>
         </is>
       </c>
       <c r="B54" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want the correct 7 left-menu tabs.</t>
+          <t>As a viewer parent, I want to invite a co-guardian.</t>
         </is>
       </c>
       <c r="C54" s="22" t="inlineStr">
         <is>
-          <t>Look at the left menu.</t>
+          <t>Invite a co-guardian by email.</t>
         </is>
       </c>
       <c r="D54" s="22" t="inlineStr">
         <is>
-          <t>Dashboard, Pending Reviews, Reviewed History, My Events, All Opportunities, My Hours, Help.</t>
+          <t>Invite email sent; shared access on registration.</t>
         </is>
       </c>
       <c r="E54" s="23" t="n"/>
       <c r="F54" s="22" t="n"/>
       <c r="G54" s="23" t="n"/>
     </row>
-    <row r="55" ht="42" customHeight="1">
-      <c r="A55" s="21" t="inlineStr">
-        <is>
-          <t>SV4</t>
-        </is>
-      </c>
-      <c r="B55" s="22" t="inlineStr">
-        <is>
-          <t>As a supervisor, I want a dashboard.</t>
-        </is>
-      </c>
-      <c r="C55" s="22" t="inlineStr">
-        <is>
-          <t>Open the dashboard.</t>
-        </is>
-      </c>
-      <c r="D55" s="22" t="inlineStr">
-        <is>
-          <t>Review queue, approved/rejected counts, registrations, hours, upcoming events + Roster links.</t>
-        </is>
-      </c>
-      <c r="E55" s="23" t="n"/>
-      <c r="F55" s="22" t="n"/>
-      <c r="G55" s="23" t="n"/>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="19" t="inlineStr">
+        <is>
+          <t>Supervisor (created by an Admin)</t>
+        </is>
+      </c>
+      <c r="B55" s="20" t="n"/>
+      <c r="C55" s="20" t="n"/>
+      <c r="D55" s="20" t="n"/>
+      <c r="E55" s="20" t="n"/>
+      <c r="F55" s="20" t="n"/>
+      <c r="G55" s="20" t="n"/>
     </row>
     <row r="56" ht="42" customHeight="1">
       <c r="A56" s="21" t="inlineStr">
         <is>
-          <t>SV5</t>
+          <t>SV1</t>
         </is>
       </c>
       <c r="B56" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to approve hours.</t>
+          <t>As the program, a supervisor cannot self-register.</t>
         </is>
       </c>
       <c r="C56" s="22" t="inlineStr">
         <is>
-          <t>Pending Reviews → open → Approve.</t>
+          <t>Review the sign-up options.</t>
         </is>
       </c>
       <c r="D56" s="22" t="inlineStr">
         <is>
-          <t>Approved; moves to Reviewed History; participant total updates; email sent.</t>
+          <t>No supervisor option exists on registration.</t>
         </is>
       </c>
       <c r="E56" s="23" t="n"/>
@@ -10498,22 +10798,22 @@
     <row r="57" ht="42" customHeight="1">
       <c r="A57" s="21" t="inlineStr">
         <is>
-          <t>SV6</t>
+          <t>SV2</t>
         </is>
       </c>
       <c r="B57" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to reject hours with a reason.</t>
+          <t>As a new supervisor, I get an invite to set my password.</t>
         </is>
       </c>
       <c r="C57" s="22" t="inlineStr">
         <is>
-          <t>Reject without a reason, then with one.</t>
+          <t>Have an Admin create your account; open the invite email; set password; sign in.</t>
         </is>
       </c>
       <c r="D57" s="22" t="inlineStr">
         <is>
-          <t>Blocked until a reason is given; then rejected and the participant notified.</t>
+          <t>Invite email arrives with a working set-password link; you can sign in.</t>
         </is>
       </c>
       <c r="E57" s="23" t="n"/>
@@ -10523,22 +10823,22 @@
     <row r="58" ht="42" customHeight="1">
       <c r="A58" s="21" t="inlineStr">
         <is>
-          <t>SV7</t>
+          <t>SV3</t>
         </is>
       </c>
       <c r="B58" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to review external submissions.</t>
+          <t>As a supervisor, I want the correct 7 left-menu tabs.</t>
         </is>
       </c>
       <c r="C58" s="22" t="inlineStr">
         <is>
-          <t>Pending Reviews → external tab → approve/reject.</t>
+          <t>Look at the left menu.</t>
         </is>
       </c>
       <c r="D58" s="22" t="inlineStr">
         <is>
-          <t>External items reviewable, including any proof.</t>
+          <t>Dashboard, Pending Reviews, Reviewed History, My Events, All Opportunities, My Hours, Help.</t>
         </is>
       </c>
       <c r="E58" s="23" t="n"/>
@@ -10548,22 +10848,22 @@
     <row r="59" ht="42" customHeight="1">
       <c r="A59" s="21" t="inlineStr">
         <is>
-          <t>SV8</t>
+          <t>SV4</t>
         </is>
       </c>
       <c r="B59" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to create an event.</t>
+          <t>As a supervisor, I want a dashboard.</t>
         </is>
       </c>
       <c r="C59" s="22" t="inlineStr">
         <is>
-          <t>New Event → title, description, slot, address, date, times, capacity, grade limits → save.</t>
+          <t>Open the dashboard.</t>
         </is>
       </c>
       <c r="D59" s="22" t="inlineStr">
         <is>
-          <t>Credit auto-calculated from times; event created in My Events.</t>
+          <t>Review queue, approved/rejected counts, registrations, hours, upcoming events + Roster links.</t>
         </is>
       </c>
       <c r="E59" s="23" t="n"/>
@@ -10573,22 +10873,22 @@
     <row r="60" ht="42" customHeight="1">
       <c r="A60" s="21" t="inlineStr">
         <is>
-          <t>SV9</t>
+          <t>SV5</t>
         </is>
       </c>
       <c r="B60" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to edit an event.</t>
+          <t>As a supervisor, I want to approve hours.</t>
         </is>
       </c>
       <c r="C60" s="22" t="inlineStr">
         <is>
-          <t>My Events → edit → save.</t>
+          <t>Pending Reviews → open → Approve.</t>
         </is>
       </c>
       <c r="D60" s="22" t="inlineStr">
         <is>
-          <t>Changes persist and show to participants.</t>
+          <t>Approved; moves to Reviewed History; participant total updates; email sent.</t>
         </is>
       </c>
       <c r="E60" s="23" t="n"/>
@@ -10598,22 +10898,22 @@
     <row r="61" ht="42" customHeight="1">
       <c r="A61" s="21" t="inlineStr">
         <is>
-          <t>SV10</t>
+          <t>SV6</t>
         </is>
       </c>
       <c r="B61" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to delete an event with no approved hours.</t>
+          <t>As a supervisor, I want to reject hours with a reason.</t>
         </is>
       </c>
       <c r="C61" s="22" t="inlineStr">
         <is>
-          <t>Delete such an event → confirm.</t>
+          <t>Reject without a reason, then with one.</t>
         </is>
       </c>
       <c r="D61" s="22" t="inlineStr">
         <is>
-          <t>Event deleted.</t>
+          <t>Blocked until a reason is given; then rejected and the participant notified.</t>
         </is>
       </c>
       <c r="E61" s="23" t="n"/>
@@ -10623,22 +10923,22 @@
     <row r="62" ht="42" customHeight="1">
       <c r="A62" s="21" t="inlineStr">
         <is>
-          <t>SV11</t>
+          <t>SV7</t>
         </is>
       </c>
       <c r="B62" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, deleting an event with approved hours is blocked.</t>
+          <t>As a supervisor, I want to review external submissions.</t>
         </is>
       </c>
       <c r="C62" s="22" t="inlineStr">
         <is>
-          <t>Try to delete an event that has approved hours.</t>
+          <t>Pending Reviews → external tab → approve/reject.</t>
         </is>
       </c>
       <c r="D62" s="22" t="inlineStr">
         <is>
-          <t>Blocked with a message that approved hours must be preserved.</t>
+          <t>External items reviewable, including any proof.</t>
         </is>
       </c>
       <c r="E62" s="23" t="n"/>
@@ -10648,22 +10948,22 @@
     <row r="63" ht="42" customHeight="1">
       <c r="A63" s="21" t="inlineStr">
         <is>
-          <t>SV12</t>
+          <t>SV8</t>
         </is>
       </c>
       <c r="B63" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to see who signed up.</t>
+          <t>As a supervisor, I want to create an event.</t>
         </is>
       </c>
       <c r="C63" s="22" t="inlineStr">
         <is>
-          <t>Open the event Roster.</t>
+          <t>New Event → title, description, slot, address, date, times, capacity, grade limits → save.</t>
         </is>
       </c>
       <c r="D63" s="22" t="inlineStr">
         <is>
-          <t>Registrants listed with grade and status.</t>
+          <t>Credit auto-calculated from times; event created in My Events.</t>
         </is>
       </c>
       <c r="E63" s="23" t="n"/>
@@ -10673,22 +10973,22 @@
     <row r="64" ht="42" customHeight="1">
       <c r="A64" s="21" t="inlineStr">
         <is>
-          <t>SV13</t>
+          <t>SV9</t>
         </is>
       </c>
       <c r="B64" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to check people in / mark no-show.</t>
+          <t>As a supervisor, I want to edit an event.</t>
         </is>
       </c>
       <c r="C64" s="22" t="inlineStr">
         <is>
-          <t>On the roster, Check in and Mark no-show.</t>
+          <t>My Events → edit → save.</t>
         </is>
       </c>
       <c r="D64" s="22" t="inlineStr">
         <is>
-          <t>Status updates and persists.</t>
+          <t>Changes persist and show to participants.</t>
         </is>
       </c>
       <c r="E64" s="23" t="n"/>
@@ -10698,22 +10998,22 @@
     <row r="65" ht="42" customHeight="1">
       <c r="A65" s="21" t="inlineStr">
         <is>
-          <t>SV14</t>
+          <t>SV10</t>
         </is>
       </c>
       <c r="B65" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to message everyone signed up.</t>
+          <t>As a supervisor, I want to delete an event with no approved hours.</t>
         </is>
       </c>
       <c r="C65" s="22" t="inlineStr">
         <is>
-          <t>Roster → Message attendees → subject+message → send (include guardians on).</t>
+          <t>Delete such an event → confirm.</t>
         </is>
       </c>
       <c r="D65" s="22" t="inlineStr">
         <is>
-          <t>Each registrant (and guardians) emailed individually; recipient count shown.</t>
+          <t>Event deleted.</t>
         </is>
       </c>
       <c r="E65" s="23" t="n"/>
@@ -10723,22 +11023,22 @@
     <row r="66" ht="42" customHeight="1">
       <c r="A66" s="21" t="inlineStr">
         <is>
-          <t>SV15</t>
+          <t>SV11</t>
         </is>
       </c>
       <c r="B66" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want a history of what I reviewed.</t>
+          <t>As a supervisor, deleting an event with approved hours is blocked.</t>
         </is>
       </c>
       <c r="C66" s="22" t="inlineStr">
         <is>
-          <t>Open Reviewed History.</t>
+          <t>Try to delete an event that has approved hours.</t>
         </is>
       </c>
       <c r="D66" s="22" t="inlineStr">
         <is>
-          <t>Every approved/rejected item with dates and volunteers.</t>
+          <t>Blocked with a message that approved hours must be preserved.</t>
         </is>
       </c>
       <c r="E66" s="23" t="n"/>
@@ -10748,22 +11048,22 @@
     <row r="67" ht="42" customHeight="1">
       <c r="A67" s="21" t="inlineStr">
         <is>
-          <t>SV16</t>
+          <t>SV12</t>
         </is>
       </c>
       <c r="B67" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to browse all opportunities view-only.</t>
+          <t>As a supervisor, I want to see who signed up.</t>
         </is>
       </c>
       <c r="C67" s="22" t="inlineStr">
         <is>
-          <t>All Opportunities → search / upcoming-past.</t>
+          <t>Open the event Roster.</t>
         </is>
       </c>
       <c r="D67" s="22" t="inlineStr">
         <is>
-          <t>Every event listed read-only; can't edit others' events.</t>
+          <t>Registrants listed with grade and status.</t>
         </is>
       </c>
       <c r="E67" s="23" t="n"/>
@@ -10773,22 +11073,22 @@
     <row r="68" ht="42" customHeight="1">
       <c r="A68" s="21" t="inlineStr">
         <is>
-          <t>SV17</t>
+          <t>SV13</t>
         </is>
       </c>
       <c r="B68" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to log my own adult hours.</t>
+          <t>As a supervisor, I want to check people in / mark no-show.</t>
         </is>
       </c>
       <c r="C68" s="22" t="inlineStr">
         <is>
-          <t>My Hours → log an activity, date, hours → save.</t>
+          <t>On the roster, Check in and Mark no-show.</t>
         </is>
       </c>
       <c r="D68" s="22" t="inlineStr">
         <is>
-          <t>Recorded instantly with a running total; clearly NOT part of the student competition.</t>
+          <t>Status updates and persists.</t>
         </is>
       </c>
       <c r="E68" s="23" t="n"/>
@@ -10798,22 +11098,22 @@
     <row r="69" ht="42" customHeight="1">
       <c r="A69" s="21" t="inlineStr">
         <is>
-          <t>SV18</t>
+          <t>SV14</t>
         </is>
       </c>
       <c r="B69" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to delete an adult-hours entry.</t>
+          <t>As a supervisor, I want to message everyone signed up.</t>
         </is>
       </c>
       <c r="C69" s="22" t="inlineStr">
         <is>
-          <t>My Hours → delete an entry → confirm.</t>
+          <t>Roster → Message attendees → subject+message → send (include guardians on).</t>
         </is>
       </c>
       <c r="D69" s="22" t="inlineStr">
         <is>
-          <t>Removed; total updates.</t>
+          <t>Each registrant (and guardians) emailed individually; recipient count shown.</t>
         </is>
       </c>
       <c r="E69" s="23" t="n"/>
@@ -10823,60 +11123,72 @@
     <row r="70" ht="42" customHeight="1">
       <c r="A70" s="21" t="inlineStr">
         <is>
-          <t>SV19</t>
+          <t>SV15</t>
         </is>
       </c>
       <c r="B70" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I must NOT access user or org management.</t>
+          <t>As a supervisor, I want a history of what I reviewed.</t>
         </is>
       </c>
       <c r="C70" s="22" t="inlineStr">
         <is>
-          <t>Look for Users / Organizations in the menu.</t>
+          <t>Open Reviewed History.</t>
         </is>
       </c>
       <c r="D70" s="22" t="inlineStr">
         <is>
-          <t>Those tabs are absent; direct URLs are blocked.</t>
+          <t>Every approved/rejected item with dates and volunteers.</t>
         </is>
       </c>
       <c r="E70" s="23" t="n"/>
       <c r="F70" s="22" t="n"/>
       <c r="G70" s="23" t="n"/>
     </row>
-    <row r="71" ht="20" customHeight="1">
-      <c r="A71" s="19" t="inlineStr">
-        <is>
-          <t>Admin (org-scoped)</t>
-        </is>
-      </c>
-      <c r="B71" s="20" t="n"/>
-      <c r="C71" s="20" t="n"/>
-      <c r="D71" s="20" t="n"/>
-      <c r="E71" s="20" t="n"/>
-      <c r="F71" s="20" t="n"/>
-      <c r="G71" s="20" t="n"/>
+    <row r="71" ht="42" customHeight="1">
+      <c r="A71" s="21" t="inlineStr">
+        <is>
+          <t>SV16</t>
+        </is>
+      </c>
+      <c r="B71" s="22" t="inlineStr">
+        <is>
+          <t>As a supervisor, I want to browse all opportunities view-only.</t>
+        </is>
+      </c>
+      <c r="C71" s="22" t="inlineStr">
+        <is>
+          <t>All Opportunities → search / upcoming-past.</t>
+        </is>
+      </c>
+      <c r="D71" s="22" t="inlineStr">
+        <is>
+          <t>Every event listed read-only; can't edit others' events.</t>
+        </is>
+      </c>
+      <c r="E71" s="23" t="n"/>
+      <c r="F71" s="22" t="n"/>
+      <c r="G71" s="23" t="n"/>
     </row>
     <row r="72" ht="42" customHeight="1">
       <c r="A72" s="21" t="inlineStr">
         <is>
-          <t>AD1</t>
+          <t>SV17</t>
         </is>
       </c>
       <c r="B72" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I want the correct menu tabs.</t>
+          <t>As a supervisor, I want to log my own adult hours.</t>
         </is>
       </c>
       <c r="C72" s="22" t="inlineStr">
         <is>
-          <t>Look at the left menu.</t>
+          <t>My Hours → log an activity, date, hours → save.</t>
         </is>
       </c>
       <c r="D72" s="22" t="inlineStr">
         <is>
-          <t>Dashboard, Pending Reviews, Reviewed History, My Events, All Opportunities, Users, Organizations, My Hours, Help.</t>
+          <t>Recorded instantly with a running total; clearly NOT part of the student competition.</t>
         </is>
       </c>
       <c r="E72" s="23" t="n"/>
@@ -10886,22 +11198,22 @@
     <row r="73" ht="42" customHeight="1">
       <c r="A73" s="21" t="inlineStr">
         <is>
-          <t>AD2</t>
+          <t>SV18</t>
         </is>
       </c>
       <c r="B73" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I can do everything a supervisor can.</t>
+          <t>As a supervisor, I want to delete an adult-hours entry.</t>
         </is>
       </c>
       <c r="C73" s="22" t="inlineStr">
         <is>
-          <t>Spot-check: approve an item and create an event.</t>
+          <t>My Hours → delete an entry → confirm.</t>
         </is>
       </c>
       <c r="D73" s="22" t="inlineStr">
         <is>
-          <t>Both work.</t>
+          <t>Removed; total updates.</t>
         </is>
       </c>
       <c r="E73" s="23" t="n"/>
@@ -10911,72 +11223,60 @@
     <row r="74" ht="42" customHeight="1">
       <c r="A74" s="21" t="inlineStr">
         <is>
-          <t>AD3</t>
+          <t>SV19</t>
         </is>
       </c>
       <c r="B74" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I only see my org's non-admin users.</t>
+          <t>As a supervisor, I must NOT access user or org management.</t>
         </is>
       </c>
       <c r="C74" s="22" t="inlineStr">
         <is>
-          <t>Open Users.</t>
+          <t>Look for Users / Organizations in the menu.</t>
         </is>
       </c>
       <c r="D74" s="22" t="inlineStr">
         <is>
-          <t>Only participants/parents/supervisors in your org; no admins/super admins; no other orgs.</t>
+          <t>Those tabs are absent; direct URLs are blocked.</t>
         </is>
       </c>
       <c r="E74" s="23" t="n"/>
       <c r="F74" s="22" t="n"/>
       <c r="G74" s="23" t="n"/>
     </row>
-    <row r="75" ht="42" customHeight="1">
-      <c r="A75" s="21" t="inlineStr">
-        <is>
-          <t>AD4</t>
-        </is>
-      </c>
-      <c r="B75" s="22" t="inlineStr">
-        <is>
-          <t>As an Admin, I want to add a supervisor.</t>
-        </is>
-      </c>
-      <c r="C75" s="22" t="inlineStr">
-        <is>
-          <t>Users → Add user → Supervisor → save.</t>
-        </is>
-      </c>
-      <c r="D75" s="22" t="inlineStr">
-        <is>
-          <t>Supervisor created, stamped to your org; invite email sent.</t>
-        </is>
-      </c>
-      <c r="E75" s="23" t="n"/>
-      <c r="F75" s="22" t="n"/>
-      <c r="G75" s="23" t="n"/>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="19" t="inlineStr">
+        <is>
+          <t>Admin (org-scoped)</t>
+        </is>
+      </c>
+      <c r="B75" s="20" t="n"/>
+      <c r="C75" s="20" t="n"/>
+      <c r="D75" s="20" t="n"/>
+      <c r="E75" s="20" t="n"/>
+      <c r="F75" s="20" t="n"/>
+      <c r="G75" s="20" t="n"/>
     </row>
     <row r="76" ht="42" customHeight="1">
       <c r="A76" s="21" t="inlineStr">
         <is>
-          <t>AD5</t>
+          <t>AD1</t>
         </is>
       </c>
       <c r="B76" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I want to create a participant as a fallback.</t>
+          <t>As an Admin, I want the correct menu tabs.</t>
         </is>
       </c>
       <c r="C76" s="22" t="inlineStr">
         <is>
-          <t>Users → Add user → Participant → save.</t>
+          <t>Look at the left menu.</t>
         </is>
       </c>
       <c r="D76" s="22" t="inlineStr">
         <is>
-          <t>Participant created with a set-password invite (no silent password).</t>
+          <t>Dashboard, Pending Reviews, Reviewed History, My Events, All Opportunities, Users, Organizations, My Hours, Help.</t>
         </is>
       </c>
       <c r="E76" s="23" t="n"/>
@@ -10986,22 +11286,22 @@
     <row r="77" ht="42" customHeight="1">
       <c r="A77" s="21" t="inlineStr">
         <is>
-          <t>AD6</t>
+          <t>AD2</t>
         </is>
       </c>
       <c r="B77" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I want to grant participant hours.</t>
+          <t>As an Admin, I can do everything a supervisor can.</t>
         </is>
       </c>
       <c r="C77" s="22" t="inlineStr">
         <is>
-          <t>Open a participant in your org → Add hours.</t>
+          <t>Spot-check: approve an item and create an event.</t>
         </is>
       </c>
       <c r="D77" s="22" t="inlineStr">
         <is>
-          <t>Hours auto-approved; count toward their total/medals.</t>
+          <t>Both work.</t>
         </is>
       </c>
       <c r="E77" s="23" t="n"/>
@@ -11011,22 +11311,22 @@
     <row r="78" ht="42" customHeight="1">
       <c r="A78" s="21" t="inlineStr">
         <is>
-          <t>AD7</t>
+          <t>AD3</t>
         </is>
       </c>
       <c r="B78" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I want a participant's service record.</t>
+          <t>As an Admin, I only see my org's non-admin users.</t>
         </is>
       </c>
       <c r="C78" s="22" t="inlineStr">
         <is>
-          <t>Users → Service record for a participant in your org.</t>
+          <t>Open Users.</t>
         </is>
       </c>
       <c r="D78" s="22" t="inlineStr">
         <is>
-          <t>Record opens.</t>
+          <t>Only participants/parents/supervisors in your org; no admins/super admins; no other orgs.</t>
         </is>
       </c>
       <c r="E78" s="23" t="n"/>
@@ -11036,22 +11336,22 @@
     <row r="79" ht="42" customHeight="1">
       <c r="A79" s="21" t="inlineStr">
         <is>
-          <t>AD8</t>
+          <t>AD4</t>
         </is>
       </c>
       <c r="B79" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I want to edit/delete my org's users.</t>
+          <t>As an Admin, I want to add a supervisor.</t>
         </is>
       </c>
       <c r="C79" s="22" t="inlineStr">
         <is>
-          <t>Edit a name/phone; delete a test user.</t>
+          <t>Users → Add user → Supervisor → save.</t>
         </is>
       </c>
       <c r="D79" s="22" t="inlineStr">
         <is>
-          <t>Changes apply within your org.</t>
+          <t>Supervisor created, stamped to your org; invite email sent.</t>
         </is>
       </c>
       <c r="E79" s="23" t="n"/>
@@ -11061,22 +11361,22 @@
     <row r="80" ht="42" customHeight="1">
       <c r="A80" s="21" t="inlineStr">
         <is>
-          <t>AD9</t>
+          <t>AD5</t>
         </is>
       </c>
       <c r="B80" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I must NOT act on users outside my org.</t>
+          <t>As an Admin, I want to create a participant as a fallback.</t>
         </is>
       </c>
       <c r="C80" s="22" t="inlineStr">
         <is>
-          <t>Attempt to reach another org's user (e.g. direct URL).</t>
+          <t>Users → Add user → Participant → save.</t>
         </is>
       </c>
       <c r="D80" s="22" t="inlineStr">
         <is>
-          <t>Blocked / not visible.</t>
+          <t>Participant created with a set-password invite (no silent password).</t>
         </is>
       </c>
       <c r="E80" s="23" t="n"/>
@@ -11086,22 +11386,22 @@
     <row r="81" ht="42" customHeight="1">
       <c r="A81" s="21" t="inlineStr">
         <is>
-          <t>AD10</t>
+          <t>AD6</t>
         </is>
       </c>
       <c r="B81" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I cannot grant Admin access or manage admins.</t>
+          <t>As an Admin, I want to grant participant hours.</t>
         </is>
       </c>
       <c r="C81" s="22" t="inlineStr">
         <is>
-          <t>Look for the 'grant Admin access' action.</t>
+          <t>Open a participant in your org → Add hours.</t>
         </is>
       </c>
       <c r="D81" s="22" t="inlineStr">
         <is>
-          <t>No such button; attempts are blocked server-side.</t>
+          <t>Hours auto-approved; count toward their total/medals.</t>
         </is>
       </c>
       <c r="E81" s="23" t="n"/>
@@ -11111,22 +11411,22 @@
     <row r="82" ht="42" customHeight="1">
       <c r="A82" s="21" t="inlineStr">
         <is>
-          <t>AD11</t>
+          <t>AD7</t>
         </is>
       </c>
       <c r="B82" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I see and edit only my own organization.</t>
+          <t>As an Admin, I want a participant's service record.</t>
         </is>
       </c>
       <c r="C82" s="22" t="inlineStr">
         <is>
-          <t>Open Organizations.</t>
+          <t>Users → Service record for a participant in your org.</t>
         </is>
       </c>
       <c r="D82" s="22" t="inlineStr">
         <is>
-          <t>Only your org shows; you can edit its settings.</t>
+          <t>Record opens.</t>
         </is>
       </c>
       <c r="E82" s="23" t="n"/>
@@ -11136,22 +11436,22 @@
     <row r="83" ht="42" customHeight="1">
       <c r="A83" s="21" t="inlineStr">
         <is>
-          <t>AD12</t>
+          <t>AD8</t>
         </is>
       </c>
       <c r="B83" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I want to generate/rotate my org's join code.</t>
+          <t>As an Admin, I want to edit/delete my org's users.</t>
         </is>
       </c>
       <c r="C83" s="22" t="inlineStr">
         <is>
-          <t>Organizations → set/generate a join code → save.</t>
+          <t>Edit a name/phone; delete a test user.</t>
         </is>
       </c>
       <c r="D83" s="22" t="inlineStr">
         <is>
-          <t>Join code saved; usable at sign-up.</t>
+          <t>Changes apply within your org.</t>
         </is>
       </c>
       <c r="E83" s="23" t="n"/>
@@ -11161,22 +11461,22 @@
     <row r="84" ht="42" customHeight="1">
       <c r="A84" s="21" t="inlineStr">
         <is>
-          <t>AD13</t>
+          <t>AD9</t>
         </is>
       </c>
       <c r="B84" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I cannot create organizations.</t>
+          <t>As an Admin, I must NOT act on users outside my org.</t>
         </is>
       </c>
       <c r="C84" s="22" t="inlineStr">
         <is>
-          <t>Look for 'Add organization'.</t>
+          <t>Attempt to reach another org's user (e.g. direct URL).</t>
         </is>
       </c>
       <c r="D84" s="22" t="inlineStr">
         <is>
-          <t>No Add button; creation blocked.</t>
+          <t>Blocked / not visible.</t>
         </is>
       </c>
       <c r="E84" s="23" t="n"/>
@@ -11186,60 +11486,72 @@
     <row r="85" ht="42" customHeight="1">
       <c r="A85" s="21" t="inlineStr">
         <is>
-          <t>AD14</t>
+          <t>AD10</t>
         </is>
       </c>
       <c r="B85" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I cannot change the recycling cans total.</t>
+          <t>As an Admin, I cannot grant Admin access or manage admins.</t>
         </is>
       </c>
       <c r="C85" s="22" t="inlineStr">
         <is>
-          <t>Look for the cans/bin admin control.</t>
+          <t>Look for the 'grant Admin access' action.</t>
         </is>
       </c>
       <c r="D85" s="22" t="inlineStr">
         <is>
-          <t>Not available (Super Admin only).</t>
+          <t>No such button; attempts are blocked server-side.</t>
         </is>
       </c>
       <c r="E85" s="23" t="n"/>
       <c r="F85" s="22" t="n"/>
       <c r="G85" s="23" t="n"/>
     </row>
-    <row r="86" ht="20" customHeight="1">
-      <c r="A86" s="19" t="inlineStr">
-        <is>
-          <t>Super Admin (global)</t>
-        </is>
-      </c>
-      <c r="B86" s="20" t="n"/>
-      <c r="C86" s="20" t="n"/>
-      <c r="D86" s="20" t="n"/>
-      <c r="E86" s="20" t="n"/>
-      <c r="F86" s="20" t="n"/>
-      <c r="G86" s="20" t="n"/>
+    <row r="86" ht="42" customHeight="1">
+      <c r="A86" s="21" t="inlineStr">
+        <is>
+          <t>AD11</t>
+        </is>
+      </c>
+      <c r="B86" s="22" t="inlineStr">
+        <is>
+          <t>As an Admin, I see and edit only my own organization.</t>
+        </is>
+      </c>
+      <c r="C86" s="22" t="inlineStr">
+        <is>
+          <t>Open Organizations.</t>
+        </is>
+      </c>
+      <c r="D86" s="22" t="inlineStr">
+        <is>
+          <t>Only your org shows; you can edit its settings.</t>
+        </is>
+      </c>
+      <c r="E86" s="23" t="n"/>
+      <c r="F86" s="22" t="n"/>
+      <c r="G86" s="23" t="n"/>
     </row>
     <row r="87" ht="42" customHeight="1">
       <c r="A87" s="21" t="inlineStr">
         <is>
-          <t>SA1</t>
+          <t>AD12</t>
         </is>
       </c>
       <c r="B87" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want the correct menu tabs.</t>
+          <t>As an Admin, I want to generate/rotate my org's join code.</t>
         </is>
       </c>
       <c r="C87" s="22" t="inlineStr">
         <is>
-          <t>Look at the left menu.</t>
+          <t>Organizations → set/generate a join code → save.</t>
         </is>
       </c>
       <c r="D87" s="22" t="inlineStr">
         <is>
-          <t>Dashboard, Reports, Users, Events, Organizations (Help in footer).</t>
+          <t>Join code saved; usable at sign-up.</t>
         </is>
       </c>
       <c r="E87" s="23" t="n"/>
@@ -11249,22 +11561,22 @@
     <row r="88" ht="42" customHeight="1">
       <c r="A88" s="21" t="inlineStr">
         <is>
-          <t>SA2</t>
+          <t>AD13</t>
         </is>
       </c>
       <c r="B88" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I can do everything an Admin can, across all orgs.</t>
+          <t>As an Admin, I cannot create organizations.</t>
         </is>
       </c>
       <c r="C88" s="22" t="inlineStr">
         <is>
-          <t>Spot-check user + org actions on more than one org.</t>
+          <t>Look for 'Add organization'.</t>
         </is>
       </c>
       <c r="D88" s="22" t="inlineStr">
         <is>
-          <t>All allowed regardless of org.</t>
+          <t>No Add button; creation blocked.</t>
         </is>
       </c>
       <c r="E88" s="23" t="n"/>
@@ -11274,72 +11586,60 @@
     <row r="89" ht="42" customHeight="1">
       <c r="A89" s="21" t="inlineStr">
         <is>
-          <t>SA3</t>
+          <t>AD14</t>
         </is>
       </c>
       <c r="B89" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to create users incl. Supervisor and Super Admin.</t>
+          <t>As an Admin, I cannot change the recycling cans total.</t>
         </is>
       </c>
       <c r="C89" s="22" t="inlineStr">
         <is>
-          <t>Users → Add user → each role.</t>
+          <t>Look for the cans/bin admin control.</t>
         </is>
       </c>
       <c r="D89" s="22" t="inlineStr">
         <is>
-          <t>Participant/Supervisor/Super Admin options available; account created + invite email.</t>
+          <t>Not available (Super Admin only).</t>
         </is>
       </c>
       <c r="E89" s="23" t="n"/>
       <c r="F89" s="22" t="n"/>
       <c r="G89" s="23" t="n"/>
     </row>
-    <row r="90" ht="42" customHeight="1">
-      <c r="A90" s="21" t="inlineStr">
-        <is>
-          <t>SA4</t>
-        </is>
-      </c>
-      <c r="B90" s="22" t="inlineStr">
-        <is>
-          <t>As a Super Admin, I want to grant/revoke Admin access.</t>
-        </is>
-      </c>
-      <c r="C90" s="22" t="inlineStr">
-        <is>
-          <t>Open a user → grant Admin access → check org(s) → save; then uncheck all → save.</t>
-        </is>
-      </c>
-      <c r="D90" s="22" t="inlineStr">
-        <is>
-          <t>Checking orgs makes an Admin; unchecking all reverts to participant.</t>
-        </is>
-      </c>
-      <c r="E90" s="23" t="n"/>
-      <c r="F90" s="22" t="n"/>
-      <c r="G90" s="23" t="n"/>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="19" t="inlineStr">
+        <is>
+          <t>Super Admin (global)</t>
+        </is>
+      </c>
+      <c r="B90" s="20" t="n"/>
+      <c r="C90" s="20" t="n"/>
+      <c r="D90" s="20" t="n"/>
+      <c r="E90" s="20" t="n"/>
+      <c r="F90" s="20" t="n"/>
+      <c r="G90" s="20" t="n"/>
     </row>
     <row r="91" ht="42" customHeight="1">
       <c r="A91" s="21" t="inlineStr">
         <is>
-          <t>SA5</t>
+          <t>SA1</t>
         </is>
       </c>
       <c r="B91" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to create organizations + join codes.</t>
+          <t>As a Super Admin, I want the correct menu tabs.</t>
         </is>
       </c>
       <c r="C91" s="22" t="inlineStr">
         <is>
-          <t>Organizations → Add organization → set details + join code.</t>
+          <t>Look at the left menu.</t>
         </is>
       </c>
       <c r="D91" s="22" t="inlineStr">
         <is>
-          <t>Org created with its join code.</t>
+          <t>Dashboard, Reports, Users, Events, Organizations (Help in footer).</t>
         </is>
       </c>
       <c r="E91" s="23" t="n"/>
@@ -11349,22 +11649,22 @@
     <row r="92" ht="42" customHeight="1">
       <c r="A92" s="21" t="inlineStr">
         <is>
-          <t>SA6</t>
+          <t>SA2</t>
         </is>
       </c>
       <c r="B92" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to find users by type.</t>
+          <t>As a Super Admin, I can do everything an Admin can, across all orgs.</t>
         </is>
       </c>
       <c r="C92" s="22" t="inlineStr">
         <is>
-          <t>Users → role filter pills + search.</t>
+          <t>Spot-check user + org actions on more than one org.</t>
         </is>
       </c>
       <c r="D92" s="22" t="inlineStr">
         <is>
-          <t>Filter by role with counts; search by name/email across all orgs.</t>
+          <t>All allowed regardless of org.</t>
         </is>
       </c>
       <c r="E92" s="23" t="n"/>
@@ -11374,22 +11674,22 @@
     <row r="93" ht="42" customHeight="1">
       <c r="A93" s="21" t="inlineStr">
         <is>
-          <t>SA7</t>
+          <t>SA3</t>
         </is>
       </c>
       <c r="B93" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to search events.</t>
+          <t>As a Super Admin, I want to create users incl. Supervisor and Super Admin.</t>
         </is>
       </c>
       <c r="C93" s="22" t="inlineStr">
         <is>
-          <t>Events → search + date range; check supervisor/org per card.</t>
+          <t>Users → Add user → each role.</t>
         </is>
       </c>
       <c r="D93" s="22" t="inlineStr">
         <is>
-          <t>Filters work; each event shows supervisor and organization.</t>
+          <t>Participant/Supervisor/Super Admin options available; account created + invite email.</t>
         </is>
       </c>
       <c r="E93" s="23" t="n"/>
@@ -11399,22 +11699,22 @@
     <row r="94" ht="42" customHeight="1">
       <c r="A94" s="21" t="inlineStr">
         <is>
-          <t>SA8</t>
+          <t>SA4</t>
         </is>
       </c>
       <c r="B94" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want clear event-visibility labels.</t>
+          <t>As a Super Admin, I want to grant/revoke Admin access.</t>
         </is>
       </c>
       <c r="C94" s="22" t="inlineStr">
         <is>
-          <t>New Event → 'Who can see this'.</t>
+          <t>Open a user → grant Admin access → check org(s) → save; then uncheck all → save.</t>
         </is>
       </c>
       <c r="D94" s="22" t="inlineStr">
         <is>
-          <t>'Open to all (community)' and 'Only &lt;org&gt; students' with helper text.</t>
+          <t>Checking orgs makes an Admin; unchecking all reverts to participant.</t>
         </is>
       </c>
       <c r="E94" s="23" t="n"/>
@@ -11424,22 +11724,22 @@
     <row r="95" ht="42" customHeight="1">
       <c r="A95" s="21" t="inlineStr">
         <is>
-          <t>SA9</t>
+          <t>SA5</t>
         </is>
       </c>
       <c r="B95" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want program-wide reports.</t>
+          <t>As a Super Admin, I want to create organizations + join codes.</t>
         </is>
       </c>
       <c r="C95" s="22" t="inlineStr">
         <is>
-          <t>Open Reports / Dashboard.</t>
+          <t>Organizations → Add organization → set details + join code.</t>
         </is>
       </c>
       <c r="D95" s="22" t="inlineStr">
         <is>
-          <t>Totals and charts across the whole program.</t>
+          <t>Org created with its join code.</t>
         </is>
       </c>
       <c r="E95" s="23" t="n"/>
@@ -11449,22 +11749,22 @@
     <row r="96" ht="42" customHeight="1">
       <c r="A96" s="21" t="inlineStr">
         <is>
-          <t>SA10</t>
+          <t>SA6</t>
         </is>
       </c>
       <c r="B96" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to verify email works.</t>
+          <t>As a Super Admin, I want to find users by type.</t>
         </is>
       </c>
       <c r="C96" s="22" t="inlineStr">
         <is>
-          <t>Dashboard → Send test email.</t>
+          <t>Users → role filter pills + search.</t>
         </is>
       </c>
       <c r="D96" s="22" t="inlineStr">
         <is>
-          <t>Result shown (success or the exact failure reason).</t>
+          <t>Filter by role with counts; search by name/email across all orgs.</t>
         </is>
       </c>
       <c r="E96" s="23" t="n"/>
@@ -11474,22 +11774,22 @@
     <row r="97" ht="42" customHeight="1">
       <c r="A97" s="21" t="inlineStr">
         <is>
-          <t>SA11</t>
+          <t>SA7</t>
         </is>
       </c>
       <c r="B97" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to update the recycling cans total.</t>
+          <t>As a Super Admin, I want to search events.</t>
         </is>
       </c>
       <c r="C97" s="22" t="inlineStr">
         <is>
-          <t>Use the cans/bin admin control.</t>
+          <t>Events → search + date range; check supervisor/org per card.</t>
         </is>
       </c>
       <c r="D97" s="22" t="inlineStr">
         <is>
-          <t>Total updates; the ribbon reflects it.</t>
+          <t>Filters work; each event shows supervisor and organization.</t>
         </is>
       </c>
       <c r="E97" s="23" t="n"/>
@@ -11499,60 +11799,72 @@
     <row r="98" ht="42" customHeight="1">
       <c r="A98" s="21" t="inlineStr">
         <is>
-          <t>SA12</t>
+          <t>SA8</t>
         </is>
       </c>
       <c r="B98" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want hours + records for any user.</t>
+          <t>As a Super Admin, I want clear event-visibility labels.</t>
         </is>
       </c>
       <c r="C98" s="22" t="inlineStr">
         <is>
-          <t>Add manual hours / open service record for any participant.</t>
+          <t>New Event → 'Who can see this'.</t>
         </is>
       </c>
       <c r="D98" s="22" t="inlineStr">
         <is>
-          <t>Works for any org.</t>
+          <t>'Open to all (community)' and 'Only &lt;org&gt; students' with helper text.</t>
         </is>
       </c>
       <c r="E98" s="23" t="n"/>
       <c r="F98" s="22" t="n"/>
       <c r="G98" s="23" t="n"/>
     </row>
-    <row r="99" ht="20" customHeight="1">
-      <c r="A99" s="19" t="inlineStr">
-        <is>
-          <t>Cross-cutting</t>
-        </is>
-      </c>
-      <c r="B99" s="20" t="n"/>
-      <c r="C99" s="20" t="n"/>
-      <c r="D99" s="20" t="n"/>
-      <c r="E99" s="20" t="n"/>
-      <c r="F99" s="20" t="n"/>
-      <c r="G99" s="20" t="n"/>
+    <row r="99" ht="42" customHeight="1">
+      <c r="A99" s="21" t="inlineStr">
+        <is>
+          <t>SA9</t>
+        </is>
+      </c>
+      <c r="B99" s="22" t="inlineStr">
+        <is>
+          <t>As a Super Admin, I want program-wide reports.</t>
+        </is>
+      </c>
+      <c r="C99" s="22" t="inlineStr">
+        <is>
+          <t>Open Reports / Dashboard.</t>
+        </is>
+      </c>
+      <c r="D99" s="22" t="inlineStr">
+        <is>
+          <t>Totals and charts across the whole program.</t>
+        </is>
+      </c>
+      <c r="E99" s="23" t="n"/>
+      <c r="F99" s="22" t="n"/>
+      <c r="G99" s="23" t="n"/>
     </row>
     <row r="100" ht="42" customHeight="1">
       <c r="A100" s="21" t="inlineStr">
         <is>
-          <t>X1</t>
+          <t>SA10</t>
         </is>
       </c>
       <c r="B100" s="22" t="inlineStr">
         <is>
-          <t>As a phone user, I want a usable mobile layout.</t>
+          <t>As a Super Admin, I want to verify email works.</t>
         </is>
       </c>
       <c r="C100" s="22" t="inlineStr">
         <is>
-          <t>Open at phone width; use the menu drawer.</t>
+          <t>Dashboard → Send test email.</t>
         </is>
       </c>
       <c r="D100" s="22" t="inlineStr">
         <is>
-          <t>Layout adapts; drawer opens/closes; no horizontal scroll.</t>
+          <t>Result shown (success or the exact failure reason).</t>
         </is>
       </c>
       <c r="E100" s="23" t="n"/>
@@ -11562,39 +11874,127 @@
     <row r="101" ht="42" customHeight="1">
       <c r="A101" s="21" t="inlineStr">
         <is>
-          <t>X2</t>
+          <t>SA11</t>
         </is>
       </c>
       <c r="B101" s="22" t="inlineStr">
         <is>
-          <t>As a visitor, I want the recycling ribbon on the login page.</t>
+          <t>As a Super Admin, I want to update the recycling cans total.</t>
         </is>
       </c>
       <c r="C101" s="22" t="inlineStr">
         <is>
-          <t>Open login signed out.</t>
+          <t>Use the cans/bin admin control.</t>
         </is>
       </c>
       <c r="D101" s="22" t="inlineStr">
         <is>
-          <t>Green ribbon shows on login.</t>
+          <t>Total updates; the ribbon reflects it.</t>
         </is>
       </c>
       <c r="E101" s="23" t="n"/>
       <c r="F101" s="22" t="n"/>
       <c r="G101" s="23" t="n"/>
     </row>
+    <row r="102" ht="42" customHeight="1">
+      <c r="A102" s="21" t="inlineStr">
+        <is>
+          <t>SA12</t>
+        </is>
+      </c>
+      <c r="B102" s="22" t="inlineStr">
+        <is>
+          <t>As a Super Admin, I want hours + records for any user.</t>
+        </is>
+      </c>
+      <c r="C102" s="22" t="inlineStr">
+        <is>
+          <t>Add manual hours / open service record for any participant.</t>
+        </is>
+      </c>
+      <c r="D102" s="22" t="inlineStr">
+        <is>
+          <t>Works for any org.</t>
+        </is>
+      </c>
+      <c r="E102" s="23" t="n"/>
+      <c r="F102" s="22" t="n"/>
+      <c r="G102" s="23" t="n"/>
+    </row>
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="19" t="inlineStr">
+        <is>
+          <t>Cross-cutting</t>
+        </is>
+      </c>
+      <c r="B103" s="20" t="n"/>
+      <c r="C103" s="20" t="n"/>
+      <c r="D103" s="20" t="n"/>
+      <c r="E103" s="20" t="n"/>
+      <c r="F103" s="20" t="n"/>
+      <c r="G103" s="20" t="n"/>
+    </row>
+    <row r="104" ht="42" customHeight="1">
+      <c r="A104" s="21" t="inlineStr">
+        <is>
+          <t>X1</t>
+        </is>
+      </c>
+      <c r="B104" s="22" t="inlineStr">
+        <is>
+          <t>As a phone user, I want a usable mobile layout.</t>
+        </is>
+      </c>
+      <c r="C104" s="22" t="inlineStr">
+        <is>
+          <t>Open at phone width; use the menu drawer.</t>
+        </is>
+      </c>
+      <c r="D104" s="22" t="inlineStr">
+        <is>
+          <t>Layout adapts; drawer opens/closes; no horizontal scroll.</t>
+        </is>
+      </c>
+      <c r="E104" s="23" t="n"/>
+      <c r="F104" s="22" t="n"/>
+      <c r="G104" s="23" t="n"/>
+    </row>
+    <row r="105" ht="42" customHeight="1">
+      <c r="A105" s="21" t="inlineStr">
+        <is>
+          <t>X2</t>
+        </is>
+      </c>
+      <c r="B105" s="22" t="inlineStr">
+        <is>
+          <t>As a visitor, I want the recycling ribbon on the login page.</t>
+        </is>
+      </c>
+      <c r="C105" s="22" t="inlineStr">
+        <is>
+          <t>Open login signed out.</t>
+        </is>
+      </c>
+      <c r="D105" s="22" t="inlineStr">
+        <is>
+          <t>Green ribbon shows on login.</t>
+        </is>
+      </c>
+      <c r="E105" s="23" t="n"/>
+      <c r="F105" s="22" t="n"/>
+      <c r="G105" s="23" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A99:G99"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A55:G55"/>
     <mergeCell ref="A35:G35"/>
-    <mergeCell ref="A86:G86"/>
-    <mergeCell ref="A71:G71"/>
-    <mergeCell ref="A51:G51"/>
+    <mergeCell ref="A90:G90"/>
+    <mergeCell ref="A49:G49"/>
     <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="A103:G103"/>
+    <mergeCell ref="A75:G75"/>
   </mergeCells>
   <conditionalFormatting sqref="E4:E9">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
@@ -11618,7 +12018,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E36:E44">
+  <conditionalFormatting sqref="E36:E48">
     <cfRule type="cellIs" priority="7" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -11629,7 +12029,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E46:E50">
+  <conditionalFormatting sqref="E50:E54">
     <cfRule type="cellIs" priority="10" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -11640,7 +12040,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E52:E70">
+  <conditionalFormatting sqref="E56:E74">
     <cfRule type="cellIs" priority="13" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -11651,7 +12051,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E72:E85">
+  <conditionalFormatting sqref="E76:E89">
     <cfRule type="cellIs" priority="16" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -11662,7 +12062,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E87:E98">
+  <conditionalFormatting sqref="E91:E102">
     <cfRule type="cellIs" priority="19" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -11673,7 +12073,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E100:E101">
+  <conditionalFormatting sqref="E104:E105">
     <cfRule type="cellIs" priority="22" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -11685,7 +12085,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E4:E9 E11:E34 E36:E44 E46:E50 E52:E70 E72:E85 E87:E98 E100:E101" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E4:E9 E11:E34 E36:E48 E50:E54 E56:E74 E76:E89 E91:E102 E104:E105" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pass,Fail,Blocked,Not tested,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -11699,7 +12099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:G105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -12775,38 +13175,50 @@
       <c r="F44" s="22" t="n"/>
       <c r="G44" s="23" t="n"/>
     </row>
-    <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="19" t="inlineStr">
-        <is>
-          <t>Parent — viewer (grades 6–12 student)</t>
-        </is>
-      </c>
-      <c r="B45" s="20" t="n"/>
-      <c r="C45" s="20" t="n"/>
-      <c r="D45" s="20" t="n"/>
-      <c r="E45" s="20" t="n"/>
-      <c r="F45" s="20" t="n"/>
-      <c r="G45" s="20" t="n"/>
+    <row r="45" ht="42" customHeight="1">
+      <c r="A45" s="21" t="inlineStr">
+        <is>
+          <t>PE10</t>
+        </is>
+      </c>
+      <c r="B45" s="22" t="inlineStr">
+        <is>
+          <t>As a parent, I want to submit my child's hours after an event (child has no login).</t>
+        </is>
+      </c>
+      <c r="C45" s="22" t="inlineStr">
+        <is>
+          <t>Dashboard → the child's 'Submit hours (past events)' → enter hours → Submit.</t>
+        </is>
+      </c>
+      <c r="D45" s="22" t="inlineStr">
+        <is>
+          <t>Hours go to the supervisor for approval; status shows 'Waiting for review'.</t>
+        </is>
+      </c>
+      <c r="E45" s="23" t="n"/>
+      <c r="F45" s="22" t="n"/>
+      <c r="G45" s="23" t="n"/>
     </row>
     <row r="46" ht="42" customHeight="1">
       <c r="A46" s="21" t="inlineStr">
         <is>
-          <t>PV1</t>
+          <t>PE11</t>
         </is>
       </c>
       <c r="B46" s="22" t="inlineStr">
         <is>
-          <t>As a parent of a 6–12 student, I want to register for view-only access.</t>
+          <t>As a parent, I want to resubmit my child's rejected hours.</t>
         </is>
       </c>
       <c r="C46" s="22" t="inlineStr">
         <is>
-          <t>Create account → parent of a 6–12 student.</t>
+          <t>On a rejected past event, enter corrected hours → Resubmit.</t>
         </is>
       </c>
       <c r="D46" s="22" t="inlineStr">
         <is>
-          <t>Account created; no invite required to register.</t>
+          <t>Returns to 'Waiting for review'.</t>
         </is>
       </c>
       <c r="E46" s="23" t="n"/>
@@ -12816,22 +13228,22 @@
     <row r="47" ht="42" customHeight="1">
       <c r="A47" s="21" t="inlineStr">
         <is>
-          <t>PV2</t>
+          <t>PE12</t>
         </is>
       </c>
       <c r="B47" s="22" t="inlineStr">
         <is>
-          <t>As a viewer parent, my student links automatically by email.</t>
+          <t>As a parent, I want to see each past event's hours status for my child.</t>
         </is>
       </c>
       <c r="C47" s="22" t="inlineStr">
         <is>
-          <t>Have a student enter this exact email as their parent email (before or after you register).</t>
+          <t>Look at the child's past events list.</t>
         </is>
       </c>
       <c r="D47" s="22" t="inlineStr">
         <is>
-          <t>The student appears on your dashboard automatically; empty until then.</t>
+          <t>Each shows Approved / Waiting / Rejected as appropriate.</t>
         </is>
       </c>
       <c r="E47" s="23" t="n"/>
@@ -12841,110 +13253,110 @@
     <row r="48" ht="42" customHeight="1">
       <c r="A48" s="21" t="inlineStr">
         <is>
-          <t>PV3</t>
+          <t>PE13</t>
         </is>
       </c>
       <c r="B48" s="22" t="inlineStr">
         <is>
-          <t>As a viewer parent, I want to see my student's schedule/progress.</t>
+          <t>As a parent, all core participant actions are available to me for my child.</t>
         </is>
       </c>
       <c r="C48" s="22" t="inlineStr">
         <is>
-          <t>Open the dashboard.</t>
+          <t>Confirm: browse, sign up, withdraw, add-to-calendar, submit hours, view progress toward medals.</t>
         </is>
       </c>
       <c r="D48" s="22" t="inlineStr">
         <is>
-          <t>View-only schedule and progress.</t>
+          <t>All participant-style actions work on the child's behalf (the child never logs in).</t>
         </is>
       </c>
       <c r="E48" s="23" t="n"/>
       <c r="F48" s="22" t="n"/>
       <c r="G48" s="23" t="n"/>
     </row>
-    <row r="49" ht="42" customHeight="1">
-      <c r="A49" s="21" t="inlineStr">
-        <is>
-          <t>PV4</t>
-        </is>
-      </c>
-      <c r="B49" s="22" t="inlineStr">
-        <is>
-          <t>As a viewer parent, I do NOT sign the student up.</t>
-        </is>
-      </c>
-      <c r="C49" s="22" t="inlineStr">
-        <is>
-          <t>Look for a sign-up action.</t>
-        </is>
-      </c>
-      <c r="D49" s="22" t="inlineStr">
-        <is>
-          <t>No sign-up on the student's behalf — the student self-serves.</t>
-        </is>
-      </c>
-      <c r="E49" s="23" t="n"/>
-      <c r="F49" s="22" t="n"/>
-      <c r="G49" s="23" t="n"/>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="19" t="inlineStr">
+        <is>
+          <t>Parent — viewer (grades 6–12 student)</t>
+        </is>
+      </c>
+      <c r="B49" s="20" t="n"/>
+      <c r="C49" s="20" t="n"/>
+      <c r="D49" s="20" t="n"/>
+      <c r="E49" s="20" t="n"/>
+      <c r="F49" s="20" t="n"/>
+      <c r="G49" s="20" t="n"/>
     </row>
     <row r="50" ht="42" customHeight="1">
       <c r="A50" s="21" t="inlineStr">
         <is>
-          <t>PV5</t>
+          <t>PV1</t>
         </is>
       </c>
       <c r="B50" s="22" t="inlineStr">
         <is>
-          <t>As a viewer parent, I want to invite a co-guardian.</t>
+          <t>As a parent of a 6–12 student, I want to register for view-only access.</t>
         </is>
       </c>
       <c r="C50" s="22" t="inlineStr">
         <is>
-          <t>Invite a co-guardian by email.</t>
+          <t>Create account → parent of a 6–12 student.</t>
         </is>
       </c>
       <c r="D50" s="22" t="inlineStr">
         <is>
-          <t>Invite email sent; shared access on registration.</t>
+          <t>Account created; no invite required to register.</t>
         </is>
       </c>
       <c r="E50" s="23" t="n"/>
       <c r="F50" s="22" t="n"/>
       <c r="G50" s="23" t="n"/>
     </row>
-    <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="19" t="inlineStr">
-        <is>
-          <t>Supervisor (created by an Admin)</t>
-        </is>
-      </c>
-      <c r="B51" s="20" t="n"/>
-      <c r="C51" s="20" t="n"/>
-      <c r="D51" s="20" t="n"/>
-      <c r="E51" s="20" t="n"/>
-      <c r="F51" s="20" t="n"/>
-      <c r="G51" s="20" t="n"/>
+    <row r="51" ht="42" customHeight="1">
+      <c r="A51" s="21" t="inlineStr">
+        <is>
+          <t>PV2</t>
+        </is>
+      </c>
+      <c r="B51" s="22" t="inlineStr">
+        <is>
+          <t>As a viewer parent, my student links automatically by email.</t>
+        </is>
+      </c>
+      <c r="C51" s="22" t="inlineStr">
+        <is>
+          <t>Have a student enter this exact email as their parent email (before or after you register).</t>
+        </is>
+      </c>
+      <c r="D51" s="22" t="inlineStr">
+        <is>
+          <t>The student appears on your dashboard automatically; empty until then.</t>
+        </is>
+      </c>
+      <c r="E51" s="23" t="n"/>
+      <c r="F51" s="22" t="n"/>
+      <c r="G51" s="23" t="n"/>
     </row>
     <row r="52" ht="42" customHeight="1">
       <c r="A52" s="21" t="inlineStr">
         <is>
-          <t>SV1</t>
+          <t>PV3</t>
         </is>
       </c>
       <c r="B52" s="22" t="inlineStr">
         <is>
-          <t>As the program, a supervisor cannot self-register.</t>
+          <t>As a viewer parent, I want to see my student's schedule/progress.</t>
         </is>
       </c>
       <c r="C52" s="22" t="inlineStr">
         <is>
-          <t>Review the sign-up options.</t>
+          <t>Open the dashboard.</t>
         </is>
       </c>
       <c r="D52" s="22" t="inlineStr">
         <is>
-          <t>No supervisor option exists on registration.</t>
+          <t>View-only schedule and progress.</t>
         </is>
       </c>
       <c r="E52" s="23" t="n"/>
@@ -12954,22 +13366,22 @@
     <row r="53" ht="42" customHeight="1">
       <c r="A53" s="21" t="inlineStr">
         <is>
-          <t>SV2</t>
+          <t>PV4</t>
         </is>
       </c>
       <c r="B53" s="22" t="inlineStr">
         <is>
-          <t>As a new supervisor, I get an invite to set my password.</t>
+          <t>As a viewer parent, I do NOT sign the student up.</t>
         </is>
       </c>
       <c r="C53" s="22" t="inlineStr">
         <is>
-          <t>Have an Admin create your account; open the invite email; set password; sign in.</t>
+          <t>Look for a sign-up action.</t>
         </is>
       </c>
       <c r="D53" s="22" t="inlineStr">
         <is>
-          <t>Invite email arrives with a working set-password link; you can sign in.</t>
+          <t>No sign-up on the student's behalf — the student self-serves.</t>
         </is>
       </c>
       <c r="E53" s="23" t="n"/>
@@ -12979,72 +13391,60 @@
     <row r="54" ht="42" customHeight="1">
       <c r="A54" s="21" t="inlineStr">
         <is>
-          <t>SV3</t>
+          <t>PV5</t>
         </is>
       </c>
       <c r="B54" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want the correct 7 left-menu tabs.</t>
+          <t>As a viewer parent, I want to invite a co-guardian.</t>
         </is>
       </c>
       <c r="C54" s="22" t="inlineStr">
         <is>
-          <t>Look at the left menu.</t>
+          <t>Invite a co-guardian by email.</t>
         </is>
       </c>
       <c r="D54" s="22" t="inlineStr">
         <is>
-          <t>Dashboard, Pending Reviews, Reviewed History, My Events, All Opportunities, My Hours, Help.</t>
+          <t>Invite email sent; shared access on registration.</t>
         </is>
       </c>
       <c r="E54" s="23" t="n"/>
       <c r="F54" s="22" t="n"/>
       <c r="G54" s="23" t="n"/>
     </row>
-    <row r="55" ht="42" customHeight="1">
-      <c r="A55" s="21" t="inlineStr">
-        <is>
-          <t>SV4</t>
-        </is>
-      </c>
-      <c r="B55" s="22" t="inlineStr">
-        <is>
-          <t>As a supervisor, I want a dashboard.</t>
-        </is>
-      </c>
-      <c r="C55" s="22" t="inlineStr">
-        <is>
-          <t>Open the dashboard.</t>
-        </is>
-      </c>
-      <c r="D55" s="22" t="inlineStr">
-        <is>
-          <t>Review queue, approved/rejected counts, registrations, hours, upcoming events + Roster links.</t>
-        </is>
-      </c>
-      <c r="E55" s="23" t="n"/>
-      <c r="F55" s="22" t="n"/>
-      <c r="G55" s="23" t="n"/>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="19" t="inlineStr">
+        <is>
+          <t>Supervisor (created by an Admin)</t>
+        </is>
+      </c>
+      <c r="B55" s="20" t="n"/>
+      <c r="C55" s="20" t="n"/>
+      <c r="D55" s="20" t="n"/>
+      <c r="E55" s="20" t="n"/>
+      <c r="F55" s="20" t="n"/>
+      <c r="G55" s="20" t="n"/>
     </row>
     <row r="56" ht="42" customHeight="1">
       <c r="A56" s="21" t="inlineStr">
         <is>
-          <t>SV5</t>
+          <t>SV1</t>
         </is>
       </c>
       <c r="B56" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to approve hours.</t>
+          <t>As the program, a supervisor cannot self-register.</t>
         </is>
       </c>
       <c r="C56" s="22" t="inlineStr">
         <is>
-          <t>Pending Reviews → open → Approve.</t>
+          <t>Review the sign-up options.</t>
         </is>
       </c>
       <c r="D56" s="22" t="inlineStr">
         <is>
-          <t>Approved; moves to Reviewed History; participant total updates; email sent.</t>
+          <t>No supervisor option exists on registration.</t>
         </is>
       </c>
       <c r="E56" s="23" t="n"/>
@@ -13054,22 +13454,22 @@
     <row r="57" ht="42" customHeight="1">
       <c r="A57" s="21" t="inlineStr">
         <is>
-          <t>SV6</t>
+          <t>SV2</t>
         </is>
       </c>
       <c r="B57" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to reject hours with a reason.</t>
+          <t>As a new supervisor, I get an invite to set my password.</t>
         </is>
       </c>
       <c r="C57" s="22" t="inlineStr">
         <is>
-          <t>Reject without a reason, then with one.</t>
+          <t>Have an Admin create your account; open the invite email; set password; sign in.</t>
         </is>
       </c>
       <c r="D57" s="22" t="inlineStr">
         <is>
-          <t>Blocked until a reason is given; then rejected and the participant notified.</t>
+          <t>Invite email arrives with a working set-password link; you can sign in.</t>
         </is>
       </c>
       <c r="E57" s="23" t="n"/>
@@ -13079,22 +13479,22 @@
     <row r="58" ht="42" customHeight="1">
       <c r="A58" s="21" t="inlineStr">
         <is>
-          <t>SV7</t>
+          <t>SV3</t>
         </is>
       </c>
       <c r="B58" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to review external submissions.</t>
+          <t>As a supervisor, I want the correct 7 left-menu tabs.</t>
         </is>
       </c>
       <c r="C58" s="22" t="inlineStr">
         <is>
-          <t>Pending Reviews → external tab → approve/reject.</t>
+          <t>Look at the left menu.</t>
         </is>
       </c>
       <c r="D58" s="22" t="inlineStr">
         <is>
-          <t>External items reviewable, including any proof.</t>
+          <t>Dashboard, Pending Reviews, Reviewed History, My Events, All Opportunities, My Hours, Help.</t>
         </is>
       </c>
       <c r="E58" s="23" t="n"/>
@@ -13104,22 +13504,22 @@
     <row r="59" ht="42" customHeight="1">
       <c r="A59" s="21" t="inlineStr">
         <is>
-          <t>SV8</t>
+          <t>SV4</t>
         </is>
       </c>
       <c r="B59" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to create an event.</t>
+          <t>As a supervisor, I want a dashboard.</t>
         </is>
       </c>
       <c r="C59" s="22" t="inlineStr">
         <is>
-          <t>New Event → title, description, slot, address, date, times, capacity, grade limits → save.</t>
+          <t>Open the dashboard.</t>
         </is>
       </c>
       <c r="D59" s="22" t="inlineStr">
         <is>
-          <t>Credit auto-calculated from times; event created in My Events.</t>
+          <t>Review queue, approved/rejected counts, registrations, hours, upcoming events + Roster links.</t>
         </is>
       </c>
       <c r="E59" s="23" t="n"/>
@@ -13129,22 +13529,22 @@
     <row r="60" ht="42" customHeight="1">
       <c r="A60" s="21" t="inlineStr">
         <is>
-          <t>SV9</t>
+          <t>SV5</t>
         </is>
       </c>
       <c r="B60" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to edit an event.</t>
+          <t>As a supervisor, I want to approve hours.</t>
         </is>
       </c>
       <c r="C60" s="22" t="inlineStr">
         <is>
-          <t>My Events → edit → save.</t>
+          <t>Pending Reviews → open → Approve.</t>
         </is>
       </c>
       <c r="D60" s="22" t="inlineStr">
         <is>
-          <t>Changes persist and show to participants.</t>
+          <t>Approved; moves to Reviewed History; participant total updates; email sent.</t>
         </is>
       </c>
       <c r="E60" s="23" t="n"/>
@@ -13154,22 +13554,22 @@
     <row r="61" ht="42" customHeight="1">
       <c r="A61" s="21" t="inlineStr">
         <is>
-          <t>SV10</t>
+          <t>SV6</t>
         </is>
       </c>
       <c r="B61" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to delete an event with no approved hours.</t>
+          <t>As a supervisor, I want to reject hours with a reason.</t>
         </is>
       </c>
       <c r="C61" s="22" t="inlineStr">
         <is>
-          <t>Delete such an event → confirm.</t>
+          <t>Reject without a reason, then with one.</t>
         </is>
       </c>
       <c r="D61" s="22" t="inlineStr">
         <is>
-          <t>Event deleted.</t>
+          <t>Blocked until a reason is given; then rejected and the participant notified.</t>
         </is>
       </c>
       <c r="E61" s="23" t="n"/>
@@ -13179,22 +13579,22 @@
     <row r="62" ht="42" customHeight="1">
       <c r="A62" s="21" t="inlineStr">
         <is>
-          <t>SV11</t>
+          <t>SV7</t>
         </is>
       </c>
       <c r="B62" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, deleting an event with approved hours is blocked.</t>
+          <t>As a supervisor, I want to review external submissions.</t>
         </is>
       </c>
       <c r="C62" s="22" t="inlineStr">
         <is>
-          <t>Try to delete an event that has approved hours.</t>
+          <t>Pending Reviews → external tab → approve/reject.</t>
         </is>
       </c>
       <c r="D62" s="22" t="inlineStr">
         <is>
-          <t>Blocked with a message that approved hours must be preserved.</t>
+          <t>External items reviewable, including any proof.</t>
         </is>
       </c>
       <c r="E62" s="23" t="n"/>
@@ -13204,22 +13604,22 @@
     <row r="63" ht="42" customHeight="1">
       <c r="A63" s="21" t="inlineStr">
         <is>
-          <t>SV12</t>
+          <t>SV8</t>
         </is>
       </c>
       <c r="B63" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to see who signed up.</t>
+          <t>As a supervisor, I want to create an event.</t>
         </is>
       </c>
       <c r="C63" s="22" t="inlineStr">
         <is>
-          <t>Open the event Roster.</t>
+          <t>New Event → title, description, slot, address, date, times, capacity, grade limits → save.</t>
         </is>
       </c>
       <c r="D63" s="22" t="inlineStr">
         <is>
-          <t>Registrants listed with grade and status.</t>
+          <t>Credit auto-calculated from times; event created in My Events.</t>
         </is>
       </c>
       <c r="E63" s="23" t="n"/>
@@ -13229,22 +13629,22 @@
     <row r="64" ht="42" customHeight="1">
       <c r="A64" s="21" t="inlineStr">
         <is>
-          <t>SV13</t>
+          <t>SV9</t>
         </is>
       </c>
       <c r="B64" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to check people in / mark no-show.</t>
+          <t>As a supervisor, I want to edit an event.</t>
         </is>
       </c>
       <c r="C64" s="22" t="inlineStr">
         <is>
-          <t>On the roster, Check in and Mark no-show.</t>
+          <t>My Events → edit → save.</t>
         </is>
       </c>
       <c r="D64" s="22" t="inlineStr">
         <is>
-          <t>Status updates and persists.</t>
+          <t>Changes persist and show to participants.</t>
         </is>
       </c>
       <c r="E64" s="23" t="n"/>
@@ -13254,22 +13654,22 @@
     <row r="65" ht="42" customHeight="1">
       <c r="A65" s="21" t="inlineStr">
         <is>
-          <t>SV14</t>
+          <t>SV10</t>
         </is>
       </c>
       <c r="B65" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to message everyone signed up.</t>
+          <t>As a supervisor, I want to delete an event with no approved hours.</t>
         </is>
       </c>
       <c r="C65" s="22" t="inlineStr">
         <is>
-          <t>Roster → Message attendees → subject+message → send (include guardians on).</t>
+          <t>Delete such an event → confirm.</t>
         </is>
       </c>
       <c r="D65" s="22" t="inlineStr">
         <is>
-          <t>Each registrant (and guardians) emailed individually; recipient count shown.</t>
+          <t>Event deleted.</t>
         </is>
       </c>
       <c r="E65" s="23" t="n"/>
@@ -13279,22 +13679,22 @@
     <row r="66" ht="42" customHeight="1">
       <c r="A66" s="21" t="inlineStr">
         <is>
-          <t>SV15</t>
+          <t>SV11</t>
         </is>
       </c>
       <c r="B66" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want a history of what I reviewed.</t>
+          <t>As a supervisor, deleting an event with approved hours is blocked.</t>
         </is>
       </c>
       <c r="C66" s="22" t="inlineStr">
         <is>
-          <t>Open Reviewed History.</t>
+          <t>Try to delete an event that has approved hours.</t>
         </is>
       </c>
       <c r="D66" s="22" t="inlineStr">
         <is>
-          <t>Every approved/rejected item with dates and volunteers.</t>
+          <t>Blocked with a message that approved hours must be preserved.</t>
         </is>
       </c>
       <c r="E66" s="23" t="n"/>
@@ -13304,22 +13704,22 @@
     <row r="67" ht="42" customHeight="1">
       <c r="A67" s="21" t="inlineStr">
         <is>
-          <t>SV16</t>
+          <t>SV12</t>
         </is>
       </c>
       <c r="B67" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to browse all opportunities view-only.</t>
+          <t>As a supervisor, I want to see who signed up.</t>
         </is>
       </c>
       <c r="C67" s="22" t="inlineStr">
         <is>
-          <t>All Opportunities → search / upcoming-past.</t>
+          <t>Open the event Roster.</t>
         </is>
       </c>
       <c r="D67" s="22" t="inlineStr">
         <is>
-          <t>Every event listed read-only; can't edit others' events.</t>
+          <t>Registrants listed with grade and status.</t>
         </is>
       </c>
       <c r="E67" s="23" t="n"/>
@@ -13329,22 +13729,22 @@
     <row r="68" ht="42" customHeight="1">
       <c r="A68" s="21" t="inlineStr">
         <is>
-          <t>SV17</t>
+          <t>SV13</t>
         </is>
       </c>
       <c r="B68" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to log my own adult hours.</t>
+          <t>As a supervisor, I want to check people in / mark no-show.</t>
         </is>
       </c>
       <c r="C68" s="22" t="inlineStr">
         <is>
-          <t>My Hours → log an activity, date, hours → save.</t>
+          <t>On the roster, Check in and Mark no-show.</t>
         </is>
       </c>
       <c r="D68" s="22" t="inlineStr">
         <is>
-          <t>Recorded instantly with a running total; clearly NOT part of the student competition.</t>
+          <t>Status updates and persists.</t>
         </is>
       </c>
       <c r="E68" s="23" t="n"/>
@@ -13354,22 +13754,22 @@
     <row r="69" ht="42" customHeight="1">
       <c r="A69" s="21" t="inlineStr">
         <is>
-          <t>SV18</t>
+          <t>SV14</t>
         </is>
       </c>
       <c r="B69" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to delete an adult-hours entry.</t>
+          <t>As a supervisor, I want to message everyone signed up.</t>
         </is>
       </c>
       <c r="C69" s="22" t="inlineStr">
         <is>
-          <t>My Hours → delete an entry → confirm.</t>
+          <t>Roster → Message attendees → subject+message → send (include guardians on).</t>
         </is>
       </c>
       <c r="D69" s="22" t="inlineStr">
         <is>
-          <t>Removed; total updates.</t>
+          <t>Each registrant (and guardians) emailed individually; recipient count shown.</t>
         </is>
       </c>
       <c r="E69" s="23" t="n"/>
@@ -13379,60 +13779,72 @@
     <row r="70" ht="42" customHeight="1">
       <c r="A70" s="21" t="inlineStr">
         <is>
-          <t>SV19</t>
+          <t>SV15</t>
         </is>
       </c>
       <c r="B70" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I must NOT access user or org management.</t>
+          <t>As a supervisor, I want a history of what I reviewed.</t>
         </is>
       </c>
       <c r="C70" s="22" t="inlineStr">
         <is>
-          <t>Look for Users / Organizations in the menu.</t>
+          <t>Open Reviewed History.</t>
         </is>
       </c>
       <c r="D70" s="22" t="inlineStr">
         <is>
-          <t>Those tabs are absent; direct URLs are blocked.</t>
+          <t>Every approved/rejected item with dates and volunteers.</t>
         </is>
       </c>
       <c r="E70" s="23" t="n"/>
       <c r="F70" s="22" t="n"/>
       <c r="G70" s="23" t="n"/>
     </row>
-    <row r="71" ht="20" customHeight="1">
-      <c r="A71" s="19" t="inlineStr">
-        <is>
-          <t>Admin (org-scoped)</t>
-        </is>
-      </c>
-      <c r="B71" s="20" t="n"/>
-      <c r="C71" s="20" t="n"/>
-      <c r="D71" s="20" t="n"/>
-      <c r="E71" s="20" t="n"/>
-      <c r="F71" s="20" t="n"/>
-      <c r="G71" s="20" t="n"/>
+    <row r="71" ht="42" customHeight="1">
+      <c r="A71" s="21" t="inlineStr">
+        <is>
+          <t>SV16</t>
+        </is>
+      </c>
+      <c r="B71" s="22" t="inlineStr">
+        <is>
+          <t>As a supervisor, I want to browse all opportunities view-only.</t>
+        </is>
+      </c>
+      <c r="C71" s="22" t="inlineStr">
+        <is>
+          <t>All Opportunities → search / upcoming-past.</t>
+        </is>
+      </c>
+      <c r="D71" s="22" t="inlineStr">
+        <is>
+          <t>Every event listed read-only; can't edit others' events.</t>
+        </is>
+      </c>
+      <c r="E71" s="23" t="n"/>
+      <c r="F71" s="22" t="n"/>
+      <c r="G71" s="23" t="n"/>
     </row>
     <row r="72" ht="42" customHeight="1">
       <c r="A72" s="21" t="inlineStr">
         <is>
-          <t>AD1</t>
+          <t>SV17</t>
         </is>
       </c>
       <c r="B72" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I want the correct menu tabs.</t>
+          <t>As a supervisor, I want to log my own adult hours.</t>
         </is>
       </c>
       <c r="C72" s="22" t="inlineStr">
         <is>
-          <t>Look at the left menu.</t>
+          <t>My Hours → log an activity, date, hours → save.</t>
         </is>
       </c>
       <c r="D72" s="22" t="inlineStr">
         <is>
-          <t>Dashboard, Pending Reviews, Reviewed History, My Events, All Opportunities, Users, Organizations, My Hours, Help.</t>
+          <t>Recorded instantly with a running total; clearly NOT part of the student competition.</t>
         </is>
       </c>
       <c r="E72" s="23" t="n"/>
@@ -13442,22 +13854,22 @@
     <row r="73" ht="42" customHeight="1">
       <c r="A73" s="21" t="inlineStr">
         <is>
-          <t>AD2</t>
+          <t>SV18</t>
         </is>
       </c>
       <c r="B73" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I can do everything a supervisor can.</t>
+          <t>As a supervisor, I want to delete an adult-hours entry.</t>
         </is>
       </c>
       <c r="C73" s="22" t="inlineStr">
         <is>
-          <t>Spot-check: approve an item and create an event.</t>
+          <t>My Hours → delete an entry → confirm.</t>
         </is>
       </c>
       <c r="D73" s="22" t="inlineStr">
         <is>
-          <t>Both work.</t>
+          <t>Removed; total updates.</t>
         </is>
       </c>
       <c r="E73" s="23" t="n"/>
@@ -13467,72 +13879,60 @@
     <row r="74" ht="42" customHeight="1">
       <c r="A74" s="21" t="inlineStr">
         <is>
-          <t>AD3</t>
+          <t>SV19</t>
         </is>
       </c>
       <c r="B74" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I only see my org's non-admin users.</t>
+          <t>As a supervisor, I must NOT access user or org management.</t>
         </is>
       </c>
       <c r="C74" s="22" t="inlineStr">
         <is>
-          <t>Open Users.</t>
+          <t>Look for Users / Organizations in the menu.</t>
         </is>
       </c>
       <c r="D74" s="22" t="inlineStr">
         <is>
-          <t>Only participants/parents/supervisors in your org; no admins/super admins; no other orgs.</t>
+          <t>Those tabs are absent; direct URLs are blocked.</t>
         </is>
       </c>
       <c r="E74" s="23" t="n"/>
       <c r="F74" s="22" t="n"/>
       <c r="G74" s="23" t="n"/>
     </row>
-    <row r="75" ht="42" customHeight="1">
-      <c r="A75" s="21" t="inlineStr">
-        <is>
-          <t>AD4</t>
-        </is>
-      </c>
-      <c r="B75" s="22" t="inlineStr">
-        <is>
-          <t>As an Admin, I want to add a supervisor.</t>
-        </is>
-      </c>
-      <c r="C75" s="22" t="inlineStr">
-        <is>
-          <t>Users → Add user → Supervisor → save.</t>
-        </is>
-      </c>
-      <c r="D75" s="22" t="inlineStr">
-        <is>
-          <t>Supervisor created, stamped to your org; invite email sent.</t>
-        </is>
-      </c>
-      <c r="E75" s="23" t="n"/>
-      <c r="F75" s="22" t="n"/>
-      <c r="G75" s="23" t="n"/>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="19" t="inlineStr">
+        <is>
+          <t>Admin (org-scoped)</t>
+        </is>
+      </c>
+      <c r="B75" s="20" t="n"/>
+      <c r="C75" s="20" t="n"/>
+      <c r="D75" s="20" t="n"/>
+      <c r="E75" s="20" t="n"/>
+      <c r="F75" s="20" t="n"/>
+      <c r="G75" s="20" t="n"/>
     </row>
     <row r="76" ht="42" customHeight="1">
       <c r="A76" s="21" t="inlineStr">
         <is>
-          <t>AD5</t>
+          <t>AD1</t>
         </is>
       </c>
       <c r="B76" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I want to create a participant as a fallback.</t>
+          <t>As an Admin, I want the correct menu tabs.</t>
         </is>
       </c>
       <c r="C76" s="22" t="inlineStr">
         <is>
-          <t>Users → Add user → Participant → save.</t>
+          <t>Look at the left menu.</t>
         </is>
       </c>
       <c r="D76" s="22" t="inlineStr">
         <is>
-          <t>Participant created with a set-password invite (no silent password).</t>
+          <t>Dashboard, Pending Reviews, Reviewed History, My Events, All Opportunities, Users, Organizations, My Hours, Help.</t>
         </is>
       </c>
       <c r="E76" s="23" t="n"/>
@@ -13542,22 +13942,22 @@
     <row r="77" ht="42" customHeight="1">
       <c r="A77" s="21" t="inlineStr">
         <is>
-          <t>AD6</t>
+          <t>AD2</t>
         </is>
       </c>
       <c r="B77" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I want to grant participant hours.</t>
+          <t>As an Admin, I can do everything a supervisor can.</t>
         </is>
       </c>
       <c r="C77" s="22" t="inlineStr">
         <is>
-          <t>Open a participant in your org → Add hours.</t>
+          <t>Spot-check: approve an item and create an event.</t>
         </is>
       </c>
       <c r="D77" s="22" t="inlineStr">
         <is>
-          <t>Hours auto-approved; count toward their total/medals.</t>
+          <t>Both work.</t>
         </is>
       </c>
       <c r="E77" s="23" t="n"/>
@@ -13567,22 +13967,22 @@
     <row r="78" ht="42" customHeight="1">
       <c r="A78" s="21" t="inlineStr">
         <is>
-          <t>AD7</t>
+          <t>AD3</t>
         </is>
       </c>
       <c r="B78" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I want a participant's service record.</t>
+          <t>As an Admin, I only see my org's non-admin users.</t>
         </is>
       </c>
       <c r="C78" s="22" t="inlineStr">
         <is>
-          <t>Users → Service record for a participant in your org.</t>
+          <t>Open Users.</t>
         </is>
       </c>
       <c r="D78" s="22" t="inlineStr">
         <is>
-          <t>Record opens.</t>
+          <t>Only participants/parents/supervisors in your org; no admins/super admins; no other orgs.</t>
         </is>
       </c>
       <c r="E78" s="23" t="n"/>
@@ -13592,22 +13992,22 @@
     <row r="79" ht="42" customHeight="1">
       <c r="A79" s="21" t="inlineStr">
         <is>
-          <t>AD8</t>
+          <t>AD4</t>
         </is>
       </c>
       <c r="B79" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I want to edit/delete my org's users.</t>
+          <t>As an Admin, I want to add a supervisor.</t>
         </is>
       </c>
       <c r="C79" s="22" t="inlineStr">
         <is>
-          <t>Edit a name/phone; delete a test user.</t>
+          <t>Users → Add user → Supervisor → save.</t>
         </is>
       </c>
       <c r="D79" s="22" t="inlineStr">
         <is>
-          <t>Changes apply within your org.</t>
+          <t>Supervisor created, stamped to your org; invite email sent.</t>
         </is>
       </c>
       <c r="E79" s="23" t="n"/>
@@ -13617,22 +14017,22 @@
     <row r="80" ht="42" customHeight="1">
       <c r="A80" s="21" t="inlineStr">
         <is>
-          <t>AD9</t>
+          <t>AD5</t>
         </is>
       </c>
       <c r="B80" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I must NOT act on users outside my org.</t>
+          <t>As an Admin, I want to create a participant as a fallback.</t>
         </is>
       </c>
       <c r="C80" s="22" t="inlineStr">
         <is>
-          <t>Attempt to reach another org's user (e.g. direct URL).</t>
+          <t>Users → Add user → Participant → save.</t>
         </is>
       </c>
       <c r="D80" s="22" t="inlineStr">
         <is>
-          <t>Blocked / not visible.</t>
+          <t>Participant created with a set-password invite (no silent password).</t>
         </is>
       </c>
       <c r="E80" s="23" t="n"/>
@@ -13642,22 +14042,22 @@
     <row r="81" ht="42" customHeight="1">
       <c r="A81" s="21" t="inlineStr">
         <is>
-          <t>AD10</t>
+          <t>AD6</t>
         </is>
       </c>
       <c r="B81" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I cannot grant Admin access or manage admins.</t>
+          <t>As an Admin, I want to grant participant hours.</t>
         </is>
       </c>
       <c r="C81" s="22" t="inlineStr">
         <is>
-          <t>Look for the 'grant Admin access' action.</t>
+          <t>Open a participant in your org → Add hours.</t>
         </is>
       </c>
       <c r="D81" s="22" t="inlineStr">
         <is>
-          <t>No such button; attempts are blocked server-side.</t>
+          <t>Hours auto-approved; count toward their total/medals.</t>
         </is>
       </c>
       <c r="E81" s="23" t="n"/>
@@ -13667,22 +14067,22 @@
     <row r="82" ht="42" customHeight="1">
       <c r="A82" s="21" t="inlineStr">
         <is>
-          <t>AD11</t>
+          <t>AD7</t>
         </is>
       </c>
       <c r="B82" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I see and edit only my own organization.</t>
+          <t>As an Admin, I want a participant's service record.</t>
         </is>
       </c>
       <c r="C82" s="22" t="inlineStr">
         <is>
-          <t>Open Organizations.</t>
+          <t>Users → Service record for a participant in your org.</t>
         </is>
       </c>
       <c r="D82" s="22" t="inlineStr">
         <is>
-          <t>Only your org shows; you can edit its settings.</t>
+          <t>Record opens.</t>
         </is>
       </c>
       <c r="E82" s="23" t="n"/>
@@ -13692,22 +14092,22 @@
     <row r="83" ht="42" customHeight="1">
       <c r="A83" s="21" t="inlineStr">
         <is>
-          <t>AD12</t>
+          <t>AD8</t>
         </is>
       </c>
       <c r="B83" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I want to generate/rotate my org's join code.</t>
+          <t>As an Admin, I want to edit/delete my org's users.</t>
         </is>
       </c>
       <c r="C83" s="22" t="inlineStr">
         <is>
-          <t>Organizations → set/generate a join code → save.</t>
+          <t>Edit a name/phone; delete a test user.</t>
         </is>
       </c>
       <c r="D83" s="22" t="inlineStr">
         <is>
-          <t>Join code saved; usable at sign-up.</t>
+          <t>Changes apply within your org.</t>
         </is>
       </c>
       <c r="E83" s="23" t="n"/>
@@ -13717,22 +14117,22 @@
     <row r="84" ht="42" customHeight="1">
       <c r="A84" s="21" t="inlineStr">
         <is>
-          <t>AD13</t>
+          <t>AD9</t>
         </is>
       </c>
       <c r="B84" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I cannot create organizations.</t>
+          <t>As an Admin, I must NOT act on users outside my org.</t>
         </is>
       </c>
       <c r="C84" s="22" t="inlineStr">
         <is>
-          <t>Look for 'Add organization'.</t>
+          <t>Attempt to reach another org's user (e.g. direct URL).</t>
         </is>
       </c>
       <c r="D84" s="22" t="inlineStr">
         <is>
-          <t>No Add button; creation blocked.</t>
+          <t>Blocked / not visible.</t>
         </is>
       </c>
       <c r="E84" s="23" t="n"/>
@@ -13742,60 +14142,72 @@
     <row r="85" ht="42" customHeight="1">
       <c r="A85" s="21" t="inlineStr">
         <is>
-          <t>AD14</t>
+          <t>AD10</t>
         </is>
       </c>
       <c r="B85" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I cannot change the recycling cans total.</t>
+          <t>As an Admin, I cannot grant Admin access or manage admins.</t>
         </is>
       </c>
       <c r="C85" s="22" t="inlineStr">
         <is>
-          <t>Look for the cans/bin admin control.</t>
+          <t>Look for the 'grant Admin access' action.</t>
         </is>
       </c>
       <c r="D85" s="22" t="inlineStr">
         <is>
-          <t>Not available (Super Admin only).</t>
+          <t>No such button; attempts are blocked server-side.</t>
         </is>
       </c>
       <c r="E85" s="23" t="n"/>
       <c r="F85" s="22" t="n"/>
       <c r="G85" s="23" t="n"/>
     </row>
-    <row r="86" ht="20" customHeight="1">
-      <c r="A86" s="19" t="inlineStr">
-        <is>
-          <t>Super Admin (global)</t>
-        </is>
-      </c>
-      <c r="B86" s="20" t="n"/>
-      <c r="C86" s="20" t="n"/>
-      <c r="D86" s="20" t="n"/>
-      <c r="E86" s="20" t="n"/>
-      <c r="F86" s="20" t="n"/>
-      <c r="G86" s="20" t="n"/>
+    <row r="86" ht="42" customHeight="1">
+      <c r="A86" s="21" t="inlineStr">
+        <is>
+          <t>AD11</t>
+        </is>
+      </c>
+      <c r="B86" s="22" t="inlineStr">
+        <is>
+          <t>As an Admin, I see and edit only my own organization.</t>
+        </is>
+      </c>
+      <c r="C86" s="22" t="inlineStr">
+        <is>
+          <t>Open Organizations.</t>
+        </is>
+      </c>
+      <c r="D86" s="22" t="inlineStr">
+        <is>
+          <t>Only your org shows; you can edit its settings.</t>
+        </is>
+      </c>
+      <c r="E86" s="23" t="n"/>
+      <c r="F86" s="22" t="n"/>
+      <c r="G86" s="23" t="n"/>
     </row>
     <row r="87" ht="42" customHeight="1">
       <c r="A87" s="21" t="inlineStr">
         <is>
-          <t>SA1</t>
+          <t>AD12</t>
         </is>
       </c>
       <c r="B87" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want the correct menu tabs.</t>
+          <t>As an Admin, I want to generate/rotate my org's join code.</t>
         </is>
       </c>
       <c r="C87" s="22" t="inlineStr">
         <is>
-          <t>Look at the left menu.</t>
+          <t>Organizations → set/generate a join code → save.</t>
         </is>
       </c>
       <c r="D87" s="22" t="inlineStr">
         <is>
-          <t>Dashboard, Reports, Users, Events, Organizations (Help in footer).</t>
+          <t>Join code saved; usable at sign-up.</t>
         </is>
       </c>
       <c r="E87" s="23" t="n"/>
@@ -13805,22 +14217,22 @@
     <row r="88" ht="42" customHeight="1">
       <c r="A88" s="21" t="inlineStr">
         <is>
-          <t>SA2</t>
+          <t>AD13</t>
         </is>
       </c>
       <c r="B88" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I can do everything an Admin can, across all orgs.</t>
+          <t>As an Admin, I cannot create organizations.</t>
         </is>
       </c>
       <c r="C88" s="22" t="inlineStr">
         <is>
-          <t>Spot-check user + org actions on more than one org.</t>
+          <t>Look for 'Add organization'.</t>
         </is>
       </c>
       <c r="D88" s="22" t="inlineStr">
         <is>
-          <t>All allowed regardless of org.</t>
+          <t>No Add button; creation blocked.</t>
         </is>
       </c>
       <c r="E88" s="23" t="n"/>
@@ -13830,72 +14242,60 @@
     <row r="89" ht="42" customHeight="1">
       <c r="A89" s="21" t="inlineStr">
         <is>
-          <t>SA3</t>
+          <t>AD14</t>
         </is>
       </c>
       <c r="B89" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to create users incl. Supervisor and Super Admin.</t>
+          <t>As an Admin, I cannot change the recycling cans total.</t>
         </is>
       </c>
       <c r="C89" s="22" t="inlineStr">
         <is>
-          <t>Users → Add user → each role.</t>
+          <t>Look for the cans/bin admin control.</t>
         </is>
       </c>
       <c r="D89" s="22" t="inlineStr">
         <is>
-          <t>Participant/Supervisor/Super Admin options available; account created + invite email.</t>
+          <t>Not available (Super Admin only).</t>
         </is>
       </c>
       <c r="E89" s="23" t="n"/>
       <c r="F89" s="22" t="n"/>
       <c r="G89" s="23" t="n"/>
     </row>
-    <row r="90" ht="42" customHeight="1">
-      <c r="A90" s="21" t="inlineStr">
-        <is>
-          <t>SA4</t>
-        </is>
-      </c>
-      <c r="B90" s="22" t="inlineStr">
-        <is>
-          <t>As a Super Admin, I want to grant/revoke Admin access.</t>
-        </is>
-      </c>
-      <c r="C90" s="22" t="inlineStr">
-        <is>
-          <t>Open a user → grant Admin access → check org(s) → save; then uncheck all → save.</t>
-        </is>
-      </c>
-      <c r="D90" s="22" t="inlineStr">
-        <is>
-          <t>Checking orgs makes an Admin; unchecking all reverts to participant.</t>
-        </is>
-      </c>
-      <c r="E90" s="23" t="n"/>
-      <c r="F90" s="22" t="n"/>
-      <c r="G90" s="23" t="n"/>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="19" t="inlineStr">
+        <is>
+          <t>Super Admin (global)</t>
+        </is>
+      </c>
+      <c r="B90" s="20" t="n"/>
+      <c r="C90" s="20" t="n"/>
+      <c r="D90" s="20" t="n"/>
+      <c r="E90" s="20" t="n"/>
+      <c r="F90" s="20" t="n"/>
+      <c r="G90" s="20" t="n"/>
     </row>
     <row r="91" ht="42" customHeight="1">
       <c r="A91" s="21" t="inlineStr">
         <is>
-          <t>SA5</t>
+          <t>SA1</t>
         </is>
       </c>
       <c r="B91" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to create organizations + join codes.</t>
+          <t>As a Super Admin, I want the correct menu tabs.</t>
         </is>
       </c>
       <c r="C91" s="22" t="inlineStr">
         <is>
-          <t>Organizations → Add organization → set details + join code.</t>
+          <t>Look at the left menu.</t>
         </is>
       </c>
       <c r="D91" s="22" t="inlineStr">
         <is>
-          <t>Org created with its join code.</t>
+          <t>Dashboard, Reports, Users, Events, Organizations (Help in footer).</t>
         </is>
       </c>
       <c r="E91" s="23" t="n"/>
@@ -13905,22 +14305,22 @@
     <row r="92" ht="42" customHeight="1">
       <c r="A92" s="21" t="inlineStr">
         <is>
-          <t>SA6</t>
+          <t>SA2</t>
         </is>
       </c>
       <c r="B92" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to find users by type.</t>
+          <t>As a Super Admin, I can do everything an Admin can, across all orgs.</t>
         </is>
       </c>
       <c r="C92" s="22" t="inlineStr">
         <is>
-          <t>Users → role filter pills + search.</t>
+          <t>Spot-check user + org actions on more than one org.</t>
         </is>
       </c>
       <c r="D92" s="22" t="inlineStr">
         <is>
-          <t>Filter by role with counts; search by name/email across all orgs.</t>
+          <t>All allowed regardless of org.</t>
         </is>
       </c>
       <c r="E92" s="23" t="n"/>
@@ -13930,22 +14330,22 @@
     <row r="93" ht="42" customHeight="1">
       <c r="A93" s="21" t="inlineStr">
         <is>
-          <t>SA7</t>
+          <t>SA3</t>
         </is>
       </c>
       <c r="B93" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to search events.</t>
+          <t>As a Super Admin, I want to create users incl. Supervisor and Super Admin.</t>
         </is>
       </c>
       <c r="C93" s="22" t="inlineStr">
         <is>
-          <t>Events → search + date range; check supervisor/org per card.</t>
+          <t>Users → Add user → each role.</t>
         </is>
       </c>
       <c r="D93" s="22" t="inlineStr">
         <is>
-          <t>Filters work; each event shows supervisor and organization.</t>
+          <t>Participant/Supervisor/Super Admin options available; account created + invite email.</t>
         </is>
       </c>
       <c r="E93" s="23" t="n"/>
@@ -13955,22 +14355,22 @@
     <row r="94" ht="42" customHeight="1">
       <c r="A94" s="21" t="inlineStr">
         <is>
-          <t>SA8</t>
+          <t>SA4</t>
         </is>
       </c>
       <c r="B94" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want clear event-visibility labels.</t>
+          <t>As a Super Admin, I want to grant/revoke Admin access.</t>
         </is>
       </c>
       <c r="C94" s="22" t="inlineStr">
         <is>
-          <t>New Event → 'Who can see this'.</t>
+          <t>Open a user → grant Admin access → check org(s) → save; then uncheck all → save.</t>
         </is>
       </c>
       <c r="D94" s="22" t="inlineStr">
         <is>
-          <t>'Open to all (community)' and 'Only &lt;org&gt; students' with helper text.</t>
+          <t>Checking orgs makes an Admin; unchecking all reverts to participant.</t>
         </is>
       </c>
       <c r="E94" s="23" t="n"/>
@@ -13980,22 +14380,22 @@
     <row r="95" ht="42" customHeight="1">
       <c r="A95" s="21" t="inlineStr">
         <is>
-          <t>SA9</t>
+          <t>SA5</t>
         </is>
       </c>
       <c r="B95" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want program-wide reports.</t>
+          <t>As a Super Admin, I want to create organizations + join codes.</t>
         </is>
       </c>
       <c r="C95" s="22" t="inlineStr">
         <is>
-          <t>Open Reports / Dashboard.</t>
+          <t>Organizations → Add organization → set details + join code.</t>
         </is>
       </c>
       <c r="D95" s="22" t="inlineStr">
         <is>
-          <t>Totals and charts across the whole program.</t>
+          <t>Org created with its join code.</t>
         </is>
       </c>
       <c r="E95" s="23" t="n"/>
@@ -14005,22 +14405,22 @@
     <row r="96" ht="42" customHeight="1">
       <c r="A96" s="21" t="inlineStr">
         <is>
-          <t>SA10</t>
+          <t>SA6</t>
         </is>
       </c>
       <c r="B96" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to verify email works.</t>
+          <t>As a Super Admin, I want to find users by type.</t>
         </is>
       </c>
       <c r="C96" s="22" t="inlineStr">
         <is>
-          <t>Dashboard → Send test email.</t>
+          <t>Users → role filter pills + search.</t>
         </is>
       </c>
       <c r="D96" s="22" t="inlineStr">
         <is>
-          <t>Result shown (success or the exact failure reason).</t>
+          <t>Filter by role with counts; search by name/email across all orgs.</t>
         </is>
       </c>
       <c r="E96" s="23" t="n"/>
@@ -14030,22 +14430,22 @@
     <row r="97" ht="42" customHeight="1">
       <c r="A97" s="21" t="inlineStr">
         <is>
-          <t>SA11</t>
+          <t>SA7</t>
         </is>
       </c>
       <c r="B97" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to update the recycling cans total.</t>
+          <t>As a Super Admin, I want to search events.</t>
         </is>
       </c>
       <c r="C97" s="22" t="inlineStr">
         <is>
-          <t>Use the cans/bin admin control.</t>
+          <t>Events → search + date range; check supervisor/org per card.</t>
         </is>
       </c>
       <c r="D97" s="22" t="inlineStr">
         <is>
-          <t>Total updates; the ribbon reflects it.</t>
+          <t>Filters work; each event shows supervisor and organization.</t>
         </is>
       </c>
       <c r="E97" s="23" t="n"/>
@@ -14055,60 +14455,72 @@
     <row r="98" ht="42" customHeight="1">
       <c r="A98" s="21" t="inlineStr">
         <is>
-          <t>SA12</t>
+          <t>SA8</t>
         </is>
       </c>
       <c r="B98" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want hours + records for any user.</t>
+          <t>As a Super Admin, I want clear event-visibility labels.</t>
         </is>
       </c>
       <c r="C98" s="22" t="inlineStr">
         <is>
-          <t>Add manual hours / open service record for any participant.</t>
+          <t>New Event → 'Who can see this'.</t>
         </is>
       </c>
       <c r="D98" s="22" t="inlineStr">
         <is>
-          <t>Works for any org.</t>
+          <t>'Open to all (community)' and 'Only &lt;org&gt; students' with helper text.</t>
         </is>
       </c>
       <c r="E98" s="23" t="n"/>
       <c r="F98" s="22" t="n"/>
       <c r="G98" s="23" t="n"/>
     </row>
-    <row r="99" ht="20" customHeight="1">
-      <c r="A99" s="19" t="inlineStr">
-        <is>
-          <t>Cross-cutting</t>
-        </is>
-      </c>
-      <c r="B99" s="20" t="n"/>
-      <c r="C99" s="20" t="n"/>
-      <c r="D99" s="20" t="n"/>
-      <c r="E99" s="20" t="n"/>
-      <c r="F99" s="20" t="n"/>
-      <c r="G99" s="20" t="n"/>
+    <row r="99" ht="42" customHeight="1">
+      <c r="A99" s="21" t="inlineStr">
+        <is>
+          <t>SA9</t>
+        </is>
+      </c>
+      <c r="B99" s="22" t="inlineStr">
+        <is>
+          <t>As a Super Admin, I want program-wide reports.</t>
+        </is>
+      </c>
+      <c r="C99" s="22" t="inlineStr">
+        <is>
+          <t>Open Reports / Dashboard.</t>
+        </is>
+      </c>
+      <c r="D99" s="22" t="inlineStr">
+        <is>
+          <t>Totals and charts across the whole program.</t>
+        </is>
+      </c>
+      <c r="E99" s="23" t="n"/>
+      <c r="F99" s="22" t="n"/>
+      <c r="G99" s="23" t="n"/>
     </row>
     <row r="100" ht="42" customHeight="1">
       <c r="A100" s="21" t="inlineStr">
         <is>
-          <t>X1</t>
+          <t>SA10</t>
         </is>
       </c>
       <c r="B100" s="22" t="inlineStr">
         <is>
-          <t>As a phone user, I want a usable mobile layout.</t>
+          <t>As a Super Admin, I want to verify email works.</t>
         </is>
       </c>
       <c r="C100" s="22" t="inlineStr">
         <is>
-          <t>Open at phone width; use the menu drawer.</t>
+          <t>Dashboard → Send test email.</t>
         </is>
       </c>
       <c r="D100" s="22" t="inlineStr">
         <is>
-          <t>Layout adapts; drawer opens/closes; no horizontal scroll.</t>
+          <t>Result shown (success or the exact failure reason).</t>
         </is>
       </c>
       <c r="E100" s="23" t="n"/>
@@ -14118,39 +14530,127 @@
     <row r="101" ht="42" customHeight="1">
       <c r="A101" s="21" t="inlineStr">
         <is>
-          <t>X2</t>
+          <t>SA11</t>
         </is>
       </c>
       <c r="B101" s="22" t="inlineStr">
         <is>
-          <t>As a visitor, I want the recycling ribbon on the login page.</t>
+          <t>As a Super Admin, I want to update the recycling cans total.</t>
         </is>
       </c>
       <c r="C101" s="22" t="inlineStr">
         <is>
-          <t>Open login signed out.</t>
+          <t>Use the cans/bin admin control.</t>
         </is>
       </c>
       <c r="D101" s="22" t="inlineStr">
         <is>
-          <t>Green ribbon shows on login.</t>
+          <t>Total updates; the ribbon reflects it.</t>
         </is>
       </c>
       <c r="E101" s="23" t="n"/>
       <c r="F101" s="22" t="n"/>
       <c r="G101" s="23" t="n"/>
     </row>
+    <row r="102" ht="42" customHeight="1">
+      <c r="A102" s="21" t="inlineStr">
+        <is>
+          <t>SA12</t>
+        </is>
+      </c>
+      <c r="B102" s="22" t="inlineStr">
+        <is>
+          <t>As a Super Admin, I want hours + records for any user.</t>
+        </is>
+      </c>
+      <c r="C102" s="22" t="inlineStr">
+        <is>
+          <t>Add manual hours / open service record for any participant.</t>
+        </is>
+      </c>
+      <c r="D102" s="22" t="inlineStr">
+        <is>
+          <t>Works for any org.</t>
+        </is>
+      </c>
+      <c r="E102" s="23" t="n"/>
+      <c r="F102" s="22" t="n"/>
+      <c r="G102" s="23" t="n"/>
+    </row>
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="19" t="inlineStr">
+        <is>
+          <t>Cross-cutting</t>
+        </is>
+      </c>
+      <c r="B103" s="20" t="n"/>
+      <c r="C103" s="20" t="n"/>
+      <c r="D103" s="20" t="n"/>
+      <c r="E103" s="20" t="n"/>
+      <c r="F103" s="20" t="n"/>
+      <c r="G103" s="20" t="n"/>
+    </row>
+    <row r="104" ht="42" customHeight="1">
+      <c r="A104" s="21" t="inlineStr">
+        <is>
+          <t>X1</t>
+        </is>
+      </c>
+      <c r="B104" s="22" t="inlineStr">
+        <is>
+          <t>As a phone user, I want a usable mobile layout.</t>
+        </is>
+      </c>
+      <c r="C104" s="22" t="inlineStr">
+        <is>
+          <t>Open at phone width; use the menu drawer.</t>
+        </is>
+      </c>
+      <c r="D104" s="22" t="inlineStr">
+        <is>
+          <t>Layout adapts; drawer opens/closes; no horizontal scroll.</t>
+        </is>
+      </c>
+      <c r="E104" s="23" t="n"/>
+      <c r="F104" s="22" t="n"/>
+      <c r="G104" s="23" t="n"/>
+    </row>
+    <row r="105" ht="42" customHeight="1">
+      <c r="A105" s="21" t="inlineStr">
+        <is>
+          <t>X2</t>
+        </is>
+      </c>
+      <c r="B105" s="22" t="inlineStr">
+        <is>
+          <t>As a visitor, I want the recycling ribbon on the login page.</t>
+        </is>
+      </c>
+      <c r="C105" s="22" t="inlineStr">
+        <is>
+          <t>Open login signed out.</t>
+        </is>
+      </c>
+      <c r="D105" s="22" t="inlineStr">
+        <is>
+          <t>Green ribbon shows on login.</t>
+        </is>
+      </c>
+      <c r="E105" s="23" t="n"/>
+      <c r="F105" s="22" t="n"/>
+      <c r="G105" s="23" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A99:G99"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A55:G55"/>
     <mergeCell ref="A35:G35"/>
-    <mergeCell ref="A86:G86"/>
-    <mergeCell ref="A71:G71"/>
-    <mergeCell ref="A51:G51"/>
+    <mergeCell ref="A90:G90"/>
+    <mergeCell ref="A49:G49"/>
     <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="A103:G103"/>
+    <mergeCell ref="A75:G75"/>
   </mergeCells>
   <conditionalFormatting sqref="E4:E9">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
@@ -14174,7 +14674,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E36:E44">
+  <conditionalFormatting sqref="E36:E48">
     <cfRule type="cellIs" priority="7" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -14185,7 +14685,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E46:E50">
+  <conditionalFormatting sqref="E50:E54">
     <cfRule type="cellIs" priority="10" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -14196,7 +14696,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E52:E70">
+  <conditionalFormatting sqref="E56:E74">
     <cfRule type="cellIs" priority="13" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -14207,7 +14707,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E72:E85">
+  <conditionalFormatting sqref="E76:E89">
     <cfRule type="cellIs" priority="16" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -14218,7 +14718,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E87:E98">
+  <conditionalFormatting sqref="E91:E102">
     <cfRule type="cellIs" priority="19" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -14229,7 +14729,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E100:E101">
+  <conditionalFormatting sqref="E104:E105">
     <cfRule type="cellIs" priority="22" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -14241,7 +14741,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E4:E9 E11:E34 E36:E44 E46:E50 E52:E70 E72:E85 E87:E98 E100:E101" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E4:E9 E11:E34 E36:E48 E50:E54 E56:E74 E76:E89 E91:E102 E104:E105" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pass,Fail,Blocked,Not tested,N/A"</formula1>
     </dataValidation>
   </dataValidations>

--- a/MedinaCares_Test_Plan.xlsx
+++ b/MedinaCares_Test_Plan.xlsx
@@ -1014,30 +1014,30 @@
         </is>
       </c>
       <c r="B6" s="13" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C6" s="14">
-        <f>COUNTIF('iOS'!$E$3:$E$105,"Pass")</f>
+        <f>COUNTIF('iOS'!$E$3:$E$107,"Pass")</f>
         <v/>
       </c>
       <c r="D6" s="14">
-        <f>COUNTIF('iOS'!$E$3:$E$105,"Fail")</f>
+        <f>COUNTIF('iOS'!$E$3:$E$107,"Fail")</f>
         <v/>
       </c>
       <c r="E6" s="14">
-        <f>COUNTIF('iOS'!$E$3:$E$105,"Blocked")</f>
+        <f>COUNTIF('iOS'!$E$3:$E$107,"Blocked")</f>
         <v/>
       </c>
       <c r="F6" s="14">
-        <f>COUNTIF('iOS'!$E$3:$E$105,"Not tested")</f>
+        <f>COUNTIF('iOS'!$E$3:$E$107,"Not tested")</f>
         <v/>
       </c>
       <c r="G6" s="14">
-        <f>$B6-COUNTA('iOS'!$E$3:$E$105)</f>
+        <f>$B6-COUNTA('iOS'!$E$3:$E$107)</f>
         <v/>
       </c>
       <c r="H6" s="15">
-        <f>IF($B6=0,0,(COUNTIF('iOS'!$E$3:$E$105,"Pass")+COUNTIF('iOS'!$E$3:$E$105,"Fail")+COUNTIF('iOS'!$E$3:$E$105,"Blocked")+COUNTIF('iOS'!$E$3:$E$105,"Not tested"))/$B6)</f>
+        <f>IF($B6=0,0,(COUNTIF('iOS'!$E$3:$E$107,"Pass")+COUNTIF('iOS'!$E$3:$E$107,"Fail")+COUNTIF('iOS'!$E$3:$E$107,"Blocked")+COUNTIF('iOS'!$E$3:$E$107,"Not tested"))/$B6)</f>
         <v/>
       </c>
     </row>
@@ -1048,30 +1048,30 @@
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C7" s="14">
-        <f>COUNTIF('Android'!$E$3:$E$105,"Pass")</f>
+        <f>COUNTIF('Android'!$E$3:$E$107,"Pass")</f>
         <v/>
       </c>
       <c r="D7" s="14">
-        <f>COUNTIF('Android'!$E$3:$E$105,"Fail")</f>
+        <f>COUNTIF('Android'!$E$3:$E$107,"Fail")</f>
         <v/>
       </c>
       <c r="E7" s="14">
-        <f>COUNTIF('Android'!$E$3:$E$105,"Blocked")</f>
+        <f>COUNTIF('Android'!$E$3:$E$107,"Blocked")</f>
         <v/>
       </c>
       <c r="F7" s="14">
-        <f>COUNTIF('Android'!$E$3:$E$105,"Not tested")</f>
+        <f>COUNTIF('Android'!$E$3:$E$107,"Not tested")</f>
         <v/>
       </c>
       <c r="G7" s="14">
-        <f>$B7-COUNTA('Android'!$E$3:$E$105)</f>
+        <f>$B7-COUNTA('Android'!$E$3:$E$107)</f>
         <v/>
       </c>
       <c r="H7" s="15">
-        <f>IF($B7=0,0,(COUNTIF('Android'!$E$3:$E$105,"Pass")+COUNTIF('Android'!$E$3:$E$105,"Fail")+COUNTIF('Android'!$E$3:$E$105,"Blocked")+COUNTIF('Android'!$E$3:$E$105,"Not tested"))/$B7)</f>
+        <f>IF($B7=0,0,(COUNTIF('Android'!$E$3:$E$107,"Pass")+COUNTIF('Android'!$E$3:$E$107,"Fail")+COUNTIF('Android'!$E$3:$E$107,"Blocked")+COUNTIF('Android'!$E$3:$E$107,"Not tested"))/$B7)</f>
         <v/>
       </c>
     </row>
@@ -1082,30 +1082,30 @@
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C8" s="14">
-        <f>COUNTIF('Desktop Chrome'!$E$3:$E$105,"Pass")</f>
+        <f>COUNTIF('Desktop Chrome'!$E$3:$E$107,"Pass")</f>
         <v/>
       </c>
       <c r="D8" s="14">
-        <f>COUNTIF('Desktop Chrome'!$E$3:$E$105,"Fail")</f>
+        <f>COUNTIF('Desktop Chrome'!$E$3:$E$107,"Fail")</f>
         <v/>
       </c>
       <c r="E8" s="14">
-        <f>COUNTIF('Desktop Chrome'!$E$3:$E$105,"Blocked")</f>
+        <f>COUNTIF('Desktop Chrome'!$E$3:$E$107,"Blocked")</f>
         <v/>
       </c>
       <c r="F8" s="14">
-        <f>COUNTIF('Desktop Chrome'!$E$3:$E$105,"Not tested")</f>
+        <f>COUNTIF('Desktop Chrome'!$E$3:$E$107,"Not tested")</f>
         <v/>
       </c>
       <c r="G8" s="14">
-        <f>$B8-COUNTA('Desktop Chrome'!$E$3:$E$105)</f>
+        <f>$B8-COUNTA('Desktop Chrome'!$E$3:$E$107)</f>
         <v/>
       </c>
       <c r="H8" s="15">
-        <f>IF($B8=0,0,(COUNTIF('Desktop Chrome'!$E$3:$E$105,"Pass")+COUNTIF('Desktop Chrome'!$E$3:$E$105,"Fail")+COUNTIF('Desktop Chrome'!$E$3:$E$105,"Blocked")+COUNTIF('Desktop Chrome'!$E$3:$E$105,"Not tested"))/$B8)</f>
+        <f>IF($B8=0,0,(COUNTIF('Desktop Chrome'!$E$3:$E$107,"Pass")+COUNTIF('Desktop Chrome'!$E$3:$E$107,"Fail")+COUNTIF('Desktop Chrome'!$E$3:$E$107,"Blocked")+COUNTIF('Desktop Chrome'!$E$3:$E$107,"Not tested"))/$B8)</f>
         <v/>
       </c>
     </row>
@@ -1116,30 +1116,30 @@
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C9" s="14">
-        <f>COUNTIF('Desktop Firefox'!$E$3:$E$105,"Pass")</f>
+        <f>COUNTIF('Desktop Firefox'!$E$3:$E$107,"Pass")</f>
         <v/>
       </c>
       <c r="D9" s="14">
-        <f>COUNTIF('Desktop Firefox'!$E$3:$E$105,"Fail")</f>
+        <f>COUNTIF('Desktop Firefox'!$E$3:$E$107,"Fail")</f>
         <v/>
       </c>
       <c r="E9" s="14">
-        <f>COUNTIF('Desktop Firefox'!$E$3:$E$105,"Blocked")</f>
+        <f>COUNTIF('Desktop Firefox'!$E$3:$E$107,"Blocked")</f>
         <v/>
       </c>
       <c r="F9" s="14">
-        <f>COUNTIF('Desktop Firefox'!$E$3:$E$105,"Not tested")</f>
+        <f>COUNTIF('Desktop Firefox'!$E$3:$E$107,"Not tested")</f>
         <v/>
       </c>
       <c r="G9" s="14">
-        <f>$B9-COUNTA('Desktop Firefox'!$E$3:$E$105)</f>
+        <f>$B9-COUNTA('Desktop Firefox'!$E$3:$E$107)</f>
         <v/>
       </c>
       <c r="H9" s="15">
-        <f>IF($B9=0,0,(COUNTIF('Desktop Firefox'!$E$3:$E$105,"Pass")+COUNTIF('Desktop Firefox'!$E$3:$E$105,"Fail")+COUNTIF('Desktop Firefox'!$E$3:$E$105,"Blocked")+COUNTIF('Desktop Firefox'!$E$3:$E$105,"Not tested"))/$B9)</f>
+        <f>IF($B9=0,0,(COUNTIF('Desktop Firefox'!$E$3:$E$107,"Pass")+COUNTIF('Desktop Firefox'!$E$3:$E$107,"Fail")+COUNTIF('Desktop Firefox'!$E$3:$E$107,"Blocked")+COUNTIF('Desktop Firefox'!$E$3:$E$107,"Not tested"))/$B9)</f>
         <v/>
       </c>
     </row>
@@ -1150,30 +1150,30 @@
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C10" s="14">
-        <f>COUNTIF('Desktop Other'!$E$3:$E$105,"Pass")</f>
+        <f>COUNTIF('Desktop Other'!$E$3:$E$107,"Pass")</f>
         <v/>
       </c>
       <c r="D10" s="14">
-        <f>COUNTIF('Desktop Other'!$E$3:$E$105,"Fail")</f>
+        <f>COUNTIF('Desktop Other'!$E$3:$E$107,"Fail")</f>
         <v/>
       </c>
       <c r="E10" s="14">
-        <f>COUNTIF('Desktop Other'!$E$3:$E$105,"Blocked")</f>
+        <f>COUNTIF('Desktop Other'!$E$3:$E$107,"Blocked")</f>
         <v/>
       </c>
       <c r="F10" s="14">
-        <f>COUNTIF('Desktop Other'!$E$3:$E$105,"Not tested")</f>
+        <f>COUNTIF('Desktop Other'!$E$3:$E$107,"Not tested")</f>
         <v/>
       </c>
       <c r="G10" s="14">
-        <f>$B10-COUNTA('Desktop Other'!$E$3:$E$105)</f>
+        <f>$B10-COUNTA('Desktop Other'!$E$3:$E$107)</f>
         <v/>
       </c>
       <c r="H10" s="15">
-        <f>IF($B10=0,0,(COUNTIF('Desktop Other'!$E$3:$E$105,"Pass")+COUNTIF('Desktop Other'!$E$3:$E$105,"Fail")+COUNTIF('Desktop Other'!$E$3:$E$105,"Blocked")+COUNTIF('Desktop Other'!$E$3:$E$105,"Not tested"))/$B10)</f>
+        <f>IF($B10=0,0,(COUNTIF('Desktop Other'!$E$3:$E$107,"Pass")+COUNTIF('Desktop Other'!$E$3:$E$107,"Fail")+COUNTIF('Desktop Other'!$E$3:$E$107,"Blocked")+COUNTIF('Desktop Other'!$E$3:$E$107,"Not tested"))/$B10)</f>
         <v/>
       </c>
     </row>
@@ -1288,27 +1288,27 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIF('iOS'!$E$36:$E$48,"Pass")</f>
+        <f>COUNTIF('iOS'!$E$36:$E$50,"Pass")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIF('Android'!$E$36:$E$48,"Pass")</f>
+        <f>COUNTIF('Android'!$E$36:$E$50,"Pass")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIF('Desktop Chrome'!$E$36:$E$48,"Pass")</f>
+        <f>COUNTIF('Desktop Chrome'!$E$36:$E$50,"Pass")</f>
         <v/>
       </c>
       <c r="E16" s="13">
-        <f>COUNTIF('Desktop Firefox'!$E$36:$E$48,"Pass")</f>
+        <f>COUNTIF('Desktop Firefox'!$E$36:$E$50,"Pass")</f>
         <v/>
       </c>
       <c r="F16" s="13">
-        <f>COUNTIF('Desktop Other'!$E$36:$E$48,"Pass")</f>
+        <f>COUNTIF('Desktop Other'!$E$36:$E$50,"Pass")</f>
         <v/>
       </c>
       <c r="G16" s="13" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
@@ -1318,23 +1318,23 @@
         </is>
       </c>
       <c r="B17" s="13">
-        <f>COUNTIF('iOS'!$E$50:$E$54,"Pass")</f>
+        <f>COUNTIF('iOS'!$E$52:$E$56,"Pass")</f>
         <v/>
       </c>
       <c r="C17" s="13">
-        <f>COUNTIF('Android'!$E$50:$E$54,"Pass")</f>
+        <f>COUNTIF('Android'!$E$52:$E$56,"Pass")</f>
         <v/>
       </c>
       <c r="D17" s="13">
-        <f>COUNTIF('Desktop Chrome'!$E$50:$E$54,"Pass")</f>
+        <f>COUNTIF('Desktop Chrome'!$E$52:$E$56,"Pass")</f>
         <v/>
       </c>
       <c r="E17" s="13">
-        <f>COUNTIF('Desktop Firefox'!$E$50:$E$54,"Pass")</f>
+        <f>COUNTIF('Desktop Firefox'!$E$52:$E$56,"Pass")</f>
         <v/>
       </c>
       <c r="F17" s="13">
-        <f>COUNTIF('Desktop Other'!$E$50:$E$54,"Pass")</f>
+        <f>COUNTIF('Desktop Other'!$E$52:$E$56,"Pass")</f>
         <v/>
       </c>
       <c r="G17" s="13" t="n">
@@ -1348,23 +1348,23 @@
         </is>
       </c>
       <c r="B18" s="13">
-        <f>COUNTIF('iOS'!$E$56:$E$74,"Pass")</f>
+        <f>COUNTIF('iOS'!$E$58:$E$76,"Pass")</f>
         <v/>
       </c>
       <c r="C18" s="13">
-        <f>COUNTIF('Android'!$E$56:$E$74,"Pass")</f>
+        <f>COUNTIF('Android'!$E$58:$E$76,"Pass")</f>
         <v/>
       </c>
       <c r="D18" s="13">
-        <f>COUNTIF('Desktop Chrome'!$E$56:$E$74,"Pass")</f>
+        <f>COUNTIF('Desktop Chrome'!$E$58:$E$76,"Pass")</f>
         <v/>
       </c>
       <c r="E18" s="13">
-        <f>COUNTIF('Desktop Firefox'!$E$56:$E$74,"Pass")</f>
+        <f>COUNTIF('Desktop Firefox'!$E$58:$E$76,"Pass")</f>
         <v/>
       </c>
       <c r="F18" s="13">
-        <f>COUNTIF('Desktop Other'!$E$56:$E$74,"Pass")</f>
+        <f>COUNTIF('Desktop Other'!$E$58:$E$76,"Pass")</f>
         <v/>
       </c>
       <c r="G18" s="13" t="n">
@@ -1378,23 +1378,23 @@
         </is>
       </c>
       <c r="B19" s="13">
-        <f>COUNTIF('iOS'!$E$76:$E$89,"Pass")</f>
+        <f>COUNTIF('iOS'!$E$78:$E$91,"Pass")</f>
         <v/>
       </c>
       <c r="C19" s="13">
-        <f>COUNTIF('Android'!$E$76:$E$89,"Pass")</f>
+        <f>COUNTIF('Android'!$E$78:$E$91,"Pass")</f>
         <v/>
       </c>
       <c r="D19" s="13">
-        <f>COUNTIF('Desktop Chrome'!$E$76:$E$89,"Pass")</f>
+        <f>COUNTIF('Desktop Chrome'!$E$78:$E$91,"Pass")</f>
         <v/>
       </c>
       <c r="E19" s="13">
-        <f>COUNTIF('Desktop Firefox'!$E$76:$E$89,"Pass")</f>
+        <f>COUNTIF('Desktop Firefox'!$E$78:$E$91,"Pass")</f>
         <v/>
       </c>
       <c r="F19" s="13">
-        <f>COUNTIF('Desktop Other'!$E$76:$E$89,"Pass")</f>
+        <f>COUNTIF('Desktop Other'!$E$78:$E$91,"Pass")</f>
         <v/>
       </c>
       <c r="G19" s="13" t="n">
@@ -1408,23 +1408,23 @@
         </is>
       </c>
       <c r="B20" s="13">
-        <f>COUNTIF('iOS'!$E$91:$E$102,"Pass")</f>
+        <f>COUNTIF('iOS'!$E$93:$E$104,"Pass")</f>
         <v/>
       </c>
       <c r="C20" s="13">
-        <f>COUNTIF('Android'!$E$91:$E$102,"Pass")</f>
+        <f>COUNTIF('Android'!$E$93:$E$104,"Pass")</f>
         <v/>
       </c>
       <c r="D20" s="13">
-        <f>COUNTIF('Desktop Chrome'!$E$91:$E$102,"Pass")</f>
+        <f>COUNTIF('Desktop Chrome'!$E$93:$E$104,"Pass")</f>
         <v/>
       </c>
       <c r="E20" s="13">
-        <f>COUNTIF('Desktop Firefox'!$E$91:$E$102,"Pass")</f>
+        <f>COUNTIF('Desktop Firefox'!$E$93:$E$104,"Pass")</f>
         <v/>
       </c>
       <c r="F20" s="13">
-        <f>COUNTIF('Desktop Other'!$E$91:$E$102,"Pass")</f>
+        <f>COUNTIF('Desktop Other'!$E$93:$E$104,"Pass")</f>
         <v/>
       </c>
       <c r="G20" s="13" t="n">
@@ -1438,23 +1438,23 @@
         </is>
       </c>
       <c r="B21" s="13">
-        <f>COUNTIF('iOS'!$E$104:$E$105,"Pass")</f>
+        <f>COUNTIF('iOS'!$E$106:$E$107,"Pass")</f>
         <v/>
       </c>
       <c r="C21" s="13">
-        <f>COUNTIF('Android'!$E$104:$E$105,"Pass")</f>
+        <f>COUNTIF('Android'!$E$106:$E$107,"Pass")</f>
         <v/>
       </c>
       <c r="D21" s="13">
-        <f>COUNTIF('Desktop Chrome'!$E$104:$E$105,"Pass")</f>
+        <f>COUNTIF('Desktop Chrome'!$E$106:$E$107,"Pass")</f>
         <v/>
       </c>
       <c r="E21" s="13">
-        <f>COUNTIF('Desktop Firefox'!$E$104:$E$105,"Pass")</f>
+        <f>COUNTIF('Desktop Firefox'!$E$106:$E$107,"Pass")</f>
         <v/>
       </c>
       <c r="F21" s="13">
-        <f>COUNTIF('Desktop Other'!$E$104:$E$105,"Pass")</f>
+        <f>COUNTIF('Desktop Other'!$E$106:$E$107,"Pass")</f>
         <v/>
       </c>
       <c r="G21" s="13" t="n">
@@ -1475,7 +1475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G105"/>
+  <dimension ref="A1:G107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2651,88 +2651,88 @@
       <c r="F48" s="22" t="n"/>
       <c r="G48" s="23" t="n"/>
     </row>
-    <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="19" t="inlineStr">
-        <is>
-          <t>Parent — viewer (grades 6–12 student)</t>
-        </is>
-      </c>
-      <c r="B49" s="20" t="n"/>
-      <c r="C49" s="20" t="n"/>
-      <c r="D49" s="20" t="n"/>
-      <c r="E49" s="20" t="n"/>
-      <c r="F49" s="20" t="n"/>
-      <c r="G49" s="20" t="n"/>
+    <row r="49" ht="42" customHeight="1">
+      <c r="A49" s="21" t="inlineStr">
+        <is>
+          <t>PE14</t>
+        </is>
+      </c>
+      <c r="B49" s="22" t="inlineStr">
+        <is>
+          <t>As a parent, I want to log my child's outside/nonprofit volunteering.</t>
+        </is>
+      </c>
+      <c r="C49" s="22" t="inlineStr">
+        <is>
+          <t>Child card → 'Outside hours' → fill activity, org, date, hours, supervisor → Submit.</t>
+        </is>
+      </c>
+      <c r="D49" s="22" t="inlineStr">
+        <is>
+          <t>External hours submitted for the child and sent for supervisor approval (proof required over 5h).</t>
+        </is>
+      </c>
+      <c r="E49" s="23" t="n"/>
+      <c r="F49" s="22" t="n"/>
+      <c r="G49" s="23" t="n"/>
     </row>
     <row r="50" ht="42" customHeight="1">
       <c r="A50" s="21" t="inlineStr">
         <is>
-          <t>PV1</t>
+          <t>PE15</t>
         </is>
       </c>
       <c r="B50" s="22" t="inlineStr">
         <is>
-          <t>As a parent of a 6–12 student, I want to register for view-only access.</t>
+          <t>As a parent, I want my child's verified service record.</t>
         </is>
       </c>
       <c r="C50" s="22" t="inlineStr">
         <is>
-          <t>Create account → parent of a 6–12 student.</t>
+          <t>Child card → 'Service record'.</t>
         </is>
       </c>
       <c r="D50" s="22" t="inlineStr">
         <is>
-          <t>Account created; no invite required to register.</t>
+          <t>The child's itemized record opens; Print / Save-as-PDF works.</t>
         </is>
       </c>
       <c r="E50" s="23" t="n"/>
       <c r="F50" s="22" t="n"/>
       <c r="G50" s="23" t="n"/>
     </row>
-    <row r="51" ht="42" customHeight="1">
-      <c r="A51" s="21" t="inlineStr">
-        <is>
-          <t>PV2</t>
-        </is>
-      </c>
-      <c r="B51" s="22" t="inlineStr">
-        <is>
-          <t>As a viewer parent, my student links automatically by email.</t>
-        </is>
-      </c>
-      <c r="C51" s="22" t="inlineStr">
-        <is>
-          <t>Have a student enter this exact email as their parent email (before or after you register).</t>
-        </is>
-      </c>
-      <c r="D51" s="22" t="inlineStr">
-        <is>
-          <t>The student appears on your dashboard automatically; empty until then.</t>
-        </is>
-      </c>
-      <c r="E51" s="23" t="n"/>
-      <c r="F51" s="22" t="n"/>
-      <c r="G51" s="23" t="n"/>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="19" t="inlineStr">
+        <is>
+          <t>Parent — viewer (grades 6–12 student)</t>
+        </is>
+      </c>
+      <c r="B51" s="20" t="n"/>
+      <c r="C51" s="20" t="n"/>
+      <c r="D51" s="20" t="n"/>
+      <c r="E51" s="20" t="n"/>
+      <c r="F51" s="20" t="n"/>
+      <c r="G51" s="20" t="n"/>
     </row>
     <row r="52" ht="42" customHeight="1">
       <c r="A52" s="21" t="inlineStr">
         <is>
-          <t>PV3</t>
+          <t>PV1</t>
         </is>
       </c>
       <c r="B52" s="22" t="inlineStr">
         <is>
-          <t>As a viewer parent, I want to see my student's schedule/progress.</t>
+          <t>As a parent of a 6–12 student, I want to register for view-only access.</t>
         </is>
       </c>
       <c r="C52" s="22" t="inlineStr">
         <is>
-          <t>Open the dashboard.</t>
+          <t>Create account → parent of a 6–12 student.</t>
         </is>
       </c>
       <c r="D52" s="22" t="inlineStr">
         <is>
-          <t>View-only schedule and progress.</t>
+          <t>Account created; no invite required to register.</t>
         </is>
       </c>
       <c r="E52" s="23" t="n"/>
@@ -2742,22 +2742,22 @@
     <row r="53" ht="42" customHeight="1">
       <c r="A53" s="21" t="inlineStr">
         <is>
-          <t>PV4</t>
+          <t>PV2</t>
         </is>
       </c>
       <c r="B53" s="22" t="inlineStr">
         <is>
-          <t>As a viewer parent, I do NOT sign the student up.</t>
+          <t>As a viewer parent, my student links automatically by email.</t>
         </is>
       </c>
       <c r="C53" s="22" t="inlineStr">
         <is>
-          <t>Look for a sign-up action.</t>
+          <t>Have a student enter this exact email as their parent email (before or after you register).</t>
         </is>
       </c>
       <c r="D53" s="22" t="inlineStr">
         <is>
-          <t>No sign-up on the student's behalf — the student self-serves.</t>
+          <t>The student appears on your dashboard automatically; empty until then.</t>
         </is>
       </c>
       <c r="E53" s="23" t="n"/>
@@ -2767,110 +2767,110 @@
     <row r="54" ht="42" customHeight="1">
       <c r="A54" s="21" t="inlineStr">
         <is>
-          <t>PV5</t>
+          <t>PV3</t>
         </is>
       </c>
       <c r="B54" s="22" t="inlineStr">
         <is>
-          <t>As a viewer parent, I want to invite a co-guardian.</t>
+          <t>As a viewer parent, I want to see my student's schedule/progress.</t>
         </is>
       </c>
       <c r="C54" s="22" t="inlineStr">
         <is>
-          <t>Invite a co-guardian by email.</t>
+          <t>Open the dashboard.</t>
         </is>
       </c>
       <c r="D54" s="22" t="inlineStr">
         <is>
-          <t>Invite email sent; shared access on registration.</t>
+          <t>View-only schedule and progress.</t>
         </is>
       </c>
       <c r="E54" s="23" t="n"/>
       <c r="F54" s="22" t="n"/>
       <c r="G54" s="23" t="n"/>
     </row>
-    <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="19" t="inlineStr">
-        <is>
-          <t>Supervisor (created by an Admin)</t>
-        </is>
-      </c>
-      <c r="B55" s="20" t="n"/>
-      <c r="C55" s="20" t="n"/>
-      <c r="D55" s="20" t="n"/>
-      <c r="E55" s="20" t="n"/>
-      <c r="F55" s="20" t="n"/>
-      <c r="G55" s="20" t="n"/>
+    <row r="55" ht="42" customHeight="1">
+      <c r="A55" s="21" t="inlineStr">
+        <is>
+          <t>PV4</t>
+        </is>
+      </c>
+      <c r="B55" s="22" t="inlineStr">
+        <is>
+          <t>As a viewer parent, I do NOT sign the student up.</t>
+        </is>
+      </c>
+      <c r="C55" s="22" t="inlineStr">
+        <is>
+          <t>Look for a sign-up action.</t>
+        </is>
+      </c>
+      <c r="D55" s="22" t="inlineStr">
+        <is>
+          <t>No sign-up on the student's behalf — the student self-serves.</t>
+        </is>
+      </c>
+      <c r="E55" s="23" t="n"/>
+      <c r="F55" s="22" t="n"/>
+      <c r="G55" s="23" t="n"/>
     </row>
     <row r="56" ht="42" customHeight="1">
       <c r="A56" s="21" t="inlineStr">
         <is>
-          <t>SV1</t>
+          <t>PV5</t>
         </is>
       </c>
       <c r="B56" s="22" t="inlineStr">
         <is>
-          <t>As the program, a supervisor cannot self-register.</t>
+          <t>As a viewer parent, I want to invite a co-guardian.</t>
         </is>
       </c>
       <c r="C56" s="22" t="inlineStr">
         <is>
-          <t>Review the sign-up options.</t>
+          <t>Invite a co-guardian by email.</t>
         </is>
       </c>
       <c r="D56" s="22" t="inlineStr">
         <is>
-          <t>No supervisor option exists on registration.</t>
+          <t>Invite email sent; shared access on registration.</t>
         </is>
       </c>
       <c r="E56" s="23" t="n"/>
       <c r="F56" s="22" t="n"/>
       <c r="G56" s="23" t="n"/>
     </row>
-    <row r="57" ht="42" customHeight="1">
-      <c r="A57" s="21" t="inlineStr">
-        <is>
-          <t>SV2</t>
-        </is>
-      </c>
-      <c r="B57" s="22" t="inlineStr">
-        <is>
-          <t>As a new supervisor, I get an invite to set my password.</t>
-        </is>
-      </c>
-      <c r="C57" s="22" t="inlineStr">
-        <is>
-          <t>Have an Admin create your account; open the invite email; set password; sign in.</t>
-        </is>
-      </c>
-      <c r="D57" s="22" t="inlineStr">
-        <is>
-          <t>Invite email arrives with a working set-password link; you can sign in.</t>
-        </is>
-      </c>
-      <c r="E57" s="23" t="n"/>
-      <c r="F57" s="22" t="n"/>
-      <c r="G57" s="23" t="n"/>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="19" t="inlineStr">
+        <is>
+          <t>Supervisor (created by an Admin)</t>
+        </is>
+      </c>
+      <c r="B57" s="20" t="n"/>
+      <c r="C57" s="20" t="n"/>
+      <c r="D57" s="20" t="n"/>
+      <c r="E57" s="20" t="n"/>
+      <c r="F57" s="20" t="n"/>
+      <c r="G57" s="20" t="n"/>
     </row>
     <row r="58" ht="42" customHeight="1">
       <c r="A58" s="21" t="inlineStr">
         <is>
-          <t>SV3</t>
+          <t>SV1</t>
         </is>
       </c>
       <c r="B58" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want the correct 7 left-menu tabs.</t>
+          <t>As the program, a supervisor cannot self-register.</t>
         </is>
       </c>
       <c r="C58" s="22" t="inlineStr">
         <is>
-          <t>Look at the left menu.</t>
+          <t>Review the sign-up options.</t>
         </is>
       </c>
       <c r="D58" s="22" t="inlineStr">
         <is>
-          <t>Dashboard, Pending Reviews, Reviewed History, My Events, All Opportunities, My Hours, Help.</t>
+          <t>No supervisor option exists on registration.</t>
         </is>
       </c>
       <c r="E58" s="23" t="n"/>
@@ -2880,22 +2880,22 @@
     <row r="59" ht="42" customHeight="1">
       <c r="A59" s="21" t="inlineStr">
         <is>
-          <t>SV4</t>
+          <t>SV2</t>
         </is>
       </c>
       <c r="B59" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want a dashboard.</t>
+          <t>As a new supervisor, I get an invite to set my password.</t>
         </is>
       </c>
       <c r="C59" s="22" t="inlineStr">
         <is>
-          <t>Open the dashboard.</t>
+          <t>Have an Admin create your account; open the invite email; set password; sign in.</t>
         </is>
       </c>
       <c r="D59" s="22" t="inlineStr">
         <is>
-          <t>Review queue, approved/rejected counts, registrations, hours, upcoming events + Roster links.</t>
+          <t>Invite email arrives with a working set-password link; you can sign in.</t>
         </is>
       </c>
       <c r="E59" s="23" t="n"/>
@@ -2905,22 +2905,22 @@
     <row r="60" ht="42" customHeight="1">
       <c r="A60" s="21" t="inlineStr">
         <is>
-          <t>SV5</t>
+          <t>SV3</t>
         </is>
       </c>
       <c r="B60" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to approve hours.</t>
+          <t>As a supervisor, I want the correct 7 left-menu tabs.</t>
         </is>
       </c>
       <c r="C60" s="22" t="inlineStr">
         <is>
-          <t>Pending Reviews → open → Approve.</t>
+          <t>Look at the left menu.</t>
         </is>
       </c>
       <c r="D60" s="22" t="inlineStr">
         <is>
-          <t>Approved; moves to Reviewed History; participant total updates; email sent.</t>
+          <t>Dashboard, Pending Reviews, Reviewed History, My Events, All Opportunities, My Hours, Help.</t>
         </is>
       </c>
       <c r="E60" s="23" t="n"/>
@@ -2930,22 +2930,22 @@
     <row r="61" ht="42" customHeight="1">
       <c r="A61" s="21" t="inlineStr">
         <is>
-          <t>SV6</t>
+          <t>SV4</t>
         </is>
       </c>
       <c r="B61" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to reject hours with a reason.</t>
+          <t>As a supervisor, I want a dashboard.</t>
         </is>
       </c>
       <c r="C61" s="22" t="inlineStr">
         <is>
-          <t>Reject without a reason, then with one.</t>
+          <t>Open the dashboard.</t>
         </is>
       </c>
       <c r="D61" s="22" t="inlineStr">
         <is>
-          <t>Blocked until a reason is given; then rejected and the participant notified.</t>
+          <t>Review queue, approved/rejected counts, registrations, hours, upcoming events + Roster links.</t>
         </is>
       </c>
       <c r="E61" s="23" t="n"/>
@@ -2955,22 +2955,22 @@
     <row r="62" ht="42" customHeight="1">
       <c r="A62" s="21" t="inlineStr">
         <is>
-          <t>SV7</t>
+          <t>SV5</t>
         </is>
       </c>
       <c r="B62" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to review external submissions.</t>
+          <t>As a supervisor, I want to approve hours.</t>
         </is>
       </c>
       <c r="C62" s="22" t="inlineStr">
         <is>
-          <t>Pending Reviews → external tab → approve/reject.</t>
+          <t>Pending Reviews → open → Approve.</t>
         </is>
       </c>
       <c r="D62" s="22" t="inlineStr">
         <is>
-          <t>External items reviewable, including any proof.</t>
+          <t>Approved; moves to Reviewed History; participant total updates; email sent.</t>
         </is>
       </c>
       <c r="E62" s="23" t="n"/>
@@ -2980,22 +2980,22 @@
     <row r="63" ht="42" customHeight="1">
       <c r="A63" s="21" t="inlineStr">
         <is>
-          <t>SV8</t>
+          <t>SV6</t>
         </is>
       </c>
       <c r="B63" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to create an event.</t>
+          <t>As a supervisor, I want to reject hours with a reason.</t>
         </is>
       </c>
       <c r="C63" s="22" t="inlineStr">
         <is>
-          <t>New Event → title, description, slot, address, date, times, capacity, grade limits → save.</t>
+          <t>Reject without a reason, then with one.</t>
         </is>
       </c>
       <c r="D63" s="22" t="inlineStr">
         <is>
-          <t>Credit auto-calculated from times; event created in My Events.</t>
+          <t>Blocked until a reason is given; then rejected and the participant notified.</t>
         </is>
       </c>
       <c r="E63" s="23" t="n"/>
@@ -3005,22 +3005,22 @@
     <row r="64" ht="42" customHeight="1">
       <c r="A64" s="21" t="inlineStr">
         <is>
-          <t>SV9</t>
+          <t>SV7</t>
         </is>
       </c>
       <c r="B64" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to edit an event.</t>
+          <t>As a supervisor, I want to review external submissions.</t>
         </is>
       </c>
       <c r="C64" s="22" t="inlineStr">
         <is>
-          <t>My Events → edit → save.</t>
+          <t>Pending Reviews → external tab → approve/reject.</t>
         </is>
       </c>
       <c r="D64" s="22" t="inlineStr">
         <is>
-          <t>Changes persist and show to participants.</t>
+          <t>External items reviewable, including any proof.</t>
         </is>
       </c>
       <c r="E64" s="23" t="n"/>
@@ -3030,22 +3030,22 @@
     <row r="65" ht="42" customHeight="1">
       <c r="A65" s="21" t="inlineStr">
         <is>
-          <t>SV10</t>
+          <t>SV8</t>
         </is>
       </c>
       <c r="B65" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to delete an event with no approved hours.</t>
+          <t>As a supervisor, I want to create an event.</t>
         </is>
       </c>
       <c r="C65" s="22" t="inlineStr">
         <is>
-          <t>Delete such an event → confirm.</t>
+          <t>New Event → title, description, slot, address, date, times, capacity, grade limits → save.</t>
         </is>
       </c>
       <c r="D65" s="22" t="inlineStr">
         <is>
-          <t>Event deleted.</t>
+          <t>Credit auto-calculated from times; event created in My Events.</t>
         </is>
       </c>
       <c r="E65" s="23" t="n"/>
@@ -3055,22 +3055,22 @@
     <row r="66" ht="42" customHeight="1">
       <c r="A66" s="21" t="inlineStr">
         <is>
-          <t>SV11</t>
+          <t>SV9</t>
         </is>
       </c>
       <c r="B66" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, deleting an event with approved hours is blocked.</t>
+          <t>As a supervisor, I want to edit an event.</t>
         </is>
       </c>
       <c r="C66" s="22" t="inlineStr">
         <is>
-          <t>Try to delete an event that has approved hours.</t>
+          <t>My Events → edit → save.</t>
         </is>
       </c>
       <c r="D66" s="22" t="inlineStr">
         <is>
-          <t>Blocked with a message that approved hours must be preserved.</t>
+          <t>Changes persist and show to participants.</t>
         </is>
       </c>
       <c r="E66" s="23" t="n"/>
@@ -3080,22 +3080,22 @@
     <row r="67" ht="42" customHeight="1">
       <c r="A67" s="21" t="inlineStr">
         <is>
-          <t>SV12</t>
+          <t>SV10</t>
         </is>
       </c>
       <c r="B67" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to see who signed up.</t>
+          <t>As a supervisor, I want to delete an event with no approved hours.</t>
         </is>
       </c>
       <c r="C67" s="22" t="inlineStr">
         <is>
-          <t>Open the event Roster.</t>
+          <t>Delete such an event → confirm.</t>
         </is>
       </c>
       <c r="D67" s="22" t="inlineStr">
         <is>
-          <t>Registrants listed with grade and status.</t>
+          <t>Event deleted.</t>
         </is>
       </c>
       <c r="E67" s="23" t="n"/>
@@ -3105,22 +3105,22 @@
     <row r="68" ht="42" customHeight="1">
       <c r="A68" s="21" t="inlineStr">
         <is>
-          <t>SV13</t>
+          <t>SV11</t>
         </is>
       </c>
       <c r="B68" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to check people in / mark no-show.</t>
+          <t>As a supervisor, deleting an event with approved hours is blocked.</t>
         </is>
       </c>
       <c r="C68" s="22" t="inlineStr">
         <is>
-          <t>On the roster, Check in and Mark no-show.</t>
+          <t>Try to delete an event that has approved hours.</t>
         </is>
       </c>
       <c r="D68" s="22" t="inlineStr">
         <is>
-          <t>Status updates and persists.</t>
+          <t>Blocked with a message that approved hours must be preserved.</t>
         </is>
       </c>
       <c r="E68" s="23" t="n"/>
@@ -3130,22 +3130,22 @@
     <row r="69" ht="42" customHeight="1">
       <c r="A69" s="21" t="inlineStr">
         <is>
-          <t>SV14</t>
+          <t>SV12</t>
         </is>
       </c>
       <c r="B69" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to message everyone signed up.</t>
+          <t>As a supervisor, I want to see who signed up.</t>
         </is>
       </c>
       <c r="C69" s="22" t="inlineStr">
         <is>
-          <t>Roster → Message attendees → subject+message → send (include guardians on).</t>
+          <t>Open the event Roster.</t>
         </is>
       </c>
       <c r="D69" s="22" t="inlineStr">
         <is>
-          <t>Each registrant (and guardians) emailed individually; recipient count shown.</t>
+          <t>Registrants listed with grade and status.</t>
         </is>
       </c>
       <c r="E69" s="23" t="n"/>
@@ -3155,22 +3155,22 @@
     <row r="70" ht="42" customHeight="1">
       <c r="A70" s="21" t="inlineStr">
         <is>
-          <t>SV15</t>
+          <t>SV13</t>
         </is>
       </c>
       <c r="B70" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want a history of what I reviewed.</t>
+          <t>As a supervisor, I want to check people in / mark no-show.</t>
         </is>
       </c>
       <c r="C70" s="22" t="inlineStr">
         <is>
-          <t>Open Reviewed History.</t>
+          <t>On the roster, Check in and Mark no-show.</t>
         </is>
       </c>
       <c r="D70" s="22" t="inlineStr">
         <is>
-          <t>Every approved/rejected item with dates and volunteers.</t>
+          <t>Status updates and persists.</t>
         </is>
       </c>
       <c r="E70" s="23" t="n"/>
@@ -3180,22 +3180,22 @@
     <row r="71" ht="42" customHeight="1">
       <c r="A71" s="21" t="inlineStr">
         <is>
-          <t>SV16</t>
+          <t>SV14</t>
         </is>
       </c>
       <c r="B71" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to browse all opportunities view-only.</t>
+          <t>As a supervisor, I want to message everyone signed up.</t>
         </is>
       </c>
       <c r="C71" s="22" t="inlineStr">
         <is>
-          <t>All Opportunities → search / upcoming-past.</t>
+          <t>Roster → Message attendees → subject+message → send (include guardians on).</t>
         </is>
       </c>
       <c r="D71" s="22" t="inlineStr">
         <is>
-          <t>Every event listed read-only; can't edit others' events.</t>
+          <t>Each registrant (and guardians) emailed individually; recipient count shown.</t>
         </is>
       </c>
       <c r="E71" s="23" t="n"/>
@@ -3205,22 +3205,22 @@
     <row r="72" ht="42" customHeight="1">
       <c r="A72" s="21" t="inlineStr">
         <is>
-          <t>SV17</t>
+          <t>SV15</t>
         </is>
       </c>
       <c r="B72" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to log my own adult hours.</t>
+          <t>As a supervisor, I want a history of what I reviewed.</t>
         </is>
       </c>
       <c r="C72" s="22" t="inlineStr">
         <is>
-          <t>My Hours → log an activity, date, hours → save.</t>
+          <t>Open Reviewed History.</t>
         </is>
       </c>
       <c r="D72" s="22" t="inlineStr">
         <is>
-          <t>Recorded instantly with a running total; clearly NOT part of the student competition.</t>
+          <t>Every approved/rejected item with dates and volunteers.</t>
         </is>
       </c>
       <c r="E72" s="23" t="n"/>
@@ -3230,22 +3230,22 @@
     <row r="73" ht="42" customHeight="1">
       <c r="A73" s="21" t="inlineStr">
         <is>
-          <t>SV18</t>
+          <t>SV16</t>
         </is>
       </c>
       <c r="B73" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to delete an adult-hours entry.</t>
+          <t>As a supervisor, I want to browse all opportunities view-only.</t>
         </is>
       </c>
       <c r="C73" s="22" t="inlineStr">
         <is>
-          <t>My Hours → delete an entry → confirm.</t>
+          <t>All Opportunities → search / upcoming-past.</t>
         </is>
       </c>
       <c r="D73" s="22" t="inlineStr">
         <is>
-          <t>Removed; total updates.</t>
+          <t>Every event listed read-only; can't edit others' events.</t>
         </is>
       </c>
       <c r="E73" s="23" t="n"/>
@@ -3255,110 +3255,110 @@
     <row r="74" ht="42" customHeight="1">
       <c r="A74" s="21" t="inlineStr">
         <is>
-          <t>SV19</t>
+          <t>SV17</t>
         </is>
       </c>
       <c r="B74" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I must NOT access user or org management.</t>
+          <t>As a supervisor, I want to log my own adult hours.</t>
         </is>
       </c>
       <c r="C74" s="22" t="inlineStr">
         <is>
-          <t>Look for Users / Organizations in the menu.</t>
+          <t>My Hours → log an activity, date, hours → save.</t>
         </is>
       </c>
       <c r="D74" s="22" t="inlineStr">
         <is>
-          <t>Those tabs are absent; direct URLs are blocked.</t>
+          <t>Recorded instantly with a running total; clearly NOT part of the student competition.</t>
         </is>
       </c>
       <c r="E74" s="23" t="n"/>
       <c r="F74" s="22" t="n"/>
       <c r="G74" s="23" t="n"/>
     </row>
-    <row r="75" ht="20" customHeight="1">
-      <c r="A75" s="19" t="inlineStr">
-        <is>
-          <t>Admin (org-scoped)</t>
-        </is>
-      </c>
-      <c r="B75" s="20" t="n"/>
-      <c r="C75" s="20" t="n"/>
-      <c r="D75" s="20" t="n"/>
-      <c r="E75" s="20" t="n"/>
-      <c r="F75" s="20" t="n"/>
-      <c r="G75" s="20" t="n"/>
+    <row r="75" ht="42" customHeight="1">
+      <c r="A75" s="21" t="inlineStr">
+        <is>
+          <t>SV18</t>
+        </is>
+      </c>
+      <c r="B75" s="22" t="inlineStr">
+        <is>
+          <t>As a supervisor, I want to delete an adult-hours entry.</t>
+        </is>
+      </c>
+      <c r="C75" s="22" t="inlineStr">
+        <is>
+          <t>My Hours → delete an entry → confirm.</t>
+        </is>
+      </c>
+      <c r="D75" s="22" t="inlineStr">
+        <is>
+          <t>Removed; total updates.</t>
+        </is>
+      </c>
+      <c r="E75" s="23" t="n"/>
+      <c r="F75" s="22" t="n"/>
+      <c r="G75" s="23" t="n"/>
     </row>
     <row r="76" ht="42" customHeight="1">
       <c r="A76" s="21" t="inlineStr">
         <is>
-          <t>AD1</t>
+          <t>SV19</t>
         </is>
       </c>
       <c r="B76" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I want the correct menu tabs.</t>
+          <t>As a supervisor, I must NOT access user or org management.</t>
         </is>
       </c>
       <c r="C76" s="22" t="inlineStr">
         <is>
-          <t>Look at the left menu.</t>
+          <t>Look for Users / Organizations in the menu.</t>
         </is>
       </c>
       <c r="D76" s="22" t="inlineStr">
         <is>
-          <t>Dashboard, Pending Reviews, Reviewed History, My Events, All Opportunities, Users, Organizations, My Hours, Help.</t>
+          <t>Those tabs are absent; direct URLs are blocked.</t>
         </is>
       </c>
       <c r="E76" s="23" t="n"/>
       <c r="F76" s="22" t="n"/>
       <c r="G76" s="23" t="n"/>
     </row>
-    <row r="77" ht="42" customHeight="1">
-      <c r="A77" s="21" t="inlineStr">
-        <is>
-          <t>AD2</t>
-        </is>
-      </c>
-      <c r="B77" s="22" t="inlineStr">
-        <is>
-          <t>As an Admin, I can do everything a supervisor can.</t>
-        </is>
-      </c>
-      <c r="C77" s="22" t="inlineStr">
-        <is>
-          <t>Spot-check: approve an item and create an event.</t>
-        </is>
-      </c>
-      <c r="D77" s="22" t="inlineStr">
-        <is>
-          <t>Both work.</t>
-        </is>
-      </c>
-      <c r="E77" s="23" t="n"/>
-      <c r="F77" s="22" t="n"/>
-      <c r="G77" s="23" t="n"/>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="19" t="inlineStr">
+        <is>
+          <t>Admin (org-scoped)</t>
+        </is>
+      </c>
+      <c r="B77" s="20" t="n"/>
+      <c r="C77" s="20" t="n"/>
+      <c r="D77" s="20" t="n"/>
+      <c r="E77" s="20" t="n"/>
+      <c r="F77" s="20" t="n"/>
+      <c r="G77" s="20" t="n"/>
     </row>
     <row r="78" ht="42" customHeight="1">
       <c r="A78" s="21" t="inlineStr">
         <is>
-          <t>AD3</t>
+          <t>AD1</t>
         </is>
       </c>
       <c r="B78" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I only see my org's non-admin users.</t>
+          <t>As an Admin, I want the correct menu tabs.</t>
         </is>
       </c>
       <c r="C78" s="22" t="inlineStr">
         <is>
-          <t>Open Users.</t>
+          <t>Look at the left menu.</t>
         </is>
       </c>
       <c r="D78" s="22" t="inlineStr">
         <is>
-          <t>Only participants/parents/supervisors in your org; no admins/super admins; no other orgs.</t>
+          <t>Dashboard, Pending Reviews, Reviewed History, My Events, All Opportunities, Users, Organizations, My Hours, Help.</t>
         </is>
       </c>
       <c r="E78" s="23" t="n"/>
@@ -3368,22 +3368,22 @@
     <row r="79" ht="42" customHeight="1">
       <c r="A79" s="21" t="inlineStr">
         <is>
-          <t>AD4</t>
+          <t>AD2</t>
         </is>
       </c>
       <c r="B79" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I want to add a supervisor.</t>
+          <t>As an Admin, I can do everything a supervisor can.</t>
         </is>
       </c>
       <c r="C79" s="22" t="inlineStr">
         <is>
-          <t>Users → Add user → Supervisor → save.</t>
+          <t>Spot-check: approve an item and create an event.</t>
         </is>
       </c>
       <c r="D79" s="22" t="inlineStr">
         <is>
-          <t>Supervisor created, stamped to your org; invite email sent.</t>
+          <t>Both work.</t>
         </is>
       </c>
       <c r="E79" s="23" t="n"/>
@@ -3393,22 +3393,22 @@
     <row r="80" ht="42" customHeight="1">
       <c r="A80" s="21" t="inlineStr">
         <is>
-          <t>AD5</t>
+          <t>AD3</t>
         </is>
       </c>
       <c r="B80" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I want to create a participant as a fallback.</t>
+          <t>As an Admin, I only see my org's non-admin users.</t>
         </is>
       </c>
       <c r="C80" s="22" t="inlineStr">
         <is>
-          <t>Users → Add user → Participant → save.</t>
+          <t>Open Users.</t>
         </is>
       </c>
       <c r="D80" s="22" t="inlineStr">
         <is>
-          <t>Participant created with a set-password invite (no silent password).</t>
+          <t>Only participants/parents/supervisors in your org; no admins/super admins; no other orgs.</t>
         </is>
       </c>
       <c r="E80" s="23" t="n"/>
@@ -3418,22 +3418,22 @@
     <row r="81" ht="42" customHeight="1">
       <c r="A81" s="21" t="inlineStr">
         <is>
-          <t>AD6</t>
+          <t>AD4</t>
         </is>
       </c>
       <c r="B81" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I want to grant participant hours.</t>
+          <t>As an Admin, I want to add a supervisor.</t>
         </is>
       </c>
       <c r="C81" s="22" t="inlineStr">
         <is>
-          <t>Open a participant in your org → Add hours.</t>
+          <t>Users → Add user → Supervisor → save.</t>
         </is>
       </c>
       <c r="D81" s="22" t="inlineStr">
         <is>
-          <t>Hours auto-approved; count toward their total/medals.</t>
+          <t>Supervisor created, stamped to your org; invite email sent.</t>
         </is>
       </c>
       <c r="E81" s="23" t="n"/>
@@ -3443,22 +3443,22 @@
     <row r="82" ht="42" customHeight="1">
       <c r="A82" s="21" t="inlineStr">
         <is>
-          <t>AD7</t>
+          <t>AD5</t>
         </is>
       </c>
       <c r="B82" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I want a participant's service record.</t>
+          <t>As an Admin, I want to create a participant as a fallback.</t>
         </is>
       </c>
       <c r="C82" s="22" t="inlineStr">
         <is>
-          <t>Users → Service record for a participant in your org.</t>
+          <t>Users → Add user → Participant → save.</t>
         </is>
       </c>
       <c r="D82" s="22" t="inlineStr">
         <is>
-          <t>Record opens.</t>
+          <t>Participant created with a set-password invite (no silent password).</t>
         </is>
       </c>
       <c r="E82" s="23" t="n"/>
@@ -3468,22 +3468,22 @@
     <row r="83" ht="42" customHeight="1">
       <c r="A83" s="21" t="inlineStr">
         <is>
-          <t>AD8</t>
+          <t>AD6</t>
         </is>
       </c>
       <c r="B83" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I want to edit/delete my org's users.</t>
+          <t>As an Admin, I want to grant participant hours.</t>
         </is>
       </c>
       <c r="C83" s="22" t="inlineStr">
         <is>
-          <t>Edit a name/phone; delete a test user.</t>
+          <t>Open a participant in your org → Add hours.</t>
         </is>
       </c>
       <c r="D83" s="22" t="inlineStr">
         <is>
-          <t>Changes apply within your org.</t>
+          <t>Hours auto-approved; count toward their total/medals.</t>
         </is>
       </c>
       <c r="E83" s="23" t="n"/>
@@ -3493,22 +3493,22 @@
     <row r="84" ht="42" customHeight="1">
       <c r="A84" s="21" t="inlineStr">
         <is>
-          <t>AD9</t>
+          <t>AD7</t>
         </is>
       </c>
       <c r="B84" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I must NOT act on users outside my org.</t>
+          <t>As an Admin, I want a participant's service record.</t>
         </is>
       </c>
       <c r="C84" s="22" t="inlineStr">
         <is>
-          <t>Attempt to reach another org's user (e.g. direct URL).</t>
+          <t>Users → Service record for a participant in your org.</t>
         </is>
       </c>
       <c r="D84" s="22" t="inlineStr">
         <is>
-          <t>Blocked / not visible.</t>
+          <t>Record opens.</t>
         </is>
       </c>
       <c r="E84" s="23" t="n"/>
@@ -3518,22 +3518,22 @@
     <row r="85" ht="42" customHeight="1">
       <c r="A85" s="21" t="inlineStr">
         <is>
-          <t>AD10</t>
+          <t>AD8</t>
         </is>
       </c>
       <c r="B85" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I cannot grant Admin access or manage admins.</t>
+          <t>As an Admin, I want to edit/delete my org's users.</t>
         </is>
       </c>
       <c r="C85" s="22" t="inlineStr">
         <is>
-          <t>Look for the 'grant Admin access' action.</t>
+          <t>Edit a name/phone; delete a test user.</t>
         </is>
       </c>
       <c r="D85" s="22" t="inlineStr">
         <is>
-          <t>No such button; attempts are blocked server-side.</t>
+          <t>Changes apply within your org.</t>
         </is>
       </c>
       <c r="E85" s="23" t="n"/>
@@ -3543,22 +3543,22 @@
     <row r="86" ht="42" customHeight="1">
       <c r="A86" s="21" t="inlineStr">
         <is>
-          <t>AD11</t>
+          <t>AD9</t>
         </is>
       </c>
       <c r="B86" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I see and edit only my own organization.</t>
+          <t>As an Admin, I must NOT act on users outside my org.</t>
         </is>
       </c>
       <c r="C86" s="22" t="inlineStr">
         <is>
-          <t>Open Organizations.</t>
+          <t>Attempt to reach another org's user (e.g. direct URL).</t>
         </is>
       </c>
       <c r="D86" s="22" t="inlineStr">
         <is>
-          <t>Only your org shows; you can edit its settings.</t>
+          <t>Blocked / not visible.</t>
         </is>
       </c>
       <c r="E86" s="23" t="n"/>
@@ -3568,22 +3568,22 @@
     <row r="87" ht="42" customHeight="1">
       <c r="A87" s="21" t="inlineStr">
         <is>
-          <t>AD12</t>
+          <t>AD10</t>
         </is>
       </c>
       <c r="B87" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I want to generate/rotate my org's join code.</t>
+          <t>As an Admin, I cannot grant Admin access or manage admins.</t>
         </is>
       </c>
       <c r="C87" s="22" t="inlineStr">
         <is>
-          <t>Organizations → set/generate a join code → save.</t>
+          <t>Look for the 'grant Admin access' action.</t>
         </is>
       </c>
       <c r="D87" s="22" t="inlineStr">
         <is>
-          <t>Join code saved; usable at sign-up.</t>
+          <t>No such button; attempts are blocked server-side.</t>
         </is>
       </c>
       <c r="E87" s="23" t="n"/>
@@ -3593,22 +3593,22 @@
     <row r="88" ht="42" customHeight="1">
       <c r="A88" s="21" t="inlineStr">
         <is>
-          <t>AD13</t>
+          <t>AD11</t>
         </is>
       </c>
       <c r="B88" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I cannot create organizations.</t>
+          <t>As an Admin, I see and edit only my own organization.</t>
         </is>
       </c>
       <c r="C88" s="22" t="inlineStr">
         <is>
-          <t>Look for 'Add organization'.</t>
+          <t>Open Organizations.</t>
         </is>
       </c>
       <c r="D88" s="22" t="inlineStr">
         <is>
-          <t>No Add button; creation blocked.</t>
+          <t>Only your org shows; you can edit its settings.</t>
         </is>
       </c>
       <c r="E88" s="23" t="n"/>
@@ -3618,110 +3618,110 @@
     <row r="89" ht="42" customHeight="1">
       <c r="A89" s="21" t="inlineStr">
         <is>
-          <t>AD14</t>
+          <t>AD12</t>
         </is>
       </c>
       <c r="B89" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I cannot change the recycling cans total.</t>
+          <t>As an Admin, I want to generate/rotate my org's join code.</t>
         </is>
       </c>
       <c r="C89" s="22" t="inlineStr">
         <is>
-          <t>Look for the cans/bin admin control.</t>
+          <t>Organizations → set/generate a join code → save.</t>
         </is>
       </c>
       <c r="D89" s="22" t="inlineStr">
         <is>
-          <t>Not available (Super Admin only).</t>
+          <t>Join code saved; usable at sign-up.</t>
         </is>
       </c>
       <c r="E89" s="23" t="n"/>
       <c r="F89" s="22" t="n"/>
       <c r="G89" s="23" t="n"/>
     </row>
-    <row r="90" ht="20" customHeight="1">
-      <c r="A90" s="19" t="inlineStr">
-        <is>
-          <t>Super Admin (global)</t>
-        </is>
-      </c>
-      <c r="B90" s="20" t="n"/>
-      <c r="C90" s="20" t="n"/>
-      <c r="D90" s="20" t="n"/>
-      <c r="E90" s="20" t="n"/>
-      <c r="F90" s="20" t="n"/>
-      <c r="G90" s="20" t="n"/>
+    <row r="90" ht="42" customHeight="1">
+      <c r="A90" s="21" t="inlineStr">
+        <is>
+          <t>AD13</t>
+        </is>
+      </c>
+      <c r="B90" s="22" t="inlineStr">
+        <is>
+          <t>As an Admin, I cannot create organizations.</t>
+        </is>
+      </c>
+      <c r="C90" s="22" t="inlineStr">
+        <is>
+          <t>Look for 'Add organization'.</t>
+        </is>
+      </c>
+      <c r="D90" s="22" t="inlineStr">
+        <is>
+          <t>No Add button; creation blocked.</t>
+        </is>
+      </c>
+      <c r="E90" s="23" t="n"/>
+      <c r="F90" s="22" t="n"/>
+      <c r="G90" s="23" t="n"/>
     </row>
     <row r="91" ht="42" customHeight="1">
       <c r="A91" s="21" t="inlineStr">
         <is>
-          <t>SA1</t>
+          <t>AD14</t>
         </is>
       </c>
       <c r="B91" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want the correct menu tabs.</t>
+          <t>As an Admin, I cannot change the recycling cans total.</t>
         </is>
       </c>
       <c r="C91" s="22" t="inlineStr">
         <is>
-          <t>Look at the left menu.</t>
+          <t>Look for the cans/bin admin control.</t>
         </is>
       </c>
       <c r="D91" s="22" t="inlineStr">
         <is>
-          <t>Dashboard, Reports, Users, Events, Organizations (Help in footer).</t>
+          <t>Not available (Super Admin only).</t>
         </is>
       </c>
       <c r="E91" s="23" t="n"/>
       <c r="F91" s="22" t="n"/>
       <c r="G91" s="23" t="n"/>
     </row>
-    <row r="92" ht="42" customHeight="1">
-      <c r="A92" s="21" t="inlineStr">
-        <is>
-          <t>SA2</t>
-        </is>
-      </c>
-      <c r="B92" s="22" t="inlineStr">
-        <is>
-          <t>As a Super Admin, I can do everything an Admin can, across all orgs.</t>
-        </is>
-      </c>
-      <c r="C92" s="22" t="inlineStr">
-        <is>
-          <t>Spot-check user + org actions on more than one org.</t>
-        </is>
-      </c>
-      <c r="D92" s="22" t="inlineStr">
-        <is>
-          <t>All allowed regardless of org.</t>
-        </is>
-      </c>
-      <c r="E92" s="23" t="n"/>
-      <c r="F92" s="22" t="n"/>
-      <c r="G92" s="23" t="n"/>
+    <row r="92" ht="20" customHeight="1">
+      <c r="A92" s="19" t="inlineStr">
+        <is>
+          <t>Super Admin (global)</t>
+        </is>
+      </c>
+      <c r="B92" s="20" t="n"/>
+      <c r="C92" s="20" t="n"/>
+      <c r="D92" s="20" t="n"/>
+      <c r="E92" s="20" t="n"/>
+      <c r="F92" s="20" t="n"/>
+      <c r="G92" s="20" t="n"/>
     </row>
     <row r="93" ht="42" customHeight="1">
       <c r="A93" s="21" t="inlineStr">
         <is>
-          <t>SA3</t>
+          <t>SA1</t>
         </is>
       </c>
       <c r="B93" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to create users incl. Supervisor and Super Admin.</t>
+          <t>As a Super Admin, I want the correct menu tabs.</t>
         </is>
       </c>
       <c r="C93" s="22" t="inlineStr">
         <is>
-          <t>Users → Add user → each role.</t>
+          <t>Look at the left menu.</t>
         </is>
       </c>
       <c r="D93" s="22" t="inlineStr">
         <is>
-          <t>Participant/Supervisor/Super Admin options available; account created + invite email.</t>
+          <t>Dashboard, Reports, Users, Events, Organizations (Help in footer).</t>
         </is>
       </c>
       <c r="E93" s="23" t="n"/>
@@ -3731,22 +3731,22 @@
     <row r="94" ht="42" customHeight="1">
       <c r="A94" s="21" t="inlineStr">
         <is>
-          <t>SA4</t>
+          <t>SA2</t>
         </is>
       </c>
       <c r="B94" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to grant/revoke Admin access.</t>
+          <t>As a Super Admin, I can do everything an Admin can, across all orgs.</t>
         </is>
       </c>
       <c r="C94" s="22" t="inlineStr">
         <is>
-          <t>Open a user → grant Admin access → check org(s) → save; then uncheck all → save.</t>
+          <t>Spot-check user + org actions on more than one org.</t>
         </is>
       </c>
       <c r="D94" s="22" t="inlineStr">
         <is>
-          <t>Checking orgs makes an Admin; unchecking all reverts to participant.</t>
+          <t>All allowed regardless of org.</t>
         </is>
       </c>
       <c r="E94" s="23" t="n"/>
@@ -3756,22 +3756,22 @@
     <row r="95" ht="42" customHeight="1">
       <c r="A95" s="21" t="inlineStr">
         <is>
-          <t>SA5</t>
+          <t>SA3</t>
         </is>
       </c>
       <c r="B95" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to create organizations + join codes.</t>
+          <t>As a Super Admin, I want to create users incl. Supervisor and Super Admin.</t>
         </is>
       </c>
       <c r="C95" s="22" t="inlineStr">
         <is>
-          <t>Organizations → Add organization → set details + join code.</t>
+          <t>Users → Add user → each role.</t>
         </is>
       </c>
       <c r="D95" s="22" t="inlineStr">
         <is>
-          <t>Org created with its join code.</t>
+          <t>Participant/Supervisor/Super Admin options available; account created + invite email.</t>
         </is>
       </c>
       <c r="E95" s="23" t="n"/>
@@ -3781,22 +3781,22 @@
     <row r="96" ht="42" customHeight="1">
       <c r="A96" s="21" t="inlineStr">
         <is>
-          <t>SA6</t>
+          <t>SA4</t>
         </is>
       </c>
       <c r="B96" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to find users by type.</t>
+          <t>As a Super Admin, I want to grant/revoke Admin access.</t>
         </is>
       </c>
       <c r="C96" s="22" t="inlineStr">
         <is>
-          <t>Users → role filter pills + search.</t>
+          <t>Open a user → grant Admin access → check org(s) → save; then uncheck all → save.</t>
         </is>
       </c>
       <c r="D96" s="22" t="inlineStr">
         <is>
-          <t>Filter by role with counts; search by name/email across all orgs.</t>
+          <t>Checking orgs makes an Admin; unchecking all reverts to participant.</t>
         </is>
       </c>
       <c r="E96" s="23" t="n"/>
@@ -3806,22 +3806,22 @@
     <row r="97" ht="42" customHeight="1">
       <c r="A97" s="21" t="inlineStr">
         <is>
-          <t>SA7</t>
+          <t>SA5</t>
         </is>
       </c>
       <c r="B97" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to search events.</t>
+          <t>As a Super Admin, I want to create organizations + join codes.</t>
         </is>
       </c>
       <c r="C97" s="22" t="inlineStr">
         <is>
-          <t>Events → search + date range; check supervisor/org per card.</t>
+          <t>Organizations → Add organization → set details + join code.</t>
         </is>
       </c>
       <c r="D97" s="22" t="inlineStr">
         <is>
-          <t>Filters work; each event shows supervisor and organization.</t>
+          <t>Org created with its join code.</t>
         </is>
       </c>
       <c r="E97" s="23" t="n"/>
@@ -3831,22 +3831,22 @@
     <row r="98" ht="42" customHeight="1">
       <c r="A98" s="21" t="inlineStr">
         <is>
-          <t>SA8</t>
+          <t>SA6</t>
         </is>
       </c>
       <c r="B98" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want clear event-visibility labels.</t>
+          <t>As a Super Admin, I want to find users by type.</t>
         </is>
       </c>
       <c r="C98" s="22" t="inlineStr">
         <is>
-          <t>New Event → 'Who can see this'.</t>
+          <t>Users → role filter pills + search.</t>
         </is>
       </c>
       <c r="D98" s="22" t="inlineStr">
         <is>
-          <t>'Open to all (community)' and 'Only &lt;org&gt; students' with helper text.</t>
+          <t>Filter by role with counts; search by name/email across all orgs.</t>
         </is>
       </c>
       <c r="E98" s="23" t="n"/>
@@ -3856,22 +3856,22 @@
     <row r="99" ht="42" customHeight="1">
       <c r="A99" s="21" t="inlineStr">
         <is>
-          <t>SA9</t>
+          <t>SA7</t>
         </is>
       </c>
       <c r="B99" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want program-wide reports.</t>
+          <t>As a Super Admin, I want to search events.</t>
         </is>
       </c>
       <c r="C99" s="22" t="inlineStr">
         <is>
-          <t>Open Reports / Dashboard.</t>
+          <t>Events → search + date range; check supervisor/org per card.</t>
         </is>
       </c>
       <c r="D99" s="22" t="inlineStr">
         <is>
-          <t>Totals and charts across the whole program.</t>
+          <t>Filters work; each event shows supervisor and organization.</t>
         </is>
       </c>
       <c r="E99" s="23" t="n"/>
@@ -3881,22 +3881,22 @@
     <row r="100" ht="42" customHeight="1">
       <c r="A100" s="21" t="inlineStr">
         <is>
-          <t>SA10</t>
+          <t>SA8</t>
         </is>
       </c>
       <c r="B100" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to verify email works.</t>
+          <t>As a Super Admin, I want clear event-visibility labels.</t>
         </is>
       </c>
       <c r="C100" s="22" t="inlineStr">
         <is>
-          <t>Dashboard → Send test email.</t>
+          <t>New Event → 'Who can see this'.</t>
         </is>
       </c>
       <c r="D100" s="22" t="inlineStr">
         <is>
-          <t>Result shown (success or the exact failure reason).</t>
+          <t>'Open to all (community)' and 'Only &lt;org&gt; students' with helper text.</t>
         </is>
       </c>
       <c r="E100" s="23" t="n"/>
@@ -3906,22 +3906,22 @@
     <row r="101" ht="42" customHeight="1">
       <c r="A101" s="21" t="inlineStr">
         <is>
-          <t>SA11</t>
+          <t>SA9</t>
         </is>
       </c>
       <c r="B101" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to update the recycling cans total.</t>
+          <t>As a Super Admin, I want program-wide reports.</t>
         </is>
       </c>
       <c r="C101" s="22" t="inlineStr">
         <is>
-          <t>Use the cans/bin admin control.</t>
+          <t>Open Reports / Dashboard.</t>
         </is>
       </c>
       <c r="D101" s="22" t="inlineStr">
         <is>
-          <t>Total updates; the ribbon reflects it.</t>
+          <t>Totals and charts across the whole program.</t>
         </is>
       </c>
       <c r="E101" s="23" t="n"/>
@@ -3931,102 +3931,152 @@
     <row r="102" ht="42" customHeight="1">
       <c r="A102" s="21" t="inlineStr">
         <is>
-          <t>SA12</t>
+          <t>SA10</t>
         </is>
       </c>
       <c r="B102" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want hours + records for any user.</t>
+          <t>As a Super Admin, I want to verify email works.</t>
         </is>
       </c>
       <c r="C102" s="22" t="inlineStr">
         <is>
-          <t>Add manual hours / open service record for any participant.</t>
+          <t>Dashboard → Send test email.</t>
         </is>
       </c>
       <c r="D102" s="22" t="inlineStr">
         <is>
-          <t>Works for any org.</t>
+          <t>Result shown (success or the exact failure reason).</t>
         </is>
       </c>
       <c r="E102" s="23" t="n"/>
       <c r="F102" s="22" t="n"/>
       <c r="G102" s="23" t="n"/>
     </row>
-    <row r="103" ht="20" customHeight="1">
-      <c r="A103" s="19" t="inlineStr">
-        <is>
-          <t>Cross-cutting</t>
-        </is>
-      </c>
-      <c r="B103" s="20" t="n"/>
-      <c r="C103" s="20" t="n"/>
-      <c r="D103" s="20" t="n"/>
-      <c r="E103" s="20" t="n"/>
-      <c r="F103" s="20" t="n"/>
-      <c r="G103" s="20" t="n"/>
+    <row r="103" ht="42" customHeight="1">
+      <c r="A103" s="21" t="inlineStr">
+        <is>
+          <t>SA11</t>
+        </is>
+      </c>
+      <c r="B103" s="22" t="inlineStr">
+        <is>
+          <t>As a Super Admin, I want to update the recycling cans total.</t>
+        </is>
+      </c>
+      <c r="C103" s="22" t="inlineStr">
+        <is>
+          <t>Use the cans/bin admin control.</t>
+        </is>
+      </c>
+      <c r="D103" s="22" t="inlineStr">
+        <is>
+          <t>Total updates; the ribbon reflects it.</t>
+        </is>
+      </c>
+      <c r="E103" s="23" t="n"/>
+      <c r="F103" s="22" t="n"/>
+      <c r="G103" s="23" t="n"/>
     </row>
     <row r="104" ht="42" customHeight="1">
       <c r="A104" s="21" t="inlineStr">
         <is>
-          <t>X1</t>
+          <t>SA12</t>
         </is>
       </c>
       <c r="B104" s="22" t="inlineStr">
         <is>
-          <t>As a phone user, I want a usable mobile layout.</t>
+          <t>As a Super Admin, I want hours + records for any user.</t>
         </is>
       </c>
       <c r="C104" s="22" t="inlineStr">
         <is>
-          <t>Open at phone width; use the menu drawer.</t>
+          <t>Add manual hours / open service record for any participant.</t>
         </is>
       </c>
       <c r="D104" s="22" t="inlineStr">
         <is>
-          <t>Layout adapts; drawer opens/closes; no horizontal scroll.</t>
+          <t>Works for any org.</t>
         </is>
       </c>
       <c r="E104" s="23" t="n"/>
       <c r="F104" s="22" t="n"/>
       <c r="G104" s="23" t="n"/>
     </row>
-    <row r="105" ht="42" customHeight="1">
-      <c r="A105" s="21" t="inlineStr">
+    <row r="105" ht="20" customHeight="1">
+      <c r="A105" s="19" t="inlineStr">
+        <is>
+          <t>Cross-cutting</t>
+        </is>
+      </c>
+      <c r="B105" s="20" t="n"/>
+      <c r="C105" s="20" t="n"/>
+      <c r="D105" s="20" t="n"/>
+      <c r="E105" s="20" t="n"/>
+      <c r="F105" s="20" t="n"/>
+      <c r="G105" s="20" t="n"/>
+    </row>
+    <row r="106" ht="42" customHeight="1">
+      <c r="A106" s="21" t="inlineStr">
+        <is>
+          <t>X1</t>
+        </is>
+      </c>
+      <c r="B106" s="22" t="inlineStr">
+        <is>
+          <t>As a phone user, I want a usable mobile layout.</t>
+        </is>
+      </c>
+      <c r="C106" s="22" t="inlineStr">
+        <is>
+          <t>Open at phone width; use the menu drawer.</t>
+        </is>
+      </c>
+      <c r="D106" s="22" t="inlineStr">
+        <is>
+          <t>Layout adapts; drawer opens/closes; no horizontal scroll.</t>
+        </is>
+      </c>
+      <c r="E106" s="23" t="n"/>
+      <c r="F106" s="22" t="n"/>
+      <c r="G106" s="23" t="n"/>
+    </row>
+    <row r="107" ht="42" customHeight="1">
+      <c r="A107" s="21" t="inlineStr">
         <is>
           <t>X2</t>
         </is>
       </c>
-      <c r="B105" s="22" t="inlineStr">
+      <c r="B107" s="22" t="inlineStr">
         <is>
           <t>As a visitor, I want the recycling ribbon on the login page.</t>
         </is>
       </c>
-      <c r="C105" s="22" t="inlineStr">
+      <c r="C107" s="22" t="inlineStr">
         <is>
           <t>Open login signed out.</t>
         </is>
       </c>
-      <c r="D105" s="22" t="inlineStr">
+      <c r="D107" s="22" t="inlineStr">
         <is>
           <t>Green ribbon shows on login.</t>
         </is>
       </c>
-      <c r="E105" s="23" t="n"/>
-      <c r="F105" s="22" t="n"/>
-      <c r="G105" s="23" t="n"/>
+      <c r="E107" s="23" t="n"/>
+      <c r="F107" s="22" t="n"/>
+      <c r="G107" s="23" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A55:G55"/>
+    <mergeCell ref="A77:G77"/>
+    <mergeCell ref="A105:G105"/>
     <mergeCell ref="A35:G35"/>
-    <mergeCell ref="A90:G90"/>
-    <mergeCell ref="A49:G49"/>
+    <mergeCell ref="A92:G92"/>
+    <mergeCell ref="A57:G57"/>
+    <mergeCell ref="A51:G51"/>
     <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A103:G103"/>
-    <mergeCell ref="A75:G75"/>
   </mergeCells>
   <conditionalFormatting sqref="E4:E9">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
@@ -4050,7 +4100,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E36:E48">
+  <conditionalFormatting sqref="E36:E50">
     <cfRule type="cellIs" priority="7" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -4061,7 +4111,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E50:E54">
+  <conditionalFormatting sqref="E52:E56">
     <cfRule type="cellIs" priority="10" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -4072,7 +4122,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E56:E74">
+  <conditionalFormatting sqref="E58:E76">
     <cfRule type="cellIs" priority="13" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -4083,7 +4133,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E76:E89">
+  <conditionalFormatting sqref="E78:E91">
     <cfRule type="cellIs" priority="16" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -4094,7 +4144,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E91:E102">
+  <conditionalFormatting sqref="E93:E104">
     <cfRule type="cellIs" priority="19" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -4105,7 +4155,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E104:E105">
+  <conditionalFormatting sqref="E106:E107">
     <cfRule type="cellIs" priority="22" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -4117,7 +4167,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E4:E9 E11:E34 E36:E48 E50:E54 E56:E74 E76:E89 E91:E102 E104:E105" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E4:E9 E11:E34 E36:E50 E52:E56 E58:E76 E78:E91 E93:E104 E106:E107" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pass,Fail,Blocked,Not tested,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4131,7 +4181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G105"/>
+  <dimension ref="A1:G107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5307,88 +5357,88 @@
       <c r="F48" s="22" t="n"/>
       <c r="G48" s="23" t="n"/>
     </row>
-    <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="19" t="inlineStr">
-        <is>
-          <t>Parent — viewer (grades 6–12 student)</t>
-        </is>
-      </c>
-      <c r="B49" s="20" t="n"/>
-      <c r="C49" s="20" t="n"/>
-      <c r="D49" s="20" t="n"/>
-      <c r="E49" s="20" t="n"/>
-      <c r="F49" s="20" t="n"/>
-      <c r="G49" s="20" t="n"/>
+    <row r="49" ht="42" customHeight="1">
+      <c r="A49" s="21" t="inlineStr">
+        <is>
+          <t>PE14</t>
+        </is>
+      </c>
+      <c r="B49" s="22" t="inlineStr">
+        <is>
+          <t>As a parent, I want to log my child's outside/nonprofit volunteering.</t>
+        </is>
+      </c>
+      <c r="C49" s="22" t="inlineStr">
+        <is>
+          <t>Child card → 'Outside hours' → fill activity, org, date, hours, supervisor → Submit.</t>
+        </is>
+      </c>
+      <c r="D49" s="22" t="inlineStr">
+        <is>
+          <t>External hours submitted for the child and sent for supervisor approval (proof required over 5h).</t>
+        </is>
+      </c>
+      <c r="E49" s="23" t="n"/>
+      <c r="F49" s="22" t="n"/>
+      <c r="G49" s="23" t="n"/>
     </row>
     <row r="50" ht="42" customHeight="1">
       <c r="A50" s="21" t="inlineStr">
         <is>
-          <t>PV1</t>
+          <t>PE15</t>
         </is>
       </c>
       <c r="B50" s="22" t="inlineStr">
         <is>
-          <t>As a parent of a 6–12 student, I want to register for view-only access.</t>
+          <t>As a parent, I want my child's verified service record.</t>
         </is>
       </c>
       <c r="C50" s="22" t="inlineStr">
         <is>
-          <t>Create account → parent of a 6–12 student.</t>
+          <t>Child card → 'Service record'.</t>
         </is>
       </c>
       <c r="D50" s="22" t="inlineStr">
         <is>
-          <t>Account created; no invite required to register.</t>
+          <t>The child's itemized record opens; Print / Save-as-PDF works.</t>
         </is>
       </c>
       <c r="E50" s="23" t="n"/>
       <c r="F50" s="22" t="n"/>
       <c r="G50" s="23" t="n"/>
     </row>
-    <row r="51" ht="42" customHeight="1">
-      <c r="A51" s="21" t="inlineStr">
-        <is>
-          <t>PV2</t>
-        </is>
-      </c>
-      <c r="B51" s="22" t="inlineStr">
-        <is>
-          <t>As a viewer parent, my student links automatically by email.</t>
-        </is>
-      </c>
-      <c r="C51" s="22" t="inlineStr">
-        <is>
-          <t>Have a student enter this exact email as their parent email (before or after you register).</t>
-        </is>
-      </c>
-      <c r="D51" s="22" t="inlineStr">
-        <is>
-          <t>The student appears on your dashboard automatically; empty until then.</t>
-        </is>
-      </c>
-      <c r="E51" s="23" t="n"/>
-      <c r="F51" s="22" t="n"/>
-      <c r="G51" s="23" t="n"/>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="19" t="inlineStr">
+        <is>
+          <t>Parent — viewer (grades 6–12 student)</t>
+        </is>
+      </c>
+      <c r="B51" s="20" t="n"/>
+      <c r="C51" s="20" t="n"/>
+      <c r="D51" s="20" t="n"/>
+      <c r="E51" s="20" t="n"/>
+      <c r="F51" s="20" t="n"/>
+      <c r="G51" s="20" t="n"/>
     </row>
     <row r="52" ht="42" customHeight="1">
       <c r="A52" s="21" t="inlineStr">
         <is>
-          <t>PV3</t>
+          <t>PV1</t>
         </is>
       </c>
       <c r="B52" s="22" t="inlineStr">
         <is>
-          <t>As a viewer parent, I want to see my student's schedule/progress.</t>
+          <t>As a parent of a 6–12 student, I want to register for view-only access.</t>
         </is>
       </c>
       <c r="C52" s="22" t="inlineStr">
         <is>
-          <t>Open the dashboard.</t>
+          <t>Create account → parent of a 6–12 student.</t>
         </is>
       </c>
       <c r="D52" s="22" t="inlineStr">
         <is>
-          <t>View-only schedule and progress.</t>
+          <t>Account created; no invite required to register.</t>
         </is>
       </c>
       <c r="E52" s="23" t="n"/>
@@ -5398,22 +5448,22 @@
     <row r="53" ht="42" customHeight="1">
       <c r="A53" s="21" t="inlineStr">
         <is>
-          <t>PV4</t>
+          <t>PV2</t>
         </is>
       </c>
       <c r="B53" s="22" t="inlineStr">
         <is>
-          <t>As a viewer parent, I do NOT sign the student up.</t>
+          <t>As a viewer parent, my student links automatically by email.</t>
         </is>
       </c>
       <c r="C53" s="22" t="inlineStr">
         <is>
-          <t>Look for a sign-up action.</t>
+          <t>Have a student enter this exact email as their parent email (before or after you register).</t>
         </is>
       </c>
       <c r="D53" s="22" t="inlineStr">
         <is>
-          <t>No sign-up on the student's behalf — the student self-serves.</t>
+          <t>The student appears on your dashboard automatically; empty until then.</t>
         </is>
       </c>
       <c r="E53" s="23" t="n"/>
@@ -5423,110 +5473,110 @@
     <row r="54" ht="42" customHeight="1">
       <c r="A54" s="21" t="inlineStr">
         <is>
-          <t>PV5</t>
+          <t>PV3</t>
         </is>
       </c>
       <c r="B54" s="22" t="inlineStr">
         <is>
-          <t>As a viewer parent, I want to invite a co-guardian.</t>
+          <t>As a viewer parent, I want to see my student's schedule/progress.</t>
         </is>
       </c>
       <c r="C54" s="22" t="inlineStr">
         <is>
-          <t>Invite a co-guardian by email.</t>
+          <t>Open the dashboard.</t>
         </is>
       </c>
       <c r="D54" s="22" t="inlineStr">
         <is>
-          <t>Invite email sent; shared access on registration.</t>
+          <t>View-only schedule and progress.</t>
         </is>
       </c>
       <c r="E54" s="23" t="n"/>
       <c r="F54" s="22" t="n"/>
       <c r="G54" s="23" t="n"/>
     </row>
-    <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="19" t="inlineStr">
-        <is>
-          <t>Supervisor (created by an Admin)</t>
-        </is>
-      </c>
-      <c r="B55" s="20" t="n"/>
-      <c r="C55" s="20" t="n"/>
-      <c r="D55" s="20" t="n"/>
-      <c r="E55" s="20" t="n"/>
-      <c r="F55" s="20" t="n"/>
-      <c r="G55" s="20" t="n"/>
+    <row r="55" ht="42" customHeight="1">
+      <c r="A55" s="21" t="inlineStr">
+        <is>
+          <t>PV4</t>
+        </is>
+      </c>
+      <c r="B55" s="22" t="inlineStr">
+        <is>
+          <t>As a viewer parent, I do NOT sign the student up.</t>
+        </is>
+      </c>
+      <c r="C55" s="22" t="inlineStr">
+        <is>
+          <t>Look for a sign-up action.</t>
+        </is>
+      </c>
+      <c r="D55" s="22" t="inlineStr">
+        <is>
+          <t>No sign-up on the student's behalf — the student self-serves.</t>
+        </is>
+      </c>
+      <c r="E55" s="23" t="n"/>
+      <c r="F55" s="22" t="n"/>
+      <c r="G55" s="23" t="n"/>
     </row>
     <row r="56" ht="42" customHeight="1">
       <c r="A56" s="21" t="inlineStr">
         <is>
-          <t>SV1</t>
+          <t>PV5</t>
         </is>
       </c>
       <c r="B56" s="22" t="inlineStr">
         <is>
-          <t>As the program, a supervisor cannot self-register.</t>
+          <t>As a viewer parent, I want to invite a co-guardian.</t>
         </is>
       </c>
       <c r="C56" s="22" t="inlineStr">
         <is>
-          <t>Review the sign-up options.</t>
+          <t>Invite a co-guardian by email.</t>
         </is>
       </c>
       <c r="D56" s="22" t="inlineStr">
         <is>
-          <t>No supervisor option exists on registration.</t>
+          <t>Invite email sent; shared access on registration.</t>
         </is>
       </c>
       <c r="E56" s="23" t="n"/>
       <c r="F56" s="22" t="n"/>
       <c r="G56" s="23" t="n"/>
     </row>
-    <row r="57" ht="42" customHeight="1">
-      <c r="A57" s="21" t="inlineStr">
-        <is>
-          <t>SV2</t>
-        </is>
-      </c>
-      <c r="B57" s="22" t="inlineStr">
-        <is>
-          <t>As a new supervisor, I get an invite to set my password.</t>
-        </is>
-      </c>
-      <c r="C57" s="22" t="inlineStr">
-        <is>
-          <t>Have an Admin create your account; open the invite email; set password; sign in.</t>
-        </is>
-      </c>
-      <c r="D57" s="22" t="inlineStr">
-        <is>
-          <t>Invite email arrives with a working set-password link; you can sign in.</t>
-        </is>
-      </c>
-      <c r="E57" s="23" t="n"/>
-      <c r="F57" s="22" t="n"/>
-      <c r="G57" s="23" t="n"/>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="19" t="inlineStr">
+        <is>
+          <t>Supervisor (created by an Admin)</t>
+        </is>
+      </c>
+      <c r="B57" s="20" t="n"/>
+      <c r="C57" s="20" t="n"/>
+      <c r="D57" s="20" t="n"/>
+      <c r="E57" s="20" t="n"/>
+      <c r="F57" s="20" t="n"/>
+      <c r="G57" s="20" t="n"/>
     </row>
     <row r="58" ht="42" customHeight="1">
       <c r="A58" s="21" t="inlineStr">
         <is>
-          <t>SV3</t>
+          <t>SV1</t>
         </is>
       </c>
       <c r="B58" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want the correct 7 left-menu tabs.</t>
+          <t>As the program, a supervisor cannot self-register.</t>
         </is>
       </c>
       <c r="C58" s="22" t="inlineStr">
         <is>
-          <t>Look at the left menu.</t>
+          <t>Review the sign-up options.</t>
         </is>
       </c>
       <c r="D58" s="22" t="inlineStr">
         <is>
-          <t>Dashboard, Pending Reviews, Reviewed History, My Events, All Opportunities, My Hours, Help.</t>
+          <t>No supervisor option exists on registration.</t>
         </is>
       </c>
       <c r="E58" s="23" t="n"/>
@@ -5536,22 +5586,22 @@
     <row r="59" ht="42" customHeight="1">
       <c r="A59" s="21" t="inlineStr">
         <is>
-          <t>SV4</t>
+          <t>SV2</t>
         </is>
       </c>
       <c r="B59" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want a dashboard.</t>
+          <t>As a new supervisor, I get an invite to set my password.</t>
         </is>
       </c>
       <c r="C59" s="22" t="inlineStr">
         <is>
-          <t>Open the dashboard.</t>
+          <t>Have an Admin create your account; open the invite email; set password; sign in.</t>
         </is>
       </c>
       <c r="D59" s="22" t="inlineStr">
         <is>
-          <t>Review queue, approved/rejected counts, registrations, hours, upcoming events + Roster links.</t>
+          <t>Invite email arrives with a working set-password link; you can sign in.</t>
         </is>
       </c>
       <c r="E59" s="23" t="n"/>
@@ -5561,22 +5611,22 @@
     <row r="60" ht="42" customHeight="1">
       <c r="A60" s="21" t="inlineStr">
         <is>
-          <t>SV5</t>
+          <t>SV3</t>
         </is>
       </c>
       <c r="B60" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to approve hours.</t>
+          <t>As a supervisor, I want the correct 7 left-menu tabs.</t>
         </is>
       </c>
       <c r="C60" s="22" t="inlineStr">
         <is>
-          <t>Pending Reviews → open → Approve.</t>
+          <t>Look at the left menu.</t>
         </is>
       </c>
       <c r="D60" s="22" t="inlineStr">
         <is>
-          <t>Approved; moves to Reviewed History; participant total updates; email sent.</t>
+          <t>Dashboard, Pending Reviews, Reviewed History, My Events, All Opportunities, My Hours, Help.</t>
         </is>
       </c>
       <c r="E60" s="23" t="n"/>
@@ -5586,22 +5636,22 @@
     <row r="61" ht="42" customHeight="1">
       <c r="A61" s="21" t="inlineStr">
         <is>
-          <t>SV6</t>
+          <t>SV4</t>
         </is>
       </c>
       <c r="B61" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to reject hours with a reason.</t>
+          <t>As a supervisor, I want a dashboard.</t>
         </is>
       </c>
       <c r="C61" s="22" t="inlineStr">
         <is>
-          <t>Reject without a reason, then with one.</t>
+          <t>Open the dashboard.</t>
         </is>
       </c>
       <c r="D61" s="22" t="inlineStr">
         <is>
-          <t>Blocked until a reason is given; then rejected and the participant notified.</t>
+          <t>Review queue, approved/rejected counts, registrations, hours, upcoming events + Roster links.</t>
         </is>
       </c>
       <c r="E61" s="23" t="n"/>
@@ -5611,22 +5661,22 @@
     <row r="62" ht="42" customHeight="1">
       <c r="A62" s="21" t="inlineStr">
         <is>
-          <t>SV7</t>
+          <t>SV5</t>
         </is>
       </c>
       <c r="B62" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to review external submissions.</t>
+          <t>As a supervisor, I want to approve hours.</t>
         </is>
       </c>
       <c r="C62" s="22" t="inlineStr">
         <is>
-          <t>Pending Reviews → external tab → approve/reject.</t>
+          <t>Pending Reviews → open → Approve.</t>
         </is>
       </c>
       <c r="D62" s="22" t="inlineStr">
         <is>
-          <t>External items reviewable, including any proof.</t>
+          <t>Approved; moves to Reviewed History; participant total updates; email sent.</t>
         </is>
       </c>
       <c r="E62" s="23" t="n"/>
@@ -5636,22 +5686,22 @@
     <row r="63" ht="42" customHeight="1">
       <c r="A63" s="21" t="inlineStr">
         <is>
-          <t>SV8</t>
+          <t>SV6</t>
         </is>
       </c>
       <c r="B63" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to create an event.</t>
+          <t>As a supervisor, I want to reject hours with a reason.</t>
         </is>
       </c>
       <c r="C63" s="22" t="inlineStr">
         <is>
-          <t>New Event → title, description, slot, address, date, times, capacity, grade limits → save.</t>
+          <t>Reject without a reason, then with one.</t>
         </is>
       </c>
       <c r="D63" s="22" t="inlineStr">
         <is>
-          <t>Credit auto-calculated from times; event created in My Events.</t>
+          <t>Blocked until a reason is given; then rejected and the participant notified.</t>
         </is>
       </c>
       <c r="E63" s="23" t="n"/>
@@ -5661,22 +5711,22 @@
     <row r="64" ht="42" customHeight="1">
       <c r="A64" s="21" t="inlineStr">
         <is>
-          <t>SV9</t>
+          <t>SV7</t>
         </is>
       </c>
       <c r="B64" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to edit an event.</t>
+          <t>As a supervisor, I want to review external submissions.</t>
         </is>
       </c>
       <c r="C64" s="22" t="inlineStr">
         <is>
-          <t>My Events → edit → save.</t>
+          <t>Pending Reviews → external tab → approve/reject.</t>
         </is>
       </c>
       <c r="D64" s="22" t="inlineStr">
         <is>
-          <t>Changes persist and show to participants.</t>
+          <t>External items reviewable, including any proof.</t>
         </is>
       </c>
       <c r="E64" s="23" t="n"/>
@@ -5686,22 +5736,22 @@
     <row r="65" ht="42" customHeight="1">
       <c r="A65" s="21" t="inlineStr">
         <is>
-          <t>SV10</t>
+          <t>SV8</t>
         </is>
       </c>
       <c r="B65" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to delete an event with no approved hours.</t>
+          <t>As a supervisor, I want to create an event.</t>
         </is>
       </c>
       <c r="C65" s="22" t="inlineStr">
         <is>
-          <t>Delete such an event → confirm.</t>
+          <t>New Event → title, description, slot, address, date, times, capacity, grade limits → save.</t>
         </is>
       </c>
       <c r="D65" s="22" t="inlineStr">
         <is>
-          <t>Event deleted.</t>
+          <t>Credit auto-calculated from times; event created in My Events.</t>
         </is>
       </c>
       <c r="E65" s="23" t="n"/>
@@ -5711,22 +5761,22 @@
     <row r="66" ht="42" customHeight="1">
       <c r="A66" s="21" t="inlineStr">
         <is>
-          <t>SV11</t>
+          <t>SV9</t>
         </is>
       </c>
       <c r="B66" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, deleting an event with approved hours is blocked.</t>
+          <t>As a supervisor, I want to edit an event.</t>
         </is>
       </c>
       <c r="C66" s="22" t="inlineStr">
         <is>
-          <t>Try to delete an event that has approved hours.</t>
+          <t>My Events → edit → save.</t>
         </is>
       </c>
       <c r="D66" s="22" t="inlineStr">
         <is>
-          <t>Blocked with a message that approved hours must be preserved.</t>
+          <t>Changes persist and show to participants.</t>
         </is>
       </c>
       <c r="E66" s="23" t="n"/>
@@ -5736,22 +5786,22 @@
     <row r="67" ht="42" customHeight="1">
       <c r="A67" s="21" t="inlineStr">
         <is>
-          <t>SV12</t>
+          <t>SV10</t>
         </is>
       </c>
       <c r="B67" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to see who signed up.</t>
+          <t>As a supervisor, I want to delete an event with no approved hours.</t>
         </is>
       </c>
       <c r="C67" s="22" t="inlineStr">
         <is>
-          <t>Open the event Roster.</t>
+          <t>Delete such an event → confirm.</t>
         </is>
       </c>
       <c r="D67" s="22" t="inlineStr">
         <is>
-          <t>Registrants listed with grade and status.</t>
+          <t>Event deleted.</t>
         </is>
       </c>
       <c r="E67" s="23" t="n"/>
@@ -5761,22 +5811,22 @@
     <row r="68" ht="42" customHeight="1">
       <c r="A68" s="21" t="inlineStr">
         <is>
-          <t>SV13</t>
+          <t>SV11</t>
         </is>
       </c>
       <c r="B68" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to check people in / mark no-show.</t>
+          <t>As a supervisor, deleting an event with approved hours is blocked.</t>
         </is>
       </c>
       <c r="C68" s="22" t="inlineStr">
         <is>
-          <t>On the roster, Check in and Mark no-show.</t>
+          <t>Try to delete an event that has approved hours.</t>
         </is>
       </c>
       <c r="D68" s="22" t="inlineStr">
         <is>
-          <t>Status updates and persists.</t>
+          <t>Blocked with a message that approved hours must be preserved.</t>
         </is>
       </c>
       <c r="E68" s="23" t="n"/>
@@ -5786,22 +5836,22 @@
     <row r="69" ht="42" customHeight="1">
       <c r="A69" s="21" t="inlineStr">
         <is>
-          <t>SV14</t>
+          <t>SV12</t>
         </is>
       </c>
       <c r="B69" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to message everyone signed up.</t>
+          <t>As a supervisor, I want to see who signed up.</t>
         </is>
       </c>
       <c r="C69" s="22" t="inlineStr">
         <is>
-          <t>Roster → Message attendees → subject+message → send (include guardians on).</t>
+          <t>Open the event Roster.</t>
         </is>
       </c>
       <c r="D69" s="22" t="inlineStr">
         <is>
-          <t>Each registrant (and guardians) emailed individually; recipient count shown.</t>
+          <t>Registrants listed with grade and status.</t>
         </is>
       </c>
       <c r="E69" s="23" t="n"/>
@@ -5811,22 +5861,22 @@
     <row r="70" ht="42" customHeight="1">
       <c r="A70" s="21" t="inlineStr">
         <is>
-          <t>SV15</t>
+          <t>SV13</t>
         </is>
       </c>
       <c r="B70" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want a history of what I reviewed.</t>
+          <t>As a supervisor, I want to check people in / mark no-show.</t>
         </is>
       </c>
       <c r="C70" s="22" t="inlineStr">
         <is>
-          <t>Open Reviewed History.</t>
+          <t>On the roster, Check in and Mark no-show.</t>
         </is>
       </c>
       <c r="D70" s="22" t="inlineStr">
         <is>
-          <t>Every approved/rejected item with dates and volunteers.</t>
+          <t>Status updates and persists.</t>
         </is>
       </c>
       <c r="E70" s="23" t="n"/>
@@ -5836,22 +5886,22 @@
     <row r="71" ht="42" customHeight="1">
       <c r="A71" s="21" t="inlineStr">
         <is>
-          <t>SV16</t>
+          <t>SV14</t>
         </is>
       </c>
       <c r="B71" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to browse all opportunities view-only.</t>
+          <t>As a supervisor, I want to message everyone signed up.</t>
         </is>
       </c>
       <c r="C71" s="22" t="inlineStr">
         <is>
-          <t>All Opportunities → search / upcoming-past.</t>
+          <t>Roster → Message attendees → subject+message → send (include guardians on).</t>
         </is>
       </c>
       <c r="D71" s="22" t="inlineStr">
         <is>
-          <t>Every event listed read-only; can't edit others' events.</t>
+          <t>Each registrant (and guardians) emailed individually; recipient count shown.</t>
         </is>
       </c>
       <c r="E71" s="23" t="n"/>
@@ -5861,22 +5911,22 @@
     <row r="72" ht="42" customHeight="1">
       <c r="A72" s="21" t="inlineStr">
         <is>
-          <t>SV17</t>
+          <t>SV15</t>
         </is>
       </c>
       <c r="B72" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to log my own adult hours.</t>
+          <t>As a supervisor, I want a history of what I reviewed.</t>
         </is>
       </c>
       <c r="C72" s="22" t="inlineStr">
         <is>
-          <t>My Hours → log an activity, date, hours → save.</t>
+          <t>Open Reviewed History.</t>
         </is>
       </c>
       <c r="D72" s="22" t="inlineStr">
         <is>
-          <t>Recorded instantly with a running total; clearly NOT part of the student competition.</t>
+          <t>Every approved/rejected item with dates and volunteers.</t>
         </is>
       </c>
       <c r="E72" s="23" t="n"/>
@@ -5886,22 +5936,22 @@
     <row r="73" ht="42" customHeight="1">
       <c r="A73" s="21" t="inlineStr">
         <is>
-          <t>SV18</t>
+          <t>SV16</t>
         </is>
       </c>
       <c r="B73" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to delete an adult-hours entry.</t>
+          <t>As a supervisor, I want to browse all opportunities view-only.</t>
         </is>
       </c>
       <c r="C73" s="22" t="inlineStr">
         <is>
-          <t>My Hours → delete an entry → confirm.</t>
+          <t>All Opportunities → search / upcoming-past.</t>
         </is>
       </c>
       <c r="D73" s="22" t="inlineStr">
         <is>
-          <t>Removed; total updates.</t>
+          <t>Every event listed read-only; can't edit others' events.</t>
         </is>
       </c>
       <c r="E73" s="23" t="n"/>
@@ -5911,110 +5961,110 @@
     <row r="74" ht="42" customHeight="1">
       <c r="A74" s="21" t="inlineStr">
         <is>
-          <t>SV19</t>
+          <t>SV17</t>
         </is>
       </c>
       <c r="B74" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I must NOT access user or org management.</t>
+          <t>As a supervisor, I want to log my own adult hours.</t>
         </is>
       </c>
       <c r="C74" s="22" t="inlineStr">
         <is>
-          <t>Look for Users / Organizations in the menu.</t>
+          <t>My Hours → log an activity, date, hours → save.</t>
         </is>
       </c>
       <c r="D74" s="22" t="inlineStr">
         <is>
-          <t>Those tabs are absent; direct URLs are blocked.</t>
+          <t>Recorded instantly with a running total; clearly NOT part of the student competition.</t>
         </is>
       </c>
       <c r="E74" s="23" t="n"/>
       <c r="F74" s="22" t="n"/>
       <c r="G74" s="23" t="n"/>
     </row>
-    <row r="75" ht="20" customHeight="1">
-      <c r="A75" s="19" t="inlineStr">
-        <is>
-          <t>Admin (org-scoped)</t>
-        </is>
-      </c>
-      <c r="B75" s="20" t="n"/>
-      <c r="C75" s="20" t="n"/>
-      <c r="D75" s="20" t="n"/>
-      <c r="E75" s="20" t="n"/>
-      <c r="F75" s="20" t="n"/>
-      <c r="G75" s="20" t="n"/>
+    <row r="75" ht="42" customHeight="1">
+      <c r="A75" s="21" t="inlineStr">
+        <is>
+          <t>SV18</t>
+        </is>
+      </c>
+      <c r="B75" s="22" t="inlineStr">
+        <is>
+          <t>As a supervisor, I want to delete an adult-hours entry.</t>
+        </is>
+      </c>
+      <c r="C75" s="22" t="inlineStr">
+        <is>
+          <t>My Hours → delete an entry → confirm.</t>
+        </is>
+      </c>
+      <c r="D75" s="22" t="inlineStr">
+        <is>
+          <t>Removed; total updates.</t>
+        </is>
+      </c>
+      <c r="E75" s="23" t="n"/>
+      <c r="F75" s="22" t="n"/>
+      <c r="G75" s="23" t="n"/>
     </row>
     <row r="76" ht="42" customHeight="1">
       <c r="A76" s="21" t="inlineStr">
         <is>
-          <t>AD1</t>
+          <t>SV19</t>
         </is>
       </c>
       <c r="B76" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I want the correct menu tabs.</t>
+          <t>As a supervisor, I must NOT access user or org management.</t>
         </is>
       </c>
       <c r="C76" s="22" t="inlineStr">
         <is>
-          <t>Look at the left menu.</t>
+          <t>Look for Users / Organizations in the menu.</t>
         </is>
       </c>
       <c r="D76" s="22" t="inlineStr">
         <is>
-          <t>Dashboard, Pending Reviews, Reviewed History, My Events, All Opportunities, Users, Organizations, My Hours, Help.</t>
+          <t>Those tabs are absent; direct URLs are blocked.</t>
         </is>
       </c>
       <c r="E76" s="23" t="n"/>
       <c r="F76" s="22" t="n"/>
       <c r="G76" s="23" t="n"/>
     </row>
-    <row r="77" ht="42" customHeight="1">
-      <c r="A77" s="21" t="inlineStr">
-        <is>
-          <t>AD2</t>
-        </is>
-      </c>
-      <c r="B77" s="22" t="inlineStr">
-        <is>
-          <t>As an Admin, I can do everything a supervisor can.</t>
-        </is>
-      </c>
-      <c r="C77" s="22" t="inlineStr">
-        <is>
-          <t>Spot-check: approve an item and create an event.</t>
-        </is>
-      </c>
-      <c r="D77" s="22" t="inlineStr">
-        <is>
-          <t>Both work.</t>
-        </is>
-      </c>
-      <c r="E77" s="23" t="n"/>
-      <c r="F77" s="22" t="n"/>
-      <c r="G77" s="23" t="n"/>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="19" t="inlineStr">
+        <is>
+          <t>Admin (org-scoped)</t>
+        </is>
+      </c>
+      <c r="B77" s="20" t="n"/>
+      <c r="C77" s="20" t="n"/>
+      <c r="D77" s="20" t="n"/>
+      <c r="E77" s="20" t="n"/>
+      <c r="F77" s="20" t="n"/>
+      <c r="G77" s="20" t="n"/>
     </row>
     <row r="78" ht="42" customHeight="1">
       <c r="A78" s="21" t="inlineStr">
         <is>
-          <t>AD3</t>
+          <t>AD1</t>
         </is>
       </c>
       <c r="B78" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I only see my org's non-admin users.</t>
+          <t>As an Admin, I want the correct menu tabs.</t>
         </is>
       </c>
       <c r="C78" s="22" t="inlineStr">
         <is>
-          <t>Open Users.</t>
+          <t>Look at the left menu.</t>
         </is>
       </c>
       <c r="D78" s="22" t="inlineStr">
         <is>
-          <t>Only participants/parents/supervisors in your org; no admins/super admins; no other orgs.</t>
+          <t>Dashboard, Pending Reviews, Reviewed History, My Events, All Opportunities, Users, Organizations, My Hours, Help.</t>
         </is>
       </c>
       <c r="E78" s="23" t="n"/>
@@ -6024,22 +6074,22 @@
     <row r="79" ht="42" customHeight="1">
       <c r="A79" s="21" t="inlineStr">
         <is>
-          <t>AD4</t>
+          <t>AD2</t>
         </is>
       </c>
       <c r="B79" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I want to add a supervisor.</t>
+          <t>As an Admin, I can do everything a supervisor can.</t>
         </is>
       </c>
       <c r="C79" s="22" t="inlineStr">
         <is>
-          <t>Users → Add user → Supervisor → save.</t>
+          <t>Spot-check: approve an item and create an event.</t>
         </is>
       </c>
       <c r="D79" s="22" t="inlineStr">
         <is>
-          <t>Supervisor created, stamped to your org; invite email sent.</t>
+          <t>Both work.</t>
         </is>
       </c>
       <c r="E79" s="23" t="n"/>
@@ -6049,22 +6099,22 @@
     <row r="80" ht="42" customHeight="1">
       <c r="A80" s="21" t="inlineStr">
         <is>
-          <t>AD5</t>
+          <t>AD3</t>
         </is>
       </c>
       <c r="B80" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I want to create a participant as a fallback.</t>
+          <t>As an Admin, I only see my org's non-admin users.</t>
         </is>
       </c>
       <c r="C80" s="22" t="inlineStr">
         <is>
-          <t>Users → Add user → Participant → save.</t>
+          <t>Open Users.</t>
         </is>
       </c>
       <c r="D80" s="22" t="inlineStr">
         <is>
-          <t>Participant created with a set-password invite (no silent password).</t>
+          <t>Only participants/parents/supervisors in your org; no admins/super admins; no other orgs.</t>
         </is>
       </c>
       <c r="E80" s="23" t="n"/>
@@ -6074,22 +6124,22 @@
     <row r="81" ht="42" customHeight="1">
       <c r="A81" s="21" t="inlineStr">
         <is>
-          <t>AD6</t>
+          <t>AD4</t>
         </is>
       </c>
       <c r="B81" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I want to grant participant hours.</t>
+          <t>As an Admin, I want to add a supervisor.</t>
         </is>
       </c>
       <c r="C81" s="22" t="inlineStr">
         <is>
-          <t>Open a participant in your org → Add hours.</t>
+          <t>Users → Add user → Supervisor → save.</t>
         </is>
       </c>
       <c r="D81" s="22" t="inlineStr">
         <is>
-          <t>Hours auto-approved; count toward their total/medals.</t>
+          <t>Supervisor created, stamped to your org; invite email sent.</t>
         </is>
       </c>
       <c r="E81" s="23" t="n"/>
@@ -6099,22 +6149,22 @@
     <row r="82" ht="42" customHeight="1">
       <c r="A82" s="21" t="inlineStr">
         <is>
-          <t>AD7</t>
+          <t>AD5</t>
         </is>
       </c>
       <c r="B82" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I want a participant's service record.</t>
+          <t>As an Admin, I want to create a participant as a fallback.</t>
         </is>
       </c>
       <c r="C82" s="22" t="inlineStr">
         <is>
-          <t>Users → Service record for a participant in your org.</t>
+          <t>Users → Add user → Participant → save.</t>
         </is>
       </c>
       <c r="D82" s="22" t="inlineStr">
         <is>
-          <t>Record opens.</t>
+          <t>Participant created with a set-password invite (no silent password).</t>
         </is>
       </c>
       <c r="E82" s="23" t="n"/>
@@ -6124,22 +6174,22 @@
     <row r="83" ht="42" customHeight="1">
       <c r="A83" s="21" t="inlineStr">
         <is>
-          <t>AD8</t>
+          <t>AD6</t>
         </is>
       </c>
       <c r="B83" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I want to edit/delete my org's users.</t>
+          <t>As an Admin, I want to grant participant hours.</t>
         </is>
       </c>
       <c r="C83" s="22" t="inlineStr">
         <is>
-          <t>Edit a name/phone; delete a test user.</t>
+          <t>Open a participant in your org → Add hours.</t>
         </is>
       </c>
       <c r="D83" s="22" t="inlineStr">
         <is>
-          <t>Changes apply within your org.</t>
+          <t>Hours auto-approved; count toward their total/medals.</t>
         </is>
       </c>
       <c r="E83" s="23" t="n"/>
@@ -6149,22 +6199,22 @@
     <row r="84" ht="42" customHeight="1">
       <c r="A84" s="21" t="inlineStr">
         <is>
-          <t>AD9</t>
+          <t>AD7</t>
         </is>
       </c>
       <c r="B84" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I must NOT act on users outside my org.</t>
+          <t>As an Admin, I want a participant's service record.</t>
         </is>
       </c>
       <c r="C84" s="22" t="inlineStr">
         <is>
-          <t>Attempt to reach another org's user (e.g. direct URL).</t>
+          <t>Users → Service record for a participant in your org.</t>
         </is>
       </c>
       <c r="D84" s="22" t="inlineStr">
         <is>
-          <t>Blocked / not visible.</t>
+          <t>Record opens.</t>
         </is>
       </c>
       <c r="E84" s="23" t="n"/>
@@ -6174,22 +6224,22 @@
     <row r="85" ht="42" customHeight="1">
       <c r="A85" s="21" t="inlineStr">
         <is>
-          <t>AD10</t>
+          <t>AD8</t>
         </is>
       </c>
       <c r="B85" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I cannot grant Admin access or manage admins.</t>
+          <t>As an Admin, I want to edit/delete my org's users.</t>
         </is>
       </c>
       <c r="C85" s="22" t="inlineStr">
         <is>
-          <t>Look for the 'grant Admin access' action.</t>
+          <t>Edit a name/phone; delete a test user.</t>
         </is>
       </c>
       <c r="D85" s="22" t="inlineStr">
         <is>
-          <t>No such button; attempts are blocked server-side.</t>
+          <t>Changes apply within your org.</t>
         </is>
       </c>
       <c r="E85" s="23" t="n"/>
@@ -6199,22 +6249,22 @@
     <row r="86" ht="42" customHeight="1">
       <c r="A86" s="21" t="inlineStr">
         <is>
-          <t>AD11</t>
+          <t>AD9</t>
         </is>
       </c>
       <c r="B86" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I see and edit only my own organization.</t>
+          <t>As an Admin, I must NOT act on users outside my org.</t>
         </is>
       </c>
       <c r="C86" s="22" t="inlineStr">
         <is>
-          <t>Open Organizations.</t>
+          <t>Attempt to reach another org's user (e.g. direct URL).</t>
         </is>
       </c>
       <c r="D86" s="22" t="inlineStr">
         <is>
-          <t>Only your org shows; you can edit its settings.</t>
+          <t>Blocked / not visible.</t>
         </is>
       </c>
       <c r="E86" s="23" t="n"/>
@@ -6224,22 +6274,22 @@
     <row r="87" ht="42" customHeight="1">
       <c r="A87" s="21" t="inlineStr">
         <is>
-          <t>AD12</t>
+          <t>AD10</t>
         </is>
       </c>
       <c r="B87" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I want to generate/rotate my org's join code.</t>
+          <t>As an Admin, I cannot grant Admin access or manage admins.</t>
         </is>
       </c>
       <c r="C87" s="22" t="inlineStr">
         <is>
-          <t>Organizations → set/generate a join code → save.</t>
+          <t>Look for the 'grant Admin access' action.</t>
         </is>
       </c>
       <c r="D87" s="22" t="inlineStr">
         <is>
-          <t>Join code saved; usable at sign-up.</t>
+          <t>No such button; attempts are blocked server-side.</t>
         </is>
       </c>
       <c r="E87" s="23" t="n"/>
@@ -6249,22 +6299,22 @@
     <row r="88" ht="42" customHeight="1">
       <c r="A88" s="21" t="inlineStr">
         <is>
-          <t>AD13</t>
+          <t>AD11</t>
         </is>
       </c>
       <c r="B88" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I cannot create organizations.</t>
+          <t>As an Admin, I see and edit only my own organization.</t>
         </is>
       </c>
       <c r="C88" s="22" t="inlineStr">
         <is>
-          <t>Look for 'Add organization'.</t>
+          <t>Open Organizations.</t>
         </is>
       </c>
       <c r="D88" s="22" t="inlineStr">
         <is>
-          <t>No Add button; creation blocked.</t>
+          <t>Only your org shows; you can edit its settings.</t>
         </is>
       </c>
       <c r="E88" s="23" t="n"/>
@@ -6274,110 +6324,110 @@
     <row r="89" ht="42" customHeight="1">
       <c r="A89" s="21" t="inlineStr">
         <is>
-          <t>AD14</t>
+          <t>AD12</t>
         </is>
       </c>
       <c r="B89" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I cannot change the recycling cans total.</t>
+          <t>As an Admin, I want to generate/rotate my org's join code.</t>
         </is>
       </c>
       <c r="C89" s="22" t="inlineStr">
         <is>
-          <t>Look for the cans/bin admin control.</t>
+          <t>Organizations → set/generate a join code → save.</t>
         </is>
       </c>
       <c r="D89" s="22" t="inlineStr">
         <is>
-          <t>Not available (Super Admin only).</t>
+          <t>Join code saved; usable at sign-up.</t>
         </is>
       </c>
       <c r="E89" s="23" t="n"/>
       <c r="F89" s="22" t="n"/>
       <c r="G89" s="23" t="n"/>
     </row>
-    <row r="90" ht="20" customHeight="1">
-      <c r="A90" s="19" t="inlineStr">
-        <is>
-          <t>Super Admin (global)</t>
-        </is>
-      </c>
-      <c r="B90" s="20" t="n"/>
-      <c r="C90" s="20" t="n"/>
-      <c r="D90" s="20" t="n"/>
-      <c r="E90" s="20" t="n"/>
-      <c r="F90" s="20" t="n"/>
-      <c r="G90" s="20" t="n"/>
+    <row r="90" ht="42" customHeight="1">
+      <c r="A90" s="21" t="inlineStr">
+        <is>
+          <t>AD13</t>
+        </is>
+      </c>
+      <c r="B90" s="22" t="inlineStr">
+        <is>
+          <t>As an Admin, I cannot create organizations.</t>
+        </is>
+      </c>
+      <c r="C90" s="22" t="inlineStr">
+        <is>
+          <t>Look for 'Add organization'.</t>
+        </is>
+      </c>
+      <c r="D90" s="22" t="inlineStr">
+        <is>
+          <t>No Add button; creation blocked.</t>
+        </is>
+      </c>
+      <c r="E90" s="23" t="n"/>
+      <c r="F90" s="22" t="n"/>
+      <c r="G90" s="23" t="n"/>
     </row>
     <row r="91" ht="42" customHeight="1">
       <c r="A91" s="21" t="inlineStr">
         <is>
-          <t>SA1</t>
+          <t>AD14</t>
         </is>
       </c>
       <c r="B91" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want the correct menu tabs.</t>
+          <t>As an Admin, I cannot change the recycling cans total.</t>
         </is>
       </c>
       <c r="C91" s="22" t="inlineStr">
         <is>
-          <t>Look at the left menu.</t>
+          <t>Look for the cans/bin admin control.</t>
         </is>
       </c>
       <c r="D91" s="22" t="inlineStr">
         <is>
-          <t>Dashboard, Reports, Users, Events, Organizations (Help in footer).</t>
+          <t>Not available (Super Admin only).</t>
         </is>
       </c>
       <c r="E91" s="23" t="n"/>
       <c r="F91" s="22" t="n"/>
       <c r="G91" s="23" t="n"/>
     </row>
-    <row r="92" ht="42" customHeight="1">
-      <c r="A92" s="21" t="inlineStr">
-        <is>
-          <t>SA2</t>
-        </is>
-      </c>
-      <c r="B92" s="22" t="inlineStr">
-        <is>
-          <t>As a Super Admin, I can do everything an Admin can, across all orgs.</t>
-        </is>
-      </c>
-      <c r="C92" s="22" t="inlineStr">
-        <is>
-          <t>Spot-check user + org actions on more than one org.</t>
-        </is>
-      </c>
-      <c r="D92" s="22" t="inlineStr">
-        <is>
-          <t>All allowed regardless of org.</t>
-        </is>
-      </c>
-      <c r="E92" s="23" t="n"/>
-      <c r="F92" s="22" t="n"/>
-      <c r="G92" s="23" t="n"/>
+    <row r="92" ht="20" customHeight="1">
+      <c r="A92" s="19" t="inlineStr">
+        <is>
+          <t>Super Admin (global)</t>
+        </is>
+      </c>
+      <c r="B92" s="20" t="n"/>
+      <c r="C92" s="20" t="n"/>
+      <c r="D92" s="20" t="n"/>
+      <c r="E92" s="20" t="n"/>
+      <c r="F92" s="20" t="n"/>
+      <c r="G92" s="20" t="n"/>
     </row>
     <row r="93" ht="42" customHeight="1">
       <c r="A93" s="21" t="inlineStr">
         <is>
-          <t>SA3</t>
+          <t>SA1</t>
         </is>
       </c>
       <c r="B93" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to create users incl. Supervisor and Super Admin.</t>
+          <t>As a Super Admin, I want the correct menu tabs.</t>
         </is>
       </c>
       <c r="C93" s="22" t="inlineStr">
         <is>
-          <t>Users → Add user → each role.</t>
+          <t>Look at the left menu.</t>
         </is>
       </c>
       <c r="D93" s="22" t="inlineStr">
         <is>
-          <t>Participant/Supervisor/Super Admin options available; account created + invite email.</t>
+          <t>Dashboard, Reports, Users, Events, Organizations (Help in footer).</t>
         </is>
       </c>
       <c r="E93" s="23" t="n"/>
@@ -6387,22 +6437,22 @@
     <row r="94" ht="42" customHeight="1">
       <c r="A94" s="21" t="inlineStr">
         <is>
-          <t>SA4</t>
+          <t>SA2</t>
         </is>
       </c>
       <c r="B94" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to grant/revoke Admin access.</t>
+          <t>As a Super Admin, I can do everything an Admin can, across all orgs.</t>
         </is>
       </c>
       <c r="C94" s="22" t="inlineStr">
         <is>
-          <t>Open a user → grant Admin access → check org(s) → save; then uncheck all → save.</t>
+          <t>Spot-check user + org actions on more than one org.</t>
         </is>
       </c>
       <c r="D94" s="22" t="inlineStr">
         <is>
-          <t>Checking orgs makes an Admin; unchecking all reverts to participant.</t>
+          <t>All allowed regardless of org.</t>
         </is>
       </c>
       <c r="E94" s="23" t="n"/>
@@ -6412,22 +6462,22 @@
     <row r="95" ht="42" customHeight="1">
       <c r="A95" s="21" t="inlineStr">
         <is>
-          <t>SA5</t>
+          <t>SA3</t>
         </is>
       </c>
       <c r="B95" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to create organizations + join codes.</t>
+          <t>As a Super Admin, I want to create users incl. Supervisor and Super Admin.</t>
         </is>
       </c>
       <c r="C95" s="22" t="inlineStr">
         <is>
-          <t>Organizations → Add organization → set details + join code.</t>
+          <t>Users → Add user → each role.</t>
         </is>
       </c>
       <c r="D95" s="22" t="inlineStr">
         <is>
-          <t>Org created with its join code.</t>
+          <t>Participant/Supervisor/Super Admin options available; account created + invite email.</t>
         </is>
       </c>
       <c r="E95" s="23" t="n"/>
@@ -6437,22 +6487,22 @@
     <row r="96" ht="42" customHeight="1">
       <c r="A96" s="21" t="inlineStr">
         <is>
-          <t>SA6</t>
+          <t>SA4</t>
         </is>
       </c>
       <c r="B96" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to find users by type.</t>
+          <t>As a Super Admin, I want to grant/revoke Admin access.</t>
         </is>
       </c>
       <c r="C96" s="22" t="inlineStr">
         <is>
-          <t>Users → role filter pills + search.</t>
+          <t>Open a user → grant Admin access → check org(s) → save; then uncheck all → save.</t>
         </is>
       </c>
       <c r="D96" s="22" t="inlineStr">
         <is>
-          <t>Filter by role with counts; search by name/email across all orgs.</t>
+          <t>Checking orgs makes an Admin; unchecking all reverts to participant.</t>
         </is>
       </c>
       <c r="E96" s="23" t="n"/>
@@ -6462,22 +6512,22 @@
     <row r="97" ht="42" customHeight="1">
       <c r="A97" s="21" t="inlineStr">
         <is>
-          <t>SA7</t>
+          <t>SA5</t>
         </is>
       </c>
       <c r="B97" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to search events.</t>
+          <t>As a Super Admin, I want to create organizations + join codes.</t>
         </is>
       </c>
       <c r="C97" s="22" t="inlineStr">
         <is>
-          <t>Events → search + date range; check supervisor/org per card.</t>
+          <t>Organizations → Add organization → set details + join code.</t>
         </is>
       </c>
       <c r="D97" s="22" t="inlineStr">
         <is>
-          <t>Filters work; each event shows supervisor and organization.</t>
+          <t>Org created with its join code.</t>
         </is>
       </c>
       <c r="E97" s="23" t="n"/>
@@ -6487,22 +6537,22 @@
     <row r="98" ht="42" customHeight="1">
       <c r="A98" s="21" t="inlineStr">
         <is>
-          <t>SA8</t>
+          <t>SA6</t>
         </is>
       </c>
       <c r="B98" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want clear event-visibility labels.</t>
+          <t>As a Super Admin, I want to find users by type.</t>
         </is>
       </c>
       <c r="C98" s="22" t="inlineStr">
         <is>
-          <t>New Event → 'Who can see this'.</t>
+          <t>Users → role filter pills + search.</t>
         </is>
       </c>
       <c r="D98" s="22" t="inlineStr">
         <is>
-          <t>'Open to all (community)' and 'Only &lt;org&gt; students' with helper text.</t>
+          <t>Filter by role with counts; search by name/email across all orgs.</t>
         </is>
       </c>
       <c r="E98" s="23" t="n"/>
@@ -6512,22 +6562,22 @@
     <row r="99" ht="42" customHeight="1">
       <c r="A99" s="21" t="inlineStr">
         <is>
-          <t>SA9</t>
+          <t>SA7</t>
         </is>
       </c>
       <c r="B99" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want program-wide reports.</t>
+          <t>As a Super Admin, I want to search events.</t>
         </is>
       </c>
       <c r="C99" s="22" t="inlineStr">
         <is>
-          <t>Open Reports / Dashboard.</t>
+          <t>Events → search + date range; check supervisor/org per card.</t>
         </is>
       </c>
       <c r="D99" s="22" t="inlineStr">
         <is>
-          <t>Totals and charts across the whole program.</t>
+          <t>Filters work; each event shows supervisor and organization.</t>
         </is>
       </c>
       <c r="E99" s="23" t="n"/>
@@ -6537,22 +6587,22 @@
     <row r="100" ht="42" customHeight="1">
       <c r="A100" s="21" t="inlineStr">
         <is>
-          <t>SA10</t>
+          <t>SA8</t>
         </is>
       </c>
       <c r="B100" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to verify email works.</t>
+          <t>As a Super Admin, I want clear event-visibility labels.</t>
         </is>
       </c>
       <c r="C100" s="22" t="inlineStr">
         <is>
-          <t>Dashboard → Send test email.</t>
+          <t>New Event → 'Who can see this'.</t>
         </is>
       </c>
       <c r="D100" s="22" t="inlineStr">
         <is>
-          <t>Result shown (success or the exact failure reason).</t>
+          <t>'Open to all (community)' and 'Only &lt;org&gt; students' with helper text.</t>
         </is>
       </c>
       <c r="E100" s="23" t="n"/>
@@ -6562,22 +6612,22 @@
     <row r="101" ht="42" customHeight="1">
       <c r="A101" s="21" t="inlineStr">
         <is>
-          <t>SA11</t>
+          <t>SA9</t>
         </is>
       </c>
       <c r="B101" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to update the recycling cans total.</t>
+          <t>As a Super Admin, I want program-wide reports.</t>
         </is>
       </c>
       <c r="C101" s="22" t="inlineStr">
         <is>
-          <t>Use the cans/bin admin control.</t>
+          <t>Open Reports / Dashboard.</t>
         </is>
       </c>
       <c r="D101" s="22" t="inlineStr">
         <is>
-          <t>Total updates; the ribbon reflects it.</t>
+          <t>Totals and charts across the whole program.</t>
         </is>
       </c>
       <c r="E101" s="23" t="n"/>
@@ -6587,102 +6637,152 @@
     <row r="102" ht="42" customHeight="1">
       <c r="A102" s="21" t="inlineStr">
         <is>
-          <t>SA12</t>
+          <t>SA10</t>
         </is>
       </c>
       <c r="B102" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want hours + records for any user.</t>
+          <t>As a Super Admin, I want to verify email works.</t>
         </is>
       </c>
       <c r="C102" s="22" t="inlineStr">
         <is>
-          <t>Add manual hours / open service record for any participant.</t>
+          <t>Dashboard → Send test email.</t>
         </is>
       </c>
       <c r="D102" s="22" t="inlineStr">
         <is>
-          <t>Works for any org.</t>
+          <t>Result shown (success or the exact failure reason).</t>
         </is>
       </c>
       <c r="E102" s="23" t="n"/>
       <c r="F102" s="22" t="n"/>
       <c r="G102" s="23" t="n"/>
     </row>
-    <row r="103" ht="20" customHeight="1">
-      <c r="A103" s="19" t="inlineStr">
-        <is>
-          <t>Cross-cutting</t>
-        </is>
-      </c>
-      <c r="B103" s="20" t="n"/>
-      <c r="C103" s="20" t="n"/>
-      <c r="D103" s="20" t="n"/>
-      <c r="E103" s="20" t="n"/>
-      <c r="F103" s="20" t="n"/>
-      <c r="G103" s="20" t="n"/>
+    <row r="103" ht="42" customHeight="1">
+      <c r="A103" s="21" t="inlineStr">
+        <is>
+          <t>SA11</t>
+        </is>
+      </c>
+      <c r="B103" s="22" t="inlineStr">
+        <is>
+          <t>As a Super Admin, I want to update the recycling cans total.</t>
+        </is>
+      </c>
+      <c r="C103" s="22" t="inlineStr">
+        <is>
+          <t>Use the cans/bin admin control.</t>
+        </is>
+      </c>
+      <c r="D103" s="22" t="inlineStr">
+        <is>
+          <t>Total updates; the ribbon reflects it.</t>
+        </is>
+      </c>
+      <c r="E103" s="23" t="n"/>
+      <c r="F103" s="22" t="n"/>
+      <c r="G103" s="23" t="n"/>
     </row>
     <row r="104" ht="42" customHeight="1">
       <c r="A104" s="21" t="inlineStr">
         <is>
-          <t>X1</t>
+          <t>SA12</t>
         </is>
       </c>
       <c r="B104" s="22" t="inlineStr">
         <is>
-          <t>As a phone user, I want a usable mobile layout.</t>
+          <t>As a Super Admin, I want hours + records for any user.</t>
         </is>
       </c>
       <c r="C104" s="22" t="inlineStr">
         <is>
-          <t>Open at phone width; use the menu drawer.</t>
+          <t>Add manual hours / open service record for any participant.</t>
         </is>
       </c>
       <c r="D104" s="22" t="inlineStr">
         <is>
-          <t>Layout adapts; drawer opens/closes; no horizontal scroll.</t>
+          <t>Works for any org.</t>
         </is>
       </c>
       <c r="E104" s="23" t="n"/>
       <c r="F104" s="22" t="n"/>
       <c r="G104" s="23" t="n"/>
     </row>
-    <row r="105" ht="42" customHeight="1">
-      <c r="A105" s="21" t="inlineStr">
+    <row r="105" ht="20" customHeight="1">
+      <c r="A105" s="19" t="inlineStr">
+        <is>
+          <t>Cross-cutting</t>
+        </is>
+      </c>
+      <c r="B105" s="20" t="n"/>
+      <c r="C105" s="20" t="n"/>
+      <c r="D105" s="20" t="n"/>
+      <c r="E105" s="20" t="n"/>
+      <c r="F105" s="20" t="n"/>
+      <c r="G105" s="20" t="n"/>
+    </row>
+    <row r="106" ht="42" customHeight="1">
+      <c r="A106" s="21" t="inlineStr">
+        <is>
+          <t>X1</t>
+        </is>
+      </c>
+      <c r="B106" s="22" t="inlineStr">
+        <is>
+          <t>As a phone user, I want a usable mobile layout.</t>
+        </is>
+      </c>
+      <c r="C106" s="22" t="inlineStr">
+        <is>
+          <t>Open at phone width; use the menu drawer.</t>
+        </is>
+      </c>
+      <c r="D106" s="22" t="inlineStr">
+        <is>
+          <t>Layout adapts; drawer opens/closes; no horizontal scroll.</t>
+        </is>
+      </c>
+      <c r="E106" s="23" t="n"/>
+      <c r="F106" s="22" t="n"/>
+      <c r="G106" s="23" t="n"/>
+    </row>
+    <row r="107" ht="42" customHeight="1">
+      <c r="A107" s="21" t="inlineStr">
         <is>
           <t>X2</t>
         </is>
       </c>
-      <c r="B105" s="22" t="inlineStr">
+      <c r="B107" s="22" t="inlineStr">
         <is>
           <t>As a visitor, I want the recycling ribbon on the login page.</t>
         </is>
       </c>
-      <c r="C105" s="22" t="inlineStr">
+      <c r="C107" s="22" t="inlineStr">
         <is>
           <t>Open login signed out.</t>
         </is>
       </c>
-      <c r="D105" s="22" t="inlineStr">
+      <c r="D107" s="22" t="inlineStr">
         <is>
           <t>Green ribbon shows on login.</t>
         </is>
       </c>
-      <c r="E105" s="23" t="n"/>
-      <c r="F105" s="22" t="n"/>
-      <c r="G105" s="23" t="n"/>
+      <c r="E107" s="23" t="n"/>
+      <c r="F107" s="22" t="n"/>
+      <c r="G107" s="23" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A55:G55"/>
+    <mergeCell ref="A77:G77"/>
+    <mergeCell ref="A105:G105"/>
     <mergeCell ref="A35:G35"/>
-    <mergeCell ref="A90:G90"/>
-    <mergeCell ref="A49:G49"/>
+    <mergeCell ref="A92:G92"/>
+    <mergeCell ref="A57:G57"/>
+    <mergeCell ref="A51:G51"/>
     <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A103:G103"/>
-    <mergeCell ref="A75:G75"/>
   </mergeCells>
   <conditionalFormatting sqref="E4:E9">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
@@ -6706,7 +6806,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E36:E48">
+  <conditionalFormatting sqref="E36:E50">
     <cfRule type="cellIs" priority="7" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -6717,7 +6817,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E50:E54">
+  <conditionalFormatting sqref="E52:E56">
     <cfRule type="cellIs" priority="10" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -6728,7 +6828,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E56:E74">
+  <conditionalFormatting sqref="E58:E76">
     <cfRule type="cellIs" priority="13" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -6739,7 +6839,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E76:E89">
+  <conditionalFormatting sqref="E78:E91">
     <cfRule type="cellIs" priority="16" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -6750,7 +6850,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E91:E102">
+  <conditionalFormatting sqref="E93:E104">
     <cfRule type="cellIs" priority="19" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -6761,7 +6861,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E104:E105">
+  <conditionalFormatting sqref="E106:E107">
     <cfRule type="cellIs" priority="22" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -6773,7 +6873,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E4:E9 E11:E34 E36:E48 E50:E54 E56:E74 E76:E89 E91:E102 E104:E105" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E4:E9 E11:E34 E36:E50 E52:E56 E58:E76 E78:E91 E93:E104 E106:E107" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pass,Fail,Blocked,Not tested,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6787,7 +6887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G105"/>
+  <dimension ref="A1:G107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7963,88 +8063,88 @@
       <c r="F48" s="22" t="n"/>
       <c r="G48" s="23" t="n"/>
     </row>
-    <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="19" t="inlineStr">
-        <is>
-          <t>Parent — viewer (grades 6–12 student)</t>
-        </is>
-      </c>
-      <c r="B49" s="20" t="n"/>
-      <c r="C49" s="20" t="n"/>
-      <c r="D49" s="20" t="n"/>
-      <c r="E49" s="20" t="n"/>
-      <c r="F49" s="20" t="n"/>
-      <c r="G49" s="20" t="n"/>
+    <row r="49" ht="42" customHeight="1">
+      <c r="A49" s="21" t="inlineStr">
+        <is>
+          <t>PE14</t>
+        </is>
+      </c>
+      <c r="B49" s="22" t="inlineStr">
+        <is>
+          <t>As a parent, I want to log my child's outside/nonprofit volunteering.</t>
+        </is>
+      </c>
+      <c r="C49" s="22" t="inlineStr">
+        <is>
+          <t>Child card → 'Outside hours' → fill activity, org, date, hours, supervisor → Submit.</t>
+        </is>
+      </c>
+      <c r="D49" s="22" t="inlineStr">
+        <is>
+          <t>External hours submitted for the child and sent for supervisor approval (proof required over 5h).</t>
+        </is>
+      </c>
+      <c r="E49" s="23" t="n"/>
+      <c r="F49" s="22" t="n"/>
+      <c r="G49" s="23" t="n"/>
     </row>
     <row r="50" ht="42" customHeight="1">
       <c r="A50" s="21" t="inlineStr">
         <is>
-          <t>PV1</t>
+          <t>PE15</t>
         </is>
       </c>
       <c r="B50" s="22" t="inlineStr">
         <is>
-          <t>As a parent of a 6–12 student, I want to register for view-only access.</t>
+          <t>As a parent, I want my child's verified service record.</t>
         </is>
       </c>
       <c r="C50" s="22" t="inlineStr">
         <is>
-          <t>Create account → parent of a 6–12 student.</t>
+          <t>Child card → 'Service record'.</t>
         </is>
       </c>
       <c r="D50" s="22" t="inlineStr">
         <is>
-          <t>Account created; no invite required to register.</t>
+          <t>The child's itemized record opens; Print / Save-as-PDF works.</t>
         </is>
       </c>
       <c r="E50" s="23" t="n"/>
       <c r="F50" s="22" t="n"/>
       <c r="G50" s="23" t="n"/>
     </row>
-    <row r="51" ht="42" customHeight="1">
-      <c r="A51" s="21" t="inlineStr">
-        <is>
-          <t>PV2</t>
-        </is>
-      </c>
-      <c r="B51" s="22" t="inlineStr">
-        <is>
-          <t>As a viewer parent, my student links automatically by email.</t>
-        </is>
-      </c>
-      <c r="C51" s="22" t="inlineStr">
-        <is>
-          <t>Have a student enter this exact email as their parent email (before or after you register).</t>
-        </is>
-      </c>
-      <c r="D51" s="22" t="inlineStr">
-        <is>
-          <t>The student appears on your dashboard automatically; empty until then.</t>
-        </is>
-      </c>
-      <c r="E51" s="23" t="n"/>
-      <c r="F51" s="22" t="n"/>
-      <c r="G51" s="23" t="n"/>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="19" t="inlineStr">
+        <is>
+          <t>Parent — viewer (grades 6–12 student)</t>
+        </is>
+      </c>
+      <c r="B51" s="20" t="n"/>
+      <c r="C51" s="20" t="n"/>
+      <c r="D51" s="20" t="n"/>
+      <c r="E51" s="20" t="n"/>
+      <c r="F51" s="20" t="n"/>
+      <c r="G51" s="20" t="n"/>
     </row>
     <row r="52" ht="42" customHeight="1">
       <c r="A52" s="21" t="inlineStr">
         <is>
-          <t>PV3</t>
+          <t>PV1</t>
         </is>
       </c>
       <c r="B52" s="22" t="inlineStr">
         <is>
-          <t>As a viewer parent, I want to see my student's schedule/progress.</t>
+          <t>As a parent of a 6–12 student, I want to register for view-only access.</t>
         </is>
       </c>
       <c r="C52" s="22" t="inlineStr">
         <is>
-          <t>Open the dashboard.</t>
+          <t>Create account → parent of a 6–12 student.</t>
         </is>
       </c>
       <c r="D52" s="22" t="inlineStr">
         <is>
-          <t>View-only schedule and progress.</t>
+          <t>Account created; no invite required to register.</t>
         </is>
       </c>
       <c r="E52" s="23" t="n"/>
@@ -8054,22 +8154,22 @@
     <row r="53" ht="42" customHeight="1">
       <c r="A53" s="21" t="inlineStr">
         <is>
-          <t>PV4</t>
+          <t>PV2</t>
         </is>
       </c>
       <c r="B53" s="22" t="inlineStr">
         <is>
-          <t>As a viewer parent, I do NOT sign the student up.</t>
+          <t>As a viewer parent, my student links automatically by email.</t>
         </is>
       </c>
       <c r="C53" s="22" t="inlineStr">
         <is>
-          <t>Look for a sign-up action.</t>
+          <t>Have a student enter this exact email as their parent email (before or after you register).</t>
         </is>
       </c>
       <c r="D53" s="22" t="inlineStr">
         <is>
-          <t>No sign-up on the student's behalf — the student self-serves.</t>
+          <t>The student appears on your dashboard automatically; empty until then.</t>
         </is>
       </c>
       <c r="E53" s="23" t="n"/>
@@ -8079,110 +8179,110 @@
     <row r="54" ht="42" customHeight="1">
       <c r="A54" s="21" t="inlineStr">
         <is>
-          <t>PV5</t>
+          <t>PV3</t>
         </is>
       </c>
       <c r="B54" s="22" t="inlineStr">
         <is>
-          <t>As a viewer parent, I want to invite a co-guardian.</t>
+          <t>As a viewer parent, I want to see my student's schedule/progress.</t>
         </is>
       </c>
       <c r="C54" s="22" t="inlineStr">
         <is>
-          <t>Invite a co-guardian by email.</t>
+          <t>Open the dashboard.</t>
         </is>
       </c>
       <c r="D54" s="22" t="inlineStr">
         <is>
-          <t>Invite email sent; shared access on registration.</t>
+          <t>View-only schedule and progress.</t>
         </is>
       </c>
       <c r="E54" s="23" t="n"/>
       <c r="F54" s="22" t="n"/>
       <c r="G54" s="23" t="n"/>
     </row>
-    <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="19" t="inlineStr">
-        <is>
-          <t>Supervisor (created by an Admin)</t>
-        </is>
-      </c>
-      <c r="B55" s="20" t="n"/>
-      <c r="C55" s="20" t="n"/>
-      <c r="D55" s="20" t="n"/>
-      <c r="E55" s="20" t="n"/>
-      <c r="F55" s="20" t="n"/>
-      <c r="G55" s="20" t="n"/>
+    <row r="55" ht="42" customHeight="1">
+      <c r="A55" s="21" t="inlineStr">
+        <is>
+          <t>PV4</t>
+        </is>
+      </c>
+      <c r="B55" s="22" t="inlineStr">
+        <is>
+          <t>As a viewer parent, I do NOT sign the student up.</t>
+        </is>
+      </c>
+      <c r="C55" s="22" t="inlineStr">
+        <is>
+          <t>Look for a sign-up action.</t>
+        </is>
+      </c>
+      <c r="D55" s="22" t="inlineStr">
+        <is>
+          <t>No sign-up on the student's behalf — the student self-serves.</t>
+        </is>
+      </c>
+      <c r="E55" s="23" t="n"/>
+      <c r="F55" s="22" t="n"/>
+      <c r="G55" s="23" t="n"/>
     </row>
     <row r="56" ht="42" customHeight="1">
       <c r="A56" s="21" t="inlineStr">
         <is>
-          <t>SV1</t>
+          <t>PV5</t>
         </is>
       </c>
       <c r="B56" s="22" t="inlineStr">
         <is>
-          <t>As the program, a supervisor cannot self-register.</t>
+          <t>As a viewer parent, I want to invite a co-guardian.</t>
         </is>
       </c>
       <c r="C56" s="22" t="inlineStr">
         <is>
-          <t>Review the sign-up options.</t>
+          <t>Invite a co-guardian by email.</t>
         </is>
       </c>
       <c r="D56" s="22" t="inlineStr">
         <is>
-          <t>No supervisor option exists on registration.</t>
+          <t>Invite email sent; shared access on registration.</t>
         </is>
       </c>
       <c r="E56" s="23" t="n"/>
       <c r="F56" s="22" t="n"/>
       <c r="G56" s="23" t="n"/>
     </row>
-    <row r="57" ht="42" customHeight="1">
-      <c r="A57" s="21" t="inlineStr">
-        <is>
-          <t>SV2</t>
-        </is>
-      </c>
-      <c r="B57" s="22" t="inlineStr">
-        <is>
-          <t>As a new supervisor, I get an invite to set my password.</t>
-        </is>
-      </c>
-      <c r="C57" s="22" t="inlineStr">
-        <is>
-          <t>Have an Admin create your account; open the invite email; set password; sign in.</t>
-        </is>
-      </c>
-      <c r="D57" s="22" t="inlineStr">
-        <is>
-          <t>Invite email arrives with a working set-password link; you can sign in.</t>
-        </is>
-      </c>
-      <c r="E57" s="23" t="n"/>
-      <c r="F57" s="22" t="n"/>
-      <c r="G57" s="23" t="n"/>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="19" t="inlineStr">
+        <is>
+          <t>Supervisor (created by an Admin)</t>
+        </is>
+      </c>
+      <c r="B57" s="20" t="n"/>
+      <c r="C57" s="20" t="n"/>
+      <c r="D57" s="20" t="n"/>
+      <c r="E57" s="20" t="n"/>
+      <c r="F57" s="20" t="n"/>
+      <c r="G57" s="20" t="n"/>
     </row>
     <row r="58" ht="42" customHeight="1">
       <c r="A58" s="21" t="inlineStr">
         <is>
-          <t>SV3</t>
+          <t>SV1</t>
         </is>
       </c>
       <c r="B58" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want the correct 7 left-menu tabs.</t>
+          <t>As the program, a supervisor cannot self-register.</t>
         </is>
       </c>
       <c r="C58" s="22" t="inlineStr">
         <is>
-          <t>Look at the left menu.</t>
+          <t>Review the sign-up options.</t>
         </is>
       </c>
       <c r="D58" s="22" t="inlineStr">
         <is>
-          <t>Dashboard, Pending Reviews, Reviewed History, My Events, All Opportunities, My Hours, Help.</t>
+          <t>No supervisor option exists on registration.</t>
         </is>
       </c>
       <c r="E58" s="23" t="n"/>
@@ -8192,22 +8292,22 @@
     <row r="59" ht="42" customHeight="1">
       <c r="A59" s="21" t="inlineStr">
         <is>
-          <t>SV4</t>
+          <t>SV2</t>
         </is>
       </c>
       <c r="B59" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want a dashboard.</t>
+          <t>As a new supervisor, I get an invite to set my password.</t>
         </is>
       </c>
       <c r="C59" s="22" t="inlineStr">
         <is>
-          <t>Open the dashboard.</t>
+          <t>Have an Admin create your account; open the invite email; set password; sign in.</t>
         </is>
       </c>
       <c r="D59" s="22" t="inlineStr">
         <is>
-          <t>Review queue, approved/rejected counts, registrations, hours, upcoming events + Roster links.</t>
+          <t>Invite email arrives with a working set-password link; you can sign in.</t>
         </is>
       </c>
       <c r="E59" s="23" t="n"/>
@@ -8217,22 +8317,22 @@
     <row r="60" ht="42" customHeight="1">
       <c r="A60" s="21" t="inlineStr">
         <is>
-          <t>SV5</t>
+          <t>SV3</t>
         </is>
       </c>
       <c r="B60" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to approve hours.</t>
+          <t>As a supervisor, I want the correct 7 left-menu tabs.</t>
         </is>
       </c>
       <c r="C60" s="22" t="inlineStr">
         <is>
-          <t>Pending Reviews → open → Approve.</t>
+          <t>Look at the left menu.</t>
         </is>
       </c>
       <c r="D60" s="22" t="inlineStr">
         <is>
-          <t>Approved; moves to Reviewed History; participant total updates; email sent.</t>
+          <t>Dashboard, Pending Reviews, Reviewed History, My Events, All Opportunities, My Hours, Help.</t>
         </is>
       </c>
       <c r="E60" s="23" t="n"/>
@@ -8242,22 +8342,22 @@
     <row r="61" ht="42" customHeight="1">
       <c r="A61" s="21" t="inlineStr">
         <is>
-          <t>SV6</t>
+          <t>SV4</t>
         </is>
       </c>
       <c r="B61" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to reject hours with a reason.</t>
+          <t>As a supervisor, I want a dashboard.</t>
         </is>
       </c>
       <c r="C61" s="22" t="inlineStr">
         <is>
-          <t>Reject without a reason, then with one.</t>
+          <t>Open the dashboard.</t>
         </is>
       </c>
       <c r="D61" s="22" t="inlineStr">
         <is>
-          <t>Blocked until a reason is given; then rejected and the participant notified.</t>
+          <t>Review queue, approved/rejected counts, registrations, hours, upcoming events + Roster links.</t>
         </is>
       </c>
       <c r="E61" s="23" t="n"/>
@@ -8267,22 +8367,22 @@
     <row r="62" ht="42" customHeight="1">
       <c r="A62" s="21" t="inlineStr">
         <is>
-          <t>SV7</t>
+          <t>SV5</t>
         </is>
       </c>
       <c r="B62" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to review external submissions.</t>
+          <t>As a supervisor, I want to approve hours.</t>
         </is>
       </c>
       <c r="C62" s="22" t="inlineStr">
         <is>
-          <t>Pending Reviews → external tab → approve/reject.</t>
+          <t>Pending Reviews → open → Approve.</t>
         </is>
       </c>
       <c r="D62" s="22" t="inlineStr">
         <is>
-          <t>External items reviewable, including any proof.</t>
+          <t>Approved; moves to Reviewed History; participant total updates; email sent.</t>
         </is>
       </c>
       <c r="E62" s="23" t="n"/>
@@ -8292,22 +8392,22 @@
     <row r="63" ht="42" customHeight="1">
       <c r="A63" s="21" t="inlineStr">
         <is>
-          <t>SV8</t>
+          <t>SV6</t>
         </is>
       </c>
       <c r="B63" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to create an event.</t>
+          <t>As a supervisor, I want to reject hours with a reason.</t>
         </is>
       </c>
       <c r="C63" s="22" t="inlineStr">
         <is>
-          <t>New Event → title, description, slot, address, date, times, capacity, grade limits → save.</t>
+          <t>Reject without a reason, then with one.</t>
         </is>
       </c>
       <c r="D63" s="22" t="inlineStr">
         <is>
-          <t>Credit auto-calculated from times; event created in My Events.</t>
+          <t>Blocked until a reason is given; then rejected and the participant notified.</t>
         </is>
       </c>
       <c r="E63" s="23" t="n"/>
@@ -8317,22 +8417,22 @@
     <row r="64" ht="42" customHeight="1">
       <c r="A64" s="21" t="inlineStr">
         <is>
-          <t>SV9</t>
+          <t>SV7</t>
         </is>
       </c>
       <c r="B64" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to edit an event.</t>
+          <t>As a supervisor, I want to review external submissions.</t>
         </is>
       </c>
       <c r="C64" s="22" t="inlineStr">
         <is>
-          <t>My Events → edit → save.</t>
+          <t>Pending Reviews → external tab → approve/reject.</t>
         </is>
       </c>
       <c r="D64" s="22" t="inlineStr">
         <is>
-          <t>Changes persist and show to participants.</t>
+          <t>External items reviewable, including any proof.</t>
         </is>
       </c>
       <c r="E64" s="23" t="n"/>
@@ -8342,22 +8442,22 @@
     <row r="65" ht="42" customHeight="1">
       <c r="A65" s="21" t="inlineStr">
         <is>
-          <t>SV10</t>
+          <t>SV8</t>
         </is>
       </c>
       <c r="B65" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to delete an event with no approved hours.</t>
+          <t>As a supervisor, I want to create an event.</t>
         </is>
       </c>
       <c r="C65" s="22" t="inlineStr">
         <is>
-          <t>Delete such an event → confirm.</t>
+          <t>New Event → title, description, slot, address, date, times, capacity, grade limits → save.</t>
         </is>
       </c>
       <c r="D65" s="22" t="inlineStr">
         <is>
-          <t>Event deleted.</t>
+          <t>Credit auto-calculated from times; event created in My Events.</t>
         </is>
       </c>
       <c r="E65" s="23" t="n"/>
@@ -8367,22 +8467,22 @@
     <row r="66" ht="42" customHeight="1">
       <c r="A66" s="21" t="inlineStr">
         <is>
-          <t>SV11</t>
+          <t>SV9</t>
         </is>
       </c>
       <c r="B66" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, deleting an event with approved hours is blocked.</t>
+          <t>As a supervisor, I want to edit an event.</t>
         </is>
       </c>
       <c r="C66" s="22" t="inlineStr">
         <is>
-          <t>Try to delete an event that has approved hours.</t>
+          <t>My Events → edit → save.</t>
         </is>
       </c>
       <c r="D66" s="22" t="inlineStr">
         <is>
-          <t>Blocked with a message that approved hours must be preserved.</t>
+          <t>Changes persist and show to participants.</t>
         </is>
       </c>
       <c r="E66" s="23" t="n"/>
@@ -8392,22 +8492,22 @@
     <row r="67" ht="42" customHeight="1">
       <c r="A67" s="21" t="inlineStr">
         <is>
-          <t>SV12</t>
+          <t>SV10</t>
         </is>
       </c>
       <c r="B67" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to see who signed up.</t>
+          <t>As a supervisor, I want to delete an event with no approved hours.</t>
         </is>
       </c>
       <c r="C67" s="22" t="inlineStr">
         <is>
-          <t>Open the event Roster.</t>
+          <t>Delete such an event → confirm.</t>
         </is>
       </c>
       <c r="D67" s="22" t="inlineStr">
         <is>
-          <t>Registrants listed with grade and status.</t>
+          <t>Event deleted.</t>
         </is>
       </c>
       <c r="E67" s="23" t="n"/>
@@ -8417,22 +8517,22 @@
     <row r="68" ht="42" customHeight="1">
       <c r="A68" s="21" t="inlineStr">
         <is>
-          <t>SV13</t>
+          <t>SV11</t>
         </is>
       </c>
       <c r="B68" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to check people in / mark no-show.</t>
+          <t>As a supervisor, deleting an event with approved hours is blocked.</t>
         </is>
       </c>
       <c r="C68" s="22" t="inlineStr">
         <is>
-          <t>On the roster, Check in and Mark no-show.</t>
+          <t>Try to delete an event that has approved hours.</t>
         </is>
       </c>
       <c r="D68" s="22" t="inlineStr">
         <is>
-          <t>Status updates and persists.</t>
+          <t>Blocked with a message that approved hours must be preserved.</t>
         </is>
       </c>
       <c r="E68" s="23" t="n"/>
@@ -8442,22 +8542,22 @@
     <row r="69" ht="42" customHeight="1">
       <c r="A69" s="21" t="inlineStr">
         <is>
-          <t>SV14</t>
+          <t>SV12</t>
         </is>
       </c>
       <c r="B69" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to message everyone signed up.</t>
+          <t>As a supervisor, I want to see who signed up.</t>
         </is>
       </c>
       <c r="C69" s="22" t="inlineStr">
         <is>
-          <t>Roster → Message attendees → subject+message → send (include guardians on).</t>
+          <t>Open the event Roster.</t>
         </is>
       </c>
       <c r="D69" s="22" t="inlineStr">
         <is>
-          <t>Each registrant (and guardians) emailed individually; recipient count shown.</t>
+          <t>Registrants listed with grade and status.</t>
         </is>
       </c>
       <c r="E69" s="23" t="n"/>
@@ -8467,22 +8567,22 @@
     <row r="70" ht="42" customHeight="1">
       <c r="A70" s="21" t="inlineStr">
         <is>
-          <t>SV15</t>
+          <t>SV13</t>
         </is>
       </c>
       <c r="B70" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want a history of what I reviewed.</t>
+          <t>As a supervisor, I want to check people in / mark no-show.</t>
         </is>
       </c>
       <c r="C70" s="22" t="inlineStr">
         <is>
-          <t>Open Reviewed History.</t>
+          <t>On the roster, Check in and Mark no-show.</t>
         </is>
       </c>
       <c r="D70" s="22" t="inlineStr">
         <is>
-          <t>Every approved/rejected item with dates and volunteers.</t>
+          <t>Status updates and persists.</t>
         </is>
       </c>
       <c r="E70" s="23" t="n"/>
@@ -8492,22 +8592,22 @@
     <row r="71" ht="42" customHeight="1">
       <c r="A71" s="21" t="inlineStr">
         <is>
-          <t>SV16</t>
+          <t>SV14</t>
         </is>
       </c>
       <c r="B71" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to browse all opportunities view-only.</t>
+          <t>As a supervisor, I want to message everyone signed up.</t>
         </is>
       </c>
       <c r="C71" s="22" t="inlineStr">
         <is>
-          <t>All Opportunities → search / upcoming-past.</t>
+          <t>Roster → Message attendees → subject+message → send (include guardians on).</t>
         </is>
       </c>
       <c r="D71" s="22" t="inlineStr">
         <is>
-          <t>Every event listed read-only; can't edit others' events.</t>
+          <t>Each registrant (and guardians) emailed individually; recipient count shown.</t>
         </is>
       </c>
       <c r="E71" s="23" t="n"/>
@@ -8517,22 +8617,22 @@
     <row r="72" ht="42" customHeight="1">
       <c r="A72" s="21" t="inlineStr">
         <is>
-          <t>SV17</t>
+          <t>SV15</t>
         </is>
       </c>
       <c r="B72" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to log my own adult hours.</t>
+          <t>As a supervisor, I want a history of what I reviewed.</t>
         </is>
       </c>
       <c r="C72" s="22" t="inlineStr">
         <is>
-          <t>My Hours → log an activity, date, hours → save.</t>
+          <t>Open Reviewed History.</t>
         </is>
       </c>
       <c r="D72" s="22" t="inlineStr">
         <is>
-          <t>Recorded instantly with a running total; clearly NOT part of the student competition.</t>
+          <t>Every approved/rejected item with dates and volunteers.</t>
         </is>
       </c>
       <c r="E72" s="23" t="n"/>
@@ -8542,22 +8642,22 @@
     <row r="73" ht="42" customHeight="1">
       <c r="A73" s="21" t="inlineStr">
         <is>
-          <t>SV18</t>
+          <t>SV16</t>
         </is>
       </c>
       <c r="B73" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to delete an adult-hours entry.</t>
+          <t>As a supervisor, I want to browse all opportunities view-only.</t>
         </is>
       </c>
       <c r="C73" s="22" t="inlineStr">
         <is>
-          <t>My Hours → delete an entry → confirm.</t>
+          <t>All Opportunities → search / upcoming-past.</t>
         </is>
       </c>
       <c r="D73" s="22" t="inlineStr">
         <is>
-          <t>Removed; total updates.</t>
+          <t>Every event listed read-only; can't edit others' events.</t>
         </is>
       </c>
       <c r="E73" s="23" t="n"/>
@@ -8567,110 +8667,110 @@
     <row r="74" ht="42" customHeight="1">
       <c r="A74" s="21" t="inlineStr">
         <is>
-          <t>SV19</t>
+          <t>SV17</t>
         </is>
       </c>
       <c r="B74" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I must NOT access user or org management.</t>
+          <t>As a supervisor, I want to log my own adult hours.</t>
         </is>
       </c>
       <c r="C74" s="22" t="inlineStr">
         <is>
-          <t>Look for Users / Organizations in the menu.</t>
+          <t>My Hours → log an activity, date, hours → save.</t>
         </is>
       </c>
       <c r="D74" s="22" t="inlineStr">
         <is>
-          <t>Those tabs are absent; direct URLs are blocked.</t>
+          <t>Recorded instantly with a running total; clearly NOT part of the student competition.</t>
         </is>
       </c>
       <c r="E74" s="23" t="n"/>
       <c r="F74" s="22" t="n"/>
       <c r="G74" s="23" t="n"/>
     </row>
-    <row r="75" ht="20" customHeight="1">
-      <c r="A75" s="19" t="inlineStr">
-        <is>
-          <t>Admin (org-scoped)</t>
-        </is>
-      </c>
-      <c r="B75" s="20" t="n"/>
-      <c r="C75" s="20" t="n"/>
-      <c r="D75" s="20" t="n"/>
-      <c r="E75" s="20" t="n"/>
-      <c r="F75" s="20" t="n"/>
-      <c r="G75" s="20" t="n"/>
+    <row r="75" ht="42" customHeight="1">
+      <c r="A75" s="21" t="inlineStr">
+        <is>
+          <t>SV18</t>
+        </is>
+      </c>
+      <c r="B75" s="22" t="inlineStr">
+        <is>
+          <t>As a supervisor, I want to delete an adult-hours entry.</t>
+        </is>
+      </c>
+      <c r="C75" s="22" t="inlineStr">
+        <is>
+          <t>My Hours → delete an entry → confirm.</t>
+        </is>
+      </c>
+      <c r="D75" s="22" t="inlineStr">
+        <is>
+          <t>Removed; total updates.</t>
+        </is>
+      </c>
+      <c r="E75" s="23" t="n"/>
+      <c r="F75" s="22" t="n"/>
+      <c r="G75" s="23" t="n"/>
     </row>
     <row r="76" ht="42" customHeight="1">
       <c r="A76" s="21" t="inlineStr">
         <is>
-          <t>AD1</t>
+          <t>SV19</t>
         </is>
       </c>
       <c r="B76" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I want the correct menu tabs.</t>
+          <t>As a supervisor, I must NOT access user or org management.</t>
         </is>
       </c>
       <c r="C76" s="22" t="inlineStr">
         <is>
-          <t>Look at the left menu.</t>
+          <t>Look for Users / Organizations in the menu.</t>
         </is>
       </c>
       <c r="D76" s="22" t="inlineStr">
         <is>
-          <t>Dashboard, Pending Reviews, Reviewed History, My Events, All Opportunities, Users, Organizations, My Hours, Help.</t>
+          <t>Those tabs are absent; direct URLs are blocked.</t>
         </is>
       </c>
       <c r="E76" s="23" t="n"/>
       <c r="F76" s="22" t="n"/>
       <c r="G76" s="23" t="n"/>
     </row>
-    <row r="77" ht="42" customHeight="1">
-      <c r="A77" s="21" t="inlineStr">
-        <is>
-          <t>AD2</t>
-        </is>
-      </c>
-      <c r="B77" s="22" t="inlineStr">
-        <is>
-          <t>As an Admin, I can do everything a supervisor can.</t>
-        </is>
-      </c>
-      <c r="C77" s="22" t="inlineStr">
-        <is>
-          <t>Spot-check: approve an item and create an event.</t>
-        </is>
-      </c>
-      <c r="D77" s="22" t="inlineStr">
-        <is>
-          <t>Both work.</t>
-        </is>
-      </c>
-      <c r="E77" s="23" t="n"/>
-      <c r="F77" s="22" t="n"/>
-      <c r="G77" s="23" t="n"/>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="19" t="inlineStr">
+        <is>
+          <t>Admin (org-scoped)</t>
+        </is>
+      </c>
+      <c r="B77" s="20" t="n"/>
+      <c r="C77" s="20" t="n"/>
+      <c r="D77" s="20" t="n"/>
+      <c r="E77" s="20" t="n"/>
+      <c r="F77" s="20" t="n"/>
+      <c r="G77" s="20" t="n"/>
     </row>
     <row r="78" ht="42" customHeight="1">
       <c r="A78" s="21" t="inlineStr">
         <is>
-          <t>AD3</t>
+          <t>AD1</t>
         </is>
       </c>
       <c r="B78" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I only see my org's non-admin users.</t>
+          <t>As an Admin, I want the correct menu tabs.</t>
         </is>
       </c>
       <c r="C78" s="22" t="inlineStr">
         <is>
-          <t>Open Users.</t>
+          <t>Look at the left menu.</t>
         </is>
       </c>
       <c r="D78" s="22" t="inlineStr">
         <is>
-          <t>Only participants/parents/supervisors in your org; no admins/super admins; no other orgs.</t>
+          <t>Dashboard, Pending Reviews, Reviewed History, My Events, All Opportunities, Users, Organizations, My Hours, Help.</t>
         </is>
       </c>
       <c r="E78" s="23" t="n"/>
@@ -8680,22 +8780,22 @@
     <row r="79" ht="42" customHeight="1">
       <c r="A79" s="21" t="inlineStr">
         <is>
-          <t>AD4</t>
+          <t>AD2</t>
         </is>
       </c>
       <c r="B79" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I want to add a supervisor.</t>
+          <t>As an Admin, I can do everything a supervisor can.</t>
         </is>
       </c>
       <c r="C79" s="22" t="inlineStr">
         <is>
-          <t>Users → Add user → Supervisor → save.</t>
+          <t>Spot-check: approve an item and create an event.</t>
         </is>
       </c>
       <c r="D79" s="22" t="inlineStr">
         <is>
-          <t>Supervisor created, stamped to your org; invite email sent.</t>
+          <t>Both work.</t>
         </is>
       </c>
       <c r="E79" s="23" t="n"/>
@@ -8705,22 +8805,22 @@
     <row r="80" ht="42" customHeight="1">
       <c r="A80" s="21" t="inlineStr">
         <is>
-          <t>AD5</t>
+          <t>AD3</t>
         </is>
       </c>
       <c r="B80" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I want to create a participant as a fallback.</t>
+          <t>As an Admin, I only see my org's non-admin users.</t>
         </is>
       </c>
       <c r="C80" s="22" t="inlineStr">
         <is>
-          <t>Users → Add user → Participant → save.</t>
+          <t>Open Users.</t>
         </is>
       </c>
       <c r="D80" s="22" t="inlineStr">
         <is>
-          <t>Participant created with a set-password invite (no silent password).</t>
+          <t>Only participants/parents/supervisors in your org; no admins/super admins; no other orgs.</t>
         </is>
       </c>
       <c r="E80" s="23" t="n"/>
@@ -8730,22 +8830,22 @@
     <row r="81" ht="42" customHeight="1">
       <c r="A81" s="21" t="inlineStr">
         <is>
-          <t>AD6</t>
+          <t>AD4</t>
         </is>
       </c>
       <c r="B81" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I want to grant participant hours.</t>
+          <t>As an Admin, I want to add a supervisor.</t>
         </is>
       </c>
       <c r="C81" s="22" t="inlineStr">
         <is>
-          <t>Open a participant in your org → Add hours.</t>
+          <t>Users → Add user → Supervisor → save.</t>
         </is>
       </c>
       <c r="D81" s="22" t="inlineStr">
         <is>
-          <t>Hours auto-approved; count toward their total/medals.</t>
+          <t>Supervisor created, stamped to your org; invite email sent.</t>
         </is>
       </c>
       <c r="E81" s="23" t="n"/>
@@ -8755,22 +8855,22 @@
     <row r="82" ht="42" customHeight="1">
       <c r="A82" s="21" t="inlineStr">
         <is>
-          <t>AD7</t>
+          <t>AD5</t>
         </is>
       </c>
       <c r="B82" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I want a participant's service record.</t>
+          <t>As an Admin, I want to create a participant as a fallback.</t>
         </is>
       </c>
       <c r="C82" s="22" t="inlineStr">
         <is>
-          <t>Users → Service record for a participant in your org.</t>
+          <t>Users → Add user → Participant → save.</t>
         </is>
       </c>
       <c r="D82" s="22" t="inlineStr">
         <is>
-          <t>Record opens.</t>
+          <t>Participant created with a set-password invite (no silent password).</t>
         </is>
       </c>
       <c r="E82" s="23" t="n"/>
@@ -8780,22 +8880,22 @@
     <row r="83" ht="42" customHeight="1">
       <c r="A83" s="21" t="inlineStr">
         <is>
-          <t>AD8</t>
+          <t>AD6</t>
         </is>
       </c>
       <c r="B83" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I want to edit/delete my org's users.</t>
+          <t>As an Admin, I want to grant participant hours.</t>
         </is>
       </c>
       <c r="C83" s="22" t="inlineStr">
         <is>
-          <t>Edit a name/phone; delete a test user.</t>
+          <t>Open a participant in your org → Add hours.</t>
         </is>
       </c>
       <c r="D83" s="22" t="inlineStr">
         <is>
-          <t>Changes apply within your org.</t>
+          <t>Hours auto-approved; count toward their total/medals.</t>
         </is>
       </c>
       <c r="E83" s="23" t="n"/>
@@ -8805,22 +8905,22 @@
     <row r="84" ht="42" customHeight="1">
       <c r="A84" s="21" t="inlineStr">
         <is>
-          <t>AD9</t>
+          <t>AD7</t>
         </is>
       </c>
       <c r="B84" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I must NOT act on users outside my org.</t>
+          <t>As an Admin, I want a participant's service record.</t>
         </is>
       </c>
       <c r="C84" s="22" t="inlineStr">
         <is>
-          <t>Attempt to reach another org's user (e.g. direct URL).</t>
+          <t>Users → Service record for a participant in your org.</t>
         </is>
       </c>
       <c r="D84" s="22" t="inlineStr">
         <is>
-          <t>Blocked / not visible.</t>
+          <t>Record opens.</t>
         </is>
       </c>
       <c r="E84" s="23" t="n"/>
@@ -8830,22 +8930,22 @@
     <row r="85" ht="42" customHeight="1">
       <c r="A85" s="21" t="inlineStr">
         <is>
-          <t>AD10</t>
+          <t>AD8</t>
         </is>
       </c>
       <c r="B85" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I cannot grant Admin access or manage admins.</t>
+          <t>As an Admin, I want to edit/delete my org's users.</t>
         </is>
       </c>
       <c r="C85" s="22" t="inlineStr">
         <is>
-          <t>Look for the 'grant Admin access' action.</t>
+          <t>Edit a name/phone; delete a test user.</t>
         </is>
       </c>
       <c r="D85" s="22" t="inlineStr">
         <is>
-          <t>No such button; attempts are blocked server-side.</t>
+          <t>Changes apply within your org.</t>
         </is>
       </c>
       <c r="E85" s="23" t="n"/>
@@ -8855,22 +8955,22 @@
     <row r="86" ht="42" customHeight="1">
       <c r="A86" s="21" t="inlineStr">
         <is>
-          <t>AD11</t>
+          <t>AD9</t>
         </is>
       </c>
       <c r="B86" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I see and edit only my own organization.</t>
+          <t>As an Admin, I must NOT act on users outside my org.</t>
         </is>
       </c>
       <c r="C86" s="22" t="inlineStr">
         <is>
-          <t>Open Organizations.</t>
+          <t>Attempt to reach another org's user (e.g. direct URL).</t>
         </is>
       </c>
       <c r="D86" s="22" t="inlineStr">
         <is>
-          <t>Only your org shows; you can edit its settings.</t>
+          <t>Blocked / not visible.</t>
         </is>
       </c>
       <c r="E86" s="23" t="n"/>
@@ -8880,22 +8980,22 @@
     <row r="87" ht="42" customHeight="1">
       <c r="A87" s="21" t="inlineStr">
         <is>
-          <t>AD12</t>
+          <t>AD10</t>
         </is>
       </c>
       <c r="B87" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I want to generate/rotate my org's join code.</t>
+          <t>As an Admin, I cannot grant Admin access or manage admins.</t>
         </is>
       </c>
       <c r="C87" s="22" t="inlineStr">
         <is>
-          <t>Organizations → set/generate a join code → save.</t>
+          <t>Look for the 'grant Admin access' action.</t>
         </is>
       </c>
       <c r="D87" s="22" t="inlineStr">
         <is>
-          <t>Join code saved; usable at sign-up.</t>
+          <t>No such button; attempts are blocked server-side.</t>
         </is>
       </c>
       <c r="E87" s="23" t="n"/>
@@ -8905,22 +9005,22 @@
     <row r="88" ht="42" customHeight="1">
       <c r="A88" s="21" t="inlineStr">
         <is>
-          <t>AD13</t>
+          <t>AD11</t>
         </is>
       </c>
       <c r="B88" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I cannot create organizations.</t>
+          <t>As an Admin, I see and edit only my own organization.</t>
         </is>
       </c>
       <c r="C88" s="22" t="inlineStr">
         <is>
-          <t>Look for 'Add organization'.</t>
+          <t>Open Organizations.</t>
         </is>
       </c>
       <c r="D88" s="22" t="inlineStr">
         <is>
-          <t>No Add button; creation blocked.</t>
+          <t>Only your org shows; you can edit its settings.</t>
         </is>
       </c>
       <c r="E88" s="23" t="n"/>
@@ -8930,110 +9030,110 @@
     <row r="89" ht="42" customHeight="1">
       <c r="A89" s="21" t="inlineStr">
         <is>
-          <t>AD14</t>
+          <t>AD12</t>
         </is>
       </c>
       <c r="B89" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I cannot change the recycling cans total.</t>
+          <t>As an Admin, I want to generate/rotate my org's join code.</t>
         </is>
       </c>
       <c r="C89" s="22" t="inlineStr">
         <is>
-          <t>Look for the cans/bin admin control.</t>
+          <t>Organizations → set/generate a join code → save.</t>
         </is>
       </c>
       <c r="D89" s="22" t="inlineStr">
         <is>
-          <t>Not available (Super Admin only).</t>
+          <t>Join code saved; usable at sign-up.</t>
         </is>
       </c>
       <c r="E89" s="23" t="n"/>
       <c r="F89" s="22" t="n"/>
       <c r="G89" s="23" t="n"/>
     </row>
-    <row r="90" ht="20" customHeight="1">
-      <c r="A90" s="19" t="inlineStr">
-        <is>
-          <t>Super Admin (global)</t>
-        </is>
-      </c>
-      <c r="B90" s="20" t="n"/>
-      <c r="C90" s="20" t="n"/>
-      <c r="D90" s="20" t="n"/>
-      <c r="E90" s="20" t="n"/>
-      <c r="F90" s="20" t="n"/>
-      <c r="G90" s="20" t="n"/>
+    <row r="90" ht="42" customHeight="1">
+      <c r="A90" s="21" t="inlineStr">
+        <is>
+          <t>AD13</t>
+        </is>
+      </c>
+      <c r="B90" s="22" t="inlineStr">
+        <is>
+          <t>As an Admin, I cannot create organizations.</t>
+        </is>
+      </c>
+      <c r="C90" s="22" t="inlineStr">
+        <is>
+          <t>Look for 'Add organization'.</t>
+        </is>
+      </c>
+      <c r="D90" s="22" t="inlineStr">
+        <is>
+          <t>No Add button; creation blocked.</t>
+        </is>
+      </c>
+      <c r="E90" s="23" t="n"/>
+      <c r="F90" s="22" t="n"/>
+      <c r="G90" s="23" t="n"/>
     </row>
     <row r="91" ht="42" customHeight="1">
       <c r="A91" s="21" t="inlineStr">
         <is>
-          <t>SA1</t>
+          <t>AD14</t>
         </is>
       </c>
       <c r="B91" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want the correct menu tabs.</t>
+          <t>As an Admin, I cannot change the recycling cans total.</t>
         </is>
       </c>
       <c r="C91" s="22" t="inlineStr">
         <is>
-          <t>Look at the left menu.</t>
+          <t>Look for the cans/bin admin control.</t>
         </is>
       </c>
       <c r="D91" s="22" t="inlineStr">
         <is>
-          <t>Dashboard, Reports, Users, Events, Organizations (Help in footer).</t>
+          <t>Not available (Super Admin only).</t>
         </is>
       </c>
       <c r="E91" s="23" t="n"/>
       <c r="F91" s="22" t="n"/>
       <c r="G91" s="23" t="n"/>
     </row>
-    <row r="92" ht="42" customHeight="1">
-      <c r="A92" s="21" t="inlineStr">
-        <is>
-          <t>SA2</t>
-        </is>
-      </c>
-      <c r="B92" s="22" t="inlineStr">
-        <is>
-          <t>As a Super Admin, I can do everything an Admin can, across all orgs.</t>
-        </is>
-      </c>
-      <c r="C92" s="22" t="inlineStr">
-        <is>
-          <t>Spot-check user + org actions on more than one org.</t>
-        </is>
-      </c>
-      <c r="D92" s="22" t="inlineStr">
-        <is>
-          <t>All allowed regardless of org.</t>
-        </is>
-      </c>
-      <c r="E92" s="23" t="n"/>
-      <c r="F92" s="22" t="n"/>
-      <c r="G92" s="23" t="n"/>
+    <row r="92" ht="20" customHeight="1">
+      <c r="A92" s="19" t="inlineStr">
+        <is>
+          <t>Super Admin (global)</t>
+        </is>
+      </c>
+      <c r="B92" s="20" t="n"/>
+      <c r="C92" s="20" t="n"/>
+      <c r="D92" s="20" t="n"/>
+      <c r="E92" s="20" t="n"/>
+      <c r="F92" s="20" t="n"/>
+      <c r="G92" s="20" t="n"/>
     </row>
     <row r="93" ht="42" customHeight="1">
       <c r="A93" s="21" t="inlineStr">
         <is>
-          <t>SA3</t>
+          <t>SA1</t>
         </is>
       </c>
       <c r="B93" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to create users incl. Supervisor and Super Admin.</t>
+          <t>As a Super Admin, I want the correct menu tabs.</t>
         </is>
       </c>
       <c r="C93" s="22" t="inlineStr">
         <is>
-          <t>Users → Add user → each role.</t>
+          <t>Look at the left menu.</t>
         </is>
       </c>
       <c r="D93" s="22" t="inlineStr">
         <is>
-          <t>Participant/Supervisor/Super Admin options available; account created + invite email.</t>
+          <t>Dashboard, Reports, Users, Events, Organizations (Help in footer).</t>
         </is>
       </c>
       <c r="E93" s="23" t="n"/>
@@ -9043,22 +9143,22 @@
     <row r="94" ht="42" customHeight="1">
       <c r="A94" s="21" t="inlineStr">
         <is>
-          <t>SA4</t>
+          <t>SA2</t>
         </is>
       </c>
       <c r="B94" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to grant/revoke Admin access.</t>
+          <t>As a Super Admin, I can do everything an Admin can, across all orgs.</t>
         </is>
       </c>
       <c r="C94" s="22" t="inlineStr">
         <is>
-          <t>Open a user → grant Admin access → check org(s) → save; then uncheck all → save.</t>
+          <t>Spot-check user + org actions on more than one org.</t>
         </is>
       </c>
       <c r="D94" s="22" t="inlineStr">
         <is>
-          <t>Checking orgs makes an Admin; unchecking all reverts to participant.</t>
+          <t>All allowed regardless of org.</t>
         </is>
       </c>
       <c r="E94" s="23" t="n"/>
@@ -9068,22 +9168,22 @@
     <row r="95" ht="42" customHeight="1">
       <c r="A95" s="21" t="inlineStr">
         <is>
-          <t>SA5</t>
+          <t>SA3</t>
         </is>
       </c>
       <c r="B95" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to create organizations + join codes.</t>
+          <t>As a Super Admin, I want to create users incl. Supervisor and Super Admin.</t>
         </is>
       </c>
       <c r="C95" s="22" t="inlineStr">
         <is>
-          <t>Organizations → Add organization → set details + join code.</t>
+          <t>Users → Add user → each role.</t>
         </is>
       </c>
       <c r="D95" s="22" t="inlineStr">
         <is>
-          <t>Org created with its join code.</t>
+          <t>Participant/Supervisor/Super Admin options available; account created + invite email.</t>
         </is>
       </c>
       <c r="E95" s="23" t="n"/>
@@ -9093,22 +9193,22 @@
     <row r="96" ht="42" customHeight="1">
       <c r="A96" s="21" t="inlineStr">
         <is>
-          <t>SA6</t>
+          <t>SA4</t>
         </is>
       </c>
       <c r="B96" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to find users by type.</t>
+          <t>As a Super Admin, I want to grant/revoke Admin access.</t>
         </is>
       </c>
       <c r="C96" s="22" t="inlineStr">
         <is>
-          <t>Users → role filter pills + search.</t>
+          <t>Open a user → grant Admin access → check org(s) → save; then uncheck all → save.</t>
         </is>
       </c>
       <c r="D96" s="22" t="inlineStr">
         <is>
-          <t>Filter by role with counts; search by name/email across all orgs.</t>
+          <t>Checking orgs makes an Admin; unchecking all reverts to participant.</t>
         </is>
       </c>
       <c r="E96" s="23" t="n"/>
@@ -9118,22 +9218,22 @@
     <row r="97" ht="42" customHeight="1">
       <c r="A97" s="21" t="inlineStr">
         <is>
-          <t>SA7</t>
+          <t>SA5</t>
         </is>
       </c>
       <c r="B97" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to search events.</t>
+          <t>As a Super Admin, I want to create organizations + join codes.</t>
         </is>
       </c>
       <c r="C97" s="22" t="inlineStr">
         <is>
-          <t>Events → search + date range; check supervisor/org per card.</t>
+          <t>Organizations → Add organization → set details + join code.</t>
         </is>
       </c>
       <c r="D97" s="22" t="inlineStr">
         <is>
-          <t>Filters work; each event shows supervisor and organization.</t>
+          <t>Org created with its join code.</t>
         </is>
       </c>
       <c r="E97" s="23" t="n"/>
@@ -9143,22 +9243,22 @@
     <row r="98" ht="42" customHeight="1">
       <c r="A98" s="21" t="inlineStr">
         <is>
-          <t>SA8</t>
+          <t>SA6</t>
         </is>
       </c>
       <c r="B98" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want clear event-visibility labels.</t>
+          <t>As a Super Admin, I want to find users by type.</t>
         </is>
       </c>
       <c r="C98" s="22" t="inlineStr">
         <is>
-          <t>New Event → 'Who can see this'.</t>
+          <t>Users → role filter pills + search.</t>
         </is>
       </c>
       <c r="D98" s="22" t="inlineStr">
         <is>
-          <t>'Open to all (community)' and 'Only &lt;org&gt; students' with helper text.</t>
+          <t>Filter by role with counts; search by name/email across all orgs.</t>
         </is>
       </c>
       <c r="E98" s="23" t="n"/>
@@ -9168,22 +9268,22 @@
     <row r="99" ht="42" customHeight="1">
       <c r="A99" s="21" t="inlineStr">
         <is>
-          <t>SA9</t>
+          <t>SA7</t>
         </is>
       </c>
       <c r="B99" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want program-wide reports.</t>
+          <t>As a Super Admin, I want to search events.</t>
         </is>
       </c>
       <c r="C99" s="22" t="inlineStr">
         <is>
-          <t>Open Reports / Dashboard.</t>
+          <t>Events → search + date range; check supervisor/org per card.</t>
         </is>
       </c>
       <c r="D99" s="22" t="inlineStr">
         <is>
-          <t>Totals and charts across the whole program.</t>
+          <t>Filters work; each event shows supervisor and organization.</t>
         </is>
       </c>
       <c r="E99" s="23" t="n"/>
@@ -9193,22 +9293,22 @@
     <row r="100" ht="42" customHeight="1">
       <c r="A100" s="21" t="inlineStr">
         <is>
-          <t>SA10</t>
+          <t>SA8</t>
         </is>
       </c>
       <c r="B100" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to verify email works.</t>
+          <t>As a Super Admin, I want clear event-visibility labels.</t>
         </is>
       </c>
       <c r="C100" s="22" t="inlineStr">
         <is>
-          <t>Dashboard → Send test email.</t>
+          <t>New Event → 'Who can see this'.</t>
         </is>
       </c>
       <c r="D100" s="22" t="inlineStr">
         <is>
-          <t>Result shown (success or the exact failure reason).</t>
+          <t>'Open to all (community)' and 'Only &lt;org&gt; students' with helper text.</t>
         </is>
       </c>
       <c r="E100" s="23" t="n"/>
@@ -9218,22 +9318,22 @@
     <row r="101" ht="42" customHeight="1">
       <c r="A101" s="21" t="inlineStr">
         <is>
-          <t>SA11</t>
+          <t>SA9</t>
         </is>
       </c>
       <c r="B101" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to update the recycling cans total.</t>
+          <t>As a Super Admin, I want program-wide reports.</t>
         </is>
       </c>
       <c r="C101" s="22" t="inlineStr">
         <is>
-          <t>Use the cans/bin admin control.</t>
+          <t>Open Reports / Dashboard.</t>
         </is>
       </c>
       <c r="D101" s="22" t="inlineStr">
         <is>
-          <t>Total updates; the ribbon reflects it.</t>
+          <t>Totals and charts across the whole program.</t>
         </is>
       </c>
       <c r="E101" s="23" t="n"/>
@@ -9243,102 +9343,152 @@
     <row r="102" ht="42" customHeight="1">
       <c r="A102" s="21" t="inlineStr">
         <is>
-          <t>SA12</t>
+          <t>SA10</t>
         </is>
       </c>
       <c r="B102" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want hours + records for any user.</t>
+          <t>As a Super Admin, I want to verify email works.</t>
         </is>
       </c>
       <c r="C102" s="22" t="inlineStr">
         <is>
-          <t>Add manual hours / open service record for any participant.</t>
+          <t>Dashboard → Send test email.</t>
         </is>
       </c>
       <c r="D102" s="22" t="inlineStr">
         <is>
-          <t>Works for any org.</t>
+          <t>Result shown (success or the exact failure reason).</t>
         </is>
       </c>
       <c r="E102" s="23" t="n"/>
       <c r="F102" s="22" t="n"/>
       <c r="G102" s="23" t="n"/>
     </row>
-    <row r="103" ht="20" customHeight="1">
-      <c r="A103" s="19" t="inlineStr">
-        <is>
-          <t>Cross-cutting</t>
-        </is>
-      </c>
-      <c r="B103" s="20" t="n"/>
-      <c r="C103" s="20" t="n"/>
-      <c r="D103" s="20" t="n"/>
-      <c r="E103" s="20" t="n"/>
-      <c r="F103" s="20" t="n"/>
-      <c r="G103" s="20" t="n"/>
+    <row r="103" ht="42" customHeight="1">
+      <c r="A103" s="21" t="inlineStr">
+        <is>
+          <t>SA11</t>
+        </is>
+      </c>
+      <c r="B103" s="22" t="inlineStr">
+        <is>
+          <t>As a Super Admin, I want to update the recycling cans total.</t>
+        </is>
+      </c>
+      <c r="C103" s="22" t="inlineStr">
+        <is>
+          <t>Use the cans/bin admin control.</t>
+        </is>
+      </c>
+      <c r="D103" s="22" t="inlineStr">
+        <is>
+          <t>Total updates; the ribbon reflects it.</t>
+        </is>
+      </c>
+      <c r="E103" s="23" t="n"/>
+      <c r="F103" s="22" t="n"/>
+      <c r="G103" s="23" t="n"/>
     </row>
     <row r="104" ht="42" customHeight="1">
       <c r="A104" s="21" t="inlineStr">
         <is>
-          <t>X1</t>
+          <t>SA12</t>
         </is>
       </c>
       <c r="B104" s="22" t="inlineStr">
         <is>
-          <t>As a phone user, I want a usable mobile layout.</t>
+          <t>As a Super Admin, I want hours + records for any user.</t>
         </is>
       </c>
       <c r="C104" s="22" t="inlineStr">
         <is>
-          <t>Open at phone width; use the menu drawer.</t>
+          <t>Add manual hours / open service record for any participant.</t>
         </is>
       </c>
       <c r="D104" s="22" t="inlineStr">
         <is>
-          <t>Layout adapts; drawer opens/closes; no horizontal scroll.</t>
+          <t>Works for any org.</t>
         </is>
       </c>
       <c r="E104" s="23" t="n"/>
       <c r="F104" s="22" t="n"/>
       <c r="G104" s="23" t="n"/>
     </row>
-    <row r="105" ht="42" customHeight="1">
-      <c r="A105" s="21" t="inlineStr">
+    <row r="105" ht="20" customHeight="1">
+      <c r="A105" s="19" t="inlineStr">
+        <is>
+          <t>Cross-cutting</t>
+        </is>
+      </c>
+      <c r="B105" s="20" t="n"/>
+      <c r="C105" s="20" t="n"/>
+      <c r="D105" s="20" t="n"/>
+      <c r="E105" s="20" t="n"/>
+      <c r="F105" s="20" t="n"/>
+      <c r="G105" s="20" t="n"/>
+    </row>
+    <row r="106" ht="42" customHeight="1">
+      <c r="A106" s="21" t="inlineStr">
+        <is>
+          <t>X1</t>
+        </is>
+      </c>
+      <c r="B106" s="22" t="inlineStr">
+        <is>
+          <t>As a phone user, I want a usable mobile layout.</t>
+        </is>
+      </c>
+      <c r="C106" s="22" t="inlineStr">
+        <is>
+          <t>Open at phone width; use the menu drawer.</t>
+        </is>
+      </c>
+      <c r="D106" s="22" t="inlineStr">
+        <is>
+          <t>Layout adapts; drawer opens/closes; no horizontal scroll.</t>
+        </is>
+      </c>
+      <c r="E106" s="23" t="n"/>
+      <c r="F106" s="22" t="n"/>
+      <c r="G106" s="23" t="n"/>
+    </row>
+    <row r="107" ht="42" customHeight="1">
+      <c r="A107" s="21" t="inlineStr">
         <is>
           <t>X2</t>
         </is>
       </c>
-      <c r="B105" s="22" t="inlineStr">
+      <c r="B107" s="22" t="inlineStr">
         <is>
           <t>As a visitor, I want the recycling ribbon on the login page.</t>
         </is>
       </c>
-      <c r="C105" s="22" t="inlineStr">
+      <c r="C107" s="22" t="inlineStr">
         <is>
           <t>Open login signed out.</t>
         </is>
       </c>
-      <c r="D105" s="22" t="inlineStr">
+      <c r="D107" s="22" t="inlineStr">
         <is>
           <t>Green ribbon shows on login.</t>
         </is>
       </c>
-      <c r="E105" s="23" t="n"/>
-      <c r="F105" s="22" t="n"/>
-      <c r="G105" s="23" t="n"/>
+      <c r="E107" s="23" t="n"/>
+      <c r="F107" s="22" t="n"/>
+      <c r="G107" s="23" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A55:G55"/>
+    <mergeCell ref="A77:G77"/>
+    <mergeCell ref="A105:G105"/>
     <mergeCell ref="A35:G35"/>
-    <mergeCell ref="A90:G90"/>
-    <mergeCell ref="A49:G49"/>
+    <mergeCell ref="A92:G92"/>
+    <mergeCell ref="A57:G57"/>
+    <mergeCell ref="A51:G51"/>
     <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A103:G103"/>
-    <mergeCell ref="A75:G75"/>
   </mergeCells>
   <conditionalFormatting sqref="E4:E9">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
@@ -9362,7 +9512,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E36:E48">
+  <conditionalFormatting sqref="E36:E50">
     <cfRule type="cellIs" priority="7" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -9373,7 +9523,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E50:E54">
+  <conditionalFormatting sqref="E52:E56">
     <cfRule type="cellIs" priority="10" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -9384,7 +9534,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E56:E74">
+  <conditionalFormatting sqref="E58:E76">
     <cfRule type="cellIs" priority="13" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -9395,7 +9545,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E76:E89">
+  <conditionalFormatting sqref="E78:E91">
     <cfRule type="cellIs" priority="16" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -9406,7 +9556,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E91:E102">
+  <conditionalFormatting sqref="E93:E104">
     <cfRule type="cellIs" priority="19" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -9417,7 +9567,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E104:E105">
+  <conditionalFormatting sqref="E106:E107">
     <cfRule type="cellIs" priority="22" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -9429,7 +9579,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E4:E9 E11:E34 E36:E48 E50:E54 E56:E74 E76:E89 E91:E102 E104:E105" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E4:E9 E11:E34 E36:E50 E52:E56 E58:E76 E78:E91 E93:E104 E106:E107" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pass,Fail,Blocked,Not tested,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -9443,7 +9593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G105"/>
+  <dimension ref="A1:G107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10619,88 +10769,88 @@
       <c r="F48" s="22" t="n"/>
       <c r="G48" s="23" t="n"/>
     </row>
-    <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="19" t="inlineStr">
-        <is>
-          <t>Parent — viewer (grades 6–12 student)</t>
-        </is>
-      </c>
-      <c r="B49" s="20" t="n"/>
-      <c r="C49" s="20" t="n"/>
-      <c r="D49" s="20" t="n"/>
-      <c r="E49" s="20" t="n"/>
-      <c r="F49" s="20" t="n"/>
-      <c r="G49" s="20" t="n"/>
+    <row r="49" ht="42" customHeight="1">
+      <c r="A49" s="21" t="inlineStr">
+        <is>
+          <t>PE14</t>
+        </is>
+      </c>
+      <c r="B49" s="22" t="inlineStr">
+        <is>
+          <t>As a parent, I want to log my child's outside/nonprofit volunteering.</t>
+        </is>
+      </c>
+      <c r="C49" s="22" t="inlineStr">
+        <is>
+          <t>Child card → 'Outside hours' → fill activity, org, date, hours, supervisor → Submit.</t>
+        </is>
+      </c>
+      <c r="D49" s="22" t="inlineStr">
+        <is>
+          <t>External hours submitted for the child and sent for supervisor approval (proof required over 5h).</t>
+        </is>
+      </c>
+      <c r="E49" s="23" t="n"/>
+      <c r="F49" s="22" t="n"/>
+      <c r="G49" s="23" t="n"/>
     </row>
     <row r="50" ht="42" customHeight="1">
       <c r="A50" s="21" t="inlineStr">
         <is>
-          <t>PV1</t>
+          <t>PE15</t>
         </is>
       </c>
       <c r="B50" s="22" t="inlineStr">
         <is>
-          <t>As a parent of a 6–12 student, I want to register for view-only access.</t>
+          <t>As a parent, I want my child's verified service record.</t>
         </is>
       </c>
       <c r="C50" s="22" t="inlineStr">
         <is>
-          <t>Create account → parent of a 6–12 student.</t>
+          <t>Child card → 'Service record'.</t>
         </is>
       </c>
       <c r="D50" s="22" t="inlineStr">
         <is>
-          <t>Account created; no invite required to register.</t>
+          <t>The child's itemized record opens; Print / Save-as-PDF works.</t>
         </is>
       </c>
       <c r="E50" s="23" t="n"/>
       <c r="F50" s="22" t="n"/>
       <c r="G50" s="23" t="n"/>
     </row>
-    <row r="51" ht="42" customHeight="1">
-      <c r="A51" s="21" t="inlineStr">
-        <is>
-          <t>PV2</t>
-        </is>
-      </c>
-      <c r="B51" s="22" t="inlineStr">
-        <is>
-          <t>As a viewer parent, my student links automatically by email.</t>
-        </is>
-      </c>
-      <c r="C51" s="22" t="inlineStr">
-        <is>
-          <t>Have a student enter this exact email as their parent email (before or after you register).</t>
-        </is>
-      </c>
-      <c r="D51" s="22" t="inlineStr">
-        <is>
-          <t>The student appears on your dashboard automatically; empty until then.</t>
-        </is>
-      </c>
-      <c r="E51" s="23" t="n"/>
-      <c r="F51" s="22" t="n"/>
-      <c r="G51" s="23" t="n"/>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="19" t="inlineStr">
+        <is>
+          <t>Parent — viewer (grades 6–12 student)</t>
+        </is>
+      </c>
+      <c r="B51" s="20" t="n"/>
+      <c r="C51" s="20" t="n"/>
+      <c r="D51" s="20" t="n"/>
+      <c r="E51" s="20" t="n"/>
+      <c r="F51" s="20" t="n"/>
+      <c r="G51" s="20" t="n"/>
     </row>
     <row r="52" ht="42" customHeight="1">
       <c r="A52" s="21" t="inlineStr">
         <is>
-          <t>PV3</t>
+          <t>PV1</t>
         </is>
       </c>
       <c r="B52" s="22" t="inlineStr">
         <is>
-          <t>As a viewer parent, I want to see my student's schedule/progress.</t>
+          <t>As a parent of a 6–12 student, I want to register for view-only access.</t>
         </is>
       </c>
       <c r="C52" s="22" t="inlineStr">
         <is>
-          <t>Open the dashboard.</t>
+          <t>Create account → parent of a 6–12 student.</t>
         </is>
       </c>
       <c r="D52" s="22" t="inlineStr">
         <is>
-          <t>View-only schedule and progress.</t>
+          <t>Account created; no invite required to register.</t>
         </is>
       </c>
       <c r="E52" s="23" t="n"/>
@@ -10710,22 +10860,22 @@
     <row r="53" ht="42" customHeight="1">
       <c r="A53" s="21" t="inlineStr">
         <is>
-          <t>PV4</t>
+          <t>PV2</t>
         </is>
       </c>
       <c r="B53" s="22" t="inlineStr">
         <is>
-          <t>As a viewer parent, I do NOT sign the student up.</t>
+          <t>As a viewer parent, my student links automatically by email.</t>
         </is>
       </c>
       <c r="C53" s="22" t="inlineStr">
         <is>
-          <t>Look for a sign-up action.</t>
+          <t>Have a student enter this exact email as their parent email (before or after you register).</t>
         </is>
       </c>
       <c r="D53" s="22" t="inlineStr">
         <is>
-          <t>No sign-up on the student's behalf — the student self-serves.</t>
+          <t>The student appears on your dashboard automatically; empty until then.</t>
         </is>
       </c>
       <c r="E53" s="23" t="n"/>
@@ -10735,110 +10885,110 @@
     <row r="54" ht="42" customHeight="1">
       <c r="A54" s="21" t="inlineStr">
         <is>
-          <t>PV5</t>
+          <t>PV3</t>
         </is>
       </c>
       <c r="B54" s="22" t="inlineStr">
         <is>
-          <t>As a viewer parent, I want to invite a co-guardian.</t>
+          <t>As a viewer parent, I want to see my student's schedule/progress.</t>
         </is>
       </c>
       <c r="C54" s="22" t="inlineStr">
         <is>
-          <t>Invite a co-guardian by email.</t>
+          <t>Open the dashboard.</t>
         </is>
       </c>
       <c r="D54" s="22" t="inlineStr">
         <is>
-          <t>Invite email sent; shared access on registration.</t>
+          <t>View-only schedule and progress.</t>
         </is>
       </c>
       <c r="E54" s="23" t="n"/>
       <c r="F54" s="22" t="n"/>
       <c r="G54" s="23" t="n"/>
     </row>
-    <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="19" t="inlineStr">
-        <is>
-          <t>Supervisor (created by an Admin)</t>
-        </is>
-      </c>
-      <c r="B55" s="20" t="n"/>
-      <c r="C55" s="20" t="n"/>
-      <c r="D55" s="20" t="n"/>
-      <c r="E55" s="20" t="n"/>
-      <c r="F55" s="20" t="n"/>
-      <c r="G55" s="20" t="n"/>
+    <row r="55" ht="42" customHeight="1">
+      <c r="A55" s="21" t="inlineStr">
+        <is>
+          <t>PV4</t>
+        </is>
+      </c>
+      <c r="B55" s="22" t="inlineStr">
+        <is>
+          <t>As a viewer parent, I do NOT sign the student up.</t>
+        </is>
+      </c>
+      <c r="C55" s="22" t="inlineStr">
+        <is>
+          <t>Look for a sign-up action.</t>
+        </is>
+      </c>
+      <c r="D55" s="22" t="inlineStr">
+        <is>
+          <t>No sign-up on the student's behalf — the student self-serves.</t>
+        </is>
+      </c>
+      <c r="E55" s="23" t="n"/>
+      <c r="F55" s="22" t="n"/>
+      <c r="G55" s="23" t="n"/>
     </row>
     <row r="56" ht="42" customHeight="1">
       <c r="A56" s="21" t="inlineStr">
         <is>
-          <t>SV1</t>
+          <t>PV5</t>
         </is>
       </c>
       <c r="B56" s="22" t="inlineStr">
         <is>
-          <t>As the program, a supervisor cannot self-register.</t>
+          <t>As a viewer parent, I want to invite a co-guardian.</t>
         </is>
       </c>
       <c r="C56" s="22" t="inlineStr">
         <is>
-          <t>Review the sign-up options.</t>
+          <t>Invite a co-guardian by email.</t>
         </is>
       </c>
       <c r="D56" s="22" t="inlineStr">
         <is>
-          <t>No supervisor option exists on registration.</t>
+          <t>Invite email sent; shared access on registration.</t>
         </is>
       </c>
       <c r="E56" s="23" t="n"/>
       <c r="F56" s="22" t="n"/>
       <c r="G56" s="23" t="n"/>
     </row>
-    <row r="57" ht="42" customHeight="1">
-      <c r="A57" s="21" t="inlineStr">
-        <is>
-          <t>SV2</t>
-        </is>
-      </c>
-      <c r="B57" s="22" t="inlineStr">
-        <is>
-          <t>As a new supervisor, I get an invite to set my password.</t>
-        </is>
-      </c>
-      <c r="C57" s="22" t="inlineStr">
-        <is>
-          <t>Have an Admin create your account; open the invite email; set password; sign in.</t>
-        </is>
-      </c>
-      <c r="D57" s="22" t="inlineStr">
-        <is>
-          <t>Invite email arrives with a working set-password link; you can sign in.</t>
-        </is>
-      </c>
-      <c r="E57" s="23" t="n"/>
-      <c r="F57" s="22" t="n"/>
-      <c r="G57" s="23" t="n"/>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="19" t="inlineStr">
+        <is>
+          <t>Supervisor (created by an Admin)</t>
+        </is>
+      </c>
+      <c r="B57" s="20" t="n"/>
+      <c r="C57" s="20" t="n"/>
+      <c r="D57" s="20" t="n"/>
+      <c r="E57" s="20" t="n"/>
+      <c r="F57" s="20" t="n"/>
+      <c r="G57" s="20" t="n"/>
     </row>
     <row r="58" ht="42" customHeight="1">
       <c r="A58" s="21" t="inlineStr">
         <is>
-          <t>SV3</t>
+          <t>SV1</t>
         </is>
       </c>
       <c r="B58" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want the correct 7 left-menu tabs.</t>
+          <t>As the program, a supervisor cannot self-register.</t>
         </is>
       </c>
       <c r="C58" s="22" t="inlineStr">
         <is>
-          <t>Look at the left menu.</t>
+          <t>Review the sign-up options.</t>
         </is>
       </c>
       <c r="D58" s="22" t="inlineStr">
         <is>
-          <t>Dashboard, Pending Reviews, Reviewed History, My Events, All Opportunities, My Hours, Help.</t>
+          <t>No supervisor option exists on registration.</t>
         </is>
       </c>
       <c r="E58" s="23" t="n"/>
@@ -10848,22 +10998,22 @@
     <row r="59" ht="42" customHeight="1">
       <c r="A59" s="21" t="inlineStr">
         <is>
-          <t>SV4</t>
+          <t>SV2</t>
         </is>
       </c>
       <c r="B59" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want a dashboard.</t>
+          <t>As a new supervisor, I get an invite to set my password.</t>
         </is>
       </c>
       <c r="C59" s="22" t="inlineStr">
         <is>
-          <t>Open the dashboard.</t>
+          <t>Have an Admin create your account; open the invite email; set password; sign in.</t>
         </is>
       </c>
       <c r="D59" s="22" t="inlineStr">
         <is>
-          <t>Review queue, approved/rejected counts, registrations, hours, upcoming events + Roster links.</t>
+          <t>Invite email arrives with a working set-password link; you can sign in.</t>
         </is>
       </c>
       <c r="E59" s="23" t="n"/>
@@ -10873,22 +11023,22 @@
     <row r="60" ht="42" customHeight="1">
       <c r="A60" s="21" t="inlineStr">
         <is>
-          <t>SV5</t>
+          <t>SV3</t>
         </is>
       </c>
       <c r="B60" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to approve hours.</t>
+          <t>As a supervisor, I want the correct 7 left-menu tabs.</t>
         </is>
       </c>
       <c r="C60" s="22" t="inlineStr">
         <is>
-          <t>Pending Reviews → open → Approve.</t>
+          <t>Look at the left menu.</t>
         </is>
       </c>
       <c r="D60" s="22" t="inlineStr">
         <is>
-          <t>Approved; moves to Reviewed History; participant total updates; email sent.</t>
+          <t>Dashboard, Pending Reviews, Reviewed History, My Events, All Opportunities, My Hours, Help.</t>
         </is>
       </c>
       <c r="E60" s="23" t="n"/>
@@ -10898,22 +11048,22 @@
     <row r="61" ht="42" customHeight="1">
       <c r="A61" s="21" t="inlineStr">
         <is>
-          <t>SV6</t>
+          <t>SV4</t>
         </is>
       </c>
       <c r="B61" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to reject hours with a reason.</t>
+          <t>As a supervisor, I want a dashboard.</t>
         </is>
       </c>
       <c r="C61" s="22" t="inlineStr">
         <is>
-          <t>Reject without a reason, then with one.</t>
+          <t>Open the dashboard.</t>
         </is>
       </c>
       <c r="D61" s="22" t="inlineStr">
         <is>
-          <t>Blocked until a reason is given; then rejected and the participant notified.</t>
+          <t>Review queue, approved/rejected counts, registrations, hours, upcoming events + Roster links.</t>
         </is>
       </c>
       <c r="E61" s="23" t="n"/>
@@ -10923,22 +11073,22 @@
     <row r="62" ht="42" customHeight="1">
       <c r="A62" s="21" t="inlineStr">
         <is>
-          <t>SV7</t>
+          <t>SV5</t>
         </is>
       </c>
       <c r="B62" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to review external submissions.</t>
+          <t>As a supervisor, I want to approve hours.</t>
         </is>
       </c>
       <c r="C62" s="22" t="inlineStr">
         <is>
-          <t>Pending Reviews → external tab → approve/reject.</t>
+          <t>Pending Reviews → open → Approve.</t>
         </is>
       </c>
       <c r="D62" s="22" t="inlineStr">
         <is>
-          <t>External items reviewable, including any proof.</t>
+          <t>Approved; moves to Reviewed History; participant total updates; email sent.</t>
         </is>
       </c>
       <c r="E62" s="23" t="n"/>
@@ -10948,22 +11098,22 @@
     <row r="63" ht="42" customHeight="1">
       <c r="A63" s="21" t="inlineStr">
         <is>
-          <t>SV8</t>
+          <t>SV6</t>
         </is>
       </c>
       <c r="B63" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to create an event.</t>
+          <t>As a supervisor, I want to reject hours with a reason.</t>
         </is>
       </c>
       <c r="C63" s="22" t="inlineStr">
         <is>
-          <t>New Event → title, description, slot, address, date, times, capacity, grade limits → save.</t>
+          <t>Reject without a reason, then with one.</t>
         </is>
       </c>
       <c r="D63" s="22" t="inlineStr">
         <is>
-          <t>Credit auto-calculated from times; event created in My Events.</t>
+          <t>Blocked until a reason is given; then rejected and the participant notified.</t>
         </is>
       </c>
       <c r="E63" s="23" t="n"/>
@@ -10973,22 +11123,22 @@
     <row r="64" ht="42" customHeight="1">
       <c r="A64" s="21" t="inlineStr">
         <is>
-          <t>SV9</t>
+          <t>SV7</t>
         </is>
       </c>
       <c r="B64" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to edit an event.</t>
+          <t>As a supervisor, I want to review external submissions.</t>
         </is>
       </c>
       <c r="C64" s="22" t="inlineStr">
         <is>
-          <t>My Events → edit → save.</t>
+          <t>Pending Reviews → external tab → approve/reject.</t>
         </is>
       </c>
       <c r="D64" s="22" t="inlineStr">
         <is>
-          <t>Changes persist and show to participants.</t>
+          <t>External items reviewable, including any proof.</t>
         </is>
       </c>
       <c r="E64" s="23" t="n"/>
@@ -10998,22 +11148,22 @@
     <row r="65" ht="42" customHeight="1">
       <c r="A65" s="21" t="inlineStr">
         <is>
-          <t>SV10</t>
+          <t>SV8</t>
         </is>
       </c>
       <c r="B65" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to delete an event with no approved hours.</t>
+          <t>As a supervisor, I want to create an event.</t>
         </is>
       </c>
       <c r="C65" s="22" t="inlineStr">
         <is>
-          <t>Delete such an event → confirm.</t>
+          <t>New Event → title, description, slot, address, date, times, capacity, grade limits → save.</t>
         </is>
       </c>
       <c r="D65" s="22" t="inlineStr">
         <is>
-          <t>Event deleted.</t>
+          <t>Credit auto-calculated from times; event created in My Events.</t>
         </is>
       </c>
       <c r="E65" s="23" t="n"/>
@@ -11023,22 +11173,22 @@
     <row r="66" ht="42" customHeight="1">
       <c r="A66" s="21" t="inlineStr">
         <is>
-          <t>SV11</t>
+          <t>SV9</t>
         </is>
       </c>
       <c r="B66" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, deleting an event with approved hours is blocked.</t>
+          <t>As a supervisor, I want to edit an event.</t>
         </is>
       </c>
       <c r="C66" s="22" t="inlineStr">
         <is>
-          <t>Try to delete an event that has approved hours.</t>
+          <t>My Events → edit → save.</t>
         </is>
       </c>
       <c r="D66" s="22" t="inlineStr">
         <is>
-          <t>Blocked with a message that approved hours must be preserved.</t>
+          <t>Changes persist and show to participants.</t>
         </is>
       </c>
       <c r="E66" s="23" t="n"/>
@@ -11048,22 +11198,22 @@
     <row r="67" ht="42" customHeight="1">
       <c r="A67" s="21" t="inlineStr">
         <is>
-          <t>SV12</t>
+          <t>SV10</t>
         </is>
       </c>
       <c r="B67" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to see who signed up.</t>
+          <t>As a supervisor, I want to delete an event with no approved hours.</t>
         </is>
       </c>
       <c r="C67" s="22" t="inlineStr">
         <is>
-          <t>Open the event Roster.</t>
+          <t>Delete such an event → confirm.</t>
         </is>
       </c>
       <c r="D67" s="22" t="inlineStr">
         <is>
-          <t>Registrants listed with grade and status.</t>
+          <t>Event deleted.</t>
         </is>
       </c>
       <c r="E67" s="23" t="n"/>
@@ -11073,22 +11223,22 @@
     <row r="68" ht="42" customHeight="1">
       <c r="A68" s="21" t="inlineStr">
         <is>
-          <t>SV13</t>
+          <t>SV11</t>
         </is>
       </c>
       <c r="B68" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to check people in / mark no-show.</t>
+          <t>As a supervisor, deleting an event with approved hours is blocked.</t>
         </is>
       </c>
       <c r="C68" s="22" t="inlineStr">
         <is>
-          <t>On the roster, Check in and Mark no-show.</t>
+          <t>Try to delete an event that has approved hours.</t>
         </is>
       </c>
       <c r="D68" s="22" t="inlineStr">
         <is>
-          <t>Status updates and persists.</t>
+          <t>Blocked with a message that approved hours must be preserved.</t>
         </is>
       </c>
       <c r="E68" s="23" t="n"/>
@@ -11098,22 +11248,22 @@
     <row r="69" ht="42" customHeight="1">
       <c r="A69" s="21" t="inlineStr">
         <is>
-          <t>SV14</t>
+          <t>SV12</t>
         </is>
       </c>
       <c r="B69" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to message everyone signed up.</t>
+          <t>As a supervisor, I want to see who signed up.</t>
         </is>
       </c>
       <c r="C69" s="22" t="inlineStr">
         <is>
-          <t>Roster → Message attendees → subject+message → send (include guardians on).</t>
+          <t>Open the event Roster.</t>
         </is>
       </c>
       <c r="D69" s="22" t="inlineStr">
         <is>
-          <t>Each registrant (and guardians) emailed individually; recipient count shown.</t>
+          <t>Registrants listed with grade and status.</t>
         </is>
       </c>
       <c r="E69" s="23" t="n"/>
@@ -11123,22 +11273,22 @@
     <row r="70" ht="42" customHeight="1">
       <c r="A70" s="21" t="inlineStr">
         <is>
-          <t>SV15</t>
+          <t>SV13</t>
         </is>
       </c>
       <c r="B70" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want a history of what I reviewed.</t>
+          <t>As a supervisor, I want to check people in / mark no-show.</t>
         </is>
       </c>
       <c r="C70" s="22" t="inlineStr">
         <is>
-          <t>Open Reviewed History.</t>
+          <t>On the roster, Check in and Mark no-show.</t>
         </is>
       </c>
       <c r="D70" s="22" t="inlineStr">
         <is>
-          <t>Every approved/rejected item with dates and volunteers.</t>
+          <t>Status updates and persists.</t>
         </is>
       </c>
       <c r="E70" s="23" t="n"/>
@@ -11148,22 +11298,22 @@
     <row r="71" ht="42" customHeight="1">
       <c r="A71" s="21" t="inlineStr">
         <is>
-          <t>SV16</t>
+          <t>SV14</t>
         </is>
       </c>
       <c r="B71" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to browse all opportunities view-only.</t>
+          <t>As a supervisor, I want to message everyone signed up.</t>
         </is>
       </c>
       <c r="C71" s="22" t="inlineStr">
         <is>
-          <t>All Opportunities → search / upcoming-past.</t>
+          <t>Roster → Message attendees → subject+message → send (include guardians on).</t>
         </is>
       </c>
       <c r="D71" s="22" t="inlineStr">
         <is>
-          <t>Every event listed read-only; can't edit others' events.</t>
+          <t>Each registrant (and guardians) emailed individually; recipient count shown.</t>
         </is>
       </c>
       <c r="E71" s="23" t="n"/>
@@ -11173,22 +11323,22 @@
     <row r="72" ht="42" customHeight="1">
       <c r="A72" s="21" t="inlineStr">
         <is>
-          <t>SV17</t>
+          <t>SV15</t>
         </is>
       </c>
       <c r="B72" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to log my own adult hours.</t>
+          <t>As a supervisor, I want a history of what I reviewed.</t>
         </is>
       </c>
       <c r="C72" s="22" t="inlineStr">
         <is>
-          <t>My Hours → log an activity, date, hours → save.</t>
+          <t>Open Reviewed History.</t>
         </is>
       </c>
       <c r="D72" s="22" t="inlineStr">
         <is>
-          <t>Recorded instantly with a running total; clearly NOT part of the student competition.</t>
+          <t>Every approved/rejected item with dates and volunteers.</t>
         </is>
       </c>
       <c r="E72" s="23" t="n"/>
@@ -11198,22 +11348,22 @@
     <row r="73" ht="42" customHeight="1">
       <c r="A73" s="21" t="inlineStr">
         <is>
-          <t>SV18</t>
+          <t>SV16</t>
         </is>
       </c>
       <c r="B73" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to delete an adult-hours entry.</t>
+          <t>As a supervisor, I want to browse all opportunities view-only.</t>
         </is>
       </c>
       <c r="C73" s="22" t="inlineStr">
         <is>
-          <t>My Hours → delete an entry → confirm.</t>
+          <t>All Opportunities → search / upcoming-past.</t>
         </is>
       </c>
       <c r="D73" s="22" t="inlineStr">
         <is>
-          <t>Removed; total updates.</t>
+          <t>Every event listed read-only; can't edit others' events.</t>
         </is>
       </c>
       <c r="E73" s="23" t="n"/>
@@ -11223,110 +11373,110 @@
     <row r="74" ht="42" customHeight="1">
       <c r="A74" s="21" t="inlineStr">
         <is>
-          <t>SV19</t>
+          <t>SV17</t>
         </is>
       </c>
       <c r="B74" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I must NOT access user or org management.</t>
+          <t>As a supervisor, I want to log my own adult hours.</t>
         </is>
       </c>
       <c r="C74" s="22" t="inlineStr">
         <is>
-          <t>Look for Users / Organizations in the menu.</t>
+          <t>My Hours → log an activity, date, hours → save.</t>
         </is>
       </c>
       <c r="D74" s="22" t="inlineStr">
         <is>
-          <t>Those tabs are absent; direct URLs are blocked.</t>
+          <t>Recorded instantly with a running total; clearly NOT part of the student competition.</t>
         </is>
       </c>
       <c r="E74" s="23" t="n"/>
       <c r="F74" s="22" t="n"/>
       <c r="G74" s="23" t="n"/>
     </row>
-    <row r="75" ht="20" customHeight="1">
-      <c r="A75" s="19" t="inlineStr">
-        <is>
-          <t>Admin (org-scoped)</t>
-        </is>
-      </c>
-      <c r="B75" s="20" t="n"/>
-      <c r="C75" s="20" t="n"/>
-      <c r="D75" s="20" t="n"/>
-      <c r="E75" s="20" t="n"/>
-      <c r="F75" s="20" t="n"/>
-      <c r="G75" s="20" t="n"/>
+    <row r="75" ht="42" customHeight="1">
+      <c r="A75" s="21" t="inlineStr">
+        <is>
+          <t>SV18</t>
+        </is>
+      </c>
+      <c r="B75" s="22" t="inlineStr">
+        <is>
+          <t>As a supervisor, I want to delete an adult-hours entry.</t>
+        </is>
+      </c>
+      <c r="C75" s="22" t="inlineStr">
+        <is>
+          <t>My Hours → delete an entry → confirm.</t>
+        </is>
+      </c>
+      <c r="D75" s="22" t="inlineStr">
+        <is>
+          <t>Removed; total updates.</t>
+        </is>
+      </c>
+      <c r="E75" s="23" t="n"/>
+      <c r="F75" s="22" t="n"/>
+      <c r="G75" s="23" t="n"/>
     </row>
     <row r="76" ht="42" customHeight="1">
       <c r="A76" s="21" t="inlineStr">
         <is>
-          <t>AD1</t>
+          <t>SV19</t>
         </is>
       </c>
       <c r="B76" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I want the correct menu tabs.</t>
+          <t>As a supervisor, I must NOT access user or org management.</t>
         </is>
       </c>
       <c r="C76" s="22" t="inlineStr">
         <is>
-          <t>Look at the left menu.</t>
+          <t>Look for Users / Organizations in the menu.</t>
         </is>
       </c>
       <c r="D76" s="22" t="inlineStr">
         <is>
-          <t>Dashboard, Pending Reviews, Reviewed History, My Events, All Opportunities, Users, Organizations, My Hours, Help.</t>
+          <t>Those tabs are absent; direct URLs are blocked.</t>
         </is>
       </c>
       <c r="E76" s="23" t="n"/>
       <c r="F76" s="22" t="n"/>
       <c r="G76" s="23" t="n"/>
     </row>
-    <row r="77" ht="42" customHeight="1">
-      <c r="A77" s="21" t="inlineStr">
-        <is>
-          <t>AD2</t>
-        </is>
-      </c>
-      <c r="B77" s="22" t="inlineStr">
-        <is>
-          <t>As an Admin, I can do everything a supervisor can.</t>
-        </is>
-      </c>
-      <c r="C77" s="22" t="inlineStr">
-        <is>
-          <t>Spot-check: approve an item and create an event.</t>
-        </is>
-      </c>
-      <c r="D77" s="22" t="inlineStr">
-        <is>
-          <t>Both work.</t>
-        </is>
-      </c>
-      <c r="E77" s="23" t="n"/>
-      <c r="F77" s="22" t="n"/>
-      <c r="G77" s="23" t="n"/>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="19" t="inlineStr">
+        <is>
+          <t>Admin (org-scoped)</t>
+        </is>
+      </c>
+      <c r="B77" s="20" t="n"/>
+      <c r="C77" s="20" t="n"/>
+      <c r="D77" s="20" t="n"/>
+      <c r="E77" s="20" t="n"/>
+      <c r="F77" s="20" t="n"/>
+      <c r="G77" s="20" t="n"/>
     </row>
     <row r="78" ht="42" customHeight="1">
       <c r="A78" s="21" t="inlineStr">
         <is>
-          <t>AD3</t>
+          <t>AD1</t>
         </is>
       </c>
       <c r="B78" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I only see my org's non-admin users.</t>
+          <t>As an Admin, I want the correct menu tabs.</t>
         </is>
       </c>
       <c r="C78" s="22" t="inlineStr">
         <is>
-          <t>Open Users.</t>
+          <t>Look at the left menu.</t>
         </is>
       </c>
       <c r="D78" s="22" t="inlineStr">
         <is>
-          <t>Only participants/parents/supervisors in your org; no admins/super admins; no other orgs.</t>
+          <t>Dashboard, Pending Reviews, Reviewed History, My Events, All Opportunities, Users, Organizations, My Hours, Help.</t>
         </is>
       </c>
       <c r="E78" s="23" t="n"/>
@@ -11336,22 +11486,22 @@
     <row r="79" ht="42" customHeight="1">
       <c r="A79" s="21" t="inlineStr">
         <is>
-          <t>AD4</t>
+          <t>AD2</t>
         </is>
       </c>
       <c r="B79" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I want to add a supervisor.</t>
+          <t>As an Admin, I can do everything a supervisor can.</t>
         </is>
       </c>
       <c r="C79" s="22" t="inlineStr">
         <is>
-          <t>Users → Add user → Supervisor → save.</t>
+          <t>Spot-check: approve an item and create an event.</t>
         </is>
       </c>
       <c r="D79" s="22" t="inlineStr">
         <is>
-          <t>Supervisor created, stamped to your org; invite email sent.</t>
+          <t>Both work.</t>
         </is>
       </c>
       <c r="E79" s="23" t="n"/>
@@ -11361,22 +11511,22 @@
     <row r="80" ht="42" customHeight="1">
       <c r="A80" s="21" t="inlineStr">
         <is>
-          <t>AD5</t>
+          <t>AD3</t>
         </is>
       </c>
       <c r="B80" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I want to create a participant as a fallback.</t>
+          <t>As an Admin, I only see my org's non-admin users.</t>
         </is>
       </c>
       <c r="C80" s="22" t="inlineStr">
         <is>
-          <t>Users → Add user → Participant → save.</t>
+          <t>Open Users.</t>
         </is>
       </c>
       <c r="D80" s="22" t="inlineStr">
         <is>
-          <t>Participant created with a set-password invite (no silent password).</t>
+          <t>Only participants/parents/supervisors in your org; no admins/super admins; no other orgs.</t>
         </is>
       </c>
       <c r="E80" s="23" t="n"/>
@@ -11386,22 +11536,22 @@
     <row r="81" ht="42" customHeight="1">
       <c r="A81" s="21" t="inlineStr">
         <is>
-          <t>AD6</t>
+          <t>AD4</t>
         </is>
       </c>
       <c r="B81" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I want to grant participant hours.</t>
+          <t>As an Admin, I want to add a supervisor.</t>
         </is>
       </c>
       <c r="C81" s="22" t="inlineStr">
         <is>
-          <t>Open a participant in your org → Add hours.</t>
+          <t>Users → Add user → Supervisor → save.</t>
         </is>
       </c>
       <c r="D81" s="22" t="inlineStr">
         <is>
-          <t>Hours auto-approved; count toward their total/medals.</t>
+          <t>Supervisor created, stamped to your org; invite email sent.</t>
         </is>
       </c>
       <c r="E81" s="23" t="n"/>
@@ -11411,22 +11561,22 @@
     <row r="82" ht="42" customHeight="1">
       <c r="A82" s="21" t="inlineStr">
         <is>
-          <t>AD7</t>
+          <t>AD5</t>
         </is>
       </c>
       <c r="B82" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I want a participant's service record.</t>
+          <t>As an Admin, I want to create a participant as a fallback.</t>
         </is>
       </c>
       <c r="C82" s="22" t="inlineStr">
         <is>
-          <t>Users → Service record for a participant in your org.</t>
+          <t>Users → Add user → Participant → save.</t>
         </is>
       </c>
       <c r="D82" s="22" t="inlineStr">
         <is>
-          <t>Record opens.</t>
+          <t>Participant created with a set-password invite (no silent password).</t>
         </is>
       </c>
       <c r="E82" s="23" t="n"/>
@@ -11436,22 +11586,22 @@
     <row r="83" ht="42" customHeight="1">
       <c r="A83" s="21" t="inlineStr">
         <is>
-          <t>AD8</t>
+          <t>AD6</t>
         </is>
       </c>
       <c r="B83" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I want to edit/delete my org's users.</t>
+          <t>As an Admin, I want to grant participant hours.</t>
         </is>
       </c>
       <c r="C83" s="22" t="inlineStr">
         <is>
-          <t>Edit a name/phone; delete a test user.</t>
+          <t>Open a participant in your org → Add hours.</t>
         </is>
       </c>
       <c r="D83" s="22" t="inlineStr">
         <is>
-          <t>Changes apply within your org.</t>
+          <t>Hours auto-approved; count toward their total/medals.</t>
         </is>
       </c>
       <c r="E83" s="23" t="n"/>
@@ -11461,22 +11611,22 @@
     <row r="84" ht="42" customHeight="1">
       <c r="A84" s="21" t="inlineStr">
         <is>
-          <t>AD9</t>
+          <t>AD7</t>
         </is>
       </c>
       <c r="B84" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I must NOT act on users outside my org.</t>
+          <t>As an Admin, I want a participant's service record.</t>
         </is>
       </c>
       <c r="C84" s="22" t="inlineStr">
         <is>
-          <t>Attempt to reach another org's user (e.g. direct URL).</t>
+          <t>Users → Service record for a participant in your org.</t>
         </is>
       </c>
       <c r="D84" s="22" t="inlineStr">
         <is>
-          <t>Blocked / not visible.</t>
+          <t>Record opens.</t>
         </is>
       </c>
       <c r="E84" s="23" t="n"/>
@@ -11486,22 +11636,22 @@
     <row r="85" ht="42" customHeight="1">
       <c r="A85" s="21" t="inlineStr">
         <is>
-          <t>AD10</t>
+          <t>AD8</t>
         </is>
       </c>
       <c r="B85" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I cannot grant Admin access or manage admins.</t>
+          <t>As an Admin, I want to edit/delete my org's users.</t>
         </is>
       </c>
       <c r="C85" s="22" t="inlineStr">
         <is>
-          <t>Look for the 'grant Admin access' action.</t>
+          <t>Edit a name/phone; delete a test user.</t>
         </is>
       </c>
       <c r="D85" s="22" t="inlineStr">
         <is>
-          <t>No such button; attempts are blocked server-side.</t>
+          <t>Changes apply within your org.</t>
         </is>
       </c>
       <c r="E85" s="23" t="n"/>
@@ -11511,22 +11661,22 @@
     <row r="86" ht="42" customHeight="1">
       <c r="A86" s="21" t="inlineStr">
         <is>
-          <t>AD11</t>
+          <t>AD9</t>
         </is>
       </c>
       <c r="B86" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I see and edit only my own organization.</t>
+          <t>As an Admin, I must NOT act on users outside my org.</t>
         </is>
       </c>
       <c r="C86" s="22" t="inlineStr">
         <is>
-          <t>Open Organizations.</t>
+          <t>Attempt to reach another org's user (e.g. direct URL).</t>
         </is>
       </c>
       <c r="D86" s="22" t="inlineStr">
         <is>
-          <t>Only your org shows; you can edit its settings.</t>
+          <t>Blocked / not visible.</t>
         </is>
       </c>
       <c r="E86" s="23" t="n"/>
@@ -11536,22 +11686,22 @@
     <row r="87" ht="42" customHeight="1">
       <c r="A87" s="21" t="inlineStr">
         <is>
-          <t>AD12</t>
+          <t>AD10</t>
         </is>
       </c>
       <c r="B87" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I want to generate/rotate my org's join code.</t>
+          <t>As an Admin, I cannot grant Admin access or manage admins.</t>
         </is>
       </c>
       <c r="C87" s="22" t="inlineStr">
         <is>
-          <t>Organizations → set/generate a join code → save.</t>
+          <t>Look for the 'grant Admin access' action.</t>
         </is>
       </c>
       <c r="D87" s="22" t="inlineStr">
         <is>
-          <t>Join code saved; usable at sign-up.</t>
+          <t>No such button; attempts are blocked server-side.</t>
         </is>
       </c>
       <c r="E87" s="23" t="n"/>
@@ -11561,22 +11711,22 @@
     <row r="88" ht="42" customHeight="1">
       <c r="A88" s="21" t="inlineStr">
         <is>
-          <t>AD13</t>
+          <t>AD11</t>
         </is>
       </c>
       <c r="B88" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I cannot create organizations.</t>
+          <t>As an Admin, I see and edit only my own organization.</t>
         </is>
       </c>
       <c r="C88" s="22" t="inlineStr">
         <is>
-          <t>Look for 'Add organization'.</t>
+          <t>Open Organizations.</t>
         </is>
       </c>
       <c r="D88" s="22" t="inlineStr">
         <is>
-          <t>No Add button; creation blocked.</t>
+          <t>Only your org shows; you can edit its settings.</t>
         </is>
       </c>
       <c r="E88" s="23" t="n"/>
@@ -11586,110 +11736,110 @@
     <row r="89" ht="42" customHeight="1">
       <c r="A89" s="21" t="inlineStr">
         <is>
-          <t>AD14</t>
+          <t>AD12</t>
         </is>
       </c>
       <c r="B89" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I cannot change the recycling cans total.</t>
+          <t>As an Admin, I want to generate/rotate my org's join code.</t>
         </is>
       </c>
       <c r="C89" s="22" t="inlineStr">
         <is>
-          <t>Look for the cans/bin admin control.</t>
+          <t>Organizations → set/generate a join code → save.</t>
         </is>
       </c>
       <c r="D89" s="22" t="inlineStr">
         <is>
-          <t>Not available (Super Admin only).</t>
+          <t>Join code saved; usable at sign-up.</t>
         </is>
       </c>
       <c r="E89" s="23" t="n"/>
       <c r="F89" s="22" t="n"/>
       <c r="G89" s="23" t="n"/>
     </row>
-    <row r="90" ht="20" customHeight="1">
-      <c r="A90" s="19" t="inlineStr">
-        <is>
-          <t>Super Admin (global)</t>
-        </is>
-      </c>
-      <c r="B90" s="20" t="n"/>
-      <c r="C90" s="20" t="n"/>
-      <c r="D90" s="20" t="n"/>
-      <c r="E90" s="20" t="n"/>
-      <c r="F90" s="20" t="n"/>
-      <c r="G90" s="20" t="n"/>
+    <row r="90" ht="42" customHeight="1">
+      <c r="A90" s="21" t="inlineStr">
+        <is>
+          <t>AD13</t>
+        </is>
+      </c>
+      <c r="B90" s="22" t="inlineStr">
+        <is>
+          <t>As an Admin, I cannot create organizations.</t>
+        </is>
+      </c>
+      <c r="C90" s="22" t="inlineStr">
+        <is>
+          <t>Look for 'Add organization'.</t>
+        </is>
+      </c>
+      <c r="D90" s="22" t="inlineStr">
+        <is>
+          <t>No Add button; creation blocked.</t>
+        </is>
+      </c>
+      <c r="E90" s="23" t="n"/>
+      <c r="F90" s="22" t="n"/>
+      <c r="G90" s="23" t="n"/>
     </row>
     <row r="91" ht="42" customHeight="1">
       <c r="A91" s="21" t="inlineStr">
         <is>
-          <t>SA1</t>
+          <t>AD14</t>
         </is>
       </c>
       <c r="B91" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want the correct menu tabs.</t>
+          <t>As an Admin, I cannot change the recycling cans total.</t>
         </is>
       </c>
       <c r="C91" s="22" t="inlineStr">
         <is>
-          <t>Look at the left menu.</t>
+          <t>Look for the cans/bin admin control.</t>
         </is>
       </c>
       <c r="D91" s="22" t="inlineStr">
         <is>
-          <t>Dashboard, Reports, Users, Events, Organizations (Help in footer).</t>
+          <t>Not available (Super Admin only).</t>
         </is>
       </c>
       <c r="E91" s="23" t="n"/>
       <c r="F91" s="22" t="n"/>
       <c r="G91" s="23" t="n"/>
     </row>
-    <row r="92" ht="42" customHeight="1">
-      <c r="A92" s="21" t="inlineStr">
-        <is>
-          <t>SA2</t>
-        </is>
-      </c>
-      <c r="B92" s="22" t="inlineStr">
-        <is>
-          <t>As a Super Admin, I can do everything an Admin can, across all orgs.</t>
-        </is>
-      </c>
-      <c r="C92" s="22" t="inlineStr">
-        <is>
-          <t>Spot-check user + org actions on more than one org.</t>
-        </is>
-      </c>
-      <c r="D92" s="22" t="inlineStr">
-        <is>
-          <t>All allowed regardless of org.</t>
-        </is>
-      </c>
-      <c r="E92" s="23" t="n"/>
-      <c r="F92" s="22" t="n"/>
-      <c r="G92" s="23" t="n"/>
+    <row r="92" ht="20" customHeight="1">
+      <c r="A92" s="19" t="inlineStr">
+        <is>
+          <t>Super Admin (global)</t>
+        </is>
+      </c>
+      <c r="B92" s="20" t="n"/>
+      <c r="C92" s="20" t="n"/>
+      <c r="D92" s="20" t="n"/>
+      <c r="E92" s="20" t="n"/>
+      <c r="F92" s="20" t="n"/>
+      <c r="G92" s="20" t="n"/>
     </row>
     <row r="93" ht="42" customHeight="1">
       <c r="A93" s="21" t="inlineStr">
         <is>
-          <t>SA3</t>
+          <t>SA1</t>
         </is>
       </c>
       <c r="B93" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to create users incl. Supervisor and Super Admin.</t>
+          <t>As a Super Admin, I want the correct menu tabs.</t>
         </is>
       </c>
       <c r="C93" s="22" t="inlineStr">
         <is>
-          <t>Users → Add user → each role.</t>
+          <t>Look at the left menu.</t>
         </is>
       </c>
       <c r="D93" s="22" t="inlineStr">
         <is>
-          <t>Participant/Supervisor/Super Admin options available; account created + invite email.</t>
+          <t>Dashboard, Reports, Users, Events, Organizations (Help in footer).</t>
         </is>
       </c>
       <c r="E93" s="23" t="n"/>
@@ -11699,22 +11849,22 @@
     <row r="94" ht="42" customHeight="1">
       <c r="A94" s="21" t="inlineStr">
         <is>
-          <t>SA4</t>
+          <t>SA2</t>
         </is>
       </c>
       <c r="B94" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to grant/revoke Admin access.</t>
+          <t>As a Super Admin, I can do everything an Admin can, across all orgs.</t>
         </is>
       </c>
       <c r="C94" s="22" t="inlineStr">
         <is>
-          <t>Open a user → grant Admin access → check org(s) → save; then uncheck all → save.</t>
+          <t>Spot-check user + org actions on more than one org.</t>
         </is>
       </c>
       <c r="D94" s="22" t="inlineStr">
         <is>
-          <t>Checking orgs makes an Admin; unchecking all reverts to participant.</t>
+          <t>All allowed regardless of org.</t>
         </is>
       </c>
       <c r="E94" s="23" t="n"/>
@@ -11724,22 +11874,22 @@
     <row r="95" ht="42" customHeight="1">
       <c r="A95" s="21" t="inlineStr">
         <is>
-          <t>SA5</t>
+          <t>SA3</t>
         </is>
       </c>
       <c r="B95" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to create organizations + join codes.</t>
+          <t>As a Super Admin, I want to create users incl. Supervisor and Super Admin.</t>
         </is>
       </c>
       <c r="C95" s="22" t="inlineStr">
         <is>
-          <t>Organizations → Add organization → set details + join code.</t>
+          <t>Users → Add user → each role.</t>
         </is>
       </c>
       <c r="D95" s="22" t="inlineStr">
         <is>
-          <t>Org created with its join code.</t>
+          <t>Participant/Supervisor/Super Admin options available; account created + invite email.</t>
         </is>
       </c>
       <c r="E95" s="23" t="n"/>
@@ -11749,22 +11899,22 @@
     <row r="96" ht="42" customHeight="1">
       <c r="A96" s="21" t="inlineStr">
         <is>
-          <t>SA6</t>
+          <t>SA4</t>
         </is>
       </c>
       <c r="B96" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to find users by type.</t>
+          <t>As a Super Admin, I want to grant/revoke Admin access.</t>
         </is>
       </c>
       <c r="C96" s="22" t="inlineStr">
         <is>
-          <t>Users → role filter pills + search.</t>
+          <t>Open a user → grant Admin access → check org(s) → save; then uncheck all → save.</t>
         </is>
       </c>
       <c r="D96" s="22" t="inlineStr">
         <is>
-          <t>Filter by role with counts; search by name/email across all orgs.</t>
+          <t>Checking orgs makes an Admin; unchecking all reverts to participant.</t>
         </is>
       </c>
       <c r="E96" s="23" t="n"/>
@@ -11774,22 +11924,22 @@
     <row r="97" ht="42" customHeight="1">
       <c r="A97" s="21" t="inlineStr">
         <is>
-          <t>SA7</t>
+          <t>SA5</t>
         </is>
       </c>
       <c r="B97" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to search events.</t>
+          <t>As a Super Admin, I want to create organizations + join codes.</t>
         </is>
       </c>
       <c r="C97" s="22" t="inlineStr">
         <is>
-          <t>Events → search + date range; check supervisor/org per card.</t>
+          <t>Organizations → Add organization → set details + join code.</t>
         </is>
       </c>
       <c r="D97" s="22" t="inlineStr">
         <is>
-          <t>Filters work; each event shows supervisor and organization.</t>
+          <t>Org created with its join code.</t>
         </is>
       </c>
       <c r="E97" s="23" t="n"/>
@@ -11799,22 +11949,22 @@
     <row r="98" ht="42" customHeight="1">
       <c r="A98" s="21" t="inlineStr">
         <is>
-          <t>SA8</t>
+          <t>SA6</t>
         </is>
       </c>
       <c r="B98" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want clear event-visibility labels.</t>
+          <t>As a Super Admin, I want to find users by type.</t>
         </is>
       </c>
       <c r="C98" s="22" t="inlineStr">
         <is>
-          <t>New Event → 'Who can see this'.</t>
+          <t>Users → role filter pills + search.</t>
         </is>
       </c>
       <c r="D98" s="22" t="inlineStr">
         <is>
-          <t>'Open to all (community)' and 'Only &lt;org&gt; students' with helper text.</t>
+          <t>Filter by role with counts; search by name/email across all orgs.</t>
         </is>
       </c>
       <c r="E98" s="23" t="n"/>
@@ -11824,22 +11974,22 @@
     <row r="99" ht="42" customHeight="1">
       <c r="A99" s="21" t="inlineStr">
         <is>
-          <t>SA9</t>
+          <t>SA7</t>
         </is>
       </c>
       <c r="B99" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want program-wide reports.</t>
+          <t>As a Super Admin, I want to search events.</t>
         </is>
       </c>
       <c r="C99" s="22" t="inlineStr">
         <is>
-          <t>Open Reports / Dashboard.</t>
+          <t>Events → search + date range; check supervisor/org per card.</t>
         </is>
       </c>
       <c r="D99" s="22" t="inlineStr">
         <is>
-          <t>Totals and charts across the whole program.</t>
+          <t>Filters work; each event shows supervisor and organization.</t>
         </is>
       </c>
       <c r="E99" s="23" t="n"/>
@@ -11849,22 +11999,22 @@
     <row r="100" ht="42" customHeight="1">
       <c r="A100" s="21" t="inlineStr">
         <is>
-          <t>SA10</t>
+          <t>SA8</t>
         </is>
       </c>
       <c r="B100" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to verify email works.</t>
+          <t>As a Super Admin, I want clear event-visibility labels.</t>
         </is>
       </c>
       <c r="C100" s="22" t="inlineStr">
         <is>
-          <t>Dashboard → Send test email.</t>
+          <t>New Event → 'Who can see this'.</t>
         </is>
       </c>
       <c r="D100" s="22" t="inlineStr">
         <is>
-          <t>Result shown (success or the exact failure reason).</t>
+          <t>'Open to all (community)' and 'Only &lt;org&gt; students' with helper text.</t>
         </is>
       </c>
       <c r="E100" s="23" t="n"/>
@@ -11874,22 +12024,22 @@
     <row r="101" ht="42" customHeight="1">
       <c r="A101" s="21" t="inlineStr">
         <is>
-          <t>SA11</t>
+          <t>SA9</t>
         </is>
       </c>
       <c r="B101" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to update the recycling cans total.</t>
+          <t>As a Super Admin, I want program-wide reports.</t>
         </is>
       </c>
       <c r="C101" s="22" t="inlineStr">
         <is>
-          <t>Use the cans/bin admin control.</t>
+          <t>Open Reports / Dashboard.</t>
         </is>
       </c>
       <c r="D101" s="22" t="inlineStr">
         <is>
-          <t>Total updates; the ribbon reflects it.</t>
+          <t>Totals and charts across the whole program.</t>
         </is>
       </c>
       <c r="E101" s="23" t="n"/>
@@ -11899,102 +12049,152 @@
     <row r="102" ht="42" customHeight="1">
       <c r="A102" s="21" t="inlineStr">
         <is>
-          <t>SA12</t>
+          <t>SA10</t>
         </is>
       </c>
       <c r="B102" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want hours + records for any user.</t>
+          <t>As a Super Admin, I want to verify email works.</t>
         </is>
       </c>
       <c r="C102" s="22" t="inlineStr">
         <is>
-          <t>Add manual hours / open service record for any participant.</t>
+          <t>Dashboard → Send test email.</t>
         </is>
       </c>
       <c r="D102" s="22" t="inlineStr">
         <is>
-          <t>Works for any org.</t>
+          <t>Result shown (success or the exact failure reason).</t>
         </is>
       </c>
       <c r="E102" s="23" t="n"/>
       <c r="F102" s="22" t="n"/>
       <c r="G102" s="23" t="n"/>
     </row>
-    <row r="103" ht="20" customHeight="1">
-      <c r="A103" s="19" t="inlineStr">
-        <is>
-          <t>Cross-cutting</t>
-        </is>
-      </c>
-      <c r="B103" s="20" t="n"/>
-      <c r="C103" s="20" t="n"/>
-      <c r="D103" s="20" t="n"/>
-      <c r="E103" s="20" t="n"/>
-      <c r="F103" s="20" t="n"/>
-      <c r="G103" s="20" t="n"/>
+    <row r="103" ht="42" customHeight="1">
+      <c r="A103" s="21" t="inlineStr">
+        <is>
+          <t>SA11</t>
+        </is>
+      </c>
+      <c r="B103" s="22" t="inlineStr">
+        <is>
+          <t>As a Super Admin, I want to update the recycling cans total.</t>
+        </is>
+      </c>
+      <c r="C103" s="22" t="inlineStr">
+        <is>
+          <t>Use the cans/bin admin control.</t>
+        </is>
+      </c>
+      <c r="D103" s="22" t="inlineStr">
+        <is>
+          <t>Total updates; the ribbon reflects it.</t>
+        </is>
+      </c>
+      <c r="E103" s="23" t="n"/>
+      <c r="F103" s="22" t="n"/>
+      <c r="G103" s="23" t="n"/>
     </row>
     <row r="104" ht="42" customHeight="1">
       <c r="A104" s="21" t="inlineStr">
         <is>
-          <t>X1</t>
+          <t>SA12</t>
         </is>
       </c>
       <c r="B104" s="22" t="inlineStr">
         <is>
-          <t>As a phone user, I want a usable mobile layout.</t>
+          <t>As a Super Admin, I want hours + records for any user.</t>
         </is>
       </c>
       <c r="C104" s="22" t="inlineStr">
         <is>
-          <t>Open at phone width; use the menu drawer.</t>
+          <t>Add manual hours / open service record for any participant.</t>
         </is>
       </c>
       <c r="D104" s="22" t="inlineStr">
         <is>
-          <t>Layout adapts; drawer opens/closes; no horizontal scroll.</t>
+          <t>Works for any org.</t>
         </is>
       </c>
       <c r="E104" s="23" t="n"/>
       <c r="F104" s="22" t="n"/>
       <c r="G104" s="23" t="n"/>
     </row>
-    <row r="105" ht="42" customHeight="1">
-      <c r="A105" s="21" t="inlineStr">
+    <row r="105" ht="20" customHeight="1">
+      <c r="A105" s="19" t="inlineStr">
+        <is>
+          <t>Cross-cutting</t>
+        </is>
+      </c>
+      <c r="B105" s="20" t="n"/>
+      <c r="C105" s="20" t="n"/>
+      <c r="D105" s="20" t="n"/>
+      <c r="E105" s="20" t="n"/>
+      <c r="F105" s="20" t="n"/>
+      <c r="G105" s="20" t="n"/>
+    </row>
+    <row r="106" ht="42" customHeight="1">
+      <c r="A106" s="21" t="inlineStr">
+        <is>
+          <t>X1</t>
+        </is>
+      </c>
+      <c r="B106" s="22" t="inlineStr">
+        <is>
+          <t>As a phone user, I want a usable mobile layout.</t>
+        </is>
+      </c>
+      <c r="C106" s="22" t="inlineStr">
+        <is>
+          <t>Open at phone width; use the menu drawer.</t>
+        </is>
+      </c>
+      <c r="D106" s="22" t="inlineStr">
+        <is>
+          <t>Layout adapts; drawer opens/closes; no horizontal scroll.</t>
+        </is>
+      </c>
+      <c r="E106" s="23" t="n"/>
+      <c r="F106" s="22" t="n"/>
+      <c r="G106" s="23" t="n"/>
+    </row>
+    <row r="107" ht="42" customHeight="1">
+      <c r="A107" s="21" t="inlineStr">
         <is>
           <t>X2</t>
         </is>
       </c>
-      <c r="B105" s="22" t="inlineStr">
+      <c r="B107" s="22" t="inlineStr">
         <is>
           <t>As a visitor, I want the recycling ribbon on the login page.</t>
         </is>
       </c>
-      <c r="C105" s="22" t="inlineStr">
+      <c r="C107" s="22" t="inlineStr">
         <is>
           <t>Open login signed out.</t>
         </is>
       </c>
-      <c r="D105" s="22" t="inlineStr">
+      <c r="D107" s="22" t="inlineStr">
         <is>
           <t>Green ribbon shows on login.</t>
         </is>
       </c>
-      <c r="E105" s="23" t="n"/>
-      <c r="F105" s="22" t="n"/>
-      <c r="G105" s="23" t="n"/>
+      <c r="E107" s="23" t="n"/>
+      <c r="F107" s="22" t="n"/>
+      <c r="G107" s="23" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A55:G55"/>
+    <mergeCell ref="A77:G77"/>
+    <mergeCell ref="A105:G105"/>
     <mergeCell ref="A35:G35"/>
-    <mergeCell ref="A90:G90"/>
-    <mergeCell ref="A49:G49"/>
+    <mergeCell ref="A92:G92"/>
+    <mergeCell ref="A57:G57"/>
+    <mergeCell ref="A51:G51"/>
     <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A103:G103"/>
-    <mergeCell ref="A75:G75"/>
   </mergeCells>
   <conditionalFormatting sqref="E4:E9">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
@@ -12018,7 +12218,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E36:E48">
+  <conditionalFormatting sqref="E36:E50">
     <cfRule type="cellIs" priority="7" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -12029,7 +12229,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E50:E54">
+  <conditionalFormatting sqref="E52:E56">
     <cfRule type="cellIs" priority="10" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -12040,7 +12240,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E56:E74">
+  <conditionalFormatting sqref="E58:E76">
     <cfRule type="cellIs" priority="13" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -12051,7 +12251,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E76:E89">
+  <conditionalFormatting sqref="E78:E91">
     <cfRule type="cellIs" priority="16" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -12062,7 +12262,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E91:E102">
+  <conditionalFormatting sqref="E93:E104">
     <cfRule type="cellIs" priority="19" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -12073,7 +12273,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E104:E105">
+  <conditionalFormatting sqref="E106:E107">
     <cfRule type="cellIs" priority="22" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -12085,7 +12285,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E4:E9 E11:E34 E36:E48 E50:E54 E56:E74 E76:E89 E91:E102 E104:E105" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E4:E9 E11:E34 E36:E50 E52:E56 E58:E76 E78:E91 E93:E104 E106:E107" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pass,Fail,Blocked,Not tested,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -12099,7 +12299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G105"/>
+  <dimension ref="A1:G107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -13275,88 +13475,88 @@
       <c r="F48" s="22" t="n"/>
       <c r="G48" s="23" t="n"/>
     </row>
-    <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="19" t="inlineStr">
-        <is>
-          <t>Parent — viewer (grades 6–12 student)</t>
-        </is>
-      </c>
-      <c r="B49" s="20" t="n"/>
-      <c r="C49" s="20" t="n"/>
-      <c r="D49" s="20" t="n"/>
-      <c r="E49" s="20" t="n"/>
-      <c r="F49" s="20" t="n"/>
-      <c r="G49" s="20" t="n"/>
+    <row r="49" ht="42" customHeight="1">
+      <c r="A49" s="21" t="inlineStr">
+        <is>
+          <t>PE14</t>
+        </is>
+      </c>
+      <c r="B49" s="22" t="inlineStr">
+        <is>
+          <t>As a parent, I want to log my child's outside/nonprofit volunteering.</t>
+        </is>
+      </c>
+      <c r="C49" s="22" t="inlineStr">
+        <is>
+          <t>Child card → 'Outside hours' → fill activity, org, date, hours, supervisor → Submit.</t>
+        </is>
+      </c>
+      <c r="D49" s="22" t="inlineStr">
+        <is>
+          <t>External hours submitted for the child and sent for supervisor approval (proof required over 5h).</t>
+        </is>
+      </c>
+      <c r="E49" s="23" t="n"/>
+      <c r="F49" s="22" t="n"/>
+      <c r="G49" s="23" t="n"/>
     </row>
     <row r="50" ht="42" customHeight="1">
       <c r="A50" s="21" t="inlineStr">
         <is>
-          <t>PV1</t>
+          <t>PE15</t>
         </is>
       </c>
       <c r="B50" s="22" t="inlineStr">
         <is>
-          <t>As a parent of a 6–12 student, I want to register for view-only access.</t>
+          <t>As a parent, I want my child's verified service record.</t>
         </is>
       </c>
       <c r="C50" s="22" t="inlineStr">
         <is>
-          <t>Create account → parent of a 6–12 student.</t>
+          <t>Child card → 'Service record'.</t>
         </is>
       </c>
       <c r="D50" s="22" t="inlineStr">
         <is>
-          <t>Account created; no invite required to register.</t>
+          <t>The child's itemized record opens; Print / Save-as-PDF works.</t>
         </is>
       </c>
       <c r="E50" s="23" t="n"/>
       <c r="F50" s="22" t="n"/>
       <c r="G50" s="23" t="n"/>
     </row>
-    <row r="51" ht="42" customHeight="1">
-      <c r="A51" s="21" t="inlineStr">
-        <is>
-          <t>PV2</t>
-        </is>
-      </c>
-      <c r="B51" s="22" t="inlineStr">
-        <is>
-          <t>As a viewer parent, my student links automatically by email.</t>
-        </is>
-      </c>
-      <c r="C51" s="22" t="inlineStr">
-        <is>
-          <t>Have a student enter this exact email as their parent email (before or after you register).</t>
-        </is>
-      </c>
-      <c r="D51" s="22" t="inlineStr">
-        <is>
-          <t>The student appears on your dashboard automatically; empty until then.</t>
-        </is>
-      </c>
-      <c r="E51" s="23" t="n"/>
-      <c r="F51" s="22" t="n"/>
-      <c r="G51" s="23" t="n"/>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="19" t="inlineStr">
+        <is>
+          <t>Parent — viewer (grades 6–12 student)</t>
+        </is>
+      </c>
+      <c r="B51" s="20" t="n"/>
+      <c r="C51" s="20" t="n"/>
+      <c r="D51" s="20" t="n"/>
+      <c r="E51" s="20" t="n"/>
+      <c r="F51" s="20" t="n"/>
+      <c r="G51" s="20" t="n"/>
     </row>
     <row r="52" ht="42" customHeight="1">
       <c r="A52" s="21" t="inlineStr">
         <is>
-          <t>PV3</t>
+          <t>PV1</t>
         </is>
       </c>
       <c r="B52" s="22" t="inlineStr">
         <is>
-          <t>As a viewer parent, I want to see my student's schedule/progress.</t>
+          <t>As a parent of a 6–12 student, I want to register for view-only access.</t>
         </is>
       </c>
       <c r="C52" s="22" t="inlineStr">
         <is>
-          <t>Open the dashboard.</t>
+          <t>Create account → parent of a 6–12 student.</t>
         </is>
       </c>
       <c r="D52" s="22" t="inlineStr">
         <is>
-          <t>View-only schedule and progress.</t>
+          <t>Account created; no invite required to register.</t>
         </is>
       </c>
       <c r="E52" s="23" t="n"/>
@@ -13366,22 +13566,22 @@
     <row r="53" ht="42" customHeight="1">
       <c r="A53" s="21" t="inlineStr">
         <is>
-          <t>PV4</t>
+          <t>PV2</t>
         </is>
       </c>
       <c r="B53" s="22" t="inlineStr">
         <is>
-          <t>As a viewer parent, I do NOT sign the student up.</t>
+          <t>As a viewer parent, my student links automatically by email.</t>
         </is>
       </c>
       <c r="C53" s="22" t="inlineStr">
         <is>
-          <t>Look for a sign-up action.</t>
+          <t>Have a student enter this exact email as their parent email (before or after you register).</t>
         </is>
       </c>
       <c r="D53" s="22" t="inlineStr">
         <is>
-          <t>No sign-up on the student's behalf — the student self-serves.</t>
+          <t>The student appears on your dashboard automatically; empty until then.</t>
         </is>
       </c>
       <c r="E53" s="23" t="n"/>
@@ -13391,110 +13591,110 @@
     <row r="54" ht="42" customHeight="1">
       <c r="A54" s="21" t="inlineStr">
         <is>
-          <t>PV5</t>
+          <t>PV3</t>
         </is>
       </c>
       <c r="B54" s="22" t="inlineStr">
         <is>
-          <t>As a viewer parent, I want to invite a co-guardian.</t>
+          <t>As a viewer parent, I want to see my student's schedule/progress.</t>
         </is>
       </c>
       <c r="C54" s="22" t="inlineStr">
         <is>
-          <t>Invite a co-guardian by email.</t>
+          <t>Open the dashboard.</t>
         </is>
       </c>
       <c r="D54" s="22" t="inlineStr">
         <is>
-          <t>Invite email sent; shared access on registration.</t>
+          <t>View-only schedule and progress.</t>
         </is>
       </c>
       <c r="E54" s="23" t="n"/>
       <c r="F54" s="22" t="n"/>
       <c r="G54" s="23" t="n"/>
     </row>
-    <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="19" t="inlineStr">
-        <is>
-          <t>Supervisor (created by an Admin)</t>
-        </is>
-      </c>
-      <c r="B55" s="20" t="n"/>
-      <c r="C55" s="20" t="n"/>
-      <c r="D55" s="20" t="n"/>
-      <c r="E55" s="20" t="n"/>
-      <c r="F55" s="20" t="n"/>
-      <c r="G55" s="20" t="n"/>
+    <row r="55" ht="42" customHeight="1">
+      <c r="A55" s="21" t="inlineStr">
+        <is>
+          <t>PV4</t>
+        </is>
+      </c>
+      <c r="B55" s="22" t="inlineStr">
+        <is>
+          <t>As a viewer parent, I do NOT sign the student up.</t>
+        </is>
+      </c>
+      <c r="C55" s="22" t="inlineStr">
+        <is>
+          <t>Look for a sign-up action.</t>
+        </is>
+      </c>
+      <c r="D55" s="22" t="inlineStr">
+        <is>
+          <t>No sign-up on the student's behalf — the student self-serves.</t>
+        </is>
+      </c>
+      <c r="E55" s="23" t="n"/>
+      <c r="F55" s="22" t="n"/>
+      <c r="G55" s="23" t="n"/>
     </row>
     <row r="56" ht="42" customHeight="1">
       <c r="A56" s="21" t="inlineStr">
         <is>
-          <t>SV1</t>
+          <t>PV5</t>
         </is>
       </c>
       <c r="B56" s="22" t="inlineStr">
         <is>
-          <t>As the program, a supervisor cannot self-register.</t>
+          <t>As a viewer parent, I want to invite a co-guardian.</t>
         </is>
       </c>
       <c r="C56" s="22" t="inlineStr">
         <is>
-          <t>Review the sign-up options.</t>
+          <t>Invite a co-guardian by email.</t>
         </is>
       </c>
       <c r="D56" s="22" t="inlineStr">
         <is>
-          <t>No supervisor option exists on registration.</t>
+          <t>Invite email sent; shared access on registration.</t>
         </is>
       </c>
       <c r="E56" s="23" t="n"/>
       <c r="F56" s="22" t="n"/>
       <c r="G56" s="23" t="n"/>
     </row>
-    <row r="57" ht="42" customHeight="1">
-      <c r="A57" s="21" t="inlineStr">
-        <is>
-          <t>SV2</t>
-        </is>
-      </c>
-      <c r="B57" s="22" t="inlineStr">
-        <is>
-          <t>As a new supervisor, I get an invite to set my password.</t>
-        </is>
-      </c>
-      <c r="C57" s="22" t="inlineStr">
-        <is>
-          <t>Have an Admin create your account; open the invite email; set password; sign in.</t>
-        </is>
-      </c>
-      <c r="D57" s="22" t="inlineStr">
-        <is>
-          <t>Invite email arrives with a working set-password link; you can sign in.</t>
-        </is>
-      </c>
-      <c r="E57" s="23" t="n"/>
-      <c r="F57" s="22" t="n"/>
-      <c r="G57" s="23" t="n"/>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="19" t="inlineStr">
+        <is>
+          <t>Supervisor (created by an Admin)</t>
+        </is>
+      </c>
+      <c r="B57" s="20" t="n"/>
+      <c r="C57" s="20" t="n"/>
+      <c r="D57" s="20" t="n"/>
+      <c r="E57" s="20" t="n"/>
+      <c r="F57" s="20" t="n"/>
+      <c r="G57" s="20" t="n"/>
     </row>
     <row r="58" ht="42" customHeight="1">
       <c r="A58" s="21" t="inlineStr">
         <is>
-          <t>SV3</t>
+          <t>SV1</t>
         </is>
       </c>
       <c r="B58" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want the correct 7 left-menu tabs.</t>
+          <t>As the program, a supervisor cannot self-register.</t>
         </is>
       </c>
       <c r="C58" s="22" t="inlineStr">
         <is>
-          <t>Look at the left menu.</t>
+          <t>Review the sign-up options.</t>
         </is>
       </c>
       <c r="D58" s="22" t="inlineStr">
         <is>
-          <t>Dashboard, Pending Reviews, Reviewed History, My Events, All Opportunities, My Hours, Help.</t>
+          <t>No supervisor option exists on registration.</t>
         </is>
       </c>
       <c r="E58" s="23" t="n"/>
@@ -13504,22 +13704,22 @@
     <row r="59" ht="42" customHeight="1">
       <c r="A59" s="21" t="inlineStr">
         <is>
-          <t>SV4</t>
+          <t>SV2</t>
         </is>
       </c>
       <c r="B59" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want a dashboard.</t>
+          <t>As a new supervisor, I get an invite to set my password.</t>
         </is>
       </c>
       <c r="C59" s="22" t="inlineStr">
         <is>
-          <t>Open the dashboard.</t>
+          <t>Have an Admin create your account; open the invite email; set password; sign in.</t>
         </is>
       </c>
       <c r="D59" s="22" t="inlineStr">
         <is>
-          <t>Review queue, approved/rejected counts, registrations, hours, upcoming events + Roster links.</t>
+          <t>Invite email arrives with a working set-password link; you can sign in.</t>
         </is>
       </c>
       <c r="E59" s="23" t="n"/>
@@ -13529,22 +13729,22 @@
     <row r="60" ht="42" customHeight="1">
       <c r="A60" s="21" t="inlineStr">
         <is>
-          <t>SV5</t>
+          <t>SV3</t>
         </is>
       </c>
       <c r="B60" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to approve hours.</t>
+          <t>As a supervisor, I want the correct 7 left-menu tabs.</t>
         </is>
       </c>
       <c r="C60" s="22" t="inlineStr">
         <is>
-          <t>Pending Reviews → open → Approve.</t>
+          <t>Look at the left menu.</t>
         </is>
       </c>
       <c r="D60" s="22" t="inlineStr">
         <is>
-          <t>Approved; moves to Reviewed History; participant total updates; email sent.</t>
+          <t>Dashboard, Pending Reviews, Reviewed History, My Events, All Opportunities, My Hours, Help.</t>
         </is>
       </c>
       <c r="E60" s="23" t="n"/>
@@ -13554,22 +13754,22 @@
     <row r="61" ht="42" customHeight="1">
       <c r="A61" s="21" t="inlineStr">
         <is>
-          <t>SV6</t>
+          <t>SV4</t>
         </is>
       </c>
       <c r="B61" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to reject hours with a reason.</t>
+          <t>As a supervisor, I want a dashboard.</t>
         </is>
       </c>
       <c r="C61" s="22" t="inlineStr">
         <is>
-          <t>Reject without a reason, then with one.</t>
+          <t>Open the dashboard.</t>
         </is>
       </c>
       <c r="D61" s="22" t="inlineStr">
         <is>
-          <t>Blocked until a reason is given; then rejected and the participant notified.</t>
+          <t>Review queue, approved/rejected counts, registrations, hours, upcoming events + Roster links.</t>
         </is>
       </c>
       <c r="E61" s="23" t="n"/>
@@ -13579,22 +13779,22 @@
     <row r="62" ht="42" customHeight="1">
       <c r="A62" s="21" t="inlineStr">
         <is>
-          <t>SV7</t>
+          <t>SV5</t>
         </is>
       </c>
       <c r="B62" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to review external submissions.</t>
+          <t>As a supervisor, I want to approve hours.</t>
         </is>
       </c>
       <c r="C62" s="22" t="inlineStr">
         <is>
-          <t>Pending Reviews → external tab → approve/reject.</t>
+          <t>Pending Reviews → open → Approve.</t>
         </is>
       </c>
       <c r="D62" s="22" t="inlineStr">
         <is>
-          <t>External items reviewable, including any proof.</t>
+          <t>Approved; moves to Reviewed History; participant total updates; email sent.</t>
         </is>
       </c>
       <c r="E62" s="23" t="n"/>
@@ -13604,22 +13804,22 @@
     <row r="63" ht="42" customHeight="1">
       <c r="A63" s="21" t="inlineStr">
         <is>
-          <t>SV8</t>
+          <t>SV6</t>
         </is>
       </c>
       <c r="B63" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to create an event.</t>
+          <t>As a supervisor, I want to reject hours with a reason.</t>
         </is>
       </c>
       <c r="C63" s="22" t="inlineStr">
         <is>
-          <t>New Event → title, description, slot, address, date, times, capacity, grade limits → save.</t>
+          <t>Reject without a reason, then with one.</t>
         </is>
       </c>
       <c r="D63" s="22" t="inlineStr">
         <is>
-          <t>Credit auto-calculated from times; event created in My Events.</t>
+          <t>Blocked until a reason is given; then rejected and the participant notified.</t>
         </is>
       </c>
       <c r="E63" s="23" t="n"/>
@@ -13629,22 +13829,22 @@
     <row r="64" ht="42" customHeight="1">
       <c r="A64" s="21" t="inlineStr">
         <is>
-          <t>SV9</t>
+          <t>SV7</t>
         </is>
       </c>
       <c r="B64" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to edit an event.</t>
+          <t>As a supervisor, I want to review external submissions.</t>
         </is>
       </c>
       <c r="C64" s="22" t="inlineStr">
         <is>
-          <t>My Events → edit → save.</t>
+          <t>Pending Reviews → external tab → approve/reject.</t>
         </is>
       </c>
       <c r="D64" s="22" t="inlineStr">
         <is>
-          <t>Changes persist and show to participants.</t>
+          <t>External items reviewable, including any proof.</t>
         </is>
       </c>
       <c r="E64" s="23" t="n"/>
@@ -13654,22 +13854,22 @@
     <row r="65" ht="42" customHeight="1">
       <c r="A65" s="21" t="inlineStr">
         <is>
-          <t>SV10</t>
+          <t>SV8</t>
         </is>
       </c>
       <c r="B65" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to delete an event with no approved hours.</t>
+          <t>As a supervisor, I want to create an event.</t>
         </is>
       </c>
       <c r="C65" s="22" t="inlineStr">
         <is>
-          <t>Delete such an event → confirm.</t>
+          <t>New Event → title, description, slot, address, date, times, capacity, grade limits → save.</t>
         </is>
       </c>
       <c r="D65" s="22" t="inlineStr">
         <is>
-          <t>Event deleted.</t>
+          <t>Credit auto-calculated from times; event created in My Events.</t>
         </is>
       </c>
       <c r="E65" s="23" t="n"/>
@@ -13679,22 +13879,22 @@
     <row r="66" ht="42" customHeight="1">
       <c r="A66" s="21" t="inlineStr">
         <is>
-          <t>SV11</t>
+          <t>SV9</t>
         </is>
       </c>
       <c r="B66" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, deleting an event with approved hours is blocked.</t>
+          <t>As a supervisor, I want to edit an event.</t>
         </is>
       </c>
       <c r="C66" s="22" t="inlineStr">
         <is>
-          <t>Try to delete an event that has approved hours.</t>
+          <t>My Events → edit → save.</t>
         </is>
       </c>
       <c r="D66" s="22" t="inlineStr">
         <is>
-          <t>Blocked with a message that approved hours must be preserved.</t>
+          <t>Changes persist and show to participants.</t>
         </is>
       </c>
       <c r="E66" s="23" t="n"/>
@@ -13704,22 +13904,22 @@
     <row r="67" ht="42" customHeight="1">
       <c r="A67" s="21" t="inlineStr">
         <is>
-          <t>SV12</t>
+          <t>SV10</t>
         </is>
       </c>
       <c r="B67" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to see who signed up.</t>
+          <t>As a supervisor, I want to delete an event with no approved hours.</t>
         </is>
       </c>
       <c r="C67" s="22" t="inlineStr">
         <is>
-          <t>Open the event Roster.</t>
+          <t>Delete such an event → confirm.</t>
         </is>
       </c>
       <c r="D67" s="22" t="inlineStr">
         <is>
-          <t>Registrants listed with grade and status.</t>
+          <t>Event deleted.</t>
         </is>
       </c>
       <c r="E67" s="23" t="n"/>
@@ -13729,22 +13929,22 @@
     <row r="68" ht="42" customHeight="1">
       <c r="A68" s="21" t="inlineStr">
         <is>
-          <t>SV13</t>
+          <t>SV11</t>
         </is>
       </c>
       <c r="B68" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to check people in / mark no-show.</t>
+          <t>As a supervisor, deleting an event with approved hours is blocked.</t>
         </is>
       </c>
       <c r="C68" s="22" t="inlineStr">
         <is>
-          <t>On the roster, Check in and Mark no-show.</t>
+          <t>Try to delete an event that has approved hours.</t>
         </is>
       </c>
       <c r="D68" s="22" t="inlineStr">
         <is>
-          <t>Status updates and persists.</t>
+          <t>Blocked with a message that approved hours must be preserved.</t>
         </is>
       </c>
       <c r="E68" s="23" t="n"/>
@@ -13754,22 +13954,22 @@
     <row r="69" ht="42" customHeight="1">
       <c r="A69" s="21" t="inlineStr">
         <is>
-          <t>SV14</t>
+          <t>SV12</t>
         </is>
       </c>
       <c r="B69" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to message everyone signed up.</t>
+          <t>As a supervisor, I want to see who signed up.</t>
         </is>
       </c>
       <c r="C69" s="22" t="inlineStr">
         <is>
-          <t>Roster → Message attendees → subject+message → send (include guardians on).</t>
+          <t>Open the event Roster.</t>
         </is>
       </c>
       <c r="D69" s="22" t="inlineStr">
         <is>
-          <t>Each registrant (and guardians) emailed individually; recipient count shown.</t>
+          <t>Registrants listed with grade and status.</t>
         </is>
       </c>
       <c r="E69" s="23" t="n"/>
@@ -13779,22 +13979,22 @@
     <row r="70" ht="42" customHeight="1">
       <c r="A70" s="21" t="inlineStr">
         <is>
-          <t>SV15</t>
+          <t>SV13</t>
         </is>
       </c>
       <c r="B70" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want a history of what I reviewed.</t>
+          <t>As a supervisor, I want to check people in / mark no-show.</t>
         </is>
       </c>
       <c r="C70" s="22" t="inlineStr">
         <is>
-          <t>Open Reviewed History.</t>
+          <t>On the roster, Check in and Mark no-show.</t>
         </is>
       </c>
       <c r="D70" s="22" t="inlineStr">
         <is>
-          <t>Every approved/rejected item with dates and volunteers.</t>
+          <t>Status updates and persists.</t>
         </is>
       </c>
       <c r="E70" s="23" t="n"/>
@@ -13804,22 +14004,22 @@
     <row r="71" ht="42" customHeight="1">
       <c r="A71" s="21" t="inlineStr">
         <is>
-          <t>SV16</t>
+          <t>SV14</t>
         </is>
       </c>
       <c r="B71" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to browse all opportunities view-only.</t>
+          <t>As a supervisor, I want to message everyone signed up.</t>
         </is>
       </c>
       <c r="C71" s="22" t="inlineStr">
         <is>
-          <t>All Opportunities → search / upcoming-past.</t>
+          <t>Roster → Message attendees → subject+message → send (include guardians on).</t>
         </is>
       </c>
       <c r="D71" s="22" t="inlineStr">
         <is>
-          <t>Every event listed read-only; can't edit others' events.</t>
+          <t>Each registrant (and guardians) emailed individually; recipient count shown.</t>
         </is>
       </c>
       <c r="E71" s="23" t="n"/>
@@ -13829,22 +14029,22 @@
     <row r="72" ht="42" customHeight="1">
       <c r="A72" s="21" t="inlineStr">
         <is>
-          <t>SV17</t>
+          <t>SV15</t>
         </is>
       </c>
       <c r="B72" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to log my own adult hours.</t>
+          <t>As a supervisor, I want a history of what I reviewed.</t>
         </is>
       </c>
       <c r="C72" s="22" t="inlineStr">
         <is>
-          <t>My Hours → log an activity, date, hours → save.</t>
+          <t>Open Reviewed History.</t>
         </is>
       </c>
       <c r="D72" s="22" t="inlineStr">
         <is>
-          <t>Recorded instantly with a running total; clearly NOT part of the student competition.</t>
+          <t>Every approved/rejected item with dates and volunteers.</t>
         </is>
       </c>
       <c r="E72" s="23" t="n"/>
@@ -13854,22 +14054,22 @@
     <row r="73" ht="42" customHeight="1">
       <c r="A73" s="21" t="inlineStr">
         <is>
-          <t>SV18</t>
+          <t>SV16</t>
         </is>
       </c>
       <c r="B73" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I want to delete an adult-hours entry.</t>
+          <t>As a supervisor, I want to browse all opportunities view-only.</t>
         </is>
       </c>
       <c r="C73" s="22" t="inlineStr">
         <is>
-          <t>My Hours → delete an entry → confirm.</t>
+          <t>All Opportunities → search / upcoming-past.</t>
         </is>
       </c>
       <c r="D73" s="22" t="inlineStr">
         <is>
-          <t>Removed; total updates.</t>
+          <t>Every event listed read-only; can't edit others' events.</t>
         </is>
       </c>
       <c r="E73" s="23" t="n"/>
@@ -13879,110 +14079,110 @@
     <row r="74" ht="42" customHeight="1">
       <c r="A74" s="21" t="inlineStr">
         <is>
-          <t>SV19</t>
+          <t>SV17</t>
         </is>
       </c>
       <c r="B74" s="22" t="inlineStr">
         <is>
-          <t>As a supervisor, I must NOT access user or org management.</t>
+          <t>As a supervisor, I want to log my own adult hours.</t>
         </is>
       </c>
       <c r="C74" s="22" t="inlineStr">
         <is>
-          <t>Look for Users / Organizations in the menu.</t>
+          <t>My Hours → log an activity, date, hours → save.</t>
         </is>
       </c>
       <c r="D74" s="22" t="inlineStr">
         <is>
-          <t>Those tabs are absent; direct URLs are blocked.</t>
+          <t>Recorded instantly with a running total; clearly NOT part of the student competition.</t>
         </is>
       </c>
       <c r="E74" s="23" t="n"/>
       <c r="F74" s="22" t="n"/>
       <c r="G74" s="23" t="n"/>
     </row>
-    <row r="75" ht="20" customHeight="1">
-      <c r="A75" s="19" t="inlineStr">
-        <is>
-          <t>Admin (org-scoped)</t>
-        </is>
-      </c>
-      <c r="B75" s="20" t="n"/>
-      <c r="C75" s="20" t="n"/>
-      <c r="D75" s="20" t="n"/>
-      <c r="E75" s="20" t="n"/>
-      <c r="F75" s="20" t="n"/>
-      <c r="G75" s="20" t="n"/>
+    <row r="75" ht="42" customHeight="1">
+      <c r="A75" s="21" t="inlineStr">
+        <is>
+          <t>SV18</t>
+        </is>
+      </c>
+      <c r="B75" s="22" t="inlineStr">
+        <is>
+          <t>As a supervisor, I want to delete an adult-hours entry.</t>
+        </is>
+      </c>
+      <c r="C75" s="22" t="inlineStr">
+        <is>
+          <t>My Hours → delete an entry → confirm.</t>
+        </is>
+      </c>
+      <c r="D75" s="22" t="inlineStr">
+        <is>
+          <t>Removed; total updates.</t>
+        </is>
+      </c>
+      <c r="E75" s="23" t="n"/>
+      <c r="F75" s="22" t="n"/>
+      <c r="G75" s="23" t="n"/>
     </row>
     <row r="76" ht="42" customHeight="1">
       <c r="A76" s="21" t="inlineStr">
         <is>
-          <t>AD1</t>
+          <t>SV19</t>
         </is>
       </c>
       <c r="B76" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I want the correct menu tabs.</t>
+          <t>As a supervisor, I must NOT access user or org management.</t>
         </is>
       </c>
       <c r="C76" s="22" t="inlineStr">
         <is>
-          <t>Look at the left menu.</t>
+          <t>Look for Users / Organizations in the menu.</t>
         </is>
       </c>
       <c r="D76" s="22" t="inlineStr">
         <is>
-          <t>Dashboard, Pending Reviews, Reviewed History, My Events, All Opportunities, Users, Organizations, My Hours, Help.</t>
+          <t>Those tabs are absent; direct URLs are blocked.</t>
         </is>
       </c>
       <c r="E76" s="23" t="n"/>
       <c r="F76" s="22" t="n"/>
       <c r="G76" s="23" t="n"/>
     </row>
-    <row r="77" ht="42" customHeight="1">
-      <c r="A77" s="21" t="inlineStr">
-        <is>
-          <t>AD2</t>
-        </is>
-      </c>
-      <c r="B77" s="22" t="inlineStr">
-        <is>
-          <t>As an Admin, I can do everything a supervisor can.</t>
-        </is>
-      </c>
-      <c r="C77" s="22" t="inlineStr">
-        <is>
-          <t>Spot-check: approve an item and create an event.</t>
-        </is>
-      </c>
-      <c r="D77" s="22" t="inlineStr">
-        <is>
-          <t>Both work.</t>
-        </is>
-      </c>
-      <c r="E77" s="23" t="n"/>
-      <c r="F77" s="22" t="n"/>
-      <c r="G77" s="23" t="n"/>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="19" t="inlineStr">
+        <is>
+          <t>Admin (org-scoped)</t>
+        </is>
+      </c>
+      <c r="B77" s="20" t="n"/>
+      <c r="C77" s="20" t="n"/>
+      <c r="D77" s="20" t="n"/>
+      <c r="E77" s="20" t="n"/>
+      <c r="F77" s="20" t="n"/>
+      <c r="G77" s="20" t="n"/>
     </row>
     <row r="78" ht="42" customHeight="1">
       <c r="A78" s="21" t="inlineStr">
         <is>
-          <t>AD3</t>
+          <t>AD1</t>
         </is>
       </c>
       <c r="B78" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I only see my org's non-admin users.</t>
+          <t>As an Admin, I want the correct menu tabs.</t>
         </is>
       </c>
       <c r="C78" s="22" t="inlineStr">
         <is>
-          <t>Open Users.</t>
+          <t>Look at the left menu.</t>
         </is>
       </c>
       <c r="D78" s="22" t="inlineStr">
         <is>
-          <t>Only participants/parents/supervisors in your org; no admins/super admins; no other orgs.</t>
+          <t>Dashboard, Pending Reviews, Reviewed History, My Events, All Opportunities, Users, Organizations, My Hours, Help.</t>
         </is>
       </c>
       <c r="E78" s="23" t="n"/>
@@ -13992,22 +14192,22 @@
     <row r="79" ht="42" customHeight="1">
       <c r="A79" s="21" t="inlineStr">
         <is>
-          <t>AD4</t>
+          <t>AD2</t>
         </is>
       </c>
       <c r="B79" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I want to add a supervisor.</t>
+          <t>As an Admin, I can do everything a supervisor can.</t>
         </is>
       </c>
       <c r="C79" s="22" t="inlineStr">
         <is>
-          <t>Users → Add user → Supervisor → save.</t>
+          <t>Spot-check: approve an item and create an event.</t>
         </is>
       </c>
       <c r="D79" s="22" t="inlineStr">
         <is>
-          <t>Supervisor created, stamped to your org; invite email sent.</t>
+          <t>Both work.</t>
         </is>
       </c>
       <c r="E79" s="23" t="n"/>
@@ -14017,22 +14217,22 @@
     <row r="80" ht="42" customHeight="1">
       <c r="A80" s="21" t="inlineStr">
         <is>
-          <t>AD5</t>
+          <t>AD3</t>
         </is>
       </c>
       <c r="B80" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I want to create a participant as a fallback.</t>
+          <t>As an Admin, I only see my org's non-admin users.</t>
         </is>
       </c>
       <c r="C80" s="22" t="inlineStr">
         <is>
-          <t>Users → Add user → Participant → save.</t>
+          <t>Open Users.</t>
         </is>
       </c>
       <c r="D80" s="22" t="inlineStr">
         <is>
-          <t>Participant created with a set-password invite (no silent password).</t>
+          <t>Only participants/parents/supervisors in your org; no admins/super admins; no other orgs.</t>
         </is>
       </c>
       <c r="E80" s="23" t="n"/>
@@ -14042,22 +14242,22 @@
     <row r="81" ht="42" customHeight="1">
       <c r="A81" s="21" t="inlineStr">
         <is>
-          <t>AD6</t>
+          <t>AD4</t>
         </is>
       </c>
       <c r="B81" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I want to grant participant hours.</t>
+          <t>As an Admin, I want to add a supervisor.</t>
         </is>
       </c>
       <c r="C81" s="22" t="inlineStr">
         <is>
-          <t>Open a participant in your org → Add hours.</t>
+          <t>Users → Add user → Supervisor → save.</t>
         </is>
       </c>
       <c r="D81" s="22" t="inlineStr">
         <is>
-          <t>Hours auto-approved; count toward their total/medals.</t>
+          <t>Supervisor created, stamped to your org; invite email sent.</t>
         </is>
       </c>
       <c r="E81" s="23" t="n"/>
@@ -14067,22 +14267,22 @@
     <row r="82" ht="42" customHeight="1">
       <c r="A82" s="21" t="inlineStr">
         <is>
-          <t>AD7</t>
+          <t>AD5</t>
         </is>
       </c>
       <c r="B82" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I want a participant's service record.</t>
+          <t>As an Admin, I want to create a participant as a fallback.</t>
         </is>
       </c>
       <c r="C82" s="22" t="inlineStr">
         <is>
-          <t>Users → Service record for a participant in your org.</t>
+          <t>Users → Add user → Participant → save.</t>
         </is>
       </c>
       <c r="D82" s="22" t="inlineStr">
         <is>
-          <t>Record opens.</t>
+          <t>Participant created with a set-password invite (no silent password).</t>
         </is>
       </c>
       <c r="E82" s="23" t="n"/>
@@ -14092,22 +14292,22 @@
     <row r="83" ht="42" customHeight="1">
       <c r="A83" s="21" t="inlineStr">
         <is>
-          <t>AD8</t>
+          <t>AD6</t>
         </is>
       </c>
       <c r="B83" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I want to edit/delete my org's users.</t>
+          <t>As an Admin, I want to grant participant hours.</t>
         </is>
       </c>
       <c r="C83" s="22" t="inlineStr">
         <is>
-          <t>Edit a name/phone; delete a test user.</t>
+          <t>Open a participant in your org → Add hours.</t>
         </is>
       </c>
       <c r="D83" s="22" t="inlineStr">
         <is>
-          <t>Changes apply within your org.</t>
+          <t>Hours auto-approved; count toward their total/medals.</t>
         </is>
       </c>
       <c r="E83" s="23" t="n"/>
@@ -14117,22 +14317,22 @@
     <row r="84" ht="42" customHeight="1">
       <c r="A84" s="21" t="inlineStr">
         <is>
-          <t>AD9</t>
+          <t>AD7</t>
         </is>
       </c>
       <c r="B84" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I must NOT act on users outside my org.</t>
+          <t>As an Admin, I want a participant's service record.</t>
         </is>
       </c>
       <c r="C84" s="22" t="inlineStr">
         <is>
-          <t>Attempt to reach another org's user (e.g. direct URL).</t>
+          <t>Users → Service record for a participant in your org.</t>
         </is>
       </c>
       <c r="D84" s="22" t="inlineStr">
         <is>
-          <t>Blocked / not visible.</t>
+          <t>Record opens.</t>
         </is>
       </c>
       <c r="E84" s="23" t="n"/>
@@ -14142,22 +14342,22 @@
     <row r="85" ht="42" customHeight="1">
       <c r="A85" s="21" t="inlineStr">
         <is>
-          <t>AD10</t>
+          <t>AD8</t>
         </is>
       </c>
       <c r="B85" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I cannot grant Admin access or manage admins.</t>
+          <t>As an Admin, I want to edit/delete my org's users.</t>
         </is>
       </c>
       <c r="C85" s="22" t="inlineStr">
         <is>
-          <t>Look for the 'grant Admin access' action.</t>
+          <t>Edit a name/phone; delete a test user.</t>
         </is>
       </c>
       <c r="D85" s="22" t="inlineStr">
         <is>
-          <t>No such button; attempts are blocked server-side.</t>
+          <t>Changes apply within your org.</t>
         </is>
       </c>
       <c r="E85" s="23" t="n"/>
@@ -14167,22 +14367,22 @@
     <row r="86" ht="42" customHeight="1">
       <c r="A86" s="21" t="inlineStr">
         <is>
-          <t>AD11</t>
+          <t>AD9</t>
         </is>
       </c>
       <c r="B86" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I see and edit only my own organization.</t>
+          <t>As an Admin, I must NOT act on users outside my org.</t>
         </is>
       </c>
       <c r="C86" s="22" t="inlineStr">
         <is>
-          <t>Open Organizations.</t>
+          <t>Attempt to reach another org's user (e.g. direct URL).</t>
         </is>
       </c>
       <c r="D86" s="22" t="inlineStr">
         <is>
-          <t>Only your org shows; you can edit its settings.</t>
+          <t>Blocked / not visible.</t>
         </is>
       </c>
       <c r="E86" s="23" t="n"/>
@@ -14192,22 +14392,22 @@
     <row r="87" ht="42" customHeight="1">
       <c r="A87" s="21" t="inlineStr">
         <is>
-          <t>AD12</t>
+          <t>AD10</t>
         </is>
       </c>
       <c r="B87" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I want to generate/rotate my org's join code.</t>
+          <t>As an Admin, I cannot grant Admin access or manage admins.</t>
         </is>
       </c>
       <c r="C87" s="22" t="inlineStr">
         <is>
-          <t>Organizations → set/generate a join code → save.</t>
+          <t>Look for the 'grant Admin access' action.</t>
         </is>
       </c>
       <c r="D87" s="22" t="inlineStr">
         <is>
-          <t>Join code saved; usable at sign-up.</t>
+          <t>No such button; attempts are blocked server-side.</t>
         </is>
       </c>
       <c r="E87" s="23" t="n"/>
@@ -14217,22 +14417,22 @@
     <row r="88" ht="42" customHeight="1">
       <c r="A88" s="21" t="inlineStr">
         <is>
-          <t>AD13</t>
+          <t>AD11</t>
         </is>
       </c>
       <c r="B88" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I cannot create organizations.</t>
+          <t>As an Admin, I see and edit only my own organization.</t>
         </is>
       </c>
       <c r="C88" s="22" t="inlineStr">
         <is>
-          <t>Look for 'Add organization'.</t>
+          <t>Open Organizations.</t>
         </is>
       </c>
       <c r="D88" s="22" t="inlineStr">
         <is>
-          <t>No Add button; creation blocked.</t>
+          <t>Only your org shows; you can edit its settings.</t>
         </is>
       </c>
       <c r="E88" s="23" t="n"/>
@@ -14242,110 +14442,110 @@
     <row r="89" ht="42" customHeight="1">
       <c r="A89" s="21" t="inlineStr">
         <is>
-          <t>AD14</t>
+          <t>AD12</t>
         </is>
       </c>
       <c r="B89" s="22" t="inlineStr">
         <is>
-          <t>As an Admin, I cannot change the recycling cans total.</t>
+          <t>As an Admin, I want to generate/rotate my org's join code.</t>
         </is>
       </c>
       <c r="C89" s="22" t="inlineStr">
         <is>
-          <t>Look for the cans/bin admin control.</t>
+          <t>Organizations → set/generate a join code → save.</t>
         </is>
       </c>
       <c r="D89" s="22" t="inlineStr">
         <is>
-          <t>Not available (Super Admin only).</t>
+          <t>Join code saved; usable at sign-up.</t>
         </is>
       </c>
       <c r="E89" s="23" t="n"/>
       <c r="F89" s="22" t="n"/>
       <c r="G89" s="23" t="n"/>
     </row>
-    <row r="90" ht="20" customHeight="1">
-      <c r="A90" s="19" t="inlineStr">
-        <is>
-          <t>Super Admin (global)</t>
-        </is>
-      </c>
-      <c r="B90" s="20" t="n"/>
-      <c r="C90" s="20" t="n"/>
-      <c r="D90" s="20" t="n"/>
-      <c r="E90" s="20" t="n"/>
-      <c r="F90" s="20" t="n"/>
-      <c r="G90" s="20" t="n"/>
+    <row r="90" ht="42" customHeight="1">
+      <c r="A90" s="21" t="inlineStr">
+        <is>
+          <t>AD13</t>
+        </is>
+      </c>
+      <c r="B90" s="22" t="inlineStr">
+        <is>
+          <t>As an Admin, I cannot create organizations.</t>
+        </is>
+      </c>
+      <c r="C90" s="22" t="inlineStr">
+        <is>
+          <t>Look for 'Add organization'.</t>
+        </is>
+      </c>
+      <c r="D90" s="22" t="inlineStr">
+        <is>
+          <t>No Add button; creation blocked.</t>
+        </is>
+      </c>
+      <c r="E90" s="23" t="n"/>
+      <c r="F90" s="22" t="n"/>
+      <c r="G90" s="23" t="n"/>
     </row>
     <row r="91" ht="42" customHeight="1">
       <c r="A91" s="21" t="inlineStr">
         <is>
-          <t>SA1</t>
+          <t>AD14</t>
         </is>
       </c>
       <c r="B91" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want the correct menu tabs.</t>
+          <t>As an Admin, I cannot change the recycling cans total.</t>
         </is>
       </c>
       <c r="C91" s="22" t="inlineStr">
         <is>
-          <t>Look at the left menu.</t>
+          <t>Look for the cans/bin admin control.</t>
         </is>
       </c>
       <c r="D91" s="22" t="inlineStr">
         <is>
-          <t>Dashboard, Reports, Users, Events, Organizations (Help in footer).</t>
+          <t>Not available (Super Admin only).</t>
         </is>
       </c>
       <c r="E91" s="23" t="n"/>
       <c r="F91" s="22" t="n"/>
       <c r="G91" s="23" t="n"/>
     </row>
-    <row r="92" ht="42" customHeight="1">
-      <c r="A92" s="21" t="inlineStr">
-        <is>
-          <t>SA2</t>
-        </is>
-      </c>
-      <c r="B92" s="22" t="inlineStr">
-        <is>
-          <t>As a Super Admin, I can do everything an Admin can, across all orgs.</t>
-        </is>
-      </c>
-      <c r="C92" s="22" t="inlineStr">
-        <is>
-          <t>Spot-check user + org actions on more than one org.</t>
-        </is>
-      </c>
-      <c r="D92" s="22" t="inlineStr">
-        <is>
-          <t>All allowed regardless of org.</t>
-        </is>
-      </c>
-      <c r="E92" s="23" t="n"/>
-      <c r="F92" s="22" t="n"/>
-      <c r="G92" s="23" t="n"/>
+    <row r="92" ht="20" customHeight="1">
+      <c r="A92" s="19" t="inlineStr">
+        <is>
+          <t>Super Admin (global)</t>
+        </is>
+      </c>
+      <c r="B92" s="20" t="n"/>
+      <c r="C92" s="20" t="n"/>
+      <c r="D92" s="20" t="n"/>
+      <c r="E92" s="20" t="n"/>
+      <c r="F92" s="20" t="n"/>
+      <c r="G92" s="20" t="n"/>
     </row>
     <row r="93" ht="42" customHeight="1">
       <c r="A93" s="21" t="inlineStr">
         <is>
-          <t>SA3</t>
+          <t>SA1</t>
         </is>
       </c>
       <c r="B93" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to create users incl. Supervisor and Super Admin.</t>
+          <t>As a Super Admin, I want the correct menu tabs.</t>
         </is>
       </c>
       <c r="C93" s="22" t="inlineStr">
         <is>
-          <t>Users → Add user → each role.</t>
+          <t>Look at the left menu.</t>
         </is>
       </c>
       <c r="D93" s="22" t="inlineStr">
         <is>
-          <t>Participant/Supervisor/Super Admin options available; account created + invite email.</t>
+          <t>Dashboard, Reports, Users, Events, Organizations (Help in footer).</t>
         </is>
       </c>
       <c r="E93" s="23" t="n"/>
@@ -14355,22 +14555,22 @@
     <row r="94" ht="42" customHeight="1">
       <c r="A94" s="21" t="inlineStr">
         <is>
-          <t>SA4</t>
+          <t>SA2</t>
         </is>
       </c>
       <c r="B94" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to grant/revoke Admin access.</t>
+          <t>As a Super Admin, I can do everything an Admin can, across all orgs.</t>
         </is>
       </c>
       <c r="C94" s="22" t="inlineStr">
         <is>
-          <t>Open a user → grant Admin access → check org(s) → save; then uncheck all → save.</t>
+          <t>Spot-check user + org actions on more than one org.</t>
         </is>
       </c>
       <c r="D94" s="22" t="inlineStr">
         <is>
-          <t>Checking orgs makes an Admin; unchecking all reverts to participant.</t>
+          <t>All allowed regardless of org.</t>
         </is>
       </c>
       <c r="E94" s="23" t="n"/>
@@ -14380,22 +14580,22 @@
     <row r="95" ht="42" customHeight="1">
       <c r="A95" s="21" t="inlineStr">
         <is>
-          <t>SA5</t>
+          <t>SA3</t>
         </is>
       </c>
       <c r="B95" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to create organizations + join codes.</t>
+          <t>As a Super Admin, I want to create users incl. Supervisor and Super Admin.</t>
         </is>
       </c>
       <c r="C95" s="22" t="inlineStr">
         <is>
-          <t>Organizations → Add organization → set details + join code.</t>
+          <t>Users → Add user → each role.</t>
         </is>
       </c>
       <c r="D95" s="22" t="inlineStr">
         <is>
-          <t>Org created with its join code.</t>
+          <t>Participant/Supervisor/Super Admin options available; account created + invite email.</t>
         </is>
       </c>
       <c r="E95" s="23" t="n"/>
@@ -14405,22 +14605,22 @@
     <row r="96" ht="42" customHeight="1">
       <c r="A96" s="21" t="inlineStr">
         <is>
-          <t>SA6</t>
+          <t>SA4</t>
         </is>
       </c>
       <c r="B96" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to find users by type.</t>
+          <t>As a Super Admin, I want to grant/revoke Admin access.</t>
         </is>
       </c>
       <c r="C96" s="22" t="inlineStr">
         <is>
-          <t>Users → role filter pills + search.</t>
+          <t>Open a user → grant Admin access → check org(s) → save; then uncheck all → save.</t>
         </is>
       </c>
       <c r="D96" s="22" t="inlineStr">
         <is>
-          <t>Filter by role with counts; search by name/email across all orgs.</t>
+          <t>Checking orgs makes an Admin; unchecking all reverts to participant.</t>
         </is>
       </c>
       <c r="E96" s="23" t="n"/>
@@ -14430,22 +14630,22 @@
     <row r="97" ht="42" customHeight="1">
       <c r="A97" s="21" t="inlineStr">
         <is>
-          <t>SA7</t>
+          <t>SA5</t>
         </is>
       </c>
       <c r="B97" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to search events.</t>
+          <t>As a Super Admin, I want to create organizations + join codes.</t>
         </is>
       </c>
       <c r="C97" s="22" t="inlineStr">
         <is>
-          <t>Events → search + date range; check supervisor/org per card.</t>
+          <t>Organizations → Add organization → set details + join code.</t>
         </is>
       </c>
       <c r="D97" s="22" t="inlineStr">
         <is>
-          <t>Filters work; each event shows supervisor and organization.</t>
+          <t>Org created with its join code.</t>
         </is>
       </c>
       <c r="E97" s="23" t="n"/>
@@ -14455,22 +14655,22 @@
     <row r="98" ht="42" customHeight="1">
       <c r="A98" s="21" t="inlineStr">
         <is>
-          <t>SA8</t>
+          <t>SA6</t>
         </is>
       </c>
       <c r="B98" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want clear event-visibility labels.</t>
+          <t>As a Super Admin, I want to find users by type.</t>
         </is>
       </c>
       <c r="C98" s="22" t="inlineStr">
         <is>
-          <t>New Event → 'Who can see this'.</t>
+          <t>Users → role filter pills + search.</t>
         </is>
       </c>
       <c r="D98" s="22" t="inlineStr">
         <is>
-          <t>'Open to all (community)' and 'Only &lt;org&gt; students' with helper text.</t>
+          <t>Filter by role with counts; search by name/email across all orgs.</t>
         </is>
       </c>
       <c r="E98" s="23" t="n"/>
@@ -14480,22 +14680,22 @@
     <row r="99" ht="42" customHeight="1">
       <c r="A99" s="21" t="inlineStr">
         <is>
-          <t>SA9</t>
+          <t>SA7</t>
         </is>
       </c>
       <c r="B99" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want program-wide reports.</t>
+          <t>As a Super Admin, I want to search events.</t>
         </is>
       </c>
       <c r="C99" s="22" t="inlineStr">
         <is>
-          <t>Open Reports / Dashboard.</t>
+          <t>Events → search + date range; check supervisor/org per card.</t>
         </is>
       </c>
       <c r="D99" s="22" t="inlineStr">
         <is>
-          <t>Totals and charts across the whole program.</t>
+          <t>Filters work; each event shows supervisor and organization.</t>
         </is>
       </c>
       <c r="E99" s="23" t="n"/>
@@ -14505,22 +14705,22 @@
     <row r="100" ht="42" customHeight="1">
       <c r="A100" s="21" t="inlineStr">
         <is>
-          <t>SA10</t>
+          <t>SA8</t>
         </is>
       </c>
       <c r="B100" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to verify email works.</t>
+          <t>As a Super Admin, I want clear event-visibility labels.</t>
         </is>
       </c>
       <c r="C100" s="22" t="inlineStr">
         <is>
-          <t>Dashboard → Send test email.</t>
+          <t>New Event → 'Who can see this'.</t>
         </is>
       </c>
       <c r="D100" s="22" t="inlineStr">
         <is>
-          <t>Result shown (success or the exact failure reason).</t>
+          <t>'Open to all (community)' and 'Only &lt;org&gt; students' with helper text.</t>
         </is>
       </c>
       <c r="E100" s="23" t="n"/>
@@ -14530,22 +14730,22 @@
     <row r="101" ht="42" customHeight="1">
       <c r="A101" s="21" t="inlineStr">
         <is>
-          <t>SA11</t>
+          <t>SA9</t>
         </is>
       </c>
       <c r="B101" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to update the recycling cans total.</t>
+          <t>As a Super Admin, I want program-wide reports.</t>
         </is>
       </c>
       <c r="C101" s="22" t="inlineStr">
         <is>
-          <t>Use the cans/bin admin control.</t>
+          <t>Open Reports / Dashboard.</t>
         </is>
       </c>
       <c r="D101" s="22" t="inlineStr">
         <is>
-          <t>Total updates; the ribbon reflects it.</t>
+          <t>Totals and charts across the whole program.</t>
         </is>
       </c>
       <c r="E101" s="23" t="n"/>
@@ -14555,102 +14755,152 @@
     <row r="102" ht="42" customHeight="1">
       <c r="A102" s="21" t="inlineStr">
         <is>
-          <t>SA12</t>
+          <t>SA10</t>
         </is>
       </c>
       <c r="B102" s="22" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want hours + records for any user.</t>
+          <t>As a Super Admin, I want to verify email works.</t>
         </is>
       </c>
       <c r="C102" s="22" t="inlineStr">
         <is>
-          <t>Add manual hours / open service record for any participant.</t>
+          <t>Dashboard → Send test email.</t>
         </is>
       </c>
       <c r="D102" s="22" t="inlineStr">
         <is>
-          <t>Works for any org.</t>
+          <t>Result shown (success or the exact failure reason).</t>
         </is>
       </c>
       <c r="E102" s="23" t="n"/>
       <c r="F102" s="22" t="n"/>
       <c r="G102" s="23" t="n"/>
     </row>
-    <row r="103" ht="20" customHeight="1">
-      <c r="A103" s="19" t="inlineStr">
-        <is>
-          <t>Cross-cutting</t>
-        </is>
-      </c>
-      <c r="B103" s="20" t="n"/>
-      <c r="C103" s="20" t="n"/>
-      <c r="D103" s="20" t="n"/>
-      <c r="E103" s="20" t="n"/>
-      <c r="F103" s="20" t="n"/>
-      <c r="G103" s="20" t="n"/>
+    <row r="103" ht="42" customHeight="1">
+      <c r="A103" s="21" t="inlineStr">
+        <is>
+          <t>SA11</t>
+        </is>
+      </c>
+      <c r="B103" s="22" t="inlineStr">
+        <is>
+          <t>As a Super Admin, I want to update the recycling cans total.</t>
+        </is>
+      </c>
+      <c r="C103" s="22" t="inlineStr">
+        <is>
+          <t>Use the cans/bin admin control.</t>
+        </is>
+      </c>
+      <c r="D103" s="22" t="inlineStr">
+        <is>
+          <t>Total updates; the ribbon reflects it.</t>
+        </is>
+      </c>
+      <c r="E103" s="23" t="n"/>
+      <c r="F103" s="22" t="n"/>
+      <c r="G103" s="23" t="n"/>
     </row>
     <row r="104" ht="42" customHeight="1">
       <c r="A104" s="21" t="inlineStr">
         <is>
-          <t>X1</t>
+          <t>SA12</t>
         </is>
       </c>
       <c r="B104" s="22" t="inlineStr">
         <is>
-          <t>As a phone user, I want a usable mobile layout.</t>
+          <t>As a Super Admin, I want hours + records for any user.</t>
         </is>
       </c>
       <c r="C104" s="22" t="inlineStr">
         <is>
-          <t>Open at phone width; use the menu drawer.</t>
+          <t>Add manual hours / open service record for any participant.</t>
         </is>
       </c>
       <c r="D104" s="22" t="inlineStr">
         <is>
-          <t>Layout adapts; drawer opens/closes; no horizontal scroll.</t>
+          <t>Works for any org.</t>
         </is>
       </c>
       <c r="E104" s="23" t="n"/>
       <c r="F104" s="22" t="n"/>
       <c r="G104" s="23" t="n"/>
     </row>
-    <row r="105" ht="42" customHeight="1">
-      <c r="A105" s="21" t="inlineStr">
+    <row r="105" ht="20" customHeight="1">
+      <c r="A105" s="19" t="inlineStr">
+        <is>
+          <t>Cross-cutting</t>
+        </is>
+      </c>
+      <c r="B105" s="20" t="n"/>
+      <c r="C105" s="20" t="n"/>
+      <c r="D105" s="20" t="n"/>
+      <c r="E105" s="20" t="n"/>
+      <c r="F105" s="20" t="n"/>
+      <c r="G105" s="20" t="n"/>
+    </row>
+    <row r="106" ht="42" customHeight="1">
+      <c r="A106" s="21" t="inlineStr">
+        <is>
+          <t>X1</t>
+        </is>
+      </c>
+      <c r="B106" s="22" t="inlineStr">
+        <is>
+          <t>As a phone user, I want a usable mobile layout.</t>
+        </is>
+      </c>
+      <c r="C106" s="22" t="inlineStr">
+        <is>
+          <t>Open at phone width; use the menu drawer.</t>
+        </is>
+      </c>
+      <c r="D106" s="22" t="inlineStr">
+        <is>
+          <t>Layout adapts; drawer opens/closes; no horizontal scroll.</t>
+        </is>
+      </c>
+      <c r="E106" s="23" t="n"/>
+      <c r="F106" s="22" t="n"/>
+      <c r="G106" s="23" t="n"/>
+    </row>
+    <row r="107" ht="42" customHeight="1">
+      <c r="A107" s="21" t="inlineStr">
         <is>
           <t>X2</t>
         </is>
       </c>
-      <c r="B105" s="22" t="inlineStr">
+      <c r="B107" s="22" t="inlineStr">
         <is>
           <t>As a visitor, I want the recycling ribbon on the login page.</t>
         </is>
       </c>
-      <c r="C105" s="22" t="inlineStr">
+      <c r="C107" s="22" t="inlineStr">
         <is>
           <t>Open login signed out.</t>
         </is>
       </c>
-      <c r="D105" s="22" t="inlineStr">
+      <c r="D107" s="22" t="inlineStr">
         <is>
           <t>Green ribbon shows on login.</t>
         </is>
       </c>
-      <c r="E105" s="23" t="n"/>
-      <c r="F105" s="22" t="n"/>
-      <c r="G105" s="23" t="n"/>
+      <c r="E107" s="23" t="n"/>
+      <c r="F107" s="22" t="n"/>
+      <c r="G107" s="23" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A55:G55"/>
+    <mergeCell ref="A77:G77"/>
+    <mergeCell ref="A105:G105"/>
     <mergeCell ref="A35:G35"/>
-    <mergeCell ref="A90:G90"/>
-    <mergeCell ref="A49:G49"/>
+    <mergeCell ref="A92:G92"/>
+    <mergeCell ref="A57:G57"/>
+    <mergeCell ref="A51:G51"/>
     <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A103:G103"/>
-    <mergeCell ref="A75:G75"/>
   </mergeCells>
   <conditionalFormatting sqref="E4:E9">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
@@ -14674,7 +14924,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E36:E48">
+  <conditionalFormatting sqref="E36:E50">
     <cfRule type="cellIs" priority="7" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -14685,7 +14935,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E50:E54">
+  <conditionalFormatting sqref="E52:E56">
     <cfRule type="cellIs" priority="10" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -14696,7 +14946,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E56:E74">
+  <conditionalFormatting sqref="E58:E76">
     <cfRule type="cellIs" priority="13" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -14707,7 +14957,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E76:E89">
+  <conditionalFormatting sqref="E78:E91">
     <cfRule type="cellIs" priority="16" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -14718,7 +14968,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E91:E102">
+  <conditionalFormatting sqref="E93:E104">
     <cfRule type="cellIs" priority="19" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -14729,7 +14979,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E104:E105">
+  <conditionalFormatting sqref="E106:E107">
     <cfRule type="cellIs" priority="22" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -14741,7 +14991,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E4:E9 E11:E34 E36:E48 E50:E54 E56:E74 E76:E89 E91:E102 E104:E105" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E4:E9 E11:E34 E36:E50 E52:E56 E58:E76 E78:E91 E93:E104 E106:E107" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pass,Fail,Blocked,Not tested,N/A"</formula1>
     </dataValidation>
   </dataValidations>

--- a/MedinaCares_Test_Plan.xlsx
+++ b/MedinaCares_Test_Plan.xlsx
@@ -1170,30 +1170,30 @@
         </is>
       </c>
       <c r="B6" s="18" t="n">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="C6" s="19">
-        <f>COUNTIF('iOS'!$E$3:$E$107,"Pass")</f>
+        <f>COUNTIF('iOS'!$E$3:$E$118,"Pass")</f>
         <v/>
       </c>
       <c r="D6" s="19">
-        <f>COUNTIF('iOS'!$E$3:$E$107,"Fail")</f>
+        <f>COUNTIF('iOS'!$E$3:$E$118,"Fail")</f>
         <v/>
       </c>
       <c r="E6" s="19">
-        <f>COUNTIF('iOS'!$E$3:$E$107,"Blocked")</f>
+        <f>COUNTIF('iOS'!$E$3:$E$118,"Blocked")</f>
         <v/>
       </c>
       <c r="F6" s="19">
-        <f>COUNTIF('iOS'!$E$3:$E$107,"Not tested")</f>
+        <f>COUNTIF('iOS'!$E$3:$E$118,"Not tested")</f>
         <v/>
       </c>
       <c r="G6" s="19">
-        <f>$B6-COUNTA('iOS'!$E$3:$E$107)</f>
+        <f>$B6-COUNTA('iOS'!$E$3:$E$118)</f>
         <v/>
       </c>
       <c r="H6" s="20">
-        <f>IF($B6=0,0,(COUNTIF('iOS'!$E$3:$E$107,"Pass")+COUNTIF('iOS'!$E$3:$E$107,"Fail")+COUNTIF('iOS'!$E$3:$E$107,"Blocked")+COUNTIF('iOS'!$E$3:$E$107,"Not tested"))/$B6)</f>
+        <f>IF($B6=0,0,(COUNTIF('iOS'!$E$3:$E$118,"Pass")+COUNTIF('iOS'!$E$3:$E$118,"Fail")+COUNTIF('iOS'!$E$3:$E$118,"Blocked")+COUNTIF('iOS'!$E$3:$E$118,"Not tested"))/$B6)</f>
         <v/>
       </c>
     </row>
@@ -1204,30 +1204,30 @@
         </is>
       </c>
       <c r="B7" s="18" t="n">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="C7" s="19">
-        <f>COUNTIF('Android'!$E$3:$E$107,"Pass")</f>
+        <f>COUNTIF('Android'!$E$3:$E$118,"Pass")</f>
         <v/>
       </c>
       <c r="D7" s="19">
-        <f>COUNTIF('Android'!$E$3:$E$107,"Fail")</f>
+        <f>COUNTIF('Android'!$E$3:$E$118,"Fail")</f>
         <v/>
       </c>
       <c r="E7" s="19">
-        <f>COUNTIF('Android'!$E$3:$E$107,"Blocked")</f>
+        <f>COUNTIF('Android'!$E$3:$E$118,"Blocked")</f>
         <v/>
       </c>
       <c r="F7" s="19">
-        <f>COUNTIF('Android'!$E$3:$E$107,"Not tested")</f>
+        <f>COUNTIF('Android'!$E$3:$E$118,"Not tested")</f>
         <v/>
       </c>
       <c r="G7" s="19">
-        <f>$B7-COUNTA('Android'!$E$3:$E$107)</f>
+        <f>$B7-COUNTA('Android'!$E$3:$E$118)</f>
         <v/>
       </c>
       <c r="H7" s="20">
-        <f>IF($B7=0,0,(COUNTIF('Android'!$E$3:$E$107,"Pass")+COUNTIF('Android'!$E$3:$E$107,"Fail")+COUNTIF('Android'!$E$3:$E$107,"Blocked")+COUNTIF('Android'!$E$3:$E$107,"Not tested"))/$B7)</f>
+        <f>IF($B7=0,0,(COUNTIF('Android'!$E$3:$E$118,"Pass")+COUNTIF('Android'!$E$3:$E$118,"Fail")+COUNTIF('Android'!$E$3:$E$118,"Blocked")+COUNTIF('Android'!$E$3:$E$118,"Not tested"))/$B7)</f>
         <v/>
       </c>
     </row>
@@ -1238,30 +1238,30 @@
         </is>
       </c>
       <c r="B8" s="18" t="n">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="C8" s="19">
-        <f>COUNTIF('Desktop Chrome'!$E$3:$E$107,"Pass")</f>
+        <f>COUNTIF('Desktop Chrome'!$E$3:$E$118,"Pass")</f>
         <v/>
       </c>
       <c r="D8" s="19">
-        <f>COUNTIF('Desktop Chrome'!$E$3:$E$107,"Fail")</f>
+        <f>COUNTIF('Desktop Chrome'!$E$3:$E$118,"Fail")</f>
         <v/>
       </c>
       <c r="E8" s="19">
-        <f>COUNTIF('Desktop Chrome'!$E$3:$E$107,"Blocked")</f>
+        <f>COUNTIF('Desktop Chrome'!$E$3:$E$118,"Blocked")</f>
         <v/>
       </c>
       <c r="F8" s="19">
-        <f>COUNTIF('Desktop Chrome'!$E$3:$E$107,"Not tested")</f>
+        <f>COUNTIF('Desktop Chrome'!$E$3:$E$118,"Not tested")</f>
         <v/>
       </c>
       <c r="G8" s="19">
-        <f>$B8-COUNTA('Desktop Chrome'!$E$3:$E$107)</f>
+        <f>$B8-COUNTA('Desktop Chrome'!$E$3:$E$118)</f>
         <v/>
       </c>
       <c r="H8" s="20">
-        <f>IF($B8=0,0,(COUNTIF('Desktop Chrome'!$E$3:$E$107,"Pass")+COUNTIF('Desktop Chrome'!$E$3:$E$107,"Fail")+COUNTIF('Desktop Chrome'!$E$3:$E$107,"Blocked")+COUNTIF('Desktop Chrome'!$E$3:$E$107,"Not tested"))/$B8)</f>
+        <f>IF($B8=0,0,(COUNTIF('Desktop Chrome'!$E$3:$E$118,"Pass")+COUNTIF('Desktop Chrome'!$E$3:$E$118,"Fail")+COUNTIF('Desktop Chrome'!$E$3:$E$118,"Blocked")+COUNTIF('Desktop Chrome'!$E$3:$E$118,"Not tested"))/$B8)</f>
         <v/>
       </c>
     </row>
@@ -1272,30 +1272,30 @@
         </is>
       </c>
       <c r="B9" s="18" t="n">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="C9" s="19">
-        <f>COUNTIF('Desktop Firefox'!$E$3:$E$107,"Pass")</f>
+        <f>COUNTIF('Desktop Firefox'!$E$3:$E$118,"Pass")</f>
         <v/>
       </c>
       <c r="D9" s="19">
-        <f>COUNTIF('Desktop Firefox'!$E$3:$E$107,"Fail")</f>
+        <f>COUNTIF('Desktop Firefox'!$E$3:$E$118,"Fail")</f>
         <v/>
       </c>
       <c r="E9" s="19">
-        <f>COUNTIF('Desktop Firefox'!$E$3:$E$107,"Blocked")</f>
+        <f>COUNTIF('Desktop Firefox'!$E$3:$E$118,"Blocked")</f>
         <v/>
       </c>
       <c r="F9" s="19">
-        <f>COUNTIF('Desktop Firefox'!$E$3:$E$107,"Not tested")</f>
+        <f>COUNTIF('Desktop Firefox'!$E$3:$E$118,"Not tested")</f>
         <v/>
       </c>
       <c r="G9" s="19">
-        <f>$B9-COUNTA('Desktop Firefox'!$E$3:$E$107)</f>
+        <f>$B9-COUNTA('Desktop Firefox'!$E$3:$E$118)</f>
         <v/>
       </c>
       <c r="H9" s="20">
-        <f>IF($B9=0,0,(COUNTIF('Desktop Firefox'!$E$3:$E$107,"Pass")+COUNTIF('Desktop Firefox'!$E$3:$E$107,"Fail")+COUNTIF('Desktop Firefox'!$E$3:$E$107,"Blocked")+COUNTIF('Desktop Firefox'!$E$3:$E$107,"Not tested"))/$B9)</f>
+        <f>IF($B9=0,0,(COUNTIF('Desktop Firefox'!$E$3:$E$118,"Pass")+COUNTIF('Desktop Firefox'!$E$3:$E$118,"Fail")+COUNTIF('Desktop Firefox'!$E$3:$E$118,"Blocked")+COUNTIF('Desktop Firefox'!$E$3:$E$118,"Not tested"))/$B9)</f>
         <v/>
       </c>
     </row>
@@ -1306,30 +1306,30 @@
         </is>
       </c>
       <c r="B10" s="18" t="n">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="C10" s="19">
-        <f>COUNTIF('Desktop Other'!$E$3:$E$107,"Pass")</f>
+        <f>COUNTIF('Desktop Other'!$E$3:$E$118,"Pass")</f>
         <v/>
       </c>
       <c r="D10" s="19">
-        <f>COUNTIF('Desktop Other'!$E$3:$E$107,"Fail")</f>
+        <f>COUNTIF('Desktop Other'!$E$3:$E$118,"Fail")</f>
         <v/>
       </c>
       <c r="E10" s="19">
-        <f>COUNTIF('Desktop Other'!$E$3:$E$107,"Blocked")</f>
+        <f>COUNTIF('Desktop Other'!$E$3:$E$118,"Blocked")</f>
         <v/>
       </c>
       <c r="F10" s="19">
-        <f>COUNTIF('Desktop Other'!$E$3:$E$107,"Not tested")</f>
+        <f>COUNTIF('Desktop Other'!$E$3:$E$118,"Not tested")</f>
         <v/>
       </c>
       <c r="G10" s="19">
-        <f>$B10-COUNTA('Desktop Other'!$E$3:$E$107)</f>
+        <f>$B10-COUNTA('Desktop Other'!$E$3:$E$118)</f>
         <v/>
       </c>
       <c r="H10" s="20">
-        <f>IF($B10=0,0,(COUNTIF('Desktop Other'!$E$3:$E$107,"Pass")+COUNTIF('Desktop Other'!$E$3:$E$107,"Fail")+COUNTIF('Desktop Other'!$E$3:$E$107,"Blocked")+COUNTIF('Desktop Other'!$E$3:$E$107,"Not tested"))/$B10)</f>
+        <f>IF($B10=0,0,(COUNTIF('Desktop Other'!$E$3:$E$118,"Pass")+COUNTIF('Desktop Other'!$E$3:$E$118,"Fail")+COUNTIF('Desktop Other'!$E$3:$E$118,"Blocked")+COUNTIF('Desktop Other'!$E$3:$E$118,"Not tested"))/$B10)</f>
         <v/>
       </c>
     </row>
@@ -1504,27 +1504,27 @@
         </is>
       </c>
       <c r="B18" s="18">
-        <f>COUNTIF('iOS'!$E$58:$E$76,"Pass")</f>
+        <f>COUNTIF('iOS'!$E$58:$E$79,"Pass")</f>
         <v/>
       </c>
       <c r="C18" s="18">
-        <f>COUNTIF('Android'!$E$58:$E$76,"Pass")</f>
+        <f>COUNTIF('Android'!$E$58:$E$79,"Pass")</f>
         <v/>
       </c>
       <c r="D18" s="18">
-        <f>COUNTIF('Desktop Chrome'!$E$58:$E$76,"Pass")</f>
+        <f>COUNTIF('Desktop Chrome'!$E$58:$E$79,"Pass")</f>
         <v/>
       </c>
       <c r="E18" s="18">
-        <f>COUNTIF('Desktop Firefox'!$E$58:$E$76,"Pass")</f>
+        <f>COUNTIF('Desktop Firefox'!$E$58:$E$79,"Pass")</f>
         <v/>
       </c>
       <c r="F18" s="18">
-        <f>COUNTIF('Desktop Other'!$E$58:$E$76,"Pass")</f>
+        <f>COUNTIF('Desktop Other'!$E$58:$E$79,"Pass")</f>
         <v/>
       </c>
       <c r="G18" s="18" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
@@ -1534,27 +1534,27 @@
         </is>
       </c>
       <c r="B19" s="18">
-        <f>COUNTIF('iOS'!$E$78:$E$91,"Pass")</f>
+        <f>COUNTIF('iOS'!$E$81:$E$96,"Pass")</f>
         <v/>
       </c>
       <c r="C19" s="18">
-        <f>COUNTIF('Android'!$E$78:$E$91,"Pass")</f>
+        <f>COUNTIF('Android'!$E$81:$E$96,"Pass")</f>
         <v/>
       </c>
       <c r="D19" s="18">
-        <f>COUNTIF('Desktop Chrome'!$E$78:$E$91,"Pass")</f>
+        <f>COUNTIF('Desktop Chrome'!$E$81:$E$96,"Pass")</f>
         <v/>
       </c>
       <c r="E19" s="18">
-        <f>COUNTIF('Desktop Firefox'!$E$78:$E$91,"Pass")</f>
+        <f>COUNTIF('Desktop Firefox'!$E$81:$E$96,"Pass")</f>
         <v/>
       </c>
       <c r="F19" s="18">
-        <f>COUNTIF('Desktop Other'!$E$78:$E$91,"Pass")</f>
+        <f>COUNTIF('Desktop Other'!$E$81:$E$96,"Pass")</f>
         <v/>
       </c>
       <c r="G19" s="18" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">
@@ -1564,27 +1564,27 @@
         </is>
       </c>
       <c r="B20" s="18">
-        <f>COUNTIF('iOS'!$E$93:$E$104,"Pass")</f>
+        <f>COUNTIF('iOS'!$E$98:$E$115,"Pass")</f>
         <v/>
       </c>
       <c r="C20" s="18">
-        <f>COUNTIF('Android'!$E$93:$E$104,"Pass")</f>
+        <f>COUNTIF('Android'!$E$98:$E$115,"Pass")</f>
         <v/>
       </c>
       <c r="D20" s="18">
-        <f>COUNTIF('Desktop Chrome'!$E$93:$E$104,"Pass")</f>
+        <f>COUNTIF('Desktop Chrome'!$E$98:$E$115,"Pass")</f>
         <v/>
       </c>
       <c r="E20" s="18">
-        <f>COUNTIF('Desktop Firefox'!$E$93:$E$104,"Pass")</f>
+        <f>COUNTIF('Desktop Firefox'!$E$98:$E$115,"Pass")</f>
         <v/>
       </c>
       <c r="F20" s="18">
-        <f>COUNTIF('Desktop Other'!$E$93:$E$104,"Pass")</f>
+        <f>COUNTIF('Desktop Other'!$E$98:$E$115,"Pass")</f>
         <v/>
       </c>
       <c r="G20" s="18" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21">
@@ -1594,23 +1594,23 @@
         </is>
       </c>
       <c r="B21" s="18">
-        <f>COUNTIF('iOS'!$E$106:$E$107,"Pass")</f>
+        <f>COUNTIF('iOS'!$E$117:$E$118,"Pass")</f>
         <v/>
       </c>
       <c r="C21" s="18">
-        <f>COUNTIF('Android'!$E$106:$E$107,"Pass")</f>
+        <f>COUNTIF('Android'!$E$117:$E$118,"Pass")</f>
         <v/>
       </c>
       <c r="D21" s="18">
-        <f>COUNTIF('Desktop Chrome'!$E$106:$E$107,"Pass")</f>
+        <f>COUNTIF('Desktop Chrome'!$E$117:$E$118,"Pass")</f>
         <v/>
       </c>
       <c r="E21" s="18">
-        <f>COUNTIF('Desktop Firefox'!$E$106:$E$107,"Pass")</f>
+        <f>COUNTIF('Desktop Firefox'!$E$117:$E$118,"Pass")</f>
         <v/>
       </c>
       <c r="F21" s="18">
-        <f>COUNTIF('Desktop Other'!$E$106:$E$107,"Pass")</f>
+        <f>COUNTIF('Desktop Other'!$E$117:$E$118,"Pass")</f>
         <v/>
       </c>
       <c r="G21" s="18" t="n">
@@ -1631,7 +1631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G107"/>
+  <dimension ref="A1:G118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1902,17 +1902,17 @@
       </c>
       <c r="B12" s="27" t="inlineStr">
         <is>
-          <t>As a student, I want to enter an organization code during sign-up.</t>
+          <t>As a student, a join code is required when I pick an organization.</t>
         </is>
       </c>
       <c r="C12" s="27" t="inlineStr">
         <is>
-          <t>Enter a code in the Organization code field (optional) and submit.</t>
+          <t>Choose an organization affiliation; the join-code field appears and is required.</t>
         </is>
       </c>
       <c r="D12" s="27" t="inlineStr">
         <is>
-          <t>A valid code enrolls me in that org; a bad code is rejected; blank is allowed.</t>
+          <t>Can't submit without a code; a valid code enrolls me in that org, a bad one is rejected. (Community/no-org path needs no code.)</t>
         </is>
       </c>
       <c r="E12" s="28" t="n"/>
@@ -3483,38 +3483,50 @@
       <c r="F76" s="27" t="n"/>
       <c r="G76" s="28" t="n"/>
     </row>
-    <row r="77" ht="20" customHeight="1">
-      <c r="A77" s="24" t="inlineStr">
-        <is>
-          <t>Admin (org-scoped)</t>
-        </is>
-      </c>
-      <c r="B77" s="25" t="n"/>
-      <c r="C77" s="25" t="n"/>
-      <c r="D77" s="25" t="n"/>
-      <c r="E77" s="25" t="n"/>
-      <c r="F77" s="25" t="n"/>
-      <c r="G77" s="25" t="n"/>
+    <row r="77" ht="42" customHeight="1">
+      <c r="A77" s="26" t="inlineStr">
+        <is>
+          <t>SV20</t>
+        </is>
+      </c>
+      <c r="B77" s="27" t="inlineStr">
+        <is>
+          <t>As a supervisor, I want to attach files to a message.</t>
+        </is>
+      </c>
+      <c r="C77" s="27" t="inlineStr">
+        <is>
+          <t>Roster → Message attendees → add an image/PDF (≤10 MB) → send.</t>
+        </is>
+      </c>
+      <c r="D77" s="27" t="inlineStr">
+        <is>
+          <t>The attachment uploads, appears in the dialog, and arrives with the email.</t>
+        </is>
+      </c>
+      <c r="E77" s="28" t="n"/>
+      <c r="F77" s="27" t="n"/>
+      <c r="G77" s="28" t="n"/>
     </row>
     <row r="78" ht="42" customHeight="1">
       <c r="A78" s="26" t="inlineStr">
         <is>
-          <t>AD1</t>
+          <t>SV21</t>
         </is>
       </c>
       <c r="B78" s="27" t="inlineStr">
         <is>
-          <t>As an Admin, I want the correct menu tabs.</t>
+          <t>As a supervisor, I want an email when someone signs up.</t>
         </is>
       </c>
       <c r="C78" s="27" t="inlineStr">
         <is>
-          <t>Look at the left menu.</t>
+          <t>Have a participant sign up for your event (with notifications on).</t>
         </is>
       </c>
       <c r="D78" s="27" t="inlineStr">
         <is>
-          <t>Dashboard, Pending Reviews, Reviewed History, My Events, All Opportunities, Users, Organizations, My Hours, Help.</t>
+          <t>You receive a sign-up email; toggling notifications off stops them.</t>
         </is>
       </c>
       <c r="E78" s="28" t="n"/>
@@ -3524,72 +3536,60 @@
     <row r="79" ht="42" customHeight="1">
       <c r="A79" s="26" t="inlineStr">
         <is>
-          <t>AD2</t>
+          <t>SV22</t>
         </is>
       </c>
       <c r="B79" s="27" t="inlineStr">
         <is>
-          <t>As an Admin, I can do everything a supervisor can.</t>
+          <t>As a supervisor, I want to verify who's a real member before sharing access.</t>
         </is>
       </c>
       <c r="C79" s="27" t="inlineStr">
         <is>
-          <t>Spot-check: approve an item and create an event.</t>
+          <t>Open the Roster and read the attendee badges.</t>
         </is>
       </c>
       <c r="D79" s="27" t="inlineStr">
         <is>
-          <t>Both work.</t>
+          <t>Each shows their org, or 'Community · unverified'; a warning reminds you to confirm before sharing a building QR.</t>
         </is>
       </c>
       <c r="E79" s="28" t="n"/>
       <c r="F79" s="27" t="n"/>
       <c r="G79" s="28" t="n"/>
     </row>
-    <row r="80" ht="42" customHeight="1">
-      <c r="A80" s="26" t="inlineStr">
-        <is>
-          <t>AD3</t>
-        </is>
-      </c>
-      <c r="B80" s="27" t="inlineStr">
-        <is>
-          <t>As an Admin, I only see my org's non-admin users.</t>
-        </is>
-      </c>
-      <c r="C80" s="27" t="inlineStr">
-        <is>
-          <t>Open Users.</t>
-        </is>
-      </c>
-      <c r="D80" s="27" t="inlineStr">
-        <is>
-          <t>Only participants/parents/supervisors in your org; no admins/super admins; no other orgs.</t>
-        </is>
-      </c>
-      <c r="E80" s="28" t="n"/>
-      <c r="F80" s="27" t="n"/>
-      <c r="G80" s="28" t="n"/>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="24" t="inlineStr">
+        <is>
+          <t>Admin (org-scoped)</t>
+        </is>
+      </c>
+      <c r="B80" s="25" t="n"/>
+      <c r="C80" s="25" t="n"/>
+      <c r="D80" s="25" t="n"/>
+      <c r="E80" s="25" t="n"/>
+      <c r="F80" s="25" t="n"/>
+      <c r="G80" s="25" t="n"/>
     </row>
     <row r="81" ht="42" customHeight="1">
       <c r="A81" s="26" t="inlineStr">
         <is>
-          <t>AD4</t>
+          <t>AD1</t>
         </is>
       </c>
       <c r="B81" s="27" t="inlineStr">
         <is>
-          <t>As an Admin, I want to add a supervisor.</t>
+          <t>As an Admin, I want the correct menu tabs.</t>
         </is>
       </c>
       <c r="C81" s="27" t="inlineStr">
         <is>
-          <t>Users → Add user → Supervisor → save.</t>
+          <t>Look at the left menu.</t>
         </is>
       </c>
       <c r="D81" s="27" t="inlineStr">
         <is>
-          <t>Supervisor created, stamped to your org; invite email sent.</t>
+          <t>Dashboard, Pending Reviews, Reviewed History, My Events, All Opportunities, Users, Organizations, My Hours, Help.</t>
         </is>
       </c>
       <c r="E81" s="28" t="n"/>
@@ -3599,22 +3599,22 @@
     <row r="82" ht="42" customHeight="1">
       <c r="A82" s="26" t="inlineStr">
         <is>
-          <t>AD5</t>
+          <t>AD2</t>
         </is>
       </c>
       <c r="B82" s="27" t="inlineStr">
         <is>
-          <t>As an Admin, I want to create a participant as a fallback.</t>
+          <t>As an Admin, I can do everything a supervisor can.</t>
         </is>
       </c>
       <c r="C82" s="27" t="inlineStr">
         <is>
-          <t>Users → Add user → Participant → save.</t>
+          <t>Spot-check: approve an item and create an event.</t>
         </is>
       </c>
       <c r="D82" s="27" t="inlineStr">
         <is>
-          <t>Participant created with a set-password invite (no silent password).</t>
+          <t>Both work.</t>
         </is>
       </c>
       <c r="E82" s="28" t="n"/>
@@ -3624,22 +3624,22 @@
     <row r="83" ht="42" customHeight="1">
       <c r="A83" s="26" t="inlineStr">
         <is>
-          <t>AD6</t>
+          <t>AD3</t>
         </is>
       </c>
       <c r="B83" s="27" t="inlineStr">
         <is>
-          <t>As an Admin, I want to grant participant hours.</t>
+          <t>As an Admin, I only see my org's non-admin users.</t>
         </is>
       </c>
       <c r="C83" s="27" t="inlineStr">
         <is>
-          <t>Open a participant in your org → Add hours.</t>
+          <t>Open Users.</t>
         </is>
       </c>
       <c r="D83" s="27" t="inlineStr">
         <is>
-          <t>Hours auto-approved; count toward their total/medals.</t>
+          <t>Only participants/parents/supervisors in your org; no admins/super admins; no other orgs.</t>
         </is>
       </c>
       <c r="E83" s="28" t="n"/>
@@ -3649,22 +3649,22 @@
     <row r="84" ht="42" customHeight="1">
       <c r="A84" s="26" t="inlineStr">
         <is>
-          <t>AD7</t>
+          <t>AD4</t>
         </is>
       </c>
       <c r="B84" s="27" t="inlineStr">
         <is>
-          <t>As an Admin, I want a participant's service record.</t>
+          <t>As an Admin, I want to add a supervisor.</t>
         </is>
       </c>
       <c r="C84" s="27" t="inlineStr">
         <is>
-          <t>Users → Service record for a participant in your org.</t>
+          <t>Users → Add user → Supervisor → save.</t>
         </is>
       </c>
       <c r="D84" s="27" t="inlineStr">
         <is>
-          <t>Record opens.</t>
+          <t>Supervisor created, stamped to your org; invite email sent.</t>
         </is>
       </c>
       <c r="E84" s="28" t="n"/>
@@ -3674,22 +3674,22 @@
     <row r="85" ht="42" customHeight="1">
       <c r="A85" s="26" t="inlineStr">
         <is>
-          <t>AD8</t>
+          <t>AD5</t>
         </is>
       </c>
       <c r="B85" s="27" t="inlineStr">
         <is>
-          <t>As an Admin, I want to edit/delete my org's users.</t>
+          <t>As an Admin, I want to create a participant as a fallback.</t>
         </is>
       </c>
       <c r="C85" s="27" t="inlineStr">
         <is>
-          <t>Edit a name/phone; delete a test user.</t>
+          <t>Users → Add user → Participant → save.</t>
         </is>
       </c>
       <c r="D85" s="27" t="inlineStr">
         <is>
-          <t>Changes apply within your org.</t>
+          <t>Participant created with a set-password invite (no silent password).</t>
         </is>
       </c>
       <c r="E85" s="28" t="n"/>
@@ -3699,22 +3699,22 @@
     <row r="86" ht="42" customHeight="1">
       <c r="A86" s="26" t="inlineStr">
         <is>
-          <t>AD9</t>
+          <t>AD6</t>
         </is>
       </c>
       <c r="B86" s="27" t="inlineStr">
         <is>
-          <t>As an Admin, I must NOT act on users outside my org.</t>
+          <t>As an Admin, I want to grant participant hours.</t>
         </is>
       </c>
       <c r="C86" s="27" t="inlineStr">
         <is>
-          <t>Attempt to reach another org's user (e.g. direct URL).</t>
+          <t>Open a participant in your org → Add hours.</t>
         </is>
       </c>
       <c r="D86" s="27" t="inlineStr">
         <is>
-          <t>Blocked / not visible.</t>
+          <t>Hours auto-approved; count toward their total/medals.</t>
         </is>
       </c>
       <c r="E86" s="28" t="n"/>
@@ -3724,22 +3724,22 @@
     <row r="87" ht="42" customHeight="1">
       <c r="A87" s="26" t="inlineStr">
         <is>
-          <t>AD10</t>
+          <t>AD7</t>
         </is>
       </c>
       <c r="B87" s="27" t="inlineStr">
         <is>
-          <t>As an Admin, I cannot grant Admin access or manage admins.</t>
+          <t>As an Admin, I want a participant's service record.</t>
         </is>
       </c>
       <c r="C87" s="27" t="inlineStr">
         <is>
-          <t>Look for the 'grant Admin access' action.</t>
+          <t>Users → Service record for a participant in your org.</t>
         </is>
       </c>
       <c r="D87" s="27" t="inlineStr">
         <is>
-          <t>No such button; attempts are blocked server-side.</t>
+          <t>Record opens.</t>
         </is>
       </c>
       <c r="E87" s="28" t="n"/>
@@ -3749,22 +3749,22 @@
     <row r="88" ht="42" customHeight="1">
       <c r="A88" s="26" t="inlineStr">
         <is>
-          <t>AD11</t>
+          <t>AD8</t>
         </is>
       </c>
       <c r="B88" s="27" t="inlineStr">
         <is>
-          <t>As an Admin, I see and edit only my own organization.</t>
+          <t>As an Admin, I want to edit/delete my org's users.</t>
         </is>
       </c>
       <c r="C88" s="27" t="inlineStr">
         <is>
-          <t>Open Organizations.</t>
+          <t>Edit a name/phone; delete a test user.</t>
         </is>
       </c>
       <c r="D88" s="27" t="inlineStr">
         <is>
-          <t>Only your org shows; you can edit its settings.</t>
+          <t>Changes apply within your org.</t>
         </is>
       </c>
       <c r="E88" s="28" t="n"/>
@@ -3774,22 +3774,22 @@
     <row r="89" ht="42" customHeight="1">
       <c r="A89" s="26" t="inlineStr">
         <is>
-          <t>AD12</t>
+          <t>AD9</t>
         </is>
       </c>
       <c r="B89" s="27" t="inlineStr">
         <is>
-          <t>As an Admin, I want to generate/rotate my org's join code.</t>
+          <t>As an Admin, I must NOT act on users outside my org.</t>
         </is>
       </c>
       <c r="C89" s="27" t="inlineStr">
         <is>
-          <t>Organizations → set/generate a join code → save.</t>
+          <t>Attempt to reach another org's user (e.g. direct URL).</t>
         </is>
       </c>
       <c r="D89" s="27" t="inlineStr">
         <is>
-          <t>Join code saved; usable at sign-up.</t>
+          <t>Blocked / not visible.</t>
         </is>
       </c>
       <c r="E89" s="28" t="n"/>
@@ -3799,22 +3799,22 @@
     <row r="90" ht="42" customHeight="1">
       <c r="A90" s="26" t="inlineStr">
         <is>
-          <t>AD13</t>
+          <t>AD10</t>
         </is>
       </c>
       <c r="B90" s="27" t="inlineStr">
         <is>
-          <t>As an Admin, I cannot create organizations.</t>
+          <t>As an Admin, I cannot grant Admin access or manage admins.</t>
         </is>
       </c>
       <c r="C90" s="27" t="inlineStr">
         <is>
-          <t>Look for 'Add organization'.</t>
+          <t>Look for the 'grant Admin access' action.</t>
         </is>
       </c>
       <c r="D90" s="27" t="inlineStr">
         <is>
-          <t>No Add button; creation blocked.</t>
+          <t>No such button; attempts are blocked server-side.</t>
         </is>
       </c>
       <c r="E90" s="28" t="n"/>
@@ -3824,60 +3824,72 @@
     <row r="91" ht="42" customHeight="1">
       <c r="A91" s="26" t="inlineStr">
         <is>
-          <t>AD14</t>
+          <t>AD11</t>
         </is>
       </c>
       <c r="B91" s="27" t="inlineStr">
         <is>
-          <t>As an Admin, I cannot change the recycling cans total.</t>
+          <t>As an Admin, I see and edit only my own organization.</t>
         </is>
       </c>
       <c r="C91" s="27" t="inlineStr">
         <is>
-          <t>Look for the cans/bin admin control.</t>
+          <t>Open Organizations.</t>
         </is>
       </c>
       <c r="D91" s="27" t="inlineStr">
         <is>
-          <t>Not available (Super Admin only).</t>
+          <t>Only your org shows; you can edit its settings.</t>
         </is>
       </c>
       <c r="E91" s="28" t="n"/>
       <c r="F91" s="27" t="n"/>
       <c r="G91" s="28" t="n"/>
     </row>
-    <row r="92" ht="20" customHeight="1">
-      <c r="A92" s="24" t="inlineStr">
-        <is>
-          <t>Super Admin (global)</t>
-        </is>
-      </c>
-      <c r="B92" s="25" t="n"/>
-      <c r="C92" s="25" t="n"/>
-      <c r="D92" s="25" t="n"/>
-      <c r="E92" s="25" t="n"/>
-      <c r="F92" s="25" t="n"/>
-      <c r="G92" s="25" t="n"/>
+    <row r="92" ht="42" customHeight="1">
+      <c r="A92" s="26" t="inlineStr">
+        <is>
+          <t>AD12</t>
+        </is>
+      </c>
+      <c r="B92" s="27" t="inlineStr">
+        <is>
+          <t>As an Admin, I want to generate/rotate my org's join code.</t>
+        </is>
+      </c>
+      <c r="C92" s="27" t="inlineStr">
+        <is>
+          <t>Organizations → set/generate a join code → save.</t>
+        </is>
+      </c>
+      <c r="D92" s="27" t="inlineStr">
+        <is>
+          <t>Join code saved; usable at sign-up.</t>
+        </is>
+      </c>
+      <c r="E92" s="28" t="n"/>
+      <c r="F92" s="27" t="n"/>
+      <c r="G92" s="28" t="n"/>
     </row>
     <row r="93" ht="42" customHeight="1">
       <c r="A93" s="26" t="inlineStr">
         <is>
-          <t>SA1</t>
+          <t>AD13</t>
         </is>
       </c>
       <c r="B93" s="27" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want the correct menu tabs.</t>
+          <t>As an Admin, I cannot create organizations.</t>
         </is>
       </c>
       <c r="C93" s="27" t="inlineStr">
         <is>
-          <t>Look at the left menu.</t>
+          <t>Look for 'Add organization'.</t>
         </is>
       </c>
       <c r="D93" s="27" t="inlineStr">
         <is>
-          <t>Dashboard, Reports, Users, Events, Organizations (Help in footer).</t>
+          <t>No Add button; creation blocked.</t>
         </is>
       </c>
       <c r="E93" s="28" t="n"/>
@@ -3887,22 +3899,22 @@
     <row r="94" ht="42" customHeight="1">
       <c r="A94" s="26" t="inlineStr">
         <is>
-          <t>SA2</t>
+          <t>AD14</t>
         </is>
       </c>
       <c r="B94" s="27" t="inlineStr">
         <is>
-          <t>As a Super Admin, I can do everything an Admin can, across all orgs.</t>
+          <t>As an Admin, I cannot change the recycling cans total.</t>
         </is>
       </c>
       <c r="C94" s="27" t="inlineStr">
         <is>
-          <t>Spot-check user + org actions on more than one org.</t>
+          <t>Look for the cans/bin admin control.</t>
         </is>
       </c>
       <c r="D94" s="27" t="inlineStr">
         <is>
-          <t>All allowed regardless of org.</t>
+          <t>Not available (Super Admin only).</t>
         </is>
       </c>
       <c r="E94" s="28" t="n"/>
@@ -3912,22 +3924,22 @@
     <row r="95" ht="42" customHeight="1">
       <c r="A95" s="26" t="inlineStr">
         <is>
-          <t>SA3</t>
+          <t>AD15</t>
         </is>
       </c>
       <c r="B95" s="27" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to create users incl. Supervisor and Super Admin.</t>
+          <t>As an Admin, I can turn my activity emails off.</t>
         </is>
       </c>
       <c r="C95" s="27" t="inlineStr">
         <is>
-          <t>Users → Add user → each role.</t>
+          <t>Dashboard → Email notifications toggle off; have a student sign up for your event.</t>
         </is>
       </c>
       <c r="D95" s="27" t="inlineStr">
         <is>
-          <t>Participant/Supervisor/Super Admin options available; account created + invite email.</t>
+          <t>No sign-up email arrives while off; turning it back on resumes them.</t>
         </is>
       </c>
       <c r="E95" s="28" t="n"/>
@@ -3937,72 +3949,60 @@
     <row r="96" ht="42" customHeight="1">
       <c r="A96" s="26" t="inlineStr">
         <is>
-          <t>SA4</t>
+          <t>AD16</t>
         </is>
       </c>
       <c r="B96" s="27" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to grant/revoke Admin access.</t>
+          <t>As an Admin creating a user, I choose among only my org(s).</t>
         </is>
       </c>
       <c r="C96" s="27" t="inlineStr">
         <is>
-          <t>Open a user → grant Admin access → check org(s) → save; then uncheck all → save.</t>
+          <t>Add user → Organization picker.</t>
         </is>
       </c>
       <c r="D96" s="27" t="inlineStr">
         <is>
-          <t>Checking orgs makes an Admin; unchecking all reverts to participant.</t>
+          <t>Only the org(s) I manage are listed (Super Admins see all + 'none').</t>
         </is>
       </c>
       <c r="E96" s="28" t="n"/>
       <c r="F96" s="27" t="n"/>
       <c r="G96" s="28" t="n"/>
     </row>
-    <row r="97" ht="42" customHeight="1">
-      <c r="A97" s="26" t="inlineStr">
-        <is>
-          <t>SA5</t>
-        </is>
-      </c>
-      <c r="B97" s="27" t="inlineStr">
-        <is>
-          <t>As a Super Admin, I want to create organizations + join codes.</t>
-        </is>
-      </c>
-      <c r="C97" s="27" t="inlineStr">
-        <is>
-          <t>Organizations → Add organization → set details + join code.</t>
-        </is>
-      </c>
-      <c r="D97" s="27" t="inlineStr">
-        <is>
-          <t>Org created with its join code.</t>
-        </is>
-      </c>
-      <c r="E97" s="28" t="n"/>
-      <c r="F97" s="27" t="n"/>
-      <c r="G97" s="28" t="n"/>
+    <row r="97" ht="20" customHeight="1">
+      <c r="A97" s="24" t="inlineStr">
+        <is>
+          <t>Super Admin (global)</t>
+        </is>
+      </c>
+      <c r="B97" s="25" t="n"/>
+      <c r="C97" s="25" t="n"/>
+      <c r="D97" s="25" t="n"/>
+      <c r="E97" s="25" t="n"/>
+      <c r="F97" s="25" t="n"/>
+      <c r="G97" s="25" t="n"/>
     </row>
     <row r="98" ht="42" customHeight="1">
       <c r="A98" s="26" t="inlineStr">
         <is>
-          <t>SA6</t>
+          <t>SA1</t>
         </is>
       </c>
       <c r="B98" s="27" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to find users by type.</t>
+          <t>As a Super Admin, I want the correct menu tabs.</t>
         </is>
       </c>
       <c r="C98" s="27" t="inlineStr">
         <is>
-          <t>Users → role filter pills + search.</t>
+          <t>Look at the left menu.</t>
         </is>
       </c>
       <c r="D98" s="27" t="inlineStr">
         <is>
-          <t>Filter by role with counts; search by name/email across all orgs.</t>
+          <t>Dashboard, Reports, Users, Events, Organizations (Help in footer).</t>
         </is>
       </c>
       <c r="E98" s="28" t="n"/>
@@ -4012,22 +4012,22 @@
     <row r="99" ht="42" customHeight="1">
       <c r="A99" s="26" t="inlineStr">
         <is>
-          <t>SA7</t>
+          <t>SA2</t>
         </is>
       </c>
       <c r="B99" s="27" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to search events.</t>
+          <t>As a Super Admin, I can do everything an Admin can, across all orgs.</t>
         </is>
       </c>
       <c r="C99" s="27" t="inlineStr">
         <is>
-          <t>Events → search + date range; check supervisor/org per card.</t>
+          <t>Spot-check user + org actions on more than one org.</t>
         </is>
       </c>
       <c r="D99" s="27" t="inlineStr">
         <is>
-          <t>Filters work; each event shows supervisor and organization.</t>
+          <t>All allowed regardless of org.</t>
         </is>
       </c>
       <c r="E99" s="28" t="n"/>
@@ -4037,22 +4037,22 @@
     <row r="100" ht="42" customHeight="1">
       <c r="A100" s="26" t="inlineStr">
         <is>
-          <t>SA8</t>
+          <t>SA3</t>
         </is>
       </c>
       <c r="B100" s="27" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want clear event-visibility labels.</t>
+          <t>As a Super Admin, I want to create users incl. Supervisor and Super Admin.</t>
         </is>
       </c>
       <c r="C100" s="27" t="inlineStr">
         <is>
-          <t>New Event → 'Who can see this'.</t>
+          <t>Users → Add user → each role.</t>
         </is>
       </c>
       <c r="D100" s="27" t="inlineStr">
         <is>
-          <t>'Open to all (community)' and 'Only &lt;org&gt; students' with helper text.</t>
+          <t>Participant/Supervisor/Super Admin options available; account created + invite email.</t>
         </is>
       </c>
       <c r="E100" s="28" t="n"/>
@@ -4062,22 +4062,22 @@
     <row r="101" ht="42" customHeight="1">
       <c r="A101" s="26" t="inlineStr">
         <is>
-          <t>SA9</t>
+          <t>SA4</t>
         </is>
       </c>
       <c r="B101" s="27" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want program-wide reports.</t>
+          <t>As a Super Admin, I want to grant/revoke Admin access.</t>
         </is>
       </c>
       <c r="C101" s="27" t="inlineStr">
         <is>
-          <t>Open Reports / Dashboard.</t>
+          <t>Open a user → grant Admin access → check org(s) → save; then uncheck all → save.</t>
         </is>
       </c>
       <c r="D101" s="27" t="inlineStr">
         <is>
-          <t>Totals and charts across the whole program.</t>
+          <t>Checking orgs makes an Admin; unchecking all reverts to participant.</t>
         </is>
       </c>
       <c r="E101" s="28" t="n"/>
@@ -4087,22 +4087,22 @@
     <row r="102" ht="42" customHeight="1">
       <c r="A102" s="26" t="inlineStr">
         <is>
-          <t>SA10</t>
+          <t>SA5</t>
         </is>
       </c>
       <c r="B102" s="27" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to verify email works.</t>
+          <t>As a Super Admin, I want to create organizations + join codes.</t>
         </is>
       </c>
       <c r="C102" s="27" t="inlineStr">
         <is>
-          <t>Dashboard → Send test email.</t>
+          <t>Organizations → Add organization → set details + join code.</t>
         </is>
       </c>
       <c r="D102" s="27" t="inlineStr">
         <is>
-          <t>Result shown (success or the exact failure reason).</t>
+          <t>Org created with its join code.</t>
         </is>
       </c>
       <c r="E102" s="28" t="n"/>
@@ -4112,22 +4112,22 @@
     <row r="103" ht="42" customHeight="1">
       <c r="A103" s="26" t="inlineStr">
         <is>
-          <t>SA11</t>
+          <t>SA6</t>
         </is>
       </c>
       <c r="B103" s="27" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to update the recycling cans total.</t>
+          <t>As a Super Admin, I want to find users by type.</t>
         </is>
       </c>
       <c r="C103" s="27" t="inlineStr">
         <is>
-          <t>Use the cans/bin admin control.</t>
+          <t>Users → role filter pills + search.</t>
         </is>
       </c>
       <c r="D103" s="27" t="inlineStr">
         <is>
-          <t>Total updates; the ribbon reflects it.</t>
+          <t>Filter by role with counts; search by name/email across all orgs.</t>
         </is>
       </c>
       <c r="E103" s="28" t="n"/>
@@ -4137,60 +4137,72 @@
     <row r="104" ht="42" customHeight="1">
       <c r="A104" s="26" t="inlineStr">
         <is>
-          <t>SA12</t>
+          <t>SA7</t>
         </is>
       </c>
       <c r="B104" s="27" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want hours + records for any user.</t>
+          <t>As a Super Admin, I want to search events.</t>
         </is>
       </c>
       <c r="C104" s="27" t="inlineStr">
         <is>
-          <t>Add manual hours / open service record for any participant.</t>
+          <t>Events → search + date range; check supervisor/org per card.</t>
         </is>
       </c>
       <c r="D104" s="27" t="inlineStr">
         <is>
-          <t>Works for any org.</t>
+          <t>Filters work; each event shows supervisor and organization.</t>
         </is>
       </c>
       <c r="E104" s="28" t="n"/>
       <c r="F104" s="27" t="n"/>
       <c r="G104" s="28" t="n"/>
     </row>
-    <row r="105" ht="20" customHeight="1">
-      <c r="A105" s="24" t="inlineStr">
-        <is>
-          <t>Cross-cutting</t>
-        </is>
-      </c>
-      <c r="B105" s="25" t="n"/>
-      <c r="C105" s="25" t="n"/>
-      <c r="D105" s="25" t="n"/>
-      <c r="E105" s="25" t="n"/>
-      <c r="F105" s="25" t="n"/>
-      <c r="G105" s="25" t="n"/>
+    <row r="105" ht="42" customHeight="1">
+      <c r="A105" s="26" t="inlineStr">
+        <is>
+          <t>SA8</t>
+        </is>
+      </c>
+      <c r="B105" s="27" t="inlineStr">
+        <is>
+          <t>As a Super Admin, I want clear event-visibility labels.</t>
+        </is>
+      </c>
+      <c r="C105" s="27" t="inlineStr">
+        <is>
+          <t>New Event → 'Who can see this'.</t>
+        </is>
+      </c>
+      <c r="D105" s="27" t="inlineStr">
+        <is>
+          <t>'Open to all (community)' and 'Only &lt;org&gt; students' with helper text.</t>
+        </is>
+      </c>
+      <c r="E105" s="28" t="n"/>
+      <c r="F105" s="27" t="n"/>
+      <c r="G105" s="28" t="n"/>
     </row>
     <row r="106" ht="42" customHeight="1">
       <c r="A106" s="26" t="inlineStr">
         <is>
-          <t>X1</t>
+          <t>SA9</t>
         </is>
       </c>
       <c r="B106" s="27" t="inlineStr">
         <is>
-          <t>As a phone user, I want a usable mobile layout.</t>
+          <t>As a Super Admin, I want program-wide reports.</t>
         </is>
       </c>
       <c r="C106" s="27" t="inlineStr">
         <is>
-          <t>Open at phone width; use the menu drawer.</t>
+          <t>Open Reports / Dashboard.</t>
         </is>
       </c>
       <c r="D106" s="27" t="inlineStr">
         <is>
-          <t>Layout adapts; drawer opens/closes; no horizontal scroll.</t>
+          <t>Totals and charts across the whole program.</t>
         </is>
       </c>
       <c r="E106" s="28" t="n"/>
@@ -4200,36 +4212,299 @@
     <row r="107" ht="42" customHeight="1">
       <c r="A107" s="26" t="inlineStr">
         <is>
-          <t>X2</t>
+          <t>SA10</t>
         </is>
       </c>
       <c r="B107" s="27" t="inlineStr">
         <is>
-          <t>As a visitor, I want the recycling ribbon on the login page.</t>
+          <t>As a Super Admin, I want to verify email works.</t>
         </is>
       </c>
       <c r="C107" s="27" t="inlineStr">
         <is>
-          <t>Open login signed out.</t>
+          <t>Dashboard → Send test email.</t>
         </is>
       </c>
       <c r="D107" s="27" t="inlineStr">
         <is>
-          <t>Green ribbon shows on login.</t>
+          <t>Result shown (success or the exact failure reason).</t>
         </is>
       </c>
       <c r="E107" s="28" t="n"/>
       <c r="F107" s="27" t="n"/>
       <c r="G107" s="28" t="n"/>
     </row>
+    <row r="108" ht="42" customHeight="1">
+      <c r="A108" s="26" t="inlineStr">
+        <is>
+          <t>SA11</t>
+        </is>
+      </c>
+      <c r="B108" s="27" t="inlineStr">
+        <is>
+          <t>As a Super Admin, I want to update the recycling cans total.</t>
+        </is>
+      </c>
+      <c r="C108" s="27" t="inlineStr">
+        <is>
+          <t>Use the cans/bin admin control.</t>
+        </is>
+      </c>
+      <c r="D108" s="27" t="inlineStr">
+        <is>
+          <t>Total updates; the ribbon reflects it.</t>
+        </is>
+      </c>
+      <c r="E108" s="28" t="n"/>
+      <c r="F108" s="27" t="n"/>
+      <c r="G108" s="28" t="n"/>
+    </row>
+    <row r="109" ht="42" customHeight="1">
+      <c r="A109" s="26" t="inlineStr">
+        <is>
+          <t>SA12</t>
+        </is>
+      </c>
+      <c r="B109" s="27" t="inlineStr">
+        <is>
+          <t>As a Super Admin, I want hours + records for any user.</t>
+        </is>
+      </c>
+      <c r="C109" s="27" t="inlineStr">
+        <is>
+          <t>Add manual hours / open service record for any participant.</t>
+        </is>
+      </c>
+      <c r="D109" s="27" t="inlineStr">
+        <is>
+          <t>Works for any org.</t>
+        </is>
+      </c>
+      <c r="E109" s="28" t="n"/>
+      <c r="F109" s="27" t="n"/>
+      <c r="G109" s="28" t="n"/>
+    </row>
+    <row r="110" ht="42" customHeight="1">
+      <c r="A110" s="26" t="inlineStr">
+        <is>
+          <t>SA13</t>
+        </is>
+      </c>
+      <c r="B110" s="27" t="inlineStr">
+        <is>
+          <t>As a Super Admin, I want to set award thresholds by grade band and/or org.</t>
+        </is>
+      </c>
+      <c r="C110" s="27" t="inlineStr">
+        <is>
+          <t>Award Thresholds → add a rule (e.g. Elementary 20/30/40) → save.</t>
+        </is>
+      </c>
+      <c r="D110" s="27" t="inlineStr">
+        <is>
+          <t>Rule saved; an affected participant's dashboard/reports show the new bars; leaderboard/record medals follow.</t>
+        </is>
+      </c>
+      <c r="E110" s="28" t="n"/>
+      <c r="F110" s="27" t="n"/>
+      <c r="G110" s="28" t="n"/>
+    </row>
+    <row r="111" ht="42" customHeight="1">
+      <c r="A111" s="26" t="inlineStr">
+        <is>
+          <t>SA14</t>
+        </is>
+      </c>
+      <c r="B111" s="27" t="inlineStr">
+        <is>
+          <t>As a Super Admin, I want an audit log of key actions.</t>
+        </is>
+      </c>
+      <c r="C111" s="27" t="inlineStr">
+        <is>
+          <t>Do an action (create user, grant hours, edit org) → open Audit Log.</t>
+        </is>
+      </c>
+      <c r="D111" s="27" t="inlineStr">
+        <is>
+          <t>The action appears with who/when; search + action filters work.</t>
+        </is>
+      </c>
+      <c r="E111" s="28" t="n"/>
+      <c r="F111" s="27" t="n"/>
+      <c r="G111" s="28" t="n"/>
+    </row>
+    <row r="112" ht="42" customHeight="1">
+      <c r="A112" s="26" t="inlineStr">
+        <is>
+          <t>SA15</t>
+        </is>
+      </c>
+      <c r="B112" s="27" t="inlineStr">
+        <is>
+          <t>As a Super Admin, deleting a supervisor who runs events is blocked.</t>
+        </is>
+      </c>
+      <c r="C112" s="27" t="inlineStr">
+        <is>
+          <t>Try to delete a supervisor who supervises 1+ events.</t>
+        </is>
+      </c>
+      <c r="D112" s="27" t="inlineStr">
+        <is>
+          <t>Blocked with a clear message to reassign or remove their events first (events/hours preserved).</t>
+        </is>
+      </c>
+      <c r="E112" s="28" t="n"/>
+      <c r="F112" s="27" t="n"/>
+      <c r="G112" s="28" t="n"/>
+    </row>
+    <row r="113" ht="42" customHeight="1">
+      <c r="A113" s="26" t="inlineStr">
+        <is>
+          <t>SA16</t>
+        </is>
+      </c>
+      <c r="B113" s="27" t="inlineStr">
+        <is>
+          <t>As a Super Admin, I want to reassign a supervisor's events, then delete them.</t>
+        </is>
+      </c>
+      <c r="C113" s="27" t="inlineStr">
+        <is>
+          <t>Users → Reassign events → pick another supervisor → confirm; then delete the original.</t>
+        </is>
+      </c>
+      <c r="D113" s="27" t="inlineStr">
+        <is>
+          <t>Events move to the new supervisor; the original can then be deleted.</t>
+        </is>
+      </c>
+      <c r="E113" s="28" t="n"/>
+      <c r="F113" s="27" t="n"/>
+      <c r="G113" s="28" t="n"/>
+    </row>
+    <row r="114" ht="42" customHeight="1">
+      <c r="A114" s="26" t="inlineStr">
+        <is>
+          <t>SA17</t>
+        </is>
+      </c>
+      <c r="B114" s="27" t="inlineStr">
+        <is>
+          <t>As a Super Admin, creating a user pre-fills a temp password and emails an invite.</t>
+        </is>
+      </c>
+      <c r="C114" s="27" t="inlineStr">
+        <is>
+          <t>Add user; note the temp password field is pre-filled (Supervisor123!); save.</t>
+        </is>
+      </c>
+      <c r="D114" s="27" t="inlineStr">
+        <is>
+          <t>Account created; the person gets a set-password invite email.</t>
+        </is>
+      </c>
+      <c r="E114" s="28" t="n"/>
+      <c r="F114" s="27" t="n"/>
+      <c r="G114" s="28" t="n"/>
+    </row>
+    <row r="115" ht="42" customHeight="1">
+      <c r="A115" s="26" t="inlineStr">
+        <is>
+          <t>SA18</t>
+        </is>
+      </c>
+      <c r="B115" s="27" t="inlineStr">
+        <is>
+          <t>As a Super Admin, I want to assign an org when creating a user.</t>
+        </is>
+      </c>
+      <c r="C115" s="27" t="inlineStr">
+        <is>
+          <t>Add user → choose an Organization (or 'No specific organization') → save.</t>
+        </is>
+      </c>
+      <c r="D115" s="27" t="inlineStr">
+        <is>
+          <t>The user is stamped to that org (visible/manageable by that org's Admin).</t>
+        </is>
+      </c>
+      <c r="E115" s="28" t="n"/>
+      <c r="F115" s="27" t="n"/>
+      <c r="G115" s="28" t="n"/>
+    </row>
+    <row r="116" ht="20" customHeight="1">
+      <c r="A116" s="24" t="inlineStr">
+        <is>
+          <t>Cross-cutting</t>
+        </is>
+      </c>
+      <c r="B116" s="25" t="n"/>
+      <c r="C116" s="25" t="n"/>
+      <c r="D116" s="25" t="n"/>
+      <c r="E116" s="25" t="n"/>
+      <c r="F116" s="25" t="n"/>
+      <c r="G116" s="25" t="n"/>
+    </row>
+    <row r="117" ht="42" customHeight="1">
+      <c r="A117" s="26" t="inlineStr">
+        <is>
+          <t>X1</t>
+        </is>
+      </c>
+      <c r="B117" s="27" t="inlineStr">
+        <is>
+          <t>As a phone user, I want a usable mobile layout.</t>
+        </is>
+      </c>
+      <c r="C117" s="27" t="inlineStr">
+        <is>
+          <t>Open at phone width; use the menu drawer.</t>
+        </is>
+      </c>
+      <c r="D117" s="27" t="inlineStr">
+        <is>
+          <t>Layout adapts; drawer opens/closes; no horizontal scroll.</t>
+        </is>
+      </c>
+      <c r="E117" s="28" t="n"/>
+      <c r="F117" s="27" t="n"/>
+      <c r="G117" s="28" t="n"/>
+    </row>
+    <row r="118" ht="42" customHeight="1">
+      <c r="A118" s="26" t="inlineStr">
+        <is>
+          <t>X2</t>
+        </is>
+      </c>
+      <c r="B118" s="27" t="inlineStr">
+        <is>
+          <t>As a visitor, I want the recycling ribbon on the login page.</t>
+        </is>
+      </c>
+      <c r="C118" s="27" t="inlineStr">
+        <is>
+          <t>Open login signed out.</t>
+        </is>
+      </c>
+      <c r="D118" s="27" t="inlineStr">
+        <is>
+          <t>Green ribbon shows on login.</t>
+        </is>
+      </c>
+      <c r="E118" s="28" t="n"/>
+      <c r="F118" s="27" t="n"/>
+      <c r="G118" s="28" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A116:G116"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A80:G80"/>
+    <mergeCell ref="A97:G97"/>
     <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A77:G77"/>
-    <mergeCell ref="A105:G105"/>
     <mergeCell ref="A35:G35"/>
-    <mergeCell ref="A92:G92"/>
     <mergeCell ref="A57:G57"/>
     <mergeCell ref="A51:G51"/>
     <mergeCell ref="A10:G10"/>
@@ -4278,7 +4553,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E58:E76">
+  <conditionalFormatting sqref="E58:E79">
     <cfRule type="cellIs" priority="13" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -4289,7 +4564,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E78:E91">
+  <conditionalFormatting sqref="E81:E96">
     <cfRule type="cellIs" priority="16" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -4300,7 +4575,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E93:E104">
+  <conditionalFormatting sqref="E98:E115">
     <cfRule type="cellIs" priority="19" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -4311,7 +4586,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E106:E107">
+  <conditionalFormatting sqref="E117:E118">
     <cfRule type="cellIs" priority="22" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -4323,7 +4598,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E4:E9 E11:E34 E36:E50 E52:E56 E58:E76 E78:E91 E93:E104 E106:E107" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E4:E9 E11:E34 E36:E50 E52:E56 E58:E79 E81:E96 E98:E115 E117:E118" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pass,Fail,Blocked,Not tested,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4337,7 +4612,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G107"/>
+  <dimension ref="A1:G118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4608,17 +4883,17 @@
       </c>
       <c r="B12" s="27" t="inlineStr">
         <is>
-          <t>As a student, I want to enter an organization code during sign-up.</t>
+          <t>As a student, a join code is required when I pick an organization.</t>
         </is>
       </c>
       <c r="C12" s="27" t="inlineStr">
         <is>
-          <t>Enter a code in the Organization code field (optional) and submit.</t>
+          <t>Choose an organization affiliation; the join-code field appears and is required.</t>
         </is>
       </c>
       <c r="D12" s="27" t="inlineStr">
         <is>
-          <t>A valid code enrolls me in that org; a bad code is rejected; blank is allowed.</t>
+          <t>Can't submit without a code; a valid code enrolls me in that org, a bad one is rejected. (Community/no-org path needs no code.)</t>
         </is>
       </c>
       <c r="E12" s="28" t="n"/>
@@ -6189,38 +6464,50 @@
       <c r="F76" s="27" t="n"/>
       <c r="G76" s="28" t="n"/>
     </row>
-    <row r="77" ht="20" customHeight="1">
-      <c r="A77" s="24" t="inlineStr">
-        <is>
-          <t>Admin (org-scoped)</t>
-        </is>
-      </c>
-      <c r="B77" s="25" t="n"/>
-      <c r="C77" s="25" t="n"/>
-      <c r="D77" s="25" t="n"/>
-      <c r="E77" s="25" t="n"/>
-      <c r="F77" s="25" t="n"/>
-      <c r="G77" s="25" t="n"/>
+    <row r="77" ht="42" customHeight="1">
+      <c r="A77" s="26" t="inlineStr">
+        <is>
+          <t>SV20</t>
+        </is>
+      </c>
+      <c r="B77" s="27" t="inlineStr">
+        <is>
+          <t>As a supervisor, I want to attach files to a message.</t>
+        </is>
+      </c>
+      <c r="C77" s="27" t="inlineStr">
+        <is>
+          <t>Roster → Message attendees → add an image/PDF (≤10 MB) → send.</t>
+        </is>
+      </c>
+      <c r="D77" s="27" t="inlineStr">
+        <is>
+          <t>The attachment uploads, appears in the dialog, and arrives with the email.</t>
+        </is>
+      </c>
+      <c r="E77" s="28" t="n"/>
+      <c r="F77" s="27" t="n"/>
+      <c r="G77" s="28" t="n"/>
     </row>
     <row r="78" ht="42" customHeight="1">
       <c r="A78" s="26" t="inlineStr">
         <is>
-          <t>AD1</t>
+          <t>SV21</t>
         </is>
       </c>
       <c r="B78" s="27" t="inlineStr">
         <is>
-          <t>As an Admin, I want the correct menu tabs.</t>
+          <t>As a supervisor, I want an email when someone signs up.</t>
         </is>
       </c>
       <c r="C78" s="27" t="inlineStr">
         <is>
-          <t>Look at the left menu.</t>
+          <t>Have a participant sign up for your event (with notifications on).</t>
         </is>
       </c>
       <c r="D78" s="27" t="inlineStr">
         <is>
-          <t>Dashboard, Pending Reviews, Reviewed History, My Events, All Opportunities, Users, Organizations, My Hours, Help.</t>
+          <t>You receive a sign-up email; toggling notifications off stops them.</t>
         </is>
       </c>
       <c r="E78" s="28" t="n"/>
@@ -6230,72 +6517,60 @@
     <row r="79" ht="42" customHeight="1">
       <c r="A79" s="26" t="inlineStr">
         <is>
-          <t>AD2</t>
+          <t>SV22</t>
         </is>
       </c>
       <c r="B79" s="27" t="inlineStr">
         <is>
-          <t>As an Admin, I can do everything a supervisor can.</t>
+          <t>As a supervisor, I want to verify who's a real member before sharing access.</t>
         </is>
       </c>
       <c r="C79" s="27" t="inlineStr">
         <is>
-          <t>Spot-check: approve an item and create an event.</t>
+          <t>Open the Roster and read the attendee badges.</t>
         </is>
       </c>
       <c r="D79" s="27" t="inlineStr">
         <is>
-          <t>Both work.</t>
+          <t>Each shows their org, or 'Community · unverified'; a warning reminds you to confirm before sharing a building QR.</t>
         </is>
       </c>
       <c r="E79" s="28" t="n"/>
       <c r="F79" s="27" t="n"/>
       <c r="G79" s="28" t="n"/>
     </row>
-    <row r="80" ht="42" customHeight="1">
-      <c r="A80" s="26" t="inlineStr">
-        <is>
-          <t>AD3</t>
-        </is>
-      </c>
-      <c r="B80" s="27" t="inlineStr">
-        <is>
-          <t>As an Admin, I only see my org's non-admin users.</t>
-        </is>
-      </c>
-      <c r="C80" s="27" t="inlineStr">
-        <is>
-          <t>Open Users.</t>
-        </is>
-      </c>
-      <c r="D80" s="27" t="inlineStr">
-        <is>
-          <t>Only participants/parents/supervisors in your org; no admins/super admins; no other orgs.</t>
-        </is>
-      </c>
-      <c r="E80" s="28" t="n"/>
-      <c r="F80" s="27" t="n"/>
-      <c r="G80" s="28" t="n"/>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="24" t="inlineStr">
+        <is>
+          <t>Admin (org-scoped)</t>
+        </is>
+      </c>
+      <c r="B80" s="25" t="n"/>
+      <c r="C80" s="25" t="n"/>
+      <c r="D80" s="25" t="n"/>
+      <c r="E80" s="25" t="n"/>
+      <c r="F80" s="25" t="n"/>
+      <c r="G80" s="25" t="n"/>
     </row>
     <row r="81" ht="42" customHeight="1">
       <c r="A81" s="26" t="inlineStr">
         <is>
-          <t>AD4</t>
+          <t>AD1</t>
         </is>
       </c>
       <c r="B81" s="27" t="inlineStr">
         <is>
-          <t>As an Admin, I want to add a supervisor.</t>
+          <t>As an Admin, I want the correct menu tabs.</t>
         </is>
       </c>
       <c r="C81" s="27" t="inlineStr">
         <is>
-          <t>Users → Add user → Supervisor → save.</t>
+          <t>Look at the left menu.</t>
         </is>
       </c>
       <c r="D81" s="27" t="inlineStr">
         <is>
-          <t>Supervisor created, stamped to your org; invite email sent.</t>
+          <t>Dashboard, Pending Reviews, Reviewed History, My Events, All Opportunities, Users, Organizations, My Hours, Help.</t>
         </is>
       </c>
       <c r="E81" s="28" t="n"/>
@@ -6305,22 +6580,22 @@
     <row r="82" ht="42" customHeight="1">
       <c r="A82" s="26" t="inlineStr">
         <is>
-          <t>AD5</t>
+          <t>AD2</t>
         </is>
       </c>
       <c r="B82" s="27" t="inlineStr">
         <is>
-          <t>As an Admin, I want to create a participant as a fallback.</t>
+          <t>As an Admin, I can do everything a supervisor can.</t>
         </is>
       </c>
       <c r="C82" s="27" t="inlineStr">
         <is>
-          <t>Users → Add user → Participant → save.</t>
+          <t>Spot-check: approve an item and create an event.</t>
         </is>
       </c>
       <c r="D82" s="27" t="inlineStr">
         <is>
-          <t>Participant created with a set-password invite (no silent password).</t>
+          <t>Both work.</t>
         </is>
       </c>
       <c r="E82" s="28" t="n"/>
@@ -6330,22 +6605,22 @@
     <row r="83" ht="42" customHeight="1">
       <c r="A83" s="26" t="inlineStr">
         <is>
-          <t>AD6</t>
+          <t>AD3</t>
         </is>
       </c>
       <c r="B83" s="27" t="inlineStr">
         <is>
-          <t>As an Admin, I want to grant participant hours.</t>
+          <t>As an Admin, I only see my org's non-admin users.</t>
         </is>
       </c>
       <c r="C83" s="27" t="inlineStr">
         <is>
-          <t>Open a participant in your org → Add hours.</t>
+          <t>Open Users.</t>
         </is>
       </c>
       <c r="D83" s="27" t="inlineStr">
         <is>
-          <t>Hours auto-approved; count toward their total/medals.</t>
+          <t>Only participants/parents/supervisors in your org; no admins/super admins; no other orgs.</t>
         </is>
       </c>
       <c r="E83" s="28" t="n"/>
@@ -6355,22 +6630,22 @@
     <row r="84" ht="42" customHeight="1">
       <c r="A84" s="26" t="inlineStr">
         <is>
-          <t>AD7</t>
+          <t>AD4</t>
         </is>
       </c>
       <c r="B84" s="27" t="inlineStr">
         <is>
-          <t>As an Admin, I want a participant's service record.</t>
+          <t>As an Admin, I want to add a supervisor.</t>
         </is>
       </c>
       <c r="C84" s="27" t="inlineStr">
         <is>
-          <t>Users → Service record for a participant in your org.</t>
+          <t>Users → Add user → Supervisor → save.</t>
         </is>
       </c>
       <c r="D84" s="27" t="inlineStr">
         <is>
-          <t>Record opens.</t>
+          <t>Supervisor created, stamped to your org; invite email sent.</t>
         </is>
       </c>
       <c r="E84" s="28" t="n"/>
@@ -6380,22 +6655,22 @@
     <row r="85" ht="42" customHeight="1">
       <c r="A85" s="26" t="inlineStr">
         <is>
-          <t>AD8</t>
+          <t>AD5</t>
         </is>
       </c>
       <c r="B85" s="27" t="inlineStr">
         <is>
-          <t>As an Admin, I want to edit/delete my org's users.</t>
+          <t>As an Admin, I want to create a participant as a fallback.</t>
         </is>
       </c>
       <c r="C85" s="27" t="inlineStr">
         <is>
-          <t>Edit a name/phone; delete a test user.</t>
+          <t>Users → Add user → Participant → save.</t>
         </is>
       </c>
       <c r="D85" s="27" t="inlineStr">
         <is>
-          <t>Changes apply within your org.</t>
+          <t>Participant created with a set-password invite (no silent password).</t>
         </is>
       </c>
       <c r="E85" s="28" t="n"/>
@@ -6405,22 +6680,22 @@
     <row r="86" ht="42" customHeight="1">
       <c r="A86" s="26" t="inlineStr">
         <is>
-          <t>AD9</t>
+          <t>AD6</t>
         </is>
       </c>
       <c r="B86" s="27" t="inlineStr">
         <is>
-          <t>As an Admin, I must NOT act on users outside my org.</t>
+          <t>As an Admin, I want to grant participant hours.</t>
         </is>
       </c>
       <c r="C86" s="27" t="inlineStr">
         <is>
-          <t>Attempt to reach another org's user (e.g. direct URL).</t>
+          <t>Open a participant in your org → Add hours.</t>
         </is>
       </c>
       <c r="D86" s="27" t="inlineStr">
         <is>
-          <t>Blocked / not visible.</t>
+          <t>Hours auto-approved; count toward their total/medals.</t>
         </is>
       </c>
       <c r="E86" s="28" t="n"/>
@@ -6430,22 +6705,22 @@
     <row r="87" ht="42" customHeight="1">
       <c r="A87" s="26" t="inlineStr">
         <is>
-          <t>AD10</t>
+          <t>AD7</t>
         </is>
       </c>
       <c r="B87" s="27" t="inlineStr">
         <is>
-          <t>As an Admin, I cannot grant Admin access or manage admins.</t>
+          <t>As an Admin, I want a participant's service record.</t>
         </is>
       </c>
       <c r="C87" s="27" t="inlineStr">
         <is>
-          <t>Look for the 'grant Admin access' action.</t>
+          <t>Users → Service record for a participant in your org.</t>
         </is>
       </c>
       <c r="D87" s="27" t="inlineStr">
         <is>
-          <t>No such button; attempts are blocked server-side.</t>
+          <t>Record opens.</t>
         </is>
       </c>
       <c r="E87" s="28" t="n"/>
@@ -6455,22 +6730,22 @@
     <row r="88" ht="42" customHeight="1">
       <c r="A88" s="26" t="inlineStr">
         <is>
-          <t>AD11</t>
+          <t>AD8</t>
         </is>
       </c>
       <c r="B88" s="27" t="inlineStr">
         <is>
-          <t>As an Admin, I see and edit only my own organization.</t>
+          <t>As an Admin, I want to edit/delete my org's users.</t>
         </is>
       </c>
       <c r="C88" s="27" t="inlineStr">
         <is>
-          <t>Open Organizations.</t>
+          <t>Edit a name/phone; delete a test user.</t>
         </is>
       </c>
       <c r="D88" s="27" t="inlineStr">
         <is>
-          <t>Only your org shows; you can edit its settings.</t>
+          <t>Changes apply within your org.</t>
         </is>
       </c>
       <c r="E88" s="28" t="n"/>
@@ -6480,22 +6755,22 @@
     <row r="89" ht="42" customHeight="1">
       <c r="A89" s="26" t="inlineStr">
         <is>
-          <t>AD12</t>
+          <t>AD9</t>
         </is>
       </c>
       <c r="B89" s="27" t="inlineStr">
         <is>
-          <t>As an Admin, I want to generate/rotate my org's join code.</t>
+          <t>As an Admin, I must NOT act on users outside my org.</t>
         </is>
       </c>
       <c r="C89" s="27" t="inlineStr">
         <is>
-          <t>Organizations → set/generate a join code → save.</t>
+          <t>Attempt to reach another org's user (e.g. direct URL).</t>
         </is>
       </c>
       <c r="D89" s="27" t="inlineStr">
         <is>
-          <t>Join code saved; usable at sign-up.</t>
+          <t>Blocked / not visible.</t>
         </is>
       </c>
       <c r="E89" s="28" t="n"/>
@@ -6505,22 +6780,22 @@
     <row r="90" ht="42" customHeight="1">
       <c r="A90" s="26" t="inlineStr">
         <is>
-          <t>AD13</t>
+          <t>AD10</t>
         </is>
       </c>
       <c r="B90" s="27" t="inlineStr">
         <is>
-          <t>As an Admin, I cannot create organizations.</t>
+          <t>As an Admin, I cannot grant Admin access or manage admins.</t>
         </is>
       </c>
       <c r="C90" s="27" t="inlineStr">
         <is>
-          <t>Look for 'Add organization'.</t>
+          <t>Look for the 'grant Admin access' action.</t>
         </is>
       </c>
       <c r="D90" s="27" t="inlineStr">
         <is>
-          <t>No Add button; creation blocked.</t>
+          <t>No such button; attempts are blocked server-side.</t>
         </is>
       </c>
       <c r="E90" s="28" t="n"/>
@@ -6530,60 +6805,72 @@
     <row r="91" ht="42" customHeight="1">
       <c r="A91" s="26" t="inlineStr">
         <is>
-          <t>AD14</t>
+          <t>AD11</t>
         </is>
       </c>
       <c r="B91" s="27" t="inlineStr">
         <is>
-          <t>As an Admin, I cannot change the recycling cans total.</t>
+          <t>As an Admin, I see and edit only my own organization.</t>
         </is>
       </c>
       <c r="C91" s="27" t="inlineStr">
         <is>
-          <t>Look for the cans/bin admin control.</t>
+          <t>Open Organizations.</t>
         </is>
       </c>
       <c r="D91" s="27" t="inlineStr">
         <is>
-          <t>Not available (Super Admin only).</t>
+          <t>Only your org shows; you can edit its settings.</t>
         </is>
       </c>
       <c r="E91" s="28" t="n"/>
       <c r="F91" s="27" t="n"/>
       <c r="G91" s="28" t="n"/>
     </row>
-    <row r="92" ht="20" customHeight="1">
-      <c r="A92" s="24" t="inlineStr">
-        <is>
-          <t>Super Admin (global)</t>
-        </is>
-      </c>
-      <c r="B92" s="25" t="n"/>
-      <c r="C92" s="25" t="n"/>
-      <c r="D92" s="25" t="n"/>
-      <c r="E92" s="25" t="n"/>
-      <c r="F92" s="25" t="n"/>
-      <c r="G92" s="25" t="n"/>
+    <row r="92" ht="42" customHeight="1">
+      <c r="A92" s="26" t="inlineStr">
+        <is>
+          <t>AD12</t>
+        </is>
+      </c>
+      <c r="B92" s="27" t="inlineStr">
+        <is>
+          <t>As an Admin, I want to generate/rotate my org's join code.</t>
+        </is>
+      </c>
+      <c r="C92" s="27" t="inlineStr">
+        <is>
+          <t>Organizations → set/generate a join code → save.</t>
+        </is>
+      </c>
+      <c r="D92" s="27" t="inlineStr">
+        <is>
+          <t>Join code saved; usable at sign-up.</t>
+        </is>
+      </c>
+      <c r="E92" s="28" t="n"/>
+      <c r="F92" s="27" t="n"/>
+      <c r="G92" s="28" t="n"/>
     </row>
     <row r="93" ht="42" customHeight="1">
       <c r="A93" s="26" t="inlineStr">
         <is>
-          <t>SA1</t>
+          <t>AD13</t>
         </is>
       </c>
       <c r="B93" s="27" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want the correct menu tabs.</t>
+          <t>As an Admin, I cannot create organizations.</t>
         </is>
       </c>
       <c r="C93" s="27" t="inlineStr">
         <is>
-          <t>Look at the left menu.</t>
+          <t>Look for 'Add organization'.</t>
         </is>
       </c>
       <c r="D93" s="27" t="inlineStr">
         <is>
-          <t>Dashboard, Reports, Users, Events, Organizations (Help in footer).</t>
+          <t>No Add button; creation blocked.</t>
         </is>
       </c>
       <c r="E93" s="28" t="n"/>
@@ -6593,22 +6880,22 @@
     <row r="94" ht="42" customHeight="1">
       <c r="A94" s="26" t="inlineStr">
         <is>
-          <t>SA2</t>
+          <t>AD14</t>
         </is>
       </c>
       <c r="B94" s="27" t="inlineStr">
         <is>
-          <t>As a Super Admin, I can do everything an Admin can, across all orgs.</t>
+          <t>As an Admin, I cannot change the recycling cans total.</t>
         </is>
       </c>
       <c r="C94" s="27" t="inlineStr">
         <is>
-          <t>Spot-check user + org actions on more than one org.</t>
+          <t>Look for the cans/bin admin control.</t>
         </is>
       </c>
       <c r="D94" s="27" t="inlineStr">
         <is>
-          <t>All allowed regardless of org.</t>
+          <t>Not available (Super Admin only).</t>
         </is>
       </c>
       <c r="E94" s="28" t="n"/>
@@ -6618,22 +6905,22 @@
     <row r="95" ht="42" customHeight="1">
       <c r="A95" s="26" t="inlineStr">
         <is>
-          <t>SA3</t>
+          <t>AD15</t>
         </is>
       </c>
       <c r="B95" s="27" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to create users incl. Supervisor and Super Admin.</t>
+          <t>As an Admin, I can turn my activity emails off.</t>
         </is>
       </c>
       <c r="C95" s="27" t="inlineStr">
         <is>
-          <t>Users → Add user → each role.</t>
+          <t>Dashboard → Email notifications toggle off; have a student sign up for your event.</t>
         </is>
       </c>
       <c r="D95" s="27" t="inlineStr">
         <is>
-          <t>Participant/Supervisor/Super Admin options available; account created + invite email.</t>
+          <t>No sign-up email arrives while off; turning it back on resumes them.</t>
         </is>
       </c>
       <c r="E95" s="28" t="n"/>
@@ -6643,72 +6930,60 @@
     <row r="96" ht="42" customHeight="1">
       <c r="A96" s="26" t="inlineStr">
         <is>
-          <t>SA4</t>
+          <t>AD16</t>
         </is>
       </c>
       <c r="B96" s="27" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to grant/revoke Admin access.</t>
+          <t>As an Admin creating a user, I choose among only my org(s).</t>
         </is>
       </c>
       <c r="C96" s="27" t="inlineStr">
         <is>
-          <t>Open a user → grant Admin access → check org(s) → save; then uncheck all → save.</t>
+          <t>Add user → Organization picker.</t>
         </is>
       </c>
       <c r="D96" s="27" t="inlineStr">
         <is>
-          <t>Checking orgs makes an Admin; unchecking all reverts to participant.</t>
+          <t>Only the org(s) I manage are listed (Super Admins see all + 'none').</t>
         </is>
       </c>
       <c r="E96" s="28" t="n"/>
       <c r="F96" s="27" t="n"/>
       <c r="G96" s="28" t="n"/>
     </row>
-    <row r="97" ht="42" customHeight="1">
-      <c r="A97" s="26" t="inlineStr">
-        <is>
-          <t>SA5</t>
-        </is>
-      </c>
-      <c r="B97" s="27" t="inlineStr">
-        <is>
-          <t>As a Super Admin, I want to create organizations + join codes.</t>
-        </is>
-      </c>
-      <c r="C97" s="27" t="inlineStr">
-        <is>
-          <t>Organizations → Add organization → set details + join code.</t>
-        </is>
-      </c>
-      <c r="D97" s="27" t="inlineStr">
-        <is>
-          <t>Org created with its join code.</t>
-        </is>
-      </c>
-      <c r="E97" s="28" t="n"/>
-      <c r="F97" s="27" t="n"/>
-      <c r="G97" s="28" t="n"/>
+    <row r="97" ht="20" customHeight="1">
+      <c r="A97" s="24" t="inlineStr">
+        <is>
+          <t>Super Admin (global)</t>
+        </is>
+      </c>
+      <c r="B97" s="25" t="n"/>
+      <c r="C97" s="25" t="n"/>
+      <c r="D97" s="25" t="n"/>
+      <c r="E97" s="25" t="n"/>
+      <c r="F97" s="25" t="n"/>
+      <c r="G97" s="25" t="n"/>
     </row>
     <row r="98" ht="42" customHeight="1">
       <c r="A98" s="26" t="inlineStr">
         <is>
-          <t>SA6</t>
+          <t>SA1</t>
         </is>
       </c>
       <c r="B98" s="27" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to find users by type.</t>
+          <t>As a Super Admin, I want the correct menu tabs.</t>
         </is>
       </c>
       <c r="C98" s="27" t="inlineStr">
         <is>
-          <t>Users → role filter pills + search.</t>
+          <t>Look at the left menu.</t>
         </is>
       </c>
       <c r="D98" s="27" t="inlineStr">
         <is>
-          <t>Filter by role with counts; search by name/email across all orgs.</t>
+          <t>Dashboard, Reports, Users, Events, Organizations (Help in footer).</t>
         </is>
       </c>
       <c r="E98" s="28" t="n"/>
@@ -6718,22 +6993,22 @@
     <row r="99" ht="42" customHeight="1">
       <c r="A99" s="26" t="inlineStr">
         <is>
-          <t>SA7</t>
+          <t>SA2</t>
         </is>
       </c>
       <c r="B99" s="27" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to search events.</t>
+          <t>As a Super Admin, I can do everything an Admin can, across all orgs.</t>
         </is>
       </c>
       <c r="C99" s="27" t="inlineStr">
         <is>
-          <t>Events → search + date range; check supervisor/org per card.</t>
+          <t>Spot-check user + org actions on more than one org.</t>
         </is>
       </c>
       <c r="D99" s="27" t="inlineStr">
         <is>
-          <t>Filters work; each event shows supervisor and organization.</t>
+          <t>All allowed regardless of org.</t>
         </is>
       </c>
       <c r="E99" s="28" t="n"/>
@@ -6743,22 +7018,22 @@
     <row r="100" ht="42" customHeight="1">
       <c r="A100" s="26" t="inlineStr">
         <is>
-          <t>SA8</t>
+          <t>SA3</t>
         </is>
       </c>
       <c r="B100" s="27" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want clear event-visibility labels.</t>
+          <t>As a Super Admin, I want to create users incl. Supervisor and Super Admin.</t>
         </is>
       </c>
       <c r="C100" s="27" t="inlineStr">
         <is>
-          <t>New Event → 'Who can see this'.</t>
+          <t>Users → Add user → each role.</t>
         </is>
       </c>
       <c r="D100" s="27" t="inlineStr">
         <is>
-          <t>'Open to all (community)' and 'Only &lt;org&gt; students' with helper text.</t>
+          <t>Participant/Supervisor/Super Admin options available; account created + invite email.</t>
         </is>
       </c>
       <c r="E100" s="28" t="n"/>
@@ -6768,22 +7043,22 @@
     <row r="101" ht="42" customHeight="1">
       <c r="A101" s="26" t="inlineStr">
         <is>
-          <t>SA9</t>
+          <t>SA4</t>
         </is>
       </c>
       <c r="B101" s="27" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want program-wide reports.</t>
+          <t>As a Super Admin, I want to grant/revoke Admin access.</t>
         </is>
       </c>
       <c r="C101" s="27" t="inlineStr">
         <is>
-          <t>Open Reports / Dashboard.</t>
+          <t>Open a user → grant Admin access → check org(s) → save; then uncheck all → save.</t>
         </is>
       </c>
       <c r="D101" s="27" t="inlineStr">
         <is>
-          <t>Totals and charts across the whole program.</t>
+          <t>Checking orgs makes an Admin; unchecking all reverts to participant.</t>
         </is>
       </c>
       <c r="E101" s="28" t="n"/>
@@ -6793,22 +7068,22 @@
     <row r="102" ht="42" customHeight="1">
       <c r="A102" s="26" t="inlineStr">
         <is>
-          <t>SA10</t>
+          <t>SA5</t>
         </is>
       </c>
       <c r="B102" s="27" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to verify email works.</t>
+          <t>As a Super Admin, I want to create organizations + join codes.</t>
         </is>
       </c>
       <c r="C102" s="27" t="inlineStr">
         <is>
-          <t>Dashboard → Send test email.</t>
+          <t>Organizations → Add organization → set details + join code.</t>
         </is>
       </c>
       <c r="D102" s="27" t="inlineStr">
         <is>
-          <t>Result shown (success or the exact failure reason).</t>
+          <t>Org created with its join code.</t>
         </is>
       </c>
       <c r="E102" s="28" t="n"/>
@@ -6818,22 +7093,22 @@
     <row r="103" ht="42" customHeight="1">
       <c r="A103" s="26" t="inlineStr">
         <is>
-          <t>SA11</t>
+          <t>SA6</t>
         </is>
       </c>
       <c r="B103" s="27" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to update the recycling cans total.</t>
+          <t>As a Super Admin, I want to find users by type.</t>
         </is>
       </c>
       <c r="C103" s="27" t="inlineStr">
         <is>
-          <t>Use the cans/bin admin control.</t>
+          <t>Users → role filter pills + search.</t>
         </is>
       </c>
       <c r="D103" s="27" t="inlineStr">
         <is>
-          <t>Total updates; the ribbon reflects it.</t>
+          <t>Filter by role with counts; search by name/email across all orgs.</t>
         </is>
       </c>
       <c r="E103" s="28" t="n"/>
@@ -6843,60 +7118,72 @@
     <row r="104" ht="42" customHeight="1">
       <c r="A104" s="26" t="inlineStr">
         <is>
-          <t>SA12</t>
+          <t>SA7</t>
         </is>
       </c>
       <c r="B104" s="27" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want hours + records for any user.</t>
+          <t>As a Super Admin, I want to search events.</t>
         </is>
       </c>
       <c r="C104" s="27" t="inlineStr">
         <is>
-          <t>Add manual hours / open service record for any participant.</t>
+          <t>Events → search + date range; check supervisor/org per card.</t>
         </is>
       </c>
       <c r="D104" s="27" t="inlineStr">
         <is>
-          <t>Works for any org.</t>
+          <t>Filters work; each event shows supervisor and organization.</t>
         </is>
       </c>
       <c r="E104" s="28" t="n"/>
       <c r="F104" s="27" t="n"/>
       <c r="G104" s="28" t="n"/>
     </row>
-    <row r="105" ht="20" customHeight="1">
-      <c r="A105" s="24" t="inlineStr">
-        <is>
-          <t>Cross-cutting</t>
-        </is>
-      </c>
-      <c r="B105" s="25" t="n"/>
-      <c r="C105" s="25" t="n"/>
-      <c r="D105" s="25" t="n"/>
-      <c r="E105" s="25" t="n"/>
-      <c r="F105" s="25" t="n"/>
-      <c r="G105" s="25" t="n"/>
+    <row r="105" ht="42" customHeight="1">
+      <c r="A105" s="26" t="inlineStr">
+        <is>
+          <t>SA8</t>
+        </is>
+      </c>
+      <c r="B105" s="27" t="inlineStr">
+        <is>
+          <t>As a Super Admin, I want clear event-visibility labels.</t>
+        </is>
+      </c>
+      <c r="C105" s="27" t="inlineStr">
+        <is>
+          <t>New Event → 'Who can see this'.</t>
+        </is>
+      </c>
+      <c r="D105" s="27" t="inlineStr">
+        <is>
+          <t>'Open to all (community)' and 'Only &lt;org&gt; students' with helper text.</t>
+        </is>
+      </c>
+      <c r="E105" s="28" t="n"/>
+      <c r="F105" s="27" t="n"/>
+      <c r="G105" s="28" t="n"/>
     </row>
     <row r="106" ht="42" customHeight="1">
       <c r="A106" s="26" t="inlineStr">
         <is>
-          <t>X1</t>
+          <t>SA9</t>
         </is>
       </c>
       <c r="B106" s="27" t="inlineStr">
         <is>
-          <t>As a phone user, I want a usable mobile layout.</t>
+          <t>As a Super Admin, I want program-wide reports.</t>
         </is>
       </c>
       <c r="C106" s="27" t="inlineStr">
         <is>
-          <t>Open at phone width; use the menu drawer.</t>
+          <t>Open Reports / Dashboard.</t>
         </is>
       </c>
       <c r="D106" s="27" t="inlineStr">
         <is>
-          <t>Layout adapts; drawer opens/closes; no horizontal scroll.</t>
+          <t>Totals and charts across the whole program.</t>
         </is>
       </c>
       <c r="E106" s="28" t="n"/>
@@ -6906,36 +7193,299 @@
     <row r="107" ht="42" customHeight="1">
       <c r="A107" s="26" t="inlineStr">
         <is>
-          <t>X2</t>
+          <t>SA10</t>
         </is>
       </c>
       <c r="B107" s="27" t="inlineStr">
         <is>
-          <t>As a visitor, I want the recycling ribbon on the login page.</t>
+          <t>As a Super Admin, I want to verify email works.</t>
         </is>
       </c>
       <c r="C107" s="27" t="inlineStr">
         <is>
-          <t>Open login signed out.</t>
+          <t>Dashboard → Send test email.</t>
         </is>
       </c>
       <c r="D107" s="27" t="inlineStr">
         <is>
-          <t>Green ribbon shows on login.</t>
+          <t>Result shown (success or the exact failure reason).</t>
         </is>
       </c>
       <c r="E107" s="28" t="n"/>
       <c r="F107" s="27" t="n"/>
       <c r="G107" s="28" t="n"/>
     </row>
+    <row r="108" ht="42" customHeight="1">
+      <c r="A108" s="26" t="inlineStr">
+        <is>
+          <t>SA11</t>
+        </is>
+      </c>
+      <c r="B108" s="27" t="inlineStr">
+        <is>
+          <t>As a Super Admin, I want to update the recycling cans total.</t>
+        </is>
+      </c>
+      <c r="C108" s="27" t="inlineStr">
+        <is>
+          <t>Use the cans/bin admin control.</t>
+        </is>
+      </c>
+      <c r="D108" s="27" t="inlineStr">
+        <is>
+          <t>Total updates; the ribbon reflects it.</t>
+        </is>
+      </c>
+      <c r="E108" s="28" t="n"/>
+      <c r="F108" s="27" t="n"/>
+      <c r="G108" s="28" t="n"/>
+    </row>
+    <row r="109" ht="42" customHeight="1">
+      <c r="A109" s="26" t="inlineStr">
+        <is>
+          <t>SA12</t>
+        </is>
+      </c>
+      <c r="B109" s="27" t="inlineStr">
+        <is>
+          <t>As a Super Admin, I want hours + records for any user.</t>
+        </is>
+      </c>
+      <c r="C109" s="27" t="inlineStr">
+        <is>
+          <t>Add manual hours / open service record for any participant.</t>
+        </is>
+      </c>
+      <c r="D109" s="27" t="inlineStr">
+        <is>
+          <t>Works for any org.</t>
+        </is>
+      </c>
+      <c r="E109" s="28" t="n"/>
+      <c r="F109" s="27" t="n"/>
+      <c r="G109" s="28" t="n"/>
+    </row>
+    <row r="110" ht="42" customHeight="1">
+      <c r="A110" s="26" t="inlineStr">
+        <is>
+          <t>SA13</t>
+        </is>
+      </c>
+      <c r="B110" s="27" t="inlineStr">
+        <is>
+          <t>As a Super Admin, I want to set award thresholds by grade band and/or org.</t>
+        </is>
+      </c>
+      <c r="C110" s="27" t="inlineStr">
+        <is>
+          <t>Award Thresholds → add a rule (e.g. Elementary 20/30/40) → save.</t>
+        </is>
+      </c>
+      <c r="D110" s="27" t="inlineStr">
+        <is>
+          <t>Rule saved; an affected participant's dashboard/reports show the new bars; leaderboard/record medals follow.</t>
+        </is>
+      </c>
+      <c r="E110" s="28" t="n"/>
+      <c r="F110" s="27" t="n"/>
+      <c r="G110" s="28" t="n"/>
+    </row>
+    <row r="111" ht="42" customHeight="1">
+      <c r="A111" s="26" t="inlineStr">
+        <is>
+          <t>SA14</t>
+        </is>
+      </c>
+      <c r="B111" s="27" t="inlineStr">
+        <is>
+          <t>As a Super Admin, I want an audit log of key actions.</t>
+        </is>
+      </c>
+      <c r="C111" s="27" t="inlineStr">
+        <is>
+          <t>Do an action (create user, grant hours, edit org) → open Audit Log.</t>
+        </is>
+      </c>
+      <c r="D111" s="27" t="inlineStr">
+        <is>
+          <t>The action appears with who/when; search + action filters work.</t>
+        </is>
+      </c>
+      <c r="E111" s="28" t="n"/>
+      <c r="F111" s="27" t="n"/>
+      <c r="G111" s="28" t="n"/>
+    </row>
+    <row r="112" ht="42" customHeight="1">
+      <c r="A112" s="26" t="inlineStr">
+        <is>
+          <t>SA15</t>
+        </is>
+      </c>
+      <c r="B112" s="27" t="inlineStr">
+        <is>
+          <t>As a Super Admin, deleting a supervisor who runs events is blocked.</t>
+        </is>
+      </c>
+      <c r="C112" s="27" t="inlineStr">
+        <is>
+          <t>Try to delete a supervisor who supervises 1+ events.</t>
+        </is>
+      </c>
+      <c r="D112" s="27" t="inlineStr">
+        <is>
+          <t>Blocked with a clear message to reassign or remove their events first (events/hours preserved).</t>
+        </is>
+      </c>
+      <c r="E112" s="28" t="n"/>
+      <c r="F112" s="27" t="n"/>
+      <c r="G112" s="28" t="n"/>
+    </row>
+    <row r="113" ht="42" customHeight="1">
+      <c r="A113" s="26" t="inlineStr">
+        <is>
+          <t>SA16</t>
+        </is>
+      </c>
+      <c r="B113" s="27" t="inlineStr">
+        <is>
+          <t>As a Super Admin, I want to reassign a supervisor's events, then delete them.</t>
+        </is>
+      </c>
+      <c r="C113" s="27" t="inlineStr">
+        <is>
+          <t>Users → Reassign events → pick another supervisor → confirm; then delete the original.</t>
+        </is>
+      </c>
+      <c r="D113" s="27" t="inlineStr">
+        <is>
+          <t>Events move to the new supervisor; the original can then be deleted.</t>
+        </is>
+      </c>
+      <c r="E113" s="28" t="n"/>
+      <c r="F113" s="27" t="n"/>
+      <c r="G113" s="28" t="n"/>
+    </row>
+    <row r="114" ht="42" customHeight="1">
+      <c r="A114" s="26" t="inlineStr">
+        <is>
+          <t>SA17</t>
+        </is>
+      </c>
+      <c r="B114" s="27" t="inlineStr">
+        <is>
+          <t>As a Super Admin, creating a user pre-fills a temp password and emails an invite.</t>
+        </is>
+      </c>
+      <c r="C114" s="27" t="inlineStr">
+        <is>
+          <t>Add user; note the temp password field is pre-filled (Supervisor123!); save.</t>
+        </is>
+      </c>
+      <c r="D114" s="27" t="inlineStr">
+        <is>
+          <t>Account created; the person gets a set-password invite email.</t>
+        </is>
+      </c>
+      <c r="E114" s="28" t="n"/>
+      <c r="F114" s="27" t="n"/>
+      <c r="G114" s="28" t="n"/>
+    </row>
+    <row r="115" ht="42" customHeight="1">
+      <c r="A115" s="26" t="inlineStr">
+        <is>
+          <t>SA18</t>
+        </is>
+      </c>
+      <c r="B115" s="27" t="inlineStr">
+        <is>
+          <t>As a Super Admin, I want to assign an org when creating a user.</t>
+        </is>
+      </c>
+      <c r="C115" s="27" t="inlineStr">
+        <is>
+          <t>Add user → choose an Organization (or 'No specific organization') → save.</t>
+        </is>
+      </c>
+      <c r="D115" s="27" t="inlineStr">
+        <is>
+          <t>The user is stamped to that org (visible/manageable by that org's Admin).</t>
+        </is>
+      </c>
+      <c r="E115" s="28" t="n"/>
+      <c r="F115" s="27" t="n"/>
+      <c r="G115" s="28" t="n"/>
+    </row>
+    <row r="116" ht="20" customHeight="1">
+      <c r="A116" s="24" t="inlineStr">
+        <is>
+          <t>Cross-cutting</t>
+        </is>
+      </c>
+      <c r="B116" s="25" t="n"/>
+      <c r="C116" s="25" t="n"/>
+      <c r="D116" s="25" t="n"/>
+      <c r="E116" s="25" t="n"/>
+      <c r="F116" s="25" t="n"/>
+      <c r="G116" s="25" t="n"/>
+    </row>
+    <row r="117" ht="42" customHeight="1">
+      <c r="A117" s="26" t="inlineStr">
+        <is>
+          <t>X1</t>
+        </is>
+      </c>
+      <c r="B117" s="27" t="inlineStr">
+        <is>
+          <t>As a phone user, I want a usable mobile layout.</t>
+        </is>
+      </c>
+      <c r="C117" s="27" t="inlineStr">
+        <is>
+          <t>Open at phone width; use the menu drawer.</t>
+        </is>
+      </c>
+      <c r="D117" s="27" t="inlineStr">
+        <is>
+          <t>Layout adapts; drawer opens/closes; no horizontal scroll.</t>
+        </is>
+      </c>
+      <c r="E117" s="28" t="n"/>
+      <c r="F117" s="27" t="n"/>
+      <c r="G117" s="28" t="n"/>
+    </row>
+    <row r="118" ht="42" customHeight="1">
+      <c r="A118" s="26" t="inlineStr">
+        <is>
+          <t>X2</t>
+        </is>
+      </c>
+      <c r="B118" s="27" t="inlineStr">
+        <is>
+          <t>As a visitor, I want the recycling ribbon on the login page.</t>
+        </is>
+      </c>
+      <c r="C118" s="27" t="inlineStr">
+        <is>
+          <t>Open login signed out.</t>
+        </is>
+      </c>
+      <c r="D118" s="27" t="inlineStr">
+        <is>
+          <t>Green ribbon shows on login.</t>
+        </is>
+      </c>
+      <c r="E118" s="28" t="n"/>
+      <c r="F118" s="27" t="n"/>
+      <c r="G118" s="28" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A116:G116"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A80:G80"/>
+    <mergeCell ref="A97:G97"/>
     <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A77:G77"/>
-    <mergeCell ref="A105:G105"/>
     <mergeCell ref="A35:G35"/>
-    <mergeCell ref="A92:G92"/>
     <mergeCell ref="A57:G57"/>
     <mergeCell ref="A51:G51"/>
     <mergeCell ref="A10:G10"/>
@@ -6984,7 +7534,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E58:E76">
+  <conditionalFormatting sqref="E58:E79">
     <cfRule type="cellIs" priority="13" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -6995,7 +7545,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E78:E91">
+  <conditionalFormatting sqref="E81:E96">
     <cfRule type="cellIs" priority="16" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -7006,7 +7556,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E93:E104">
+  <conditionalFormatting sqref="E98:E115">
     <cfRule type="cellIs" priority="19" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -7017,7 +7567,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E106:E107">
+  <conditionalFormatting sqref="E117:E118">
     <cfRule type="cellIs" priority="22" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -7029,7 +7579,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E4:E9 E11:E34 E36:E50 E52:E56 E58:E76 E78:E91 E93:E104 E106:E107" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E4:E9 E11:E34 E36:E50 E52:E56 E58:E79 E81:E96 E98:E115 E117:E118" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pass,Fail,Blocked,Not tested,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7043,7 +7593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G107"/>
+  <dimension ref="A1:G118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7314,17 +7864,17 @@
       </c>
       <c r="B12" s="27" t="inlineStr">
         <is>
-          <t>As a student, I want to enter an organization code during sign-up.</t>
+          <t>As a student, a join code is required when I pick an organization.</t>
         </is>
       </c>
       <c r="C12" s="27" t="inlineStr">
         <is>
-          <t>Enter a code in the Organization code field (optional) and submit.</t>
+          <t>Choose an organization affiliation; the join-code field appears and is required.</t>
         </is>
       </c>
       <c r="D12" s="27" t="inlineStr">
         <is>
-          <t>A valid code enrolls me in that org; a bad code is rejected; blank is allowed.</t>
+          <t>Can't submit without a code; a valid code enrolls me in that org, a bad one is rejected. (Community/no-org path needs no code.)</t>
         </is>
       </c>
       <c r="E12" s="28" t="n"/>
@@ -8895,38 +9445,50 @@
       <c r="F76" s="27" t="n"/>
       <c r="G76" s="28" t="n"/>
     </row>
-    <row r="77" ht="20" customHeight="1">
-      <c r="A77" s="24" t="inlineStr">
-        <is>
-          <t>Admin (org-scoped)</t>
-        </is>
-      </c>
-      <c r="B77" s="25" t="n"/>
-      <c r="C77" s="25" t="n"/>
-      <c r="D77" s="25" t="n"/>
-      <c r="E77" s="25" t="n"/>
-      <c r="F77" s="25" t="n"/>
-      <c r="G77" s="25" t="n"/>
+    <row r="77" ht="42" customHeight="1">
+      <c r="A77" s="26" t="inlineStr">
+        <is>
+          <t>SV20</t>
+        </is>
+      </c>
+      <c r="B77" s="27" t="inlineStr">
+        <is>
+          <t>As a supervisor, I want to attach files to a message.</t>
+        </is>
+      </c>
+      <c r="C77" s="27" t="inlineStr">
+        <is>
+          <t>Roster → Message attendees → add an image/PDF (≤10 MB) → send.</t>
+        </is>
+      </c>
+      <c r="D77" s="27" t="inlineStr">
+        <is>
+          <t>The attachment uploads, appears in the dialog, and arrives with the email.</t>
+        </is>
+      </c>
+      <c r="E77" s="28" t="n"/>
+      <c r="F77" s="27" t="n"/>
+      <c r="G77" s="28" t="n"/>
     </row>
     <row r="78" ht="42" customHeight="1">
       <c r="A78" s="26" t="inlineStr">
         <is>
-          <t>AD1</t>
+          <t>SV21</t>
         </is>
       </c>
       <c r="B78" s="27" t="inlineStr">
         <is>
-          <t>As an Admin, I want the correct menu tabs.</t>
+          <t>As a supervisor, I want an email when someone signs up.</t>
         </is>
       </c>
       <c r="C78" s="27" t="inlineStr">
         <is>
-          <t>Look at the left menu.</t>
+          <t>Have a participant sign up for your event (with notifications on).</t>
         </is>
       </c>
       <c r="D78" s="27" t="inlineStr">
         <is>
-          <t>Dashboard, Pending Reviews, Reviewed History, My Events, All Opportunities, Users, Organizations, My Hours, Help.</t>
+          <t>You receive a sign-up email; toggling notifications off stops them.</t>
         </is>
       </c>
       <c r="E78" s="28" t="n"/>
@@ -8936,72 +9498,60 @@
     <row r="79" ht="42" customHeight="1">
       <c r="A79" s="26" t="inlineStr">
         <is>
-          <t>AD2</t>
+          <t>SV22</t>
         </is>
       </c>
       <c r="B79" s="27" t="inlineStr">
         <is>
-          <t>As an Admin, I can do everything a supervisor can.</t>
+          <t>As a supervisor, I want to verify who's a real member before sharing access.</t>
         </is>
       </c>
       <c r="C79" s="27" t="inlineStr">
         <is>
-          <t>Spot-check: approve an item and create an event.</t>
+          <t>Open the Roster and read the attendee badges.</t>
         </is>
       </c>
       <c r="D79" s="27" t="inlineStr">
         <is>
-          <t>Both work.</t>
+          <t>Each shows their org, or 'Community · unverified'; a warning reminds you to confirm before sharing a building QR.</t>
         </is>
       </c>
       <c r="E79" s="28" t="n"/>
       <c r="F79" s="27" t="n"/>
       <c r="G79" s="28" t="n"/>
     </row>
-    <row r="80" ht="42" customHeight="1">
-      <c r="A80" s="26" t="inlineStr">
-        <is>
-          <t>AD3</t>
-        </is>
-      </c>
-      <c r="B80" s="27" t="inlineStr">
-        <is>
-          <t>As an Admin, I only see my org's non-admin users.</t>
-        </is>
-      </c>
-      <c r="C80" s="27" t="inlineStr">
-        <is>
-          <t>Open Users.</t>
-        </is>
-      </c>
-      <c r="D80" s="27" t="inlineStr">
-        <is>
-          <t>Only participants/parents/supervisors in your org; no admins/super admins; no other orgs.</t>
-        </is>
-      </c>
-      <c r="E80" s="28" t="n"/>
-      <c r="F80" s="27" t="n"/>
-      <c r="G80" s="28" t="n"/>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="24" t="inlineStr">
+        <is>
+          <t>Admin (org-scoped)</t>
+        </is>
+      </c>
+      <c r="B80" s="25" t="n"/>
+      <c r="C80" s="25" t="n"/>
+      <c r="D80" s="25" t="n"/>
+      <c r="E80" s="25" t="n"/>
+      <c r="F80" s="25" t="n"/>
+      <c r="G80" s="25" t="n"/>
     </row>
     <row r="81" ht="42" customHeight="1">
       <c r="A81" s="26" t="inlineStr">
         <is>
-          <t>AD4</t>
+          <t>AD1</t>
         </is>
       </c>
       <c r="B81" s="27" t="inlineStr">
         <is>
-          <t>As an Admin, I want to add a supervisor.</t>
+          <t>As an Admin, I want the correct menu tabs.</t>
         </is>
       </c>
       <c r="C81" s="27" t="inlineStr">
         <is>
-          <t>Users → Add user → Supervisor → save.</t>
+          <t>Look at the left menu.</t>
         </is>
       </c>
       <c r="D81" s="27" t="inlineStr">
         <is>
-          <t>Supervisor created, stamped to your org; invite email sent.</t>
+          <t>Dashboard, Pending Reviews, Reviewed History, My Events, All Opportunities, Users, Organizations, My Hours, Help.</t>
         </is>
       </c>
       <c r="E81" s="28" t="n"/>
@@ -9011,22 +9561,22 @@
     <row r="82" ht="42" customHeight="1">
       <c r="A82" s="26" t="inlineStr">
         <is>
-          <t>AD5</t>
+          <t>AD2</t>
         </is>
       </c>
       <c r="B82" s="27" t="inlineStr">
         <is>
-          <t>As an Admin, I want to create a participant as a fallback.</t>
+          <t>As an Admin, I can do everything a supervisor can.</t>
         </is>
       </c>
       <c r="C82" s="27" t="inlineStr">
         <is>
-          <t>Users → Add user → Participant → save.</t>
+          <t>Spot-check: approve an item and create an event.</t>
         </is>
       </c>
       <c r="D82" s="27" t="inlineStr">
         <is>
-          <t>Participant created with a set-password invite (no silent password).</t>
+          <t>Both work.</t>
         </is>
       </c>
       <c r="E82" s="28" t="n"/>
@@ -9036,22 +9586,22 @@
     <row r="83" ht="42" customHeight="1">
       <c r="A83" s="26" t="inlineStr">
         <is>
-          <t>AD6</t>
+          <t>AD3</t>
         </is>
       </c>
       <c r="B83" s="27" t="inlineStr">
         <is>
-          <t>As an Admin, I want to grant participant hours.</t>
+          <t>As an Admin, I only see my org's non-admin users.</t>
         </is>
       </c>
       <c r="C83" s="27" t="inlineStr">
         <is>
-          <t>Open a participant in your org → Add hours.</t>
+          <t>Open Users.</t>
         </is>
       </c>
       <c r="D83" s="27" t="inlineStr">
         <is>
-          <t>Hours auto-approved; count toward their total/medals.</t>
+          <t>Only participants/parents/supervisors in your org; no admins/super admins; no other orgs.</t>
         </is>
       </c>
       <c r="E83" s="28" t="n"/>
@@ -9061,22 +9611,22 @@
     <row r="84" ht="42" customHeight="1">
       <c r="A84" s="26" t="inlineStr">
         <is>
-          <t>AD7</t>
+          <t>AD4</t>
         </is>
       </c>
       <c r="B84" s="27" t="inlineStr">
         <is>
-          <t>As an Admin, I want a participant's service record.</t>
+          <t>As an Admin, I want to add a supervisor.</t>
         </is>
       </c>
       <c r="C84" s="27" t="inlineStr">
         <is>
-          <t>Users → Service record for a participant in your org.</t>
+          <t>Users → Add user → Supervisor → save.</t>
         </is>
       </c>
       <c r="D84" s="27" t="inlineStr">
         <is>
-          <t>Record opens.</t>
+          <t>Supervisor created, stamped to your org; invite email sent.</t>
         </is>
       </c>
       <c r="E84" s="28" t="n"/>
@@ -9086,22 +9636,22 @@
     <row r="85" ht="42" customHeight="1">
       <c r="A85" s="26" t="inlineStr">
         <is>
-          <t>AD8</t>
+          <t>AD5</t>
         </is>
       </c>
       <c r="B85" s="27" t="inlineStr">
         <is>
-          <t>As an Admin, I want to edit/delete my org's users.</t>
+          <t>As an Admin, I want to create a participant as a fallback.</t>
         </is>
       </c>
       <c r="C85" s="27" t="inlineStr">
         <is>
-          <t>Edit a name/phone; delete a test user.</t>
+          <t>Users → Add user → Participant → save.</t>
         </is>
       </c>
       <c r="D85" s="27" t="inlineStr">
         <is>
-          <t>Changes apply within your org.</t>
+          <t>Participant created with a set-password invite (no silent password).</t>
         </is>
       </c>
       <c r="E85" s="28" t="n"/>
@@ -9111,22 +9661,22 @@
     <row r="86" ht="42" customHeight="1">
       <c r="A86" s="26" t="inlineStr">
         <is>
-          <t>AD9</t>
+          <t>AD6</t>
         </is>
       </c>
       <c r="B86" s="27" t="inlineStr">
         <is>
-          <t>As an Admin, I must NOT act on users outside my org.</t>
+          <t>As an Admin, I want to grant participant hours.</t>
         </is>
       </c>
       <c r="C86" s="27" t="inlineStr">
         <is>
-          <t>Attempt to reach another org's user (e.g. direct URL).</t>
+          <t>Open a participant in your org → Add hours.</t>
         </is>
       </c>
       <c r="D86" s="27" t="inlineStr">
         <is>
-          <t>Blocked / not visible.</t>
+          <t>Hours auto-approved; count toward their total/medals.</t>
         </is>
       </c>
       <c r="E86" s="28" t="n"/>
@@ -9136,22 +9686,22 @@
     <row r="87" ht="42" customHeight="1">
       <c r="A87" s="26" t="inlineStr">
         <is>
-          <t>AD10</t>
+          <t>AD7</t>
         </is>
       </c>
       <c r="B87" s="27" t="inlineStr">
         <is>
-          <t>As an Admin, I cannot grant Admin access or manage admins.</t>
+          <t>As an Admin, I want a participant's service record.</t>
         </is>
       </c>
       <c r="C87" s="27" t="inlineStr">
         <is>
-          <t>Look for the 'grant Admin access' action.</t>
+          <t>Users → Service record for a participant in your org.</t>
         </is>
       </c>
       <c r="D87" s="27" t="inlineStr">
         <is>
-          <t>No such button; attempts are blocked server-side.</t>
+          <t>Record opens.</t>
         </is>
       </c>
       <c r="E87" s="28" t="n"/>
@@ -9161,22 +9711,22 @@
     <row r="88" ht="42" customHeight="1">
       <c r="A88" s="26" t="inlineStr">
         <is>
-          <t>AD11</t>
+          <t>AD8</t>
         </is>
       </c>
       <c r="B88" s="27" t="inlineStr">
         <is>
-          <t>As an Admin, I see and edit only my own organization.</t>
+          <t>As an Admin, I want to edit/delete my org's users.</t>
         </is>
       </c>
       <c r="C88" s="27" t="inlineStr">
         <is>
-          <t>Open Organizations.</t>
+          <t>Edit a name/phone; delete a test user.</t>
         </is>
       </c>
       <c r="D88" s="27" t="inlineStr">
         <is>
-          <t>Only your org shows; you can edit its settings.</t>
+          <t>Changes apply within your org.</t>
         </is>
       </c>
       <c r="E88" s="28" t="n"/>
@@ -9186,22 +9736,22 @@
     <row r="89" ht="42" customHeight="1">
       <c r="A89" s="26" t="inlineStr">
         <is>
-          <t>AD12</t>
+          <t>AD9</t>
         </is>
       </c>
       <c r="B89" s="27" t="inlineStr">
         <is>
-          <t>As an Admin, I want to generate/rotate my org's join code.</t>
+          <t>As an Admin, I must NOT act on users outside my org.</t>
         </is>
       </c>
       <c r="C89" s="27" t="inlineStr">
         <is>
-          <t>Organizations → set/generate a join code → save.</t>
+          <t>Attempt to reach another org's user (e.g. direct URL).</t>
         </is>
       </c>
       <c r="D89" s="27" t="inlineStr">
         <is>
-          <t>Join code saved; usable at sign-up.</t>
+          <t>Blocked / not visible.</t>
         </is>
       </c>
       <c r="E89" s="28" t="n"/>
@@ -9211,22 +9761,22 @@
     <row r="90" ht="42" customHeight="1">
       <c r="A90" s="26" t="inlineStr">
         <is>
-          <t>AD13</t>
+          <t>AD10</t>
         </is>
       </c>
       <c r="B90" s="27" t="inlineStr">
         <is>
-          <t>As an Admin, I cannot create organizations.</t>
+          <t>As an Admin, I cannot grant Admin access or manage admins.</t>
         </is>
       </c>
       <c r="C90" s="27" t="inlineStr">
         <is>
-          <t>Look for 'Add organization'.</t>
+          <t>Look for the 'grant Admin access' action.</t>
         </is>
       </c>
       <c r="D90" s="27" t="inlineStr">
         <is>
-          <t>No Add button; creation blocked.</t>
+          <t>No such button; attempts are blocked server-side.</t>
         </is>
       </c>
       <c r="E90" s="28" t="n"/>
@@ -9236,60 +9786,72 @@
     <row r="91" ht="42" customHeight="1">
       <c r="A91" s="26" t="inlineStr">
         <is>
-          <t>AD14</t>
+          <t>AD11</t>
         </is>
       </c>
       <c r="B91" s="27" t="inlineStr">
         <is>
-          <t>As an Admin, I cannot change the recycling cans total.</t>
+          <t>As an Admin, I see and edit only my own organization.</t>
         </is>
       </c>
       <c r="C91" s="27" t="inlineStr">
         <is>
-          <t>Look for the cans/bin admin control.</t>
+          <t>Open Organizations.</t>
         </is>
       </c>
       <c r="D91" s="27" t="inlineStr">
         <is>
-          <t>Not available (Super Admin only).</t>
+          <t>Only your org shows; you can edit its settings.</t>
         </is>
       </c>
       <c r="E91" s="28" t="n"/>
       <c r="F91" s="27" t="n"/>
       <c r="G91" s="28" t="n"/>
     </row>
-    <row r="92" ht="20" customHeight="1">
-      <c r="A92" s="24" t="inlineStr">
-        <is>
-          <t>Super Admin (global)</t>
-        </is>
-      </c>
-      <c r="B92" s="25" t="n"/>
-      <c r="C92" s="25" t="n"/>
-      <c r="D92" s="25" t="n"/>
-      <c r="E92" s="25" t="n"/>
-      <c r="F92" s="25" t="n"/>
-      <c r="G92" s="25" t="n"/>
+    <row r="92" ht="42" customHeight="1">
+      <c r="A92" s="26" t="inlineStr">
+        <is>
+          <t>AD12</t>
+        </is>
+      </c>
+      <c r="B92" s="27" t="inlineStr">
+        <is>
+          <t>As an Admin, I want to generate/rotate my org's join code.</t>
+        </is>
+      </c>
+      <c r="C92" s="27" t="inlineStr">
+        <is>
+          <t>Organizations → set/generate a join code → save.</t>
+        </is>
+      </c>
+      <c r="D92" s="27" t="inlineStr">
+        <is>
+          <t>Join code saved; usable at sign-up.</t>
+        </is>
+      </c>
+      <c r="E92" s="28" t="n"/>
+      <c r="F92" s="27" t="n"/>
+      <c r="G92" s="28" t="n"/>
     </row>
     <row r="93" ht="42" customHeight="1">
       <c r="A93" s="26" t="inlineStr">
         <is>
-          <t>SA1</t>
+          <t>AD13</t>
         </is>
       </c>
       <c r="B93" s="27" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want the correct menu tabs.</t>
+          <t>As an Admin, I cannot create organizations.</t>
         </is>
       </c>
       <c r="C93" s="27" t="inlineStr">
         <is>
-          <t>Look at the left menu.</t>
+          <t>Look for 'Add organization'.</t>
         </is>
       </c>
       <c r="D93" s="27" t="inlineStr">
         <is>
-          <t>Dashboard, Reports, Users, Events, Organizations (Help in footer).</t>
+          <t>No Add button; creation blocked.</t>
         </is>
       </c>
       <c r="E93" s="28" t="n"/>
@@ -9299,22 +9861,22 @@
     <row r="94" ht="42" customHeight="1">
       <c r="A94" s="26" t="inlineStr">
         <is>
-          <t>SA2</t>
+          <t>AD14</t>
         </is>
       </c>
       <c r="B94" s="27" t="inlineStr">
         <is>
-          <t>As a Super Admin, I can do everything an Admin can, across all orgs.</t>
+          <t>As an Admin, I cannot change the recycling cans total.</t>
         </is>
       </c>
       <c r="C94" s="27" t="inlineStr">
         <is>
-          <t>Spot-check user + org actions on more than one org.</t>
+          <t>Look for the cans/bin admin control.</t>
         </is>
       </c>
       <c r="D94" s="27" t="inlineStr">
         <is>
-          <t>All allowed regardless of org.</t>
+          <t>Not available (Super Admin only).</t>
         </is>
       </c>
       <c r="E94" s="28" t="n"/>
@@ -9324,22 +9886,22 @@
     <row r="95" ht="42" customHeight="1">
       <c r="A95" s="26" t="inlineStr">
         <is>
-          <t>SA3</t>
+          <t>AD15</t>
         </is>
       </c>
       <c r="B95" s="27" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to create users incl. Supervisor and Super Admin.</t>
+          <t>As an Admin, I can turn my activity emails off.</t>
         </is>
       </c>
       <c r="C95" s="27" t="inlineStr">
         <is>
-          <t>Users → Add user → each role.</t>
+          <t>Dashboard → Email notifications toggle off; have a student sign up for your event.</t>
         </is>
       </c>
       <c r="D95" s="27" t="inlineStr">
         <is>
-          <t>Participant/Supervisor/Super Admin options available; account created + invite email.</t>
+          <t>No sign-up email arrives while off; turning it back on resumes them.</t>
         </is>
       </c>
       <c r="E95" s="28" t="n"/>
@@ -9349,72 +9911,60 @@
     <row r="96" ht="42" customHeight="1">
       <c r="A96" s="26" t="inlineStr">
         <is>
-          <t>SA4</t>
+          <t>AD16</t>
         </is>
       </c>
       <c r="B96" s="27" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to grant/revoke Admin access.</t>
+          <t>As an Admin creating a user, I choose among only my org(s).</t>
         </is>
       </c>
       <c r="C96" s="27" t="inlineStr">
         <is>
-          <t>Open a user → grant Admin access → check org(s) → save; then uncheck all → save.</t>
+          <t>Add user → Organization picker.</t>
         </is>
       </c>
       <c r="D96" s="27" t="inlineStr">
         <is>
-          <t>Checking orgs makes an Admin; unchecking all reverts to participant.</t>
+          <t>Only the org(s) I manage are listed (Super Admins see all + 'none').</t>
         </is>
       </c>
       <c r="E96" s="28" t="n"/>
       <c r="F96" s="27" t="n"/>
       <c r="G96" s="28" t="n"/>
     </row>
-    <row r="97" ht="42" customHeight="1">
-      <c r="A97" s="26" t="inlineStr">
-        <is>
-          <t>SA5</t>
-        </is>
-      </c>
-      <c r="B97" s="27" t="inlineStr">
-        <is>
-          <t>As a Super Admin, I want to create organizations + join codes.</t>
-        </is>
-      </c>
-      <c r="C97" s="27" t="inlineStr">
-        <is>
-          <t>Organizations → Add organization → set details + join code.</t>
-        </is>
-      </c>
-      <c r="D97" s="27" t="inlineStr">
-        <is>
-          <t>Org created with its join code.</t>
-        </is>
-      </c>
-      <c r="E97" s="28" t="n"/>
-      <c r="F97" s="27" t="n"/>
-      <c r="G97" s="28" t="n"/>
+    <row r="97" ht="20" customHeight="1">
+      <c r="A97" s="24" t="inlineStr">
+        <is>
+          <t>Super Admin (global)</t>
+        </is>
+      </c>
+      <c r="B97" s="25" t="n"/>
+      <c r="C97" s="25" t="n"/>
+      <c r="D97" s="25" t="n"/>
+      <c r="E97" s="25" t="n"/>
+      <c r="F97" s="25" t="n"/>
+      <c r="G97" s="25" t="n"/>
     </row>
     <row r="98" ht="42" customHeight="1">
       <c r="A98" s="26" t="inlineStr">
         <is>
-          <t>SA6</t>
+          <t>SA1</t>
         </is>
       </c>
       <c r="B98" s="27" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to find users by type.</t>
+          <t>As a Super Admin, I want the correct menu tabs.</t>
         </is>
       </c>
       <c r="C98" s="27" t="inlineStr">
         <is>
-          <t>Users → role filter pills + search.</t>
+          <t>Look at the left menu.</t>
         </is>
       </c>
       <c r="D98" s="27" t="inlineStr">
         <is>
-          <t>Filter by role with counts; search by name/email across all orgs.</t>
+          <t>Dashboard, Reports, Users, Events, Organizations (Help in footer).</t>
         </is>
       </c>
       <c r="E98" s="28" t="n"/>
@@ -9424,22 +9974,22 @@
     <row r="99" ht="42" customHeight="1">
       <c r="A99" s="26" t="inlineStr">
         <is>
-          <t>SA7</t>
+          <t>SA2</t>
         </is>
       </c>
       <c r="B99" s="27" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to search events.</t>
+          <t>As a Super Admin, I can do everything an Admin can, across all orgs.</t>
         </is>
       </c>
       <c r="C99" s="27" t="inlineStr">
         <is>
-          <t>Events → search + date range; check supervisor/org per card.</t>
+          <t>Spot-check user + org actions on more than one org.</t>
         </is>
       </c>
       <c r="D99" s="27" t="inlineStr">
         <is>
-          <t>Filters work; each event shows supervisor and organization.</t>
+          <t>All allowed regardless of org.</t>
         </is>
       </c>
       <c r="E99" s="28" t="n"/>
@@ -9449,22 +9999,22 @@
     <row r="100" ht="42" customHeight="1">
       <c r="A100" s="26" t="inlineStr">
         <is>
-          <t>SA8</t>
+          <t>SA3</t>
         </is>
       </c>
       <c r="B100" s="27" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want clear event-visibility labels.</t>
+          <t>As a Super Admin, I want to create users incl. Supervisor and Super Admin.</t>
         </is>
       </c>
       <c r="C100" s="27" t="inlineStr">
         <is>
-          <t>New Event → 'Who can see this'.</t>
+          <t>Users → Add user → each role.</t>
         </is>
       </c>
       <c r="D100" s="27" t="inlineStr">
         <is>
-          <t>'Open to all (community)' and 'Only &lt;org&gt; students' with helper text.</t>
+          <t>Participant/Supervisor/Super Admin options available; account created + invite email.</t>
         </is>
       </c>
       <c r="E100" s="28" t="n"/>
@@ -9474,22 +10024,22 @@
     <row r="101" ht="42" customHeight="1">
       <c r="A101" s="26" t="inlineStr">
         <is>
-          <t>SA9</t>
+          <t>SA4</t>
         </is>
       </c>
       <c r="B101" s="27" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want program-wide reports.</t>
+          <t>As a Super Admin, I want to grant/revoke Admin access.</t>
         </is>
       </c>
       <c r="C101" s="27" t="inlineStr">
         <is>
-          <t>Open Reports / Dashboard.</t>
+          <t>Open a user → grant Admin access → check org(s) → save; then uncheck all → save.</t>
         </is>
       </c>
       <c r="D101" s="27" t="inlineStr">
         <is>
-          <t>Totals and charts across the whole program.</t>
+          <t>Checking orgs makes an Admin; unchecking all reverts to participant.</t>
         </is>
       </c>
       <c r="E101" s="28" t="n"/>
@@ -9499,22 +10049,22 @@
     <row r="102" ht="42" customHeight="1">
       <c r="A102" s="26" t="inlineStr">
         <is>
-          <t>SA10</t>
+          <t>SA5</t>
         </is>
       </c>
       <c r="B102" s="27" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to verify email works.</t>
+          <t>As a Super Admin, I want to create organizations + join codes.</t>
         </is>
       </c>
       <c r="C102" s="27" t="inlineStr">
         <is>
-          <t>Dashboard → Send test email.</t>
+          <t>Organizations → Add organization → set details + join code.</t>
         </is>
       </c>
       <c r="D102" s="27" t="inlineStr">
         <is>
-          <t>Result shown (success or the exact failure reason).</t>
+          <t>Org created with its join code.</t>
         </is>
       </c>
       <c r="E102" s="28" t="n"/>
@@ -9524,22 +10074,22 @@
     <row r="103" ht="42" customHeight="1">
       <c r="A103" s="26" t="inlineStr">
         <is>
-          <t>SA11</t>
+          <t>SA6</t>
         </is>
       </c>
       <c r="B103" s="27" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to update the recycling cans total.</t>
+          <t>As a Super Admin, I want to find users by type.</t>
         </is>
       </c>
       <c r="C103" s="27" t="inlineStr">
         <is>
-          <t>Use the cans/bin admin control.</t>
+          <t>Users → role filter pills + search.</t>
         </is>
       </c>
       <c r="D103" s="27" t="inlineStr">
         <is>
-          <t>Total updates; the ribbon reflects it.</t>
+          <t>Filter by role with counts; search by name/email across all orgs.</t>
         </is>
       </c>
       <c r="E103" s="28" t="n"/>
@@ -9549,60 +10099,72 @@
     <row r="104" ht="42" customHeight="1">
       <c r="A104" s="26" t="inlineStr">
         <is>
-          <t>SA12</t>
+          <t>SA7</t>
         </is>
       </c>
       <c r="B104" s="27" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want hours + records for any user.</t>
+          <t>As a Super Admin, I want to search events.</t>
         </is>
       </c>
       <c r="C104" s="27" t="inlineStr">
         <is>
-          <t>Add manual hours / open service record for any participant.</t>
+          <t>Events → search + date range; check supervisor/org per card.</t>
         </is>
       </c>
       <c r="D104" s="27" t="inlineStr">
         <is>
-          <t>Works for any org.</t>
+          <t>Filters work; each event shows supervisor and organization.</t>
         </is>
       </c>
       <c r="E104" s="28" t="n"/>
       <c r="F104" s="27" t="n"/>
       <c r="G104" s="28" t="n"/>
     </row>
-    <row r="105" ht="20" customHeight="1">
-      <c r="A105" s="24" t="inlineStr">
-        <is>
-          <t>Cross-cutting</t>
-        </is>
-      </c>
-      <c r="B105" s="25" t="n"/>
-      <c r="C105" s="25" t="n"/>
-      <c r="D105" s="25" t="n"/>
-      <c r="E105" s="25" t="n"/>
-      <c r="F105" s="25" t="n"/>
-      <c r="G105" s="25" t="n"/>
+    <row r="105" ht="42" customHeight="1">
+      <c r="A105" s="26" t="inlineStr">
+        <is>
+          <t>SA8</t>
+        </is>
+      </c>
+      <c r="B105" s="27" t="inlineStr">
+        <is>
+          <t>As a Super Admin, I want clear event-visibility labels.</t>
+        </is>
+      </c>
+      <c r="C105" s="27" t="inlineStr">
+        <is>
+          <t>New Event → 'Who can see this'.</t>
+        </is>
+      </c>
+      <c r="D105" s="27" t="inlineStr">
+        <is>
+          <t>'Open to all (community)' and 'Only &lt;org&gt; students' with helper text.</t>
+        </is>
+      </c>
+      <c r="E105" s="28" t="n"/>
+      <c r="F105" s="27" t="n"/>
+      <c r="G105" s="28" t="n"/>
     </row>
     <row r="106" ht="42" customHeight="1">
       <c r="A106" s="26" t="inlineStr">
         <is>
-          <t>X1</t>
+          <t>SA9</t>
         </is>
       </c>
       <c r="B106" s="27" t="inlineStr">
         <is>
-          <t>As a phone user, I want a usable mobile layout.</t>
+          <t>As a Super Admin, I want program-wide reports.</t>
         </is>
       </c>
       <c r="C106" s="27" t="inlineStr">
         <is>
-          <t>Open at phone width; use the menu drawer.</t>
+          <t>Open Reports / Dashboard.</t>
         </is>
       </c>
       <c r="D106" s="27" t="inlineStr">
         <is>
-          <t>Layout adapts; drawer opens/closes; no horizontal scroll.</t>
+          <t>Totals and charts across the whole program.</t>
         </is>
       </c>
       <c r="E106" s="28" t="n"/>
@@ -9612,36 +10174,299 @@
     <row r="107" ht="42" customHeight="1">
       <c r="A107" s="26" t="inlineStr">
         <is>
-          <t>X2</t>
+          <t>SA10</t>
         </is>
       </c>
       <c r="B107" s="27" t="inlineStr">
         <is>
-          <t>As a visitor, I want the recycling ribbon on the login page.</t>
+          <t>As a Super Admin, I want to verify email works.</t>
         </is>
       </c>
       <c r="C107" s="27" t="inlineStr">
         <is>
-          <t>Open login signed out.</t>
+          <t>Dashboard → Send test email.</t>
         </is>
       </c>
       <c r="D107" s="27" t="inlineStr">
         <is>
-          <t>Green ribbon shows on login.</t>
+          <t>Result shown (success or the exact failure reason).</t>
         </is>
       </c>
       <c r="E107" s="28" t="n"/>
       <c r="F107" s="27" t="n"/>
       <c r="G107" s="28" t="n"/>
     </row>
+    <row r="108" ht="42" customHeight="1">
+      <c r="A108" s="26" t="inlineStr">
+        <is>
+          <t>SA11</t>
+        </is>
+      </c>
+      <c r="B108" s="27" t="inlineStr">
+        <is>
+          <t>As a Super Admin, I want to update the recycling cans total.</t>
+        </is>
+      </c>
+      <c r="C108" s="27" t="inlineStr">
+        <is>
+          <t>Use the cans/bin admin control.</t>
+        </is>
+      </c>
+      <c r="D108" s="27" t="inlineStr">
+        <is>
+          <t>Total updates; the ribbon reflects it.</t>
+        </is>
+      </c>
+      <c r="E108" s="28" t="n"/>
+      <c r="F108" s="27" t="n"/>
+      <c r="G108" s="28" t="n"/>
+    </row>
+    <row r="109" ht="42" customHeight="1">
+      <c r="A109" s="26" t="inlineStr">
+        <is>
+          <t>SA12</t>
+        </is>
+      </c>
+      <c r="B109" s="27" t="inlineStr">
+        <is>
+          <t>As a Super Admin, I want hours + records for any user.</t>
+        </is>
+      </c>
+      <c r="C109" s="27" t="inlineStr">
+        <is>
+          <t>Add manual hours / open service record for any participant.</t>
+        </is>
+      </c>
+      <c r="D109" s="27" t="inlineStr">
+        <is>
+          <t>Works for any org.</t>
+        </is>
+      </c>
+      <c r="E109" s="28" t="n"/>
+      <c r="F109" s="27" t="n"/>
+      <c r="G109" s="28" t="n"/>
+    </row>
+    <row r="110" ht="42" customHeight="1">
+      <c r="A110" s="26" t="inlineStr">
+        <is>
+          <t>SA13</t>
+        </is>
+      </c>
+      <c r="B110" s="27" t="inlineStr">
+        <is>
+          <t>As a Super Admin, I want to set award thresholds by grade band and/or org.</t>
+        </is>
+      </c>
+      <c r="C110" s="27" t="inlineStr">
+        <is>
+          <t>Award Thresholds → add a rule (e.g. Elementary 20/30/40) → save.</t>
+        </is>
+      </c>
+      <c r="D110" s="27" t="inlineStr">
+        <is>
+          <t>Rule saved; an affected participant's dashboard/reports show the new bars; leaderboard/record medals follow.</t>
+        </is>
+      </c>
+      <c r="E110" s="28" t="n"/>
+      <c r="F110" s="27" t="n"/>
+      <c r="G110" s="28" t="n"/>
+    </row>
+    <row r="111" ht="42" customHeight="1">
+      <c r="A111" s="26" t="inlineStr">
+        <is>
+          <t>SA14</t>
+        </is>
+      </c>
+      <c r="B111" s="27" t="inlineStr">
+        <is>
+          <t>As a Super Admin, I want an audit log of key actions.</t>
+        </is>
+      </c>
+      <c r="C111" s="27" t="inlineStr">
+        <is>
+          <t>Do an action (create user, grant hours, edit org) → open Audit Log.</t>
+        </is>
+      </c>
+      <c r="D111" s="27" t="inlineStr">
+        <is>
+          <t>The action appears with who/when; search + action filters work.</t>
+        </is>
+      </c>
+      <c r="E111" s="28" t="n"/>
+      <c r="F111" s="27" t="n"/>
+      <c r="G111" s="28" t="n"/>
+    </row>
+    <row r="112" ht="42" customHeight="1">
+      <c r="A112" s="26" t="inlineStr">
+        <is>
+          <t>SA15</t>
+        </is>
+      </c>
+      <c r="B112" s="27" t="inlineStr">
+        <is>
+          <t>As a Super Admin, deleting a supervisor who runs events is blocked.</t>
+        </is>
+      </c>
+      <c r="C112" s="27" t="inlineStr">
+        <is>
+          <t>Try to delete a supervisor who supervises 1+ events.</t>
+        </is>
+      </c>
+      <c r="D112" s="27" t="inlineStr">
+        <is>
+          <t>Blocked with a clear message to reassign or remove their events first (events/hours preserved).</t>
+        </is>
+      </c>
+      <c r="E112" s="28" t="n"/>
+      <c r="F112" s="27" t="n"/>
+      <c r="G112" s="28" t="n"/>
+    </row>
+    <row r="113" ht="42" customHeight="1">
+      <c r="A113" s="26" t="inlineStr">
+        <is>
+          <t>SA16</t>
+        </is>
+      </c>
+      <c r="B113" s="27" t="inlineStr">
+        <is>
+          <t>As a Super Admin, I want to reassign a supervisor's events, then delete them.</t>
+        </is>
+      </c>
+      <c r="C113" s="27" t="inlineStr">
+        <is>
+          <t>Users → Reassign events → pick another supervisor → confirm; then delete the original.</t>
+        </is>
+      </c>
+      <c r="D113" s="27" t="inlineStr">
+        <is>
+          <t>Events move to the new supervisor; the original can then be deleted.</t>
+        </is>
+      </c>
+      <c r="E113" s="28" t="n"/>
+      <c r="F113" s="27" t="n"/>
+      <c r="G113" s="28" t="n"/>
+    </row>
+    <row r="114" ht="42" customHeight="1">
+      <c r="A114" s="26" t="inlineStr">
+        <is>
+          <t>SA17</t>
+        </is>
+      </c>
+      <c r="B114" s="27" t="inlineStr">
+        <is>
+          <t>As a Super Admin, creating a user pre-fills a temp password and emails an invite.</t>
+        </is>
+      </c>
+      <c r="C114" s="27" t="inlineStr">
+        <is>
+          <t>Add user; note the temp password field is pre-filled (Supervisor123!); save.</t>
+        </is>
+      </c>
+      <c r="D114" s="27" t="inlineStr">
+        <is>
+          <t>Account created; the person gets a set-password invite email.</t>
+        </is>
+      </c>
+      <c r="E114" s="28" t="n"/>
+      <c r="F114" s="27" t="n"/>
+      <c r="G114" s="28" t="n"/>
+    </row>
+    <row r="115" ht="42" customHeight="1">
+      <c r="A115" s="26" t="inlineStr">
+        <is>
+          <t>SA18</t>
+        </is>
+      </c>
+      <c r="B115" s="27" t="inlineStr">
+        <is>
+          <t>As a Super Admin, I want to assign an org when creating a user.</t>
+        </is>
+      </c>
+      <c r="C115" s="27" t="inlineStr">
+        <is>
+          <t>Add user → choose an Organization (or 'No specific organization') → save.</t>
+        </is>
+      </c>
+      <c r="D115" s="27" t="inlineStr">
+        <is>
+          <t>The user is stamped to that org (visible/manageable by that org's Admin).</t>
+        </is>
+      </c>
+      <c r="E115" s="28" t="n"/>
+      <c r="F115" s="27" t="n"/>
+      <c r="G115" s="28" t="n"/>
+    </row>
+    <row r="116" ht="20" customHeight="1">
+      <c r="A116" s="24" t="inlineStr">
+        <is>
+          <t>Cross-cutting</t>
+        </is>
+      </c>
+      <c r="B116" s="25" t="n"/>
+      <c r="C116" s="25" t="n"/>
+      <c r="D116" s="25" t="n"/>
+      <c r="E116" s="25" t="n"/>
+      <c r="F116" s="25" t="n"/>
+      <c r="G116" s="25" t="n"/>
+    </row>
+    <row r="117" ht="42" customHeight="1">
+      <c r="A117" s="26" t="inlineStr">
+        <is>
+          <t>X1</t>
+        </is>
+      </c>
+      <c r="B117" s="27" t="inlineStr">
+        <is>
+          <t>As a phone user, I want a usable mobile layout.</t>
+        </is>
+      </c>
+      <c r="C117" s="27" t="inlineStr">
+        <is>
+          <t>Open at phone width; use the menu drawer.</t>
+        </is>
+      </c>
+      <c r="D117" s="27" t="inlineStr">
+        <is>
+          <t>Layout adapts; drawer opens/closes; no horizontal scroll.</t>
+        </is>
+      </c>
+      <c r="E117" s="28" t="n"/>
+      <c r="F117" s="27" t="n"/>
+      <c r="G117" s="28" t="n"/>
+    </row>
+    <row r="118" ht="42" customHeight="1">
+      <c r="A118" s="26" t="inlineStr">
+        <is>
+          <t>X2</t>
+        </is>
+      </c>
+      <c r="B118" s="27" t="inlineStr">
+        <is>
+          <t>As a visitor, I want the recycling ribbon on the login page.</t>
+        </is>
+      </c>
+      <c r="C118" s="27" t="inlineStr">
+        <is>
+          <t>Open login signed out.</t>
+        </is>
+      </c>
+      <c r="D118" s="27" t="inlineStr">
+        <is>
+          <t>Green ribbon shows on login.</t>
+        </is>
+      </c>
+      <c r="E118" s="28" t="n"/>
+      <c r="F118" s="27" t="n"/>
+      <c r="G118" s="28" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A116:G116"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A80:G80"/>
+    <mergeCell ref="A97:G97"/>
     <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A77:G77"/>
-    <mergeCell ref="A105:G105"/>
     <mergeCell ref="A35:G35"/>
-    <mergeCell ref="A92:G92"/>
     <mergeCell ref="A57:G57"/>
     <mergeCell ref="A51:G51"/>
     <mergeCell ref="A10:G10"/>
@@ -9690,7 +10515,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E58:E76">
+  <conditionalFormatting sqref="E58:E79">
     <cfRule type="cellIs" priority="13" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -9701,7 +10526,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E78:E91">
+  <conditionalFormatting sqref="E81:E96">
     <cfRule type="cellIs" priority="16" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -9712,7 +10537,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E93:E104">
+  <conditionalFormatting sqref="E98:E115">
     <cfRule type="cellIs" priority="19" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -9723,7 +10548,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E106:E107">
+  <conditionalFormatting sqref="E117:E118">
     <cfRule type="cellIs" priority="22" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -9735,7 +10560,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E4:E9 E11:E34 E36:E50 E52:E56 E58:E76 E78:E91 E93:E104 E106:E107" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E4:E9 E11:E34 E36:E50 E52:E56 E58:E79 E81:E96 E98:E115 E117:E118" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pass,Fail,Blocked,Not tested,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -9749,7 +10574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G107"/>
+  <dimension ref="A1:G118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10020,17 +10845,17 @@
       </c>
       <c r="B12" s="27" t="inlineStr">
         <is>
-          <t>As a student, I want to enter an organization code during sign-up.</t>
+          <t>As a student, a join code is required when I pick an organization.</t>
         </is>
       </c>
       <c r="C12" s="27" t="inlineStr">
         <is>
-          <t>Enter a code in the Organization code field (optional) and submit.</t>
+          <t>Choose an organization affiliation; the join-code field appears and is required.</t>
         </is>
       </c>
       <c r="D12" s="27" t="inlineStr">
         <is>
-          <t>A valid code enrolls me in that org; a bad code is rejected; blank is allowed.</t>
+          <t>Can't submit without a code; a valid code enrolls me in that org, a bad one is rejected. (Community/no-org path needs no code.)</t>
         </is>
       </c>
       <c r="E12" s="28" t="n"/>
@@ -11601,38 +12426,50 @@
       <c r="F76" s="27" t="n"/>
       <c r="G76" s="28" t="n"/>
     </row>
-    <row r="77" ht="20" customHeight="1">
-      <c r="A77" s="24" t="inlineStr">
-        <is>
-          <t>Admin (org-scoped)</t>
-        </is>
-      </c>
-      <c r="B77" s="25" t="n"/>
-      <c r="C77" s="25" t="n"/>
-      <c r="D77" s="25" t="n"/>
-      <c r="E77" s="25" t="n"/>
-      <c r="F77" s="25" t="n"/>
-      <c r="G77" s="25" t="n"/>
+    <row r="77" ht="42" customHeight="1">
+      <c r="A77" s="26" t="inlineStr">
+        <is>
+          <t>SV20</t>
+        </is>
+      </c>
+      <c r="B77" s="27" t="inlineStr">
+        <is>
+          <t>As a supervisor, I want to attach files to a message.</t>
+        </is>
+      </c>
+      <c r="C77" s="27" t="inlineStr">
+        <is>
+          <t>Roster → Message attendees → add an image/PDF (≤10 MB) → send.</t>
+        </is>
+      </c>
+      <c r="D77" s="27" t="inlineStr">
+        <is>
+          <t>The attachment uploads, appears in the dialog, and arrives with the email.</t>
+        </is>
+      </c>
+      <c r="E77" s="28" t="n"/>
+      <c r="F77" s="27" t="n"/>
+      <c r="G77" s="28" t="n"/>
     </row>
     <row r="78" ht="42" customHeight="1">
       <c r="A78" s="26" t="inlineStr">
         <is>
-          <t>AD1</t>
+          <t>SV21</t>
         </is>
       </c>
       <c r="B78" s="27" t="inlineStr">
         <is>
-          <t>As an Admin, I want the correct menu tabs.</t>
+          <t>As a supervisor, I want an email when someone signs up.</t>
         </is>
       </c>
       <c r="C78" s="27" t="inlineStr">
         <is>
-          <t>Look at the left menu.</t>
+          <t>Have a participant sign up for your event (with notifications on).</t>
         </is>
       </c>
       <c r="D78" s="27" t="inlineStr">
         <is>
-          <t>Dashboard, Pending Reviews, Reviewed History, My Events, All Opportunities, Users, Organizations, My Hours, Help.</t>
+          <t>You receive a sign-up email; toggling notifications off stops them.</t>
         </is>
       </c>
       <c r="E78" s="28" t="n"/>
@@ -11642,72 +12479,60 @@
     <row r="79" ht="42" customHeight="1">
       <c r="A79" s="26" t="inlineStr">
         <is>
-          <t>AD2</t>
+          <t>SV22</t>
         </is>
       </c>
       <c r="B79" s="27" t="inlineStr">
         <is>
-          <t>As an Admin, I can do everything a supervisor can.</t>
+          <t>As a supervisor, I want to verify who's a real member before sharing access.</t>
         </is>
       </c>
       <c r="C79" s="27" t="inlineStr">
         <is>
-          <t>Spot-check: approve an item and create an event.</t>
+          <t>Open the Roster and read the attendee badges.</t>
         </is>
       </c>
       <c r="D79" s="27" t="inlineStr">
         <is>
-          <t>Both work.</t>
+          <t>Each shows their org, or 'Community · unverified'; a warning reminds you to confirm before sharing a building QR.</t>
         </is>
       </c>
       <c r="E79" s="28" t="n"/>
       <c r="F79" s="27" t="n"/>
       <c r="G79" s="28" t="n"/>
     </row>
-    <row r="80" ht="42" customHeight="1">
-      <c r="A80" s="26" t="inlineStr">
-        <is>
-          <t>AD3</t>
-        </is>
-      </c>
-      <c r="B80" s="27" t="inlineStr">
-        <is>
-          <t>As an Admin, I only see my org's non-admin users.</t>
-        </is>
-      </c>
-      <c r="C80" s="27" t="inlineStr">
-        <is>
-          <t>Open Users.</t>
-        </is>
-      </c>
-      <c r="D80" s="27" t="inlineStr">
-        <is>
-          <t>Only participants/parents/supervisors in your org; no admins/super admins; no other orgs.</t>
-        </is>
-      </c>
-      <c r="E80" s="28" t="n"/>
-      <c r="F80" s="27" t="n"/>
-      <c r="G80" s="28" t="n"/>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="24" t="inlineStr">
+        <is>
+          <t>Admin (org-scoped)</t>
+        </is>
+      </c>
+      <c r="B80" s="25" t="n"/>
+      <c r="C80" s="25" t="n"/>
+      <c r="D80" s="25" t="n"/>
+      <c r="E80" s="25" t="n"/>
+      <c r="F80" s="25" t="n"/>
+      <c r="G80" s="25" t="n"/>
     </row>
     <row r="81" ht="42" customHeight="1">
       <c r="A81" s="26" t="inlineStr">
         <is>
-          <t>AD4</t>
+          <t>AD1</t>
         </is>
       </c>
       <c r="B81" s="27" t="inlineStr">
         <is>
-          <t>As an Admin, I want to add a supervisor.</t>
+          <t>As an Admin, I want the correct menu tabs.</t>
         </is>
       </c>
       <c r="C81" s="27" t="inlineStr">
         <is>
-          <t>Users → Add user → Supervisor → save.</t>
+          <t>Look at the left menu.</t>
         </is>
       </c>
       <c r="D81" s="27" t="inlineStr">
         <is>
-          <t>Supervisor created, stamped to your org; invite email sent.</t>
+          <t>Dashboard, Pending Reviews, Reviewed History, My Events, All Opportunities, Users, Organizations, My Hours, Help.</t>
         </is>
       </c>
       <c r="E81" s="28" t="n"/>
@@ -11717,22 +12542,22 @@
     <row r="82" ht="42" customHeight="1">
       <c r="A82" s="26" t="inlineStr">
         <is>
-          <t>AD5</t>
+          <t>AD2</t>
         </is>
       </c>
       <c r="B82" s="27" t="inlineStr">
         <is>
-          <t>As an Admin, I want to create a participant as a fallback.</t>
+          <t>As an Admin, I can do everything a supervisor can.</t>
         </is>
       </c>
       <c r="C82" s="27" t="inlineStr">
         <is>
-          <t>Users → Add user → Participant → save.</t>
+          <t>Spot-check: approve an item and create an event.</t>
         </is>
       </c>
       <c r="D82" s="27" t="inlineStr">
         <is>
-          <t>Participant created with a set-password invite (no silent password).</t>
+          <t>Both work.</t>
         </is>
       </c>
       <c r="E82" s="28" t="n"/>
@@ -11742,22 +12567,22 @@
     <row r="83" ht="42" customHeight="1">
       <c r="A83" s="26" t="inlineStr">
         <is>
-          <t>AD6</t>
+          <t>AD3</t>
         </is>
       </c>
       <c r="B83" s="27" t="inlineStr">
         <is>
-          <t>As an Admin, I want to grant participant hours.</t>
+          <t>As an Admin, I only see my org's non-admin users.</t>
         </is>
       </c>
       <c r="C83" s="27" t="inlineStr">
         <is>
-          <t>Open a participant in your org → Add hours.</t>
+          <t>Open Users.</t>
         </is>
       </c>
       <c r="D83" s="27" t="inlineStr">
         <is>
-          <t>Hours auto-approved; count toward their total/medals.</t>
+          <t>Only participants/parents/supervisors in your org; no admins/super admins; no other orgs.</t>
         </is>
       </c>
       <c r="E83" s="28" t="n"/>
@@ -11767,22 +12592,22 @@
     <row r="84" ht="42" customHeight="1">
       <c r="A84" s="26" t="inlineStr">
         <is>
-          <t>AD7</t>
+          <t>AD4</t>
         </is>
       </c>
       <c r="B84" s="27" t="inlineStr">
         <is>
-          <t>As an Admin, I want a participant's service record.</t>
+          <t>As an Admin, I want to add a supervisor.</t>
         </is>
       </c>
       <c r="C84" s="27" t="inlineStr">
         <is>
-          <t>Users → Service record for a participant in your org.</t>
+          <t>Users → Add user → Supervisor → save.</t>
         </is>
       </c>
       <c r="D84" s="27" t="inlineStr">
         <is>
-          <t>Record opens.</t>
+          <t>Supervisor created, stamped to your org; invite email sent.</t>
         </is>
       </c>
       <c r="E84" s="28" t="n"/>
@@ -11792,22 +12617,22 @@
     <row r="85" ht="42" customHeight="1">
       <c r="A85" s="26" t="inlineStr">
         <is>
-          <t>AD8</t>
+          <t>AD5</t>
         </is>
       </c>
       <c r="B85" s="27" t="inlineStr">
         <is>
-          <t>As an Admin, I want to edit/delete my org's users.</t>
+          <t>As an Admin, I want to create a participant as a fallback.</t>
         </is>
       </c>
       <c r="C85" s="27" t="inlineStr">
         <is>
-          <t>Edit a name/phone; delete a test user.</t>
+          <t>Users → Add user → Participant → save.</t>
         </is>
       </c>
       <c r="D85" s="27" t="inlineStr">
         <is>
-          <t>Changes apply within your org.</t>
+          <t>Participant created with a set-password invite (no silent password).</t>
         </is>
       </c>
       <c r="E85" s="28" t="n"/>
@@ -11817,22 +12642,22 @@
     <row r="86" ht="42" customHeight="1">
       <c r="A86" s="26" t="inlineStr">
         <is>
-          <t>AD9</t>
+          <t>AD6</t>
         </is>
       </c>
       <c r="B86" s="27" t="inlineStr">
         <is>
-          <t>As an Admin, I must NOT act on users outside my org.</t>
+          <t>As an Admin, I want to grant participant hours.</t>
         </is>
       </c>
       <c r="C86" s="27" t="inlineStr">
         <is>
-          <t>Attempt to reach another org's user (e.g. direct URL).</t>
+          <t>Open a participant in your org → Add hours.</t>
         </is>
       </c>
       <c r="D86" s="27" t="inlineStr">
         <is>
-          <t>Blocked / not visible.</t>
+          <t>Hours auto-approved; count toward their total/medals.</t>
         </is>
       </c>
       <c r="E86" s="28" t="n"/>
@@ -11842,22 +12667,22 @@
     <row r="87" ht="42" customHeight="1">
       <c r="A87" s="26" t="inlineStr">
         <is>
-          <t>AD10</t>
+          <t>AD7</t>
         </is>
       </c>
       <c r="B87" s="27" t="inlineStr">
         <is>
-          <t>As an Admin, I cannot grant Admin access or manage admins.</t>
+          <t>As an Admin, I want a participant's service record.</t>
         </is>
       </c>
       <c r="C87" s="27" t="inlineStr">
         <is>
-          <t>Look for the 'grant Admin access' action.</t>
+          <t>Users → Service record for a participant in your org.</t>
         </is>
       </c>
       <c r="D87" s="27" t="inlineStr">
         <is>
-          <t>No such button; attempts are blocked server-side.</t>
+          <t>Record opens.</t>
         </is>
       </c>
       <c r="E87" s="28" t="n"/>
@@ -11867,22 +12692,22 @@
     <row r="88" ht="42" customHeight="1">
       <c r="A88" s="26" t="inlineStr">
         <is>
-          <t>AD11</t>
+          <t>AD8</t>
         </is>
       </c>
       <c r="B88" s="27" t="inlineStr">
         <is>
-          <t>As an Admin, I see and edit only my own organization.</t>
+          <t>As an Admin, I want to edit/delete my org's users.</t>
         </is>
       </c>
       <c r="C88" s="27" t="inlineStr">
         <is>
-          <t>Open Organizations.</t>
+          <t>Edit a name/phone; delete a test user.</t>
         </is>
       </c>
       <c r="D88" s="27" t="inlineStr">
         <is>
-          <t>Only your org shows; you can edit its settings.</t>
+          <t>Changes apply within your org.</t>
         </is>
       </c>
       <c r="E88" s="28" t="n"/>
@@ -11892,22 +12717,22 @@
     <row r="89" ht="42" customHeight="1">
       <c r="A89" s="26" t="inlineStr">
         <is>
-          <t>AD12</t>
+          <t>AD9</t>
         </is>
       </c>
       <c r="B89" s="27" t="inlineStr">
         <is>
-          <t>As an Admin, I want to generate/rotate my org's join code.</t>
+          <t>As an Admin, I must NOT act on users outside my org.</t>
         </is>
       </c>
       <c r="C89" s="27" t="inlineStr">
         <is>
-          <t>Organizations → set/generate a join code → save.</t>
+          <t>Attempt to reach another org's user (e.g. direct URL).</t>
         </is>
       </c>
       <c r="D89" s="27" t="inlineStr">
         <is>
-          <t>Join code saved; usable at sign-up.</t>
+          <t>Blocked / not visible.</t>
         </is>
       </c>
       <c r="E89" s="28" t="n"/>
@@ -11917,22 +12742,22 @@
     <row r="90" ht="42" customHeight="1">
       <c r="A90" s="26" t="inlineStr">
         <is>
-          <t>AD13</t>
+          <t>AD10</t>
         </is>
       </c>
       <c r="B90" s="27" t="inlineStr">
         <is>
-          <t>As an Admin, I cannot create organizations.</t>
+          <t>As an Admin, I cannot grant Admin access or manage admins.</t>
         </is>
       </c>
       <c r="C90" s="27" t="inlineStr">
         <is>
-          <t>Look for 'Add organization'.</t>
+          <t>Look for the 'grant Admin access' action.</t>
         </is>
       </c>
       <c r="D90" s="27" t="inlineStr">
         <is>
-          <t>No Add button; creation blocked.</t>
+          <t>No such button; attempts are blocked server-side.</t>
         </is>
       </c>
       <c r="E90" s="28" t="n"/>
@@ -11942,60 +12767,72 @@
     <row r="91" ht="42" customHeight="1">
       <c r="A91" s="26" t="inlineStr">
         <is>
-          <t>AD14</t>
+          <t>AD11</t>
         </is>
       </c>
       <c r="B91" s="27" t="inlineStr">
         <is>
-          <t>As an Admin, I cannot change the recycling cans total.</t>
+          <t>As an Admin, I see and edit only my own organization.</t>
         </is>
       </c>
       <c r="C91" s="27" t="inlineStr">
         <is>
-          <t>Look for the cans/bin admin control.</t>
+          <t>Open Organizations.</t>
         </is>
       </c>
       <c r="D91" s="27" t="inlineStr">
         <is>
-          <t>Not available (Super Admin only).</t>
+          <t>Only your org shows; you can edit its settings.</t>
         </is>
       </c>
       <c r="E91" s="28" t="n"/>
       <c r="F91" s="27" t="n"/>
       <c r="G91" s="28" t="n"/>
     </row>
-    <row r="92" ht="20" customHeight="1">
-      <c r="A92" s="24" t="inlineStr">
-        <is>
-          <t>Super Admin (global)</t>
-        </is>
-      </c>
-      <c r="B92" s="25" t="n"/>
-      <c r="C92" s="25" t="n"/>
-      <c r="D92" s="25" t="n"/>
-      <c r="E92" s="25" t="n"/>
-      <c r="F92" s="25" t="n"/>
-      <c r="G92" s="25" t="n"/>
+    <row r="92" ht="42" customHeight="1">
+      <c r="A92" s="26" t="inlineStr">
+        <is>
+          <t>AD12</t>
+        </is>
+      </c>
+      <c r="B92" s="27" t="inlineStr">
+        <is>
+          <t>As an Admin, I want to generate/rotate my org's join code.</t>
+        </is>
+      </c>
+      <c r="C92" s="27" t="inlineStr">
+        <is>
+          <t>Organizations → set/generate a join code → save.</t>
+        </is>
+      </c>
+      <c r="D92" s="27" t="inlineStr">
+        <is>
+          <t>Join code saved; usable at sign-up.</t>
+        </is>
+      </c>
+      <c r="E92" s="28" t="n"/>
+      <c r="F92" s="27" t="n"/>
+      <c r="G92" s="28" t="n"/>
     </row>
     <row r="93" ht="42" customHeight="1">
       <c r="A93" s="26" t="inlineStr">
         <is>
-          <t>SA1</t>
+          <t>AD13</t>
         </is>
       </c>
       <c r="B93" s="27" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want the correct menu tabs.</t>
+          <t>As an Admin, I cannot create organizations.</t>
         </is>
       </c>
       <c r="C93" s="27" t="inlineStr">
         <is>
-          <t>Look at the left menu.</t>
+          <t>Look for 'Add organization'.</t>
         </is>
       </c>
       <c r="D93" s="27" t="inlineStr">
         <is>
-          <t>Dashboard, Reports, Users, Events, Organizations (Help in footer).</t>
+          <t>No Add button; creation blocked.</t>
         </is>
       </c>
       <c r="E93" s="28" t="n"/>
@@ -12005,22 +12842,22 @@
     <row r="94" ht="42" customHeight="1">
       <c r="A94" s="26" t="inlineStr">
         <is>
-          <t>SA2</t>
+          <t>AD14</t>
         </is>
       </c>
       <c r="B94" s="27" t="inlineStr">
         <is>
-          <t>As a Super Admin, I can do everything an Admin can, across all orgs.</t>
+          <t>As an Admin, I cannot change the recycling cans total.</t>
         </is>
       </c>
       <c r="C94" s="27" t="inlineStr">
         <is>
-          <t>Spot-check user + org actions on more than one org.</t>
+          <t>Look for the cans/bin admin control.</t>
         </is>
       </c>
       <c r="D94" s="27" t="inlineStr">
         <is>
-          <t>All allowed regardless of org.</t>
+          <t>Not available (Super Admin only).</t>
         </is>
       </c>
       <c r="E94" s="28" t="n"/>
@@ -12030,22 +12867,22 @@
     <row r="95" ht="42" customHeight="1">
       <c r="A95" s="26" t="inlineStr">
         <is>
-          <t>SA3</t>
+          <t>AD15</t>
         </is>
       </c>
       <c r="B95" s="27" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to create users incl. Supervisor and Super Admin.</t>
+          <t>As an Admin, I can turn my activity emails off.</t>
         </is>
       </c>
       <c r="C95" s="27" t="inlineStr">
         <is>
-          <t>Users → Add user → each role.</t>
+          <t>Dashboard → Email notifications toggle off; have a student sign up for your event.</t>
         </is>
       </c>
       <c r="D95" s="27" t="inlineStr">
         <is>
-          <t>Participant/Supervisor/Super Admin options available; account created + invite email.</t>
+          <t>No sign-up email arrives while off; turning it back on resumes them.</t>
         </is>
       </c>
       <c r="E95" s="28" t="n"/>
@@ -12055,72 +12892,60 @@
     <row r="96" ht="42" customHeight="1">
       <c r="A96" s="26" t="inlineStr">
         <is>
-          <t>SA4</t>
+          <t>AD16</t>
         </is>
       </c>
       <c r="B96" s="27" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to grant/revoke Admin access.</t>
+          <t>As an Admin creating a user, I choose among only my org(s).</t>
         </is>
       </c>
       <c r="C96" s="27" t="inlineStr">
         <is>
-          <t>Open a user → grant Admin access → check org(s) → save; then uncheck all → save.</t>
+          <t>Add user → Organization picker.</t>
         </is>
       </c>
       <c r="D96" s="27" t="inlineStr">
         <is>
-          <t>Checking orgs makes an Admin; unchecking all reverts to participant.</t>
+          <t>Only the org(s) I manage are listed (Super Admins see all + 'none').</t>
         </is>
       </c>
       <c r="E96" s="28" t="n"/>
       <c r="F96" s="27" t="n"/>
       <c r="G96" s="28" t="n"/>
     </row>
-    <row r="97" ht="42" customHeight="1">
-      <c r="A97" s="26" t="inlineStr">
-        <is>
-          <t>SA5</t>
-        </is>
-      </c>
-      <c r="B97" s="27" t="inlineStr">
-        <is>
-          <t>As a Super Admin, I want to create organizations + join codes.</t>
-        </is>
-      </c>
-      <c r="C97" s="27" t="inlineStr">
-        <is>
-          <t>Organizations → Add organization → set details + join code.</t>
-        </is>
-      </c>
-      <c r="D97" s="27" t="inlineStr">
-        <is>
-          <t>Org created with its join code.</t>
-        </is>
-      </c>
-      <c r="E97" s="28" t="n"/>
-      <c r="F97" s="27" t="n"/>
-      <c r="G97" s="28" t="n"/>
+    <row r="97" ht="20" customHeight="1">
+      <c r="A97" s="24" t="inlineStr">
+        <is>
+          <t>Super Admin (global)</t>
+        </is>
+      </c>
+      <c r="B97" s="25" t="n"/>
+      <c r="C97" s="25" t="n"/>
+      <c r="D97" s="25" t="n"/>
+      <c r="E97" s="25" t="n"/>
+      <c r="F97" s="25" t="n"/>
+      <c r="G97" s="25" t="n"/>
     </row>
     <row r="98" ht="42" customHeight="1">
       <c r="A98" s="26" t="inlineStr">
         <is>
-          <t>SA6</t>
+          <t>SA1</t>
         </is>
       </c>
       <c r="B98" s="27" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to find users by type.</t>
+          <t>As a Super Admin, I want the correct menu tabs.</t>
         </is>
       </c>
       <c r="C98" s="27" t="inlineStr">
         <is>
-          <t>Users → role filter pills + search.</t>
+          <t>Look at the left menu.</t>
         </is>
       </c>
       <c r="D98" s="27" t="inlineStr">
         <is>
-          <t>Filter by role with counts; search by name/email across all orgs.</t>
+          <t>Dashboard, Reports, Users, Events, Organizations (Help in footer).</t>
         </is>
       </c>
       <c r="E98" s="28" t="n"/>
@@ -12130,22 +12955,22 @@
     <row r="99" ht="42" customHeight="1">
       <c r="A99" s="26" t="inlineStr">
         <is>
-          <t>SA7</t>
+          <t>SA2</t>
         </is>
       </c>
       <c r="B99" s="27" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to search events.</t>
+          <t>As a Super Admin, I can do everything an Admin can, across all orgs.</t>
         </is>
       </c>
       <c r="C99" s="27" t="inlineStr">
         <is>
-          <t>Events → search + date range; check supervisor/org per card.</t>
+          <t>Spot-check user + org actions on more than one org.</t>
         </is>
       </c>
       <c r="D99" s="27" t="inlineStr">
         <is>
-          <t>Filters work; each event shows supervisor and organization.</t>
+          <t>All allowed regardless of org.</t>
         </is>
       </c>
       <c r="E99" s="28" t="n"/>
@@ -12155,22 +12980,22 @@
     <row r="100" ht="42" customHeight="1">
       <c r="A100" s="26" t="inlineStr">
         <is>
-          <t>SA8</t>
+          <t>SA3</t>
         </is>
       </c>
       <c r="B100" s="27" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want clear event-visibility labels.</t>
+          <t>As a Super Admin, I want to create users incl. Supervisor and Super Admin.</t>
         </is>
       </c>
       <c r="C100" s="27" t="inlineStr">
         <is>
-          <t>New Event → 'Who can see this'.</t>
+          <t>Users → Add user → each role.</t>
         </is>
       </c>
       <c r="D100" s="27" t="inlineStr">
         <is>
-          <t>'Open to all (community)' and 'Only &lt;org&gt; students' with helper text.</t>
+          <t>Participant/Supervisor/Super Admin options available; account created + invite email.</t>
         </is>
       </c>
       <c r="E100" s="28" t="n"/>
@@ -12180,22 +13005,22 @@
     <row r="101" ht="42" customHeight="1">
       <c r="A101" s="26" t="inlineStr">
         <is>
-          <t>SA9</t>
+          <t>SA4</t>
         </is>
       </c>
       <c r="B101" s="27" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want program-wide reports.</t>
+          <t>As a Super Admin, I want to grant/revoke Admin access.</t>
         </is>
       </c>
       <c r="C101" s="27" t="inlineStr">
         <is>
-          <t>Open Reports / Dashboard.</t>
+          <t>Open a user → grant Admin access → check org(s) → save; then uncheck all → save.</t>
         </is>
       </c>
       <c r="D101" s="27" t="inlineStr">
         <is>
-          <t>Totals and charts across the whole program.</t>
+          <t>Checking orgs makes an Admin; unchecking all reverts to participant.</t>
         </is>
       </c>
       <c r="E101" s="28" t="n"/>
@@ -12205,22 +13030,22 @@
     <row r="102" ht="42" customHeight="1">
       <c r="A102" s="26" t="inlineStr">
         <is>
-          <t>SA10</t>
+          <t>SA5</t>
         </is>
       </c>
       <c r="B102" s="27" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to verify email works.</t>
+          <t>As a Super Admin, I want to create organizations + join codes.</t>
         </is>
       </c>
       <c r="C102" s="27" t="inlineStr">
         <is>
-          <t>Dashboard → Send test email.</t>
+          <t>Organizations → Add organization → set details + join code.</t>
         </is>
       </c>
       <c r="D102" s="27" t="inlineStr">
         <is>
-          <t>Result shown (success or the exact failure reason).</t>
+          <t>Org created with its join code.</t>
         </is>
       </c>
       <c r="E102" s="28" t="n"/>
@@ -12230,22 +13055,22 @@
     <row r="103" ht="42" customHeight="1">
       <c r="A103" s="26" t="inlineStr">
         <is>
-          <t>SA11</t>
+          <t>SA6</t>
         </is>
       </c>
       <c r="B103" s="27" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to update the recycling cans total.</t>
+          <t>As a Super Admin, I want to find users by type.</t>
         </is>
       </c>
       <c r="C103" s="27" t="inlineStr">
         <is>
-          <t>Use the cans/bin admin control.</t>
+          <t>Users → role filter pills + search.</t>
         </is>
       </c>
       <c r="D103" s="27" t="inlineStr">
         <is>
-          <t>Total updates; the ribbon reflects it.</t>
+          <t>Filter by role with counts; search by name/email across all orgs.</t>
         </is>
       </c>
       <c r="E103" s="28" t="n"/>
@@ -12255,60 +13080,72 @@
     <row r="104" ht="42" customHeight="1">
       <c r="A104" s="26" t="inlineStr">
         <is>
-          <t>SA12</t>
+          <t>SA7</t>
         </is>
       </c>
       <c r="B104" s="27" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want hours + records for any user.</t>
+          <t>As a Super Admin, I want to search events.</t>
         </is>
       </c>
       <c r="C104" s="27" t="inlineStr">
         <is>
-          <t>Add manual hours / open service record for any participant.</t>
+          <t>Events → search + date range; check supervisor/org per card.</t>
         </is>
       </c>
       <c r="D104" s="27" t="inlineStr">
         <is>
-          <t>Works for any org.</t>
+          <t>Filters work; each event shows supervisor and organization.</t>
         </is>
       </c>
       <c r="E104" s="28" t="n"/>
       <c r="F104" s="27" t="n"/>
       <c r="G104" s="28" t="n"/>
     </row>
-    <row r="105" ht="20" customHeight="1">
-      <c r="A105" s="24" t="inlineStr">
-        <is>
-          <t>Cross-cutting</t>
-        </is>
-      </c>
-      <c r="B105" s="25" t="n"/>
-      <c r="C105" s="25" t="n"/>
-      <c r="D105" s="25" t="n"/>
-      <c r="E105" s="25" t="n"/>
-      <c r="F105" s="25" t="n"/>
-      <c r="G105" s="25" t="n"/>
+    <row r="105" ht="42" customHeight="1">
+      <c r="A105" s="26" t="inlineStr">
+        <is>
+          <t>SA8</t>
+        </is>
+      </c>
+      <c r="B105" s="27" t="inlineStr">
+        <is>
+          <t>As a Super Admin, I want clear event-visibility labels.</t>
+        </is>
+      </c>
+      <c r="C105" s="27" t="inlineStr">
+        <is>
+          <t>New Event → 'Who can see this'.</t>
+        </is>
+      </c>
+      <c r="D105" s="27" t="inlineStr">
+        <is>
+          <t>'Open to all (community)' and 'Only &lt;org&gt; students' with helper text.</t>
+        </is>
+      </c>
+      <c r="E105" s="28" t="n"/>
+      <c r="F105" s="27" t="n"/>
+      <c r="G105" s="28" t="n"/>
     </row>
     <row r="106" ht="42" customHeight="1">
       <c r="A106" s="26" t="inlineStr">
         <is>
-          <t>X1</t>
+          <t>SA9</t>
         </is>
       </c>
       <c r="B106" s="27" t="inlineStr">
         <is>
-          <t>As a phone user, I want a usable mobile layout.</t>
+          <t>As a Super Admin, I want program-wide reports.</t>
         </is>
       </c>
       <c r="C106" s="27" t="inlineStr">
         <is>
-          <t>Open at phone width; use the menu drawer.</t>
+          <t>Open Reports / Dashboard.</t>
         </is>
       </c>
       <c r="D106" s="27" t="inlineStr">
         <is>
-          <t>Layout adapts; drawer opens/closes; no horizontal scroll.</t>
+          <t>Totals and charts across the whole program.</t>
         </is>
       </c>
       <c r="E106" s="28" t="n"/>
@@ -12318,36 +13155,299 @@
     <row r="107" ht="42" customHeight="1">
       <c r="A107" s="26" t="inlineStr">
         <is>
-          <t>X2</t>
+          <t>SA10</t>
         </is>
       </c>
       <c r="B107" s="27" t="inlineStr">
         <is>
-          <t>As a visitor, I want the recycling ribbon on the login page.</t>
+          <t>As a Super Admin, I want to verify email works.</t>
         </is>
       </c>
       <c r="C107" s="27" t="inlineStr">
         <is>
-          <t>Open login signed out.</t>
+          <t>Dashboard → Send test email.</t>
         </is>
       </c>
       <c r="D107" s="27" t="inlineStr">
         <is>
-          <t>Green ribbon shows on login.</t>
+          <t>Result shown (success or the exact failure reason).</t>
         </is>
       </c>
       <c r="E107" s="28" t="n"/>
       <c r="F107" s="27" t="n"/>
       <c r="G107" s="28" t="n"/>
     </row>
+    <row r="108" ht="42" customHeight="1">
+      <c r="A108" s="26" t="inlineStr">
+        <is>
+          <t>SA11</t>
+        </is>
+      </c>
+      <c r="B108" s="27" t="inlineStr">
+        <is>
+          <t>As a Super Admin, I want to update the recycling cans total.</t>
+        </is>
+      </c>
+      <c r="C108" s="27" t="inlineStr">
+        <is>
+          <t>Use the cans/bin admin control.</t>
+        </is>
+      </c>
+      <c r="D108" s="27" t="inlineStr">
+        <is>
+          <t>Total updates; the ribbon reflects it.</t>
+        </is>
+      </c>
+      <c r="E108" s="28" t="n"/>
+      <c r="F108" s="27" t="n"/>
+      <c r="G108" s="28" t="n"/>
+    </row>
+    <row r="109" ht="42" customHeight="1">
+      <c r="A109" s="26" t="inlineStr">
+        <is>
+          <t>SA12</t>
+        </is>
+      </c>
+      <c r="B109" s="27" t="inlineStr">
+        <is>
+          <t>As a Super Admin, I want hours + records for any user.</t>
+        </is>
+      </c>
+      <c r="C109" s="27" t="inlineStr">
+        <is>
+          <t>Add manual hours / open service record for any participant.</t>
+        </is>
+      </c>
+      <c r="D109" s="27" t="inlineStr">
+        <is>
+          <t>Works for any org.</t>
+        </is>
+      </c>
+      <c r="E109" s="28" t="n"/>
+      <c r="F109" s="27" t="n"/>
+      <c r="G109" s="28" t="n"/>
+    </row>
+    <row r="110" ht="42" customHeight="1">
+      <c r="A110" s="26" t="inlineStr">
+        <is>
+          <t>SA13</t>
+        </is>
+      </c>
+      <c r="B110" s="27" t="inlineStr">
+        <is>
+          <t>As a Super Admin, I want to set award thresholds by grade band and/or org.</t>
+        </is>
+      </c>
+      <c r="C110" s="27" t="inlineStr">
+        <is>
+          <t>Award Thresholds → add a rule (e.g. Elementary 20/30/40) → save.</t>
+        </is>
+      </c>
+      <c r="D110" s="27" t="inlineStr">
+        <is>
+          <t>Rule saved; an affected participant's dashboard/reports show the new bars; leaderboard/record medals follow.</t>
+        </is>
+      </c>
+      <c r="E110" s="28" t="n"/>
+      <c r="F110" s="27" t="n"/>
+      <c r="G110" s="28" t="n"/>
+    </row>
+    <row r="111" ht="42" customHeight="1">
+      <c r="A111" s="26" t="inlineStr">
+        <is>
+          <t>SA14</t>
+        </is>
+      </c>
+      <c r="B111" s="27" t="inlineStr">
+        <is>
+          <t>As a Super Admin, I want an audit log of key actions.</t>
+        </is>
+      </c>
+      <c r="C111" s="27" t="inlineStr">
+        <is>
+          <t>Do an action (create user, grant hours, edit org) → open Audit Log.</t>
+        </is>
+      </c>
+      <c r="D111" s="27" t="inlineStr">
+        <is>
+          <t>The action appears with who/when; search + action filters work.</t>
+        </is>
+      </c>
+      <c r="E111" s="28" t="n"/>
+      <c r="F111" s="27" t="n"/>
+      <c r="G111" s="28" t="n"/>
+    </row>
+    <row r="112" ht="42" customHeight="1">
+      <c r="A112" s="26" t="inlineStr">
+        <is>
+          <t>SA15</t>
+        </is>
+      </c>
+      <c r="B112" s="27" t="inlineStr">
+        <is>
+          <t>As a Super Admin, deleting a supervisor who runs events is blocked.</t>
+        </is>
+      </c>
+      <c r="C112" s="27" t="inlineStr">
+        <is>
+          <t>Try to delete a supervisor who supervises 1+ events.</t>
+        </is>
+      </c>
+      <c r="D112" s="27" t="inlineStr">
+        <is>
+          <t>Blocked with a clear message to reassign or remove their events first (events/hours preserved).</t>
+        </is>
+      </c>
+      <c r="E112" s="28" t="n"/>
+      <c r="F112" s="27" t="n"/>
+      <c r="G112" s="28" t="n"/>
+    </row>
+    <row r="113" ht="42" customHeight="1">
+      <c r="A113" s="26" t="inlineStr">
+        <is>
+          <t>SA16</t>
+        </is>
+      </c>
+      <c r="B113" s="27" t="inlineStr">
+        <is>
+          <t>As a Super Admin, I want to reassign a supervisor's events, then delete them.</t>
+        </is>
+      </c>
+      <c r="C113" s="27" t="inlineStr">
+        <is>
+          <t>Users → Reassign events → pick another supervisor → confirm; then delete the original.</t>
+        </is>
+      </c>
+      <c r="D113" s="27" t="inlineStr">
+        <is>
+          <t>Events move to the new supervisor; the original can then be deleted.</t>
+        </is>
+      </c>
+      <c r="E113" s="28" t="n"/>
+      <c r="F113" s="27" t="n"/>
+      <c r="G113" s="28" t="n"/>
+    </row>
+    <row r="114" ht="42" customHeight="1">
+      <c r="A114" s="26" t="inlineStr">
+        <is>
+          <t>SA17</t>
+        </is>
+      </c>
+      <c r="B114" s="27" t="inlineStr">
+        <is>
+          <t>As a Super Admin, creating a user pre-fills a temp password and emails an invite.</t>
+        </is>
+      </c>
+      <c r="C114" s="27" t="inlineStr">
+        <is>
+          <t>Add user; note the temp password field is pre-filled (Supervisor123!); save.</t>
+        </is>
+      </c>
+      <c r="D114" s="27" t="inlineStr">
+        <is>
+          <t>Account created; the person gets a set-password invite email.</t>
+        </is>
+      </c>
+      <c r="E114" s="28" t="n"/>
+      <c r="F114" s="27" t="n"/>
+      <c r="G114" s="28" t="n"/>
+    </row>
+    <row r="115" ht="42" customHeight="1">
+      <c r="A115" s="26" t="inlineStr">
+        <is>
+          <t>SA18</t>
+        </is>
+      </c>
+      <c r="B115" s="27" t="inlineStr">
+        <is>
+          <t>As a Super Admin, I want to assign an org when creating a user.</t>
+        </is>
+      </c>
+      <c r="C115" s="27" t="inlineStr">
+        <is>
+          <t>Add user → choose an Organization (or 'No specific organization') → save.</t>
+        </is>
+      </c>
+      <c r="D115" s="27" t="inlineStr">
+        <is>
+          <t>The user is stamped to that org (visible/manageable by that org's Admin).</t>
+        </is>
+      </c>
+      <c r="E115" s="28" t="n"/>
+      <c r="F115" s="27" t="n"/>
+      <c r="G115" s="28" t="n"/>
+    </row>
+    <row r="116" ht="20" customHeight="1">
+      <c r="A116" s="24" t="inlineStr">
+        <is>
+          <t>Cross-cutting</t>
+        </is>
+      </c>
+      <c r="B116" s="25" t="n"/>
+      <c r="C116" s="25" t="n"/>
+      <c r="D116" s="25" t="n"/>
+      <c r="E116" s="25" t="n"/>
+      <c r="F116" s="25" t="n"/>
+      <c r="G116" s="25" t="n"/>
+    </row>
+    <row r="117" ht="42" customHeight="1">
+      <c r="A117" s="26" t="inlineStr">
+        <is>
+          <t>X1</t>
+        </is>
+      </c>
+      <c r="B117" s="27" t="inlineStr">
+        <is>
+          <t>As a phone user, I want a usable mobile layout.</t>
+        </is>
+      </c>
+      <c r="C117" s="27" t="inlineStr">
+        <is>
+          <t>Open at phone width; use the menu drawer.</t>
+        </is>
+      </c>
+      <c r="D117" s="27" t="inlineStr">
+        <is>
+          <t>Layout adapts; drawer opens/closes; no horizontal scroll.</t>
+        </is>
+      </c>
+      <c r="E117" s="28" t="n"/>
+      <c r="F117" s="27" t="n"/>
+      <c r="G117" s="28" t="n"/>
+    </row>
+    <row r="118" ht="42" customHeight="1">
+      <c r="A118" s="26" t="inlineStr">
+        <is>
+          <t>X2</t>
+        </is>
+      </c>
+      <c r="B118" s="27" t="inlineStr">
+        <is>
+          <t>As a visitor, I want the recycling ribbon on the login page.</t>
+        </is>
+      </c>
+      <c r="C118" s="27" t="inlineStr">
+        <is>
+          <t>Open login signed out.</t>
+        </is>
+      </c>
+      <c r="D118" s="27" t="inlineStr">
+        <is>
+          <t>Green ribbon shows on login.</t>
+        </is>
+      </c>
+      <c r="E118" s="28" t="n"/>
+      <c r="F118" s="27" t="n"/>
+      <c r="G118" s="28" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A116:G116"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A80:G80"/>
+    <mergeCell ref="A97:G97"/>
     <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A77:G77"/>
-    <mergeCell ref="A105:G105"/>
     <mergeCell ref="A35:G35"/>
-    <mergeCell ref="A92:G92"/>
     <mergeCell ref="A57:G57"/>
     <mergeCell ref="A51:G51"/>
     <mergeCell ref="A10:G10"/>
@@ -12396,7 +13496,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E58:E76">
+  <conditionalFormatting sqref="E58:E79">
     <cfRule type="cellIs" priority="13" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -12407,7 +13507,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E78:E91">
+  <conditionalFormatting sqref="E81:E96">
     <cfRule type="cellIs" priority="16" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -12418,7 +13518,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E93:E104">
+  <conditionalFormatting sqref="E98:E115">
     <cfRule type="cellIs" priority="19" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -12429,7 +13529,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E106:E107">
+  <conditionalFormatting sqref="E117:E118">
     <cfRule type="cellIs" priority="22" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -12441,7 +13541,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E4:E9 E11:E34 E36:E50 E52:E56 E58:E76 E78:E91 E93:E104 E106:E107" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E4:E9 E11:E34 E36:E50 E52:E56 E58:E79 E81:E96 E98:E115 E117:E118" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pass,Fail,Blocked,Not tested,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -12455,7 +13555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G107"/>
+  <dimension ref="A1:G118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -12726,17 +13826,17 @@
       </c>
       <c r="B12" s="27" t="inlineStr">
         <is>
-          <t>As a student, I want to enter an organization code during sign-up.</t>
+          <t>As a student, a join code is required when I pick an organization.</t>
         </is>
       </c>
       <c r="C12" s="27" t="inlineStr">
         <is>
-          <t>Enter a code in the Organization code field (optional) and submit.</t>
+          <t>Choose an organization affiliation; the join-code field appears and is required.</t>
         </is>
       </c>
       <c r="D12" s="27" t="inlineStr">
         <is>
-          <t>A valid code enrolls me in that org; a bad code is rejected; blank is allowed.</t>
+          <t>Can't submit without a code; a valid code enrolls me in that org, a bad one is rejected. (Community/no-org path needs no code.)</t>
         </is>
       </c>
       <c r="E12" s="28" t="n"/>
@@ -14307,38 +15407,50 @@
       <c r="F76" s="27" t="n"/>
       <c r="G76" s="28" t="n"/>
     </row>
-    <row r="77" ht="20" customHeight="1">
-      <c r="A77" s="24" t="inlineStr">
-        <is>
-          <t>Admin (org-scoped)</t>
-        </is>
-      </c>
-      <c r="B77" s="25" t="n"/>
-      <c r="C77" s="25" t="n"/>
-      <c r="D77" s="25" t="n"/>
-      <c r="E77" s="25" t="n"/>
-      <c r="F77" s="25" t="n"/>
-      <c r="G77" s="25" t="n"/>
+    <row r="77" ht="42" customHeight="1">
+      <c r="A77" s="26" t="inlineStr">
+        <is>
+          <t>SV20</t>
+        </is>
+      </c>
+      <c r="B77" s="27" t="inlineStr">
+        <is>
+          <t>As a supervisor, I want to attach files to a message.</t>
+        </is>
+      </c>
+      <c r="C77" s="27" t="inlineStr">
+        <is>
+          <t>Roster → Message attendees → add an image/PDF (≤10 MB) → send.</t>
+        </is>
+      </c>
+      <c r="D77" s="27" t="inlineStr">
+        <is>
+          <t>The attachment uploads, appears in the dialog, and arrives with the email.</t>
+        </is>
+      </c>
+      <c r="E77" s="28" t="n"/>
+      <c r="F77" s="27" t="n"/>
+      <c r="G77" s="28" t="n"/>
     </row>
     <row r="78" ht="42" customHeight="1">
       <c r="A78" s="26" t="inlineStr">
         <is>
-          <t>AD1</t>
+          <t>SV21</t>
         </is>
       </c>
       <c r="B78" s="27" t="inlineStr">
         <is>
-          <t>As an Admin, I want the correct menu tabs.</t>
+          <t>As a supervisor, I want an email when someone signs up.</t>
         </is>
       </c>
       <c r="C78" s="27" t="inlineStr">
         <is>
-          <t>Look at the left menu.</t>
+          <t>Have a participant sign up for your event (with notifications on).</t>
         </is>
       </c>
       <c r="D78" s="27" t="inlineStr">
         <is>
-          <t>Dashboard, Pending Reviews, Reviewed History, My Events, All Opportunities, Users, Organizations, My Hours, Help.</t>
+          <t>You receive a sign-up email; toggling notifications off stops them.</t>
         </is>
       </c>
       <c r="E78" s="28" t="n"/>
@@ -14348,72 +15460,60 @@
     <row r="79" ht="42" customHeight="1">
       <c r="A79" s="26" t="inlineStr">
         <is>
-          <t>AD2</t>
+          <t>SV22</t>
         </is>
       </c>
       <c r="B79" s="27" t="inlineStr">
         <is>
-          <t>As an Admin, I can do everything a supervisor can.</t>
+          <t>As a supervisor, I want to verify who's a real member before sharing access.</t>
         </is>
       </c>
       <c r="C79" s="27" t="inlineStr">
         <is>
-          <t>Spot-check: approve an item and create an event.</t>
+          <t>Open the Roster and read the attendee badges.</t>
         </is>
       </c>
       <c r="D79" s="27" t="inlineStr">
         <is>
-          <t>Both work.</t>
+          <t>Each shows their org, or 'Community · unverified'; a warning reminds you to confirm before sharing a building QR.</t>
         </is>
       </c>
       <c r="E79" s="28" t="n"/>
       <c r="F79" s="27" t="n"/>
       <c r="G79" s="28" t="n"/>
     </row>
-    <row r="80" ht="42" customHeight="1">
-      <c r="A80" s="26" t="inlineStr">
-        <is>
-          <t>AD3</t>
-        </is>
-      </c>
-      <c r="B80" s="27" t="inlineStr">
-        <is>
-          <t>As an Admin, I only see my org's non-admin users.</t>
-        </is>
-      </c>
-      <c r="C80" s="27" t="inlineStr">
-        <is>
-          <t>Open Users.</t>
-        </is>
-      </c>
-      <c r="D80" s="27" t="inlineStr">
-        <is>
-          <t>Only participants/parents/supervisors in your org; no admins/super admins; no other orgs.</t>
-        </is>
-      </c>
-      <c r="E80" s="28" t="n"/>
-      <c r="F80" s="27" t="n"/>
-      <c r="G80" s="28" t="n"/>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="24" t="inlineStr">
+        <is>
+          <t>Admin (org-scoped)</t>
+        </is>
+      </c>
+      <c r="B80" s="25" t="n"/>
+      <c r="C80" s="25" t="n"/>
+      <c r="D80" s="25" t="n"/>
+      <c r="E80" s="25" t="n"/>
+      <c r="F80" s="25" t="n"/>
+      <c r="G80" s="25" t="n"/>
     </row>
     <row r="81" ht="42" customHeight="1">
       <c r="A81" s="26" t="inlineStr">
         <is>
-          <t>AD4</t>
+          <t>AD1</t>
         </is>
       </c>
       <c r="B81" s="27" t="inlineStr">
         <is>
-          <t>As an Admin, I want to add a supervisor.</t>
+          <t>As an Admin, I want the correct menu tabs.</t>
         </is>
       </c>
       <c r="C81" s="27" t="inlineStr">
         <is>
-          <t>Users → Add user → Supervisor → save.</t>
+          <t>Look at the left menu.</t>
         </is>
       </c>
       <c r="D81" s="27" t="inlineStr">
         <is>
-          <t>Supervisor created, stamped to your org; invite email sent.</t>
+          <t>Dashboard, Pending Reviews, Reviewed History, My Events, All Opportunities, Users, Organizations, My Hours, Help.</t>
         </is>
       </c>
       <c r="E81" s="28" t="n"/>
@@ -14423,22 +15523,22 @@
     <row r="82" ht="42" customHeight="1">
       <c r="A82" s="26" t="inlineStr">
         <is>
-          <t>AD5</t>
+          <t>AD2</t>
         </is>
       </c>
       <c r="B82" s="27" t="inlineStr">
         <is>
-          <t>As an Admin, I want to create a participant as a fallback.</t>
+          <t>As an Admin, I can do everything a supervisor can.</t>
         </is>
       </c>
       <c r="C82" s="27" t="inlineStr">
         <is>
-          <t>Users → Add user → Participant → save.</t>
+          <t>Spot-check: approve an item and create an event.</t>
         </is>
       </c>
       <c r="D82" s="27" t="inlineStr">
         <is>
-          <t>Participant created with a set-password invite (no silent password).</t>
+          <t>Both work.</t>
         </is>
       </c>
       <c r="E82" s="28" t="n"/>
@@ -14448,22 +15548,22 @@
     <row r="83" ht="42" customHeight="1">
       <c r="A83" s="26" t="inlineStr">
         <is>
-          <t>AD6</t>
+          <t>AD3</t>
         </is>
       </c>
       <c r="B83" s="27" t="inlineStr">
         <is>
-          <t>As an Admin, I want to grant participant hours.</t>
+          <t>As an Admin, I only see my org's non-admin users.</t>
         </is>
       </c>
       <c r="C83" s="27" t="inlineStr">
         <is>
-          <t>Open a participant in your org → Add hours.</t>
+          <t>Open Users.</t>
         </is>
       </c>
       <c r="D83" s="27" t="inlineStr">
         <is>
-          <t>Hours auto-approved; count toward their total/medals.</t>
+          <t>Only participants/parents/supervisors in your org; no admins/super admins; no other orgs.</t>
         </is>
       </c>
       <c r="E83" s="28" t="n"/>
@@ -14473,22 +15573,22 @@
     <row r="84" ht="42" customHeight="1">
       <c r="A84" s="26" t="inlineStr">
         <is>
-          <t>AD7</t>
+          <t>AD4</t>
         </is>
       </c>
       <c r="B84" s="27" t="inlineStr">
         <is>
-          <t>As an Admin, I want a participant's service record.</t>
+          <t>As an Admin, I want to add a supervisor.</t>
         </is>
       </c>
       <c r="C84" s="27" t="inlineStr">
         <is>
-          <t>Users → Service record for a participant in your org.</t>
+          <t>Users → Add user → Supervisor → save.</t>
         </is>
       </c>
       <c r="D84" s="27" t="inlineStr">
         <is>
-          <t>Record opens.</t>
+          <t>Supervisor created, stamped to your org; invite email sent.</t>
         </is>
       </c>
       <c r="E84" s="28" t="n"/>
@@ -14498,22 +15598,22 @@
     <row r="85" ht="42" customHeight="1">
       <c r="A85" s="26" t="inlineStr">
         <is>
-          <t>AD8</t>
+          <t>AD5</t>
         </is>
       </c>
       <c r="B85" s="27" t="inlineStr">
         <is>
-          <t>As an Admin, I want to edit/delete my org's users.</t>
+          <t>As an Admin, I want to create a participant as a fallback.</t>
         </is>
       </c>
       <c r="C85" s="27" t="inlineStr">
         <is>
-          <t>Edit a name/phone; delete a test user.</t>
+          <t>Users → Add user → Participant → save.</t>
         </is>
       </c>
       <c r="D85" s="27" t="inlineStr">
         <is>
-          <t>Changes apply within your org.</t>
+          <t>Participant created with a set-password invite (no silent password).</t>
         </is>
       </c>
       <c r="E85" s="28" t="n"/>
@@ -14523,22 +15623,22 @@
     <row r="86" ht="42" customHeight="1">
       <c r="A86" s="26" t="inlineStr">
         <is>
-          <t>AD9</t>
+          <t>AD6</t>
         </is>
       </c>
       <c r="B86" s="27" t="inlineStr">
         <is>
-          <t>As an Admin, I must NOT act on users outside my org.</t>
+          <t>As an Admin, I want to grant participant hours.</t>
         </is>
       </c>
       <c r="C86" s="27" t="inlineStr">
         <is>
-          <t>Attempt to reach another org's user (e.g. direct URL).</t>
+          <t>Open a participant in your org → Add hours.</t>
         </is>
       </c>
       <c r="D86" s="27" t="inlineStr">
         <is>
-          <t>Blocked / not visible.</t>
+          <t>Hours auto-approved; count toward their total/medals.</t>
         </is>
       </c>
       <c r="E86" s="28" t="n"/>
@@ -14548,22 +15648,22 @@
     <row r="87" ht="42" customHeight="1">
       <c r="A87" s="26" t="inlineStr">
         <is>
-          <t>AD10</t>
+          <t>AD7</t>
         </is>
       </c>
       <c r="B87" s="27" t="inlineStr">
         <is>
-          <t>As an Admin, I cannot grant Admin access or manage admins.</t>
+          <t>As an Admin, I want a participant's service record.</t>
         </is>
       </c>
       <c r="C87" s="27" t="inlineStr">
         <is>
-          <t>Look for the 'grant Admin access' action.</t>
+          <t>Users → Service record for a participant in your org.</t>
         </is>
       </c>
       <c r="D87" s="27" t="inlineStr">
         <is>
-          <t>No such button; attempts are blocked server-side.</t>
+          <t>Record opens.</t>
         </is>
       </c>
       <c r="E87" s="28" t="n"/>
@@ -14573,22 +15673,22 @@
     <row r="88" ht="42" customHeight="1">
       <c r="A88" s="26" t="inlineStr">
         <is>
-          <t>AD11</t>
+          <t>AD8</t>
         </is>
       </c>
       <c r="B88" s="27" t="inlineStr">
         <is>
-          <t>As an Admin, I see and edit only my own organization.</t>
+          <t>As an Admin, I want to edit/delete my org's users.</t>
         </is>
       </c>
       <c r="C88" s="27" t="inlineStr">
         <is>
-          <t>Open Organizations.</t>
+          <t>Edit a name/phone; delete a test user.</t>
         </is>
       </c>
       <c r="D88" s="27" t="inlineStr">
         <is>
-          <t>Only your org shows; you can edit its settings.</t>
+          <t>Changes apply within your org.</t>
         </is>
       </c>
       <c r="E88" s="28" t="n"/>
@@ -14598,22 +15698,22 @@
     <row r="89" ht="42" customHeight="1">
       <c r="A89" s="26" t="inlineStr">
         <is>
-          <t>AD12</t>
+          <t>AD9</t>
         </is>
       </c>
       <c r="B89" s="27" t="inlineStr">
         <is>
-          <t>As an Admin, I want to generate/rotate my org's join code.</t>
+          <t>As an Admin, I must NOT act on users outside my org.</t>
         </is>
       </c>
       <c r="C89" s="27" t="inlineStr">
         <is>
-          <t>Organizations → set/generate a join code → save.</t>
+          <t>Attempt to reach another org's user (e.g. direct URL).</t>
         </is>
       </c>
       <c r="D89" s="27" t="inlineStr">
         <is>
-          <t>Join code saved; usable at sign-up.</t>
+          <t>Blocked / not visible.</t>
         </is>
       </c>
       <c r="E89" s="28" t="n"/>
@@ -14623,22 +15723,22 @@
     <row r="90" ht="42" customHeight="1">
       <c r="A90" s="26" t="inlineStr">
         <is>
-          <t>AD13</t>
+          <t>AD10</t>
         </is>
       </c>
       <c r="B90" s="27" t="inlineStr">
         <is>
-          <t>As an Admin, I cannot create organizations.</t>
+          <t>As an Admin, I cannot grant Admin access or manage admins.</t>
         </is>
       </c>
       <c r="C90" s="27" t="inlineStr">
         <is>
-          <t>Look for 'Add organization'.</t>
+          <t>Look for the 'grant Admin access' action.</t>
         </is>
       </c>
       <c r="D90" s="27" t="inlineStr">
         <is>
-          <t>No Add button; creation blocked.</t>
+          <t>No such button; attempts are blocked server-side.</t>
         </is>
       </c>
       <c r="E90" s="28" t="n"/>
@@ -14648,60 +15748,72 @@
     <row r="91" ht="42" customHeight="1">
       <c r="A91" s="26" t="inlineStr">
         <is>
-          <t>AD14</t>
+          <t>AD11</t>
         </is>
       </c>
       <c r="B91" s="27" t="inlineStr">
         <is>
-          <t>As an Admin, I cannot change the recycling cans total.</t>
+          <t>As an Admin, I see and edit only my own organization.</t>
         </is>
       </c>
       <c r="C91" s="27" t="inlineStr">
         <is>
-          <t>Look for the cans/bin admin control.</t>
+          <t>Open Organizations.</t>
         </is>
       </c>
       <c r="D91" s="27" t="inlineStr">
         <is>
-          <t>Not available (Super Admin only).</t>
+          <t>Only your org shows; you can edit its settings.</t>
         </is>
       </c>
       <c r="E91" s="28" t="n"/>
       <c r="F91" s="27" t="n"/>
       <c r="G91" s="28" t="n"/>
     </row>
-    <row r="92" ht="20" customHeight="1">
-      <c r="A92" s="24" t="inlineStr">
-        <is>
-          <t>Super Admin (global)</t>
-        </is>
-      </c>
-      <c r="B92" s="25" t="n"/>
-      <c r="C92" s="25" t="n"/>
-      <c r="D92" s="25" t="n"/>
-      <c r="E92" s="25" t="n"/>
-      <c r="F92" s="25" t="n"/>
-      <c r="G92" s="25" t="n"/>
+    <row r="92" ht="42" customHeight="1">
+      <c r="A92" s="26" t="inlineStr">
+        <is>
+          <t>AD12</t>
+        </is>
+      </c>
+      <c r="B92" s="27" t="inlineStr">
+        <is>
+          <t>As an Admin, I want to generate/rotate my org's join code.</t>
+        </is>
+      </c>
+      <c r="C92" s="27" t="inlineStr">
+        <is>
+          <t>Organizations → set/generate a join code → save.</t>
+        </is>
+      </c>
+      <c r="D92" s="27" t="inlineStr">
+        <is>
+          <t>Join code saved; usable at sign-up.</t>
+        </is>
+      </c>
+      <c r="E92" s="28" t="n"/>
+      <c r="F92" s="27" t="n"/>
+      <c r="G92" s="28" t="n"/>
     </row>
     <row r="93" ht="42" customHeight="1">
       <c r="A93" s="26" t="inlineStr">
         <is>
-          <t>SA1</t>
+          <t>AD13</t>
         </is>
       </c>
       <c r="B93" s="27" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want the correct menu tabs.</t>
+          <t>As an Admin, I cannot create organizations.</t>
         </is>
       </c>
       <c r="C93" s="27" t="inlineStr">
         <is>
-          <t>Look at the left menu.</t>
+          <t>Look for 'Add organization'.</t>
         </is>
       </c>
       <c r="D93" s="27" t="inlineStr">
         <is>
-          <t>Dashboard, Reports, Users, Events, Organizations (Help in footer).</t>
+          <t>No Add button; creation blocked.</t>
         </is>
       </c>
       <c r="E93" s="28" t="n"/>
@@ -14711,22 +15823,22 @@
     <row r="94" ht="42" customHeight="1">
       <c r="A94" s="26" t="inlineStr">
         <is>
-          <t>SA2</t>
+          <t>AD14</t>
         </is>
       </c>
       <c r="B94" s="27" t="inlineStr">
         <is>
-          <t>As a Super Admin, I can do everything an Admin can, across all orgs.</t>
+          <t>As an Admin, I cannot change the recycling cans total.</t>
         </is>
       </c>
       <c r="C94" s="27" t="inlineStr">
         <is>
-          <t>Spot-check user + org actions on more than one org.</t>
+          <t>Look for the cans/bin admin control.</t>
         </is>
       </c>
       <c r="D94" s="27" t="inlineStr">
         <is>
-          <t>All allowed regardless of org.</t>
+          <t>Not available (Super Admin only).</t>
         </is>
       </c>
       <c r="E94" s="28" t="n"/>
@@ -14736,22 +15848,22 @@
     <row r="95" ht="42" customHeight="1">
       <c r="A95" s="26" t="inlineStr">
         <is>
-          <t>SA3</t>
+          <t>AD15</t>
         </is>
       </c>
       <c r="B95" s="27" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to create users incl. Supervisor and Super Admin.</t>
+          <t>As an Admin, I can turn my activity emails off.</t>
         </is>
       </c>
       <c r="C95" s="27" t="inlineStr">
         <is>
-          <t>Users → Add user → each role.</t>
+          <t>Dashboard → Email notifications toggle off; have a student sign up for your event.</t>
         </is>
       </c>
       <c r="D95" s="27" t="inlineStr">
         <is>
-          <t>Participant/Supervisor/Super Admin options available; account created + invite email.</t>
+          <t>No sign-up email arrives while off; turning it back on resumes them.</t>
         </is>
       </c>
       <c r="E95" s="28" t="n"/>
@@ -14761,72 +15873,60 @@
     <row r="96" ht="42" customHeight="1">
       <c r="A96" s="26" t="inlineStr">
         <is>
-          <t>SA4</t>
+          <t>AD16</t>
         </is>
       </c>
       <c r="B96" s="27" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to grant/revoke Admin access.</t>
+          <t>As an Admin creating a user, I choose among only my org(s).</t>
         </is>
       </c>
       <c r="C96" s="27" t="inlineStr">
         <is>
-          <t>Open a user → grant Admin access → check org(s) → save; then uncheck all → save.</t>
+          <t>Add user → Organization picker.</t>
         </is>
       </c>
       <c r="D96" s="27" t="inlineStr">
         <is>
-          <t>Checking orgs makes an Admin; unchecking all reverts to participant.</t>
+          <t>Only the org(s) I manage are listed (Super Admins see all + 'none').</t>
         </is>
       </c>
       <c r="E96" s="28" t="n"/>
       <c r="F96" s="27" t="n"/>
       <c r="G96" s="28" t="n"/>
     </row>
-    <row r="97" ht="42" customHeight="1">
-      <c r="A97" s="26" t="inlineStr">
-        <is>
-          <t>SA5</t>
-        </is>
-      </c>
-      <c r="B97" s="27" t="inlineStr">
-        <is>
-          <t>As a Super Admin, I want to create organizations + join codes.</t>
-        </is>
-      </c>
-      <c r="C97" s="27" t="inlineStr">
-        <is>
-          <t>Organizations → Add organization → set details + join code.</t>
-        </is>
-      </c>
-      <c r="D97" s="27" t="inlineStr">
-        <is>
-          <t>Org created with its join code.</t>
-        </is>
-      </c>
-      <c r="E97" s="28" t="n"/>
-      <c r="F97" s="27" t="n"/>
-      <c r="G97" s="28" t="n"/>
+    <row r="97" ht="20" customHeight="1">
+      <c r="A97" s="24" t="inlineStr">
+        <is>
+          <t>Super Admin (global)</t>
+        </is>
+      </c>
+      <c r="B97" s="25" t="n"/>
+      <c r="C97" s="25" t="n"/>
+      <c r="D97" s="25" t="n"/>
+      <c r="E97" s="25" t="n"/>
+      <c r="F97" s="25" t="n"/>
+      <c r="G97" s="25" t="n"/>
     </row>
     <row r="98" ht="42" customHeight="1">
       <c r="A98" s="26" t="inlineStr">
         <is>
-          <t>SA6</t>
+          <t>SA1</t>
         </is>
       </c>
       <c r="B98" s="27" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to find users by type.</t>
+          <t>As a Super Admin, I want the correct menu tabs.</t>
         </is>
       </c>
       <c r="C98" s="27" t="inlineStr">
         <is>
-          <t>Users → role filter pills + search.</t>
+          <t>Look at the left menu.</t>
         </is>
       </c>
       <c r="D98" s="27" t="inlineStr">
         <is>
-          <t>Filter by role with counts; search by name/email across all orgs.</t>
+          <t>Dashboard, Reports, Users, Events, Organizations (Help in footer).</t>
         </is>
       </c>
       <c r="E98" s="28" t="n"/>
@@ -14836,22 +15936,22 @@
     <row r="99" ht="42" customHeight="1">
       <c r="A99" s="26" t="inlineStr">
         <is>
-          <t>SA7</t>
+          <t>SA2</t>
         </is>
       </c>
       <c r="B99" s="27" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to search events.</t>
+          <t>As a Super Admin, I can do everything an Admin can, across all orgs.</t>
         </is>
       </c>
       <c r="C99" s="27" t="inlineStr">
         <is>
-          <t>Events → search + date range; check supervisor/org per card.</t>
+          <t>Spot-check user + org actions on more than one org.</t>
         </is>
       </c>
       <c r="D99" s="27" t="inlineStr">
         <is>
-          <t>Filters work; each event shows supervisor and organization.</t>
+          <t>All allowed regardless of org.</t>
         </is>
       </c>
       <c r="E99" s="28" t="n"/>
@@ -14861,22 +15961,22 @@
     <row r="100" ht="42" customHeight="1">
       <c r="A100" s="26" t="inlineStr">
         <is>
-          <t>SA8</t>
+          <t>SA3</t>
         </is>
       </c>
       <c r="B100" s="27" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want clear event-visibility labels.</t>
+          <t>As a Super Admin, I want to create users incl. Supervisor and Super Admin.</t>
         </is>
       </c>
       <c r="C100" s="27" t="inlineStr">
         <is>
-          <t>New Event → 'Who can see this'.</t>
+          <t>Users → Add user → each role.</t>
         </is>
       </c>
       <c r="D100" s="27" t="inlineStr">
         <is>
-          <t>'Open to all (community)' and 'Only &lt;org&gt; students' with helper text.</t>
+          <t>Participant/Supervisor/Super Admin options available; account created + invite email.</t>
         </is>
       </c>
       <c r="E100" s="28" t="n"/>
@@ -14886,22 +15986,22 @@
     <row r="101" ht="42" customHeight="1">
       <c r="A101" s="26" t="inlineStr">
         <is>
-          <t>SA9</t>
+          <t>SA4</t>
         </is>
       </c>
       <c r="B101" s="27" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want program-wide reports.</t>
+          <t>As a Super Admin, I want to grant/revoke Admin access.</t>
         </is>
       </c>
       <c r="C101" s="27" t="inlineStr">
         <is>
-          <t>Open Reports / Dashboard.</t>
+          <t>Open a user → grant Admin access → check org(s) → save; then uncheck all → save.</t>
         </is>
       </c>
       <c r="D101" s="27" t="inlineStr">
         <is>
-          <t>Totals and charts across the whole program.</t>
+          <t>Checking orgs makes an Admin; unchecking all reverts to participant.</t>
         </is>
       </c>
       <c r="E101" s="28" t="n"/>
@@ -14911,22 +16011,22 @@
     <row r="102" ht="42" customHeight="1">
       <c r="A102" s="26" t="inlineStr">
         <is>
-          <t>SA10</t>
+          <t>SA5</t>
         </is>
       </c>
       <c r="B102" s="27" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to verify email works.</t>
+          <t>As a Super Admin, I want to create organizations + join codes.</t>
         </is>
       </c>
       <c r="C102" s="27" t="inlineStr">
         <is>
-          <t>Dashboard → Send test email.</t>
+          <t>Organizations → Add organization → set details + join code.</t>
         </is>
       </c>
       <c r="D102" s="27" t="inlineStr">
         <is>
-          <t>Result shown (success or the exact failure reason).</t>
+          <t>Org created with its join code.</t>
         </is>
       </c>
       <c r="E102" s="28" t="n"/>
@@ -14936,22 +16036,22 @@
     <row r="103" ht="42" customHeight="1">
       <c r="A103" s="26" t="inlineStr">
         <is>
-          <t>SA11</t>
+          <t>SA6</t>
         </is>
       </c>
       <c r="B103" s="27" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to update the recycling cans total.</t>
+          <t>As a Super Admin, I want to find users by type.</t>
         </is>
       </c>
       <c r="C103" s="27" t="inlineStr">
         <is>
-          <t>Use the cans/bin admin control.</t>
+          <t>Users → role filter pills + search.</t>
         </is>
       </c>
       <c r="D103" s="27" t="inlineStr">
         <is>
-          <t>Total updates; the ribbon reflects it.</t>
+          <t>Filter by role with counts; search by name/email across all orgs.</t>
         </is>
       </c>
       <c r="E103" s="28" t="n"/>
@@ -14961,60 +16061,72 @@
     <row r="104" ht="42" customHeight="1">
       <c r="A104" s="26" t="inlineStr">
         <is>
-          <t>SA12</t>
+          <t>SA7</t>
         </is>
       </c>
       <c r="B104" s="27" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want hours + records for any user.</t>
+          <t>As a Super Admin, I want to search events.</t>
         </is>
       </c>
       <c r="C104" s="27" t="inlineStr">
         <is>
-          <t>Add manual hours / open service record for any participant.</t>
+          <t>Events → search + date range; check supervisor/org per card.</t>
         </is>
       </c>
       <c r="D104" s="27" t="inlineStr">
         <is>
-          <t>Works for any org.</t>
+          <t>Filters work; each event shows supervisor and organization.</t>
         </is>
       </c>
       <c r="E104" s="28" t="n"/>
       <c r="F104" s="27" t="n"/>
       <c r="G104" s="28" t="n"/>
     </row>
-    <row r="105" ht="20" customHeight="1">
-      <c r="A105" s="24" t="inlineStr">
-        <is>
-          <t>Cross-cutting</t>
-        </is>
-      </c>
-      <c r="B105" s="25" t="n"/>
-      <c r="C105" s="25" t="n"/>
-      <c r="D105" s="25" t="n"/>
-      <c r="E105" s="25" t="n"/>
-      <c r="F105" s="25" t="n"/>
-      <c r="G105" s="25" t="n"/>
+    <row r="105" ht="42" customHeight="1">
+      <c r="A105" s="26" t="inlineStr">
+        <is>
+          <t>SA8</t>
+        </is>
+      </c>
+      <c r="B105" s="27" t="inlineStr">
+        <is>
+          <t>As a Super Admin, I want clear event-visibility labels.</t>
+        </is>
+      </c>
+      <c r="C105" s="27" t="inlineStr">
+        <is>
+          <t>New Event → 'Who can see this'.</t>
+        </is>
+      </c>
+      <c r="D105" s="27" t="inlineStr">
+        <is>
+          <t>'Open to all (community)' and 'Only &lt;org&gt; students' with helper text.</t>
+        </is>
+      </c>
+      <c r="E105" s="28" t="n"/>
+      <c r="F105" s="27" t="n"/>
+      <c r="G105" s="28" t="n"/>
     </row>
     <row r="106" ht="42" customHeight="1">
       <c r="A106" s="26" t="inlineStr">
         <is>
-          <t>X1</t>
+          <t>SA9</t>
         </is>
       </c>
       <c r="B106" s="27" t="inlineStr">
         <is>
-          <t>As a phone user, I want a usable mobile layout.</t>
+          <t>As a Super Admin, I want program-wide reports.</t>
         </is>
       </c>
       <c r="C106" s="27" t="inlineStr">
         <is>
-          <t>Open at phone width; use the menu drawer.</t>
+          <t>Open Reports / Dashboard.</t>
         </is>
       </c>
       <c r="D106" s="27" t="inlineStr">
         <is>
-          <t>Layout adapts; drawer opens/closes; no horizontal scroll.</t>
+          <t>Totals and charts across the whole program.</t>
         </is>
       </c>
       <c r="E106" s="28" t="n"/>
@@ -15024,36 +16136,299 @@
     <row r="107" ht="42" customHeight="1">
       <c r="A107" s="26" t="inlineStr">
         <is>
-          <t>X2</t>
+          <t>SA10</t>
         </is>
       </c>
       <c r="B107" s="27" t="inlineStr">
         <is>
-          <t>As a visitor, I want the recycling ribbon on the login page.</t>
+          <t>As a Super Admin, I want to verify email works.</t>
         </is>
       </c>
       <c r="C107" s="27" t="inlineStr">
         <is>
-          <t>Open login signed out.</t>
+          <t>Dashboard → Send test email.</t>
         </is>
       </c>
       <c r="D107" s="27" t="inlineStr">
         <is>
-          <t>Green ribbon shows on login.</t>
+          <t>Result shown (success or the exact failure reason).</t>
         </is>
       </c>
       <c r="E107" s="28" t="n"/>
       <c r="F107" s="27" t="n"/>
       <c r="G107" s="28" t="n"/>
     </row>
+    <row r="108" ht="42" customHeight="1">
+      <c r="A108" s="26" t="inlineStr">
+        <is>
+          <t>SA11</t>
+        </is>
+      </c>
+      <c r="B108" s="27" t="inlineStr">
+        <is>
+          <t>As a Super Admin, I want to update the recycling cans total.</t>
+        </is>
+      </c>
+      <c r="C108" s="27" t="inlineStr">
+        <is>
+          <t>Use the cans/bin admin control.</t>
+        </is>
+      </c>
+      <c r="D108" s="27" t="inlineStr">
+        <is>
+          <t>Total updates; the ribbon reflects it.</t>
+        </is>
+      </c>
+      <c r="E108" s="28" t="n"/>
+      <c r="F108" s="27" t="n"/>
+      <c r="G108" s="28" t="n"/>
+    </row>
+    <row r="109" ht="42" customHeight="1">
+      <c r="A109" s="26" t="inlineStr">
+        <is>
+          <t>SA12</t>
+        </is>
+      </c>
+      <c r="B109" s="27" t="inlineStr">
+        <is>
+          <t>As a Super Admin, I want hours + records for any user.</t>
+        </is>
+      </c>
+      <c r="C109" s="27" t="inlineStr">
+        <is>
+          <t>Add manual hours / open service record for any participant.</t>
+        </is>
+      </c>
+      <c r="D109" s="27" t="inlineStr">
+        <is>
+          <t>Works for any org.</t>
+        </is>
+      </c>
+      <c r="E109" s="28" t="n"/>
+      <c r="F109" s="27" t="n"/>
+      <c r="G109" s="28" t="n"/>
+    </row>
+    <row r="110" ht="42" customHeight="1">
+      <c r="A110" s="26" t="inlineStr">
+        <is>
+          <t>SA13</t>
+        </is>
+      </c>
+      <c r="B110" s="27" t="inlineStr">
+        <is>
+          <t>As a Super Admin, I want to set award thresholds by grade band and/or org.</t>
+        </is>
+      </c>
+      <c r="C110" s="27" t="inlineStr">
+        <is>
+          <t>Award Thresholds → add a rule (e.g. Elementary 20/30/40) → save.</t>
+        </is>
+      </c>
+      <c r="D110" s="27" t="inlineStr">
+        <is>
+          <t>Rule saved; an affected participant's dashboard/reports show the new bars; leaderboard/record medals follow.</t>
+        </is>
+      </c>
+      <c r="E110" s="28" t="n"/>
+      <c r="F110" s="27" t="n"/>
+      <c r="G110" s="28" t="n"/>
+    </row>
+    <row r="111" ht="42" customHeight="1">
+      <c r="A111" s="26" t="inlineStr">
+        <is>
+          <t>SA14</t>
+        </is>
+      </c>
+      <c r="B111" s="27" t="inlineStr">
+        <is>
+          <t>As a Super Admin, I want an audit log of key actions.</t>
+        </is>
+      </c>
+      <c r="C111" s="27" t="inlineStr">
+        <is>
+          <t>Do an action (create user, grant hours, edit org) → open Audit Log.</t>
+        </is>
+      </c>
+      <c r="D111" s="27" t="inlineStr">
+        <is>
+          <t>The action appears with who/when; search + action filters work.</t>
+        </is>
+      </c>
+      <c r="E111" s="28" t="n"/>
+      <c r="F111" s="27" t="n"/>
+      <c r="G111" s="28" t="n"/>
+    </row>
+    <row r="112" ht="42" customHeight="1">
+      <c r="A112" s="26" t="inlineStr">
+        <is>
+          <t>SA15</t>
+        </is>
+      </c>
+      <c r="B112" s="27" t="inlineStr">
+        <is>
+          <t>As a Super Admin, deleting a supervisor who runs events is blocked.</t>
+        </is>
+      </c>
+      <c r="C112" s="27" t="inlineStr">
+        <is>
+          <t>Try to delete a supervisor who supervises 1+ events.</t>
+        </is>
+      </c>
+      <c r="D112" s="27" t="inlineStr">
+        <is>
+          <t>Blocked with a clear message to reassign or remove their events first (events/hours preserved).</t>
+        </is>
+      </c>
+      <c r="E112" s="28" t="n"/>
+      <c r="F112" s="27" t="n"/>
+      <c r="G112" s="28" t="n"/>
+    </row>
+    <row r="113" ht="42" customHeight="1">
+      <c r="A113" s="26" t="inlineStr">
+        <is>
+          <t>SA16</t>
+        </is>
+      </c>
+      <c r="B113" s="27" t="inlineStr">
+        <is>
+          <t>As a Super Admin, I want to reassign a supervisor's events, then delete them.</t>
+        </is>
+      </c>
+      <c r="C113" s="27" t="inlineStr">
+        <is>
+          <t>Users → Reassign events → pick another supervisor → confirm; then delete the original.</t>
+        </is>
+      </c>
+      <c r="D113" s="27" t="inlineStr">
+        <is>
+          <t>Events move to the new supervisor; the original can then be deleted.</t>
+        </is>
+      </c>
+      <c r="E113" s="28" t="n"/>
+      <c r="F113" s="27" t="n"/>
+      <c r="G113" s="28" t="n"/>
+    </row>
+    <row r="114" ht="42" customHeight="1">
+      <c r="A114" s="26" t="inlineStr">
+        <is>
+          <t>SA17</t>
+        </is>
+      </c>
+      <c r="B114" s="27" t="inlineStr">
+        <is>
+          <t>As a Super Admin, creating a user pre-fills a temp password and emails an invite.</t>
+        </is>
+      </c>
+      <c r="C114" s="27" t="inlineStr">
+        <is>
+          <t>Add user; note the temp password field is pre-filled (Supervisor123!); save.</t>
+        </is>
+      </c>
+      <c r="D114" s="27" t="inlineStr">
+        <is>
+          <t>Account created; the person gets a set-password invite email.</t>
+        </is>
+      </c>
+      <c r="E114" s="28" t="n"/>
+      <c r="F114" s="27" t="n"/>
+      <c r="G114" s="28" t="n"/>
+    </row>
+    <row r="115" ht="42" customHeight="1">
+      <c r="A115" s="26" t="inlineStr">
+        <is>
+          <t>SA18</t>
+        </is>
+      </c>
+      <c r="B115" s="27" t="inlineStr">
+        <is>
+          <t>As a Super Admin, I want to assign an org when creating a user.</t>
+        </is>
+      </c>
+      <c r="C115" s="27" t="inlineStr">
+        <is>
+          <t>Add user → choose an Organization (or 'No specific organization') → save.</t>
+        </is>
+      </c>
+      <c r="D115" s="27" t="inlineStr">
+        <is>
+          <t>The user is stamped to that org (visible/manageable by that org's Admin).</t>
+        </is>
+      </c>
+      <c r="E115" s="28" t="n"/>
+      <c r="F115" s="27" t="n"/>
+      <c r="G115" s="28" t="n"/>
+    </row>
+    <row r="116" ht="20" customHeight="1">
+      <c r="A116" s="24" t="inlineStr">
+        <is>
+          <t>Cross-cutting</t>
+        </is>
+      </c>
+      <c r="B116" s="25" t="n"/>
+      <c r="C116" s="25" t="n"/>
+      <c r="D116" s="25" t="n"/>
+      <c r="E116" s="25" t="n"/>
+      <c r="F116" s="25" t="n"/>
+      <c r="G116" s="25" t="n"/>
+    </row>
+    <row r="117" ht="42" customHeight="1">
+      <c r="A117" s="26" t="inlineStr">
+        <is>
+          <t>X1</t>
+        </is>
+      </c>
+      <c r="B117" s="27" t="inlineStr">
+        <is>
+          <t>As a phone user, I want a usable mobile layout.</t>
+        </is>
+      </c>
+      <c r="C117" s="27" t="inlineStr">
+        <is>
+          <t>Open at phone width; use the menu drawer.</t>
+        </is>
+      </c>
+      <c r="D117" s="27" t="inlineStr">
+        <is>
+          <t>Layout adapts; drawer opens/closes; no horizontal scroll.</t>
+        </is>
+      </c>
+      <c r="E117" s="28" t="n"/>
+      <c r="F117" s="27" t="n"/>
+      <c r="G117" s="28" t="n"/>
+    </row>
+    <row r="118" ht="42" customHeight="1">
+      <c r="A118" s="26" t="inlineStr">
+        <is>
+          <t>X2</t>
+        </is>
+      </c>
+      <c r="B118" s="27" t="inlineStr">
+        <is>
+          <t>As a visitor, I want the recycling ribbon on the login page.</t>
+        </is>
+      </c>
+      <c r="C118" s="27" t="inlineStr">
+        <is>
+          <t>Open login signed out.</t>
+        </is>
+      </c>
+      <c r="D118" s="27" t="inlineStr">
+        <is>
+          <t>Green ribbon shows on login.</t>
+        </is>
+      </c>
+      <c r="E118" s="28" t="n"/>
+      <c r="F118" s="27" t="n"/>
+      <c r="G118" s="28" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A116:G116"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A80:G80"/>
+    <mergeCell ref="A97:G97"/>
     <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A77:G77"/>
-    <mergeCell ref="A105:G105"/>
     <mergeCell ref="A35:G35"/>
-    <mergeCell ref="A92:G92"/>
     <mergeCell ref="A57:G57"/>
     <mergeCell ref="A51:G51"/>
     <mergeCell ref="A10:G10"/>
@@ -15102,7 +16477,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E58:E76">
+  <conditionalFormatting sqref="E58:E79">
     <cfRule type="cellIs" priority="13" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -15113,7 +16488,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E78:E91">
+  <conditionalFormatting sqref="E81:E96">
     <cfRule type="cellIs" priority="16" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -15124,7 +16499,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E93:E104">
+  <conditionalFormatting sqref="E98:E115">
     <cfRule type="cellIs" priority="19" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -15135,7 +16510,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E106:E107">
+  <conditionalFormatting sqref="E117:E118">
     <cfRule type="cellIs" priority="22" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -15147,7 +16522,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E4:E9 E11:E34 E36:E50 E52:E56 E58:E76 E78:E91 E93:E104 E106:E107" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E4:E9 E11:E34 E36:E50 E52:E56 E58:E79 E81:E96 E98:E115 E117:E118" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pass,Fail,Blocked,Not tested,N/A"</formula1>
     </dataValidation>
   </dataValidations>

--- a/MedinaCares_Test_Plan.xlsx
+++ b/MedinaCares_Test_Plan.xlsx
@@ -2205,7 +2205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="54" min="1" max="1"/>
@@ -3098,6 +3098,1122 @@
       <c r="G35" s="64" t="n"/>
       <c r="H35" s="64" t="n"/>
     </row>
+    <row r="36" ht="42" customHeight="1" s="54">
+      <c r="A36" s="62" t="inlineStr">
+        <is>
+          <t>PT25</t>
+        </is>
+      </c>
+      <c r="B36" s="63" t="inlineStr">
+        <is>
+          <t>As a participant, when a supervisor/admin adds me to an event, I'm notified and it shows in my schedule.</t>
+        </is>
+      </c>
+      <c r="C36" s="63" t="inlineStr">
+        <is>
+          <t>Have a supervisor or Super Admin add your account email to an event → then open your dashboard/My sign-ups.</t>
+        </is>
+      </c>
+      <c r="D36" s="63" t="inlineStr">
+        <is>
+          <t>You (and your parent, if a parent email is on file) receive an 'added to &lt;event&gt;' email; the event appears in your upcoming sign-ups.</t>
+        </is>
+      </c>
+      <c r="E36" s="64" t="n"/>
+      <c r="F36" s="64" t="n"/>
+      <c r="G36" s="64" t="n"/>
+      <c r="H36" s="64" t="n"/>
+    </row>
+    <row r="37" ht="20" customHeight="1" s="54">
+      <c r="A37" s="61" t="inlineStr">
+        <is>
+          <t>Cross-cutting</t>
+        </is>
+      </c>
+      <c r="B37" s="59" t="n"/>
+      <c r="C37" s="59" t="n"/>
+      <c r="D37" s="59" t="n"/>
+      <c r="E37" s="59" t="n"/>
+      <c r="F37" s="59" t="n"/>
+      <c r="G37" s="59" t="n"/>
+      <c r="H37" s="59" t="n"/>
+    </row>
+    <row r="38" ht="42" customHeight="1" s="54">
+      <c r="A38" s="62" t="inlineStr">
+        <is>
+          <t>X1</t>
+        </is>
+      </c>
+      <c r="B38" s="63" t="inlineStr">
+        <is>
+          <t>As a phone user, I want a usable mobile layout.</t>
+        </is>
+      </c>
+      <c r="C38" s="63" t="inlineStr">
+        <is>
+          <t>Open at phone width; use the menu drawer.</t>
+        </is>
+      </c>
+      <c r="D38" s="63" t="inlineStr">
+        <is>
+          <t>Layout adapts; drawer opens/closes; no horizontal scroll.</t>
+        </is>
+      </c>
+      <c r="E38" s="64" t="n"/>
+      <c r="F38" s="64" t="n"/>
+      <c r="G38" s="64" t="n"/>
+      <c r="H38" s="64" t="n"/>
+    </row>
+    <row r="39" ht="42" customHeight="1" s="54">
+      <c r="A39" s="62" t="inlineStr">
+        <is>
+          <t>X2</t>
+        </is>
+      </c>
+      <c r="B39" s="63" t="inlineStr">
+        <is>
+          <t>As a visitor, I want the recycling ribbon on the login page.</t>
+        </is>
+      </c>
+      <c r="C39" s="63" t="inlineStr">
+        <is>
+          <t>Open login signed out.</t>
+        </is>
+      </c>
+      <c r="D39" s="63" t="inlineStr">
+        <is>
+          <t>Green ribbon shows on login.</t>
+        </is>
+      </c>
+      <c r="E39" s="64" t="n"/>
+      <c r="F39" s="64" t="n"/>
+      <c r="G39" s="64" t="n"/>
+      <c r="H39" s="64" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A37:H37"/>
+  </mergeCells>
+  <conditionalFormatting sqref="E4:E39">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="3">
+      <formula>"Pass"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="4">
+      <formula>"Fail"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="5">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4:G39">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
+      <formula>"Pass"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4">
+      <formula>"Fail"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="5">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="E4:E39 G4:G39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Pass,Fail,Blocked,Not tested,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" style="54" min="1" max="1"/>
+    <col width="56" customWidth="1" style="54" min="2" max="2"/>
+    <col width="50" customWidth="1" style="54" min="3" max="3"/>
+    <col width="50" customWidth="1" style="54" min="4" max="4"/>
+    <col width="13" customWidth="1" style="54" min="5" max="5"/>
+    <col width="30" customWidth="1" style="54" min="6" max="6"/>
+    <col width="13" customWidth="1" style="54" min="7" max="7"/>
+    <col width="30" customWidth="1" style="54" min="8" max="8"/>
+    <col width="13" customWidth="1" style="54" min="9" max="9"/>
+    <col width="30" customWidth="1" style="54" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1" s="54">
+      <c r="A1" s="56" t="inlineStr">
+        <is>
+          <t>Test cases — Parent — elementary (2–5 child)</t>
+        </is>
+      </c>
+      <c r="B1" s="57" t="n"/>
+      <c r="C1" s="57" t="n"/>
+      <c r="D1" s="57" t="n"/>
+      <c r="E1" s="57" t="n"/>
+      <c r="F1" s="57" t="n"/>
+      <c r="G1" s="57" t="n"/>
+      <c r="H1" s="57" t="n"/>
+      <c r="I1" s="57" t="n"/>
+      <c r="J1" s="57" t="n"/>
+    </row>
+    <row r="2" ht="30" customHeight="1" s="54">
+      <c r="E2" s="58" t="inlineStr">
+        <is>
+          <t>Noreen Sultana
+Platform: ?</t>
+        </is>
+      </c>
+      <c r="F2" s="59" t="n"/>
+      <c r="G2" s="58" t="inlineStr">
+        <is>
+          <t>Tester 2
+Platform: ?</t>
+        </is>
+      </c>
+      <c r="H2" s="59" t="n"/>
+      <c r="I2" s="58" t="inlineStr">
+        <is>
+          <t>Tester 3
+Platform: ?</t>
+        </is>
+      </c>
+      <c r="J2" s="59" t="n"/>
+    </row>
+    <row r="3" ht="28" customHeight="1" s="54">
+      <c r="A3" s="60" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B3" s="60" t="inlineStr">
+        <is>
+          <t>User story</t>
+        </is>
+      </c>
+      <c r="C3" s="60" t="inlineStr">
+        <is>
+          <t>Steps to perform</t>
+        </is>
+      </c>
+      <c r="D3" s="60" t="inlineStr">
+        <is>
+          <t>Expected behavior (what you should see)</t>
+        </is>
+      </c>
+      <c r="E3" s="60" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="F3" s="60" t="inlineStr">
+        <is>
+          <t>Comments</t>
+        </is>
+      </c>
+      <c r="G3" s="60" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="H3" s="60" t="inlineStr">
+        <is>
+          <t>Comments</t>
+        </is>
+      </c>
+      <c r="I3" s="60" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="J3" s="60" t="inlineStr">
+        <is>
+          <t>Comments</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1" s="54">
+      <c r="A4" s="61" t="inlineStr">
+        <is>
+          <t>Account &amp; access (all roles)</t>
+        </is>
+      </c>
+      <c r="B4" s="59" t="n"/>
+      <c r="C4" s="59" t="n"/>
+      <c r="D4" s="59" t="n"/>
+      <c r="E4" s="59" t="n"/>
+      <c r="F4" s="59" t="n"/>
+      <c r="G4" s="59" t="n"/>
+      <c r="H4" s="59" t="n"/>
+      <c r="I4" s="59" t="n"/>
+      <c r="J4" s="59" t="n"/>
+    </row>
+    <row r="5" ht="42" customHeight="1" s="54">
+      <c r="A5" s="62" t="inlineStr">
+        <is>
+          <t>AC1</t>
+        </is>
+      </c>
+      <c r="B5" s="63" t="inlineStr">
+        <is>
+          <t>As any user, I want to log in with email and password.</t>
+        </is>
+      </c>
+      <c r="C5" s="63" t="inlineStr">
+        <is>
+          <t>Enter valid email/password and Sign in.</t>
+        </is>
+      </c>
+      <c r="D5" s="63" t="inlineStr">
+        <is>
+          <t>You're signed in and taken to your role's home.</t>
+        </is>
+      </c>
+      <c r="E5" s="64" t="n"/>
+      <c r="F5" s="64" t="n"/>
+      <c r="G5" s="64" t="n"/>
+      <c r="H5" s="64" t="n"/>
+      <c r="I5" s="64" t="n"/>
+      <c r="J5" s="64" t="n"/>
+    </row>
+    <row r="6" ht="42" customHeight="1" s="54">
+      <c r="A6" s="62" t="inlineStr">
+        <is>
+          <t>AC2</t>
+        </is>
+      </c>
+      <c r="B6" s="63" t="inlineStr">
+        <is>
+          <t>As any user, I want to reveal my password while typing.</t>
+        </is>
+      </c>
+      <c r="C6" s="63" t="inlineStr">
+        <is>
+          <t>Tap the eye icon in the password field.</t>
+        </is>
+      </c>
+      <c r="D6" s="63" t="inlineStr">
+        <is>
+          <t>Password text toggles visible/hidden.</t>
+        </is>
+      </c>
+      <c r="E6" s="64" t="n"/>
+      <c r="F6" s="64" t="n"/>
+      <c r="G6" s="64" t="n"/>
+      <c r="H6" s="64" t="n"/>
+      <c r="I6" s="64" t="n"/>
+      <c r="J6" s="64" t="n"/>
+    </row>
+    <row r="7" ht="42" customHeight="1" s="54">
+      <c r="A7" s="62" t="inlineStr">
+        <is>
+          <t>AC3</t>
+        </is>
+      </c>
+      <c r="B7" s="63" t="inlineStr">
+        <is>
+          <t>As any user, I want to reset a forgotten password by email.</t>
+        </is>
+      </c>
+      <c r="C7" s="63" t="inlineStr">
+        <is>
+          <t>Forgot password → enter email → open email → follow link → set new password → sign in.</t>
+        </is>
+      </c>
+      <c r="D7" s="63" t="inlineStr">
+        <is>
+          <t>Reset email arrives; link works; new password signs in; old one fails.</t>
+        </is>
+      </c>
+      <c r="E7" s="64" t="n"/>
+      <c r="F7" s="64" t="n"/>
+      <c r="G7" s="64" t="n"/>
+      <c r="H7" s="64" t="n"/>
+      <c r="I7" s="64" t="n"/>
+      <c r="J7" s="64" t="n"/>
+    </row>
+    <row r="8" ht="42" customHeight="1" s="54">
+      <c r="A8" s="62" t="inlineStr">
+        <is>
+          <t>AC4</t>
+        </is>
+      </c>
+      <c r="B8" s="63" t="inlineStr">
+        <is>
+          <t>As any user, I want to sign out.</t>
+        </is>
+      </c>
+      <c r="C8" s="63" t="inlineStr">
+        <is>
+          <t>Use Sign out.</t>
+        </is>
+      </c>
+      <c r="D8" s="63" t="inlineStr">
+        <is>
+          <t>Logged out; returned to login/landing.</t>
+        </is>
+      </c>
+      <c r="E8" s="64" t="n"/>
+      <c r="F8" s="64" t="n"/>
+      <c r="G8" s="64" t="n"/>
+      <c r="H8" s="64" t="n"/>
+      <c r="I8" s="64" t="n"/>
+      <c r="J8" s="64" t="n"/>
+    </row>
+    <row r="9" ht="42" customHeight="1" s="54">
+      <c r="A9" s="62" t="inlineStr">
+        <is>
+          <t>AC5</t>
+        </is>
+      </c>
+      <c r="B9" s="63" t="inlineStr">
+        <is>
+          <t>As any user, I want a clear error for bad credentials.</t>
+        </is>
+      </c>
+      <c r="C9" s="63" t="inlineStr">
+        <is>
+          <t>Enter a wrong password.</t>
+        </is>
+      </c>
+      <c r="D9" s="63" t="inlineStr">
+        <is>
+          <t>Clear 'login failed' message; stay on login.</t>
+        </is>
+      </c>
+      <c r="E9" s="64" t="n"/>
+      <c r="F9" s="64" t="n"/>
+      <c r="G9" s="64" t="n"/>
+      <c r="H9" s="64" t="n"/>
+      <c r="I9" s="64" t="n"/>
+      <c r="J9" s="64" t="n"/>
+    </row>
+    <row r="10" ht="42" customHeight="1" s="54">
+      <c r="A10" s="62" t="inlineStr">
+        <is>
+          <t>AC6</t>
+        </is>
+      </c>
+      <c r="B10" s="63" t="inlineStr">
+        <is>
+          <t>As any user, my session persists and protected pages are guarded.</t>
+        </is>
+      </c>
+      <c r="C10" s="63" t="inlineStr">
+        <is>
+          <t>Sign in, refresh; then sign out and open a protected URL directly.</t>
+        </is>
+      </c>
+      <c r="D10" s="63" t="inlineStr">
+        <is>
+          <t>Refresh stays signed in; protected pages redirect to login when signed out.</t>
+        </is>
+      </c>
+      <c r="E10" s="64" t="n"/>
+      <c r="F10" s="64" t="n"/>
+      <c r="G10" s="64" t="n"/>
+      <c r="H10" s="64" t="n"/>
+      <c r="I10" s="64" t="n"/>
+      <c r="J10" s="64" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1" s="54">
+      <c r="A11" s="61" t="inlineStr">
+        <is>
+          <t>Parent — elementary (grades 2–5 child)</t>
+        </is>
+      </c>
+      <c r="B11" s="59" t="n"/>
+      <c r="C11" s="59" t="n"/>
+      <c r="D11" s="59" t="n"/>
+      <c r="E11" s="59" t="n"/>
+      <c r="F11" s="59" t="n"/>
+      <c r="G11" s="59" t="n"/>
+      <c r="H11" s="59" t="n"/>
+      <c r="I11" s="59" t="n"/>
+      <c r="J11" s="59" t="n"/>
+    </row>
+    <row r="12" ht="42" customHeight="1" s="54">
+      <c r="A12" s="62" t="inlineStr">
+        <is>
+          <t>PE1</t>
+        </is>
+      </c>
+      <c r="B12" s="63" t="inlineStr">
+        <is>
+          <t>As a parent, I want to register to manage my grade 2–5 child.</t>
+        </is>
+      </c>
+      <c r="C12" s="63" t="inlineStr">
+        <is>
+          <t>Create account → parent of a 2–5 child.</t>
+        </is>
+      </c>
+      <c r="D12" s="63" t="inlineStr">
+        <is>
+          <t>Parent account created.</t>
+        </is>
+      </c>
+      <c r="E12" s="64" t="n"/>
+      <c r="F12" s="64" t="n"/>
+      <c r="G12" s="64" t="n"/>
+      <c r="H12" s="64" t="n"/>
+      <c r="I12" s="64" t="n"/>
+      <c r="J12" s="64" t="n"/>
+    </row>
+    <row r="13" ht="42" customHeight="1" s="54">
+      <c r="A13" s="62" t="inlineStr">
+        <is>
+          <t>PE2</t>
+        </is>
+      </c>
+      <c r="B13" s="63" t="inlineStr">
+        <is>
+          <t>As an elementary parent, I want the right menu tabs.</t>
+        </is>
+      </c>
+      <c r="C13" s="63" t="inlineStr">
+        <is>
+          <t>Look at the left menu.</t>
+        </is>
+      </c>
+      <c r="D13" s="63" t="inlineStr">
+        <is>
+          <t>Dashboard and Find Opportunities (Help in footer).</t>
+        </is>
+      </c>
+      <c r="E13" s="64" t="n"/>
+      <c r="F13" s="64" t="n"/>
+      <c r="G13" s="64" t="n"/>
+      <c r="H13" s="64" t="n"/>
+      <c r="I13" s="64" t="n"/>
+      <c r="J13" s="64" t="n"/>
+    </row>
+    <row r="14" ht="42" customHeight="1" s="54">
+      <c r="A14" s="62" t="inlineStr">
+        <is>
+          <t>PE3</t>
+        </is>
+      </c>
+      <c r="B14" s="63" t="inlineStr">
+        <is>
+          <t>As a parent, I want to add a managed child (2–5).</t>
+        </is>
+      </c>
+      <c r="C14" s="63" t="inlineStr">
+        <is>
+          <t>Add child with name and grade (join code if required).</t>
+        </is>
+      </c>
+      <c r="D14" s="63" t="inlineStr">
+        <is>
+          <t>Child added; no separate login.</t>
+        </is>
+      </c>
+      <c r="E14" s="64" t="n"/>
+      <c r="F14" s="64" t="n"/>
+      <c r="G14" s="64" t="n"/>
+      <c r="H14" s="64" t="n"/>
+      <c r="I14" s="64" t="n"/>
+      <c r="J14" s="64" t="n"/>
+    </row>
+    <row r="15" ht="42" customHeight="1" s="54">
+      <c r="A15" s="62" t="inlineStr">
+        <is>
+          <t>PE4</t>
+        </is>
+      </c>
+      <c r="B15" s="63" t="inlineStr">
+        <is>
+          <t>As a parent with several kids, I want to switch child.</t>
+        </is>
+      </c>
+      <c r="C15" s="63" t="inlineStr">
+        <is>
+          <t>Use the child picker.</t>
+        </is>
+      </c>
+      <c r="D15" s="63" t="inlineStr">
+        <is>
+          <t>Selected child's context is used.</t>
+        </is>
+      </c>
+      <c r="E15" s="64" t="n"/>
+      <c r="F15" s="64" t="n"/>
+      <c r="G15" s="64" t="n"/>
+      <c r="H15" s="64" t="n"/>
+      <c r="I15" s="64" t="n"/>
+      <c r="J15" s="64" t="n"/>
+    </row>
+    <row r="16" ht="42" customHeight="1" s="54">
+      <c r="A16" s="62" t="inlineStr">
+        <is>
+          <t>PE5</t>
+        </is>
+      </c>
+      <c r="B16" s="63" t="inlineStr">
+        <is>
+          <t>As a parent, I want to sign my child up.</t>
+        </is>
+      </c>
+      <c r="C16" s="63" t="inlineStr">
+        <is>
+          <t>Find Opportunities → pick child → open event → sign up.</t>
+        </is>
+      </c>
+      <c r="D16" s="63" t="inlineStr">
+        <is>
+          <t>Child registered; appears on dashboard with calendar.</t>
+        </is>
+      </c>
+      <c r="E16" s="64" t="n"/>
+      <c r="F16" s="64" t="n"/>
+      <c r="G16" s="64" t="n"/>
+      <c r="H16" s="64" t="n"/>
+      <c r="I16" s="64" t="n"/>
+      <c r="J16" s="64" t="n"/>
+    </row>
+    <row r="17" ht="42" customHeight="1" s="54">
+      <c r="A17" s="62" t="inlineStr">
+        <is>
+          <t>PE6</t>
+        </is>
+      </c>
+      <c r="B17" s="63" t="inlineStr">
+        <is>
+          <t>As a parent, child sign-up respects grade/org limits.</t>
+        </is>
+      </c>
+      <c r="C17" s="63" t="inlineStr">
+        <is>
+          <t>Try an ineligible event.</t>
+        </is>
+      </c>
+      <c r="D17" s="63" t="inlineStr">
+        <is>
+          <t>Hidden or blocked with a message.</t>
+        </is>
+      </c>
+      <c r="E17" s="64" t="n"/>
+      <c r="F17" s="64" t="n"/>
+      <c r="G17" s="64" t="n"/>
+      <c r="H17" s="64" t="n"/>
+      <c r="I17" s="64" t="n"/>
+      <c r="J17" s="64" t="n"/>
+    </row>
+    <row r="18" ht="42" customHeight="1" s="54">
+      <c r="A18" s="62" t="inlineStr">
+        <is>
+          <t>PE7</t>
+        </is>
+      </c>
+      <c r="B18" s="63" t="inlineStr">
+        <is>
+          <t>As a parent, I want to see my child's schedule.</t>
+        </is>
+      </c>
+      <c r="C18" s="63" t="inlineStr">
+        <is>
+          <t>Open the dashboard.</t>
+        </is>
+      </c>
+      <c r="D18" s="63" t="inlineStr">
+        <is>
+          <t>Child's upcoming events with add-to-calendar; new sign-ups flagged.</t>
+        </is>
+      </c>
+      <c r="E18" s="64" t="n"/>
+      <c r="F18" s="64" t="n"/>
+      <c r="G18" s="64" t="n"/>
+      <c r="H18" s="64" t="n"/>
+      <c r="I18" s="64" t="n"/>
+      <c r="J18" s="64" t="n"/>
+    </row>
+    <row r="19" ht="42" customHeight="1" s="54">
+      <c r="A19" s="62" t="inlineStr">
+        <is>
+          <t>PE8</t>
+        </is>
+      </c>
+      <c r="B19" s="63" t="inlineStr">
+        <is>
+          <t>As a parent, I want to invite a co-guardian.</t>
+        </is>
+      </c>
+      <c r="C19" s="63" t="inlineStr">
+        <is>
+          <t>Invite a co-guardian by email.</t>
+        </is>
+      </c>
+      <c r="D19" s="63" t="inlineStr">
+        <is>
+          <t>Invite email sent; on registering with that email they share access.</t>
+        </is>
+      </c>
+      <c r="E19" s="64" t="n"/>
+      <c r="F19" s="64" t="n"/>
+      <c r="G19" s="64" t="n"/>
+      <c r="H19" s="64" t="n"/>
+      <c r="I19" s="64" t="n"/>
+      <c r="J19" s="64" t="n"/>
+    </row>
+    <row r="20" ht="42" customHeight="1" s="54">
+      <c r="A20" s="62" t="inlineStr">
+        <is>
+          <t>PE9</t>
+        </is>
+      </c>
+      <c r="B20" s="63" t="inlineStr">
+        <is>
+          <t>As a parent, I want notice when my child signs up.</t>
+        </is>
+      </c>
+      <c r="C20" s="63" t="inlineStr">
+        <is>
+          <t>Sign a child up (or have the other guardian do it).</t>
+        </is>
+      </c>
+      <c r="D20" s="63" t="inlineStr">
+        <is>
+          <t>A notification/confirmation is produced.</t>
+        </is>
+      </c>
+      <c r="E20" s="64" t="n"/>
+      <c r="F20" s="64" t="n"/>
+      <c r="G20" s="64" t="n"/>
+      <c r="H20" s="64" t="n"/>
+      <c r="I20" s="64" t="n"/>
+      <c r="J20" s="64" t="n"/>
+    </row>
+    <row r="21" ht="42" customHeight="1" s="54">
+      <c r="A21" s="62" t="inlineStr">
+        <is>
+          <t>PE10</t>
+        </is>
+      </c>
+      <c r="B21" s="63" t="inlineStr">
+        <is>
+          <t>As a parent, I want to submit my child's hours after an event (child has no login).</t>
+        </is>
+      </c>
+      <c r="C21" s="63" t="inlineStr">
+        <is>
+          <t>Dashboard → the child's 'Submit hours (past events)' → enter hours → Submit.</t>
+        </is>
+      </c>
+      <c r="D21" s="63" t="inlineStr">
+        <is>
+          <t>Hours go to the supervisor for approval; status shows 'Waiting for review'.</t>
+        </is>
+      </c>
+      <c r="E21" s="64" t="n"/>
+      <c r="F21" s="64" t="n"/>
+      <c r="G21" s="64" t="n"/>
+      <c r="H21" s="64" t="n"/>
+      <c r="I21" s="64" t="n"/>
+      <c r="J21" s="64" t="n"/>
+    </row>
+    <row r="22" ht="42" customHeight="1" s="54">
+      <c r="A22" s="62" t="inlineStr">
+        <is>
+          <t>PE11</t>
+        </is>
+      </c>
+      <c r="B22" s="63" t="inlineStr">
+        <is>
+          <t>As a parent, I want to resubmit my child's rejected hours.</t>
+        </is>
+      </c>
+      <c r="C22" s="63" t="inlineStr">
+        <is>
+          <t>On a rejected past event, enter corrected hours → Resubmit.</t>
+        </is>
+      </c>
+      <c r="D22" s="63" t="inlineStr">
+        <is>
+          <t>Returns to 'Waiting for review'.</t>
+        </is>
+      </c>
+      <c r="E22" s="64" t="n"/>
+      <c r="F22" s="64" t="n"/>
+      <c r="G22" s="64" t="n"/>
+      <c r="H22" s="64" t="n"/>
+      <c r="I22" s="64" t="n"/>
+      <c r="J22" s="64" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1" s="54">
+      <c r="A23" s="62" t="inlineStr">
+        <is>
+          <t>PE12</t>
+        </is>
+      </c>
+      <c r="B23" s="63" t="inlineStr">
+        <is>
+          <t>As a parent, I want to see each past event's hours status for my child.</t>
+        </is>
+      </c>
+      <c r="C23" s="63" t="inlineStr">
+        <is>
+          <t>Look at the child's past events list.</t>
+        </is>
+      </c>
+      <c r="D23" s="63" t="inlineStr">
+        <is>
+          <t>Each shows Approved / Waiting / Rejected as appropriate.</t>
+        </is>
+      </c>
+      <c r="E23" s="64" t="n"/>
+      <c r="F23" s="64" t="n"/>
+      <c r="G23" s="64" t="n"/>
+      <c r="H23" s="64" t="n"/>
+      <c r="I23" s="64" t="n"/>
+      <c r="J23" s="64" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1" s="54">
+      <c r="A24" s="62" t="inlineStr">
+        <is>
+          <t>PE13</t>
+        </is>
+      </c>
+      <c r="B24" s="63" t="inlineStr">
+        <is>
+          <t>As a parent, all core participant actions are available to me for my child.</t>
+        </is>
+      </c>
+      <c r="C24" s="63" t="inlineStr">
+        <is>
+          <t>Confirm: browse, sign up, withdraw, add-to-calendar, submit hours, view progress toward medals.</t>
+        </is>
+      </c>
+      <c r="D24" s="63" t="inlineStr">
+        <is>
+          <t>All participant-style actions work on the child's behalf (the child never logs in).</t>
+        </is>
+      </c>
+      <c r="E24" s="64" t="n"/>
+      <c r="F24" s="64" t="n"/>
+      <c r="G24" s="64" t="n"/>
+      <c r="H24" s="64" t="n"/>
+      <c r="I24" s="64" t="n"/>
+      <c r="J24" s="64" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1" s="54">
+      <c r="A25" s="62" t="inlineStr">
+        <is>
+          <t>PE16</t>
+        </is>
+      </c>
+      <c r="B25" s="63" t="inlineStr">
+        <is>
+          <t>As a parent, I want to browse/search opportunities for my child (upcoming &amp; past).</t>
+        </is>
+      </c>
+      <c r="C25" s="63" t="inlineStr">
+        <is>
+          <t>Find Opportunities with the child selected; use search and the upcoming/past views.</t>
+        </is>
+      </c>
+      <c r="D25" s="63" t="inlineStr">
+        <is>
+          <t>Same event list a participant sees, scoped to the child's grade/org.</t>
+        </is>
+      </c>
+      <c r="E25" s="64" t="n"/>
+      <c r="F25" s="64" t="n"/>
+      <c r="G25" s="64" t="n"/>
+      <c r="H25" s="64" t="n"/>
+      <c r="I25" s="64" t="n"/>
+      <c r="J25" s="64" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1" s="54">
+      <c r="A26" s="62" t="inlineStr">
+        <is>
+          <t>PE17</t>
+        </is>
+      </c>
+      <c r="B26" s="63" t="inlineStr">
+        <is>
+          <t>As a parent, I want to withdraw my child from an event.</t>
+        </is>
+      </c>
+      <c r="C26" s="63" t="inlineStr">
+        <is>
+          <t>Open the child's upcoming events → withdraw.</t>
+        </is>
+      </c>
+      <c r="D26" s="63" t="inlineStr">
+        <is>
+          <t>The child is removed; the slot frees up.</t>
+        </is>
+      </c>
+      <c r="E26" s="64" t="n"/>
+      <c r="F26" s="64" t="n"/>
+      <c r="G26" s="64" t="n"/>
+      <c r="H26" s="64" t="n"/>
+      <c r="I26" s="64" t="n"/>
+      <c r="J26" s="64" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1" s="54">
+      <c r="A27" s="62" t="inlineStr">
+        <is>
+          <t>PE18</t>
+        </is>
+      </c>
+      <c r="B27" s="63" t="inlineStr">
+        <is>
+          <t>As a parent, I want to check my child in on event day.</t>
+        </is>
+      </c>
+      <c r="C27" s="63" t="inlineStr">
+        <is>
+          <t>On the event day within the window, check the child in.</t>
+        </is>
+      </c>
+      <c r="D27" s="63" t="inlineStr">
+        <is>
+          <t>Check-in succeeds for the child.</t>
+        </is>
+      </c>
+      <c r="E27" s="64" t="n"/>
+      <c r="F27" s="64" t="n"/>
+      <c r="G27" s="64" t="n"/>
+      <c r="H27" s="64" t="n"/>
+      <c r="I27" s="64" t="n"/>
+      <c r="J27" s="64" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1" s="54">
+      <c r="A28" s="62" t="inlineStr">
+        <is>
+          <t>PE19</t>
+        </is>
+      </c>
+      <c r="B28" s="63" t="inlineStr">
+        <is>
+          <t>As a parent, I want to see my child's medal progress.</t>
+        </is>
+      </c>
+      <c r="C28" s="63" t="inlineStr">
+        <is>
+          <t>Open the dashboard / child card.</t>
+        </is>
+      </c>
+      <c r="D28" s="63" t="inlineStr">
+        <is>
+          <t>Progress uses the child's grade-based thresholds (e.g. lower bar for younger grades).</t>
+        </is>
+      </c>
+      <c r="E28" s="64" t="n"/>
+      <c r="F28" s="64" t="n"/>
+      <c r="G28" s="64" t="n"/>
+      <c r="H28" s="64" t="n"/>
+      <c r="I28" s="64" t="n"/>
+      <c r="J28" s="64" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1" s="54">
+      <c r="A29" s="62" t="inlineStr">
+        <is>
+          <t>PE20</t>
+        </is>
+      </c>
+      <c r="B29" s="63" t="inlineStr">
+        <is>
+          <t>As a parent, external &gt;5h for my child requires proof.</t>
+        </is>
+      </c>
+      <c r="C29" s="63" t="inlineStr">
+        <is>
+          <t>Outside hours for the child, over 5 hours, without then with a proof file.</t>
+        </is>
+      </c>
+      <c r="D29" s="63" t="inlineStr">
+        <is>
+          <t>Blocked without proof; submits with a photo/letter.</t>
+        </is>
+      </c>
+      <c r="E29" s="64" t="n"/>
+      <c r="F29" s="64" t="n"/>
+      <c r="G29" s="64" t="n"/>
+      <c r="H29" s="64" t="n"/>
+      <c r="I29" s="64" t="n"/>
+      <c r="J29" s="64" t="n"/>
+    </row>
+    <row r="30" ht="42" customHeight="1" s="54">
+      <c r="A30" s="62" t="inlineStr">
+        <is>
+          <t>PE14</t>
+        </is>
+      </c>
+      <c r="B30" s="63" t="inlineStr">
+        <is>
+          <t>As a parent, I want to log my child's outside/nonprofit volunteering.</t>
+        </is>
+      </c>
+      <c r="C30" s="63" t="inlineStr">
+        <is>
+          <t>Child card → 'Outside hours' → fill activity, org, date, hours, supervisor → Submit.</t>
+        </is>
+      </c>
+      <c r="D30" s="63" t="inlineStr">
+        <is>
+          <t>External hours submitted for the child and sent for supervisor approval (proof required over 5h).</t>
+        </is>
+      </c>
+      <c r="E30" s="64" t="n"/>
+      <c r="F30" s="64" t="n"/>
+      <c r="G30" s="64" t="n"/>
+      <c r="H30" s="64" t="n"/>
+      <c r="I30" s="64" t="n"/>
+      <c r="J30" s="64" t="n"/>
+    </row>
+    <row r="31" ht="42" customHeight="1" s="54">
+      <c r="A31" s="62" t="inlineStr">
+        <is>
+          <t>PE15</t>
+        </is>
+      </c>
+      <c r="B31" s="63" t="inlineStr">
+        <is>
+          <t>As a parent, I want my child's verified service record.</t>
+        </is>
+      </c>
+      <c r="C31" s="63" t="inlineStr">
+        <is>
+          <t>Child card → 'Service record'.</t>
+        </is>
+      </c>
+      <c r="D31" s="63" t="inlineStr">
+        <is>
+          <t>The child's itemized record opens; Print / Save-as-PDF works.</t>
+        </is>
+      </c>
+      <c r="E31" s="64" t="n"/>
+      <c r="F31" s="64" t="n"/>
+      <c r="G31" s="64" t="n"/>
+      <c r="H31" s="64" t="n"/>
+      <c r="I31" s="64" t="n"/>
+      <c r="J31" s="64" t="n"/>
+    </row>
+    <row r="32" ht="42" customHeight="1" s="54">
+      <c r="A32" s="62" t="inlineStr">
+        <is>
+          <t>PE22</t>
+        </is>
+      </c>
+      <c r="B32" s="63" t="inlineStr">
+        <is>
+          <t>As a parent, I want to be emailed when my child's hours are reviewed.</t>
+        </is>
+      </c>
+      <c r="C32" s="63" t="inlineStr">
+        <is>
+          <t>Have a supervisor approve then reject a submission for a managed child.</t>
+        </is>
+      </c>
+      <c r="D32" s="63" t="inlineStr">
+        <is>
+          <t>You (the guardian) receive the approved / needs-attention emails, even though the child has no email of their own.</t>
+        </is>
+      </c>
+      <c r="E32" s="64" t="n"/>
+      <c r="F32" s="64" t="n"/>
+      <c r="G32" s="64" t="n"/>
+      <c r="H32" s="64" t="n"/>
+      <c r="I32" s="64" t="n"/>
+      <c r="J32" s="64" t="n"/>
+    </row>
+    <row r="33" ht="42" customHeight="1" s="54">
+      <c r="A33" s="62" t="inlineStr">
+        <is>
+          <t>PE23</t>
+        </is>
+      </c>
+      <c r="B33" s="63" t="inlineStr">
+        <is>
+          <t>As a parent, I want to edit my child's details.</t>
+        </is>
+      </c>
+      <c r="C33" s="63" t="inlineStr">
+        <is>
+          <t>Child card → Edit → change name/grade/school → save.</t>
+        </is>
+      </c>
+      <c r="D33" s="63" t="inlineStr">
+        <is>
+          <t>Changes save for the managed child.</t>
+        </is>
+      </c>
+      <c r="E33" s="64" t="n"/>
+      <c r="F33" s="64" t="n"/>
+      <c r="G33" s="64" t="n"/>
+      <c r="H33" s="64" t="n"/>
+      <c r="I33" s="64" t="n"/>
+      <c r="J33" s="64" t="n"/>
+    </row>
+    <row r="34" ht="42" customHeight="1" s="54">
+      <c r="A34" s="62" t="inlineStr">
+        <is>
+          <t>PE24</t>
+        </is>
+      </c>
+      <c r="B34" s="63" t="inlineStr">
+        <is>
+          <t>As a parent, I understand a managed child can't be added to an event by a supervisor's by-email tool.</t>
+        </is>
+      </c>
+      <c r="C34" s="63" t="inlineStr">
+        <is>
+          <t>Ask a supervisor/admin to try adding the child via Roster → Add a participant; then sign the child up yourself from Find Opportunities.</t>
+        </is>
+      </c>
+      <c r="D34" s="63" t="inlineStr">
+        <is>
+          <t>The by-email add can't find the child (no login/email of their own); the supported path is the guardian signing the child up, which puts the event on the child's schedule.</t>
+        </is>
+      </c>
+      <c r="E34" s="64" t="n"/>
+      <c r="F34" s="64" t="n"/>
+      <c r="G34" s="64" t="n"/>
+      <c r="H34" s="64" t="n"/>
+      <c r="I34" s="64" t="n"/>
+      <c r="J34" s="64" t="n"/>
+    </row>
+    <row r="35" ht="42" customHeight="1" s="54">
+      <c r="A35" s="62" t="inlineStr">
+        <is>
+          <t>PE25</t>
+        </is>
+      </c>
+      <c r="B35" s="63" t="inlineStr">
+        <is>
+          <t>As a parent, when I sign my child up, it appears on the child's schedule.</t>
+        </is>
+      </c>
+      <c r="C35" s="63" t="inlineStr">
+        <is>
+          <t>Find Opportunities → pick child → sign up → open dashboard.</t>
+        </is>
+      </c>
+      <c r="D35" s="63" t="inlineStr">
+        <is>
+          <t>The event shows on the child's upcoming schedule with add-to-calendar; a new-sign-up flag/confirmation appears.</t>
+        </is>
+      </c>
+      <c r="E35" s="64" t="n"/>
+      <c r="F35" s="64" t="n"/>
+      <c r="G35" s="64" t="n"/>
+      <c r="H35" s="64" t="n"/>
+      <c r="I35" s="64" t="n"/>
+      <c r="J35" s="64" t="n"/>
+    </row>
     <row r="36" ht="20" customHeight="1" s="54">
       <c r="A36" s="61" t="inlineStr">
         <is>
@@ -3111,6 +4227,8 @@
       <c r="F36" s="59" t="n"/>
       <c r="G36" s="59" t="n"/>
       <c r="H36" s="59" t="n"/>
+      <c r="I36" s="59" t="n"/>
+      <c r="J36" s="59" t="n"/>
     </row>
     <row r="37" ht="42" customHeight="1" s="54">
       <c r="A37" s="62" t="inlineStr">
@@ -3137,6 +4255,8 @@
       <c r="F37" s="64" t="n"/>
       <c r="G37" s="64" t="n"/>
       <c r="H37" s="64" t="n"/>
+      <c r="I37" s="64" t="n"/>
+      <c r="J37" s="64" t="n"/>
     </row>
     <row r="38" ht="42" customHeight="1" s="54">
       <c r="A38" s="62" t="inlineStr">
@@ -3163,15 +4283,18 @@
       <c r="F38" s="64" t="n"/>
       <c r="G38" s="64" t="n"/>
       <c r="H38" s="64" t="n"/>
+      <c r="I38" s="64" t="n"/>
+      <c r="J38" s="64" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A4:H4"/>
+  <mergeCells count="7">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A36:J36"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="E2:F2"/>
-    <mergeCell ref="A36:H36"/>
-    <mergeCell ref="A11:H11"/>
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A11:J11"/>
   </mergeCells>
   <conditionalFormatting sqref="E4:E38">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="3">
@@ -3195,1048 +4318,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation sqref="E4:E38 G4:G38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Pass,Fail,Blocked,Not tested,N/A"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J36"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" style="54" min="1" max="1"/>
-    <col width="56" customWidth="1" style="54" min="2" max="2"/>
-    <col width="50" customWidth="1" style="54" min="3" max="3"/>
-    <col width="50" customWidth="1" style="54" min="4" max="4"/>
-    <col width="13" customWidth="1" style="54" min="5" max="5"/>
-    <col width="30" customWidth="1" style="54" min="6" max="6"/>
-    <col width="13" customWidth="1" style="54" min="7" max="7"/>
-    <col width="30" customWidth="1" style="54" min="8" max="8"/>
-    <col width="13" customWidth="1" style="54" min="9" max="9"/>
-    <col width="30" customWidth="1" style="54" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1" s="54">
-      <c r="A1" s="56" t="inlineStr">
-        <is>
-          <t>Test cases — Parent — elementary (2–5 child)</t>
-        </is>
-      </c>
-      <c r="B1" s="57" t="n"/>
-      <c r="C1" s="57" t="n"/>
-      <c r="D1" s="57" t="n"/>
-      <c r="E1" s="57" t="n"/>
-      <c r="F1" s="57" t="n"/>
-      <c r="G1" s="57" t="n"/>
-      <c r="H1" s="57" t="n"/>
-      <c r="I1" s="57" t="n"/>
-      <c r="J1" s="57" t="n"/>
-    </row>
-    <row r="2" ht="30" customHeight="1" s="54">
-      <c r="E2" s="58" t="inlineStr">
-        <is>
-          <t>Noreen Sultana
-Platform: ?</t>
-        </is>
-      </c>
-      <c r="F2" s="59" t="n"/>
-      <c r="G2" s="58" t="inlineStr">
-        <is>
-          <t>Tester 2
-Platform: ?</t>
-        </is>
-      </c>
-      <c r="H2" s="59" t="n"/>
-      <c r="I2" s="58" t="inlineStr">
-        <is>
-          <t>Tester 3
-Platform: ?</t>
-        </is>
-      </c>
-      <c r="J2" s="59" t="n"/>
-    </row>
-    <row r="3" ht="28" customHeight="1" s="54">
-      <c r="A3" s="60" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B3" s="60" t="inlineStr">
-        <is>
-          <t>User story</t>
-        </is>
-      </c>
-      <c r="C3" s="60" t="inlineStr">
-        <is>
-          <t>Steps to perform</t>
-        </is>
-      </c>
-      <c r="D3" s="60" t="inlineStr">
-        <is>
-          <t>Expected behavior (what you should see)</t>
-        </is>
-      </c>
-      <c r="E3" s="60" t="inlineStr">
-        <is>
-          <t>Result</t>
-        </is>
-      </c>
-      <c r="F3" s="60" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="G3" s="60" t="inlineStr">
-        <is>
-          <t>Result</t>
-        </is>
-      </c>
-      <c r="H3" s="60" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="I3" s="60" t="inlineStr">
-        <is>
-          <t>Result</t>
-        </is>
-      </c>
-      <c r="J3" s="60" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1" s="54">
-      <c r="A4" s="61" t="inlineStr">
-        <is>
-          <t>Account &amp; access (all roles)</t>
-        </is>
-      </c>
-      <c r="B4" s="59" t="n"/>
-      <c r="C4" s="59" t="n"/>
-      <c r="D4" s="59" t="n"/>
-      <c r="E4" s="59" t="n"/>
-      <c r="F4" s="59" t="n"/>
-      <c r="G4" s="59" t="n"/>
-      <c r="H4" s="59" t="n"/>
-      <c r="I4" s="59" t="n"/>
-      <c r="J4" s="59" t="n"/>
-    </row>
-    <row r="5" ht="42" customHeight="1" s="54">
-      <c r="A5" s="62" t="inlineStr">
-        <is>
-          <t>AC1</t>
-        </is>
-      </c>
-      <c r="B5" s="63" t="inlineStr">
-        <is>
-          <t>As any user, I want to log in with email and password.</t>
-        </is>
-      </c>
-      <c r="C5" s="63" t="inlineStr">
-        <is>
-          <t>Enter valid email/password and Sign in.</t>
-        </is>
-      </c>
-      <c r="D5" s="63" t="inlineStr">
-        <is>
-          <t>You're signed in and taken to your role's home.</t>
-        </is>
-      </c>
-      <c r="E5" s="64" t="n"/>
-      <c r="F5" s="64" t="n"/>
-      <c r="G5" s="64" t="n"/>
-      <c r="H5" s="64" t="n"/>
-      <c r="I5" s="64" t="n"/>
-      <c r="J5" s="64" t="n"/>
-    </row>
-    <row r="6" ht="42" customHeight="1" s="54">
-      <c r="A6" s="62" t="inlineStr">
-        <is>
-          <t>AC2</t>
-        </is>
-      </c>
-      <c r="B6" s="63" t="inlineStr">
-        <is>
-          <t>As any user, I want to reveal my password while typing.</t>
-        </is>
-      </c>
-      <c r="C6" s="63" t="inlineStr">
-        <is>
-          <t>Tap the eye icon in the password field.</t>
-        </is>
-      </c>
-      <c r="D6" s="63" t="inlineStr">
-        <is>
-          <t>Password text toggles visible/hidden.</t>
-        </is>
-      </c>
-      <c r="E6" s="64" t="n"/>
-      <c r="F6" s="64" t="n"/>
-      <c r="G6" s="64" t="n"/>
-      <c r="H6" s="64" t="n"/>
-      <c r="I6" s="64" t="n"/>
-      <c r="J6" s="64" t="n"/>
-    </row>
-    <row r="7" ht="42" customHeight="1" s="54">
-      <c r="A7" s="62" t="inlineStr">
-        <is>
-          <t>AC3</t>
-        </is>
-      </c>
-      <c r="B7" s="63" t="inlineStr">
-        <is>
-          <t>As any user, I want to reset a forgotten password by email.</t>
-        </is>
-      </c>
-      <c r="C7" s="63" t="inlineStr">
-        <is>
-          <t>Forgot password → enter email → open email → follow link → set new password → sign in.</t>
-        </is>
-      </c>
-      <c r="D7" s="63" t="inlineStr">
-        <is>
-          <t>Reset email arrives; link works; new password signs in; old one fails.</t>
-        </is>
-      </c>
-      <c r="E7" s="64" t="n"/>
-      <c r="F7" s="64" t="n"/>
-      <c r="G7" s="64" t="n"/>
-      <c r="H7" s="64" t="n"/>
-      <c r="I7" s="64" t="n"/>
-      <c r="J7" s="64" t="n"/>
-    </row>
-    <row r="8" ht="42" customHeight="1" s="54">
-      <c r="A8" s="62" t="inlineStr">
-        <is>
-          <t>AC4</t>
-        </is>
-      </c>
-      <c r="B8" s="63" t="inlineStr">
-        <is>
-          <t>As any user, I want to sign out.</t>
-        </is>
-      </c>
-      <c r="C8" s="63" t="inlineStr">
-        <is>
-          <t>Use Sign out.</t>
-        </is>
-      </c>
-      <c r="D8" s="63" t="inlineStr">
-        <is>
-          <t>Logged out; returned to login/landing.</t>
-        </is>
-      </c>
-      <c r="E8" s="64" t="n"/>
-      <c r="F8" s="64" t="n"/>
-      <c r="G8" s="64" t="n"/>
-      <c r="H8" s="64" t="n"/>
-      <c r="I8" s="64" t="n"/>
-      <c r="J8" s="64" t="n"/>
-    </row>
-    <row r="9" ht="42" customHeight="1" s="54">
-      <c r="A9" s="62" t="inlineStr">
-        <is>
-          <t>AC5</t>
-        </is>
-      </c>
-      <c r="B9" s="63" t="inlineStr">
-        <is>
-          <t>As any user, I want a clear error for bad credentials.</t>
-        </is>
-      </c>
-      <c r="C9" s="63" t="inlineStr">
-        <is>
-          <t>Enter a wrong password.</t>
-        </is>
-      </c>
-      <c r="D9" s="63" t="inlineStr">
-        <is>
-          <t>Clear 'login failed' message; stay on login.</t>
-        </is>
-      </c>
-      <c r="E9" s="64" t="n"/>
-      <c r="F9" s="64" t="n"/>
-      <c r="G9" s="64" t="n"/>
-      <c r="H9" s="64" t="n"/>
-      <c r="I9" s="64" t="n"/>
-      <c r="J9" s="64" t="n"/>
-    </row>
-    <row r="10" ht="42" customHeight="1" s="54">
-      <c r="A10" s="62" t="inlineStr">
-        <is>
-          <t>AC6</t>
-        </is>
-      </c>
-      <c r="B10" s="63" t="inlineStr">
-        <is>
-          <t>As any user, my session persists and protected pages are guarded.</t>
-        </is>
-      </c>
-      <c r="C10" s="63" t="inlineStr">
-        <is>
-          <t>Sign in, refresh; then sign out and open a protected URL directly.</t>
-        </is>
-      </c>
-      <c r="D10" s="63" t="inlineStr">
-        <is>
-          <t>Refresh stays signed in; protected pages redirect to login when signed out.</t>
-        </is>
-      </c>
-      <c r="E10" s="64" t="n"/>
-      <c r="F10" s="64" t="n"/>
-      <c r="G10" s="64" t="n"/>
-      <c r="H10" s="64" t="n"/>
-      <c r="I10" s="64" t="n"/>
-      <c r="J10" s="64" t="n"/>
-    </row>
-    <row r="11" ht="20" customHeight="1" s="54">
-      <c r="A11" s="61" t="inlineStr">
-        <is>
-          <t>Parent — elementary (grades 2–5 child)</t>
-        </is>
-      </c>
-      <c r="B11" s="59" t="n"/>
-      <c r="C11" s="59" t="n"/>
-      <c r="D11" s="59" t="n"/>
-      <c r="E11" s="59" t="n"/>
-      <c r="F11" s="59" t="n"/>
-      <c r="G11" s="59" t="n"/>
-      <c r="H11" s="59" t="n"/>
-      <c r="I11" s="59" t="n"/>
-      <c r="J11" s="59" t="n"/>
-    </row>
-    <row r="12" ht="42" customHeight="1" s="54">
-      <c r="A12" s="62" t="inlineStr">
-        <is>
-          <t>PE1</t>
-        </is>
-      </c>
-      <c r="B12" s="63" t="inlineStr">
-        <is>
-          <t>As a parent, I want to register to manage my grade 2–5 child.</t>
-        </is>
-      </c>
-      <c r="C12" s="63" t="inlineStr">
-        <is>
-          <t>Create account → parent of a 2–5 child.</t>
-        </is>
-      </c>
-      <c r="D12" s="63" t="inlineStr">
-        <is>
-          <t>Parent account created.</t>
-        </is>
-      </c>
-      <c r="E12" s="64" t="n"/>
-      <c r="F12" s="64" t="n"/>
-      <c r="G12" s="64" t="n"/>
-      <c r="H12" s="64" t="n"/>
-      <c r="I12" s="64" t="n"/>
-      <c r="J12" s="64" t="n"/>
-    </row>
-    <row r="13" ht="42" customHeight="1" s="54">
-      <c r="A13" s="62" t="inlineStr">
-        <is>
-          <t>PE2</t>
-        </is>
-      </c>
-      <c r="B13" s="63" t="inlineStr">
-        <is>
-          <t>As an elementary parent, I want the right menu tabs.</t>
-        </is>
-      </c>
-      <c r="C13" s="63" t="inlineStr">
-        <is>
-          <t>Look at the left menu.</t>
-        </is>
-      </c>
-      <c r="D13" s="63" t="inlineStr">
-        <is>
-          <t>Dashboard and Find Opportunities (Help in footer).</t>
-        </is>
-      </c>
-      <c r="E13" s="64" t="n"/>
-      <c r="F13" s="64" t="n"/>
-      <c r="G13" s="64" t="n"/>
-      <c r="H13" s="64" t="n"/>
-      <c r="I13" s="64" t="n"/>
-      <c r="J13" s="64" t="n"/>
-    </row>
-    <row r="14" ht="42" customHeight="1" s="54">
-      <c r="A14" s="62" t="inlineStr">
-        <is>
-          <t>PE3</t>
-        </is>
-      </c>
-      <c r="B14" s="63" t="inlineStr">
-        <is>
-          <t>As a parent, I want to add a managed child (2–5).</t>
-        </is>
-      </c>
-      <c r="C14" s="63" t="inlineStr">
-        <is>
-          <t>Add child with name and grade (join code if required).</t>
-        </is>
-      </c>
-      <c r="D14" s="63" t="inlineStr">
-        <is>
-          <t>Child added; no separate login.</t>
-        </is>
-      </c>
-      <c r="E14" s="64" t="n"/>
-      <c r="F14" s="64" t="n"/>
-      <c r="G14" s="64" t="n"/>
-      <c r="H14" s="64" t="n"/>
-      <c r="I14" s="64" t="n"/>
-      <c r="J14" s="64" t="n"/>
-    </row>
-    <row r="15" ht="42" customHeight="1" s="54">
-      <c r="A15" s="62" t="inlineStr">
-        <is>
-          <t>PE4</t>
-        </is>
-      </c>
-      <c r="B15" s="63" t="inlineStr">
-        <is>
-          <t>As a parent with several kids, I want to switch child.</t>
-        </is>
-      </c>
-      <c r="C15" s="63" t="inlineStr">
-        <is>
-          <t>Use the child picker.</t>
-        </is>
-      </c>
-      <c r="D15" s="63" t="inlineStr">
-        <is>
-          <t>Selected child's context is used.</t>
-        </is>
-      </c>
-      <c r="E15" s="64" t="n"/>
-      <c r="F15" s="64" t="n"/>
-      <c r="G15" s="64" t="n"/>
-      <c r="H15" s="64" t="n"/>
-      <c r="I15" s="64" t="n"/>
-      <c r="J15" s="64" t="n"/>
-    </row>
-    <row r="16" ht="42" customHeight="1" s="54">
-      <c r="A16" s="62" t="inlineStr">
-        <is>
-          <t>PE5</t>
-        </is>
-      </c>
-      <c r="B16" s="63" t="inlineStr">
-        <is>
-          <t>As a parent, I want to sign my child up.</t>
-        </is>
-      </c>
-      <c r="C16" s="63" t="inlineStr">
-        <is>
-          <t>Find Opportunities → pick child → open event → sign up.</t>
-        </is>
-      </c>
-      <c r="D16" s="63" t="inlineStr">
-        <is>
-          <t>Child registered; appears on dashboard with calendar.</t>
-        </is>
-      </c>
-      <c r="E16" s="64" t="n"/>
-      <c r="F16" s="64" t="n"/>
-      <c r="G16" s="64" t="n"/>
-      <c r="H16" s="64" t="n"/>
-      <c r="I16" s="64" t="n"/>
-      <c r="J16" s="64" t="n"/>
-    </row>
-    <row r="17" ht="42" customHeight="1" s="54">
-      <c r="A17" s="62" t="inlineStr">
-        <is>
-          <t>PE6</t>
-        </is>
-      </c>
-      <c r="B17" s="63" t="inlineStr">
-        <is>
-          <t>As a parent, child sign-up respects grade/org limits.</t>
-        </is>
-      </c>
-      <c r="C17" s="63" t="inlineStr">
-        <is>
-          <t>Try an ineligible event.</t>
-        </is>
-      </c>
-      <c r="D17" s="63" t="inlineStr">
-        <is>
-          <t>Hidden or blocked with a message.</t>
-        </is>
-      </c>
-      <c r="E17" s="64" t="n"/>
-      <c r="F17" s="64" t="n"/>
-      <c r="G17" s="64" t="n"/>
-      <c r="H17" s="64" t="n"/>
-      <c r="I17" s="64" t="n"/>
-      <c r="J17" s="64" t="n"/>
-    </row>
-    <row r="18" ht="42" customHeight="1" s="54">
-      <c r="A18" s="62" t="inlineStr">
-        <is>
-          <t>PE7</t>
-        </is>
-      </c>
-      <c r="B18" s="63" t="inlineStr">
-        <is>
-          <t>As a parent, I want to see my child's schedule.</t>
-        </is>
-      </c>
-      <c r="C18" s="63" t="inlineStr">
-        <is>
-          <t>Open the dashboard.</t>
-        </is>
-      </c>
-      <c r="D18" s="63" t="inlineStr">
-        <is>
-          <t>Child's upcoming events with add-to-calendar; new sign-ups flagged.</t>
-        </is>
-      </c>
-      <c r="E18" s="64" t="n"/>
-      <c r="F18" s="64" t="n"/>
-      <c r="G18" s="64" t="n"/>
-      <c r="H18" s="64" t="n"/>
-      <c r="I18" s="64" t="n"/>
-      <c r="J18" s="64" t="n"/>
-    </row>
-    <row r="19" ht="42" customHeight="1" s="54">
-      <c r="A19" s="62" t="inlineStr">
-        <is>
-          <t>PE8</t>
-        </is>
-      </c>
-      <c r="B19" s="63" t="inlineStr">
-        <is>
-          <t>As a parent, I want to invite a co-guardian.</t>
-        </is>
-      </c>
-      <c r="C19" s="63" t="inlineStr">
-        <is>
-          <t>Invite a co-guardian by email.</t>
-        </is>
-      </c>
-      <c r="D19" s="63" t="inlineStr">
-        <is>
-          <t>Invite email sent; on registering with that email they share access.</t>
-        </is>
-      </c>
-      <c r="E19" s="64" t="n"/>
-      <c r="F19" s="64" t="n"/>
-      <c r="G19" s="64" t="n"/>
-      <c r="H19" s="64" t="n"/>
-      <c r="I19" s="64" t="n"/>
-      <c r="J19" s="64" t="n"/>
-    </row>
-    <row r="20" ht="42" customHeight="1" s="54">
-      <c r="A20" s="62" t="inlineStr">
-        <is>
-          <t>PE9</t>
-        </is>
-      </c>
-      <c r="B20" s="63" t="inlineStr">
-        <is>
-          <t>As a parent, I want notice when my child signs up.</t>
-        </is>
-      </c>
-      <c r="C20" s="63" t="inlineStr">
-        <is>
-          <t>Sign a child up (or have the other guardian do it).</t>
-        </is>
-      </c>
-      <c r="D20" s="63" t="inlineStr">
-        <is>
-          <t>A notification/confirmation is produced.</t>
-        </is>
-      </c>
-      <c r="E20" s="64" t="n"/>
-      <c r="F20" s="64" t="n"/>
-      <c r="G20" s="64" t="n"/>
-      <c r="H20" s="64" t="n"/>
-      <c r="I20" s="64" t="n"/>
-      <c r="J20" s="64" t="n"/>
-    </row>
-    <row r="21" ht="42" customHeight="1" s="54">
-      <c r="A21" s="62" t="inlineStr">
-        <is>
-          <t>PE10</t>
-        </is>
-      </c>
-      <c r="B21" s="63" t="inlineStr">
-        <is>
-          <t>As a parent, I want to submit my child's hours after an event (child has no login).</t>
-        </is>
-      </c>
-      <c r="C21" s="63" t="inlineStr">
-        <is>
-          <t>Dashboard → the child's 'Submit hours (past events)' → enter hours → Submit.</t>
-        </is>
-      </c>
-      <c r="D21" s="63" t="inlineStr">
-        <is>
-          <t>Hours go to the supervisor for approval; status shows 'Waiting for review'.</t>
-        </is>
-      </c>
-      <c r="E21" s="64" t="n"/>
-      <c r="F21" s="64" t="n"/>
-      <c r="G21" s="64" t="n"/>
-      <c r="H21" s="64" t="n"/>
-      <c r="I21" s="64" t="n"/>
-      <c r="J21" s="64" t="n"/>
-    </row>
-    <row r="22" ht="42" customHeight="1" s="54">
-      <c r="A22" s="62" t="inlineStr">
-        <is>
-          <t>PE11</t>
-        </is>
-      </c>
-      <c r="B22" s="63" t="inlineStr">
-        <is>
-          <t>As a parent, I want to resubmit my child's rejected hours.</t>
-        </is>
-      </c>
-      <c r="C22" s="63" t="inlineStr">
-        <is>
-          <t>On a rejected past event, enter corrected hours → Resubmit.</t>
-        </is>
-      </c>
-      <c r="D22" s="63" t="inlineStr">
-        <is>
-          <t>Returns to 'Waiting for review'.</t>
-        </is>
-      </c>
-      <c r="E22" s="64" t="n"/>
-      <c r="F22" s="64" t="n"/>
-      <c r="G22" s="64" t="n"/>
-      <c r="H22" s="64" t="n"/>
-      <c r="I22" s="64" t="n"/>
-      <c r="J22" s="64" t="n"/>
-    </row>
-    <row r="23" ht="42" customHeight="1" s="54">
-      <c r="A23" s="62" t="inlineStr">
-        <is>
-          <t>PE12</t>
-        </is>
-      </c>
-      <c r="B23" s="63" t="inlineStr">
-        <is>
-          <t>As a parent, I want to see each past event's hours status for my child.</t>
-        </is>
-      </c>
-      <c r="C23" s="63" t="inlineStr">
-        <is>
-          <t>Look at the child's past events list.</t>
-        </is>
-      </c>
-      <c r="D23" s="63" t="inlineStr">
-        <is>
-          <t>Each shows Approved / Waiting / Rejected as appropriate.</t>
-        </is>
-      </c>
-      <c r="E23" s="64" t="n"/>
-      <c r="F23" s="64" t="n"/>
-      <c r="G23" s="64" t="n"/>
-      <c r="H23" s="64" t="n"/>
-      <c r="I23" s="64" t="n"/>
-      <c r="J23" s="64" t="n"/>
-    </row>
-    <row r="24" ht="42" customHeight="1" s="54">
-      <c r="A24" s="62" t="inlineStr">
-        <is>
-          <t>PE13</t>
-        </is>
-      </c>
-      <c r="B24" s="63" t="inlineStr">
-        <is>
-          <t>As a parent, all core participant actions are available to me for my child.</t>
-        </is>
-      </c>
-      <c r="C24" s="63" t="inlineStr">
-        <is>
-          <t>Confirm: browse, sign up, withdraw, add-to-calendar, submit hours, view progress toward medals.</t>
-        </is>
-      </c>
-      <c r="D24" s="63" t="inlineStr">
-        <is>
-          <t>All participant-style actions work on the child's behalf (the child never logs in).</t>
-        </is>
-      </c>
-      <c r="E24" s="64" t="n"/>
-      <c r="F24" s="64" t="n"/>
-      <c r="G24" s="64" t="n"/>
-      <c r="H24" s="64" t="n"/>
-      <c r="I24" s="64" t="n"/>
-      <c r="J24" s="64" t="n"/>
-    </row>
-    <row r="25" ht="42" customHeight="1" s="54">
-      <c r="A25" s="62" t="inlineStr">
-        <is>
-          <t>PE16</t>
-        </is>
-      </c>
-      <c r="B25" s="63" t="inlineStr">
-        <is>
-          <t>As a parent, I want to browse/search opportunities for my child (upcoming &amp; past).</t>
-        </is>
-      </c>
-      <c r="C25" s="63" t="inlineStr">
-        <is>
-          <t>Find Opportunities with the child selected; use search and the upcoming/past views.</t>
-        </is>
-      </c>
-      <c r="D25" s="63" t="inlineStr">
-        <is>
-          <t>Same event list a participant sees, scoped to the child's grade/org.</t>
-        </is>
-      </c>
-      <c r="E25" s="64" t="n"/>
-      <c r="F25" s="64" t="n"/>
-      <c r="G25" s="64" t="n"/>
-      <c r="H25" s="64" t="n"/>
-      <c r="I25" s="64" t="n"/>
-      <c r="J25" s="64" t="n"/>
-    </row>
-    <row r="26" ht="42" customHeight="1" s="54">
-      <c r="A26" s="62" t="inlineStr">
-        <is>
-          <t>PE17</t>
-        </is>
-      </c>
-      <c r="B26" s="63" t="inlineStr">
-        <is>
-          <t>As a parent, I want to withdraw my child from an event.</t>
-        </is>
-      </c>
-      <c r="C26" s="63" t="inlineStr">
-        <is>
-          <t>Open the child's upcoming events → withdraw.</t>
-        </is>
-      </c>
-      <c r="D26" s="63" t="inlineStr">
-        <is>
-          <t>The child is removed; the slot frees up.</t>
-        </is>
-      </c>
-      <c r="E26" s="64" t="n"/>
-      <c r="F26" s="64" t="n"/>
-      <c r="G26" s="64" t="n"/>
-      <c r="H26" s="64" t="n"/>
-      <c r="I26" s="64" t="n"/>
-      <c r="J26" s="64" t="n"/>
-    </row>
-    <row r="27" ht="42" customHeight="1" s="54">
-      <c r="A27" s="62" t="inlineStr">
-        <is>
-          <t>PE18</t>
-        </is>
-      </c>
-      <c r="B27" s="63" t="inlineStr">
-        <is>
-          <t>As a parent, I want to check my child in on event day.</t>
-        </is>
-      </c>
-      <c r="C27" s="63" t="inlineStr">
-        <is>
-          <t>On the event day within the window, check the child in.</t>
-        </is>
-      </c>
-      <c r="D27" s="63" t="inlineStr">
-        <is>
-          <t>Check-in succeeds for the child.</t>
-        </is>
-      </c>
-      <c r="E27" s="64" t="n"/>
-      <c r="F27" s="64" t="n"/>
-      <c r="G27" s="64" t="n"/>
-      <c r="H27" s="64" t="n"/>
-      <c r="I27" s="64" t="n"/>
-      <c r="J27" s="64" t="n"/>
-    </row>
-    <row r="28" ht="42" customHeight="1" s="54">
-      <c r="A28" s="62" t="inlineStr">
-        <is>
-          <t>PE19</t>
-        </is>
-      </c>
-      <c r="B28" s="63" t="inlineStr">
-        <is>
-          <t>As a parent, I want to see my child's medal progress.</t>
-        </is>
-      </c>
-      <c r="C28" s="63" t="inlineStr">
-        <is>
-          <t>Open the dashboard / child card.</t>
-        </is>
-      </c>
-      <c r="D28" s="63" t="inlineStr">
-        <is>
-          <t>Progress uses the child's grade-based thresholds (e.g. lower bar for younger grades).</t>
-        </is>
-      </c>
-      <c r="E28" s="64" t="n"/>
-      <c r="F28" s="64" t="n"/>
-      <c r="G28" s="64" t="n"/>
-      <c r="H28" s="64" t="n"/>
-      <c r="I28" s="64" t="n"/>
-      <c r="J28" s="64" t="n"/>
-    </row>
-    <row r="29" ht="42" customHeight="1" s="54">
-      <c r="A29" s="62" t="inlineStr">
-        <is>
-          <t>PE20</t>
-        </is>
-      </c>
-      <c r="B29" s="63" t="inlineStr">
-        <is>
-          <t>As a parent, external &gt;5h for my child requires proof.</t>
-        </is>
-      </c>
-      <c r="C29" s="63" t="inlineStr">
-        <is>
-          <t>Outside hours for the child, over 5 hours, without then with a proof file.</t>
-        </is>
-      </c>
-      <c r="D29" s="63" t="inlineStr">
-        <is>
-          <t>Blocked without proof; submits with a photo/letter.</t>
-        </is>
-      </c>
-      <c r="E29" s="64" t="n"/>
-      <c r="F29" s="64" t="n"/>
-      <c r="G29" s="64" t="n"/>
-      <c r="H29" s="64" t="n"/>
-      <c r="I29" s="64" t="n"/>
-      <c r="J29" s="64" t="n"/>
-    </row>
-    <row r="30" ht="42" customHeight="1" s="54">
-      <c r="A30" s="62" t="inlineStr">
-        <is>
-          <t>PE14</t>
-        </is>
-      </c>
-      <c r="B30" s="63" t="inlineStr">
-        <is>
-          <t>As a parent, I want to log my child's outside/nonprofit volunteering.</t>
-        </is>
-      </c>
-      <c r="C30" s="63" t="inlineStr">
-        <is>
-          <t>Child card → 'Outside hours' → fill activity, org, date, hours, supervisor → Submit.</t>
-        </is>
-      </c>
-      <c r="D30" s="63" t="inlineStr">
-        <is>
-          <t>External hours submitted for the child and sent for supervisor approval (proof required over 5h).</t>
-        </is>
-      </c>
-      <c r="E30" s="64" t="n"/>
-      <c r="F30" s="64" t="n"/>
-      <c r="G30" s="64" t="n"/>
-      <c r="H30" s="64" t="n"/>
-      <c r="I30" s="64" t="n"/>
-      <c r="J30" s="64" t="n"/>
-    </row>
-    <row r="31" ht="42" customHeight="1" s="54">
-      <c r="A31" s="62" t="inlineStr">
-        <is>
-          <t>PE15</t>
-        </is>
-      </c>
-      <c r="B31" s="63" t="inlineStr">
-        <is>
-          <t>As a parent, I want my child's verified service record.</t>
-        </is>
-      </c>
-      <c r="C31" s="63" t="inlineStr">
-        <is>
-          <t>Child card → 'Service record'.</t>
-        </is>
-      </c>
-      <c r="D31" s="63" t="inlineStr">
-        <is>
-          <t>The child's itemized record opens; Print / Save-as-PDF works.</t>
-        </is>
-      </c>
-      <c r="E31" s="64" t="n"/>
-      <c r="F31" s="64" t="n"/>
-      <c r="G31" s="64" t="n"/>
-      <c r="H31" s="64" t="n"/>
-      <c r="I31" s="64" t="n"/>
-      <c r="J31" s="64" t="n"/>
-    </row>
-    <row r="32" ht="42" customHeight="1" s="54">
-      <c r="A32" s="62" t="inlineStr">
-        <is>
-          <t>PE22</t>
-        </is>
-      </c>
-      <c r="B32" s="63" t="inlineStr">
-        <is>
-          <t>As a parent, I want to be emailed when my child's hours are reviewed.</t>
-        </is>
-      </c>
-      <c r="C32" s="63" t="inlineStr">
-        <is>
-          <t>Have a supervisor approve then reject a submission for a managed child.</t>
-        </is>
-      </c>
-      <c r="D32" s="63" t="inlineStr">
-        <is>
-          <t>You (the guardian) receive the approved / needs-attention emails, even though the child has no email of their own.</t>
-        </is>
-      </c>
-      <c r="E32" s="64" t="n"/>
-      <c r="F32" s="64" t="n"/>
-      <c r="G32" s="64" t="n"/>
-      <c r="H32" s="64" t="n"/>
-      <c r="I32" s="64" t="n"/>
-      <c r="J32" s="64" t="n"/>
-    </row>
-    <row r="33" ht="42" customHeight="1" s="54">
-      <c r="A33" s="62" t="inlineStr">
-        <is>
-          <t>PE23</t>
-        </is>
-      </c>
-      <c r="B33" s="63" t="inlineStr">
-        <is>
-          <t>As a parent, I want to edit my child's details.</t>
-        </is>
-      </c>
-      <c r="C33" s="63" t="inlineStr">
-        <is>
-          <t>Child card → Edit → change name/grade/school → save.</t>
-        </is>
-      </c>
-      <c r="D33" s="63" t="inlineStr">
-        <is>
-          <t>Changes save for the managed child.</t>
-        </is>
-      </c>
-      <c r="E33" s="64" t="n"/>
-      <c r="F33" s="64" t="n"/>
-      <c r="G33" s="64" t="n"/>
-      <c r="H33" s="64" t="n"/>
-      <c r="I33" s="64" t="n"/>
-      <c r="J33" s="64" t="n"/>
-    </row>
-    <row r="34" ht="20" customHeight="1" s="54">
-      <c r="A34" s="61" t="inlineStr">
-        <is>
-          <t>Cross-cutting</t>
-        </is>
-      </c>
-      <c r="B34" s="59" t="n"/>
-      <c r="C34" s="59" t="n"/>
-      <c r="D34" s="59" t="n"/>
-      <c r="E34" s="59" t="n"/>
-      <c r="F34" s="59" t="n"/>
-      <c r="G34" s="59" t="n"/>
-      <c r="H34" s="59" t="n"/>
-      <c r="I34" s="59" t="n"/>
-      <c r="J34" s="59" t="n"/>
-    </row>
-    <row r="35" ht="42" customHeight="1" s="54">
-      <c r="A35" s="62" t="inlineStr">
-        <is>
-          <t>X1</t>
-        </is>
-      </c>
-      <c r="B35" s="63" t="inlineStr">
-        <is>
-          <t>As a phone user, I want a usable mobile layout.</t>
-        </is>
-      </c>
-      <c r="C35" s="63" t="inlineStr">
-        <is>
-          <t>Open at phone width; use the menu drawer.</t>
-        </is>
-      </c>
-      <c r="D35" s="63" t="inlineStr">
-        <is>
-          <t>Layout adapts; drawer opens/closes; no horizontal scroll.</t>
-        </is>
-      </c>
-      <c r="E35" s="64" t="n"/>
-      <c r="F35" s="64" t="n"/>
-      <c r="G35" s="64" t="n"/>
-      <c r="H35" s="64" t="n"/>
-      <c r="I35" s="64" t="n"/>
-      <c r="J35" s="64" t="n"/>
-    </row>
-    <row r="36" ht="42" customHeight="1" s="54">
-      <c r="A36" s="62" t="inlineStr">
-        <is>
-          <t>X2</t>
-        </is>
-      </c>
-      <c r="B36" s="63" t="inlineStr">
-        <is>
-          <t>As a visitor, I want the recycling ribbon on the login page.</t>
-        </is>
-      </c>
-      <c r="C36" s="63" t="inlineStr">
-        <is>
-          <t>Open login signed out.</t>
-        </is>
-      </c>
-      <c r="D36" s="63" t="inlineStr">
-        <is>
-          <t>Green ribbon shows on login.</t>
-        </is>
-      </c>
-      <c r="E36" s="64" t="n"/>
-      <c r="F36" s="64" t="n"/>
-      <c r="G36" s="64" t="n"/>
-      <c r="H36" s="64" t="n"/>
-      <c r="I36" s="64" t="n"/>
-      <c r="J36" s="64" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="A34:J34"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A11:J11"/>
-  </mergeCells>
-  <conditionalFormatting sqref="E4:E36">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="3">
-      <formula>"Pass"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="4">
-      <formula>"Fail"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="5">
-      <formula>"Blocked"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G36">
-    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
-      <formula>"Pass"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4">
-      <formula>"Fail"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" dxfId="5">
-      <formula>"Blocked"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I4:I36">
+  <conditionalFormatting sqref="I4:I38">
     <cfRule type="cellIs" priority="7" operator="equal" dxfId="3">
       <formula>"Pass"</formula>
     </cfRule>
@@ -4248,7 +4330,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E4:E36 G4:G36 I4:I36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E4:E38 G4:G38 I4:I38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pass,Fail,Blocked,Not tested,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6678,7 +6760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="54" min="1" max="1"/>
@@ -6965,7 +7047,7 @@
       </c>
       <c r="D12" s="63" t="inlineStr">
         <is>
-          <t>Dashboard, Reports, Users, Events, Organizations (Help in footer).</t>
+          <t>Dashboard, Reports, Users, Events, Organizations, Award Thresholds, Audit Log (Help in footer).</t>
         </is>
       </c>
       <c r="E12" s="64" t="n"/>
@@ -7007,17 +7089,17 @@
       </c>
       <c r="B14" s="63" t="inlineStr">
         <is>
-          <t>As a Super Admin, I want to create users incl. Supervisor and Super Admin.</t>
+          <t>As a Super Admin, I want to create users of any role.</t>
         </is>
       </c>
       <c r="C14" s="63" t="inlineStr">
         <is>
-          <t>Users → Add user → each role.</t>
+          <t>Users → Add user → open the Role list.</t>
         </is>
       </c>
       <c r="D14" s="63" t="inlineStr">
         <is>
-          <t>Participant/Supervisor/Super Admin options available; account created + invite email.</t>
+          <t>Participant, Supervisor, Admin, and Super Admin options are all available; account created + invite email.</t>
         </is>
       </c>
       <c r="E14" s="64" t="n"/>
@@ -7371,17 +7453,17 @@
       </c>
       <c r="B28" s="63" t="inlineStr">
         <is>
-          <t>As a Super Admin, creating a user pre-fills a temp password and emails an invite.</t>
+          <t>As a Super Admin, creating a user auto-fills a temp password per role and emails an invite.</t>
         </is>
       </c>
       <c r="C28" s="63" t="inlineStr">
         <is>
-          <t>Add user; note the temp password field is pre-filled (Supervisor123!); save.</t>
+          <t>Add user; change the Role and watch the temp password auto-fill (Supervisor→Supervisor123!, Participant→Participant123!, Admin→Admin123!, Super Admin→SuperAdmin123!); save.</t>
         </is>
       </c>
       <c r="D28" s="63" t="inlineStr">
         <is>
-          <t>Account created; the person gets a set-password invite email.</t>
+          <t>Password auto-fills to match the role (and is editable); the browser does NOT autofill your own email/password; account created; the person gets a set-password invite email.</t>
         </is>
       </c>
       <c r="E28" s="64" t="n"/>
@@ -7407,7 +7489,7 @@
       </c>
       <c r="D29" s="63" t="inlineStr">
         <is>
-          <t>The user is stamped to that org (visible/manageable by that org's Admin).</t>
+          <t>The Organization field is shown; the user is stamped to that org. Creating an 'Admin' with an org makes them manage that org.</t>
         </is>
       </c>
       <c r="E29" s="64" t="n"/>
@@ -7415,65 +7497,65 @@
       <c r="G29" s="64" t="n"/>
       <c r="H29" s="64" t="n"/>
     </row>
-    <row r="30" ht="20" customHeight="1" s="54">
-      <c r="A30" s="61" t="inlineStr">
+    <row r="30" ht="42" customHeight="1" s="54">
+      <c r="A30" s="62" t="inlineStr">
+        <is>
+          <t>SA19</t>
+        </is>
+      </c>
+      <c r="B30" s="63" t="inlineStr">
+        <is>
+          <t>As a Super Admin, I want to add a specific participant to an event by email.</t>
+        </is>
+      </c>
+      <c r="C30" s="63" t="inlineStr">
+        <is>
+          <t>Open an event's Roster → Add a participant → enter a participant's account email → Add.</t>
+        </is>
+      </c>
+      <c r="D30" s="63" t="inlineStr">
+        <is>
+          <t>They're registered and emailed ('added to &lt;event&gt;'); it appears in their schedule. A managed elementary child (no email) can't be added this way — a guardian signs them up instead.</t>
+        </is>
+      </c>
+      <c r="E30" s="64" t="n"/>
+      <c r="F30" s="64" t="n"/>
+      <c r="G30" s="64" t="n"/>
+      <c r="H30" s="64" t="n"/>
+    </row>
+    <row r="31" ht="20" customHeight="1" s="54">
+      <c r="A31" s="61" t="inlineStr">
         <is>
           <t>Cross-cutting</t>
         </is>
       </c>
-      <c r="B30" s="59" t="n"/>
-      <c r="C30" s="59" t="n"/>
-      <c r="D30" s="59" t="n"/>
-      <c r="E30" s="59" t="n"/>
-      <c r="F30" s="59" t="n"/>
-      <c r="G30" s="59" t="n"/>
-      <c r="H30" s="59" t="n"/>
-    </row>
-    <row r="31" ht="42" customHeight="1" s="54">
-      <c r="A31" s="62" t="inlineStr">
-        <is>
-          <t>X1</t>
-        </is>
-      </c>
-      <c r="B31" s="63" t="inlineStr">
-        <is>
-          <t>As a phone user, I want a usable mobile layout.</t>
-        </is>
-      </c>
-      <c r="C31" s="63" t="inlineStr">
-        <is>
-          <t>Open at phone width; use the menu drawer.</t>
-        </is>
-      </c>
-      <c r="D31" s="63" t="inlineStr">
-        <is>
-          <t>Layout adapts; drawer opens/closes; no horizontal scroll.</t>
-        </is>
-      </c>
-      <c r="E31" s="64" t="n"/>
-      <c r="F31" s="64" t="n"/>
-      <c r="G31" s="64" t="n"/>
-      <c r="H31" s="64" t="n"/>
+      <c r="B31" s="59" t="n"/>
+      <c r="C31" s="59" t="n"/>
+      <c r="D31" s="59" t="n"/>
+      <c r="E31" s="59" t="n"/>
+      <c r="F31" s="59" t="n"/>
+      <c r="G31" s="59" t="n"/>
+      <c r="H31" s="59" t="n"/>
     </row>
     <row r="32" ht="42" customHeight="1" s="54">
       <c r="A32" s="62" t="inlineStr">
         <is>
-          <t>X2</t>
+          <t>X1</t>
         </is>
       </c>
       <c r="B32" s="63" t="inlineStr">
         <is>
-          <t>As a visitor, I want the recycling ribbon on the login page.</t>
+          <t>As a phone user, I want a usable mobile layout.</t>
         </is>
       </c>
       <c r="C32" s="63" t="inlineStr">
         <is>
-          <t>Open login signed out.</t>
+          <t>Open at phone width; use the menu drawer.</t>
         </is>
       </c>
       <c r="D32" s="63" t="inlineStr">
         <is>
-          <t>Green ribbon shows on login.</t>
+          <t>Layout adapts; drawer opens/closes; no horizontal scroll.</t>
         </is>
       </c>
       <c r="E32" s="64" t="n"/>
@@ -7481,16 +7563,42 @@
       <c r="G32" s="64" t="n"/>
       <c r="H32" s="64" t="n"/>
     </row>
+    <row r="33" ht="42" customHeight="1" s="54">
+      <c r="A33" s="62" t="inlineStr">
+        <is>
+          <t>X2</t>
+        </is>
+      </c>
+      <c r="B33" s="63" t="inlineStr">
+        <is>
+          <t>As a visitor, I want the recycling ribbon on the login page.</t>
+        </is>
+      </c>
+      <c r="C33" s="63" t="inlineStr">
+        <is>
+          <t>Open login signed out.</t>
+        </is>
+      </c>
+      <c r="D33" s="63" t="inlineStr">
+        <is>
+          <t>Green ribbon shows on login.</t>
+        </is>
+      </c>
+      <c r="E33" s="64" t="n"/>
+      <c r="F33" s="64" t="n"/>
+      <c r="G33" s="64" t="n"/>
+      <c r="H33" s="64" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A30:H30"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="A11:H11"/>
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A31:H31"/>
   </mergeCells>
-  <conditionalFormatting sqref="E4:E32">
+  <conditionalFormatting sqref="E4:E33">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="3">
       <formula>"Pass"</formula>
     </cfRule>
@@ -7501,7 +7609,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G32">
+  <conditionalFormatting sqref="G4:G33">
     <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
       <formula>"Pass"</formula>
     </cfRule>
@@ -7513,7 +7621,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E4:E32 G4:G32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E4:E33 G4:G33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pass,Fail,Blocked,Not tested,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7610,7 +7718,7 @@
         </is>
       </c>
       <c r="B5" s="69" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C5" s="69" t="n">
         <v>2</v>
@@ -7643,7 +7751,7 @@
         </is>
       </c>
       <c r="B6" s="69" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C6" s="69" t="n">
         <v>3</v>
@@ -7775,7 +7883,7 @@
         </is>
       </c>
       <c r="B10" s="69" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" s="69" t="n">
         <v>2</v>
